--- a/inputData/Parameters.xlsx
+++ b/inputData/Parameters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sillewiberg/Desktop/Skole/Speciale/Master-Thesis-eVTOL-1/inputData/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B71FD1D-22DA-E547-AC66-2E55276B429E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5EA3A5C-B68C-8444-868C-6B4E1B007986}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="11920" windowHeight="16340" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
   </bookViews>
@@ -156,9 +156,6 @@
     <t>fd_sum</t>
   </si>
   <si>
-    <t>2,1% battery charged per unit time</t>
-  </si>
-  <si>
     <t>rt_{i,j} = 0.2 min/km</t>
   </si>
   <si>
@@ -171,9 +168,6 @@
     <t>penalty for not serving passengergroup</t>
   </si>
   <si>
-    <t>penalty for exceeding bmax</t>
-  </si>
-  <si>
     <t>bmid</t>
   </si>
   <si>
@@ -184,6 +178,12 @@
   </si>
   <si>
     <t>minuts/unit</t>
+  </si>
+  <si>
+    <t>penalty for exceeding bmid</t>
+  </si>
+  <si>
+    <t>2,1% battery charged per min</t>
   </si>
 </sst>
 </file>
@@ -642,13 +642,13 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B4" s="4">
         <v>400</v>
       </c>
       <c r="D4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
@@ -659,7 +659,7 @@
         <v>300</v>
       </c>
       <c r="D5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
@@ -690,10 +690,10 @@
       </c>
       <c r="B8" s="4">
         <f>0.2/B20</f>
-        <v>0.04</v>
+        <v>0.2</v>
       </c>
       <c r="D8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
@@ -720,7 +720,7 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B11" s="4">
         <v>80</v>
@@ -742,13 +742,13 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B13" s="4">
         <v>20</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
@@ -757,10 +757,10 @@
       </c>
       <c r="B14" s="4">
         <f>2.11*B20</f>
-        <v>10.549999999999999</v>
+        <v>2.11</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
@@ -769,7 +769,7 @@
       </c>
       <c r="B15" s="4">
         <f>30/B20</f>
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>12</v>
@@ -781,7 +781,7 @@
       </c>
       <c r="B16" s="4">
         <f>20/B20</f>
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>13</v>
@@ -793,7 +793,7 @@
       </c>
       <c r="B17" s="4">
         <f>120/B20</f>
-        <v>24</v>
+        <v>120</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>14</v>
@@ -801,13 +801,13 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B20" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>

--- a/inputData/Parameters.xlsx
+++ b/inputData/Parameters.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sillewiberg/Desktop/Skole/Speciale/Master-Thesis-eVTOL-1/inputData/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kapta\Documents\DTU\Speciale\GitHubFiles\inputData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B71FD1D-22DA-E547-AC66-2E55276B429E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F6BECB4-727C-4CD8-864E-4DD0622BE9E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="11920" windowHeight="16340" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
   </bookViews>
   <sheets>
     <sheet name="Parameters" sheetId="9" r:id="rId1"/>
@@ -607,18 +607,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B15C49E0-A7B4-734A-8962-DC2A879F4079}">
   <dimension ref="A1:D20"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="22.6640625" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>20</v>
       </c>
@@ -629,7 +629,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -640,7 +640,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>46</v>
       </c>
@@ -651,7 +651,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -662,7 +662,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -673,7 +673,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -684,19 +684,19 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>19</v>
       </c>
       <c r="B8" s="4">
         <f>0.2/B20</f>
-        <v>0.04</v>
+        <v>0.2</v>
       </c>
       <c r="D8" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
         <v>0</v>
       </c>
@@ -707,7 +707,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
         <v>1</v>
       </c>
@@ -718,7 +718,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
         <v>45</v>
       </c>
@@ -729,7 +729,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
         <v>2</v>
       </c>
@@ -740,7 +740,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
         <v>42</v>
       </c>
@@ -751,60 +751,60 @@
         <v>44</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
         <v>3</v>
       </c>
       <c r="B14" s="4">
         <f>2.11*B20</f>
-        <v>10.549999999999999</v>
+        <v>2.11</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
         <v>4</v>
       </c>
       <c r="B15" s="4">
         <f>30/B20</f>
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
         <v>5</v>
       </c>
       <c r="B16" s="4">
         <f>20/B20</f>
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
         <v>6</v>
       </c>
       <c r="B17" s="4">
         <f>120/B20</f>
-        <v>24</v>
+        <v>120</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
         <v>41</v>
       </c>
       <c r="B20" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>48</v>
@@ -819,7 +819,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAF0D5EA-53B5-1240-9D84-6FE223856A18}">
   <dimension ref="A1:N24"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="17.1640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.1640625" bestFit="1" customWidth="1"/>
@@ -828,7 +828,7 @@
     <col min="6" max="6" width="18.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1" s="12" t="s">
         <v>36</v>
       </c>
@@ -867,7 +867,7 @@
       </c>
       <c r="N1" s="6"/>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>1</v>
       </c>
@@ -915,7 +915,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>1</v>
       </c>
@@ -963,7 +963,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>1</v>
       </c>
@@ -1008,7 +1008,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>1</v>
       </c>
@@ -1056,7 +1056,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>2</v>
       </c>
@@ -1095,7 +1095,7 @@
         <v>2489</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>2</v>
       </c>
@@ -1134,7 +1134,7 @@
         <v>2109</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>2</v>
       </c>
@@ -1173,7 +1173,7 @@
         <v>1520</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>3</v>
       </c>
@@ -1211,7 +1211,7 @@
         <v>1915.6666666666665</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>3</v>
       </c>
@@ -1249,7 +1249,7 @@
         <v>1197</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>4</v>
       </c>
@@ -1287,7 +1287,7 @@
         <v>1767</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>1</v>
       </c>
@@ -1303,7 +1303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>2</v>
       </c>
@@ -1319,7 +1319,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>3</v>
       </c>
@@ -1330,7 +1330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>4</v>
       </c>
@@ -1341,7 +1341,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A16">
         <v>5</v>
       </c>
@@ -1353,19 +1353,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="20" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E20" s="1"/>
     </row>
-    <row r="21" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="21" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E21" s="2"/>
     </row>
-    <row r="22" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="22" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E22" s="2"/>
     </row>
-    <row r="23" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="23" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E23" s="1"/>
     </row>
-    <row r="24" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="24" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E24" s="1"/>
     </row>
   </sheetData>

--- a/inputData/Parameters.xlsx
+++ b/inputData/Parameters.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sillewiberg/Desktop/Skole/Speciale/Master-Thesis-eVTOL-1/inputData/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kapta\Documents\DTU\Speciale\GitHubFiles\inputData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5EA3A5C-B68C-8444-868C-6B4E1B007986}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F6BECB4-727C-4CD8-864E-4DD0622BE9E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="11920" windowHeight="16340" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
   </bookViews>
   <sheets>
     <sheet name="Parameters" sheetId="9" r:id="rId1"/>
@@ -156,6 +156,9 @@
     <t>fd_sum</t>
   </si>
   <si>
+    <t>2,1% battery charged per unit time</t>
+  </si>
+  <si>
     <t>rt_{i,j} = 0.2 min/km</t>
   </si>
   <si>
@@ -168,6 +171,9 @@
     <t>penalty for not serving passengergroup</t>
   </si>
   <si>
+    <t>penalty for exceeding bmax</t>
+  </si>
+  <si>
     <t>bmid</t>
   </si>
   <si>
@@ -178,12 +184,6 @@
   </si>
   <si>
     <t>minuts/unit</t>
-  </si>
-  <si>
-    <t>penalty for exceeding bmid</t>
-  </si>
-  <si>
-    <t>2,1% battery charged per min</t>
   </si>
 </sst>
 </file>
@@ -607,18 +607,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B15C49E0-A7B4-734A-8962-DC2A879F4079}">
   <dimension ref="A1:D20"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="22.6640625" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>20</v>
       </c>
@@ -629,7 +629,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -640,18 +640,18 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B4" s="4">
         <v>400</v>
       </c>
       <c r="D4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -659,10 +659,10 @@
         <v>300</v>
       </c>
       <c r="D5" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -673,7 +673,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -684,7 +684,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -693,10 +693,10 @@
         <v>0.2</v>
       </c>
       <c r="D8" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
         <v>0</v>
       </c>
@@ -707,7 +707,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
         <v>1</v>
       </c>
@@ -718,9 +718,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B11" s="4">
         <v>80</v>
@@ -729,7 +729,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
         <v>2</v>
       </c>
@@ -740,18 +740,18 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B13" s="4">
         <v>20</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -760,10 +760,10 @@
         <v>2.11</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
         <v>4</v>
       </c>
@@ -775,7 +775,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
         <v>5</v>
       </c>
@@ -787,7 +787,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
         <v>6</v>
       </c>
@@ -799,15 +799,15 @@
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B20" s="4">
         <v>1</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -819,7 +819,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAF0D5EA-53B5-1240-9D84-6FE223856A18}">
   <dimension ref="A1:N24"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="17.1640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.1640625" bestFit="1" customWidth="1"/>
@@ -828,7 +828,7 @@
     <col min="6" max="6" width="18.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1" s="12" t="s">
         <v>36</v>
       </c>
@@ -867,7 +867,7 @@
       </c>
       <c r="N1" s="6"/>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>1</v>
       </c>
@@ -915,7 +915,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>1</v>
       </c>
@@ -963,7 +963,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>1</v>
       </c>
@@ -1008,7 +1008,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>1</v>
       </c>
@@ -1056,7 +1056,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>2</v>
       </c>
@@ -1095,7 +1095,7 @@
         <v>2489</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>2</v>
       </c>
@@ -1134,7 +1134,7 @@
         <v>2109</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>2</v>
       </c>
@@ -1173,7 +1173,7 @@
         <v>1520</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>3</v>
       </c>
@@ -1211,7 +1211,7 @@
         <v>1915.6666666666665</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>3</v>
       </c>
@@ -1249,7 +1249,7 @@
         <v>1197</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>4</v>
       </c>
@@ -1287,7 +1287,7 @@
         <v>1767</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>1</v>
       </c>
@@ -1303,7 +1303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>2</v>
       </c>
@@ -1319,7 +1319,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>3</v>
       </c>
@@ -1330,7 +1330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>4</v>
       </c>
@@ -1341,7 +1341,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A16">
         <v>5</v>
       </c>
@@ -1353,19 +1353,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="20" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E20" s="1"/>
     </row>
-    <row r="21" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="21" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E21" s="2"/>
     </row>
-    <row r="22" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="22" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E22" s="2"/>
     </row>
-    <row r="23" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="23" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E23" s="1"/>
     </row>
-    <row r="24" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="24" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E24" s="1"/>
     </row>
   </sheetData>

--- a/inputData/Parameters.xlsx
+++ b/inputData/Parameters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kapta\Documents\DTU\Speciale\GitHubFiles\inputData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F6BECB4-727C-4CD8-864E-4DD0622BE9E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E853C988-B6AC-4B4D-A660-2EEFA7D08239}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
   </bookViews>
@@ -656,7 +656,7 @@
         <v>16</v>
       </c>
       <c r="B5" s="4">
-        <v>300</v>
+        <v>3000</v>
       </c>
       <c r="D5" t="s">
         <v>43</v>
@@ -689,8 +689,7 @@
         <v>19</v>
       </c>
       <c r="B8" s="4">
-        <f>0.2/B20</f>
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="D8" t="s">
         <v>40</v>
@@ -734,7 +733,7 @@
         <v>2</v>
       </c>
       <c r="B12" s="4">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="D12" s="3">
         <v>0.1</v>

--- a/inputData/Parameters.xlsx
+++ b/inputData/Parameters.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kapta\Documents\DTU\Speciale\GitHubFiles\inputData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E853C988-B6AC-4B4D-A660-2EEFA7D08239}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A24315D7-801C-405F-93C4-E43B62ED5969}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
   </bookViews>
   <sheets>
     <sheet name="Parameters" sheetId="9" r:id="rId1"/>
@@ -656,7 +656,7 @@
         <v>16</v>
       </c>
       <c r="B5" s="4">
-        <v>3000</v>
+        <v>300</v>
       </c>
       <c r="D5" t="s">
         <v>43</v>

--- a/inputData/Parameters.xlsx
+++ b/inputData/Parameters.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kapta\Documents\DTU\Speciale\GitHubFiles\inputData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sillewiberg/Desktop/Skole/Speciale/Master-Thesis-eVTOL-1/inputData/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F6BECB4-727C-4CD8-864E-4DD0622BE9E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A655786-C4CA-DA4F-925A-95EFB8E73112}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16320" activeTab="1" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
   </bookViews>
   <sheets>
     <sheet name="Parameters" sheetId="9" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="61">
   <si>
     <t>cap_u</t>
   </si>
@@ -184,16 +184,49 @@
   </si>
   <si>
     <t>minuts/unit</t>
+  </si>
+  <si>
+    <t>cord_from</t>
+  </si>
+  <si>
+    <t>cord_to</t>
+  </si>
+  <si>
+    <t>(55.629053, 12.647601)</t>
+  </si>
+  <si>
+    <t>(55.740278, 9.151667)</t>
+  </si>
+  <si>
+    <t>(55.7003, 11.2500)</t>
+  </si>
+  <si>
+    <t>(56.3000, 10.6180)</t>
+  </si>
+  <si>
+    <t>(55.4767, 10.3308)</t>
+  </si>
+  <si>
+    <t>(54.931394, 9.781081)</t>
+  </si>
+  <si>
+    <t>(57.019081, 9.957817)</t>
+  </si>
+  <si>
+    <t>(55.581790, 9.722994)</t>
+  </si>
+  <si>
+    <t>(55.726059, 9.574035)</t>
+  </si>
+  <si>
+    <t>(55.924974, 12.265524)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.0"/>
-  </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -227,6 +260,20 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <strike/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -248,7 +295,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -262,16 +309,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -607,18 +647,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B15C49E0-A7B4-734A-8962-DC2A879F4079}">
   <dimension ref="A1:D20"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="22.6640625" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>20</v>
       </c>
@@ -629,7 +669,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -640,7 +680,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>46</v>
       </c>
@@ -651,7 +691,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -662,7 +702,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -673,7 +713,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -684,7 +724,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -696,7 +736,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>0</v>
       </c>
@@ -707,7 +747,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>1</v>
       </c>
@@ -718,7 +758,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>45</v>
       </c>
@@ -729,7 +769,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>2</v>
       </c>
@@ -740,7 +780,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>42</v>
       </c>
@@ -751,7 +791,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -763,7 +803,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>4</v>
       </c>
@@ -775,7 +815,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>5</v>
       </c>
@@ -787,7 +827,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>6</v>
       </c>
@@ -799,7 +839,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>41</v>
       </c>
@@ -818,558 +858,2152 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAF0D5EA-53B5-1240-9D84-6FE223856A18}">
-  <dimension ref="A1:N24"/>
-  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:P59"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="17.1640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.1640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="17.1640625" customWidth="1"/>
+    <col min="5" max="5" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A1" s="9" t="s">
         <v>36</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>37</v>
       </c>
       <c r="C1" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="F1" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="G1" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="H1" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="I1" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="J1" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="K1" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="L1" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="N1" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="M1" s="7">
+      <c r="O1" s="7">
         <v>0.2</v>
       </c>
-      <c r="N1" s="6"/>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="P1" s="6"/>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" s="8">
         <v>2</v>
       </c>
-      <c r="C2" s="8">
-        <f>(180)</f>
-        <v>180</v>
-      </c>
-      <c r="D2" s="8">
+      <c r="C2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E2">
+        <v>185</v>
+      </c>
+      <c r="F2">
         <v>219</v>
       </c>
-      <c r="E2" s="8">
-        <f t="shared" ref="E2:E11" si="0">$M$1*D2</f>
-        <v>43.800000000000004</v>
-      </c>
-      <c r="F2" s="9">
-        <f>C2/E2</f>
-        <v>4.10958904109589</v>
-      </c>
-      <c r="G2" s="10">
-        <f t="shared" ref="G2:G11" si="1">D2*$M$2</f>
+      <c r="G2">
+        <v>43.8</v>
+      </c>
+      <c r="H2">
+        <v>4.2</v>
+      </c>
+      <c r="I2">
         <v>4161</v>
       </c>
-      <c r="H2" s="11">
-        <f t="shared" ref="H2:H11" si="2">(C2-E2)*$M$3*$M$4</f>
-        <v>1589</v>
-      </c>
-      <c r="I2" s="11">
-        <f>G2+H2</f>
-        <v>5750</v>
-      </c>
-      <c r="J2" s="11">
-        <f t="shared" ref="J2:J11" si="3">MAX($M$2*D2+$M$5,$M$4*$M$3*(C2-E2))</f>
+      <c r="J2">
+        <v>1647</v>
+      </c>
+      <c r="K2">
+        <v>5808</v>
+      </c>
+      <c r="L2">
         <v>4161</v>
       </c>
-      <c r="L2" t="s">
+      <c r="N2" t="s">
         <v>29</v>
       </c>
-      <c r="M2" s="4">
+      <c r="O2" s="4">
         <v>19</v>
       </c>
-      <c r="N2" t="s">
+      <c r="P2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" s="8">
         <v>3</v>
       </c>
-      <c r="C3" s="8">
-        <v>60</v>
-      </c>
-      <c r="D3" s="8">
+      <c r="C3" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E3">
+        <v>82</v>
+      </c>
+      <c r="F3">
         <v>88</v>
       </c>
-      <c r="E3" s="8">
-        <f t="shared" si="0"/>
+      <c r="G3">
         <v>17.600000000000001</v>
       </c>
-      <c r="F3" s="9">
-        <f t="shared" ref="F3:F11" si="4">C3/E3</f>
-        <v>3.4090909090909087</v>
-      </c>
-      <c r="G3" s="10">
-        <f t="shared" si="1"/>
+      <c r="H3">
+        <v>4.7</v>
+      </c>
+      <c r="I3">
         <v>1672</v>
       </c>
-      <c r="H3" s="11">
-        <f t="shared" si="2"/>
-        <v>494.66666666666669</v>
-      </c>
-      <c r="I3" s="11">
-        <f t="shared" ref="I3:I11" si="5">G3+H3</f>
-        <v>2166.6666666666665</v>
-      </c>
-      <c r="J3" s="11">
-        <f t="shared" si="3"/>
+      <c r="J3">
+        <v>751</v>
+      </c>
+      <c r="K3">
+        <v>2423</v>
+      </c>
+      <c r="L3">
         <v>1672</v>
       </c>
-      <c r="L3" t="s">
+      <c r="N3" t="s">
         <v>31</v>
       </c>
-      <c r="M3" s="4">
+      <c r="O3" s="4">
         <f>1000/60</f>
         <v>16.666666666666668</v>
       </c>
-      <c r="N3" t="s">
+      <c r="P3" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>1</v>
       </c>
       <c r="B4" s="8">
         <v>4</v>
       </c>
-      <c r="C4" s="8">
-        <f>200</f>
-        <v>200</v>
-      </c>
-      <c r="D4" s="8">
+      <c r="C4" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E4">
+        <v>228</v>
+      </c>
+      <c r="F4">
         <v>147</v>
       </c>
-      <c r="E4" s="8">
-        <f t="shared" si="0"/>
-        <v>29.400000000000002</v>
-      </c>
-      <c r="F4" s="9">
-        <f t="shared" si="4"/>
-        <v>6.8027210884353737</v>
-      </c>
-      <c r="G4" s="10">
-        <f t="shared" si="1"/>
+      <c r="G4">
+        <v>29.4</v>
+      </c>
+      <c r="H4">
+        <v>7.8</v>
+      </c>
+      <c r="I4">
         <v>2793</v>
       </c>
-      <c r="H4" s="11">
-        <f t="shared" si="2"/>
-        <v>1990.3333333333333</v>
-      </c>
-      <c r="I4" s="11">
-        <f t="shared" si="5"/>
-        <v>4783.333333333333</v>
-      </c>
-      <c r="J4" s="11">
-        <f t="shared" si="3"/>
+      <c r="J4">
+        <v>2317</v>
+      </c>
+      <c r="K4">
+        <v>5110</v>
+      </c>
+      <c r="L4">
         <v>2793</v>
       </c>
-      <c r="L4" t="s">
+      <c r="N4" t="s">
         <v>33</v>
       </c>
-      <c r="M4" s="4">
+      <c r="O4" s="4">
         <v>0.7</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>1</v>
       </c>
       <c r="B5" s="8">
         <v>5</v>
       </c>
-      <c r="C5" s="8">
-        <f>(60+50)</f>
+      <c r="C5" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E5">
+        <v>126</v>
+      </c>
+      <c r="F5">
+        <v>147</v>
+      </c>
+      <c r="G5">
+        <v>29.4</v>
+      </c>
+      <c r="H5">
+        <v>4.3</v>
+      </c>
+      <c r="I5">
+        <v>2793</v>
+      </c>
+      <c r="J5">
+        <v>1127</v>
+      </c>
+      <c r="K5">
+        <v>3920</v>
+      </c>
+      <c r="L5">
+        <v>2793</v>
+      </c>
+      <c r="N5" t="s">
+        <v>34</v>
+      </c>
+      <c r="O5" s="4">
+        <v>0</v>
+      </c>
+      <c r="P5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6" s="8">
+        <v>6</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E6">
+        <v>205</v>
+      </c>
+      <c r="F6">
+        <v>197</v>
+      </c>
+      <c r="G6">
+        <v>39.4</v>
+      </c>
+      <c r="H6">
+        <v>5.2</v>
+      </c>
+      <c r="I6">
+        <v>3743</v>
+      </c>
+      <c r="J6">
+        <v>1932</v>
+      </c>
+      <c r="K6">
+        <v>5675</v>
+      </c>
+      <c r="L6">
+        <v>3743</v>
+      </c>
+      <c r="O6" s="4"/>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>1</v>
+      </c>
+      <c r="B7" s="8">
+        <v>7</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E7">
+        <v>263</v>
+      </c>
+      <c r="F7">
+        <v>227</v>
+      </c>
+      <c r="G7">
+        <v>45.4</v>
+      </c>
+      <c r="H7">
+        <v>5.8</v>
+      </c>
+      <c r="I7">
+        <v>4313</v>
+      </c>
+      <c r="J7">
+        <v>2539</v>
+      </c>
+      <c r="K7">
+        <v>6852</v>
+      </c>
+      <c r="L7">
+        <v>4313</v>
+      </c>
+      <c r="O7" s="4"/>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>1</v>
+      </c>
+      <c r="B8" s="8">
+        <v>8</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E8">
+        <v>143</v>
+      </c>
+      <c r="F8">
+        <v>184</v>
+      </c>
+      <c r="G8">
+        <v>36.799999999999997</v>
+      </c>
+      <c r="H8">
+        <v>3.9</v>
+      </c>
+      <c r="I8">
+        <v>3496</v>
+      </c>
+      <c r="J8">
+        <v>1239</v>
+      </c>
+      <c r="K8">
+        <v>4735</v>
+      </c>
+      <c r="L8">
+        <v>3496</v>
+      </c>
+      <c r="O8" s="4"/>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>1</v>
+      </c>
+      <c r="B9" s="8">
+        <v>9</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E9">
+        <v>155</v>
+      </c>
+      <c r="F9">
+        <v>193</v>
+      </c>
+      <c r="G9">
+        <v>38.6</v>
+      </c>
+      <c r="H9">
+        <v>4</v>
+      </c>
+      <c r="I9">
+        <v>3667</v>
+      </c>
+      <c r="J9">
+        <v>1358</v>
+      </c>
+      <c r="K9">
+        <v>5025</v>
+      </c>
+      <c r="L9">
+        <v>3667</v>
+      </c>
+      <c r="O9" s="4"/>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>1</v>
+      </c>
+      <c r="B10" s="8">
+        <v>10</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E10">
+        <v>42</v>
+      </c>
+      <c r="F10">
+        <v>41</v>
+      </c>
+      <c r="G10">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="H10">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="I10">
+        <v>779</v>
+      </c>
+      <c r="J10">
+        <v>394</v>
+      </c>
+      <c r="K10">
+        <v>1173</v>
+      </c>
+      <c r="L10">
+        <v>779</v>
+      </c>
+      <c r="O10" s="4"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>2</v>
+      </c>
+      <c r="B11" s="8">
+        <v>3</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E11">
+        <v>173</v>
+      </c>
+      <c r="F11">
+        <v>131</v>
+      </c>
+      <c r="G11">
+        <v>26.2</v>
+      </c>
+      <c r="H11">
+        <v>6.6</v>
+      </c>
+      <c r="I11">
+        <v>2489</v>
+      </c>
+      <c r="J11">
+        <v>1713</v>
+      </c>
+      <c r="K11">
+        <v>4202</v>
+      </c>
+      <c r="L11">
+        <v>2489</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>2</v>
+      </c>
+      <c r="B12" s="8">
+        <v>4</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E12">
+        <v>103</v>
+      </c>
+      <c r="F12">
         <v>110</v>
       </c>
-      <c r="D5" s="8">
-        <v>147</v>
-      </c>
-      <c r="E5" s="8">
-        <f t="shared" si="0"/>
-        <v>29.400000000000002</v>
-      </c>
-      <c r="F5" s="9">
-        <f t="shared" si="4"/>
-        <v>3.7414965986394555</v>
-      </c>
-      <c r="G5" s="10">
-        <f t="shared" si="1"/>
-        <v>2793</v>
-      </c>
-      <c r="H5" s="11">
-        <f t="shared" si="2"/>
-        <v>940.33333333333326</v>
-      </c>
-      <c r="I5" s="11">
-        <f t="shared" si="5"/>
-        <v>3733.333333333333</v>
-      </c>
-      <c r="J5" s="11">
-        <f t="shared" si="3"/>
-        <v>2793</v>
-      </c>
-      <c r="L5" t="s">
-        <v>34</v>
-      </c>
-      <c r="M5" s="4">
-        <v>0</v>
-      </c>
-      <c r="N5" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A6">
-        <v>2</v>
-      </c>
-      <c r="B6" s="8">
-        <v>3</v>
-      </c>
-      <c r="C6" s="8">
-        <f>(120+40)</f>
-        <v>160</v>
-      </c>
-      <c r="D6" s="8">
-        <v>131</v>
-      </c>
-      <c r="E6" s="8">
-        <f t="shared" si="0"/>
-        <v>26.200000000000003</v>
-      </c>
-      <c r="F6" s="9">
-        <f t="shared" si="4"/>
-        <v>6.1068702290076331</v>
-      </c>
-      <c r="G6" s="10">
-        <f t="shared" si="1"/>
-        <v>2489</v>
-      </c>
-      <c r="H6" s="11">
-        <f t="shared" si="2"/>
-        <v>1561.0000000000002</v>
-      </c>
-      <c r="I6" s="11">
-        <f t="shared" si="5"/>
-        <v>4050</v>
-      </c>
-      <c r="J6" s="11">
-        <f t="shared" si="3"/>
-        <v>2489</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A7">
-        <v>2</v>
-      </c>
-      <c r="B7" s="8">
-        <v>4</v>
-      </c>
-      <c r="C7" s="8">
-        <f>90</f>
-        <v>90</v>
-      </c>
-      <c r="D7" s="8">
-        <v>111</v>
-      </c>
-      <c r="E7" s="8">
-        <f t="shared" si="0"/>
-        <v>22.200000000000003</v>
-      </c>
-      <c r="F7" s="9">
-        <f t="shared" si="4"/>
-        <v>4.0540540540540535</v>
-      </c>
-      <c r="G7" s="10">
-        <f t="shared" si="1"/>
-        <v>2109</v>
-      </c>
-      <c r="H7" s="11">
-        <f t="shared" si="2"/>
-        <v>791</v>
-      </c>
-      <c r="I7" s="11">
-        <f t="shared" si="5"/>
-        <v>2900</v>
-      </c>
-      <c r="J7" s="11">
-        <f t="shared" si="3"/>
-        <v>2109</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A8">
-        <v>2</v>
-      </c>
-      <c r="B8" s="8">
-        <v>5</v>
-      </c>
-      <c r="C8" s="8">
-        <f>75</f>
-        <v>75</v>
-      </c>
-      <c r="D8" s="8">
-        <v>80</v>
-      </c>
-      <c r="E8" s="8">
-        <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="F8" s="9">
-        <f t="shared" si="4"/>
-        <v>4.6875</v>
-      </c>
-      <c r="G8" s="10">
-        <f t="shared" si="1"/>
-        <v>1520</v>
-      </c>
-      <c r="H8" s="11">
-        <f t="shared" si="2"/>
-        <v>688.33333333333337</v>
-      </c>
-      <c r="I8" s="11">
-        <f t="shared" si="5"/>
-        <v>2208.3333333333335</v>
-      </c>
-      <c r="J8" s="11">
-        <f t="shared" si="3"/>
-        <v>1520</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A9">
-        <v>3</v>
-      </c>
-      <c r="B9" s="8">
-        <v>4</v>
-      </c>
-      <c r="C9" s="8">
-        <v>180</v>
-      </c>
-      <c r="D9" s="8">
-        <v>79</v>
-      </c>
-      <c r="E9" s="8">
-        <f t="shared" si="0"/>
-        <v>15.8</v>
-      </c>
-      <c r="F9" s="9">
-        <f t="shared" si="4"/>
-        <v>11.39240506329114</v>
-      </c>
-      <c r="G9" s="10">
-        <f t="shared" si="1"/>
-        <v>1501</v>
-      </c>
-      <c r="H9" s="11">
-        <f t="shared" si="2"/>
-        <v>1915.6666666666665</v>
-      </c>
-      <c r="I9" s="11">
-        <f t="shared" si="5"/>
-        <v>3416.6666666666665</v>
-      </c>
-      <c r="J9" s="11">
-        <f t="shared" si="3"/>
-        <v>1915.6666666666665</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A10">
-        <v>3</v>
-      </c>
-      <c r="B10" s="8">
-        <v>5</v>
-      </c>
-      <c r="C10" s="8">
-        <v>90</v>
-      </c>
-      <c r="D10" s="8">
-        <v>63</v>
-      </c>
-      <c r="E10" s="8">
-        <f t="shared" si="0"/>
-        <v>12.600000000000001</v>
-      </c>
-      <c r="F10" s="9">
-        <f t="shared" si="4"/>
-        <v>7.1428571428571423</v>
-      </c>
-      <c r="G10" s="10">
-        <f t="shared" si="1"/>
-        <v>1197</v>
-      </c>
-      <c r="H10" s="11">
-        <f t="shared" si="2"/>
-        <v>903.00000000000011</v>
-      </c>
-      <c r="I10" s="11">
-        <f t="shared" si="5"/>
-        <v>2100</v>
-      </c>
-      <c r="J10" s="11">
-        <f t="shared" si="3"/>
-        <v>1197</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A11">
-        <v>4</v>
-      </c>
-      <c r="B11" s="8">
-        <v>5</v>
-      </c>
-      <c r="C11" s="8">
-        <v>120</v>
-      </c>
-      <c r="D11" s="8">
-        <v>93</v>
-      </c>
-      <c r="E11" s="8">
-        <f t="shared" si="0"/>
-        <v>18.600000000000001</v>
-      </c>
-      <c r="F11" s="9">
-        <f t="shared" si="4"/>
-        <v>6.4516129032258061</v>
-      </c>
-      <c r="G11" s="10">
-        <f t="shared" si="1"/>
-        <v>1767</v>
-      </c>
-      <c r="H11" s="11">
-        <f t="shared" si="2"/>
-        <v>1183</v>
-      </c>
-      <c r="I11" s="11">
-        <f t="shared" si="5"/>
-        <v>2950</v>
-      </c>
-      <c r="J11" s="11">
-        <f t="shared" si="3"/>
-        <v>1767</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A12">
-        <v>1</v>
-      </c>
-      <c r="B12" s="8">
-        <v>1</v>
-      </c>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="10"/>
+      <c r="G12">
+        <v>22</v>
+      </c>
+      <c r="H12">
+        <v>4.7</v>
+      </c>
       <c r="I12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.4">
+        <v>2090</v>
+      </c>
+      <c r="J12">
+        <v>945</v>
+      </c>
+      <c r="K12">
+        <v>3035</v>
+      </c>
+      <c r="L12">
+        <v>2090</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>2</v>
       </c>
       <c r="B13" s="8">
+        <v>5</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E13">
+        <v>89</v>
+      </c>
+      <c r="F13">
+        <v>80</v>
+      </c>
+      <c r="G13">
+        <v>16</v>
+      </c>
+      <c r="H13">
+        <v>5.6</v>
+      </c>
+      <c r="I13">
+        <v>1520</v>
+      </c>
+      <c r="J13">
+        <v>852</v>
+      </c>
+      <c r="K13">
+        <v>2372</v>
+      </c>
+      <c r="L13">
+        <v>1520</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A14">
         <v>2</v>
       </c>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="8"/>
-      <c r="I13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A14">
+      <c r="B14" s="8">
+        <v>6</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E14">
+        <v>100</v>
+      </c>
+      <c r="F14">
+        <v>98</v>
+      </c>
+      <c r="G14">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="H14">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="I14">
+        <v>1862</v>
+      </c>
+      <c r="J14">
+        <v>938</v>
+      </c>
+      <c r="K14">
+        <v>2800</v>
+      </c>
+      <c r="L14">
+        <v>1862</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>2</v>
+      </c>
+      <c r="B15" s="8">
+        <v>7</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="E15">
+        <v>138</v>
+      </c>
+      <c r="F15">
+        <v>151</v>
+      </c>
+      <c r="G15">
+        <v>30.2</v>
+      </c>
+      <c r="H15">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="I15">
+        <v>2869</v>
+      </c>
+      <c r="J15">
+        <v>1258</v>
+      </c>
+      <c r="K15">
+        <v>4127</v>
+      </c>
+      <c r="L15">
+        <v>2869</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>2</v>
+      </c>
+      <c r="B16" s="8">
+        <v>8</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E16">
+        <v>55</v>
+      </c>
+      <c r="F16">
+        <v>40</v>
+      </c>
+      <c r="G16">
+        <v>8</v>
+      </c>
+      <c r="H16">
+        <v>6.9</v>
+      </c>
+      <c r="I16">
+        <v>760</v>
+      </c>
+      <c r="J16">
+        <v>548</v>
+      </c>
+      <c r="K16">
+        <v>1308</v>
+      </c>
+      <c r="L16">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>2</v>
+      </c>
+      <c r="B17" s="8">
+        <v>9</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E17">
+        <v>38</v>
+      </c>
+      <c r="F17">
+        <v>26</v>
+      </c>
+      <c r="G17">
+        <v>5.2</v>
+      </c>
+      <c r="H17">
+        <v>7.3</v>
+      </c>
+      <c r="I17">
+        <v>494</v>
+      </c>
+      <c r="J17">
+        <v>383</v>
+      </c>
+      <c r="K17">
+        <v>877</v>
+      </c>
+      <c r="L17">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>2</v>
+      </c>
+      <c r="B18" s="8">
+        <v>10</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E18">
+        <v>205</v>
+      </c>
+      <c r="F18">
+        <v>196</v>
+      </c>
+      <c r="G18">
+        <v>39.200000000000003</v>
+      </c>
+      <c r="H18">
+        <v>5.2</v>
+      </c>
+      <c r="I18">
+        <v>3724</v>
+      </c>
+      <c r="J18">
+        <v>1934</v>
+      </c>
+      <c r="K18">
+        <v>5658</v>
+      </c>
+      <c r="L18">
+        <v>3724</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A19">
         <v>3</v>
       </c>
-      <c r="B14" s="8">
+      <c r="B19" s="8">
+        <v>4</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E19">
+        <v>215</v>
+      </c>
+      <c r="F19">
+        <v>77</v>
+      </c>
+      <c r="G19">
+        <v>15.4</v>
+      </c>
+      <c r="H19">
+        <v>14</v>
+      </c>
+      <c r="I19">
+        <v>1463</v>
+      </c>
+      <c r="J19">
+        <v>2329</v>
+      </c>
+      <c r="K19">
+        <v>3792</v>
+      </c>
+      <c r="L19">
+        <v>2329</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A20">
         <v>3</v>
       </c>
-      <c r="I14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A15">
+      <c r="B20" s="8">
+        <v>5</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E20">
+        <v>113</v>
+      </c>
+      <c r="F20">
+        <v>63</v>
+      </c>
+      <c r="G20">
+        <v>12.6</v>
+      </c>
+      <c r="H20">
+        <v>9</v>
+      </c>
+      <c r="I20">
+        <v>1197</v>
+      </c>
+      <c r="J20">
+        <v>1171</v>
+      </c>
+      <c r="K20">
+        <v>2368</v>
+      </c>
+      <c r="L20">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>3</v>
+      </c>
+      <c r="B21" s="8">
+        <v>6</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E21">
+        <v>192</v>
+      </c>
+      <c r="F21">
+        <v>126</v>
+      </c>
+      <c r="G21">
+        <v>25.2</v>
+      </c>
+      <c r="H21">
+        <v>7.6</v>
+      </c>
+      <c r="I21">
+        <v>2394</v>
+      </c>
+      <c r="J21">
+        <v>1946</v>
+      </c>
+      <c r="K21">
+        <v>4340</v>
+      </c>
+      <c r="L21">
+        <v>2394</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>3</v>
+      </c>
+      <c r="B22" s="8">
+        <v>7</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="E22">
+        <v>250</v>
+      </c>
+      <c r="F22">
+        <v>167</v>
+      </c>
+      <c r="G22">
+        <v>33.4</v>
+      </c>
+      <c r="H22">
+        <v>7.5</v>
+      </c>
+      <c r="I22">
+        <v>3173</v>
+      </c>
+      <c r="J22">
+        <v>2527</v>
+      </c>
+      <c r="K22">
+        <v>5700</v>
+      </c>
+      <c r="L22">
+        <v>3173</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>3</v>
+      </c>
+      <c r="B23" s="8">
+        <v>8</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E23">
+        <v>130</v>
+      </c>
+      <c r="F23">
+        <v>97</v>
+      </c>
+      <c r="G23">
+        <v>19.399999999999999</v>
+      </c>
+      <c r="H23">
+        <v>6.7</v>
+      </c>
+      <c r="I23">
+        <v>1843</v>
+      </c>
+      <c r="J23">
+        <v>1290</v>
+      </c>
+      <c r="K23">
+        <v>3133</v>
+      </c>
+      <c r="L23">
+        <v>1843</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>3</v>
+      </c>
+      <c r="B24" s="8">
+        <v>9</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E24">
+        <v>142</v>
+      </c>
+      <c r="F24">
+        <v>105</v>
+      </c>
+      <c r="G24">
+        <v>21</v>
+      </c>
+      <c r="H24">
+        <v>6.8</v>
+      </c>
+      <c r="I24">
+        <v>1995</v>
+      </c>
+      <c r="J24">
+        <v>1412</v>
+      </c>
+      <c r="K24">
+        <v>3407</v>
+      </c>
+      <c r="L24">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <v>3</v>
+      </c>
+      <c r="B25" s="8">
+        <v>10</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E25">
+        <v>89</v>
+      </c>
+      <c r="F25">
+        <v>68</v>
+      </c>
+      <c r="G25">
+        <v>13.6</v>
+      </c>
+      <c r="H25">
+        <v>6.5</v>
+      </c>
+      <c r="I25">
+        <v>1292</v>
+      </c>
+      <c r="J25">
+        <v>880</v>
+      </c>
+      <c r="K25">
+        <v>2172</v>
+      </c>
+      <c r="L25">
+        <v>1292</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A26">
         <v>4</v>
       </c>
-      <c r="B15" s="8">
+      <c r="B26" s="8">
+        <v>5</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E26">
+        <v>130</v>
+      </c>
+      <c r="F26">
+        <v>93</v>
+      </c>
+      <c r="G26">
+        <v>18.600000000000001</v>
+      </c>
+      <c r="H26">
+        <v>7</v>
+      </c>
+      <c r="I26">
+        <v>1767</v>
+      </c>
+      <c r="J26">
+        <v>1300</v>
+      </c>
+      <c r="K26">
+        <v>3067</v>
+      </c>
+      <c r="L26">
+        <v>1767</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A27">
         <v>4</v>
       </c>
-      <c r="I15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A16">
+      <c r="B27" s="8">
+        <v>6</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E27">
+        <v>149</v>
+      </c>
+      <c r="F27">
+        <v>161</v>
+      </c>
+      <c r="G27">
+        <v>32.200000000000003</v>
+      </c>
+      <c r="H27">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="I27">
+        <v>3059</v>
+      </c>
+      <c r="J27">
+        <v>1363</v>
+      </c>
+      <c r="K27">
+        <v>4422</v>
+      </c>
+      <c r="L27">
+        <v>3059</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <v>4</v>
+      </c>
+      <c r="B28" s="8">
+        <v>7</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D28" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="E28">
+        <v>93</v>
+      </c>
+      <c r="F28">
+        <v>90</v>
+      </c>
+      <c r="G28">
+        <v>18</v>
+      </c>
+      <c r="H28">
+        <v>5.2</v>
+      </c>
+      <c r="I28">
+        <v>1710</v>
+      </c>
+      <c r="J28">
+        <v>875</v>
+      </c>
+      <c r="K28">
+        <v>2585</v>
+      </c>
+      <c r="L28">
+        <v>1710</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>4</v>
+      </c>
+      <c r="B29" s="8">
+        <v>8</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E29">
+        <v>97</v>
+      </c>
+      <c r="F29">
+        <v>97</v>
+      </c>
+      <c r="G29">
+        <v>19.399999999999999</v>
+      </c>
+      <c r="H29">
         <v>5</v>
       </c>
-      <c r="B16" s="8">
+      <c r="I29">
+        <v>1843</v>
+      </c>
+      <c r="J29">
+        <v>905</v>
+      </c>
+      <c r="K29">
+        <v>2748</v>
+      </c>
+      <c r="L29">
+        <v>1843</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <v>4</v>
+      </c>
+      <c r="B30" s="8">
+        <v>9</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E30">
+        <v>76</v>
+      </c>
+      <c r="F30">
+        <v>91</v>
+      </c>
+      <c r="G30">
+        <v>18.2</v>
+      </c>
+      <c r="H30">
+        <v>4.2</v>
+      </c>
+      <c r="I30">
+        <v>1729</v>
+      </c>
+      <c r="J30">
+        <v>674</v>
+      </c>
+      <c r="K30">
+        <v>2403</v>
+      </c>
+      <c r="L30">
+        <v>1729</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <v>4</v>
+      </c>
+      <c r="B31" s="8">
+        <v>10</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E31">
+        <v>246</v>
+      </c>
+      <c r="F31">
+        <v>110</v>
+      </c>
+      <c r="G31">
+        <v>22</v>
+      </c>
+      <c r="H31">
+        <v>11.2</v>
+      </c>
+      <c r="I31">
+        <v>2090</v>
+      </c>
+      <c r="J31">
+        <v>2613</v>
+      </c>
+      <c r="K31">
+        <v>4703</v>
+      </c>
+      <c r="L31">
+        <v>2613</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A32">
         <v>5</v>
       </c>
-      <c r="E16" s="6"/>
-      <c r="I16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="5:5" x14ac:dyDescent="0.4">
-      <c r="E20" s="1"/>
-    </row>
-    <row r="21" spans="5:5" x14ac:dyDescent="0.4">
-      <c r="E21" s="2"/>
-    </row>
-    <row r="22" spans="5:5" x14ac:dyDescent="0.4">
-      <c r="E22" s="2"/>
-    </row>
-    <row r="23" spans="5:5" x14ac:dyDescent="0.4">
-      <c r="E23" s="1"/>
-    </row>
-    <row r="24" spans="5:5" x14ac:dyDescent="0.4">
-      <c r="E24" s="1"/>
+      <c r="B32" s="8">
+        <v>6</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E32">
+        <v>110</v>
+      </c>
+      <c r="F32">
+        <v>70</v>
+      </c>
+      <c r="G32">
+        <v>14</v>
+      </c>
+      <c r="H32">
+        <v>7.9</v>
+      </c>
+      <c r="I32">
+        <v>1330</v>
+      </c>
+      <c r="J32">
+        <v>1120</v>
+      </c>
+      <c r="K32">
+        <v>2450</v>
+      </c>
+      <c r="L32">
+        <v>1330</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A33" s="10">
+        <v>5</v>
+      </c>
+      <c r="B33" s="8">
+        <v>7</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D33" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="E33">
+        <v>168</v>
+      </c>
+      <c r="F33">
+        <v>173</v>
+      </c>
+      <c r="G33">
+        <v>34.6</v>
+      </c>
+      <c r="H33">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="I33">
+        <v>3287</v>
+      </c>
+      <c r="J33">
+        <v>1556</v>
+      </c>
+      <c r="K33">
+        <v>4843</v>
+      </c>
+      <c r="L33">
+        <v>3287</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A34">
+        <v>5</v>
+      </c>
+      <c r="B34" s="8">
+        <v>8</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E34">
+        <v>48</v>
+      </c>
+      <c r="F34">
+        <v>40</v>
+      </c>
+      <c r="G34">
+        <v>8</v>
+      </c>
+      <c r="H34">
+        <v>6</v>
+      </c>
+      <c r="I34">
+        <v>760</v>
+      </c>
+      <c r="J34">
+        <v>467</v>
+      </c>
+      <c r="K34">
+        <v>1227</v>
+      </c>
+      <c r="L34">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A35">
+        <v>5</v>
+      </c>
+      <c r="B35" s="8">
+        <v>9</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E35">
+        <v>60</v>
+      </c>
+      <c r="F35">
+        <v>55</v>
+      </c>
+      <c r="G35">
+        <v>11</v>
+      </c>
+      <c r="H35">
+        <v>5.5</v>
+      </c>
+      <c r="I35">
+        <v>1045</v>
+      </c>
+      <c r="J35">
+        <v>572</v>
+      </c>
+      <c r="K35">
+        <v>1617</v>
+      </c>
+      <c r="L35">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A36">
+        <v>5</v>
+      </c>
+      <c r="B36" s="8">
+        <v>10</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E36">
+        <v>145</v>
+      </c>
+      <c r="F36">
+        <v>131</v>
+      </c>
+      <c r="G36">
+        <v>26.2</v>
+      </c>
+      <c r="H36">
+        <v>5.5</v>
+      </c>
+      <c r="I36">
+        <v>2489</v>
+      </c>
+      <c r="J36">
+        <v>1386</v>
+      </c>
+      <c r="K36">
+        <v>3875</v>
+      </c>
+      <c r="L36">
+        <v>2489</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A37">
+        <v>6</v>
+      </c>
+      <c r="B37" s="8">
+        <v>7</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D37" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="E37">
+        <v>185</v>
+      </c>
+      <c r="F37">
+        <v>232</v>
+      </c>
+      <c r="G37">
+        <v>46.4</v>
+      </c>
+      <c r="H37">
+        <v>4</v>
+      </c>
+      <c r="I37">
+        <v>4408</v>
+      </c>
+      <c r="J37">
+        <v>1617</v>
+      </c>
+      <c r="K37">
+        <v>6025</v>
+      </c>
+      <c r="L37">
+        <v>4408</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A38">
+        <v>6</v>
+      </c>
+      <c r="B38" s="8">
+        <v>8</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E38">
+        <v>77</v>
+      </c>
+      <c r="F38">
+        <v>72</v>
+      </c>
+      <c r="G38">
+        <v>14.4</v>
+      </c>
+      <c r="H38">
+        <v>5.3</v>
+      </c>
+      <c r="I38">
+        <v>1368</v>
+      </c>
+      <c r="J38">
+        <v>730</v>
+      </c>
+      <c r="K38">
+        <v>2098</v>
+      </c>
+      <c r="L38">
+        <v>1368</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A39">
+        <v>6</v>
+      </c>
+      <c r="B39" s="8">
+        <v>9</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E39">
+        <v>78</v>
+      </c>
+      <c r="F39">
+        <v>89</v>
+      </c>
+      <c r="G39">
+        <v>17.8</v>
+      </c>
+      <c r="H39">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="I39">
+        <v>1691</v>
+      </c>
+      <c r="J39">
+        <v>702</v>
+      </c>
+      <c r="K39">
+        <v>2393</v>
+      </c>
+      <c r="L39">
+        <v>1691</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A40">
+        <v>6</v>
+      </c>
+      <c r="B40" s="8">
+        <v>10</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E40">
+        <v>224</v>
+      </c>
+      <c r="F40">
+        <v>192</v>
+      </c>
+      <c r="G40">
+        <v>38.4</v>
+      </c>
+      <c r="H40">
+        <v>5.8</v>
+      </c>
+      <c r="I40">
+        <v>3648</v>
+      </c>
+      <c r="J40">
+        <v>2165</v>
+      </c>
+      <c r="K40">
+        <v>5813</v>
+      </c>
+      <c r="L40">
+        <v>3648</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A41">
+        <v>7</v>
+      </c>
+      <c r="B41" s="8">
+        <v>8</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E41">
+        <v>131</v>
+      </c>
+      <c r="F41">
+        <v>160</v>
+      </c>
+      <c r="G41">
+        <v>32</v>
+      </c>
+      <c r="H41">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="I41">
+        <v>3040</v>
+      </c>
+      <c r="J41">
+        <v>1155</v>
+      </c>
+      <c r="K41">
+        <v>4195</v>
+      </c>
+      <c r="L41">
+        <v>3040</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A42">
+        <v>7</v>
+      </c>
+      <c r="B42" s="8">
+        <v>9</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E42">
+        <v>110</v>
+      </c>
+      <c r="F42">
+        <v>146</v>
+      </c>
+      <c r="G42">
+        <v>29.2</v>
+      </c>
+      <c r="H42">
+        <v>3.8</v>
+      </c>
+      <c r="I42">
+        <v>2774</v>
+      </c>
+      <c r="J42">
+        <v>943</v>
+      </c>
+      <c r="K42">
+        <v>3717</v>
+      </c>
+      <c r="L42">
+        <v>2774</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A43">
+        <v>7</v>
+      </c>
+      <c r="B43" s="8">
+        <v>10</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E43">
+        <v>280</v>
+      </c>
+      <c r="F43">
+        <v>187</v>
+      </c>
+      <c r="G43">
+        <v>37.4</v>
+      </c>
+      <c r="H43">
+        <v>7.5</v>
+      </c>
+      <c r="I43">
+        <v>3553</v>
+      </c>
+      <c r="J43">
+        <v>2830</v>
+      </c>
+      <c r="K43">
+        <v>6383</v>
+      </c>
+      <c r="L43">
+        <v>3553</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A44">
+        <v>8</v>
+      </c>
+      <c r="B44" s="8">
+        <v>9</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E44">
+        <v>26</v>
+      </c>
+      <c r="F44">
+        <v>19</v>
+      </c>
+      <c r="G44">
+        <v>3.8</v>
+      </c>
+      <c r="H44">
+        <v>6.8</v>
+      </c>
+      <c r="I44">
+        <v>361</v>
+      </c>
+      <c r="J44">
+        <v>259</v>
+      </c>
+      <c r="K44">
+        <v>620</v>
+      </c>
+      <c r="L44">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A45">
+        <v>8</v>
+      </c>
+      <c r="B45" s="8">
+        <v>10</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E45">
+        <v>163</v>
+      </c>
+      <c r="F45">
+        <v>164</v>
+      </c>
+      <c r="G45">
+        <v>32.799999999999997</v>
+      </c>
+      <c r="H45">
+        <v>5</v>
+      </c>
+      <c r="I45">
+        <v>3116</v>
+      </c>
+      <c r="J45">
+        <v>1519</v>
+      </c>
+      <c r="K45">
+        <v>4635</v>
+      </c>
+      <c r="L45">
+        <v>3116</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A46">
+        <v>9</v>
+      </c>
+      <c r="B46" s="8">
+        <v>10</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E46">
+        <v>175</v>
+      </c>
+      <c r="F46">
+        <v>170</v>
+      </c>
+      <c r="G46">
+        <v>34</v>
+      </c>
+      <c r="H46">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="I46">
+        <v>3230</v>
+      </c>
+      <c r="J46">
+        <v>1645</v>
+      </c>
+      <c r="K46">
+        <v>4875</v>
+      </c>
+      <c r="L46">
+        <v>3230</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A47">
+        <v>1</v>
+      </c>
+      <c r="B47" s="8">
+        <v>1</v>
+      </c>
+      <c r="C47" s="8"/>
+      <c r="D47" s="8"/>
+      <c r="E47">
+        <v>0</v>
+      </c>
+      <c r="F47">
+        <v>0</v>
+      </c>
+      <c r="G47">
+        <v>0</v>
+      </c>
+      <c r="H47">
+        <v>0</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>0</v>
+      </c>
+      <c r="K47">
+        <v>0</v>
+      </c>
+      <c r="L47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A48">
+        <v>2</v>
+      </c>
+      <c r="B48" s="8">
+        <v>2</v>
+      </c>
+      <c r="C48" s="8"/>
+      <c r="D48" s="8"/>
+      <c r="E48">
+        <v>0</v>
+      </c>
+      <c r="F48">
+        <v>0</v>
+      </c>
+      <c r="G48">
+        <v>0</v>
+      </c>
+      <c r="H48">
+        <v>0</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
+      <c r="K48">
+        <v>0</v>
+      </c>
+      <c r="L48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A49">
+        <v>3</v>
+      </c>
+      <c r="B49" s="8">
+        <v>3</v>
+      </c>
+      <c r="C49" s="8"/>
+      <c r="D49" s="8"/>
+      <c r="E49">
+        <v>0</v>
+      </c>
+      <c r="F49">
+        <v>0</v>
+      </c>
+      <c r="G49">
+        <v>0</v>
+      </c>
+      <c r="H49">
+        <v>0</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>0</v>
+      </c>
+      <c r="K49">
+        <v>0</v>
+      </c>
+      <c r="L49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A50">
+        <v>4</v>
+      </c>
+      <c r="B50" s="8">
+        <v>4</v>
+      </c>
+      <c r="C50" s="8"/>
+      <c r="D50" s="8"/>
+      <c r="E50">
+        <v>0</v>
+      </c>
+      <c r="F50">
+        <v>0</v>
+      </c>
+      <c r="G50">
+        <v>0</v>
+      </c>
+      <c r="H50">
+        <v>0</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>0</v>
+      </c>
+      <c r="K50">
+        <v>0</v>
+      </c>
+      <c r="L50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A51">
+        <v>5</v>
+      </c>
+      <c r="B51" s="8">
+        <v>5</v>
+      </c>
+      <c r="C51" s="8"/>
+      <c r="D51" s="8"/>
+      <c r="E51">
+        <v>0</v>
+      </c>
+      <c r="F51">
+        <v>0</v>
+      </c>
+      <c r="G51">
+        <v>0</v>
+      </c>
+      <c r="H51">
+        <v>0</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>0</v>
+      </c>
+      <c r="K51">
+        <v>0</v>
+      </c>
+      <c r="L51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A52">
+        <v>6</v>
+      </c>
+      <c r="B52" s="8">
+        <v>6</v>
+      </c>
+      <c r="E52">
+        <v>0</v>
+      </c>
+      <c r="F52">
+        <v>0</v>
+      </c>
+      <c r="G52">
+        <v>0</v>
+      </c>
+      <c r="H52">
+        <v>0</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>0</v>
+      </c>
+      <c r="K52">
+        <v>0</v>
+      </c>
+      <c r="L52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A53">
+        <v>7</v>
+      </c>
+      <c r="B53" s="8">
+        <v>7</v>
+      </c>
+      <c r="E53">
+        <v>0</v>
+      </c>
+      <c r="F53">
+        <v>0</v>
+      </c>
+      <c r="G53">
+        <v>0</v>
+      </c>
+      <c r="H53">
+        <v>0</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>0</v>
+      </c>
+      <c r="K53">
+        <v>0</v>
+      </c>
+      <c r="L53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A54">
+        <v>8</v>
+      </c>
+      <c r="B54" s="8">
+        <v>8</v>
+      </c>
+      <c r="E54">
+        <v>0</v>
+      </c>
+      <c r="F54">
+        <v>0</v>
+      </c>
+      <c r="G54">
+        <v>0</v>
+      </c>
+      <c r="H54">
+        <v>0</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>0</v>
+      </c>
+      <c r="K54">
+        <v>0</v>
+      </c>
+      <c r="L54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A55">
+        <v>9</v>
+      </c>
+      <c r="B55" s="8">
+        <v>9</v>
+      </c>
+      <c r="E55">
+        <v>0</v>
+      </c>
+      <c r="F55">
+        <v>0</v>
+      </c>
+      <c r="G55">
+        <v>0</v>
+      </c>
+      <c r="H55">
+        <v>0</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>0</v>
+      </c>
+      <c r="K55">
+        <v>0</v>
+      </c>
+      <c r="L55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A56">
+        <v>10</v>
+      </c>
+      <c r="B56" s="8">
+        <v>10</v>
+      </c>
+      <c r="E56">
+        <v>0</v>
+      </c>
+      <c r="F56">
+        <v>0</v>
+      </c>
+      <c r="G56">
+        <v>0</v>
+      </c>
+      <c r="H56">
+        <v>0</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>0</v>
+      </c>
+      <c r="K56">
+        <v>0</v>
+      </c>
+      <c r="L56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="G57" s="2"/>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="G58" s="1"/>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="G59" s="1"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="G2:G11">
+  <conditionalFormatting sqref="I2:I46">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -1381,7 +3015,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H11">
+  <conditionalFormatting sqref="J2:J46">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -1393,7 +3027,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I11">
+  <conditionalFormatting sqref="K2:K46">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -1405,7 +3039,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J11">
+  <conditionalFormatting sqref="L2:L46">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>

--- a/inputData/Parameters.xlsx
+++ b/inputData/Parameters.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kapta\Documents\DTU\Speciale\GitHubFiles\inputData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A24315D7-801C-405F-93C4-E43B62ED5969}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1764DAD6-3748-4CDE-B441-34E634E8D666}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
   </bookViews>
   <sheets>
     <sheet name="Parameters" sheetId="9" r:id="rId1"/>
@@ -689,7 +689,7 @@
         <v>19</v>
       </c>
       <c r="B8" s="4">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="D8" t="s">
         <v>40</v>
@@ -733,7 +733,7 @@
         <v>2</v>
       </c>
       <c r="B12" s="4">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="D12" s="3">
         <v>0.1</v>

--- a/inputData/Parameters.xlsx
+++ b/inputData/Parameters.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="49">
   <si>
     <t>cap_u</t>
   </si>
@@ -613,13 +613,13 @@
     <col min="2" max="2" width="10.83203125" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:4" dyDescent="0.4">
       <c r="A1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:4" dyDescent="0.4">
+      <c r="A2" t="s" s="1">
         <v>20</v>
       </c>
       <c r="B2" s="4">
@@ -629,7 +629,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:4" dyDescent="0.4">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -640,7 +640,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:4" dyDescent="0.4">
       <c r="A4" t="s">
         <v>46</v>
       </c>
@@ -651,7 +651,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:4" dyDescent="0.4">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -662,7 +662,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:4" dyDescent="0.4">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -673,7 +673,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:4" dyDescent="0.4">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -684,7 +684,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:4" dyDescent="0.4">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -695,7 +695,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:4" dyDescent="0.4">
       <c r="A9" t="s">
         <v>0</v>
       </c>
@@ -706,7 +706,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:4" dyDescent="0.4">
       <c r="A10" t="s">
         <v>1</v>
       </c>
@@ -717,7 +717,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:4" dyDescent="0.4">
       <c r="A11" t="s">
         <v>45</v>
       </c>
@@ -728,7 +728,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:4" dyDescent="0.4">
       <c r="A12" t="s">
         <v>2</v>
       </c>
@@ -739,18 +739,18 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:4" dyDescent="0.4">
       <c r="A13" t="s">
         <v>42</v>
       </c>
       <c r="B13" s="4">
         <v>20</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="D13" t="s" s="3">
         <v>44</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:4" dyDescent="0.4">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -758,11 +758,11 @@
         <f>2.11*B20</f>
         <v>2.11</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" t="s" s="3">
         <v>39</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:4" dyDescent="0.4">
       <c r="A15" t="s">
         <v>4</v>
       </c>
@@ -770,11 +770,11 @@
         <f>30/B20</f>
         <v>30</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="D15" t="s" s="3">
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:4" dyDescent="0.4">
       <c r="A16" t="s">
         <v>5</v>
       </c>
@@ -782,11 +782,11 @@
         <f>20/B20</f>
         <v>20</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="D16" t="s" s="3">
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:4" dyDescent="0.4">
       <c r="A17" t="s">
         <v>6</v>
       </c>
@@ -794,18 +794,18 @@
         <f>120/B20</f>
         <v>120</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="D17" t="s" s="3">
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:4" dyDescent="0.4">
       <c r="A20" t="s">
         <v>41</v>
       </c>
       <c r="B20" s="4">
         <v>1</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="D20" t="s" s="3">
         <v>48</v>
       </c>
     </row>
@@ -827,38 +827,38 @@
     <col min="6" max="6" width="18.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:14" dyDescent="0.4">
+      <c r="A1" t="s" s="12">
         <v>36</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" t="s" s="5">
         <v>37</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" t="s" s="5">
         <v>22</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" t="s" s="5">
         <v>23</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" t="s" s="5">
         <v>24</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" t="s" s="5">
         <v>25</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" t="s" s="5">
         <v>26</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" t="s" s="5">
         <v>27</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" t="s" s="5">
         <v>38</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" t="s" s="5">
         <v>28</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="L1" t="s" s="6">
         <v>19</v>
       </c>
       <c r="M1" s="7">
@@ -866,7 +866,7 @@
       </c>
       <c r="N1" s="6"/>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:14" dyDescent="0.4">
       <c r="A2">
         <v>1</v>
       </c>
@@ -881,7 +881,7 @@
         <v>219</v>
       </c>
       <c r="E2" s="8">
-        <f t="shared" ref="E2:E11" si="0">$M$1*D2</f>
+        <f t="shared" si="0" ref="E2:E11">$M$1*D2</f>
         <v>43.800000000000004</v>
       </c>
       <c r="F2" s="9">
@@ -889,11 +889,11 @@
         <v>4.10958904109589</v>
       </c>
       <c r="G2" s="10">
-        <f t="shared" ref="G2:G11" si="1">D2*$M$2</f>
+        <f t="shared" si="1" ref="G2:G11">D2*$M$2</f>
         <v>4161</v>
       </c>
       <c r="H2" s="11">
-        <f t="shared" ref="H2:H11" si="2">(C2-E2)*$M$3*$M$4</f>
+        <f t="shared" si="2" ref="H2:H11">(C2-E2)*$M$3*$M$4</f>
         <v>1589</v>
       </c>
       <c r="I2" s="11">
@@ -901,7 +901,7 @@
         <v>5750</v>
       </c>
       <c r="J2" s="11">
-        <f t="shared" ref="J2:J11" si="3">MAX($M$2*D2+$M$5,$M$4*$M$3*(C2-E2))</f>
+        <f t="shared" si="3" ref="J2:J11">MAX($M$2*D2+$M$5,$M$4*$M$3*(C2-E2))</f>
         <v>4161</v>
       </c>
       <c r="L2" t="s">
@@ -914,7 +914,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:14" dyDescent="0.4">
       <c r="A3">
         <v>1</v>
       </c>
@@ -932,7 +932,7 @@
         <v>17.600000000000001</v>
       </c>
       <c r="F3" s="9">
-        <f t="shared" ref="F3:F11" si="4">C3/E3</f>
+        <f t="shared" si="4" ref="F3:F11">C3/E3</f>
         <v>3.4090909090909087</v>
       </c>
       <c r="G3" s="10">
@@ -944,7 +944,7 @@
         <v>494.66666666666669</v>
       </c>
       <c r="I3" s="11">
-        <f t="shared" ref="I3:I11" si="5">G3+H3</f>
+        <f t="shared" si="5" ref="I3:I11">G3+H3</f>
         <v>2166.6666666666665</v>
       </c>
       <c r="J3" s="11">
@@ -962,7 +962,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:14" dyDescent="0.4">
       <c r="A4">
         <v>1</v>
       </c>
@@ -1007,7 +1007,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:14" dyDescent="0.4">
       <c r="A5">
         <v>1</v>
       </c>
@@ -1055,7 +1055,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:14" dyDescent="0.4">
       <c r="A6">
         <v>2</v>
       </c>
@@ -1094,7 +1094,7 @@
         <v>2489</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:14" dyDescent="0.4">
       <c r="A7">
         <v>2</v>
       </c>
@@ -1133,7 +1133,7 @@
         <v>2109</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:14" dyDescent="0.4">
       <c r="A8">
         <v>2</v>
       </c>
@@ -1172,7 +1172,7 @@
         <v>1520</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:14" dyDescent="0.4">
       <c r="A9">
         <v>3</v>
       </c>
@@ -1210,7 +1210,7 @@
         <v>1915.6666666666665</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:14" dyDescent="0.4">
       <c r="A10">
         <v>3</v>
       </c>
@@ -1248,7 +1248,7 @@
         <v>1197</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:14" dyDescent="0.4">
       <c r="A11">
         <v>4</v>
       </c>
@@ -1286,7 +1286,7 @@
         <v>1767</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:14" dyDescent="0.4">
       <c r="A12">
         <v>1</v>
       </c>
@@ -1302,7 +1302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:14" dyDescent="0.4">
       <c r="A13">
         <v>2</v>
       </c>
@@ -1318,7 +1318,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:14" dyDescent="0.4">
       <c r="A14">
         <v>3</v>
       </c>
@@ -1329,7 +1329,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:14" dyDescent="0.4">
       <c r="A15">
         <v>4</v>
       </c>
@@ -1340,7 +1340,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:14" dyDescent="0.4">
       <c r="A16">
         <v>5</v>
       </c>
@@ -1352,19 +1352,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="5:5" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:14" dyDescent="0.4">
       <c r="E20" s="1"/>
     </row>
-    <row r="21" spans="5:5" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:14" dyDescent="0.4">
       <c r="E21" s="2"/>
     </row>
-    <row r="22" spans="5:5" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:14" dyDescent="0.4">
       <c r="E22" s="2"/>
     </row>
-    <row r="23" spans="5:5" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:14" dyDescent="0.4">
       <c r="E23" s="1"/>
     </row>
-    <row r="24" spans="5:5" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:14" dyDescent="0.4">
       <c r="E24" s="1"/>
     </row>
   </sheetData>

--- a/inputData/Parameters.xlsx
+++ b/inputData/Parameters.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="61">
   <si>
     <t>cap_u</t>
   </si>
@@ -653,13 +653,13 @@
     <col min="2" max="2" width="10.83203125" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" dyDescent="0.2">
       <c r="A1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:4" dyDescent="0.2">
+      <c r="A2" t="s" s="1">
         <v>20</v>
       </c>
       <c r="B2" s="4">
@@ -669,7 +669,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" dyDescent="0.2">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -680,7 +680,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" dyDescent="0.2">
       <c r="A4" t="s">
         <v>46</v>
       </c>
@@ -691,7 +691,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" dyDescent="0.2">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -702,7 +702,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4" dyDescent="0.2">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -713,7 +713,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4" dyDescent="0.2">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -724,7 +724,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4" dyDescent="0.2">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -736,7 +736,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4" dyDescent="0.2">
       <c r="A9" t="s">
         <v>0</v>
       </c>
@@ -747,7 +747,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4" dyDescent="0.2">
       <c r="A10" t="s">
         <v>1</v>
       </c>
@@ -758,7 +758,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4" dyDescent="0.2">
       <c r="A11" t="s">
         <v>45</v>
       </c>
@@ -769,7 +769,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4" dyDescent="0.2">
       <c r="A12" t="s">
         <v>2</v>
       </c>
@@ -780,18 +780,18 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4" dyDescent="0.2">
       <c r="A13" t="s">
         <v>42</v>
       </c>
       <c r="B13" s="4">
         <v>20</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="D13" t="s" s="3">
         <v>44</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:4" dyDescent="0.2">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -799,11 +799,11 @@
         <f>2.11*B20</f>
         <v>2.11</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" t="s" s="3">
         <v>39</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:4" dyDescent="0.2">
       <c r="A15" t="s">
         <v>4</v>
       </c>
@@ -811,11 +811,11 @@
         <f>30/B20</f>
         <v>30</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="D15" t="s" s="3">
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:4" dyDescent="0.2">
       <c r="A16" t="s">
         <v>5</v>
       </c>
@@ -823,11 +823,11 @@
         <f>20/B20</f>
         <v>20</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="D16" t="s" s="3">
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:4" dyDescent="0.2">
       <c r="A17" t="s">
         <v>6</v>
       </c>
@@ -835,18 +835,18 @@
         <f>120/B20</f>
         <v>120</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="D17" t="s" s="3">
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:4" dyDescent="0.2">
       <c r="A20" t="s">
         <v>41</v>
       </c>
       <c r="B20" s="4">
         <v>1</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="D20" t="s" s="3">
         <v>48</v>
       </c>
     </row>
@@ -869,44 +869,44 @@
     <col min="8" max="8" width="18.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:16" dyDescent="0.2">
+      <c r="A1" t="s" s="9">
         <v>36</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" t="s" s="5">
         <v>37</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" t="s" s="5">
         <v>49</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" t="s" s="5">
         <v>50</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" t="s" s="5">
         <v>22</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" t="s" s="5">
         <v>23</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" t="s" s="5">
         <v>24</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" t="s" s="5">
         <v>25</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" t="s" s="5">
         <v>26</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" t="s" s="5">
         <v>27</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="K1" t="s" s="5">
         <v>38</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="L1" t="s" s="5">
         <v>28</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="N1" t="s" s="6">
         <v>19</v>
       </c>
       <c r="O1" s="7">
@@ -914,24 +914,24 @@
       </c>
       <c r="P1" s="6"/>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:16" dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" s="8">
         <v>2</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" t="s" s="1">
         <v>51</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" t="s" s="2">
         <v>52</v>
       </c>
       <c r="E2">
-        <v>185</v>
+        <v>185.0</v>
       </c>
       <c r="F2">
-        <v>219</v>
+        <v>219.0</v>
       </c>
       <c r="G2">
         <v>43.8</v>
@@ -940,16 +940,16 @@
         <v>4.2</v>
       </c>
       <c r="I2">
-        <v>4161</v>
+        <v>4161.0</v>
       </c>
       <c r="J2">
-        <v>1647</v>
+        <v>1647.0</v>
       </c>
       <c r="K2">
-        <v>5808</v>
+        <v>5808.0</v>
       </c>
       <c r="L2">
-        <v>4161</v>
+        <v>4161.0</v>
       </c>
       <c r="N2" t="s">
         <v>29</v>
@@ -961,42 +961,42 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:16" dyDescent="0.2">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" s="8">
         <v>3</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" t="s" s="1">
         <v>51</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" t="s" s="2">
         <v>53</v>
       </c>
       <c r="E3">
-        <v>82</v>
+        <v>82.0</v>
       </c>
       <c r="F3">
-        <v>88</v>
+        <v>88.0</v>
       </c>
       <c r="G3">
-        <v>17.600000000000001</v>
+        <v>17.6</v>
       </c>
       <c r="H3">
         <v>4.7</v>
       </c>
       <c r="I3">
-        <v>1672</v>
+        <v>1672.0</v>
       </c>
       <c r="J3">
-        <v>751</v>
+        <v>751.0</v>
       </c>
       <c r="K3">
-        <v>2423</v>
+        <v>2423.0</v>
       </c>
       <c r="L3">
-        <v>1672</v>
+        <v>1672.0</v>
       </c>
       <c r="N3" t="s">
         <v>31</v>
@@ -1009,24 +1009,24 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:16" dyDescent="0.2">
       <c r="A4">
         <v>1</v>
       </c>
       <c r="B4" s="8">
         <v>4</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" t="s" s="1">
         <v>51</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" t="s" s="1">
         <v>54</v>
       </c>
       <c r="E4">
-        <v>228</v>
+        <v>228.0</v>
       </c>
       <c r="F4">
-        <v>147</v>
+        <v>147.0</v>
       </c>
       <c r="G4">
         <v>29.4</v>
@@ -1035,16 +1035,16 @@
         <v>7.8</v>
       </c>
       <c r="I4">
-        <v>2793</v>
+        <v>2793.0</v>
       </c>
       <c r="J4">
-        <v>2317</v>
+        <v>2317.0</v>
       </c>
       <c r="K4">
-        <v>5110</v>
+        <v>5110.0</v>
       </c>
       <c r="L4">
-        <v>2793</v>
+        <v>2793.0</v>
       </c>
       <c r="N4" t="s">
         <v>33</v>
@@ -1053,24 +1053,24 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" dyDescent="0.2">
       <c r="A5">
         <v>1</v>
       </c>
       <c r="B5" s="8">
         <v>5</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" t="s" s="1">
         <v>51</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" t="s" s="1">
         <v>55</v>
       </c>
       <c r="E5">
-        <v>126</v>
+        <v>126.0</v>
       </c>
       <c r="F5">
-        <v>147</v>
+        <v>147.0</v>
       </c>
       <c r="G5">
         <v>29.4</v>
@@ -1079,16 +1079,16 @@
         <v>4.3</v>
       </c>
       <c r="I5">
-        <v>2793</v>
+        <v>2793.0</v>
       </c>
       <c r="J5">
-        <v>1127</v>
+        <v>1127.0</v>
       </c>
       <c r="K5">
-        <v>3920</v>
+        <v>3920.0</v>
       </c>
       <c r="L5">
-        <v>2793</v>
+        <v>2793.0</v>
       </c>
       <c r="N5" t="s">
         <v>34</v>
@@ -1100,24 +1100,24 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" dyDescent="0.2">
       <c r="A6">
         <v>1</v>
       </c>
       <c r="B6" s="8">
         <v>6</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" t="s" s="1">
         <v>51</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" t="s" s="1">
         <v>56</v>
       </c>
       <c r="E6">
-        <v>205</v>
+        <v>205.0</v>
       </c>
       <c r="F6">
-        <v>197</v>
+        <v>197.0</v>
       </c>
       <c r="G6">
         <v>39.4</v>
@@ -1126,37 +1126,37 @@
         <v>5.2</v>
       </c>
       <c r="I6">
-        <v>3743</v>
+        <v>3743.0</v>
       </c>
       <c r="J6">
-        <v>1932</v>
+        <v>1932.0</v>
       </c>
       <c r="K6">
-        <v>5675</v>
+        <v>5675.0</v>
       </c>
       <c r="L6">
-        <v>3743</v>
+        <v>3743.0</v>
       </c>
       <c r="O6" s="4"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" dyDescent="0.2">
       <c r="A7">
         <v>1</v>
       </c>
       <c r="B7" s="8">
         <v>7</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" t="s" s="1">
         <v>51</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" t="s" s="1">
         <v>57</v>
       </c>
       <c r="E7">
-        <v>263</v>
+        <v>263.0</v>
       </c>
       <c r="F7">
-        <v>227</v>
+        <v>227.0</v>
       </c>
       <c r="G7">
         <v>45.4</v>
@@ -1165,154 +1165,154 @@
         <v>5.8</v>
       </c>
       <c r="I7">
-        <v>4313</v>
+        <v>4313.0</v>
       </c>
       <c r="J7">
-        <v>2539</v>
+        <v>2539.0</v>
       </c>
       <c r="K7">
-        <v>6852</v>
+        <v>6852.0</v>
       </c>
       <c r="L7">
-        <v>4313</v>
+        <v>4313.0</v>
       </c>
       <c r="O7" s="4"/>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" dyDescent="0.2">
       <c r="A8">
         <v>1</v>
       </c>
       <c r="B8" s="8">
         <v>8</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" t="s" s="1">
         <v>51</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" t="s" s="1">
         <v>58</v>
       </c>
       <c r="E8">
-        <v>143</v>
+        <v>143.0</v>
       </c>
       <c r="F8">
-        <v>184</v>
+        <v>184.0</v>
       </c>
       <c r="G8">
-        <v>36.799999999999997</v>
+        <v>36.8</v>
       </c>
       <c r="H8">
         <v>3.9</v>
       </c>
       <c r="I8">
-        <v>3496</v>
+        <v>3496.0</v>
       </c>
       <c r="J8">
-        <v>1239</v>
+        <v>1239.0</v>
       </c>
       <c r="K8">
-        <v>4735</v>
+        <v>4735.0</v>
       </c>
       <c r="L8">
-        <v>3496</v>
+        <v>3496.0</v>
       </c>
       <c r="O8" s="4"/>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:16" dyDescent="0.2">
       <c r="A9">
         <v>1</v>
       </c>
       <c r="B9" s="8">
         <v>9</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" t="s" s="1">
         <v>51</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" t="s" s="1">
         <v>59</v>
       </c>
       <c r="E9">
-        <v>155</v>
+        <v>155.0</v>
       </c>
       <c r="F9">
-        <v>193</v>
+        <v>193.0</v>
       </c>
       <c r="G9">
         <v>38.6</v>
       </c>
       <c r="H9">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="I9">
-        <v>3667</v>
+        <v>3667.0</v>
       </c>
       <c r="J9">
-        <v>1358</v>
+        <v>1358.0</v>
       </c>
       <c r="K9">
-        <v>5025</v>
+        <v>5025.0</v>
       </c>
       <c r="L9">
-        <v>3667</v>
+        <v>3667.0</v>
       </c>
       <c r="O9" s="4"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:16" dyDescent="0.2">
       <c r="A10">
         <v>1</v>
       </c>
       <c r="B10" s="8">
         <v>10</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" t="s" s="1">
         <v>51</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" t="s" s="1">
         <v>60</v>
       </c>
       <c r="E10">
-        <v>42</v>
+        <v>42.0</v>
       </c>
       <c r="F10">
-        <v>41</v>
+        <v>41.0</v>
       </c>
       <c r="G10">
-        <v>8.1999999999999993</v>
+        <v>8.2</v>
       </c>
       <c r="H10">
-        <v>5.0999999999999996</v>
+        <v>5.1</v>
       </c>
       <c r="I10">
-        <v>779</v>
+        <v>779.0</v>
       </c>
       <c r="J10">
-        <v>394</v>
+        <v>394.0</v>
       </c>
       <c r="K10">
-        <v>1173</v>
+        <v>1173.0</v>
       </c>
       <c r="L10">
-        <v>779</v>
+        <v>779.0</v>
       </c>
       <c r="O10" s="4"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:16" dyDescent="0.2">
       <c r="A11">
         <v>2</v>
       </c>
       <c r="B11" s="8">
         <v>3</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" t="s" s="2">
         <v>52</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" t="s" s="2">
         <v>53</v>
       </c>
       <c r="E11">
-        <v>173</v>
+        <v>173.0</v>
       </c>
       <c r="F11">
-        <v>131</v>
+        <v>131.0</v>
       </c>
       <c r="G11">
         <v>26.2</v>
@@ -1321,226 +1321,226 @@
         <v>6.6</v>
       </c>
       <c r="I11">
-        <v>2489</v>
+        <v>2489.0</v>
       </c>
       <c r="J11">
-        <v>1713</v>
+        <v>1713.0</v>
       </c>
       <c r="K11">
-        <v>4202</v>
+        <v>4202.0</v>
       </c>
       <c r="L11">
-        <v>2489</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+        <v>2489.0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" dyDescent="0.2">
       <c r="A12">
         <v>2</v>
       </c>
       <c r="B12" s="8">
         <v>4</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" t="s" s="2">
         <v>52</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D12" t="s" s="1">
         <v>54</v>
       </c>
       <c r="E12">
-        <v>103</v>
+        <v>103.0</v>
       </c>
       <c r="F12">
-        <v>110</v>
+        <v>110.0</v>
       </c>
       <c r="G12">
-        <v>22</v>
+        <v>22.0</v>
       </c>
       <c r="H12">
         <v>4.7</v>
       </c>
       <c r="I12">
-        <v>2090</v>
+        <v>2090.0</v>
       </c>
       <c r="J12">
-        <v>945</v>
+        <v>945.0</v>
       </c>
       <c r="K12">
-        <v>3035</v>
+        <v>3035.0</v>
       </c>
       <c r="L12">
-        <v>2090</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+        <v>2090.0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" dyDescent="0.2">
       <c r="A13">
         <v>2</v>
       </c>
       <c r="B13" s="8">
         <v>5</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" t="s" s="2">
         <v>52</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D13" t="s" s="1">
         <v>55</v>
       </c>
       <c r="E13">
-        <v>89</v>
+        <v>89.0</v>
       </c>
       <c r="F13">
-        <v>80</v>
+        <v>80.0</v>
       </c>
       <c r="G13">
-        <v>16</v>
+        <v>16.0</v>
       </c>
       <c r="H13">
         <v>5.6</v>
       </c>
       <c r="I13">
-        <v>1520</v>
+        <v>1520.0</v>
       </c>
       <c r="J13">
-        <v>852</v>
+        <v>852.0</v>
       </c>
       <c r="K13">
-        <v>2372</v>
+        <v>2372.0</v>
       </c>
       <c r="L13">
-        <v>1520</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+        <v>1520.0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" dyDescent="0.2">
       <c r="A14">
         <v>2</v>
       </c>
       <c r="B14" s="8">
         <v>6</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" t="s" s="2">
         <v>52</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="D14" t="s" s="1">
         <v>56</v>
       </c>
       <c r="E14">
-        <v>100</v>
+        <v>100.0</v>
       </c>
       <c r="F14">
-        <v>98</v>
+        <v>98.0</v>
       </c>
       <c r="G14">
-        <v>19.600000000000001</v>
+        <v>19.6</v>
       </c>
       <c r="H14">
-        <v>5.0999999999999996</v>
+        <v>5.1</v>
       </c>
       <c r="I14">
-        <v>1862</v>
+        <v>1862.0</v>
       </c>
       <c r="J14">
-        <v>938</v>
+        <v>938.0</v>
       </c>
       <c r="K14">
-        <v>2800</v>
+        <v>2800.0</v>
       </c>
       <c r="L14">
-        <v>1862</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+        <v>1862.0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" dyDescent="0.2">
       <c r="A15">
         <v>2</v>
       </c>
       <c r="B15" s="8">
         <v>7</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" t="s" s="2">
         <v>52</v>
       </c>
-      <c r="D15" s="11" t="s">
+      <c r="D15" t="s" s="11">
         <v>57</v>
       </c>
       <c r="E15">
-        <v>138</v>
+        <v>138.0</v>
       </c>
       <c r="F15">
-        <v>151</v>
+        <v>151.0</v>
       </c>
       <c r="G15">
         <v>30.2</v>
       </c>
       <c r="H15">
-        <v>4.5999999999999996</v>
+        <v>4.6</v>
       </c>
       <c r="I15">
-        <v>2869</v>
+        <v>2869.0</v>
       </c>
       <c r="J15">
-        <v>1258</v>
+        <v>1258.0</v>
       </c>
       <c r="K15">
-        <v>4127</v>
+        <v>4127.0</v>
       </c>
       <c r="L15">
-        <v>2869</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+        <v>2869.0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" dyDescent="0.2">
       <c r="A16">
         <v>2</v>
       </c>
       <c r="B16" s="8">
         <v>8</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" t="s" s="2">
         <v>52</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="D16" t="s" s="1">
         <v>58</v>
       </c>
       <c r="E16">
-        <v>55</v>
+        <v>55.0</v>
       </c>
       <c r="F16">
-        <v>40</v>
+        <v>40.0</v>
       </c>
       <c r="G16">
-        <v>8</v>
+        <v>8.0</v>
       </c>
       <c r="H16">
         <v>6.9</v>
       </c>
       <c r="I16">
-        <v>760</v>
+        <v>760.0</v>
       </c>
       <c r="J16">
-        <v>548</v>
+        <v>548.0</v>
       </c>
       <c r="K16">
-        <v>1308</v>
+        <v>1308.0</v>
       </c>
       <c r="L16">
-        <v>760</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
+        <v>760.0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" dyDescent="0.2">
       <c r="A17">
         <v>2</v>
       </c>
       <c r="B17" s="8">
         <v>9</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" t="s" s="2">
         <v>52</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="D17" t="s" s="1">
         <v>59</v>
       </c>
       <c r="E17">
-        <v>38</v>
+        <v>38.0</v>
       </c>
       <c r="F17">
-        <v>26</v>
+        <v>26.0</v>
       </c>
       <c r="G17">
         <v>5.2</v>
@@ -1549,150 +1549,150 @@
         <v>7.3</v>
       </c>
       <c r="I17">
-        <v>494</v>
+        <v>494.0</v>
       </c>
       <c r="J17">
-        <v>383</v>
+        <v>383.0</v>
       </c>
       <c r="K17">
-        <v>877</v>
+        <v>877.0</v>
       </c>
       <c r="L17">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
+        <v>494.0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" dyDescent="0.2">
       <c r="A18">
         <v>2</v>
       </c>
       <c r="B18" s="8">
         <v>10</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" t="s" s="2">
         <v>52</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="D18" t="s" s="1">
         <v>60</v>
       </c>
       <c r="E18">
-        <v>205</v>
+        <v>205.0</v>
       </c>
       <c r="F18">
-        <v>196</v>
+        <v>196.0</v>
       </c>
       <c r="G18">
-        <v>39.200000000000003</v>
+        <v>39.2</v>
       </c>
       <c r="H18">
         <v>5.2</v>
       </c>
       <c r="I18">
-        <v>3724</v>
+        <v>3724.0</v>
       </c>
       <c r="J18">
-        <v>1934</v>
+        <v>1934.0</v>
       </c>
       <c r="K18">
-        <v>5658</v>
+        <v>5658.0</v>
       </c>
       <c r="L18">
-        <v>3724</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
+        <v>3724.0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" dyDescent="0.2">
       <c r="A19">
         <v>3</v>
       </c>
       <c r="B19" s="8">
         <v>4</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" t="s" s="2">
         <v>53</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="D19" t="s" s="1">
         <v>54</v>
       </c>
       <c r="E19">
-        <v>215</v>
+        <v>215.0</v>
       </c>
       <c r="F19">
-        <v>77</v>
+        <v>77.0</v>
       </c>
       <c r="G19">
         <v>15.4</v>
       </c>
       <c r="H19">
-        <v>14</v>
+        <v>14.0</v>
       </c>
       <c r="I19">
-        <v>1463</v>
+        <v>1463.0</v>
       </c>
       <c r="J19">
-        <v>2329</v>
+        <v>2329.0</v>
       </c>
       <c r="K19">
-        <v>3792</v>
+        <v>3792.0</v>
       </c>
       <c r="L19">
-        <v>2329</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
+        <v>2329.0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" dyDescent="0.2">
       <c r="A20">
         <v>3</v>
       </c>
       <c r="B20" s="8">
         <v>5</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C20" t="s" s="2">
         <v>53</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="D20" t="s" s="1">
         <v>55</v>
       </c>
       <c r="E20">
-        <v>113</v>
+        <v>113.0</v>
       </c>
       <c r="F20">
-        <v>63</v>
+        <v>63.0</v>
       </c>
       <c r="G20">
         <v>12.6</v>
       </c>
       <c r="H20">
-        <v>9</v>
+        <v>9.0</v>
       </c>
       <c r="I20">
-        <v>1197</v>
+        <v>1197.0</v>
       </c>
       <c r="J20">
-        <v>1171</v>
+        <v>1171.0</v>
       </c>
       <c r="K20">
-        <v>2368</v>
+        <v>2368.0</v>
       </c>
       <c r="L20">
-        <v>1197</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
+        <v>1197.0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" dyDescent="0.2">
       <c r="A21">
         <v>3</v>
       </c>
       <c r="B21" s="8">
         <v>6</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C21" t="s" s="2">
         <v>53</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="D21" t="s" s="1">
         <v>56</v>
       </c>
       <c r="E21">
-        <v>192</v>
+        <v>192.0</v>
       </c>
       <c r="F21">
-        <v>126</v>
+        <v>126.0</v>
       </c>
       <c r="G21">
         <v>25.2</v>
@@ -1701,36 +1701,36 @@
         <v>7.6</v>
       </c>
       <c r="I21">
-        <v>2394</v>
+        <v>2394.0</v>
       </c>
       <c r="J21">
-        <v>1946</v>
+        <v>1946.0</v>
       </c>
       <c r="K21">
-        <v>4340</v>
+        <v>4340.0</v>
       </c>
       <c r="L21">
-        <v>2394</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
+        <v>2394.0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" dyDescent="0.2">
       <c r="A22">
         <v>3</v>
       </c>
       <c r="B22" s="8">
         <v>7</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C22" t="s" s="2">
         <v>53</v>
       </c>
-      <c r="D22" s="11" t="s">
+      <c r="D22" t="s" s="11">
         <v>57</v>
       </c>
       <c r="E22">
-        <v>250</v>
+        <v>250.0</v>
       </c>
       <c r="F22">
-        <v>167</v>
+        <v>167.0</v>
       </c>
       <c r="G22">
         <v>33.4</v>
@@ -1739,112 +1739,112 @@
         <v>7.5</v>
       </c>
       <c r="I22">
-        <v>3173</v>
+        <v>3173.0</v>
       </c>
       <c r="J22">
-        <v>2527</v>
+        <v>2527.0</v>
       </c>
       <c r="K22">
-        <v>5700</v>
+        <v>5700.0</v>
       </c>
       <c r="L22">
-        <v>3173</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
+        <v>3173.0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" dyDescent="0.2">
       <c r="A23">
         <v>3</v>
       </c>
       <c r="B23" s="8">
         <v>8</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C23" t="s" s="2">
         <v>53</v>
       </c>
-      <c r="D23" s="1" t="s">
+      <c r="D23" t="s" s="1">
         <v>58</v>
       </c>
       <c r="E23">
-        <v>130</v>
+        <v>130.0</v>
       </c>
       <c r="F23">
-        <v>97</v>
+        <v>97.0</v>
       </c>
       <c r="G23">
-        <v>19.399999999999999</v>
+        <v>19.4</v>
       </c>
       <c r="H23">
         <v>6.7</v>
       </c>
       <c r="I23">
-        <v>1843</v>
+        <v>1843.0</v>
       </c>
       <c r="J23">
-        <v>1290</v>
+        <v>1290.0</v>
       </c>
       <c r="K23">
-        <v>3133</v>
+        <v>3133.0</v>
       </c>
       <c r="L23">
-        <v>1843</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
+        <v>1843.0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" dyDescent="0.2">
       <c r="A24">
         <v>3</v>
       </c>
       <c r="B24" s="8">
         <v>9</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C24" t="s" s="2">
         <v>53</v>
       </c>
-      <c r="D24" s="1" t="s">
+      <c r="D24" t="s" s="1">
         <v>59</v>
       </c>
       <c r="E24">
-        <v>142</v>
+        <v>142.0</v>
       </c>
       <c r="F24">
-        <v>105</v>
+        <v>105.0</v>
       </c>
       <c r="G24">
-        <v>21</v>
+        <v>21.0</v>
       </c>
       <c r="H24">
         <v>6.8</v>
       </c>
       <c r="I24">
-        <v>1995</v>
+        <v>1995.0</v>
       </c>
       <c r="J24">
-        <v>1412</v>
+        <v>1412.0</v>
       </c>
       <c r="K24">
-        <v>3407</v>
+        <v>3407.0</v>
       </c>
       <c r="L24">
-        <v>1995</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
+        <v>1995.0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" dyDescent="0.2">
       <c r="A25">
         <v>3</v>
       </c>
       <c r="B25" s="8">
         <v>10</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C25" t="s" s="2">
         <v>53</v>
       </c>
-      <c r="D25" s="1" t="s">
+      <c r="D25" t="s" s="1">
         <v>60</v>
       </c>
       <c r="E25">
-        <v>89</v>
+        <v>89.0</v>
       </c>
       <c r="F25">
-        <v>68</v>
+        <v>68.0</v>
       </c>
       <c r="G25">
         <v>13.6</v>
@@ -1853,188 +1853,188 @@
         <v>6.5</v>
       </c>
       <c r="I25">
-        <v>1292</v>
+        <v>1292.0</v>
       </c>
       <c r="J25">
-        <v>880</v>
+        <v>880.0</v>
       </c>
       <c r="K25">
-        <v>2172</v>
+        <v>2172.0</v>
       </c>
       <c r="L25">
-        <v>1292</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
+        <v>1292.0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" dyDescent="0.2">
       <c r="A26">
         <v>4</v>
       </c>
       <c r="B26" s="8">
         <v>5</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="C26" t="s" s="1">
         <v>54</v>
       </c>
-      <c r="D26" s="1" t="s">
+      <c r="D26" t="s" s="1">
         <v>55</v>
       </c>
       <c r="E26">
-        <v>130</v>
+        <v>130.0</v>
       </c>
       <c r="F26">
-        <v>93</v>
+        <v>93.0</v>
       </c>
       <c r="G26">
-        <v>18.600000000000001</v>
+        <v>18.6</v>
       </c>
       <c r="H26">
-        <v>7</v>
+        <v>7.0</v>
       </c>
       <c r="I26">
-        <v>1767</v>
+        <v>1767.0</v>
       </c>
       <c r="J26">
-        <v>1300</v>
+        <v>1300.0</v>
       </c>
       <c r="K26">
-        <v>3067</v>
+        <v>3067.0</v>
       </c>
       <c r="L26">
-        <v>1767</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
+        <v>1767.0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" dyDescent="0.2">
       <c r="A27">
         <v>4</v>
       </c>
       <c r="B27" s="8">
         <v>6</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="C27" t="s" s="1">
         <v>54</v>
       </c>
-      <c r="D27" s="1" t="s">
+      <c r="D27" t="s" s="1">
         <v>56</v>
       </c>
       <c r="E27">
-        <v>149</v>
+        <v>149.0</v>
       </c>
       <c r="F27">
-        <v>161</v>
+        <v>161.0</v>
       </c>
       <c r="G27">
-        <v>32.200000000000003</v>
+        <v>32.2</v>
       </c>
       <c r="H27">
-        <v>4.5999999999999996</v>
+        <v>4.6</v>
       </c>
       <c r="I27">
-        <v>3059</v>
+        <v>3059.0</v>
       </c>
       <c r="J27">
-        <v>1363</v>
+        <v>1363.0</v>
       </c>
       <c r="K27">
-        <v>4422</v>
+        <v>4422.0</v>
       </c>
       <c r="L27">
-        <v>3059</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
+        <v>3059.0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" dyDescent="0.2">
       <c r="A28">
         <v>4</v>
       </c>
       <c r="B28" s="8">
         <v>7</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="C28" t="s" s="1">
         <v>54</v>
       </c>
-      <c r="D28" s="11" t="s">
+      <c r="D28" t="s" s="11">
         <v>57</v>
       </c>
       <c r="E28">
-        <v>93</v>
+        <v>93.0</v>
       </c>
       <c r="F28">
-        <v>90</v>
+        <v>90.0</v>
       </c>
       <c r="G28">
-        <v>18</v>
+        <v>18.0</v>
       </c>
       <c r="H28">
         <v>5.2</v>
       </c>
       <c r="I28">
-        <v>1710</v>
+        <v>1710.0</v>
       </c>
       <c r="J28">
-        <v>875</v>
+        <v>875.0</v>
       </c>
       <c r="K28">
-        <v>2585</v>
+        <v>2585.0</v>
       </c>
       <c r="L28">
-        <v>1710</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
+        <v>1710.0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" dyDescent="0.2">
       <c r="A29">
         <v>4</v>
       </c>
       <c r="B29" s="8">
         <v>8</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="C29" t="s" s="1">
         <v>54</v>
       </c>
-      <c r="D29" s="1" t="s">
+      <c r="D29" t="s" s="1">
         <v>58</v>
       </c>
       <c r="E29">
-        <v>97</v>
+        <v>97.0</v>
       </c>
       <c r="F29">
-        <v>97</v>
+        <v>97.0</v>
       </c>
       <c r="G29">
-        <v>19.399999999999999</v>
+        <v>19.4</v>
       </c>
       <c r="H29">
-        <v>5</v>
+        <v>5.0</v>
       </c>
       <c r="I29">
-        <v>1843</v>
+        <v>1843.0</v>
       </c>
       <c r="J29">
-        <v>905</v>
+        <v>905.0</v>
       </c>
       <c r="K29">
-        <v>2748</v>
+        <v>2748.0</v>
       </c>
       <c r="L29">
-        <v>1843</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
+        <v>1843.0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" dyDescent="0.2">
       <c r="A30">
         <v>4</v>
       </c>
       <c r="B30" s="8">
         <v>9</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="C30" t="s" s="1">
         <v>54</v>
       </c>
-      <c r="D30" s="1" t="s">
+      <c r="D30" t="s" s="1">
         <v>59</v>
       </c>
       <c r="E30">
-        <v>76</v>
+        <v>76.0</v>
       </c>
       <c r="F30">
-        <v>91</v>
+        <v>91.0</v>
       </c>
       <c r="G30">
         <v>18.2</v>
@@ -2043,226 +2043,226 @@
         <v>4.2</v>
       </c>
       <c r="I30">
-        <v>1729</v>
+        <v>1729.0</v>
       </c>
       <c r="J30">
-        <v>674</v>
+        <v>674.0</v>
       </c>
       <c r="K30">
-        <v>2403</v>
+        <v>2403.0</v>
       </c>
       <c r="L30">
-        <v>1729</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
+        <v>1729.0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" dyDescent="0.2">
       <c r="A31">
         <v>4</v>
       </c>
       <c r="B31" s="8">
         <v>10</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C31" t="s" s="1">
         <v>54</v>
       </c>
-      <c r="D31" s="1" t="s">
+      <c r="D31" t="s" s="1">
         <v>60</v>
       </c>
       <c r="E31">
-        <v>246</v>
+        <v>246.0</v>
       </c>
       <c r="F31">
-        <v>110</v>
+        <v>110.0</v>
       </c>
       <c r="G31">
-        <v>22</v>
+        <v>22.0</v>
       </c>
       <c r="H31">
         <v>11.2</v>
       </c>
       <c r="I31">
-        <v>2090</v>
+        <v>2090.0</v>
       </c>
       <c r="J31">
-        <v>2613</v>
+        <v>2613.0</v>
       </c>
       <c r="K31">
-        <v>4703</v>
+        <v>4703.0</v>
       </c>
       <c r="L31">
-        <v>2613</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
+        <v>2613.0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" dyDescent="0.2">
       <c r="A32">
         <v>5</v>
       </c>
       <c r="B32" s="8">
         <v>6</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="C32" t="s" s="1">
         <v>55</v>
       </c>
-      <c r="D32" s="1" t="s">
+      <c r="D32" t="s" s="1">
         <v>56</v>
       </c>
       <c r="E32">
-        <v>110</v>
+        <v>110.0</v>
       </c>
       <c r="F32">
-        <v>70</v>
+        <v>70.0</v>
       </c>
       <c r="G32">
-        <v>14</v>
+        <v>14.0</v>
       </c>
       <c r="H32">
         <v>7.9</v>
       </c>
       <c r="I32">
-        <v>1330</v>
+        <v>1330.0</v>
       </c>
       <c r="J32">
-        <v>1120</v>
+        <v>1120.0</v>
       </c>
       <c r="K32">
-        <v>2450</v>
+        <v>2450.0</v>
       </c>
       <c r="L32">
-        <v>1330</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
+        <v>1330.0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" dyDescent="0.2">
       <c r="A33" s="10">
         <v>5</v>
       </c>
       <c r="B33" s="8">
         <v>7</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C33" t="s" s="1">
         <v>55</v>
       </c>
-      <c r="D33" s="11" t="s">
+      <c r="D33" t="s" s="11">
         <v>57</v>
       </c>
       <c r="E33">
-        <v>168</v>
+        <v>168.0</v>
       </c>
       <c r="F33">
-        <v>173</v>
+        <v>173.0</v>
       </c>
       <c r="G33">
         <v>34.6</v>
       </c>
       <c r="H33">
-        <v>4.9000000000000004</v>
+        <v>4.9</v>
       </c>
       <c r="I33">
-        <v>3287</v>
+        <v>3287.0</v>
       </c>
       <c r="J33">
-        <v>1556</v>
+        <v>1556.0</v>
       </c>
       <c r="K33">
-        <v>4843</v>
+        <v>4843.0</v>
       </c>
       <c r="L33">
-        <v>3287</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
+        <v>3287.0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" dyDescent="0.2">
       <c r="A34">
         <v>5</v>
       </c>
       <c r="B34" s="8">
         <v>8</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="C34" t="s" s="1">
         <v>55</v>
       </c>
-      <c r="D34" s="1" t="s">
+      <c r="D34" t="s" s="1">
         <v>58</v>
       </c>
       <c r="E34">
-        <v>48</v>
+        <v>48.0</v>
       </c>
       <c r="F34">
-        <v>40</v>
+        <v>40.0</v>
       </c>
       <c r="G34">
-        <v>8</v>
+        <v>8.0</v>
       </c>
       <c r="H34">
-        <v>6</v>
+        <v>6.0</v>
       </c>
       <c r="I34">
-        <v>760</v>
+        <v>760.0</v>
       </c>
       <c r="J34">
-        <v>467</v>
+        <v>467.0</v>
       </c>
       <c r="K34">
-        <v>1227</v>
+        <v>1227.0</v>
       </c>
       <c r="L34">
-        <v>760</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
+        <v>760.0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" dyDescent="0.2">
       <c r="A35">
         <v>5</v>
       </c>
       <c r="B35" s="8">
         <v>9</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="C35" t="s" s="1">
         <v>55</v>
       </c>
-      <c r="D35" s="1" t="s">
+      <c r="D35" t="s" s="1">
         <v>59</v>
       </c>
       <c r="E35">
-        <v>60</v>
+        <v>60.0</v>
       </c>
       <c r="F35">
-        <v>55</v>
+        <v>55.0</v>
       </c>
       <c r="G35">
-        <v>11</v>
+        <v>11.0</v>
       </c>
       <c r="H35">
         <v>5.5</v>
       </c>
       <c r="I35">
-        <v>1045</v>
+        <v>1045.0</v>
       </c>
       <c r="J35">
-        <v>572</v>
+        <v>572.0</v>
       </c>
       <c r="K35">
-        <v>1617</v>
+        <v>1617.0</v>
       </c>
       <c r="L35">
-        <v>1045</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
+        <v>1045.0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" dyDescent="0.2">
       <c r="A36">
         <v>5</v>
       </c>
       <c r="B36" s="8">
         <v>10</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="C36" t="s" s="1">
         <v>55</v>
       </c>
-      <c r="D36" s="1" t="s">
+      <c r="D36" t="s" s="1">
         <v>60</v>
       </c>
       <c r="E36">
-        <v>145</v>
+        <v>145.0</v>
       </c>
       <c r="F36">
-        <v>131</v>
+        <v>131.0</v>
       </c>
       <c r="G36">
         <v>26.2</v>
@@ -2271,74 +2271,74 @@
         <v>5.5</v>
       </c>
       <c r="I36">
-        <v>2489</v>
+        <v>2489.0</v>
       </c>
       <c r="J36">
-        <v>1386</v>
+        <v>1386.0</v>
       </c>
       <c r="K36">
-        <v>3875</v>
+        <v>3875.0</v>
       </c>
       <c r="L36">
-        <v>2489</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
+        <v>2489.0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" dyDescent="0.2">
       <c r="A37">
         <v>6</v>
       </c>
       <c r="B37" s="8">
         <v>7</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="C37" t="s" s="1">
         <v>56</v>
       </c>
-      <c r="D37" s="11" t="s">
+      <c r="D37" t="s" s="11">
         <v>57</v>
       </c>
       <c r="E37">
-        <v>185</v>
+        <v>185.0</v>
       </c>
       <c r="F37">
-        <v>232</v>
+        <v>232.0</v>
       </c>
       <c r="G37">
         <v>46.4</v>
       </c>
       <c r="H37">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="I37">
-        <v>4408</v>
+        <v>4408.0</v>
       </c>
       <c r="J37">
-        <v>1617</v>
+        <v>1617.0</v>
       </c>
       <c r="K37">
-        <v>6025</v>
+        <v>6025.0</v>
       </c>
       <c r="L37">
-        <v>4408</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
+        <v>4408.0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" dyDescent="0.2">
       <c r="A38">
         <v>6</v>
       </c>
       <c r="B38" s="8">
         <v>8</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="C38" t="s" s="1">
         <v>56</v>
       </c>
-      <c r="D38" s="1" t="s">
+      <c r="D38" t="s" s="1">
         <v>58</v>
       </c>
       <c r="E38">
-        <v>77</v>
+        <v>77.0</v>
       </c>
       <c r="F38">
-        <v>72</v>
+        <v>72.0</v>
       </c>
       <c r="G38">
         <v>14.4</v>
@@ -2347,74 +2347,74 @@
         <v>5.3</v>
       </c>
       <c r="I38">
-        <v>1368</v>
+        <v>1368.0</v>
       </c>
       <c r="J38">
-        <v>730</v>
+        <v>730.0</v>
       </c>
       <c r="K38">
-        <v>2098</v>
+        <v>2098.0</v>
       </c>
       <c r="L38">
-        <v>1368</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
+        <v>1368.0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" dyDescent="0.2">
       <c r="A39">
         <v>6</v>
       </c>
       <c r="B39" s="8">
         <v>9</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="C39" t="s" s="1">
         <v>56</v>
       </c>
-      <c r="D39" s="1" t="s">
+      <c r="D39" t="s" s="1">
         <v>59</v>
       </c>
       <c r="E39">
-        <v>78</v>
+        <v>78.0</v>
       </c>
       <c r="F39">
-        <v>89</v>
+        <v>89.0</v>
       </c>
       <c r="G39">
         <v>17.8</v>
       </c>
       <c r="H39">
-        <v>4.4000000000000004</v>
+        <v>4.4</v>
       </c>
       <c r="I39">
-        <v>1691</v>
+        <v>1691.0</v>
       </c>
       <c r="J39">
-        <v>702</v>
+        <v>702.0</v>
       </c>
       <c r="K39">
-        <v>2393</v>
+        <v>2393.0</v>
       </c>
       <c r="L39">
-        <v>1691</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
+        <v>1691.0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" dyDescent="0.2">
       <c r="A40">
         <v>6</v>
       </c>
       <c r="B40" s="8">
         <v>10</v>
       </c>
-      <c r="C40" s="1" t="s">
+      <c r="C40" t="s" s="1">
         <v>56</v>
       </c>
-      <c r="D40" s="1" t="s">
+      <c r="D40" t="s" s="1">
         <v>60</v>
       </c>
       <c r="E40">
-        <v>224</v>
+        <v>224.0</v>
       </c>
       <c r="F40">
-        <v>192</v>
+        <v>192.0</v>
       </c>
       <c r="G40">
         <v>38.4</v>
@@ -2423,74 +2423,74 @@
         <v>5.8</v>
       </c>
       <c r="I40">
-        <v>3648</v>
+        <v>3648.0</v>
       </c>
       <c r="J40">
-        <v>2165</v>
+        <v>2165.0</v>
       </c>
       <c r="K40">
-        <v>5813</v>
+        <v>5813.0</v>
       </c>
       <c r="L40">
-        <v>3648</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
+        <v>3648.0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" dyDescent="0.2">
       <c r="A41">
         <v>7</v>
       </c>
       <c r="B41" s="8">
         <v>8</v>
       </c>
-      <c r="C41" s="1" t="s">
+      <c r="C41" t="s" s="1">
         <v>57</v>
       </c>
-      <c r="D41" s="1" t="s">
+      <c r="D41" t="s" s="1">
         <v>58</v>
       </c>
       <c r="E41">
-        <v>131</v>
+        <v>131.0</v>
       </c>
       <c r="F41">
-        <v>160</v>
+        <v>160.0</v>
       </c>
       <c r="G41">
-        <v>32</v>
+        <v>32.0</v>
       </c>
       <c r="H41">
-        <v>4.0999999999999996</v>
+        <v>4.1</v>
       </c>
       <c r="I41">
-        <v>3040</v>
+        <v>3040.0</v>
       </c>
       <c r="J41">
-        <v>1155</v>
+        <v>1155.0</v>
       </c>
       <c r="K41">
-        <v>4195</v>
+        <v>4195.0</v>
       </c>
       <c r="L41">
-        <v>3040</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
+        <v>3040.0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" dyDescent="0.2">
       <c r="A42">
         <v>7</v>
       </c>
       <c r="B42" s="8">
         <v>9</v>
       </c>
-      <c r="C42" s="1" t="s">
+      <c r="C42" t="s" s="1">
         <v>57</v>
       </c>
-      <c r="D42" s="1" t="s">
+      <c r="D42" t="s" s="1">
         <v>59</v>
       </c>
       <c r="E42">
-        <v>110</v>
+        <v>110.0</v>
       </c>
       <c r="F42">
-        <v>146</v>
+        <v>146.0</v>
       </c>
       <c r="G42">
         <v>29.2</v>
@@ -2499,36 +2499,36 @@
         <v>3.8</v>
       </c>
       <c r="I42">
-        <v>2774</v>
+        <v>2774.0</v>
       </c>
       <c r="J42">
-        <v>943</v>
+        <v>943.0</v>
       </c>
       <c r="K42">
-        <v>3717</v>
+        <v>3717.0</v>
       </c>
       <c r="L42">
-        <v>2774</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
+        <v>2774.0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" dyDescent="0.2">
       <c r="A43">
         <v>7</v>
       </c>
       <c r="B43" s="8">
         <v>10</v>
       </c>
-      <c r="C43" s="1" t="s">
+      <c r="C43" t="s" s="1">
         <v>57</v>
       </c>
-      <c r="D43" s="1" t="s">
+      <c r="D43" t="s" s="1">
         <v>60</v>
       </c>
       <c r="E43">
-        <v>280</v>
+        <v>280.0</v>
       </c>
       <c r="F43">
-        <v>187</v>
+        <v>187.0</v>
       </c>
       <c r="G43">
         <v>37.4</v>
@@ -2537,36 +2537,36 @@
         <v>7.5</v>
       </c>
       <c r="I43">
-        <v>3553</v>
+        <v>3553.0</v>
       </c>
       <c r="J43">
-        <v>2830</v>
+        <v>2830.0</v>
       </c>
       <c r="K43">
-        <v>6383</v>
+        <v>6383.0</v>
       </c>
       <c r="L43">
-        <v>3553</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
+        <v>3553.0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" dyDescent="0.2">
       <c r="A44">
         <v>8</v>
       </c>
       <c r="B44" s="8">
         <v>9</v>
       </c>
-      <c r="C44" s="1" t="s">
+      <c r="C44" t="s" s="1">
         <v>58</v>
       </c>
-      <c r="D44" s="1" t="s">
+      <c r="D44" t="s" s="1">
         <v>59</v>
       </c>
       <c r="E44">
-        <v>26</v>
+        <v>26.0</v>
       </c>
       <c r="F44">
-        <v>19</v>
+        <v>19.0</v>
       </c>
       <c r="G44">
         <v>3.8</v>
@@ -2575,95 +2575,95 @@
         <v>6.8</v>
       </c>
       <c r="I44">
-        <v>361</v>
+        <v>361.0</v>
       </c>
       <c r="J44">
-        <v>259</v>
+        <v>259.0</v>
       </c>
       <c r="K44">
-        <v>620</v>
+        <v>620.0</v>
       </c>
       <c r="L44">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.2">
+        <v>361.0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" dyDescent="0.2">
       <c r="A45">
         <v>8</v>
       </c>
       <c r="B45" s="8">
         <v>10</v>
       </c>
-      <c r="C45" s="1" t="s">
+      <c r="C45" t="s" s="1">
         <v>58</v>
       </c>
-      <c r="D45" s="1" t="s">
+      <c r="D45" t="s" s="1">
         <v>60</v>
       </c>
       <c r="E45">
-        <v>163</v>
+        <v>163.0</v>
       </c>
       <c r="F45">
-        <v>164</v>
+        <v>164.0</v>
       </c>
       <c r="G45">
-        <v>32.799999999999997</v>
+        <v>32.8</v>
       </c>
       <c r="H45">
-        <v>5</v>
+        <v>5.0</v>
       </c>
       <c r="I45">
-        <v>3116</v>
+        <v>3116.0</v>
       </c>
       <c r="J45">
-        <v>1519</v>
+        <v>1519.0</v>
       </c>
       <c r="K45">
-        <v>4635</v>
+        <v>4635.0</v>
       </c>
       <c r="L45">
-        <v>3116</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.2">
+        <v>3116.0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" dyDescent="0.2">
       <c r="A46">
         <v>9</v>
       </c>
       <c r="B46" s="8">
         <v>10</v>
       </c>
-      <c r="C46" s="1" t="s">
+      <c r="C46" t="s" s="1">
         <v>59</v>
       </c>
-      <c r="D46" s="1" t="s">
+      <c r="D46" t="s" s="1">
         <v>60</v>
       </c>
       <c r="E46">
-        <v>175</v>
+        <v>175.0</v>
       </c>
       <c r="F46">
-        <v>170</v>
+        <v>170.0</v>
       </c>
       <c r="G46">
-        <v>34</v>
+        <v>34.0</v>
       </c>
       <c r="H46">
-        <v>5.0999999999999996</v>
+        <v>5.1</v>
       </c>
       <c r="I46">
-        <v>3230</v>
+        <v>3230.0</v>
       </c>
       <c r="J46">
-        <v>1645</v>
+        <v>1645.0</v>
       </c>
       <c r="K46">
-        <v>4875</v>
+        <v>4875.0</v>
       </c>
       <c r="L46">
-        <v>3230</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.2">
+        <v>3230.0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" dyDescent="0.2">
       <c r="A47">
         <v>1</v>
       </c>
@@ -2697,7 +2697,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:16" dyDescent="0.2">
       <c r="A48">
         <v>2</v>
       </c>
@@ -2731,7 +2731,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:16" dyDescent="0.2">
       <c r="A49">
         <v>3</v>
       </c>
@@ -2765,7 +2765,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:16" dyDescent="0.2">
       <c r="A50">
         <v>4</v>
       </c>
@@ -2799,7 +2799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:16" dyDescent="0.2">
       <c r="A51">
         <v>5</v>
       </c>
@@ -2833,7 +2833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:16" dyDescent="0.2">
       <c r="A52">
         <v>6</v>
       </c>
@@ -2865,7 +2865,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:16" dyDescent="0.2">
       <c r="A53">
         <v>7</v>
       </c>
@@ -2897,7 +2897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:16" dyDescent="0.2">
       <c r="A54">
         <v>8</v>
       </c>
@@ -2929,7 +2929,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:16" dyDescent="0.2">
       <c r="A55">
         <v>9</v>
       </c>
@@ -2961,7 +2961,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:16" dyDescent="0.2">
       <c r="A56">
         <v>10</v>
       </c>
@@ -2993,13 +2993,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:16" dyDescent="0.2">
       <c r="G57" s="2"/>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:16" dyDescent="0.2">
       <c r="G58" s="1"/>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:16" dyDescent="0.2">
       <c r="G59" s="1"/>
     </row>
   </sheetData>

--- a/inputData/Parameters.xlsx
+++ b/inputData/Parameters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sillewiberg/Desktop/Skole/Speciale/Master-Thesis-eVTOL-1/inputData/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A655786-C4CA-DA4F-925A-95EFB8E73112}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC525445-B921-7444-8BE9-F0D2537C0186}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16320" activeTab="1" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="61">
   <si>
     <t>cap_u</t>
   </si>
@@ -653,13 +653,13 @@
     <col min="2" max="2" width="10.83203125" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:4" dyDescent="0.2">
-      <c r="A2" t="s" s="1">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B2" s="4">
@@ -669,7 +669,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" dyDescent="0.2">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -680,7 +680,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:4" dyDescent="0.2">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>46</v>
       </c>
@@ -691,7 +691,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="5" spans="1:4" dyDescent="0.2">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -702,7 +702,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="6" spans="1:4" dyDescent="0.2">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -713,7 +713,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:4" dyDescent="0.2">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -724,7 +724,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:4" dyDescent="0.2">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -736,7 +736,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:4" dyDescent="0.2">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>0</v>
       </c>
@@ -747,7 +747,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:4" dyDescent="0.2">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>1</v>
       </c>
@@ -758,7 +758,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:4" dyDescent="0.2">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>45</v>
       </c>
@@ -769,7 +769,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="12" spans="1:4" dyDescent="0.2">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>2</v>
       </c>
@@ -777,21 +777,21 @@
         <v>40</v>
       </c>
       <c r="D12" s="3">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" dyDescent="0.2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>42</v>
       </c>
       <c r="B13" s="4">
         <v>20</v>
       </c>
-      <c r="D13" t="s" s="3">
+      <c r="D13" s="3" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="14" spans="1:4" dyDescent="0.2">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -799,11 +799,11 @@
         <f>2.11*B20</f>
         <v>2.11</v>
       </c>
-      <c r="D14" t="s" s="3">
+      <c r="D14" s="3" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="15" spans="1:4" dyDescent="0.2">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>4</v>
       </c>
@@ -811,11 +811,11 @@
         <f>30/B20</f>
         <v>30</v>
       </c>
-      <c r="D15" t="s" s="3">
+      <c r="D15" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:4" dyDescent="0.2">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>5</v>
       </c>
@@ -823,11 +823,11 @@
         <f>20/B20</f>
         <v>20</v>
       </c>
-      <c r="D16" t="s" s="3">
+      <c r="D16" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:4" dyDescent="0.2">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>6</v>
       </c>
@@ -835,18 +835,18 @@
         <f>120/B20</f>
         <v>120</v>
       </c>
-      <c r="D17" t="s" s="3">
+      <c r="D17" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:4" dyDescent="0.2">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>41</v>
       </c>
       <c r="B20" s="4">
         <v>1</v>
       </c>
-      <c r="D20" t="s" s="3">
+      <c r="D20" s="3" t="s">
         <v>48</v>
       </c>
     </row>
@@ -869,44 +869,44 @@
     <col min="8" max="8" width="18.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" dyDescent="0.2">
-      <c r="A1" t="s" s="9">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A1" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="B1" t="s" s="5">
+      <c r="B1" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C1" t="s" s="5">
+      <c r="C1" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="D1" t="s" s="5">
+      <c r="D1" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="E1" t="s" s="5">
+      <c r="E1" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="F1" t="s" s="5">
+      <c r="F1" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="G1" t="s" s="5">
+      <c r="G1" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="H1" t="s" s="5">
+      <c r="H1" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="I1" t="s" s="5">
+      <c r="I1" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="J1" t="s" s="5">
+      <c r="J1" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="K1" t="s" s="5">
+      <c r="K1" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="L1" t="s" s="5">
+      <c r="L1" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="N1" t="s" s="6">
+      <c r="N1" s="6" t="s">
         <v>19</v>
       </c>
       <c r="O1" s="7">
@@ -914,24 +914,24 @@
       </c>
       <c r="P1" s="6"/>
     </row>
-    <row r="2" spans="1:16" dyDescent="0.2">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" s="8">
         <v>2</v>
       </c>
-      <c r="C2" t="s" s="1">
+      <c r="C2" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D2" t="s" s="2">
+      <c r="D2" s="2" t="s">
         <v>52</v>
       </c>
       <c r="E2">
-        <v>185.0</v>
+        <v>185</v>
       </c>
       <c r="F2">
-        <v>219.0</v>
+        <v>219</v>
       </c>
       <c r="G2">
         <v>43.8</v>
@@ -940,16 +940,16 @@
         <v>4.2</v>
       </c>
       <c r="I2">
-        <v>4161.0</v>
+        <v>4161</v>
       </c>
       <c r="J2">
-        <v>1647.0</v>
+        <v>1647</v>
       </c>
       <c r="K2">
-        <v>5808.0</v>
+        <v>5808</v>
       </c>
       <c r="L2">
-        <v>4161.0</v>
+        <v>4161</v>
       </c>
       <c r="N2" t="s">
         <v>29</v>
@@ -961,42 +961,42 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:16" dyDescent="0.2">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" s="8">
         <v>3</v>
       </c>
-      <c r="C3" t="s" s="1">
+      <c r="C3" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D3" t="s" s="2">
+      <c r="D3" s="2" t="s">
         <v>53</v>
       </c>
       <c r="E3">
-        <v>82.0</v>
+        <v>82</v>
       </c>
       <c r="F3">
-        <v>88.0</v>
+        <v>88</v>
       </c>
       <c r="G3">
-        <v>17.6</v>
+        <v>17.600000000000001</v>
       </c>
       <c r="H3">
         <v>4.7</v>
       </c>
       <c r="I3">
-        <v>1672.0</v>
+        <v>1672</v>
       </c>
       <c r="J3">
-        <v>751.0</v>
+        <v>751</v>
       </c>
       <c r="K3">
-        <v>2423.0</v>
+        <v>2423</v>
       </c>
       <c r="L3">
-        <v>1672.0</v>
+        <v>1672</v>
       </c>
       <c r="N3" t="s">
         <v>31</v>
@@ -1009,24 +1009,24 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:16" dyDescent="0.2">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>1</v>
       </c>
       <c r="B4" s="8">
         <v>4</v>
       </c>
-      <c r="C4" t="s" s="1">
+      <c r="C4" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D4" t="s" s="1">
+      <c r="D4" s="1" t="s">
         <v>54</v>
       </c>
       <c r="E4">
-        <v>228.0</v>
+        <v>228</v>
       </c>
       <c r="F4">
-        <v>147.0</v>
+        <v>147</v>
       </c>
       <c r="G4">
         <v>29.4</v>
@@ -1035,16 +1035,16 @@
         <v>7.8</v>
       </c>
       <c r="I4">
-        <v>2793.0</v>
+        <v>2793</v>
       </c>
       <c r="J4">
-        <v>2317.0</v>
+        <v>2317</v>
       </c>
       <c r="K4">
-        <v>5110.0</v>
+        <v>5110</v>
       </c>
       <c r="L4">
-        <v>2793.0</v>
+        <v>2793</v>
       </c>
       <c r="N4" t="s">
         <v>33</v>
@@ -1053,24 +1053,24 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="5" spans="1:16" dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>1</v>
       </c>
       <c r="B5" s="8">
         <v>5</v>
       </c>
-      <c r="C5" t="s" s="1">
+      <c r="C5" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D5" t="s" s="1">
+      <c r="D5" s="1" t="s">
         <v>55</v>
       </c>
       <c r="E5">
-        <v>126.0</v>
+        <v>126</v>
       </c>
       <c r="F5">
-        <v>147.0</v>
+        <v>147</v>
       </c>
       <c r="G5">
         <v>29.4</v>
@@ -1079,16 +1079,16 @@
         <v>4.3</v>
       </c>
       <c r="I5">
-        <v>2793.0</v>
+        <v>2793</v>
       </c>
       <c r="J5">
-        <v>1127.0</v>
+        <v>1127</v>
       </c>
       <c r="K5">
-        <v>3920.0</v>
+        <v>3920</v>
       </c>
       <c r="L5">
-        <v>2793.0</v>
+        <v>2793</v>
       </c>
       <c r="N5" t="s">
         <v>34</v>
@@ -1100,24 +1100,24 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:16" dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>1</v>
       </c>
       <c r="B6" s="8">
         <v>6</v>
       </c>
-      <c r="C6" t="s" s="1">
+      <c r="C6" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D6" t="s" s="1">
+      <c r="D6" s="1" t="s">
         <v>56</v>
       </c>
       <c r="E6">
-        <v>205.0</v>
+        <v>205</v>
       </c>
       <c r="F6">
-        <v>197.0</v>
+        <v>197</v>
       </c>
       <c r="G6">
         <v>39.4</v>
@@ -1126,37 +1126,37 @@
         <v>5.2</v>
       </c>
       <c r="I6">
-        <v>3743.0</v>
+        <v>3743</v>
       </c>
       <c r="J6">
-        <v>1932.0</v>
+        <v>1932</v>
       </c>
       <c r="K6">
-        <v>5675.0</v>
+        <v>5675</v>
       </c>
       <c r="L6">
-        <v>3743.0</v>
+        <v>3743</v>
       </c>
       <c r="O6" s="4"/>
     </row>
-    <row r="7" spans="1:16" dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>1</v>
       </c>
       <c r="B7" s="8">
         <v>7</v>
       </c>
-      <c r="C7" t="s" s="1">
+      <c r="C7" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D7" t="s" s="1">
+      <c r="D7" s="1" t="s">
         <v>57</v>
       </c>
       <c r="E7">
-        <v>263.0</v>
+        <v>263</v>
       </c>
       <c r="F7">
-        <v>227.0</v>
+        <v>227</v>
       </c>
       <c r="G7">
         <v>45.4</v>
@@ -1165,154 +1165,154 @@
         <v>5.8</v>
       </c>
       <c r="I7">
-        <v>4313.0</v>
+        <v>4313</v>
       </c>
       <c r="J7">
-        <v>2539.0</v>
+        <v>2539</v>
       </c>
       <c r="K7">
-        <v>6852.0</v>
+        <v>6852</v>
       </c>
       <c r="L7">
-        <v>4313.0</v>
+        <v>4313</v>
       </c>
       <c r="O7" s="4"/>
     </row>
-    <row r="8" spans="1:16" dyDescent="0.2">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>1</v>
       </c>
       <c r="B8" s="8">
         <v>8</v>
       </c>
-      <c r="C8" t="s" s="1">
+      <c r="C8" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D8" t="s" s="1">
+      <c r="D8" s="1" t="s">
         <v>58</v>
       </c>
       <c r="E8">
-        <v>143.0</v>
+        <v>143</v>
       </c>
       <c r="F8">
-        <v>184.0</v>
+        <v>184</v>
       </c>
       <c r="G8">
-        <v>36.8</v>
+        <v>36.799999999999997</v>
       </c>
       <c r="H8">
         <v>3.9</v>
       </c>
       <c r="I8">
-        <v>3496.0</v>
+        <v>3496</v>
       </c>
       <c r="J8">
-        <v>1239.0</v>
+        <v>1239</v>
       </c>
       <c r="K8">
-        <v>4735.0</v>
+        <v>4735</v>
       </c>
       <c r="L8">
-        <v>3496.0</v>
+        <v>3496</v>
       </c>
       <c r="O8" s="4"/>
     </row>
-    <row r="9" spans="1:16" dyDescent="0.2">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>1</v>
       </c>
       <c r="B9" s="8">
         <v>9</v>
       </c>
-      <c r="C9" t="s" s="1">
+      <c r="C9" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D9" t="s" s="1">
+      <c r="D9" s="1" t="s">
         <v>59</v>
       </c>
       <c r="E9">
-        <v>155.0</v>
+        <v>155</v>
       </c>
       <c r="F9">
-        <v>193.0</v>
+        <v>193</v>
       </c>
       <c r="G9">
         <v>38.6</v>
       </c>
       <c r="H9">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="I9">
-        <v>3667.0</v>
+        <v>3667</v>
       </c>
       <c r="J9">
-        <v>1358.0</v>
+        <v>1358</v>
       </c>
       <c r="K9">
-        <v>5025.0</v>
+        <v>5025</v>
       </c>
       <c r="L9">
-        <v>3667.0</v>
+        <v>3667</v>
       </c>
       <c r="O9" s="4"/>
     </row>
-    <row r="10" spans="1:16" dyDescent="0.2">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>1</v>
       </c>
       <c r="B10" s="8">
         <v>10</v>
       </c>
-      <c r="C10" t="s" s="1">
+      <c r="C10" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D10" t="s" s="1">
+      <c r="D10" s="1" t="s">
         <v>60</v>
       </c>
       <c r="E10">
-        <v>42.0</v>
+        <v>42</v>
       </c>
       <c r="F10">
-        <v>41.0</v>
+        <v>41</v>
       </c>
       <c r="G10">
-        <v>8.2</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="H10">
-        <v>5.1</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="I10">
-        <v>779.0</v>
+        <v>779</v>
       </c>
       <c r="J10">
-        <v>394.0</v>
+        <v>394</v>
       </c>
       <c r="K10">
-        <v>1173.0</v>
+        <v>1173</v>
       </c>
       <c r="L10">
-        <v>779.0</v>
+        <v>779</v>
       </c>
       <c r="O10" s="4"/>
     </row>
-    <row r="11" spans="1:16" dyDescent="0.2">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>2</v>
       </c>
       <c r="B11" s="8">
         <v>3</v>
       </c>
-      <c r="C11" t="s" s="2">
+      <c r="C11" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D11" t="s" s="2">
+      <c r="D11" s="2" t="s">
         <v>53</v>
       </c>
       <c r="E11">
-        <v>173.0</v>
+        <v>173</v>
       </c>
       <c r="F11">
-        <v>131.0</v>
+        <v>131</v>
       </c>
       <c r="G11">
         <v>26.2</v>
@@ -1321,226 +1321,226 @@
         <v>6.6</v>
       </c>
       <c r="I11">
-        <v>2489.0</v>
+        <v>2489</v>
       </c>
       <c r="J11">
-        <v>1713.0</v>
+        <v>1713</v>
       </c>
       <c r="K11">
-        <v>4202.0</v>
+        <v>4202</v>
       </c>
       <c r="L11">
-        <v>2489.0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" dyDescent="0.2">
+        <v>2489</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>2</v>
       </c>
       <c r="B12" s="8">
         <v>4</v>
       </c>
-      <c r="C12" t="s" s="2">
+      <c r="C12" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D12" t="s" s="1">
+      <c r="D12" s="1" t="s">
         <v>54</v>
       </c>
       <c r="E12">
-        <v>103.0</v>
+        <v>103</v>
       </c>
       <c r="F12">
-        <v>110.0</v>
+        <v>110</v>
       </c>
       <c r="G12">
-        <v>22.0</v>
+        <v>22</v>
       </c>
       <c r="H12">
         <v>4.7</v>
       </c>
       <c r="I12">
-        <v>2090.0</v>
+        <v>2090</v>
       </c>
       <c r="J12">
-        <v>945.0</v>
+        <v>945</v>
       </c>
       <c r="K12">
-        <v>3035.0</v>
+        <v>3035</v>
       </c>
       <c r="L12">
-        <v>2090.0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" dyDescent="0.2">
+        <v>2090</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>2</v>
       </c>
       <c r="B13" s="8">
         <v>5</v>
       </c>
-      <c r="C13" t="s" s="2">
+      <c r="C13" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D13" t="s" s="1">
+      <c r="D13" s="1" t="s">
         <v>55</v>
       </c>
       <c r="E13">
-        <v>89.0</v>
+        <v>89</v>
       </c>
       <c r="F13">
-        <v>80.0</v>
+        <v>80</v>
       </c>
       <c r="G13">
-        <v>16.0</v>
+        <v>16</v>
       </c>
       <c r="H13">
         <v>5.6</v>
       </c>
       <c r="I13">
-        <v>1520.0</v>
+        <v>1520</v>
       </c>
       <c r="J13">
-        <v>852.0</v>
+        <v>852</v>
       </c>
       <c r="K13">
-        <v>2372.0</v>
+        <v>2372</v>
       </c>
       <c r="L13">
-        <v>1520.0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" dyDescent="0.2">
+        <v>1520</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>2</v>
       </c>
       <c r="B14" s="8">
         <v>6</v>
       </c>
-      <c r="C14" t="s" s="2">
+      <c r="C14" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D14" t="s" s="1">
+      <c r="D14" s="1" t="s">
         <v>56</v>
       </c>
       <c r="E14">
-        <v>100.0</v>
+        <v>100</v>
       </c>
       <c r="F14">
-        <v>98.0</v>
+        <v>98</v>
       </c>
       <c r="G14">
-        <v>19.6</v>
+        <v>19.600000000000001</v>
       </c>
       <c r="H14">
-        <v>5.1</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="I14">
-        <v>1862.0</v>
+        <v>1862</v>
       </c>
       <c r="J14">
-        <v>938.0</v>
+        <v>938</v>
       </c>
       <c r="K14">
-        <v>2800.0</v>
+        <v>2800</v>
       </c>
       <c r="L14">
-        <v>1862.0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" dyDescent="0.2">
+        <v>1862</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>2</v>
       </c>
       <c r="B15" s="8">
         <v>7</v>
       </c>
-      <c r="C15" t="s" s="2">
+      <c r="C15" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D15" t="s" s="11">
+      <c r="D15" s="11" t="s">
         <v>57</v>
       </c>
       <c r="E15">
-        <v>138.0</v>
+        <v>138</v>
       </c>
       <c r="F15">
-        <v>151.0</v>
+        <v>151</v>
       </c>
       <c r="G15">
         <v>30.2</v>
       </c>
       <c r="H15">
-        <v>4.6</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="I15">
-        <v>2869.0</v>
+        <v>2869</v>
       </c>
       <c r="J15">
-        <v>1258.0</v>
+        <v>1258</v>
       </c>
       <c r="K15">
-        <v>4127.0</v>
+        <v>4127</v>
       </c>
       <c r="L15">
-        <v>2869.0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" dyDescent="0.2">
+        <v>2869</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>2</v>
       </c>
       <c r="B16" s="8">
         <v>8</v>
       </c>
-      <c r="C16" t="s" s="2">
+      <c r="C16" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D16" t="s" s="1">
+      <c r="D16" s="1" t="s">
         <v>58</v>
       </c>
       <c r="E16">
-        <v>55.0</v>
+        <v>55</v>
       </c>
       <c r="F16">
-        <v>40.0</v>
+        <v>40</v>
       </c>
       <c r="G16">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="H16">
         <v>6.9</v>
       </c>
       <c r="I16">
-        <v>760.0</v>
+        <v>760</v>
       </c>
       <c r="J16">
-        <v>548.0</v>
+        <v>548</v>
       </c>
       <c r="K16">
-        <v>1308.0</v>
+        <v>1308</v>
       </c>
       <c r="L16">
-        <v>760.0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" dyDescent="0.2">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>2</v>
       </c>
       <c r="B17" s="8">
         <v>9</v>
       </c>
-      <c r="C17" t="s" s="2">
+      <c r="C17" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D17" t="s" s="1">
+      <c r="D17" s="1" t="s">
         <v>59</v>
       </c>
       <c r="E17">
-        <v>38.0</v>
+        <v>38</v>
       </c>
       <c r="F17">
-        <v>26.0</v>
+        <v>26</v>
       </c>
       <c r="G17">
         <v>5.2</v>
@@ -1549,150 +1549,150 @@
         <v>7.3</v>
       </c>
       <c r="I17">
-        <v>494.0</v>
+        <v>494</v>
       </c>
       <c r="J17">
-        <v>383.0</v>
+        <v>383</v>
       </c>
       <c r="K17">
-        <v>877.0</v>
+        <v>877</v>
       </c>
       <c r="L17">
-        <v>494.0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" dyDescent="0.2">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>2</v>
       </c>
       <c r="B18" s="8">
         <v>10</v>
       </c>
-      <c r="C18" t="s" s="2">
+      <c r="C18" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D18" t="s" s="1">
+      <c r="D18" s="1" t="s">
         <v>60</v>
       </c>
       <c r="E18">
-        <v>205.0</v>
+        <v>205</v>
       </c>
       <c r="F18">
-        <v>196.0</v>
+        <v>196</v>
       </c>
       <c r="G18">
-        <v>39.2</v>
+        <v>39.200000000000003</v>
       </c>
       <c r="H18">
         <v>5.2</v>
       </c>
       <c r="I18">
-        <v>3724.0</v>
+        <v>3724</v>
       </c>
       <c r="J18">
-        <v>1934.0</v>
+        <v>1934</v>
       </c>
       <c r="K18">
-        <v>5658.0</v>
+        <v>5658</v>
       </c>
       <c r="L18">
-        <v>3724.0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" dyDescent="0.2">
+        <v>3724</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>3</v>
       </c>
       <c r="B19" s="8">
         <v>4</v>
       </c>
-      <c r="C19" t="s" s="2">
+      <c r="C19" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="D19" t="s" s="1">
+      <c r="D19" s="1" t="s">
         <v>54</v>
       </c>
       <c r="E19">
-        <v>215.0</v>
+        <v>215</v>
       </c>
       <c r="F19">
-        <v>77.0</v>
+        <v>77</v>
       </c>
       <c r="G19">
         <v>15.4</v>
       </c>
       <c r="H19">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="I19">
-        <v>1463.0</v>
+        <v>1463</v>
       </c>
       <c r="J19">
-        <v>2329.0</v>
+        <v>2329</v>
       </c>
       <c r="K19">
-        <v>3792.0</v>
+        <v>3792</v>
       </c>
       <c r="L19">
-        <v>2329.0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" dyDescent="0.2">
+        <v>2329</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>3</v>
       </c>
       <c r="B20" s="8">
         <v>5</v>
       </c>
-      <c r="C20" t="s" s="2">
+      <c r="C20" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="D20" t="s" s="1">
+      <c r="D20" s="1" t="s">
         <v>55</v>
       </c>
       <c r="E20">
-        <v>113.0</v>
+        <v>113</v>
       </c>
       <c r="F20">
-        <v>63.0</v>
+        <v>63</v>
       </c>
       <c r="G20">
         <v>12.6</v>
       </c>
       <c r="H20">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="I20">
-        <v>1197.0</v>
+        <v>1197</v>
       </c>
       <c r="J20">
-        <v>1171.0</v>
+        <v>1171</v>
       </c>
       <c r="K20">
-        <v>2368.0</v>
+        <v>2368</v>
       </c>
       <c r="L20">
-        <v>1197.0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" dyDescent="0.2">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>3</v>
       </c>
       <c r="B21" s="8">
         <v>6</v>
       </c>
-      <c r="C21" t="s" s="2">
+      <c r="C21" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="D21" t="s" s="1">
+      <c r="D21" s="1" t="s">
         <v>56</v>
       </c>
       <c r="E21">
-        <v>192.0</v>
+        <v>192</v>
       </c>
       <c r="F21">
-        <v>126.0</v>
+        <v>126</v>
       </c>
       <c r="G21">
         <v>25.2</v>
@@ -1701,36 +1701,36 @@
         <v>7.6</v>
       </c>
       <c r="I21">
-        <v>2394.0</v>
+        <v>2394</v>
       </c>
       <c r="J21">
-        <v>1946.0</v>
+        <v>1946</v>
       </c>
       <c r="K21">
-        <v>4340.0</v>
+        <v>4340</v>
       </c>
       <c r="L21">
-        <v>2394.0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" dyDescent="0.2">
+        <v>2394</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>3</v>
       </c>
       <c r="B22" s="8">
         <v>7</v>
       </c>
-      <c r="C22" t="s" s="2">
+      <c r="C22" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="D22" t="s" s="11">
+      <c r="D22" s="11" t="s">
         <v>57</v>
       </c>
       <c r="E22">
-        <v>250.0</v>
+        <v>250</v>
       </c>
       <c r="F22">
-        <v>167.0</v>
+        <v>167</v>
       </c>
       <c r="G22">
         <v>33.4</v>
@@ -1739,112 +1739,112 @@
         <v>7.5</v>
       </c>
       <c r="I22">
-        <v>3173.0</v>
+        <v>3173</v>
       </c>
       <c r="J22">
-        <v>2527.0</v>
+        <v>2527</v>
       </c>
       <c r="K22">
-        <v>5700.0</v>
+        <v>5700</v>
       </c>
       <c r="L22">
-        <v>3173.0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" dyDescent="0.2">
+        <v>3173</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>3</v>
       </c>
       <c r="B23" s="8">
         <v>8</v>
       </c>
-      <c r="C23" t="s" s="2">
+      <c r="C23" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="D23" t="s" s="1">
+      <c r="D23" s="1" t="s">
         <v>58</v>
       </c>
       <c r="E23">
-        <v>130.0</v>
+        <v>130</v>
       </c>
       <c r="F23">
-        <v>97.0</v>
+        <v>97</v>
       </c>
       <c r="G23">
-        <v>19.4</v>
+        <v>19.399999999999999</v>
       </c>
       <c r="H23">
         <v>6.7</v>
       </c>
       <c r="I23">
-        <v>1843.0</v>
+        <v>1843</v>
       </c>
       <c r="J23">
-        <v>1290.0</v>
+        <v>1290</v>
       </c>
       <c r="K23">
-        <v>3133.0</v>
+        <v>3133</v>
       </c>
       <c r="L23">
-        <v>1843.0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" dyDescent="0.2">
+        <v>1843</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>3</v>
       </c>
       <c r="B24" s="8">
         <v>9</v>
       </c>
-      <c r="C24" t="s" s="2">
+      <c r="C24" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="D24" t="s" s="1">
+      <c r="D24" s="1" t="s">
         <v>59</v>
       </c>
       <c r="E24">
-        <v>142.0</v>
+        <v>142</v>
       </c>
       <c r="F24">
-        <v>105.0</v>
+        <v>105</v>
       </c>
       <c r="G24">
-        <v>21.0</v>
+        <v>21</v>
       </c>
       <c r="H24">
         <v>6.8</v>
       </c>
       <c r="I24">
-        <v>1995.0</v>
+        <v>1995</v>
       </c>
       <c r="J24">
-        <v>1412.0</v>
+        <v>1412</v>
       </c>
       <c r="K24">
-        <v>3407.0</v>
+        <v>3407</v>
       </c>
       <c r="L24">
-        <v>1995.0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" dyDescent="0.2">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>3</v>
       </c>
       <c r="B25" s="8">
         <v>10</v>
       </c>
-      <c r="C25" t="s" s="2">
+      <c r="C25" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="D25" t="s" s="1">
+      <c r="D25" s="1" t="s">
         <v>60</v>
       </c>
       <c r="E25">
-        <v>89.0</v>
+        <v>89</v>
       </c>
       <c r="F25">
-        <v>68.0</v>
+        <v>68</v>
       </c>
       <c r="G25">
         <v>13.6</v>
@@ -1853,188 +1853,188 @@
         <v>6.5</v>
       </c>
       <c r="I25">
-        <v>1292.0</v>
+        <v>1292</v>
       </c>
       <c r="J25">
-        <v>880.0</v>
+        <v>880</v>
       </c>
       <c r="K25">
-        <v>2172.0</v>
+        <v>2172</v>
       </c>
       <c r="L25">
-        <v>1292.0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" dyDescent="0.2">
+        <v>1292</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>4</v>
       </c>
       <c r="B26" s="8">
         <v>5</v>
       </c>
-      <c r="C26" t="s" s="1">
+      <c r="C26" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D26" t="s" s="1">
+      <c r="D26" s="1" t="s">
         <v>55</v>
       </c>
       <c r="E26">
-        <v>130.0</v>
+        <v>130</v>
       </c>
       <c r="F26">
-        <v>93.0</v>
+        <v>93</v>
       </c>
       <c r="G26">
-        <v>18.6</v>
+        <v>18.600000000000001</v>
       </c>
       <c r="H26">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="I26">
-        <v>1767.0</v>
+        <v>1767</v>
       </c>
       <c r="J26">
-        <v>1300.0</v>
+        <v>1300</v>
       </c>
       <c r="K26">
-        <v>3067.0</v>
+        <v>3067</v>
       </c>
       <c r="L26">
-        <v>1767.0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" dyDescent="0.2">
+        <v>1767</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>4</v>
       </c>
       <c r="B27" s="8">
         <v>6</v>
       </c>
-      <c r="C27" t="s" s="1">
+      <c r="C27" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D27" t="s" s="1">
+      <c r="D27" s="1" t="s">
         <v>56</v>
       </c>
       <c r="E27">
-        <v>149.0</v>
+        <v>149</v>
       </c>
       <c r="F27">
-        <v>161.0</v>
+        <v>161</v>
       </c>
       <c r="G27">
-        <v>32.2</v>
+        <v>32.200000000000003</v>
       </c>
       <c r="H27">
-        <v>4.6</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="I27">
-        <v>3059.0</v>
+        <v>3059</v>
       </c>
       <c r="J27">
-        <v>1363.0</v>
+        <v>1363</v>
       </c>
       <c r="K27">
-        <v>4422.0</v>
+        <v>4422</v>
       </c>
       <c r="L27">
-        <v>3059.0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" dyDescent="0.2">
+        <v>3059</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>4</v>
       </c>
       <c r="B28" s="8">
         <v>7</v>
       </c>
-      <c r="C28" t="s" s="1">
+      <c r="C28" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D28" t="s" s="11">
+      <c r="D28" s="11" t="s">
         <v>57</v>
       </c>
       <c r="E28">
-        <v>93.0</v>
+        <v>93</v>
       </c>
       <c r="F28">
-        <v>90.0</v>
+        <v>90</v>
       </c>
       <c r="G28">
-        <v>18.0</v>
+        <v>18</v>
       </c>
       <c r="H28">
         <v>5.2</v>
       </c>
       <c r="I28">
-        <v>1710.0</v>
+        <v>1710</v>
       </c>
       <c r="J28">
-        <v>875.0</v>
+        <v>875</v>
       </c>
       <c r="K28">
-        <v>2585.0</v>
+        <v>2585</v>
       </c>
       <c r="L28">
-        <v>1710.0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" dyDescent="0.2">
+        <v>1710</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>4</v>
       </c>
       <c r="B29" s="8">
         <v>8</v>
       </c>
-      <c r="C29" t="s" s="1">
+      <c r="C29" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D29" t="s" s="1">
+      <c r="D29" s="1" t="s">
         <v>58</v>
       </c>
       <c r="E29">
-        <v>97.0</v>
+        <v>97</v>
       </c>
       <c r="F29">
-        <v>97.0</v>
+        <v>97</v>
       </c>
       <c r="G29">
-        <v>19.4</v>
+        <v>19.399999999999999</v>
       </c>
       <c r="H29">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="I29">
-        <v>1843.0</v>
+        <v>1843</v>
       </c>
       <c r="J29">
-        <v>905.0</v>
+        <v>905</v>
       </c>
       <c r="K29">
-        <v>2748.0</v>
+        <v>2748</v>
       </c>
       <c r="L29">
-        <v>1843.0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16" dyDescent="0.2">
+        <v>1843</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>4</v>
       </c>
       <c r="B30" s="8">
         <v>9</v>
       </c>
-      <c r="C30" t="s" s="1">
+      <c r="C30" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D30" t="s" s="1">
+      <c r="D30" s="1" t="s">
         <v>59</v>
       </c>
       <c r="E30">
-        <v>76.0</v>
+        <v>76</v>
       </c>
       <c r="F30">
-        <v>91.0</v>
+        <v>91</v>
       </c>
       <c r="G30">
         <v>18.2</v>
@@ -2043,226 +2043,226 @@
         <v>4.2</v>
       </c>
       <c r="I30">
-        <v>1729.0</v>
+        <v>1729</v>
       </c>
       <c r="J30">
-        <v>674.0</v>
+        <v>674</v>
       </c>
       <c r="K30">
-        <v>2403.0</v>
+        <v>2403</v>
       </c>
       <c r="L30">
-        <v>1729.0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16" dyDescent="0.2">
+        <v>1729</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>4</v>
       </c>
       <c r="B31" s="8">
         <v>10</v>
       </c>
-      <c r="C31" t="s" s="1">
+      <c r="C31" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D31" t="s" s="1">
+      <c r="D31" s="1" t="s">
         <v>60</v>
       </c>
       <c r="E31">
-        <v>246.0</v>
+        <v>246</v>
       </c>
       <c r="F31">
-        <v>110.0</v>
+        <v>110</v>
       </c>
       <c r="G31">
-        <v>22.0</v>
+        <v>22</v>
       </c>
       <c r="H31">
         <v>11.2</v>
       </c>
       <c r="I31">
-        <v>2090.0</v>
+        <v>2090</v>
       </c>
       <c r="J31">
-        <v>2613.0</v>
+        <v>2613</v>
       </c>
       <c r="K31">
-        <v>4703.0</v>
+        <v>4703</v>
       </c>
       <c r="L31">
-        <v>2613.0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16" dyDescent="0.2">
+        <v>2613</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>5</v>
       </c>
       <c r="B32" s="8">
         <v>6</v>
       </c>
-      <c r="C32" t="s" s="1">
+      <c r="C32" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D32" t="s" s="1">
+      <c r="D32" s="1" t="s">
         <v>56</v>
       </c>
       <c r="E32">
-        <v>110.0</v>
+        <v>110</v>
       </c>
       <c r="F32">
-        <v>70.0</v>
+        <v>70</v>
       </c>
       <c r="G32">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="H32">
         <v>7.9</v>
       </c>
       <c r="I32">
-        <v>1330.0</v>
+        <v>1330</v>
       </c>
       <c r="J32">
-        <v>1120.0</v>
+        <v>1120</v>
       </c>
       <c r="K32">
-        <v>2450.0</v>
+        <v>2450</v>
       </c>
       <c r="L32">
-        <v>1330.0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" dyDescent="0.2">
+        <v>1330</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A33" s="10">
         <v>5</v>
       </c>
       <c r="B33" s="8">
         <v>7</v>
       </c>
-      <c r="C33" t="s" s="1">
+      <c r="C33" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D33" t="s" s="11">
+      <c r="D33" s="11" t="s">
         <v>57</v>
       </c>
       <c r="E33">
-        <v>168.0</v>
+        <v>168</v>
       </c>
       <c r="F33">
-        <v>173.0</v>
+        <v>173</v>
       </c>
       <c r="G33">
         <v>34.6</v>
       </c>
       <c r="H33">
-        <v>4.9</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="I33">
-        <v>3287.0</v>
+        <v>3287</v>
       </c>
       <c r="J33">
-        <v>1556.0</v>
+        <v>1556</v>
       </c>
       <c r="K33">
-        <v>4843.0</v>
+        <v>4843</v>
       </c>
       <c r="L33">
-        <v>3287.0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" dyDescent="0.2">
+        <v>3287</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>5</v>
       </c>
       <c r="B34" s="8">
         <v>8</v>
       </c>
-      <c r="C34" t="s" s="1">
+      <c r="C34" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D34" t="s" s="1">
+      <c r="D34" s="1" t="s">
         <v>58</v>
       </c>
       <c r="E34">
-        <v>48.0</v>
+        <v>48</v>
       </c>
       <c r="F34">
-        <v>40.0</v>
+        <v>40</v>
       </c>
       <c r="G34">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="H34">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="I34">
-        <v>760.0</v>
+        <v>760</v>
       </c>
       <c r="J34">
-        <v>467.0</v>
+        <v>467</v>
       </c>
       <c r="K34">
-        <v>1227.0</v>
+        <v>1227</v>
       </c>
       <c r="L34">
-        <v>760.0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" dyDescent="0.2">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>5</v>
       </c>
       <c r="B35" s="8">
         <v>9</v>
       </c>
-      <c r="C35" t="s" s="1">
+      <c r="C35" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D35" t="s" s="1">
+      <c r="D35" s="1" t="s">
         <v>59</v>
       </c>
       <c r="E35">
-        <v>60.0</v>
+        <v>60</v>
       </c>
       <c r="F35">
-        <v>55.0</v>
+        <v>55</v>
       </c>
       <c r="G35">
-        <v>11.0</v>
+        <v>11</v>
       </c>
       <c r="H35">
         <v>5.5</v>
       </c>
       <c r="I35">
-        <v>1045.0</v>
+        <v>1045</v>
       </c>
       <c r="J35">
-        <v>572.0</v>
+        <v>572</v>
       </c>
       <c r="K35">
-        <v>1617.0</v>
+        <v>1617</v>
       </c>
       <c r="L35">
-        <v>1045.0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16" dyDescent="0.2">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>5</v>
       </c>
       <c r="B36" s="8">
         <v>10</v>
       </c>
-      <c r="C36" t="s" s="1">
+      <c r="C36" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D36" t="s" s="1">
+      <c r="D36" s="1" t="s">
         <v>60</v>
       </c>
       <c r="E36">
-        <v>145.0</v>
+        <v>145</v>
       </c>
       <c r="F36">
-        <v>131.0</v>
+        <v>131</v>
       </c>
       <c r="G36">
         <v>26.2</v>
@@ -2271,74 +2271,74 @@
         <v>5.5</v>
       </c>
       <c r="I36">
-        <v>2489.0</v>
+        <v>2489</v>
       </c>
       <c r="J36">
-        <v>1386.0</v>
+        <v>1386</v>
       </c>
       <c r="K36">
-        <v>3875.0</v>
+        <v>3875</v>
       </c>
       <c r="L36">
-        <v>2489.0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16" dyDescent="0.2">
+        <v>2489</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>6</v>
       </c>
       <c r="B37" s="8">
         <v>7</v>
       </c>
-      <c r="C37" t="s" s="1">
+      <c r="C37" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="D37" t="s" s="11">
+      <c r="D37" s="11" t="s">
         <v>57</v>
       </c>
       <c r="E37">
-        <v>185.0</v>
+        <v>185</v>
       </c>
       <c r="F37">
-        <v>232.0</v>
+        <v>232</v>
       </c>
       <c r="G37">
         <v>46.4</v>
       </c>
       <c r="H37">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="I37">
-        <v>4408.0</v>
+        <v>4408</v>
       </c>
       <c r="J37">
-        <v>1617.0</v>
+        <v>1617</v>
       </c>
       <c r="K37">
-        <v>6025.0</v>
+        <v>6025</v>
       </c>
       <c r="L37">
-        <v>4408.0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:16" dyDescent="0.2">
+        <v>4408</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>6</v>
       </c>
       <c r="B38" s="8">
         <v>8</v>
       </c>
-      <c r="C38" t="s" s="1">
+      <c r="C38" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="D38" t="s" s="1">
+      <c r="D38" s="1" t="s">
         <v>58</v>
       </c>
       <c r="E38">
-        <v>77.0</v>
+        <v>77</v>
       </c>
       <c r="F38">
-        <v>72.0</v>
+        <v>72</v>
       </c>
       <c r="G38">
         <v>14.4</v>
@@ -2347,74 +2347,74 @@
         <v>5.3</v>
       </c>
       <c r="I38">
-        <v>1368.0</v>
+        <v>1368</v>
       </c>
       <c r="J38">
-        <v>730.0</v>
+        <v>730</v>
       </c>
       <c r="K38">
-        <v>2098.0</v>
+        <v>2098</v>
       </c>
       <c r="L38">
-        <v>1368.0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16" dyDescent="0.2">
+        <v>1368</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>6</v>
       </c>
       <c r="B39" s="8">
         <v>9</v>
       </c>
-      <c r="C39" t="s" s="1">
+      <c r="C39" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="D39" t="s" s="1">
+      <c r="D39" s="1" t="s">
         <v>59</v>
       </c>
       <c r="E39">
-        <v>78.0</v>
+        <v>78</v>
       </c>
       <c r="F39">
-        <v>89.0</v>
+        <v>89</v>
       </c>
       <c r="G39">
         <v>17.8</v>
       </c>
       <c r="H39">
-        <v>4.4</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="I39">
-        <v>1691.0</v>
+        <v>1691</v>
       </c>
       <c r="J39">
-        <v>702.0</v>
+        <v>702</v>
       </c>
       <c r="K39">
-        <v>2393.0</v>
+        <v>2393</v>
       </c>
       <c r="L39">
-        <v>1691.0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:16" dyDescent="0.2">
+        <v>1691</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>6</v>
       </c>
       <c r="B40" s="8">
         <v>10</v>
       </c>
-      <c r="C40" t="s" s="1">
+      <c r="C40" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="D40" t="s" s="1">
+      <c r="D40" s="1" t="s">
         <v>60</v>
       </c>
       <c r="E40">
-        <v>224.0</v>
+        <v>224</v>
       </c>
       <c r="F40">
-        <v>192.0</v>
+        <v>192</v>
       </c>
       <c r="G40">
         <v>38.4</v>
@@ -2423,74 +2423,74 @@
         <v>5.8</v>
       </c>
       <c r="I40">
-        <v>3648.0</v>
+        <v>3648</v>
       </c>
       <c r="J40">
-        <v>2165.0</v>
+        <v>2165</v>
       </c>
       <c r="K40">
-        <v>5813.0</v>
+        <v>5813</v>
       </c>
       <c r="L40">
-        <v>3648.0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:16" dyDescent="0.2">
+        <v>3648</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>7</v>
       </c>
       <c r="B41" s="8">
         <v>8</v>
       </c>
-      <c r="C41" t="s" s="1">
+      <c r="C41" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="D41" t="s" s="1">
+      <c r="D41" s="1" t="s">
         <v>58</v>
       </c>
       <c r="E41">
-        <v>131.0</v>
+        <v>131</v>
       </c>
       <c r="F41">
-        <v>160.0</v>
+        <v>160</v>
       </c>
       <c r="G41">
-        <v>32.0</v>
+        <v>32</v>
       </c>
       <c r="H41">
-        <v>4.1</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="I41">
-        <v>3040.0</v>
+        <v>3040</v>
       </c>
       <c r="J41">
-        <v>1155.0</v>
+        <v>1155</v>
       </c>
       <c r="K41">
-        <v>4195.0</v>
+        <v>4195</v>
       </c>
       <c r="L41">
-        <v>3040.0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:16" dyDescent="0.2">
+        <v>3040</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>7</v>
       </c>
       <c r="B42" s="8">
         <v>9</v>
       </c>
-      <c r="C42" t="s" s="1">
+      <c r="C42" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="D42" t="s" s="1">
+      <c r="D42" s="1" t="s">
         <v>59</v>
       </c>
       <c r="E42">
-        <v>110.0</v>
+        <v>110</v>
       </c>
       <c r="F42">
-        <v>146.0</v>
+        <v>146</v>
       </c>
       <c r="G42">
         <v>29.2</v>
@@ -2499,36 +2499,36 @@
         <v>3.8</v>
       </c>
       <c r="I42">
-        <v>2774.0</v>
+        <v>2774</v>
       </c>
       <c r="J42">
-        <v>943.0</v>
+        <v>943</v>
       </c>
       <c r="K42">
-        <v>3717.0</v>
+        <v>3717</v>
       </c>
       <c r="L42">
-        <v>2774.0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:16" dyDescent="0.2">
+        <v>2774</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>7</v>
       </c>
       <c r="B43" s="8">
         <v>10</v>
       </c>
-      <c r="C43" t="s" s="1">
+      <c r="C43" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="D43" t="s" s="1">
+      <c r="D43" s="1" t="s">
         <v>60</v>
       </c>
       <c r="E43">
-        <v>280.0</v>
+        <v>280</v>
       </c>
       <c r="F43">
-        <v>187.0</v>
+        <v>187</v>
       </c>
       <c r="G43">
         <v>37.4</v>
@@ -2537,36 +2537,36 @@
         <v>7.5</v>
       </c>
       <c r="I43">
-        <v>3553.0</v>
+        <v>3553</v>
       </c>
       <c r="J43">
-        <v>2830.0</v>
+        <v>2830</v>
       </c>
       <c r="K43">
-        <v>6383.0</v>
+        <v>6383</v>
       </c>
       <c r="L43">
-        <v>3553.0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:16" dyDescent="0.2">
+        <v>3553</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>8</v>
       </c>
       <c r="B44" s="8">
         <v>9</v>
       </c>
-      <c r="C44" t="s" s="1">
+      <c r="C44" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D44" t="s" s="1">
+      <c r="D44" s="1" t="s">
         <v>59</v>
       </c>
       <c r="E44">
-        <v>26.0</v>
+        <v>26</v>
       </c>
       <c r="F44">
-        <v>19.0</v>
+        <v>19</v>
       </c>
       <c r="G44">
         <v>3.8</v>
@@ -2575,95 +2575,95 @@
         <v>6.8</v>
       </c>
       <c r="I44">
-        <v>361.0</v>
+        <v>361</v>
       </c>
       <c r="J44">
-        <v>259.0</v>
+        <v>259</v>
       </c>
       <c r="K44">
-        <v>620.0</v>
+        <v>620</v>
       </c>
       <c r="L44">
-        <v>361.0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:16" dyDescent="0.2">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>8</v>
       </c>
       <c r="B45" s="8">
         <v>10</v>
       </c>
-      <c r="C45" t="s" s="1">
+      <c r="C45" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D45" t="s" s="1">
+      <c r="D45" s="1" t="s">
         <v>60</v>
       </c>
       <c r="E45">
-        <v>163.0</v>
+        <v>163</v>
       </c>
       <c r="F45">
-        <v>164.0</v>
+        <v>164</v>
       </c>
       <c r="G45">
-        <v>32.8</v>
+        <v>32.799999999999997</v>
       </c>
       <c r="H45">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="I45">
-        <v>3116.0</v>
+        <v>3116</v>
       </c>
       <c r="J45">
-        <v>1519.0</v>
+        <v>1519</v>
       </c>
       <c r="K45">
-        <v>4635.0</v>
+        <v>4635</v>
       </c>
       <c r="L45">
-        <v>3116.0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:16" dyDescent="0.2">
+        <v>3116</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>9</v>
       </c>
       <c r="B46" s="8">
         <v>10</v>
       </c>
-      <c r="C46" t="s" s="1">
+      <c r="C46" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D46" t="s" s="1">
+      <c r="D46" s="1" t="s">
         <v>60</v>
       </c>
       <c r="E46">
-        <v>175.0</v>
+        <v>175</v>
       </c>
       <c r="F46">
-        <v>170.0</v>
+        <v>170</v>
       </c>
       <c r="G46">
-        <v>34.0</v>
+        <v>34</v>
       </c>
       <c r="H46">
-        <v>5.1</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="I46">
-        <v>3230.0</v>
+        <v>3230</v>
       </c>
       <c r="J46">
-        <v>1645.0</v>
+        <v>1645</v>
       </c>
       <c r="K46">
-        <v>4875.0</v>
+        <v>4875</v>
       </c>
       <c r="L46">
-        <v>3230.0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:16" dyDescent="0.2">
+        <v>3230</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>1</v>
       </c>
@@ -2697,7 +2697,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:16" dyDescent="0.2">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>2</v>
       </c>
@@ -2731,7 +2731,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:16" dyDescent="0.2">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>3</v>
       </c>
@@ -2765,7 +2765,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:16" dyDescent="0.2">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>4</v>
       </c>
@@ -2799,7 +2799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:16" dyDescent="0.2">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>5</v>
       </c>
@@ -2833,7 +2833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:16" dyDescent="0.2">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>6</v>
       </c>
@@ -2865,7 +2865,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:16" dyDescent="0.2">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>7</v>
       </c>
@@ -2897,7 +2897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:16" dyDescent="0.2">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>8</v>
       </c>
@@ -2929,7 +2929,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:16" dyDescent="0.2">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>9</v>
       </c>
@@ -2961,7 +2961,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:16" dyDescent="0.2">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>10</v>
       </c>
@@ -2993,13 +2993,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:16" dyDescent="0.2">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G57" s="2"/>
     </row>
-    <row r="58" spans="1:16" dyDescent="0.2">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G58" s="1"/>
     </row>
-    <row r="59" spans="1:16" dyDescent="0.2">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G59" s="1"/>
     </row>
   </sheetData>

--- a/inputData/Parameters.xlsx
+++ b/inputData/Parameters.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="61">
   <si>
     <t>cap_u</t>
   </si>
@@ -653,13 +653,13 @@
     <col min="2" max="2" width="10.83203125" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" dyDescent="0.2">
       <c r="A1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:4" dyDescent="0.2">
+      <c r="A2" t="s" s="1">
         <v>20</v>
       </c>
       <c r="B2" s="4">
@@ -669,7 +669,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" dyDescent="0.2">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -680,7 +680,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" dyDescent="0.2">
       <c r="A4" t="s">
         <v>46</v>
       </c>
@@ -691,7 +691,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" dyDescent="0.2">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -702,7 +702,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4" dyDescent="0.2">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -713,7 +713,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4" dyDescent="0.2">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -724,7 +724,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4" dyDescent="0.2">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -736,7 +736,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4" dyDescent="0.2">
       <c r="A9" t="s">
         <v>0</v>
       </c>
@@ -747,7 +747,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4" dyDescent="0.2">
       <c r="A10" t="s">
         <v>1</v>
       </c>
@@ -758,7 +758,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4" dyDescent="0.2">
       <c r="A11" t="s">
         <v>45</v>
       </c>
@@ -769,7 +769,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4" dyDescent="0.2">
       <c r="A12" t="s">
         <v>2</v>
       </c>
@@ -780,18 +780,18 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4" dyDescent="0.2">
       <c r="A13" t="s">
         <v>42</v>
       </c>
       <c r="B13" s="4">
         <v>20</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="D13" t="s" s="3">
         <v>44</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:4" dyDescent="0.2">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -799,11 +799,11 @@
         <f>2.11*B20</f>
         <v>2.11</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" t="s" s="3">
         <v>39</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:4" dyDescent="0.2">
       <c r="A15" t="s">
         <v>4</v>
       </c>
@@ -811,11 +811,11 @@
         <f>30/B20</f>
         <v>30</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="D15" t="s" s="3">
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:4" dyDescent="0.2">
       <c r="A16" t="s">
         <v>5</v>
       </c>
@@ -823,11 +823,11 @@
         <f>20/B20</f>
         <v>20</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="D16" t="s" s="3">
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:4" dyDescent="0.2">
       <c r="A17" t="s">
         <v>6</v>
       </c>
@@ -835,18 +835,18 @@
         <f>120/B20</f>
         <v>120</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="D17" t="s" s="3">
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:4" dyDescent="0.2">
       <c r="A20" t="s">
         <v>41</v>
       </c>
       <c r="B20" s="4">
         <v>1</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="D20" t="s" s="3">
         <v>48</v>
       </c>
     </row>
@@ -869,44 +869,44 @@
     <col min="8" max="8" width="18.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:16" dyDescent="0.2">
+      <c r="A1" t="s" s="9">
         <v>36</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" t="s" s="5">
         <v>37</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" t="s" s="5">
         <v>49</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" t="s" s="5">
         <v>50</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" t="s" s="5">
         <v>22</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" t="s" s="5">
         <v>23</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" t="s" s="5">
         <v>24</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" t="s" s="5">
         <v>25</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" t="s" s="5">
         <v>26</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" t="s" s="5">
         <v>27</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="K1" t="s" s="5">
         <v>38</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="L1" t="s" s="5">
         <v>28</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="N1" t="s" s="6">
         <v>19</v>
       </c>
       <c r="O1" s="7">
@@ -914,24 +914,24 @@
       </c>
       <c r="P1" s="6"/>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:16" dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" s="8">
         <v>2</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" t="s" s="1">
         <v>51</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" t="s" s="2">
         <v>52</v>
       </c>
       <c r="E2">
-        <v>185</v>
+        <v>185.0</v>
       </c>
       <c r="F2">
-        <v>219</v>
+        <v>219.0</v>
       </c>
       <c r="G2">
         <v>43.8</v>
@@ -940,16 +940,16 @@
         <v>4.2</v>
       </c>
       <c r="I2">
-        <v>4161</v>
+        <v>4161.0</v>
       </c>
       <c r="J2">
-        <v>1647</v>
+        <v>1647.0</v>
       </c>
       <c r="K2">
-        <v>5808</v>
+        <v>5808.0</v>
       </c>
       <c r="L2">
-        <v>4161</v>
+        <v>4161.0</v>
       </c>
       <c r="N2" t="s">
         <v>29</v>
@@ -961,42 +961,42 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:16" dyDescent="0.2">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" s="8">
         <v>3</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" t="s" s="1">
         <v>51</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" t="s" s="2">
         <v>53</v>
       </c>
       <c r="E3">
-        <v>82</v>
+        <v>82.0</v>
       </c>
       <c r="F3">
-        <v>88</v>
+        <v>88.0</v>
       </c>
       <c r="G3">
-        <v>17.600000000000001</v>
+        <v>17.6</v>
       </c>
       <c r="H3">
         <v>4.7</v>
       </c>
       <c r="I3">
-        <v>1672</v>
+        <v>1672.0</v>
       </c>
       <c r="J3">
-        <v>751</v>
+        <v>751.0</v>
       </c>
       <c r="K3">
-        <v>2423</v>
+        <v>2423.0</v>
       </c>
       <c r="L3">
-        <v>1672</v>
+        <v>1672.0</v>
       </c>
       <c r="N3" t="s">
         <v>31</v>
@@ -1009,24 +1009,24 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:16" dyDescent="0.2">
       <c r="A4">
         <v>1</v>
       </c>
       <c r="B4" s="8">
         <v>4</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" t="s" s="1">
         <v>51</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" t="s" s="1">
         <v>54</v>
       </c>
       <c r="E4">
-        <v>228</v>
+        <v>228.0</v>
       </c>
       <c r="F4">
-        <v>147</v>
+        <v>147.0</v>
       </c>
       <c r="G4">
         <v>29.4</v>
@@ -1035,16 +1035,16 @@
         <v>7.8</v>
       </c>
       <c r="I4">
-        <v>2793</v>
+        <v>2793.0</v>
       </c>
       <c r="J4">
-        <v>2317</v>
+        <v>2317.0</v>
       </c>
       <c r="K4">
-        <v>5110</v>
+        <v>5110.0</v>
       </c>
       <c r="L4">
-        <v>2793</v>
+        <v>2793.0</v>
       </c>
       <c r="N4" t="s">
         <v>33</v>
@@ -1053,24 +1053,24 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" dyDescent="0.2">
       <c r="A5">
         <v>1</v>
       </c>
       <c r="B5" s="8">
         <v>5</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" t="s" s="1">
         <v>51</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" t="s" s="1">
         <v>55</v>
       </c>
       <c r="E5">
-        <v>126</v>
+        <v>126.0</v>
       </c>
       <c r="F5">
-        <v>147</v>
+        <v>147.0</v>
       </c>
       <c r="G5">
         <v>29.4</v>
@@ -1079,16 +1079,16 @@
         <v>4.3</v>
       </c>
       <c r="I5">
-        <v>2793</v>
+        <v>2793.0</v>
       </c>
       <c r="J5">
-        <v>1127</v>
+        <v>1127.0</v>
       </c>
       <c r="K5">
-        <v>3920</v>
+        <v>3920.0</v>
       </c>
       <c r="L5">
-        <v>2793</v>
+        <v>2793.0</v>
       </c>
       <c r="N5" t="s">
         <v>34</v>
@@ -1100,24 +1100,24 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" dyDescent="0.2">
       <c r="A6">
         <v>1</v>
       </c>
       <c r="B6" s="8">
         <v>6</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" t="s" s="1">
         <v>51</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" t="s" s="1">
         <v>56</v>
       </c>
       <c r="E6">
-        <v>205</v>
+        <v>205.0</v>
       </c>
       <c r="F6">
-        <v>197</v>
+        <v>197.0</v>
       </c>
       <c r="G6">
         <v>39.4</v>
@@ -1126,37 +1126,37 @@
         <v>5.2</v>
       </c>
       <c r="I6">
-        <v>3743</v>
+        <v>3743.0</v>
       </c>
       <c r="J6">
-        <v>1932</v>
+        <v>1932.0</v>
       </c>
       <c r="K6">
-        <v>5675</v>
+        <v>5675.0</v>
       </c>
       <c r="L6">
-        <v>3743</v>
+        <v>3743.0</v>
       </c>
       <c r="O6" s="4"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" dyDescent="0.2">
       <c r="A7">
         <v>1</v>
       </c>
       <c r="B7" s="8">
         <v>7</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" t="s" s="1">
         <v>51</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" t="s" s="1">
         <v>57</v>
       </c>
       <c r="E7">
-        <v>263</v>
+        <v>263.0</v>
       </c>
       <c r="F7">
-        <v>227</v>
+        <v>227.0</v>
       </c>
       <c r="G7">
         <v>45.4</v>
@@ -1165,154 +1165,154 @@
         <v>5.8</v>
       </c>
       <c r="I7">
-        <v>4313</v>
+        <v>4313.0</v>
       </c>
       <c r="J7">
-        <v>2539</v>
+        <v>2539.0</v>
       </c>
       <c r="K7">
-        <v>6852</v>
+        <v>6852.0</v>
       </c>
       <c r="L7">
-        <v>4313</v>
+        <v>4313.0</v>
       </c>
       <c r="O7" s="4"/>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" dyDescent="0.2">
       <c r="A8">
         <v>1</v>
       </c>
       <c r="B8" s="8">
         <v>8</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" t="s" s="1">
         <v>51</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" t="s" s="1">
         <v>58</v>
       </c>
       <c r="E8">
-        <v>143</v>
+        <v>143.0</v>
       </c>
       <c r="F8">
-        <v>184</v>
+        <v>184.0</v>
       </c>
       <c r="G8">
-        <v>36.799999999999997</v>
+        <v>36.8</v>
       </c>
       <c r="H8">
         <v>3.9</v>
       </c>
       <c r="I8">
-        <v>3496</v>
+        <v>3496.0</v>
       </c>
       <c r="J8">
-        <v>1239</v>
+        <v>1239.0</v>
       </c>
       <c r="K8">
-        <v>4735</v>
+        <v>4735.0</v>
       </c>
       <c r="L8">
-        <v>3496</v>
+        <v>3496.0</v>
       </c>
       <c r="O8" s="4"/>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:16" dyDescent="0.2">
       <c r="A9">
         <v>1</v>
       </c>
       <c r="B9" s="8">
         <v>9</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" t="s" s="1">
         <v>51</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" t="s" s="1">
         <v>59</v>
       </c>
       <c r="E9">
-        <v>155</v>
+        <v>155.0</v>
       </c>
       <c r="F9">
-        <v>193</v>
+        <v>193.0</v>
       </c>
       <c r="G9">
         <v>38.6</v>
       </c>
       <c r="H9">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="I9">
-        <v>3667</v>
+        <v>3667.0</v>
       </c>
       <c r="J9">
-        <v>1358</v>
+        <v>1358.0</v>
       </c>
       <c r="K9">
-        <v>5025</v>
+        <v>5025.0</v>
       </c>
       <c r="L9">
-        <v>3667</v>
+        <v>3667.0</v>
       </c>
       <c r="O9" s="4"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:16" dyDescent="0.2">
       <c r="A10">
         <v>1</v>
       </c>
       <c r="B10" s="8">
         <v>10</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" t="s" s="1">
         <v>51</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" t="s" s="1">
         <v>60</v>
       </c>
       <c r="E10">
-        <v>42</v>
+        <v>42.0</v>
       </c>
       <c r="F10">
-        <v>41</v>
+        <v>41.0</v>
       </c>
       <c r="G10">
-        <v>8.1999999999999993</v>
+        <v>8.2</v>
       </c>
       <c r="H10">
-        <v>5.0999999999999996</v>
+        <v>5.1</v>
       </c>
       <c r="I10">
-        <v>779</v>
+        <v>779.0</v>
       </c>
       <c r="J10">
-        <v>394</v>
+        <v>394.0</v>
       </c>
       <c r="K10">
-        <v>1173</v>
+        <v>1173.0</v>
       </c>
       <c r="L10">
-        <v>779</v>
+        <v>779.0</v>
       </c>
       <c r="O10" s="4"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:16" dyDescent="0.2">
       <c r="A11">
         <v>2</v>
       </c>
       <c r="B11" s="8">
         <v>3</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" t="s" s="2">
         <v>52</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" t="s" s="2">
         <v>53</v>
       </c>
       <c r="E11">
-        <v>173</v>
+        <v>173.0</v>
       </c>
       <c r="F11">
-        <v>131</v>
+        <v>131.0</v>
       </c>
       <c r="G11">
         <v>26.2</v>
@@ -1321,226 +1321,226 @@
         <v>6.6</v>
       </c>
       <c r="I11">
-        <v>2489</v>
+        <v>2489.0</v>
       </c>
       <c r="J11">
-        <v>1713</v>
+        <v>1713.0</v>
       </c>
       <c r="K11">
-        <v>4202</v>
+        <v>4202.0</v>
       </c>
       <c r="L11">
-        <v>2489</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+        <v>2489.0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" dyDescent="0.2">
       <c r="A12">
         <v>2</v>
       </c>
       <c r="B12" s="8">
         <v>4</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" t="s" s="2">
         <v>52</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D12" t="s" s="1">
         <v>54</v>
       </c>
       <c r="E12">
-        <v>103</v>
+        <v>103.0</v>
       </c>
       <c r="F12">
-        <v>110</v>
+        <v>110.0</v>
       </c>
       <c r="G12">
-        <v>22</v>
+        <v>22.0</v>
       </c>
       <c r="H12">
         <v>4.7</v>
       </c>
       <c r="I12">
-        <v>2090</v>
+        <v>2090.0</v>
       </c>
       <c r="J12">
-        <v>945</v>
+        <v>945.0</v>
       </c>
       <c r="K12">
-        <v>3035</v>
+        <v>3035.0</v>
       </c>
       <c r="L12">
-        <v>2090</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+        <v>2090.0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" dyDescent="0.2">
       <c r="A13">
         <v>2</v>
       </c>
       <c r="B13" s="8">
         <v>5</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" t="s" s="2">
         <v>52</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D13" t="s" s="1">
         <v>55</v>
       </c>
       <c r="E13">
-        <v>89</v>
+        <v>89.0</v>
       </c>
       <c r="F13">
-        <v>80</v>
+        <v>80.0</v>
       </c>
       <c r="G13">
-        <v>16</v>
+        <v>16.0</v>
       </c>
       <c r="H13">
         <v>5.6</v>
       </c>
       <c r="I13">
-        <v>1520</v>
+        <v>1520.0</v>
       </c>
       <c r="J13">
-        <v>852</v>
+        <v>852.0</v>
       </c>
       <c r="K13">
-        <v>2372</v>
+        <v>2372.0</v>
       </c>
       <c r="L13">
-        <v>1520</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+        <v>1520.0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" dyDescent="0.2">
       <c r="A14">
         <v>2</v>
       </c>
       <c r="B14" s="8">
         <v>6</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" t="s" s="2">
         <v>52</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="D14" t="s" s="1">
         <v>56</v>
       </c>
       <c r="E14">
-        <v>100</v>
+        <v>100.0</v>
       </c>
       <c r="F14">
-        <v>98</v>
+        <v>98.0</v>
       </c>
       <c r="G14">
-        <v>19.600000000000001</v>
+        <v>19.6</v>
       </c>
       <c r="H14">
-        <v>5.0999999999999996</v>
+        <v>5.1</v>
       </c>
       <c r="I14">
-        <v>1862</v>
+        <v>1862.0</v>
       </c>
       <c r="J14">
-        <v>938</v>
+        <v>938.0</v>
       </c>
       <c r="K14">
-        <v>2800</v>
+        <v>2800.0</v>
       </c>
       <c r="L14">
-        <v>1862</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+        <v>1862.0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" dyDescent="0.2">
       <c r="A15">
         <v>2</v>
       </c>
       <c r="B15" s="8">
         <v>7</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" t="s" s="2">
         <v>52</v>
       </c>
-      <c r="D15" s="11" t="s">
+      <c r="D15" t="s" s="11">
         <v>57</v>
       </c>
       <c r="E15">
-        <v>138</v>
+        <v>138.0</v>
       </c>
       <c r="F15">
-        <v>151</v>
+        <v>151.0</v>
       </c>
       <c r="G15">
         <v>30.2</v>
       </c>
       <c r="H15">
-        <v>4.5999999999999996</v>
+        <v>4.6</v>
       </c>
       <c r="I15">
-        <v>2869</v>
+        <v>2869.0</v>
       </c>
       <c r="J15">
-        <v>1258</v>
+        <v>1258.0</v>
       </c>
       <c r="K15">
-        <v>4127</v>
+        <v>4127.0</v>
       </c>
       <c r="L15">
-        <v>2869</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+        <v>2869.0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" dyDescent="0.2">
       <c r="A16">
         <v>2</v>
       </c>
       <c r="B16" s="8">
         <v>8</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" t="s" s="2">
         <v>52</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="D16" t="s" s="1">
         <v>58</v>
       </c>
       <c r="E16">
-        <v>55</v>
+        <v>55.0</v>
       </c>
       <c r="F16">
-        <v>40</v>
+        <v>40.0</v>
       </c>
       <c r="G16">
-        <v>8</v>
+        <v>8.0</v>
       </c>
       <c r="H16">
         <v>6.9</v>
       </c>
       <c r="I16">
-        <v>760</v>
+        <v>760.0</v>
       </c>
       <c r="J16">
-        <v>548</v>
+        <v>548.0</v>
       </c>
       <c r="K16">
-        <v>1308</v>
+        <v>1308.0</v>
       </c>
       <c r="L16">
-        <v>760</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
+        <v>760.0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" dyDescent="0.2">
       <c r="A17">
         <v>2</v>
       </c>
       <c r="B17" s="8">
         <v>9</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" t="s" s="2">
         <v>52</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="D17" t="s" s="1">
         <v>59</v>
       </c>
       <c r="E17">
-        <v>38</v>
+        <v>38.0</v>
       </c>
       <c r="F17">
-        <v>26</v>
+        <v>26.0</v>
       </c>
       <c r="G17">
         <v>5.2</v>
@@ -1549,150 +1549,150 @@
         <v>7.3</v>
       </c>
       <c r="I17">
-        <v>494</v>
+        <v>494.0</v>
       </c>
       <c r="J17">
-        <v>383</v>
+        <v>383.0</v>
       </c>
       <c r="K17">
-        <v>877</v>
+        <v>877.0</v>
       </c>
       <c r="L17">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
+        <v>494.0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" dyDescent="0.2">
       <c r="A18">
         <v>2</v>
       </c>
       <c r="B18" s="8">
         <v>10</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" t="s" s="2">
         <v>52</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="D18" t="s" s="1">
         <v>60</v>
       </c>
       <c r="E18">
-        <v>205</v>
+        <v>205.0</v>
       </c>
       <c r="F18">
-        <v>196</v>
+        <v>196.0</v>
       </c>
       <c r="G18">
-        <v>39.200000000000003</v>
+        <v>39.2</v>
       </c>
       <c r="H18">
         <v>5.2</v>
       </c>
       <c r="I18">
-        <v>3724</v>
+        <v>3724.0</v>
       </c>
       <c r="J18">
-        <v>1934</v>
+        <v>1934.0</v>
       </c>
       <c r="K18">
-        <v>5658</v>
+        <v>5658.0</v>
       </c>
       <c r="L18">
-        <v>3724</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
+        <v>3724.0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" dyDescent="0.2">
       <c r="A19">
         <v>3</v>
       </c>
       <c r="B19" s="8">
         <v>4</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" t="s" s="2">
         <v>53</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="D19" t="s" s="1">
         <v>54</v>
       </c>
       <c r="E19">
-        <v>215</v>
+        <v>215.0</v>
       </c>
       <c r="F19">
-        <v>77</v>
+        <v>77.0</v>
       </c>
       <c r="G19">
         <v>15.4</v>
       </c>
       <c r="H19">
-        <v>14</v>
+        <v>14.0</v>
       </c>
       <c r="I19">
-        <v>1463</v>
+        <v>1463.0</v>
       </c>
       <c r="J19">
-        <v>2329</v>
+        <v>2329.0</v>
       </c>
       <c r="K19">
-        <v>3792</v>
+        <v>3792.0</v>
       </c>
       <c r="L19">
-        <v>2329</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
+        <v>2329.0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" dyDescent="0.2">
       <c r="A20">
         <v>3</v>
       </c>
       <c r="B20" s="8">
         <v>5</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C20" t="s" s="2">
         <v>53</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="D20" t="s" s="1">
         <v>55</v>
       </c>
       <c r="E20">
-        <v>113</v>
+        <v>113.0</v>
       </c>
       <c r="F20">
-        <v>63</v>
+        <v>63.0</v>
       </c>
       <c r="G20">
         <v>12.6</v>
       </c>
       <c r="H20">
-        <v>9</v>
+        <v>9.0</v>
       </c>
       <c r="I20">
-        <v>1197</v>
+        <v>1197.0</v>
       </c>
       <c r="J20">
-        <v>1171</v>
+        <v>1171.0</v>
       </c>
       <c r="K20">
-        <v>2368</v>
+        <v>2368.0</v>
       </c>
       <c r="L20">
-        <v>1197</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
+        <v>1197.0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" dyDescent="0.2">
       <c r="A21">
         <v>3</v>
       </c>
       <c r="B21" s="8">
         <v>6</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C21" t="s" s="2">
         <v>53</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="D21" t="s" s="1">
         <v>56</v>
       </c>
       <c r="E21">
-        <v>192</v>
+        <v>192.0</v>
       </c>
       <c r="F21">
-        <v>126</v>
+        <v>126.0</v>
       </c>
       <c r="G21">
         <v>25.2</v>
@@ -1701,36 +1701,36 @@
         <v>7.6</v>
       </c>
       <c r="I21">
-        <v>2394</v>
+        <v>2394.0</v>
       </c>
       <c r="J21">
-        <v>1946</v>
+        <v>1946.0</v>
       </c>
       <c r="K21">
-        <v>4340</v>
+        <v>4340.0</v>
       </c>
       <c r="L21">
-        <v>2394</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
+        <v>2394.0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" dyDescent="0.2">
       <c r="A22">
         <v>3</v>
       </c>
       <c r="B22" s="8">
         <v>7</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C22" t="s" s="2">
         <v>53</v>
       </c>
-      <c r="D22" s="11" t="s">
+      <c r="D22" t="s" s="11">
         <v>57</v>
       </c>
       <c r="E22">
-        <v>250</v>
+        <v>250.0</v>
       </c>
       <c r="F22">
-        <v>167</v>
+        <v>167.0</v>
       </c>
       <c r="G22">
         <v>33.4</v>
@@ -1739,112 +1739,112 @@
         <v>7.5</v>
       </c>
       <c r="I22">
-        <v>3173</v>
+        <v>3173.0</v>
       </c>
       <c r="J22">
-        <v>2527</v>
+        <v>2527.0</v>
       </c>
       <c r="K22">
-        <v>5700</v>
+        <v>5700.0</v>
       </c>
       <c r="L22">
-        <v>3173</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
+        <v>3173.0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" dyDescent="0.2">
       <c r="A23">
         <v>3</v>
       </c>
       <c r="B23" s="8">
         <v>8</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C23" t="s" s="2">
         <v>53</v>
       </c>
-      <c r="D23" s="1" t="s">
+      <c r="D23" t="s" s="1">
         <v>58</v>
       </c>
       <c r="E23">
-        <v>130</v>
+        <v>130.0</v>
       </c>
       <c r="F23">
-        <v>97</v>
+        <v>97.0</v>
       </c>
       <c r="G23">
-        <v>19.399999999999999</v>
+        <v>19.4</v>
       </c>
       <c r="H23">
         <v>6.7</v>
       </c>
       <c r="I23">
-        <v>1843</v>
+        <v>1843.0</v>
       </c>
       <c r="J23">
-        <v>1290</v>
+        <v>1290.0</v>
       </c>
       <c r="K23">
-        <v>3133</v>
+        <v>3133.0</v>
       </c>
       <c r="L23">
-        <v>1843</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
+        <v>1843.0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" dyDescent="0.2">
       <c r="A24">
         <v>3</v>
       </c>
       <c r="B24" s="8">
         <v>9</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C24" t="s" s="2">
         <v>53</v>
       </c>
-      <c r="D24" s="1" t="s">
+      <c r="D24" t="s" s="1">
         <v>59</v>
       </c>
       <c r="E24">
-        <v>142</v>
+        <v>142.0</v>
       </c>
       <c r="F24">
-        <v>105</v>
+        <v>105.0</v>
       </c>
       <c r="G24">
-        <v>21</v>
+        <v>21.0</v>
       </c>
       <c r="H24">
         <v>6.8</v>
       </c>
       <c r="I24">
-        <v>1995</v>
+        <v>1995.0</v>
       </c>
       <c r="J24">
-        <v>1412</v>
+        <v>1412.0</v>
       </c>
       <c r="K24">
-        <v>3407</v>
+        <v>3407.0</v>
       </c>
       <c r="L24">
-        <v>1995</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
+        <v>1995.0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" dyDescent="0.2">
       <c r="A25">
         <v>3</v>
       </c>
       <c r="B25" s="8">
         <v>10</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C25" t="s" s="2">
         <v>53</v>
       </c>
-      <c r="D25" s="1" t="s">
+      <c r="D25" t="s" s="1">
         <v>60</v>
       </c>
       <c r="E25">
-        <v>89</v>
+        <v>89.0</v>
       </c>
       <c r="F25">
-        <v>68</v>
+        <v>68.0</v>
       </c>
       <c r="G25">
         <v>13.6</v>
@@ -1853,188 +1853,188 @@
         <v>6.5</v>
       </c>
       <c r="I25">
-        <v>1292</v>
+        <v>1292.0</v>
       </c>
       <c r="J25">
-        <v>880</v>
+        <v>880.0</v>
       </c>
       <c r="K25">
-        <v>2172</v>
+        <v>2172.0</v>
       </c>
       <c r="L25">
-        <v>1292</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
+        <v>1292.0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" dyDescent="0.2">
       <c r="A26">
         <v>4</v>
       </c>
       <c r="B26" s="8">
         <v>5</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="C26" t="s" s="1">
         <v>54</v>
       </c>
-      <c r="D26" s="1" t="s">
+      <c r="D26" t="s" s="1">
         <v>55</v>
       </c>
       <c r="E26">
-        <v>130</v>
+        <v>130.0</v>
       </c>
       <c r="F26">
-        <v>93</v>
+        <v>93.0</v>
       </c>
       <c r="G26">
-        <v>18.600000000000001</v>
+        <v>18.6</v>
       </c>
       <c r="H26">
-        <v>7</v>
+        <v>7.0</v>
       </c>
       <c r="I26">
-        <v>1767</v>
+        <v>1767.0</v>
       </c>
       <c r="J26">
-        <v>1300</v>
+        <v>1300.0</v>
       </c>
       <c r="K26">
-        <v>3067</v>
+        <v>3067.0</v>
       </c>
       <c r="L26">
-        <v>1767</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
+        <v>1767.0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" dyDescent="0.2">
       <c r="A27">
         <v>4</v>
       </c>
       <c r="B27" s="8">
         <v>6</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="C27" t="s" s="1">
         <v>54</v>
       </c>
-      <c r="D27" s="1" t="s">
+      <c r="D27" t="s" s="1">
         <v>56</v>
       </c>
       <c r="E27">
-        <v>149</v>
+        <v>149.0</v>
       </c>
       <c r="F27">
-        <v>161</v>
+        <v>161.0</v>
       </c>
       <c r="G27">
-        <v>32.200000000000003</v>
+        <v>32.2</v>
       </c>
       <c r="H27">
-        <v>4.5999999999999996</v>
+        <v>4.6</v>
       </c>
       <c r="I27">
-        <v>3059</v>
+        <v>3059.0</v>
       </c>
       <c r="J27">
-        <v>1363</v>
+        <v>1363.0</v>
       </c>
       <c r="K27">
-        <v>4422</v>
+        <v>4422.0</v>
       </c>
       <c r="L27">
-        <v>3059</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
+        <v>3059.0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" dyDescent="0.2">
       <c r="A28">
         <v>4</v>
       </c>
       <c r="B28" s="8">
         <v>7</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="C28" t="s" s="1">
         <v>54</v>
       </c>
-      <c r="D28" s="11" t="s">
+      <c r="D28" t="s" s="11">
         <v>57</v>
       </c>
       <c r="E28">
-        <v>93</v>
+        <v>93.0</v>
       </c>
       <c r="F28">
-        <v>90</v>
+        <v>90.0</v>
       </c>
       <c r="G28">
-        <v>18</v>
+        <v>18.0</v>
       </c>
       <c r="H28">
         <v>5.2</v>
       </c>
       <c r="I28">
-        <v>1710</v>
+        <v>1710.0</v>
       </c>
       <c r="J28">
-        <v>875</v>
+        <v>875.0</v>
       </c>
       <c r="K28">
-        <v>2585</v>
+        <v>2585.0</v>
       </c>
       <c r="L28">
-        <v>1710</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
+        <v>1710.0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" dyDescent="0.2">
       <c r="A29">
         <v>4</v>
       </c>
       <c r="B29" s="8">
         <v>8</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="C29" t="s" s="1">
         <v>54</v>
       </c>
-      <c r="D29" s="1" t="s">
+      <c r="D29" t="s" s="1">
         <v>58</v>
       </c>
       <c r="E29">
-        <v>97</v>
+        <v>97.0</v>
       </c>
       <c r="F29">
-        <v>97</v>
+        <v>97.0</v>
       </c>
       <c r="G29">
-        <v>19.399999999999999</v>
+        <v>19.4</v>
       </c>
       <c r="H29">
-        <v>5</v>
+        <v>5.0</v>
       </c>
       <c r="I29">
-        <v>1843</v>
+        <v>1843.0</v>
       </c>
       <c r="J29">
-        <v>905</v>
+        <v>905.0</v>
       </c>
       <c r="K29">
-        <v>2748</v>
+        <v>2748.0</v>
       </c>
       <c r="L29">
-        <v>1843</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
+        <v>1843.0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" dyDescent="0.2">
       <c r="A30">
         <v>4</v>
       </c>
       <c r="B30" s="8">
         <v>9</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="C30" t="s" s="1">
         <v>54</v>
       </c>
-      <c r="D30" s="1" t="s">
+      <c r="D30" t="s" s="1">
         <v>59</v>
       </c>
       <c r="E30">
-        <v>76</v>
+        <v>76.0</v>
       </c>
       <c r="F30">
-        <v>91</v>
+        <v>91.0</v>
       </c>
       <c r="G30">
         <v>18.2</v>
@@ -2043,226 +2043,226 @@
         <v>4.2</v>
       </c>
       <c r="I30">
-        <v>1729</v>
+        <v>1729.0</v>
       </c>
       <c r="J30">
-        <v>674</v>
+        <v>674.0</v>
       </c>
       <c r="K30">
-        <v>2403</v>
+        <v>2403.0</v>
       </c>
       <c r="L30">
-        <v>1729</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
+        <v>1729.0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" dyDescent="0.2">
       <c r="A31">
         <v>4</v>
       </c>
       <c r="B31" s="8">
         <v>10</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C31" t="s" s="1">
         <v>54</v>
       </c>
-      <c r="D31" s="1" t="s">
+      <c r="D31" t="s" s="1">
         <v>60</v>
       </c>
       <c r="E31">
-        <v>246</v>
+        <v>246.0</v>
       </c>
       <c r="F31">
-        <v>110</v>
+        <v>110.0</v>
       </c>
       <c r="G31">
-        <v>22</v>
+        <v>22.0</v>
       </c>
       <c r="H31">
         <v>11.2</v>
       </c>
       <c r="I31">
-        <v>2090</v>
+        <v>2090.0</v>
       </c>
       <c r="J31">
-        <v>2613</v>
+        <v>2613.0</v>
       </c>
       <c r="K31">
-        <v>4703</v>
+        <v>4703.0</v>
       </c>
       <c r="L31">
-        <v>2613</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
+        <v>2613.0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" dyDescent="0.2">
       <c r="A32">
         <v>5</v>
       </c>
       <c r="B32" s="8">
         <v>6</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="C32" t="s" s="1">
         <v>55</v>
       </c>
-      <c r="D32" s="1" t="s">
+      <c r="D32" t="s" s="1">
         <v>56</v>
       </c>
       <c r="E32">
-        <v>110</v>
+        <v>110.0</v>
       </c>
       <c r="F32">
-        <v>70</v>
+        <v>70.0</v>
       </c>
       <c r="G32">
-        <v>14</v>
+        <v>14.0</v>
       </c>
       <c r="H32">
         <v>7.9</v>
       </c>
       <c r="I32">
-        <v>1330</v>
+        <v>1330.0</v>
       </c>
       <c r="J32">
-        <v>1120</v>
+        <v>1120.0</v>
       </c>
       <c r="K32">
-        <v>2450</v>
+        <v>2450.0</v>
       </c>
       <c r="L32">
-        <v>1330</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
+        <v>1330.0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" dyDescent="0.2">
       <c r="A33" s="10">
         <v>5</v>
       </c>
       <c r="B33" s="8">
         <v>7</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C33" t="s" s="1">
         <v>55</v>
       </c>
-      <c r="D33" s="11" t="s">
+      <c r="D33" t="s" s="11">
         <v>57</v>
       </c>
       <c r="E33">
-        <v>168</v>
+        <v>168.0</v>
       </c>
       <c r="F33">
-        <v>173</v>
+        <v>173.0</v>
       </c>
       <c r="G33">
         <v>34.6</v>
       </c>
       <c r="H33">
-        <v>4.9000000000000004</v>
+        <v>4.9</v>
       </c>
       <c r="I33">
-        <v>3287</v>
+        <v>3287.0</v>
       </c>
       <c r="J33">
-        <v>1556</v>
+        <v>1556.0</v>
       </c>
       <c r="K33">
-        <v>4843</v>
+        <v>4843.0</v>
       </c>
       <c r="L33">
-        <v>3287</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
+        <v>3287.0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" dyDescent="0.2">
       <c r="A34">
         <v>5</v>
       </c>
       <c r="B34" s="8">
         <v>8</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="C34" t="s" s="1">
         <v>55</v>
       </c>
-      <c r="D34" s="1" t="s">
+      <c r="D34" t="s" s="1">
         <v>58</v>
       </c>
       <c r="E34">
-        <v>48</v>
+        <v>48.0</v>
       </c>
       <c r="F34">
-        <v>40</v>
+        <v>40.0</v>
       </c>
       <c r="G34">
-        <v>8</v>
+        <v>8.0</v>
       </c>
       <c r="H34">
-        <v>6</v>
+        <v>6.0</v>
       </c>
       <c r="I34">
-        <v>760</v>
+        <v>760.0</v>
       </c>
       <c r="J34">
-        <v>467</v>
+        <v>467.0</v>
       </c>
       <c r="K34">
-        <v>1227</v>
+        <v>1227.0</v>
       </c>
       <c r="L34">
-        <v>760</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
+        <v>760.0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" dyDescent="0.2">
       <c r="A35">
         <v>5</v>
       </c>
       <c r="B35" s="8">
         <v>9</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="C35" t="s" s="1">
         <v>55</v>
       </c>
-      <c r="D35" s="1" t="s">
+      <c r="D35" t="s" s="1">
         <v>59</v>
       </c>
       <c r="E35">
-        <v>60</v>
+        <v>60.0</v>
       </c>
       <c r="F35">
-        <v>55</v>
+        <v>55.0</v>
       </c>
       <c r="G35">
-        <v>11</v>
+        <v>11.0</v>
       </c>
       <c r="H35">
         <v>5.5</v>
       </c>
       <c r="I35">
-        <v>1045</v>
+        <v>1045.0</v>
       </c>
       <c r="J35">
-        <v>572</v>
+        <v>572.0</v>
       </c>
       <c r="K35">
-        <v>1617</v>
+        <v>1617.0</v>
       </c>
       <c r="L35">
-        <v>1045</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
+        <v>1045.0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" dyDescent="0.2">
       <c r="A36">
         <v>5</v>
       </c>
       <c r="B36" s="8">
         <v>10</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="C36" t="s" s="1">
         <v>55</v>
       </c>
-      <c r="D36" s="1" t="s">
+      <c r="D36" t="s" s="1">
         <v>60</v>
       </c>
       <c r="E36">
-        <v>145</v>
+        <v>145.0</v>
       </c>
       <c r="F36">
-        <v>131</v>
+        <v>131.0</v>
       </c>
       <c r="G36">
         <v>26.2</v>
@@ -2271,74 +2271,74 @@
         <v>5.5</v>
       </c>
       <c r="I36">
-        <v>2489</v>
+        <v>2489.0</v>
       </c>
       <c r="J36">
-        <v>1386</v>
+        <v>1386.0</v>
       </c>
       <c r="K36">
-        <v>3875</v>
+        <v>3875.0</v>
       </c>
       <c r="L36">
-        <v>2489</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
+        <v>2489.0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" dyDescent="0.2">
       <c r="A37">
         <v>6</v>
       </c>
       <c r="B37" s="8">
         <v>7</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="C37" t="s" s="1">
         <v>56</v>
       </c>
-      <c r="D37" s="11" t="s">
+      <c r="D37" t="s" s="11">
         <v>57</v>
       </c>
       <c r="E37">
-        <v>185</v>
+        <v>185.0</v>
       </c>
       <c r="F37">
-        <v>232</v>
+        <v>232.0</v>
       </c>
       <c r="G37">
         <v>46.4</v>
       </c>
       <c r="H37">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="I37">
-        <v>4408</v>
+        <v>4408.0</v>
       </c>
       <c r="J37">
-        <v>1617</v>
+        <v>1617.0</v>
       </c>
       <c r="K37">
-        <v>6025</v>
+        <v>6025.0</v>
       </c>
       <c r="L37">
-        <v>4408</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
+        <v>4408.0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" dyDescent="0.2">
       <c r="A38">
         <v>6</v>
       </c>
       <c r="B38" s="8">
         <v>8</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="C38" t="s" s="1">
         <v>56</v>
       </c>
-      <c r="D38" s="1" t="s">
+      <c r="D38" t="s" s="1">
         <v>58</v>
       </c>
       <c r="E38">
-        <v>77</v>
+        <v>77.0</v>
       </c>
       <c r="F38">
-        <v>72</v>
+        <v>72.0</v>
       </c>
       <c r="G38">
         <v>14.4</v>
@@ -2347,74 +2347,74 @@
         <v>5.3</v>
       </c>
       <c r="I38">
-        <v>1368</v>
+        <v>1368.0</v>
       </c>
       <c r="J38">
-        <v>730</v>
+        <v>730.0</v>
       </c>
       <c r="K38">
-        <v>2098</v>
+        <v>2098.0</v>
       </c>
       <c r="L38">
-        <v>1368</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
+        <v>1368.0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" dyDescent="0.2">
       <c r="A39">
         <v>6</v>
       </c>
       <c r="B39" s="8">
         <v>9</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="C39" t="s" s="1">
         <v>56</v>
       </c>
-      <c r="D39" s="1" t="s">
+      <c r="D39" t="s" s="1">
         <v>59</v>
       </c>
       <c r="E39">
-        <v>78</v>
+        <v>78.0</v>
       </c>
       <c r="F39">
-        <v>89</v>
+        <v>89.0</v>
       </c>
       <c r="G39">
         <v>17.8</v>
       </c>
       <c r="H39">
-        <v>4.4000000000000004</v>
+        <v>4.4</v>
       </c>
       <c r="I39">
-        <v>1691</v>
+        <v>1691.0</v>
       </c>
       <c r="J39">
-        <v>702</v>
+        <v>702.0</v>
       </c>
       <c r="K39">
-        <v>2393</v>
+        <v>2393.0</v>
       </c>
       <c r="L39">
-        <v>1691</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
+        <v>1691.0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" dyDescent="0.2">
       <c r="A40">
         <v>6</v>
       </c>
       <c r="B40" s="8">
         <v>10</v>
       </c>
-      <c r="C40" s="1" t="s">
+      <c r="C40" t="s" s="1">
         <v>56</v>
       </c>
-      <c r="D40" s="1" t="s">
+      <c r="D40" t="s" s="1">
         <v>60</v>
       </c>
       <c r="E40">
-        <v>224</v>
+        <v>224.0</v>
       </c>
       <c r="F40">
-        <v>192</v>
+        <v>192.0</v>
       </c>
       <c r="G40">
         <v>38.4</v>
@@ -2423,74 +2423,74 @@
         <v>5.8</v>
       </c>
       <c r="I40">
-        <v>3648</v>
+        <v>3648.0</v>
       </c>
       <c r="J40">
-        <v>2165</v>
+        <v>2165.0</v>
       </c>
       <c r="K40">
-        <v>5813</v>
+        <v>5813.0</v>
       </c>
       <c r="L40">
-        <v>3648</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
+        <v>3648.0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" dyDescent="0.2">
       <c r="A41">
         <v>7</v>
       </c>
       <c r="B41" s="8">
         <v>8</v>
       </c>
-      <c r="C41" s="1" t="s">
+      <c r="C41" t="s" s="1">
         <v>57</v>
       </c>
-      <c r="D41" s="1" t="s">
+      <c r="D41" t="s" s="1">
         <v>58</v>
       </c>
       <c r="E41">
-        <v>131</v>
+        <v>131.0</v>
       </c>
       <c r="F41">
-        <v>160</v>
+        <v>160.0</v>
       </c>
       <c r="G41">
-        <v>32</v>
+        <v>32.0</v>
       </c>
       <c r="H41">
-        <v>4.0999999999999996</v>
+        <v>4.1</v>
       </c>
       <c r="I41">
-        <v>3040</v>
+        <v>3040.0</v>
       </c>
       <c r="J41">
-        <v>1155</v>
+        <v>1155.0</v>
       </c>
       <c r="K41">
-        <v>4195</v>
+        <v>4195.0</v>
       </c>
       <c r="L41">
-        <v>3040</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
+        <v>3040.0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" dyDescent="0.2">
       <c r="A42">
         <v>7</v>
       </c>
       <c r="B42" s="8">
         <v>9</v>
       </c>
-      <c r="C42" s="1" t="s">
+      <c r="C42" t="s" s="1">
         <v>57</v>
       </c>
-      <c r="D42" s="1" t="s">
+      <c r="D42" t="s" s="1">
         <v>59</v>
       </c>
       <c r="E42">
-        <v>110</v>
+        <v>110.0</v>
       </c>
       <c r="F42">
-        <v>146</v>
+        <v>146.0</v>
       </c>
       <c r="G42">
         <v>29.2</v>
@@ -2499,36 +2499,36 @@
         <v>3.8</v>
       </c>
       <c r="I42">
-        <v>2774</v>
+        <v>2774.0</v>
       </c>
       <c r="J42">
-        <v>943</v>
+        <v>943.0</v>
       </c>
       <c r="K42">
-        <v>3717</v>
+        <v>3717.0</v>
       </c>
       <c r="L42">
-        <v>2774</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
+        <v>2774.0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" dyDescent="0.2">
       <c r="A43">
         <v>7</v>
       </c>
       <c r="B43" s="8">
         <v>10</v>
       </c>
-      <c r="C43" s="1" t="s">
+      <c r="C43" t="s" s="1">
         <v>57</v>
       </c>
-      <c r="D43" s="1" t="s">
+      <c r="D43" t="s" s="1">
         <v>60</v>
       </c>
       <c r="E43">
-        <v>280</v>
+        <v>280.0</v>
       </c>
       <c r="F43">
-        <v>187</v>
+        <v>187.0</v>
       </c>
       <c r="G43">
         <v>37.4</v>
@@ -2537,36 +2537,36 @@
         <v>7.5</v>
       </c>
       <c r="I43">
-        <v>3553</v>
+        <v>3553.0</v>
       </c>
       <c r="J43">
-        <v>2830</v>
+        <v>2830.0</v>
       </c>
       <c r="K43">
-        <v>6383</v>
+        <v>6383.0</v>
       </c>
       <c r="L43">
-        <v>3553</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
+        <v>3553.0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" dyDescent="0.2">
       <c r="A44">
         <v>8</v>
       </c>
       <c r="B44" s="8">
         <v>9</v>
       </c>
-      <c r="C44" s="1" t="s">
+      <c r="C44" t="s" s="1">
         <v>58</v>
       </c>
-      <c r="D44" s="1" t="s">
+      <c r="D44" t="s" s="1">
         <v>59</v>
       </c>
       <c r="E44">
-        <v>26</v>
+        <v>26.0</v>
       </c>
       <c r="F44">
-        <v>19</v>
+        <v>19.0</v>
       </c>
       <c r="G44">
         <v>3.8</v>
@@ -2575,95 +2575,95 @@
         <v>6.8</v>
       </c>
       <c r="I44">
-        <v>361</v>
+        <v>361.0</v>
       </c>
       <c r="J44">
-        <v>259</v>
+        <v>259.0</v>
       </c>
       <c r="K44">
-        <v>620</v>
+        <v>620.0</v>
       </c>
       <c r="L44">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.2">
+        <v>361.0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" dyDescent="0.2">
       <c r="A45">
         <v>8</v>
       </c>
       <c r="B45" s="8">
         <v>10</v>
       </c>
-      <c r="C45" s="1" t="s">
+      <c r="C45" t="s" s="1">
         <v>58</v>
       </c>
-      <c r="D45" s="1" t="s">
+      <c r="D45" t="s" s="1">
         <v>60</v>
       </c>
       <c r="E45">
-        <v>163</v>
+        <v>163.0</v>
       </c>
       <c r="F45">
-        <v>164</v>
+        <v>164.0</v>
       </c>
       <c r="G45">
-        <v>32.799999999999997</v>
+        <v>32.8</v>
       </c>
       <c r="H45">
-        <v>5</v>
+        <v>5.0</v>
       </c>
       <c r="I45">
-        <v>3116</v>
+        <v>3116.0</v>
       </c>
       <c r="J45">
-        <v>1519</v>
+        <v>1519.0</v>
       </c>
       <c r="K45">
-        <v>4635</v>
+        <v>4635.0</v>
       </c>
       <c r="L45">
-        <v>3116</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.2">
+        <v>3116.0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" dyDescent="0.2">
       <c r="A46">
         <v>9</v>
       </c>
       <c r="B46" s="8">
         <v>10</v>
       </c>
-      <c r="C46" s="1" t="s">
+      <c r="C46" t="s" s="1">
         <v>59</v>
       </c>
-      <c r="D46" s="1" t="s">
+      <c r="D46" t="s" s="1">
         <v>60</v>
       </c>
       <c r="E46">
-        <v>175</v>
+        <v>175.0</v>
       </c>
       <c r="F46">
-        <v>170</v>
+        <v>170.0</v>
       </c>
       <c r="G46">
-        <v>34</v>
+        <v>34.0</v>
       </c>
       <c r="H46">
-        <v>5.0999999999999996</v>
+        <v>5.1</v>
       </c>
       <c r="I46">
-        <v>3230</v>
+        <v>3230.0</v>
       </c>
       <c r="J46">
-        <v>1645</v>
+        <v>1645.0</v>
       </c>
       <c r="K46">
-        <v>4875</v>
+        <v>4875.0</v>
       </c>
       <c r="L46">
-        <v>3230</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.2">
+        <v>3230.0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" dyDescent="0.2">
       <c r="A47">
         <v>1</v>
       </c>
@@ -2697,7 +2697,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:16" dyDescent="0.2">
       <c r="A48">
         <v>2</v>
       </c>
@@ -2731,7 +2731,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:16" dyDescent="0.2">
       <c r="A49">
         <v>3</v>
       </c>
@@ -2765,7 +2765,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:16" dyDescent="0.2">
       <c r="A50">
         <v>4</v>
       </c>
@@ -2799,7 +2799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:16" dyDescent="0.2">
       <c r="A51">
         <v>5</v>
       </c>
@@ -2833,7 +2833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:16" dyDescent="0.2">
       <c r="A52">
         <v>6</v>
       </c>
@@ -2865,7 +2865,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:16" dyDescent="0.2">
       <c r="A53">
         <v>7</v>
       </c>
@@ -2897,7 +2897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:16" dyDescent="0.2">
       <c r="A54">
         <v>8</v>
       </c>
@@ -2929,7 +2929,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:16" dyDescent="0.2">
       <c r="A55">
         <v>9</v>
       </c>
@@ -2961,7 +2961,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:16" dyDescent="0.2">
       <c r="A56">
         <v>10</v>
       </c>
@@ -2993,13 +2993,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:16" dyDescent="0.2">
       <c r="G57" s="2"/>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:16" dyDescent="0.2">
       <c r="G58" s="1"/>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:16" dyDescent="0.2">
       <c r="G59" s="1"/>
     </row>
   </sheetData>

--- a/inputData/Parameters.xlsx
+++ b/inputData/Parameters.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kapta\Documents\DTU\Speciale\GitHubFiles\inputData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sillewiberg/Desktop/Skole/Speciale/Master-Thesis-eVTOL-1/inputData/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1764DAD6-3748-4CDE-B441-34E634E8D666}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC525445-B921-7444-8BE9-F0D2537C0186}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16320" activeTab="1" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
   </bookViews>
   <sheets>
     <sheet name="Parameters" sheetId="9" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="61">
   <si>
     <t>cap_u</t>
   </si>
@@ -184,16 +184,49 @@
   </si>
   <si>
     <t>minuts/unit</t>
+  </si>
+  <si>
+    <t>cord_from</t>
+  </si>
+  <si>
+    <t>cord_to</t>
+  </si>
+  <si>
+    <t>(55.629053, 12.647601)</t>
+  </si>
+  <si>
+    <t>(55.740278, 9.151667)</t>
+  </si>
+  <si>
+    <t>(55.7003, 11.2500)</t>
+  </si>
+  <si>
+    <t>(56.3000, 10.6180)</t>
+  </si>
+  <si>
+    <t>(55.4767, 10.3308)</t>
+  </si>
+  <si>
+    <t>(54.931394, 9.781081)</t>
+  </si>
+  <si>
+    <t>(57.019081, 9.957817)</t>
+  </si>
+  <si>
+    <t>(55.581790, 9.722994)</t>
+  </si>
+  <si>
+    <t>(55.726059, 9.574035)</t>
+  </si>
+  <si>
+    <t>(55.924974, 12.265524)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.0"/>
-  </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -227,6 +260,20 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <strike/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -248,7 +295,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -262,16 +309,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -607,18 +647,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B15C49E0-A7B4-734A-8962-DC2A879F4079}">
   <dimension ref="A1:D20"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="22.6640625" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" dyDescent="0.4">
+    <row r="1" spans="1:4" dyDescent="0.2">
       <c r="A1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:4" dyDescent="0.4">
+    <row r="2" spans="1:4" dyDescent="0.2">
       <c r="A2" t="s" s="1">
         <v>20</v>
       </c>
@@ -629,7 +669,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" dyDescent="0.4">
+    <row r="3" spans="1:4" dyDescent="0.2">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -640,7 +680,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:4" dyDescent="0.4">
+    <row r="4" spans="1:4" dyDescent="0.2">
       <c r="A4" t="s">
         <v>46</v>
       </c>
@@ -651,7 +691,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="5" spans="1:4" dyDescent="0.4">
+    <row r="5" spans="1:4" dyDescent="0.2">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -662,7 +702,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="6" spans="1:4" dyDescent="0.4">
+    <row r="6" spans="1:4" dyDescent="0.2">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -673,7 +713,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:4" dyDescent="0.4">
+    <row r="7" spans="1:4" dyDescent="0.2">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -684,18 +724,19 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:4" dyDescent="0.4">
+    <row r="8" spans="1:4" dyDescent="0.2">
       <c r="A8" t="s">
         <v>19</v>
       </c>
       <c r="B8" s="4">
+        <f>0.2/B20</f>
         <v>0.2</v>
       </c>
       <c r="D8" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:4" dyDescent="0.4">
+    <row r="9" spans="1:4" dyDescent="0.2">
       <c r="A9" t="s">
         <v>0</v>
       </c>
@@ -706,7 +747,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:4" dyDescent="0.4">
+    <row r="10" spans="1:4" dyDescent="0.2">
       <c r="A10" t="s">
         <v>1</v>
       </c>
@@ -717,7 +758,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:4" dyDescent="0.4">
+    <row r="11" spans="1:4" dyDescent="0.2">
       <c r="A11" t="s">
         <v>45</v>
       </c>
@@ -728,7 +769,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="12" spans="1:4" dyDescent="0.4">
+    <row r="12" spans="1:4" dyDescent="0.2">
       <c r="A12" t="s">
         <v>2</v>
       </c>
@@ -736,10 +777,10 @@
         <v>40</v>
       </c>
       <c r="D12" s="3">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" dyDescent="0.4">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" dyDescent="0.2">
       <c r="A13" t="s">
         <v>42</v>
       </c>
@@ -750,7 +791,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="14" spans="1:4" dyDescent="0.4">
+    <row r="14" spans="1:4" dyDescent="0.2">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -762,7 +803,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="15" spans="1:4" dyDescent="0.4">
+    <row r="15" spans="1:4" dyDescent="0.2">
       <c r="A15" t="s">
         <v>4</v>
       </c>
@@ -774,7 +815,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:4" dyDescent="0.4">
+    <row r="16" spans="1:4" dyDescent="0.2">
       <c r="A16" t="s">
         <v>5</v>
       </c>
@@ -786,7 +827,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:4" dyDescent="0.4">
+    <row r="17" spans="1:4" dyDescent="0.2">
       <c r="A17" t="s">
         <v>6</v>
       </c>
@@ -798,7 +839,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:4" dyDescent="0.4">
+    <row r="20" spans="1:4" dyDescent="0.2">
       <c r="A20" t="s">
         <v>41</v>
       </c>
@@ -817,558 +858,2152 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAF0D5EA-53B5-1240-9D84-6FE223856A18}">
-  <dimension ref="A1:N24"/>
-  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:P59"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="17.1640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.1640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="17.1640625" customWidth="1"/>
+    <col min="5" max="5" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" dyDescent="0.4">
-      <c r="A1" t="s" s="12">
+    <row r="1" spans="1:16" dyDescent="0.2">
+      <c r="A1" t="s" s="9">
         <v>36</v>
       </c>
       <c r="B1" t="s" s="5">
         <v>37</v>
       </c>
       <c r="C1" t="s" s="5">
+        <v>49</v>
+      </c>
+      <c r="D1" t="s" s="5">
+        <v>50</v>
+      </c>
+      <c r="E1" t="s" s="5">
         <v>22</v>
       </c>
-      <c r="D1" t="s" s="5">
+      <c r="F1" t="s" s="5">
         <v>23</v>
       </c>
-      <c r="E1" t="s" s="5">
+      <c r="G1" t="s" s="5">
         <v>24</v>
       </c>
-      <c r="F1" t="s" s="5">
+      <c r="H1" t="s" s="5">
         <v>25</v>
       </c>
-      <c r="G1" t="s" s="5">
+      <c r="I1" t="s" s="5">
         <v>26</v>
       </c>
-      <c r="H1" t="s" s="5">
+      <c r="J1" t="s" s="5">
         <v>27</v>
       </c>
-      <c r="I1" t="s" s="5">
+      <c r="K1" t="s" s="5">
         <v>38</v>
       </c>
-      <c r="J1" t="s" s="5">
+      <c r="L1" t="s" s="5">
         <v>28</v>
       </c>
-      <c r="L1" t="s" s="6">
+      <c r="N1" t="s" s="6">
         <v>19</v>
       </c>
-      <c r="M1" s="7">
+      <c r="O1" s="7">
         <v>0.2</v>
       </c>
-      <c r="N1" s="6"/>
-    </row>
-    <row r="2" spans="1:14" dyDescent="0.4">
+      <c r="P1" s="6"/>
+    </row>
+    <row r="2" spans="1:16" dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" s="8">
         <v>2</v>
       </c>
-      <c r="C2" s="8">
-        <f>(180)</f>
-        <v>180</v>
-      </c>
-      <c r="D2" s="8">
-        <v>219</v>
-      </c>
-      <c r="E2" s="8">
-        <f t="shared" si="0" ref="E2:E11">$M$1*D2</f>
-        <v>43.800000000000004</v>
-      </c>
-      <c r="F2" s="9">
-        <f>C2/E2</f>
-        <v>4.10958904109589</v>
-      </c>
-      <c r="G2" s="10">
-        <f t="shared" si="1" ref="G2:G11">D2*$M$2</f>
-        <v>4161</v>
-      </c>
-      <c r="H2" s="11">
-        <f t="shared" si="2" ref="H2:H11">(C2-E2)*$M$3*$M$4</f>
-        <v>1589</v>
-      </c>
-      <c r="I2" s="11">
-        <f>G2+H2</f>
-        <v>5750</v>
-      </c>
-      <c r="J2" s="11">
-        <f t="shared" si="3" ref="J2:J11">MAX($M$2*D2+$M$5,$M$4*$M$3*(C2-E2))</f>
-        <v>4161</v>
-      </c>
-      <c r="L2" t="s">
+      <c r="C2" t="s" s="1">
+        <v>51</v>
+      </c>
+      <c r="D2" t="s" s="2">
+        <v>52</v>
+      </c>
+      <c r="E2">
+        <v>185.0</v>
+      </c>
+      <c r="F2">
+        <v>219.0</v>
+      </c>
+      <c r="G2">
+        <v>43.8</v>
+      </c>
+      <c r="H2">
+        <v>4.2</v>
+      </c>
+      <c r="I2">
+        <v>4161.0</v>
+      </c>
+      <c r="J2">
+        <v>1647.0</v>
+      </c>
+      <c r="K2">
+        <v>5808.0</v>
+      </c>
+      <c r="L2">
+        <v>4161.0</v>
+      </c>
+      <c r="N2" t="s">
         <v>29</v>
       </c>
-      <c r="M2" s="4">
+      <c r="O2" s="4">
         <v>19</v>
       </c>
-      <c r="N2" t="s">
+      <c r="P2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:14" dyDescent="0.4">
+    <row r="3" spans="1:16" dyDescent="0.2">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" s="8">
         <v>3</v>
       </c>
-      <c r="C3" s="8">
-        <v>60</v>
-      </c>
-      <c r="D3" s="8">
-        <v>88</v>
-      </c>
-      <c r="E3" s="8">
-        <f t="shared" si="0"/>
-        <v>17.600000000000001</v>
-      </c>
-      <c r="F3" s="9">
-        <f t="shared" si="4" ref="F3:F11">C3/E3</f>
-        <v>3.4090909090909087</v>
-      </c>
-      <c r="G3" s="10">
-        <f t="shared" si="1"/>
-        <v>1672</v>
-      </c>
-      <c r="H3" s="11">
-        <f t="shared" si="2"/>
-        <v>494.66666666666669</v>
-      </c>
-      <c r="I3" s="11">
-        <f t="shared" si="5" ref="I3:I11">G3+H3</f>
-        <v>2166.6666666666665</v>
-      </c>
-      <c r="J3" s="11">
-        <f t="shared" si="3"/>
-        <v>1672</v>
-      </c>
-      <c r="L3" t="s">
+      <c r="C3" t="s" s="1">
+        <v>51</v>
+      </c>
+      <c r="D3" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="E3">
+        <v>82.0</v>
+      </c>
+      <c r="F3">
+        <v>88.0</v>
+      </c>
+      <c r="G3">
+        <v>17.6</v>
+      </c>
+      <c r="H3">
+        <v>4.7</v>
+      </c>
+      <c r="I3">
+        <v>1672.0</v>
+      </c>
+      <c r="J3">
+        <v>751.0</v>
+      </c>
+      <c r="K3">
+        <v>2423.0</v>
+      </c>
+      <c r="L3">
+        <v>1672.0</v>
+      </c>
+      <c r="N3" t="s">
         <v>31</v>
       </c>
-      <c r="M3" s="4">
+      <c r="O3" s="4">
         <f>1000/60</f>
         <v>16.666666666666668</v>
       </c>
-      <c r="N3" t="s">
+      <c r="P3" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:14" dyDescent="0.4">
+    <row r="4" spans="1:16" dyDescent="0.2">
       <c r="A4">
         <v>1</v>
       </c>
       <c r="B4" s="8">
         <v>4</v>
       </c>
-      <c r="C4" s="8">
-        <f>200</f>
-        <v>200</v>
-      </c>
-      <c r="D4" s="8">
-        <v>147</v>
-      </c>
-      <c r="E4" s="8">
-        <f t="shared" si="0"/>
-        <v>29.400000000000002</v>
-      </c>
-      <c r="F4" s="9">
-        <f t="shared" si="4"/>
-        <v>6.8027210884353737</v>
-      </c>
-      <c r="G4" s="10">
-        <f t="shared" si="1"/>
-        <v>2793</v>
-      </c>
-      <c r="H4" s="11">
-        <f t="shared" si="2"/>
-        <v>1990.3333333333333</v>
-      </c>
-      <c r="I4" s="11">
-        <f t="shared" si="5"/>
-        <v>4783.333333333333</v>
-      </c>
-      <c r="J4" s="11">
-        <f t="shared" si="3"/>
-        <v>2793</v>
-      </c>
-      <c r="L4" t="s">
+      <c r="C4" t="s" s="1">
+        <v>51</v>
+      </c>
+      <c r="D4" t="s" s="1">
+        <v>54</v>
+      </c>
+      <c r="E4">
+        <v>228.0</v>
+      </c>
+      <c r="F4">
+        <v>147.0</v>
+      </c>
+      <c r="G4">
+        <v>29.4</v>
+      </c>
+      <c r="H4">
+        <v>7.8</v>
+      </c>
+      <c r="I4">
+        <v>2793.0</v>
+      </c>
+      <c r="J4">
+        <v>2317.0</v>
+      </c>
+      <c r="K4">
+        <v>5110.0</v>
+      </c>
+      <c r="L4">
+        <v>2793.0</v>
+      </c>
+      <c r="N4" t="s">
         <v>33</v>
       </c>
-      <c r="M4" s="4">
+      <c r="O4" s="4">
         <v>0.7</v>
       </c>
     </row>
-    <row r="5" spans="1:14" dyDescent="0.4">
+    <row r="5" spans="1:16" dyDescent="0.2">
       <c r="A5">
         <v>1</v>
       </c>
       <c r="B5" s="8">
         <v>5</v>
       </c>
-      <c r="C5" s="8">
-        <f>(60+50)</f>
-        <v>110</v>
-      </c>
-      <c r="D5" s="8">
-        <v>147</v>
-      </c>
-      <c r="E5" s="8">
-        <f t="shared" si="0"/>
-        <v>29.400000000000002</v>
-      </c>
-      <c r="F5" s="9">
-        <f t="shared" si="4"/>
-        <v>3.7414965986394555</v>
-      </c>
-      <c r="G5" s="10">
-        <f t="shared" si="1"/>
-        <v>2793</v>
-      </c>
-      <c r="H5" s="11">
-        <f t="shared" si="2"/>
-        <v>940.33333333333326</v>
-      </c>
-      <c r="I5" s="11">
-        <f t="shared" si="5"/>
-        <v>3733.333333333333</v>
-      </c>
-      <c r="J5" s="11">
-        <f t="shared" si="3"/>
-        <v>2793</v>
-      </c>
-      <c r="L5" t="s">
+      <c r="C5" t="s" s="1">
+        <v>51</v>
+      </c>
+      <c r="D5" t="s" s="1">
+        <v>55</v>
+      </c>
+      <c r="E5">
+        <v>126.0</v>
+      </c>
+      <c r="F5">
+        <v>147.0</v>
+      </c>
+      <c r="G5">
+        <v>29.4</v>
+      </c>
+      <c r="H5">
+        <v>4.3</v>
+      </c>
+      <c r="I5">
+        <v>2793.0</v>
+      </c>
+      <c r="J5">
+        <v>1127.0</v>
+      </c>
+      <c r="K5">
+        <v>3920.0</v>
+      </c>
+      <c r="L5">
+        <v>2793.0</v>
+      </c>
+      <c r="N5" t="s">
         <v>34</v>
       </c>
-      <c r="M5" s="4">
-        <v>0</v>
-      </c>
-      <c r="N5" t="s">
+      <c r="O5" s="4">
+        <v>0</v>
+      </c>
+      <c r="P5" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:14" dyDescent="0.4">
+    <row r="6" spans="1:16" dyDescent="0.2">
       <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6" s="8">
+        <v>6</v>
+      </c>
+      <c r="C6" t="s" s="1">
+        <v>51</v>
+      </c>
+      <c r="D6" t="s" s="1">
+        <v>56</v>
+      </c>
+      <c r="E6">
+        <v>205.0</v>
+      </c>
+      <c r="F6">
+        <v>197.0</v>
+      </c>
+      <c r="G6">
+        <v>39.4</v>
+      </c>
+      <c r="H6">
+        <v>5.2</v>
+      </c>
+      <c r="I6">
+        <v>3743.0</v>
+      </c>
+      <c r="J6">
+        <v>1932.0</v>
+      </c>
+      <c r="K6">
+        <v>5675.0</v>
+      </c>
+      <c r="L6">
+        <v>3743.0</v>
+      </c>
+      <c r="O6" s="4"/>
+    </row>
+    <row r="7" spans="1:16" dyDescent="0.2">
+      <c r="A7">
+        <v>1</v>
+      </c>
+      <c r="B7" s="8">
+        <v>7</v>
+      </c>
+      <c r="C7" t="s" s="1">
+        <v>51</v>
+      </c>
+      <c r="D7" t="s" s="1">
+        <v>57</v>
+      </c>
+      <c r="E7">
+        <v>263.0</v>
+      </c>
+      <c r="F7">
+        <v>227.0</v>
+      </c>
+      <c r="G7">
+        <v>45.4</v>
+      </c>
+      <c r="H7">
+        <v>5.8</v>
+      </c>
+      <c r="I7">
+        <v>4313.0</v>
+      </c>
+      <c r="J7">
+        <v>2539.0</v>
+      </c>
+      <c r="K7">
+        <v>6852.0</v>
+      </c>
+      <c r="L7">
+        <v>4313.0</v>
+      </c>
+      <c r="O7" s="4"/>
+    </row>
+    <row r="8" spans="1:16" dyDescent="0.2">
+      <c r="A8">
+        <v>1</v>
+      </c>
+      <c r="B8" s="8">
+        <v>8</v>
+      </c>
+      <c r="C8" t="s" s="1">
+        <v>51</v>
+      </c>
+      <c r="D8" t="s" s="1">
+        <v>58</v>
+      </c>
+      <c r="E8">
+        <v>143.0</v>
+      </c>
+      <c r="F8">
+        <v>184.0</v>
+      </c>
+      <c r="G8">
+        <v>36.8</v>
+      </c>
+      <c r="H8">
+        <v>3.9</v>
+      </c>
+      <c r="I8">
+        <v>3496.0</v>
+      </c>
+      <c r="J8">
+        <v>1239.0</v>
+      </c>
+      <c r="K8">
+        <v>4735.0</v>
+      </c>
+      <c r="L8">
+        <v>3496.0</v>
+      </c>
+      <c r="O8" s="4"/>
+    </row>
+    <row r="9" spans="1:16" dyDescent="0.2">
+      <c r="A9">
+        <v>1</v>
+      </c>
+      <c r="B9" s="8">
+        <v>9</v>
+      </c>
+      <c r="C9" t="s" s="1">
+        <v>51</v>
+      </c>
+      <c r="D9" t="s" s="1">
+        <v>59</v>
+      </c>
+      <c r="E9">
+        <v>155.0</v>
+      </c>
+      <c r="F9">
+        <v>193.0</v>
+      </c>
+      <c r="G9">
+        <v>38.6</v>
+      </c>
+      <c r="H9">
+        <v>4.0</v>
+      </c>
+      <c r="I9">
+        <v>3667.0</v>
+      </c>
+      <c r="J9">
+        <v>1358.0</v>
+      </c>
+      <c r="K9">
+        <v>5025.0</v>
+      </c>
+      <c r="L9">
+        <v>3667.0</v>
+      </c>
+      <c r="O9" s="4"/>
+    </row>
+    <row r="10" spans="1:16" dyDescent="0.2">
+      <c r="A10">
+        <v>1</v>
+      </c>
+      <c r="B10" s="8">
+        <v>10</v>
+      </c>
+      <c r="C10" t="s" s="1">
+        <v>51</v>
+      </c>
+      <c r="D10" t="s" s="1">
+        <v>60</v>
+      </c>
+      <c r="E10">
+        <v>42.0</v>
+      </c>
+      <c r="F10">
+        <v>41.0</v>
+      </c>
+      <c r="G10">
+        <v>8.2</v>
+      </c>
+      <c r="H10">
+        <v>5.1</v>
+      </c>
+      <c r="I10">
+        <v>779.0</v>
+      </c>
+      <c r="J10">
+        <v>394.0</v>
+      </c>
+      <c r="K10">
+        <v>1173.0</v>
+      </c>
+      <c r="L10">
+        <v>779.0</v>
+      </c>
+      <c r="O10" s="4"/>
+    </row>
+    <row r="11" spans="1:16" dyDescent="0.2">
+      <c r="A11">
         <v>2</v>
       </c>
-      <c r="B6" s="8">
+      <c r="B11" s="8">
         <v>3</v>
       </c>
-      <c r="C6" s="8">
-        <f>(120+40)</f>
-        <v>160</v>
-      </c>
-      <c r="D6" s="8">
-        <v>131</v>
-      </c>
-      <c r="E6" s="8">
-        <f t="shared" si="0"/>
-        <v>26.200000000000003</v>
-      </c>
-      <c r="F6" s="9">
-        <f t="shared" si="4"/>
-        <v>6.1068702290076331</v>
-      </c>
-      <c r="G6" s="10">
-        <f t="shared" si="1"/>
-        <v>2489</v>
-      </c>
-      <c r="H6" s="11">
-        <f t="shared" si="2"/>
-        <v>1561.0000000000002</v>
-      </c>
-      <c r="I6" s="11">
-        <f t="shared" si="5"/>
-        <v>4050</v>
-      </c>
-      <c r="J6" s="11">
-        <f t="shared" si="3"/>
-        <v>2489</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" dyDescent="0.4">
-      <c r="A7">
+      <c r="C11" t="s" s="2">
+        <v>52</v>
+      </c>
+      <c r="D11" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="E11">
+        <v>173.0</v>
+      </c>
+      <c r="F11">
+        <v>131.0</v>
+      </c>
+      <c r="G11">
+        <v>26.2</v>
+      </c>
+      <c r="H11">
+        <v>6.6</v>
+      </c>
+      <c r="I11">
+        <v>2489.0</v>
+      </c>
+      <c r="J11">
+        <v>1713.0</v>
+      </c>
+      <c r="K11">
+        <v>4202.0</v>
+      </c>
+      <c r="L11">
+        <v>2489.0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" dyDescent="0.2">
+      <c r="A12">
         <v>2</v>
       </c>
-      <c r="B7" s="8">
+      <c r="B12" s="8">
         <v>4</v>
       </c>
-      <c r="C7" s="8">
-        <f>90</f>
-        <v>90</v>
-      </c>
-      <c r="D7" s="8">
-        <v>111</v>
-      </c>
-      <c r="E7" s="8">
-        <f t="shared" si="0"/>
-        <v>22.200000000000003</v>
-      </c>
-      <c r="F7" s="9">
-        <f t="shared" si="4"/>
-        <v>4.0540540540540535</v>
-      </c>
-      <c r="G7" s="10">
-        <f t="shared" si="1"/>
-        <v>2109</v>
-      </c>
-      <c r="H7" s="11">
-        <f t="shared" si="2"/>
-        <v>791</v>
-      </c>
-      <c r="I7" s="11">
-        <f t="shared" si="5"/>
-        <v>2900</v>
-      </c>
-      <c r="J7" s="11">
-        <f t="shared" si="3"/>
-        <v>2109</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" dyDescent="0.4">
-      <c r="A8">
-        <v>2</v>
-      </c>
-      <c r="B8" s="8">
-        <v>5</v>
-      </c>
-      <c r="C8" s="8">
-        <f>75</f>
-        <v>75</v>
-      </c>
-      <c r="D8" s="8">
-        <v>80</v>
-      </c>
-      <c r="E8" s="8">
-        <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="F8" s="9">
-        <f t="shared" si="4"/>
-        <v>4.6875</v>
-      </c>
-      <c r="G8" s="10">
-        <f t="shared" si="1"/>
-        <v>1520</v>
-      </c>
-      <c r="H8" s="11">
-        <f t="shared" si="2"/>
-        <v>688.33333333333337</v>
-      </c>
-      <c r="I8" s="11">
-        <f t="shared" si="5"/>
-        <v>2208.3333333333335</v>
-      </c>
-      <c r="J8" s="11">
-        <f t="shared" si="3"/>
-        <v>1520</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" dyDescent="0.4">
-      <c r="A9">
-        <v>3</v>
-      </c>
-      <c r="B9" s="8">
-        <v>4</v>
-      </c>
-      <c r="C9" s="8">
-        <v>180</v>
-      </c>
-      <c r="D9" s="8">
-        <v>79</v>
-      </c>
-      <c r="E9" s="8">
-        <f t="shared" si="0"/>
-        <v>15.8</v>
-      </c>
-      <c r="F9" s="9">
-        <f t="shared" si="4"/>
-        <v>11.39240506329114</v>
-      </c>
-      <c r="G9" s="10">
-        <f t="shared" si="1"/>
-        <v>1501</v>
-      </c>
-      <c r="H9" s="11">
-        <f t="shared" si="2"/>
-        <v>1915.6666666666665</v>
-      </c>
-      <c r="I9" s="11">
-        <f t="shared" si="5"/>
-        <v>3416.6666666666665</v>
-      </c>
-      <c r="J9" s="11">
-        <f t="shared" si="3"/>
-        <v>1915.6666666666665</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" dyDescent="0.4">
-      <c r="A10">
-        <v>3</v>
-      </c>
-      <c r="B10" s="8">
-        <v>5</v>
-      </c>
-      <c r="C10" s="8">
-        <v>90</v>
-      </c>
-      <c r="D10" s="8">
-        <v>63</v>
-      </c>
-      <c r="E10" s="8">
-        <f t="shared" si="0"/>
-        <v>12.600000000000001</v>
-      </c>
-      <c r="F10" s="9">
-        <f t="shared" si="4"/>
-        <v>7.1428571428571423</v>
-      </c>
-      <c r="G10" s="10">
-        <f t="shared" si="1"/>
-        <v>1197</v>
-      </c>
-      <c r="H10" s="11">
-        <f t="shared" si="2"/>
-        <v>903.00000000000011</v>
-      </c>
-      <c r="I10" s="11">
-        <f t="shared" si="5"/>
-        <v>2100</v>
-      </c>
-      <c r="J10" s="11">
-        <f t="shared" si="3"/>
-        <v>1197</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" dyDescent="0.4">
-      <c r="A11">
-        <v>4</v>
-      </c>
-      <c r="B11" s="8">
-        <v>5</v>
-      </c>
-      <c r="C11" s="8">
-        <v>120</v>
-      </c>
-      <c r="D11" s="8">
-        <v>93</v>
-      </c>
-      <c r="E11" s="8">
-        <f t="shared" si="0"/>
-        <v>18.600000000000001</v>
-      </c>
-      <c r="F11" s="9">
-        <f t="shared" si="4"/>
-        <v>6.4516129032258061</v>
-      </c>
-      <c r="G11" s="10">
-        <f t="shared" si="1"/>
-        <v>1767</v>
-      </c>
-      <c r="H11" s="11">
-        <f t="shared" si="2"/>
-        <v>1183</v>
-      </c>
-      <c r="I11" s="11">
-        <f t="shared" si="5"/>
-        <v>2950</v>
-      </c>
-      <c r="J11" s="11">
-        <f t="shared" si="3"/>
-        <v>1767</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" dyDescent="0.4">
-      <c r="A12">
-        <v>1</v>
-      </c>
-      <c r="B12" s="8">
-        <v>1</v>
-      </c>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="10"/>
+      <c r="C12" t="s" s="2">
+        <v>52</v>
+      </c>
+      <c r="D12" t="s" s="1">
+        <v>54</v>
+      </c>
+      <c r="E12">
+        <v>103.0</v>
+      </c>
+      <c r="F12">
+        <v>110.0</v>
+      </c>
+      <c r="G12">
+        <v>22.0</v>
+      </c>
+      <c r="H12">
+        <v>4.7</v>
+      </c>
       <c r="I12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" dyDescent="0.4">
+        <v>2090.0</v>
+      </c>
+      <c r="J12">
+        <v>945.0</v>
+      </c>
+      <c r="K12">
+        <v>3035.0</v>
+      </c>
+      <c r="L12">
+        <v>2090.0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" dyDescent="0.2">
       <c r="A13">
         <v>2</v>
       </c>
       <c r="B13" s="8">
+        <v>5</v>
+      </c>
+      <c r="C13" t="s" s="2">
+        <v>52</v>
+      </c>
+      <c r="D13" t="s" s="1">
+        <v>55</v>
+      </c>
+      <c r="E13">
+        <v>89.0</v>
+      </c>
+      <c r="F13">
+        <v>80.0</v>
+      </c>
+      <c r="G13">
+        <v>16.0</v>
+      </c>
+      <c r="H13">
+        <v>5.6</v>
+      </c>
+      <c r="I13">
+        <v>1520.0</v>
+      </c>
+      <c r="J13">
+        <v>852.0</v>
+      </c>
+      <c r="K13">
+        <v>2372.0</v>
+      </c>
+      <c r="L13">
+        <v>1520.0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" dyDescent="0.2">
+      <c r="A14">
         <v>2</v>
       </c>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="8"/>
-      <c r="I13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" dyDescent="0.4">
-      <c r="A14">
+      <c r="B14" s="8">
+        <v>6</v>
+      </c>
+      <c r="C14" t="s" s="2">
+        <v>52</v>
+      </c>
+      <c r="D14" t="s" s="1">
+        <v>56</v>
+      </c>
+      <c r="E14">
+        <v>100.0</v>
+      </c>
+      <c r="F14">
+        <v>98.0</v>
+      </c>
+      <c r="G14">
+        <v>19.6</v>
+      </c>
+      <c r="H14">
+        <v>5.1</v>
+      </c>
+      <c r="I14">
+        <v>1862.0</v>
+      </c>
+      <c r="J14">
+        <v>938.0</v>
+      </c>
+      <c r="K14">
+        <v>2800.0</v>
+      </c>
+      <c r="L14">
+        <v>1862.0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" dyDescent="0.2">
+      <c r="A15">
+        <v>2</v>
+      </c>
+      <c r="B15" s="8">
+        <v>7</v>
+      </c>
+      <c r="C15" t="s" s="2">
+        <v>52</v>
+      </c>
+      <c r="D15" t="s" s="11">
+        <v>57</v>
+      </c>
+      <c r="E15">
+        <v>138.0</v>
+      </c>
+      <c r="F15">
+        <v>151.0</v>
+      </c>
+      <c r="G15">
+        <v>30.2</v>
+      </c>
+      <c r="H15">
+        <v>4.6</v>
+      </c>
+      <c r="I15">
+        <v>2869.0</v>
+      </c>
+      <c r="J15">
+        <v>1258.0</v>
+      </c>
+      <c r="K15">
+        <v>4127.0</v>
+      </c>
+      <c r="L15">
+        <v>2869.0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" dyDescent="0.2">
+      <c r="A16">
+        <v>2</v>
+      </c>
+      <c r="B16" s="8">
+        <v>8</v>
+      </c>
+      <c r="C16" t="s" s="2">
+        <v>52</v>
+      </c>
+      <c r="D16" t="s" s="1">
+        <v>58</v>
+      </c>
+      <c r="E16">
+        <v>55.0</v>
+      </c>
+      <c r="F16">
+        <v>40.0</v>
+      </c>
+      <c r="G16">
+        <v>8.0</v>
+      </c>
+      <c r="H16">
+        <v>6.9</v>
+      </c>
+      <c r="I16">
+        <v>760.0</v>
+      </c>
+      <c r="J16">
+        <v>548.0</v>
+      </c>
+      <c r="K16">
+        <v>1308.0</v>
+      </c>
+      <c r="L16">
+        <v>760.0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" dyDescent="0.2">
+      <c r="A17">
+        <v>2</v>
+      </c>
+      <c r="B17" s="8">
+        <v>9</v>
+      </c>
+      <c r="C17" t="s" s="2">
+        <v>52</v>
+      </c>
+      <c r="D17" t="s" s="1">
+        <v>59</v>
+      </c>
+      <c r="E17">
+        <v>38.0</v>
+      </c>
+      <c r="F17">
+        <v>26.0</v>
+      </c>
+      <c r="G17">
+        <v>5.2</v>
+      </c>
+      <c r="H17">
+        <v>7.3</v>
+      </c>
+      <c r="I17">
+        <v>494.0</v>
+      </c>
+      <c r="J17">
+        <v>383.0</v>
+      </c>
+      <c r="K17">
+        <v>877.0</v>
+      </c>
+      <c r="L17">
+        <v>494.0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" dyDescent="0.2">
+      <c r="A18">
+        <v>2</v>
+      </c>
+      <c r="B18" s="8">
+        <v>10</v>
+      </c>
+      <c r="C18" t="s" s="2">
+        <v>52</v>
+      </c>
+      <c r="D18" t="s" s="1">
+        <v>60</v>
+      </c>
+      <c r="E18">
+        <v>205.0</v>
+      </c>
+      <c r="F18">
+        <v>196.0</v>
+      </c>
+      <c r="G18">
+        <v>39.2</v>
+      </c>
+      <c r="H18">
+        <v>5.2</v>
+      </c>
+      <c r="I18">
+        <v>3724.0</v>
+      </c>
+      <c r="J18">
+        <v>1934.0</v>
+      </c>
+      <c r="K18">
+        <v>5658.0</v>
+      </c>
+      <c r="L18">
+        <v>3724.0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" dyDescent="0.2">
+      <c r="A19">
         <v>3</v>
       </c>
-      <c r="B14" s="8">
+      <c r="B19" s="8">
+        <v>4</v>
+      </c>
+      <c r="C19" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="D19" t="s" s="1">
+        <v>54</v>
+      </c>
+      <c r="E19">
+        <v>215.0</v>
+      </c>
+      <c r="F19">
+        <v>77.0</v>
+      </c>
+      <c r="G19">
+        <v>15.4</v>
+      </c>
+      <c r="H19">
+        <v>14.0</v>
+      </c>
+      <c r="I19">
+        <v>1463.0</v>
+      </c>
+      <c r="J19">
+        <v>2329.0</v>
+      </c>
+      <c r="K19">
+        <v>3792.0</v>
+      </c>
+      <c r="L19">
+        <v>2329.0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" dyDescent="0.2">
+      <c r="A20">
         <v>3</v>
       </c>
-      <c r="I14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" dyDescent="0.4">
-      <c r="A15">
+      <c r="B20" s="8">
+        <v>5</v>
+      </c>
+      <c r="C20" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="D20" t="s" s="1">
+        <v>55</v>
+      </c>
+      <c r="E20">
+        <v>113.0</v>
+      </c>
+      <c r="F20">
+        <v>63.0</v>
+      </c>
+      <c r="G20">
+        <v>12.6</v>
+      </c>
+      <c r="H20">
+        <v>9.0</v>
+      </c>
+      <c r="I20">
+        <v>1197.0</v>
+      </c>
+      <c r="J20">
+        <v>1171.0</v>
+      </c>
+      <c r="K20">
+        <v>2368.0</v>
+      </c>
+      <c r="L20">
+        <v>1197.0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" dyDescent="0.2">
+      <c r="A21">
+        <v>3</v>
+      </c>
+      <c r="B21" s="8">
+        <v>6</v>
+      </c>
+      <c r="C21" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="D21" t="s" s="1">
+        <v>56</v>
+      </c>
+      <c r="E21">
+        <v>192.0</v>
+      </c>
+      <c r="F21">
+        <v>126.0</v>
+      </c>
+      <c r="G21">
+        <v>25.2</v>
+      </c>
+      <c r="H21">
+        <v>7.6</v>
+      </c>
+      <c r="I21">
+        <v>2394.0</v>
+      </c>
+      <c r="J21">
+        <v>1946.0</v>
+      </c>
+      <c r="K21">
+        <v>4340.0</v>
+      </c>
+      <c r="L21">
+        <v>2394.0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" dyDescent="0.2">
+      <c r="A22">
+        <v>3</v>
+      </c>
+      <c r="B22" s="8">
+        <v>7</v>
+      </c>
+      <c r="C22" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="D22" t="s" s="11">
+        <v>57</v>
+      </c>
+      <c r="E22">
+        <v>250.0</v>
+      </c>
+      <c r="F22">
+        <v>167.0</v>
+      </c>
+      <c r="G22">
+        <v>33.4</v>
+      </c>
+      <c r="H22">
+        <v>7.5</v>
+      </c>
+      <c r="I22">
+        <v>3173.0</v>
+      </c>
+      <c r="J22">
+        <v>2527.0</v>
+      </c>
+      <c r="K22">
+        <v>5700.0</v>
+      </c>
+      <c r="L22">
+        <v>3173.0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" dyDescent="0.2">
+      <c r="A23">
+        <v>3</v>
+      </c>
+      <c r="B23" s="8">
+        <v>8</v>
+      </c>
+      <c r="C23" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="D23" t="s" s="1">
+        <v>58</v>
+      </c>
+      <c r="E23">
+        <v>130.0</v>
+      </c>
+      <c r="F23">
+        <v>97.0</v>
+      </c>
+      <c r="G23">
+        <v>19.4</v>
+      </c>
+      <c r="H23">
+        <v>6.7</v>
+      </c>
+      <c r="I23">
+        <v>1843.0</v>
+      </c>
+      <c r="J23">
+        <v>1290.0</v>
+      </c>
+      <c r="K23">
+        <v>3133.0</v>
+      </c>
+      <c r="L23">
+        <v>1843.0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" dyDescent="0.2">
+      <c r="A24">
+        <v>3</v>
+      </c>
+      <c r="B24" s="8">
+        <v>9</v>
+      </c>
+      <c r="C24" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="D24" t="s" s="1">
+        <v>59</v>
+      </c>
+      <c r="E24">
+        <v>142.0</v>
+      </c>
+      <c r="F24">
+        <v>105.0</v>
+      </c>
+      <c r="G24">
+        <v>21.0</v>
+      </c>
+      <c r="H24">
+        <v>6.8</v>
+      </c>
+      <c r="I24">
+        <v>1995.0</v>
+      </c>
+      <c r="J24">
+        <v>1412.0</v>
+      </c>
+      <c r="K24">
+        <v>3407.0</v>
+      </c>
+      <c r="L24">
+        <v>1995.0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" dyDescent="0.2">
+      <c r="A25">
+        <v>3</v>
+      </c>
+      <c r="B25" s="8">
+        <v>10</v>
+      </c>
+      <c r="C25" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="D25" t="s" s="1">
+        <v>60</v>
+      </c>
+      <c r="E25">
+        <v>89.0</v>
+      </c>
+      <c r="F25">
+        <v>68.0</v>
+      </c>
+      <c r="G25">
+        <v>13.6</v>
+      </c>
+      <c r="H25">
+        <v>6.5</v>
+      </c>
+      <c r="I25">
+        <v>1292.0</v>
+      </c>
+      <c r="J25">
+        <v>880.0</v>
+      </c>
+      <c r="K25">
+        <v>2172.0</v>
+      </c>
+      <c r="L25">
+        <v>1292.0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" dyDescent="0.2">
+      <c r="A26">
         <v>4</v>
       </c>
-      <c r="B15" s="8">
+      <c r="B26" s="8">
+        <v>5</v>
+      </c>
+      <c r="C26" t="s" s="1">
+        <v>54</v>
+      </c>
+      <c r="D26" t="s" s="1">
+        <v>55</v>
+      </c>
+      <c r="E26">
+        <v>130.0</v>
+      </c>
+      <c r="F26">
+        <v>93.0</v>
+      </c>
+      <c r="G26">
+        <v>18.6</v>
+      </c>
+      <c r="H26">
+        <v>7.0</v>
+      </c>
+      <c r="I26">
+        <v>1767.0</v>
+      </c>
+      <c r="J26">
+        <v>1300.0</v>
+      </c>
+      <c r="K26">
+        <v>3067.0</v>
+      </c>
+      <c r="L26">
+        <v>1767.0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" dyDescent="0.2">
+      <c r="A27">
         <v>4</v>
       </c>
-      <c r="I15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" dyDescent="0.4">
-      <c r="A16">
+      <c r="B27" s="8">
+        <v>6</v>
+      </c>
+      <c r="C27" t="s" s="1">
+        <v>54</v>
+      </c>
+      <c r="D27" t="s" s="1">
+        <v>56</v>
+      </c>
+      <c r="E27">
+        <v>149.0</v>
+      </c>
+      <c r="F27">
+        <v>161.0</v>
+      </c>
+      <c r="G27">
+        <v>32.2</v>
+      </c>
+      <c r="H27">
+        <v>4.6</v>
+      </c>
+      <c r="I27">
+        <v>3059.0</v>
+      </c>
+      <c r="J27">
+        <v>1363.0</v>
+      </c>
+      <c r="K27">
+        <v>4422.0</v>
+      </c>
+      <c r="L27">
+        <v>3059.0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" dyDescent="0.2">
+      <c r="A28">
+        <v>4</v>
+      </c>
+      <c r="B28" s="8">
+        <v>7</v>
+      </c>
+      <c r="C28" t="s" s="1">
+        <v>54</v>
+      </c>
+      <c r="D28" t="s" s="11">
+        <v>57</v>
+      </c>
+      <c r="E28">
+        <v>93.0</v>
+      </c>
+      <c r="F28">
+        <v>90.0</v>
+      </c>
+      <c r="G28">
+        <v>18.0</v>
+      </c>
+      <c r="H28">
+        <v>5.2</v>
+      </c>
+      <c r="I28">
+        <v>1710.0</v>
+      </c>
+      <c r="J28">
+        <v>875.0</v>
+      </c>
+      <c r="K28">
+        <v>2585.0</v>
+      </c>
+      <c r="L28">
+        <v>1710.0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" dyDescent="0.2">
+      <c r="A29">
+        <v>4</v>
+      </c>
+      <c r="B29" s="8">
+        <v>8</v>
+      </c>
+      <c r="C29" t="s" s="1">
+        <v>54</v>
+      </c>
+      <c r="D29" t="s" s="1">
+        <v>58</v>
+      </c>
+      <c r="E29">
+        <v>97.0</v>
+      </c>
+      <c r="F29">
+        <v>97.0</v>
+      </c>
+      <c r="G29">
+        <v>19.4</v>
+      </c>
+      <c r="H29">
+        <v>5.0</v>
+      </c>
+      <c r="I29">
+        <v>1843.0</v>
+      </c>
+      <c r="J29">
+        <v>905.0</v>
+      </c>
+      <c r="K29">
+        <v>2748.0</v>
+      </c>
+      <c r="L29">
+        <v>1843.0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" dyDescent="0.2">
+      <c r="A30">
+        <v>4</v>
+      </c>
+      <c r="B30" s="8">
+        <v>9</v>
+      </c>
+      <c r="C30" t="s" s="1">
+        <v>54</v>
+      </c>
+      <c r="D30" t="s" s="1">
+        <v>59</v>
+      </c>
+      <c r="E30">
+        <v>76.0</v>
+      </c>
+      <c r="F30">
+        <v>91.0</v>
+      </c>
+      <c r="G30">
+        <v>18.2</v>
+      </c>
+      <c r="H30">
+        <v>4.2</v>
+      </c>
+      <c r="I30">
+        <v>1729.0</v>
+      </c>
+      <c r="J30">
+        <v>674.0</v>
+      </c>
+      <c r="K30">
+        <v>2403.0</v>
+      </c>
+      <c r="L30">
+        <v>1729.0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" dyDescent="0.2">
+      <c r="A31">
+        <v>4</v>
+      </c>
+      <c r="B31" s="8">
+        <v>10</v>
+      </c>
+      <c r="C31" t="s" s="1">
+        <v>54</v>
+      </c>
+      <c r="D31" t="s" s="1">
+        <v>60</v>
+      </c>
+      <c r="E31">
+        <v>246.0</v>
+      </c>
+      <c r="F31">
+        <v>110.0</v>
+      </c>
+      <c r="G31">
+        <v>22.0</v>
+      </c>
+      <c r="H31">
+        <v>11.2</v>
+      </c>
+      <c r="I31">
+        <v>2090.0</v>
+      </c>
+      <c r="J31">
+        <v>2613.0</v>
+      </c>
+      <c r="K31">
+        <v>4703.0</v>
+      </c>
+      <c r="L31">
+        <v>2613.0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" dyDescent="0.2">
+      <c r="A32">
         <v>5</v>
       </c>
-      <c r="B16" s="8">
+      <c r="B32" s="8">
+        <v>6</v>
+      </c>
+      <c r="C32" t="s" s="1">
+        <v>55</v>
+      </c>
+      <c r="D32" t="s" s="1">
+        <v>56</v>
+      </c>
+      <c r="E32">
+        <v>110.0</v>
+      </c>
+      <c r="F32">
+        <v>70.0</v>
+      </c>
+      <c r="G32">
+        <v>14.0</v>
+      </c>
+      <c r="H32">
+        <v>7.9</v>
+      </c>
+      <c r="I32">
+        <v>1330.0</v>
+      </c>
+      <c r="J32">
+        <v>1120.0</v>
+      </c>
+      <c r="K32">
+        <v>2450.0</v>
+      </c>
+      <c r="L32">
+        <v>1330.0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" dyDescent="0.2">
+      <c r="A33" s="10">
         <v>5</v>
       </c>
-      <c r="E16" s="6"/>
-      <c r="I16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" dyDescent="0.4">
-      <c r="E20" s="1"/>
-    </row>
-    <row r="21" spans="1:14" dyDescent="0.4">
-      <c r="E21" s="2"/>
-    </row>
-    <row r="22" spans="1:14" dyDescent="0.4">
-      <c r="E22" s="2"/>
-    </row>
-    <row r="23" spans="1:14" dyDescent="0.4">
-      <c r="E23" s="1"/>
-    </row>
-    <row r="24" spans="1:14" dyDescent="0.4">
-      <c r="E24" s="1"/>
+      <c r="B33" s="8">
+        <v>7</v>
+      </c>
+      <c r="C33" t="s" s="1">
+        <v>55</v>
+      </c>
+      <c r="D33" t="s" s="11">
+        <v>57</v>
+      </c>
+      <c r="E33">
+        <v>168.0</v>
+      </c>
+      <c r="F33">
+        <v>173.0</v>
+      </c>
+      <c r="G33">
+        <v>34.6</v>
+      </c>
+      <c r="H33">
+        <v>4.9</v>
+      </c>
+      <c r="I33">
+        <v>3287.0</v>
+      </c>
+      <c r="J33">
+        <v>1556.0</v>
+      </c>
+      <c r="K33">
+        <v>4843.0</v>
+      </c>
+      <c r="L33">
+        <v>3287.0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" dyDescent="0.2">
+      <c r="A34">
+        <v>5</v>
+      </c>
+      <c r="B34" s="8">
+        <v>8</v>
+      </c>
+      <c r="C34" t="s" s="1">
+        <v>55</v>
+      </c>
+      <c r="D34" t="s" s="1">
+        <v>58</v>
+      </c>
+      <c r="E34">
+        <v>48.0</v>
+      </c>
+      <c r="F34">
+        <v>40.0</v>
+      </c>
+      <c r="G34">
+        <v>8.0</v>
+      </c>
+      <c r="H34">
+        <v>6.0</v>
+      </c>
+      <c r="I34">
+        <v>760.0</v>
+      </c>
+      <c r="J34">
+        <v>467.0</v>
+      </c>
+      <c r="K34">
+        <v>1227.0</v>
+      </c>
+      <c r="L34">
+        <v>760.0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" dyDescent="0.2">
+      <c r="A35">
+        <v>5</v>
+      </c>
+      <c r="B35" s="8">
+        <v>9</v>
+      </c>
+      <c r="C35" t="s" s="1">
+        <v>55</v>
+      </c>
+      <c r="D35" t="s" s="1">
+        <v>59</v>
+      </c>
+      <c r="E35">
+        <v>60.0</v>
+      </c>
+      <c r="F35">
+        <v>55.0</v>
+      </c>
+      <c r="G35">
+        <v>11.0</v>
+      </c>
+      <c r="H35">
+        <v>5.5</v>
+      </c>
+      <c r="I35">
+        <v>1045.0</v>
+      </c>
+      <c r="J35">
+        <v>572.0</v>
+      </c>
+      <c r="K35">
+        <v>1617.0</v>
+      </c>
+      <c r="L35">
+        <v>1045.0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" dyDescent="0.2">
+      <c r="A36">
+        <v>5</v>
+      </c>
+      <c r="B36" s="8">
+        <v>10</v>
+      </c>
+      <c r="C36" t="s" s="1">
+        <v>55</v>
+      </c>
+      <c r="D36" t="s" s="1">
+        <v>60</v>
+      </c>
+      <c r="E36">
+        <v>145.0</v>
+      </c>
+      <c r="F36">
+        <v>131.0</v>
+      </c>
+      <c r="G36">
+        <v>26.2</v>
+      </c>
+      <c r="H36">
+        <v>5.5</v>
+      </c>
+      <c r="I36">
+        <v>2489.0</v>
+      </c>
+      <c r="J36">
+        <v>1386.0</v>
+      </c>
+      <c r="K36">
+        <v>3875.0</v>
+      </c>
+      <c r="L36">
+        <v>2489.0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" dyDescent="0.2">
+      <c r="A37">
+        <v>6</v>
+      </c>
+      <c r="B37" s="8">
+        <v>7</v>
+      </c>
+      <c r="C37" t="s" s="1">
+        <v>56</v>
+      </c>
+      <c r="D37" t="s" s="11">
+        <v>57</v>
+      </c>
+      <c r="E37">
+        <v>185.0</v>
+      </c>
+      <c r="F37">
+        <v>232.0</v>
+      </c>
+      <c r="G37">
+        <v>46.4</v>
+      </c>
+      <c r="H37">
+        <v>4.0</v>
+      </c>
+      <c r="I37">
+        <v>4408.0</v>
+      </c>
+      <c r="J37">
+        <v>1617.0</v>
+      </c>
+      <c r="K37">
+        <v>6025.0</v>
+      </c>
+      <c r="L37">
+        <v>4408.0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" dyDescent="0.2">
+      <c r="A38">
+        <v>6</v>
+      </c>
+      <c r="B38" s="8">
+        <v>8</v>
+      </c>
+      <c r="C38" t="s" s="1">
+        <v>56</v>
+      </c>
+      <c r="D38" t="s" s="1">
+        <v>58</v>
+      </c>
+      <c r="E38">
+        <v>77.0</v>
+      </c>
+      <c r="F38">
+        <v>72.0</v>
+      </c>
+      <c r="G38">
+        <v>14.4</v>
+      </c>
+      <c r="H38">
+        <v>5.3</v>
+      </c>
+      <c r="I38">
+        <v>1368.0</v>
+      </c>
+      <c r="J38">
+        <v>730.0</v>
+      </c>
+      <c r="K38">
+        <v>2098.0</v>
+      </c>
+      <c r="L38">
+        <v>1368.0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" dyDescent="0.2">
+      <c r="A39">
+        <v>6</v>
+      </c>
+      <c r="B39" s="8">
+        <v>9</v>
+      </c>
+      <c r="C39" t="s" s="1">
+        <v>56</v>
+      </c>
+      <c r="D39" t="s" s="1">
+        <v>59</v>
+      </c>
+      <c r="E39">
+        <v>78.0</v>
+      </c>
+      <c r="F39">
+        <v>89.0</v>
+      </c>
+      <c r="G39">
+        <v>17.8</v>
+      </c>
+      <c r="H39">
+        <v>4.4</v>
+      </c>
+      <c r="I39">
+        <v>1691.0</v>
+      </c>
+      <c r="J39">
+        <v>702.0</v>
+      </c>
+      <c r="K39">
+        <v>2393.0</v>
+      </c>
+      <c r="L39">
+        <v>1691.0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" dyDescent="0.2">
+      <c r="A40">
+        <v>6</v>
+      </c>
+      <c r="B40" s="8">
+        <v>10</v>
+      </c>
+      <c r="C40" t="s" s="1">
+        <v>56</v>
+      </c>
+      <c r="D40" t="s" s="1">
+        <v>60</v>
+      </c>
+      <c r="E40">
+        <v>224.0</v>
+      </c>
+      <c r="F40">
+        <v>192.0</v>
+      </c>
+      <c r="G40">
+        <v>38.4</v>
+      </c>
+      <c r="H40">
+        <v>5.8</v>
+      </c>
+      <c r="I40">
+        <v>3648.0</v>
+      </c>
+      <c r="J40">
+        <v>2165.0</v>
+      </c>
+      <c r="K40">
+        <v>5813.0</v>
+      </c>
+      <c r="L40">
+        <v>3648.0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" dyDescent="0.2">
+      <c r="A41">
+        <v>7</v>
+      </c>
+      <c r="B41" s="8">
+        <v>8</v>
+      </c>
+      <c r="C41" t="s" s="1">
+        <v>57</v>
+      </c>
+      <c r="D41" t="s" s="1">
+        <v>58</v>
+      </c>
+      <c r="E41">
+        <v>131.0</v>
+      </c>
+      <c r="F41">
+        <v>160.0</v>
+      </c>
+      <c r="G41">
+        <v>32.0</v>
+      </c>
+      <c r="H41">
+        <v>4.1</v>
+      </c>
+      <c r="I41">
+        <v>3040.0</v>
+      </c>
+      <c r="J41">
+        <v>1155.0</v>
+      </c>
+      <c r="K41">
+        <v>4195.0</v>
+      </c>
+      <c r="L41">
+        <v>3040.0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" dyDescent="0.2">
+      <c r="A42">
+        <v>7</v>
+      </c>
+      <c r="B42" s="8">
+        <v>9</v>
+      </c>
+      <c r="C42" t="s" s="1">
+        <v>57</v>
+      </c>
+      <c r="D42" t="s" s="1">
+        <v>59</v>
+      </c>
+      <c r="E42">
+        <v>110.0</v>
+      </c>
+      <c r="F42">
+        <v>146.0</v>
+      </c>
+      <c r="G42">
+        <v>29.2</v>
+      </c>
+      <c r="H42">
+        <v>3.8</v>
+      </c>
+      <c r="I42">
+        <v>2774.0</v>
+      </c>
+      <c r="J42">
+        <v>943.0</v>
+      </c>
+      <c r="K42">
+        <v>3717.0</v>
+      </c>
+      <c r="L42">
+        <v>2774.0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" dyDescent="0.2">
+      <c r="A43">
+        <v>7</v>
+      </c>
+      <c r="B43" s="8">
+        <v>10</v>
+      </c>
+      <c r="C43" t="s" s="1">
+        <v>57</v>
+      </c>
+      <c r="D43" t="s" s="1">
+        <v>60</v>
+      </c>
+      <c r="E43">
+        <v>280.0</v>
+      </c>
+      <c r="F43">
+        <v>187.0</v>
+      </c>
+      <c r="G43">
+        <v>37.4</v>
+      </c>
+      <c r="H43">
+        <v>7.5</v>
+      </c>
+      <c r="I43">
+        <v>3553.0</v>
+      </c>
+      <c r="J43">
+        <v>2830.0</v>
+      </c>
+      <c r="K43">
+        <v>6383.0</v>
+      </c>
+      <c r="L43">
+        <v>3553.0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" dyDescent="0.2">
+      <c r="A44">
+        <v>8</v>
+      </c>
+      <c r="B44" s="8">
+        <v>9</v>
+      </c>
+      <c r="C44" t="s" s="1">
+        <v>58</v>
+      </c>
+      <c r="D44" t="s" s="1">
+        <v>59</v>
+      </c>
+      <c r="E44">
+        <v>26.0</v>
+      </c>
+      <c r="F44">
+        <v>19.0</v>
+      </c>
+      <c r="G44">
+        <v>3.8</v>
+      </c>
+      <c r="H44">
+        <v>6.8</v>
+      </c>
+      <c r="I44">
+        <v>361.0</v>
+      </c>
+      <c r="J44">
+        <v>259.0</v>
+      </c>
+      <c r="K44">
+        <v>620.0</v>
+      </c>
+      <c r="L44">
+        <v>361.0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" dyDescent="0.2">
+      <c r="A45">
+        <v>8</v>
+      </c>
+      <c r="B45" s="8">
+        <v>10</v>
+      </c>
+      <c r="C45" t="s" s="1">
+        <v>58</v>
+      </c>
+      <c r="D45" t="s" s="1">
+        <v>60</v>
+      </c>
+      <c r="E45">
+        <v>163.0</v>
+      </c>
+      <c r="F45">
+        <v>164.0</v>
+      </c>
+      <c r="G45">
+        <v>32.8</v>
+      </c>
+      <c r="H45">
+        <v>5.0</v>
+      </c>
+      <c r="I45">
+        <v>3116.0</v>
+      </c>
+      <c r="J45">
+        <v>1519.0</v>
+      </c>
+      <c r="K45">
+        <v>4635.0</v>
+      </c>
+      <c r="L45">
+        <v>3116.0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" dyDescent="0.2">
+      <c r="A46">
+        <v>9</v>
+      </c>
+      <c r="B46" s="8">
+        <v>10</v>
+      </c>
+      <c r="C46" t="s" s="1">
+        <v>59</v>
+      </c>
+      <c r="D46" t="s" s="1">
+        <v>60</v>
+      </c>
+      <c r="E46">
+        <v>175.0</v>
+      </c>
+      <c r="F46">
+        <v>170.0</v>
+      </c>
+      <c r="G46">
+        <v>34.0</v>
+      </c>
+      <c r="H46">
+        <v>5.1</v>
+      </c>
+      <c r="I46">
+        <v>3230.0</v>
+      </c>
+      <c r="J46">
+        <v>1645.0</v>
+      </c>
+      <c r="K46">
+        <v>4875.0</v>
+      </c>
+      <c r="L46">
+        <v>3230.0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" dyDescent="0.2">
+      <c r="A47">
+        <v>1</v>
+      </c>
+      <c r="B47" s="8">
+        <v>1</v>
+      </c>
+      <c r="C47" s="8"/>
+      <c r="D47" s="8"/>
+      <c r="E47">
+        <v>0</v>
+      </c>
+      <c r="F47">
+        <v>0</v>
+      </c>
+      <c r="G47">
+        <v>0</v>
+      </c>
+      <c r="H47">
+        <v>0</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>0</v>
+      </c>
+      <c r="K47">
+        <v>0</v>
+      </c>
+      <c r="L47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16" dyDescent="0.2">
+      <c r="A48">
+        <v>2</v>
+      </c>
+      <c r="B48" s="8">
+        <v>2</v>
+      </c>
+      <c r="C48" s="8"/>
+      <c r="D48" s="8"/>
+      <c r="E48">
+        <v>0</v>
+      </c>
+      <c r="F48">
+        <v>0</v>
+      </c>
+      <c r="G48">
+        <v>0</v>
+      </c>
+      <c r="H48">
+        <v>0</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
+      <c r="K48">
+        <v>0</v>
+      </c>
+      <c r="L48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16" dyDescent="0.2">
+      <c r="A49">
+        <v>3</v>
+      </c>
+      <c r="B49" s="8">
+        <v>3</v>
+      </c>
+      <c r="C49" s="8"/>
+      <c r="D49" s="8"/>
+      <c r="E49">
+        <v>0</v>
+      </c>
+      <c r="F49">
+        <v>0</v>
+      </c>
+      <c r="G49">
+        <v>0</v>
+      </c>
+      <c r="H49">
+        <v>0</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>0</v>
+      </c>
+      <c r="K49">
+        <v>0</v>
+      </c>
+      <c r="L49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16" dyDescent="0.2">
+      <c r="A50">
+        <v>4</v>
+      </c>
+      <c r="B50" s="8">
+        <v>4</v>
+      </c>
+      <c r="C50" s="8"/>
+      <c r="D50" s="8"/>
+      <c r="E50">
+        <v>0</v>
+      </c>
+      <c r="F50">
+        <v>0</v>
+      </c>
+      <c r="G50">
+        <v>0</v>
+      </c>
+      <c r="H50">
+        <v>0</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>0</v>
+      </c>
+      <c r="K50">
+        <v>0</v>
+      </c>
+      <c r="L50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16" dyDescent="0.2">
+      <c r="A51">
+        <v>5</v>
+      </c>
+      <c r="B51" s="8">
+        <v>5</v>
+      </c>
+      <c r="C51" s="8"/>
+      <c r="D51" s="8"/>
+      <c r="E51">
+        <v>0</v>
+      </c>
+      <c r="F51">
+        <v>0</v>
+      </c>
+      <c r="G51">
+        <v>0</v>
+      </c>
+      <c r="H51">
+        <v>0</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>0</v>
+      </c>
+      <c r="K51">
+        <v>0</v>
+      </c>
+      <c r="L51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16" dyDescent="0.2">
+      <c r="A52">
+        <v>6</v>
+      </c>
+      <c r="B52" s="8">
+        <v>6</v>
+      </c>
+      <c r="E52">
+        <v>0</v>
+      </c>
+      <c r="F52">
+        <v>0</v>
+      </c>
+      <c r="G52">
+        <v>0</v>
+      </c>
+      <c r="H52">
+        <v>0</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>0</v>
+      </c>
+      <c r="K52">
+        <v>0</v>
+      </c>
+      <c r="L52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16" dyDescent="0.2">
+      <c r="A53">
+        <v>7</v>
+      </c>
+      <c r="B53" s="8">
+        <v>7</v>
+      </c>
+      <c r="E53">
+        <v>0</v>
+      </c>
+      <c r="F53">
+        <v>0</v>
+      </c>
+      <c r="G53">
+        <v>0</v>
+      </c>
+      <c r="H53">
+        <v>0</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>0</v>
+      </c>
+      <c r="K53">
+        <v>0</v>
+      </c>
+      <c r="L53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16" dyDescent="0.2">
+      <c r="A54">
+        <v>8</v>
+      </c>
+      <c r="B54" s="8">
+        <v>8</v>
+      </c>
+      <c r="E54">
+        <v>0</v>
+      </c>
+      <c r="F54">
+        <v>0</v>
+      </c>
+      <c r="G54">
+        <v>0</v>
+      </c>
+      <c r="H54">
+        <v>0</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>0</v>
+      </c>
+      <c r="K54">
+        <v>0</v>
+      </c>
+      <c r="L54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16" dyDescent="0.2">
+      <c r="A55">
+        <v>9</v>
+      </c>
+      <c r="B55" s="8">
+        <v>9</v>
+      </c>
+      <c r="E55">
+        <v>0</v>
+      </c>
+      <c r="F55">
+        <v>0</v>
+      </c>
+      <c r="G55">
+        <v>0</v>
+      </c>
+      <c r="H55">
+        <v>0</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>0</v>
+      </c>
+      <c r="K55">
+        <v>0</v>
+      </c>
+      <c r="L55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16" dyDescent="0.2">
+      <c r="A56">
+        <v>10</v>
+      </c>
+      <c r="B56" s="8">
+        <v>10</v>
+      </c>
+      <c r="E56">
+        <v>0</v>
+      </c>
+      <c r="F56">
+        <v>0</v>
+      </c>
+      <c r="G56">
+        <v>0</v>
+      </c>
+      <c r="H56">
+        <v>0</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>0</v>
+      </c>
+      <c r="K56">
+        <v>0</v>
+      </c>
+      <c r="L56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16" dyDescent="0.2">
+      <c r="G57" s="2"/>
+    </row>
+    <row r="58" spans="1:16" dyDescent="0.2">
+      <c r="G58" s="1"/>
+    </row>
+    <row r="59" spans="1:16" dyDescent="0.2">
+      <c r="G59" s="1"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="G2:G11">
+  <conditionalFormatting sqref="I2:I46">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -1380,7 +3015,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H11">
+  <conditionalFormatting sqref="J2:J46">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -1392,7 +3027,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I11">
+  <conditionalFormatting sqref="K2:K46">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -1404,7 +3039,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J11">
+  <conditionalFormatting sqref="L2:L46">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>

--- a/inputData/Parameters.xlsx
+++ b/inputData/Parameters.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sillewiberg/Desktop/Skole/Speciale/Master-Thesis-eVTOL-1/inputData/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kapta\Documents\DTU\Speciale\GitHubFiles\inputData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC525445-B921-7444-8BE9-F0D2537C0186}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CBE765F-9084-4140-9ADF-71B92BC0CEA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16320" activeTab="1" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
   </bookViews>
   <sheets>
     <sheet name="Parameters" sheetId="9" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="61">
   <si>
     <t>cap_u</t>
   </si>
@@ -647,19 +647,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B15C49E0-A7B4-734A-8962-DC2A879F4079}">
   <dimension ref="A1:D20"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="22.6640625" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:4" dyDescent="0.2">
-      <c r="A2" t="s" s="1">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A2" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B2" s="4">
@@ -669,7 +669,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" dyDescent="0.2">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -680,7 +680,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:4" dyDescent="0.2">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>46</v>
       </c>
@@ -691,7 +691,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="5" spans="1:4" dyDescent="0.2">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -702,7 +702,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="6" spans="1:4" dyDescent="0.2">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -713,7 +713,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:4" dyDescent="0.2">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -724,7 +724,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:4" dyDescent="0.2">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -736,7 +736,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:4" dyDescent="0.2">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
         <v>0</v>
       </c>
@@ -747,7 +747,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:4" dyDescent="0.2">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
         <v>1</v>
       </c>
@@ -758,7 +758,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:4" dyDescent="0.2">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
         <v>45</v>
       </c>
@@ -769,7 +769,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="12" spans="1:4" dyDescent="0.2">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
         <v>2</v>
       </c>
@@ -780,18 +780,18 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="13" spans="1:4" dyDescent="0.2">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
         <v>42</v>
       </c>
       <c r="B13" s="4">
         <v>20</v>
       </c>
-      <c r="D13" t="s" s="3">
+      <c r="D13" s="3" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="14" spans="1:4" dyDescent="0.2">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -799,11 +799,11 @@
         <f>2.11*B20</f>
         <v>2.11</v>
       </c>
-      <c r="D14" t="s" s="3">
+      <c r="D14" s="3" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="15" spans="1:4" dyDescent="0.2">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
         <v>4</v>
       </c>
@@ -811,11 +811,11 @@
         <f>30/B20</f>
         <v>30</v>
       </c>
-      <c r="D15" t="s" s="3">
+      <c r="D15" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:4" dyDescent="0.2">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
         <v>5</v>
       </c>
@@ -823,30 +823,29 @@
         <f>20/B20</f>
         <v>20</v>
       </c>
-      <c r="D16" t="s" s="3">
+      <c r="D16" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:4" dyDescent="0.2">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
         <v>6</v>
       </c>
       <c r="B17" s="4">
-        <f>120/B20</f>
-        <v>120</v>
-      </c>
-      <c r="D17" t="s" s="3">
+        <v>780</v>
+      </c>
+      <c r="D17" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:4" dyDescent="0.2">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
         <v>41</v>
       </c>
       <c r="B20" s="4">
         <v>1</v>
       </c>
-      <c r="D20" t="s" s="3">
+      <c r="D20" s="3" t="s">
         <v>48</v>
       </c>
     </row>
@@ -859,7 +858,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAF0D5EA-53B5-1240-9D84-6FE223856A18}">
   <dimension ref="A1:P59"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="17.1640625" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="17.1640625" customWidth="1"/>
@@ -869,44 +868,44 @@
     <col min="8" max="8" width="18.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" dyDescent="0.2">
-      <c r="A1" t="s" s="9">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A1" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="B1" t="s" s="5">
+      <c r="B1" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C1" t="s" s="5">
+      <c r="C1" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="D1" t="s" s="5">
+      <c r="D1" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="E1" t="s" s="5">
+      <c r="E1" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="F1" t="s" s="5">
+      <c r="F1" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="G1" t="s" s="5">
+      <c r="G1" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="H1" t="s" s="5">
+      <c r="H1" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="I1" t="s" s="5">
+      <c r="I1" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="J1" t="s" s="5">
+      <c r="J1" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="K1" t="s" s="5">
+      <c r="K1" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="L1" t="s" s="5">
+      <c r="L1" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="N1" t="s" s="6">
+      <c r="N1" s="6" t="s">
         <v>19</v>
       </c>
       <c r="O1" s="7">
@@ -914,24 +913,24 @@
       </c>
       <c r="P1" s="6"/>
     </row>
-    <row r="2" spans="1:16" dyDescent="0.2">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" s="8">
         <v>2</v>
       </c>
-      <c r="C2" t="s" s="1">
+      <c r="C2" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D2" t="s" s="2">
+      <c r="D2" s="2" t="s">
         <v>52</v>
       </c>
       <c r="E2">
-        <v>185.0</v>
+        <v>185</v>
       </c>
       <c r="F2">
-        <v>219.0</v>
+        <v>219</v>
       </c>
       <c r="G2">
         <v>43.8</v>
@@ -940,16 +939,16 @@
         <v>4.2</v>
       </c>
       <c r="I2">
-        <v>4161.0</v>
+        <v>4161</v>
       </c>
       <c r="J2">
-        <v>1647.0</v>
+        <v>1647</v>
       </c>
       <c r="K2">
-        <v>5808.0</v>
+        <v>5808</v>
       </c>
       <c r="L2">
-        <v>4161.0</v>
+        <v>4161</v>
       </c>
       <c r="N2" t="s">
         <v>29</v>
@@ -961,42 +960,42 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:16" dyDescent="0.2">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" s="8">
         <v>3</v>
       </c>
-      <c r="C3" t="s" s="1">
+      <c r="C3" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D3" t="s" s="2">
+      <c r="D3" s="2" t="s">
         <v>53</v>
       </c>
       <c r="E3">
-        <v>82.0</v>
+        <v>82</v>
       </c>
       <c r="F3">
-        <v>88.0</v>
+        <v>88</v>
       </c>
       <c r="G3">
-        <v>17.6</v>
+        <v>17.600000000000001</v>
       </c>
       <c r="H3">
         <v>4.7</v>
       </c>
       <c r="I3">
-        <v>1672.0</v>
+        <v>1672</v>
       </c>
       <c r="J3">
-        <v>751.0</v>
+        <v>751</v>
       </c>
       <c r="K3">
-        <v>2423.0</v>
+        <v>2423</v>
       </c>
       <c r="L3">
-        <v>1672.0</v>
+        <v>1672</v>
       </c>
       <c r="N3" t="s">
         <v>31</v>
@@ -1009,24 +1008,24 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:16" dyDescent="0.2">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>1</v>
       </c>
       <c r="B4" s="8">
         <v>4</v>
       </c>
-      <c r="C4" t="s" s="1">
+      <c r="C4" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D4" t="s" s="1">
+      <c r="D4" s="1" t="s">
         <v>54</v>
       </c>
       <c r="E4">
-        <v>228.0</v>
+        <v>228</v>
       </c>
       <c r="F4">
-        <v>147.0</v>
+        <v>147</v>
       </c>
       <c r="G4">
         <v>29.4</v>
@@ -1035,16 +1034,16 @@
         <v>7.8</v>
       </c>
       <c r="I4">
-        <v>2793.0</v>
+        <v>2793</v>
       </c>
       <c r="J4">
-        <v>2317.0</v>
+        <v>2317</v>
       </c>
       <c r="K4">
-        <v>5110.0</v>
+        <v>5110</v>
       </c>
       <c r="L4">
-        <v>2793.0</v>
+        <v>2793</v>
       </c>
       <c r="N4" t="s">
         <v>33</v>
@@ -1053,24 +1052,24 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="5" spans="1:16" dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>1</v>
       </c>
       <c r="B5" s="8">
         <v>5</v>
       </c>
-      <c r="C5" t="s" s="1">
+      <c r="C5" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D5" t="s" s="1">
+      <c r="D5" s="1" t="s">
         <v>55</v>
       </c>
       <c r="E5">
-        <v>126.0</v>
+        <v>126</v>
       </c>
       <c r="F5">
-        <v>147.0</v>
+        <v>147</v>
       </c>
       <c r="G5">
         <v>29.4</v>
@@ -1079,16 +1078,16 @@
         <v>4.3</v>
       </c>
       <c r="I5">
-        <v>2793.0</v>
+        <v>2793</v>
       </c>
       <c r="J5">
-        <v>1127.0</v>
+        <v>1127</v>
       </c>
       <c r="K5">
-        <v>3920.0</v>
+        <v>3920</v>
       </c>
       <c r="L5">
-        <v>2793.0</v>
+        <v>2793</v>
       </c>
       <c r="N5" t="s">
         <v>34</v>
@@ -1100,24 +1099,24 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:16" dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>1</v>
       </c>
       <c r="B6" s="8">
         <v>6</v>
       </c>
-      <c r="C6" t="s" s="1">
+      <c r="C6" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D6" t="s" s="1">
+      <c r="D6" s="1" t="s">
         <v>56</v>
       </c>
       <c r="E6">
-        <v>205.0</v>
+        <v>205</v>
       </c>
       <c r="F6">
-        <v>197.0</v>
+        <v>197</v>
       </c>
       <c r="G6">
         <v>39.4</v>
@@ -1126,37 +1125,37 @@
         <v>5.2</v>
       </c>
       <c r="I6">
-        <v>3743.0</v>
+        <v>3743</v>
       </c>
       <c r="J6">
-        <v>1932.0</v>
+        <v>1932</v>
       </c>
       <c r="K6">
-        <v>5675.0</v>
+        <v>5675</v>
       </c>
       <c r="L6">
-        <v>3743.0</v>
+        <v>3743</v>
       </c>
       <c r="O6" s="4"/>
     </row>
-    <row r="7" spans="1:16" dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>1</v>
       </c>
       <c r="B7" s="8">
         <v>7</v>
       </c>
-      <c r="C7" t="s" s="1">
+      <c r="C7" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D7" t="s" s="1">
+      <c r="D7" s="1" t="s">
         <v>57</v>
       </c>
       <c r="E7">
-        <v>263.0</v>
+        <v>263</v>
       </c>
       <c r="F7">
-        <v>227.0</v>
+        <v>227</v>
       </c>
       <c r="G7">
         <v>45.4</v>
@@ -1165,154 +1164,154 @@
         <v>5.8</v>
       </c>
       <c r="I7">
-        <v>4313.0</v>
+        <v>4313</v>
       </c>
       <c r="J7">
-        <v>2539.0</v>
+        <v>2539</v>
       </c>
       <c r="K7">
-        <v>6852.0</v>
+        <v>6852</v>
       </c>
       <c r="L7">
-        <v>4313.0</v>
+        <v>4313</v>
       </c>
       <c r="O7" s="4"/>
     </row>
-    <row r="8" spans="1:16" dyDescent="0.2">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>1</v>
       </c>
       <c r="B8" s="8">
         <v>8</v>
       </c>
-      <c r="C8" t="s" s="1">
+      <c r="C8" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D8" t="s" s="1">
+      <c r="D8" s="1" t="s">
         <v>58</v>
       </c>
       <c r="E8">
-        <v>143.0</v>
+        <v>143</v>
       </c>
       <c r="F8">
-        <v>184.0</v>
+        <v>184</v>
       </c>
       <c r="G8">
-        <v>36.8</v>
+        <v>36.799999999999997</v>
       </c>
       <c r="H8">
         <v>3.9</v>
       </c>
       <c r="I8">
-        <v>3496.0</v>
+        <v>3496</v>
       </c>
       <c r="J8">
-        <v>1239.0</v>
+        <v>1239</v>
       </c>
       <c r="K8">
-        <v>4735.0</v>
+        <v>4735</v>
       </c>
       <c r="L8">
-        <v>3496.0</v>
+        <v>3496</v>
       </c>
       <c r="O8" s="4"/>
     </row>
-    <row r="9" spans="1:16" dyDescent="0.2">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>1</v>
       </c>
       <c r="B9" s="8">
         <v>9</v>
       </c>
-      <c r="C9" t="s" s="1">
+      <c r="C9" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D9" t="s" s="1">
+      <c r="D9" s="1" t="s">
         <v>59</v>
       </c>
       <c r="E9">
-        <v>155.0</v>
+        <v>155</v>
       </c>
       <c r="F9">
-        <v>193.0</v>
+        <v>193</v>
       </c>
       <c r="G9">
         <v>38.6</v>
       </c>
       <c r="H9">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="I9">
-        <v>3667.0</v>
+        <v>3667</v>
       </c>
       <c r="J9">
-        <v>1358.0</v>
+        <v>1358</v>
       </c>
       <c r="K9">
-        <v>5025.0</v>
+        <v>5025</v>
       </c>
       <c r="L9">
-        <v>3667.0</v>
+        <v>3667</v>
       </c>
       <c r="O9" s="4"/>
     </row>
-    <row r="10" spans="1:16" dyDescent="0.2">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>1</v>
       </c>
       <c r="B10" s="8">
         <v>10</v>
       </c>
-      <c r="C10" t="s" s="1">
+      <c r="C10" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D10" t="s" s="1">
+      <c r="D10" s="1" t="s">
         <v>60</v>
       </c>
       <c r="E10">
-        <v>42.0</v>
+        <v>42</v>
       </c>
       <c r="F10">
-        <v>41.0</v>
+        <v>41</v>
       </c>
       <c r="G10">
-        <v>8.2</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="H10">
-        <v>5.1</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="I10">
-        <v>779.0</v>
+        <v>779</v>
       </c>
       <c r="J10">
-        <v>394.0</v>
+        <v>394</v>
       </c>
       <c r="K10">
-        <v>1173.0</v>
+        <v>1173</v>
       </c>
       <c r="L10">
-        <v>779.0</v>
+        <v>779</v>
       </c>
       <c r="O10" s="4"/>
     </row>
-    <row r="11" spans="1:16" dyDescent="0.2">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>2</v>
       </c>
       <c r="B11" s="8">
         <v>3</v>
       </c>
-      <c r="C11" t="s" s="2">
+      <c r="C11" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D11" t="s" s="2">
+      <c r="D11" s="2" t="s">
         <v>53</v>
       </c>
       <c r="E11">
-        <v>173.0</v>
+        <v>173</v>
       </c>
       <c r="F11">
-        <v>131.0</v>
+        <v>131</v>
       </c>
       <c r="G11">
         <v>26.2</v>
@@ -1321,226 +1320,226 @@
         <v>6.6</v>
       </c>
       <c r="I11">
-        <v>2489.0</v>
+        <v>2489</v>
       </c>
       <c r="J11">
-        <v>1713.0</v>
+        <v>1713</v>
       </c>
       <c r="K11">
-        <v>4202.0</v>
+        <v>4202</v>
       </c>
       <c r="L11">
-        <v>2489.0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" dyDescent="0.2">
+        <v>2489</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>2</v>
       </c>
       <c r="B12" s="8">
         <v>4</v>
       </c>
-      <c r="C12" t="s" s="2">
+      <c r="C12" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D12" t="s" s="1">
+      <c r="D12" s="1" t="s">
         <v>54</v>
       </c>
       <c r="E12">
-        <v>103.0</v>
+        <v>103</v>
       </c>
       <c r="F12">
-        <v>110.0</v>
+        <v>110</v>
       </c>
       <c r="G12">
-        <v>22.0</v>
+        <v>22</v>
       </c>
       <c r="H12">
         <v>4.7</v>
       </c>
       <c r="I12">
-        <v>2090.0</v>
+        <v>2090</v>
       </c>
       <c r="J12">
-        <v>945.0</v>
+        <v>945</v>
       </c>
       <c r="K12">
-        <v>3035.0</v>
+        <v>3035</v>
       </c>
       <c r="L12">
-        <v>2090.0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" dyDescent="0.2">
+        <v>2090</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>2</v>
       </c>
       <c r="B13" s="8">
         <v>5</v>
       </c>
-      <c r="C13" t="s" s="2">
+      <c r="C13" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D13" t="s" s="1">
+      <c r="D13" s="1" t="s">
         <v>55</v>
       </c>
       <c r="E13">
-        <v>89.0</v>
+        <v>89</v>
       </c>
       <c r="F13">
-        <v>80.0</v>
+        <v>80</v>
       </c>
       <c r="G13">
-        <v>16.0</v>
+        <v>16</v>
       </c>
       <c r="H13">
         <v>5.6</v>
       </c>
       <c r="I13">
-        <v>1520.0</v>
+        <v>1520</v>
       </c>
       <c r="J13">
-        <v>852.0</v>
+        <v>852</v>
       </c>
       <c r="K13">
-        <v>2372.0</v>
+        <v>2372</v>
       </c>
       <c r="L13">
-        <v>1520.0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" dyDescent="0.2">
+        <v>1520</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>2</v>
       </c>
       <c r="B14" s="8">
         <v>6</v>
       </c>
-      <c r="C14" t="s" s="2">
+      <c r="C14" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D14" t="s" s="1">
+      <c r="D14" s="1" t="s">
         <v>56</v>
       </c>
       <c r="E14">
-        <v>100.0</v>
+        <v>100</v>
       </c>
       <c r="F14">
-        <v>98.0</v>
+        <v>98</v>
       </c>
       <c r="G14">
-        <v>19.6</v>
+        <v>19.600000000000001</v>
       </c>
       <c r="H14">
-        <v>5.1</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="I14">
-        <v>1862.0</v>
+        <v>1862</v>
       </c>
       <c r="J14">
-        <v>938.0</v>
+        <v>938</v>
       </c>
       <c r="K14">
-        <v>2800.0</v>
+        <v>2800</v>
       </c>
       <c r="L14">
-        <v>1862.0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" dyDescent="0.2">
+        <v>1862</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>2</v>
       </c>
       <c r="B15" s="8">
         <v>7</v>
       </c>
-      <c r="C15" t="s" s="2">
+      <c r="C15" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D15" t="s" s="11">
+      <c r="D15" s="11" t="s">
         <v>57</v>
       </c>
       <c r="E15">
-        <v>138.0</v>
+        <v>138</v>
       </c>
       <c r="F15">
-        <v>151.0</v>
+        <v>151</v>
       </c>
       <c r="G15">
         <v>30.2</v>
       </c>
       <c r="H15">
-        <v>4.6</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="I15">
-        <v>2869.0</v>
+        <v>2869</v>
       </c>
       <c r="J15">
-        <v>1258.0</v>
+        <v>1258</v>
       </c>
       <c r="K15">
-        <v>4127.0</v>
+        <v>4127</v>
       </c>
       <c r="L15">
-        <v>2869.0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" dyDescent="0.2">
+        <v>2869</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A16">
         <v>2</v>
       </c>
       <c r="B16" s="8">
         <v>8</v>
       </c>
-      <c r="C16" t="s" s="2">
+      <c r="C16" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D16" t="s" s="1">
+      <c r="D16" s="1" t="s">
         <v>58</v>
       </c>
       <c r="E16">
-        <v>55.0</v>
+        <v>55</v>
       </c>
       <c r="F16">
-        <v>40.0</v>
+        <v>40</v>
       </c>
       <c r="G16">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="H16">
         <v>6.9</v>
       </c>
       <c r="I16">
-        <v>760.0</v>
+        <v>760</v>
       </c>
       <c r="J16">
-        <v>548.0</v>
+        <v>548</v>
       </c>
       <c r="K16">
-        <v>1308.0</v>
+        <v>1308</v>
       </c>
       <c r="L16">
-        <v>760.0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" dyDescent="0.2">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A17">
         <v>2</v>
       </c>
       <c r="B17" s="8">
         <v>9</v>
       </c>
-      <c r="C17" t="s" s="2">
+      <c r="C17" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D17" t="s" s="1">
+      <c r="D17" s="1" t="s">
         <v>59</v>
       </c>
       <c r="E17">
-        <v>38.0</v>
+        <v>38</v>
       </c>
       <c r="F17">
-        <v>26.0</v>
+        <v>26</v>
       </c>
       <c r="G17">
         <v>5.2</v>
@@ -1549,150 +1548,150 @@
         <v>7.3</v>
       </c>
       <c r="I17">
-        <v>494.0</v>
+        <v>494</v>
       </c>
       <c r="J17">
-        <v>383.0</v>
+        <v>383</v>
       </c>
       <c r="K17">
-        <v>877.0</v>
+        <v>877</v>
       </c>
       <c r="L17">
-        <v>494.0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" dyDescent="0.2">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A18">
         <v>2</v>
       </c>
       <c r="B18" s="8">
         <v>10</v>
       </c>
-      <c r="C18" t="s" s="2">
+      <c r="C18" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D18" t="s" s="1">
+      <c r="D18" s="1" t="s">
         <v>60</v>
       </c>
       <c r="E18">
-        <v>205.0</v>
+        <v>205</v>
       </c>
       <c r="F18">
-        <v>196.0</v>
+        <v>196</v>
       </c>
       <c r="G18">
-        <v>39.2</v>
+        <v>39.200000000000003</v>
       </c>
       <c r="H18">
         <v>5.2</v>
       </c>
       <c r="I18">
-        <v>3724.0</v>
+        <v>3724</v>
       </c>
       <c r="J18">
-        <v>1934.0</v>
+        <v>1934</v>
       </c>
       <c r="K18">
-        <v>5658.0</v>
+        <v>5658</v>
       </c>
       <c r="L18">
-        <v>3724.0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" dyDescent="0.2">
+        <v>3724</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A19">
         <v>3</v>
       </c>
       <c r="B19" s="8">
         <v>4</v>
       </c>
-      <c r="C19" t="s" s="2">
+      <c r="C19" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="D19" t="s" s="1">
+      <c r="D19" s="1" t="s">
         <v>54</v>
       </c>
       <c r="E19">
-        <v>215.0</v>
+        <v>215</v>
       </c>
       <c r="F19">
-        <v>77.0</v>
+        <v>77</v>
       </c>
       <c r="G19">
         <v>15.4</v>
       </c>
       <c r="H19">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="I19">
-        <v>1463.0</v>
+        <v>1463</v>
       </c>
       <c r="J19">
-        <v>2329.0</v>
+        <v>2329</v>
       </c>
       <c r="K19">
-        <v>3792.0</v>
+        <v>3792</v>
       </c>
       <c r="L19">
-        <v>2329.0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" dyDescent="0.2">
+        <v>2329</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A20">
         <v>3</v>
       </c>
       <c r="B20" s="8">
         <v>5</v>
       </c>
-      <c r="C20" t="s" s="2">
+      <c r="C20" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="D20" t="s" s="1">
+      <c r="D20" s="1" t="s">
         <v>55</v>
       </c>
       <c r="E20">
-        <v>113.0</v>
+        <v>113</v>
       </c>
       <c r="F20">
-        <v>63.0</v>
+        <v>63</v>
       </c>
       <c r="G20">
         <v>12.6</v>
       </c>
       <c r="H20">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="I20">
-        <v>1197.0</v>
+        <v>1197</v>
       </c>
       <c r="J20">
-        <v>1171.0</v>
+        <v>1171</v>
       </c>
       <c r="K20">
-        <v>2368.0</v>
+        <v>2368</v>
       </c>
       <c r="L20">
-        <v>1197.0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" dyDescent="0.2">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A21">
         <v>3</v>
       </c>
       <c r="B21" s="8">
         <v>6</v>
       </c>
-      <c r="C21" t="s" s="2">
+      <c r="C21" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="D21" t="s" s="1">
+      <c r="D21" s="1" t="s">
         <v>56</v>
       </c>
       <c r="E21">
-        <v>192.0</v>
+        <v>192</v>
       </c>
       <c r="F21">
-        <v>126.0</v>
+        <v>126</v>
       </c>
       <c r="G21">
         <v>25.2</v>
@@ -1701,36 +1700,36 @@
         <v>7.6</v>
       </c>
       <c r="I21">
-        <v>2394.0</v>
+        <v>2394</v>
       </c>
       <c r="J21">
-        <v>1946.0</v>
+        <v>1946</v>
       </c>
       <c r="K21">
-        <v>4340.0</v>
+        <v>4340</v>
       </c>
       <c r="L21">
-        <v>2394.0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" dyDescent="0.2">
+        <v>2394</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A22">
         <v>3</v>
       </c>
       <c r="B22" s="8">
         <v>7</v>
       </c>
-      <c r="C22" t="s" s="2">
+      <c r="C22" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="D22" t="s" s="11">
+      <c r="D22" s="11" t="s">
         <v>57</v>
       </c>
       <c r="E22">
-        <v>250.0</v>
+        <v>250</v>
       </c>
       <c r="F22">
-        <v>167.0</v>
+        <v>167</v>
       </c>
       <c r="G22">
         <v>33.4</v>
@@ -1739,112 +1738,112 @@
         <v>7.5</v>
       </c>
       <c r="I22">
-        <v>3173.0</v>
+        <v>3173</v>
       </c>
       <c r="J22">
-        <v>2527.0</v>
+        <v>2527</v>
       </c>
       <c r="K22">
-        <v>5700.0</v>
+        <v>5700</v>
       </c>
       <c r="L22">
-        <v>3173.0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" dyDescent="0.2">
+        <v>3173</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A23">
         <v>3</v>
       </c>
       <c r="B23" s="8">
         <v>8</v>
       </c>
-      <c r="C23" t="s" s="2">
+      <c r="C23" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="D23" t="s" s="1">
+      <c r="D23" s="1" t="s">
         <v>58</v>
       </c>
       <c r="E23">
-        <v>130.0</v>
+        <v>130</v>
       </c>
       <c r="F23">
-        <v>97.0</v>
+        <v>97</v>
       </c>
       <c r="G23">
-        <v>19.4</v>
+        <v>19.399999999999999</v>
       </c>
       <c r="H23">
         <v>6.7</v>
       </c>
       <c r="I23">
-        <v>1843.0</v>
+        <v>1843</v>
       </c>
       <c r="J23">
-        <v>1290.0</v>
+        <v>1290</v>
       </c>
       <c r="K23">
-        <v>3133.0</v>
+        <v>3133</v>
       </c>
       <c r="L23">
-        <v>1843.0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" dyDescent="0.2">
+        <v>1843</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A24">
         <v>3</v>
       </c>
       <c r="B24" s="8">
         <v>9</v>
       </c>
-      <c r="C24" t="s" s="2">
+      <c r="C24" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="D24" t="s" s="1">
+      <c r="D24" s="1" t="s">
         <v>59</v>
       </c>
       <c r="E24">
-        <v>142.0</v>
+        <v>142</v>
       </c>
       <c r="F24">
-        <v>105.0</v>
+        <v>105</v>
       </c>
       <c r="G24">
-        <v>21.0</v>
+        <v>21</v>
       </c>
       <c r="H24">
         <v>6.8</v>
       </c>
       <c r="I24">
-        <v>1995.0</v>
+        <v>1995</v>
       </c>
       <c r="J24">
-        <v>1412.0</v>
+        <v>1412</v>
       </c>
       <c r="K24">
-        <v>3407.0</v>
+        <v>3407</v>
       </c>
       <c r="L24">
-        <v>1995.0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" dyDescent="0.2">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A25">
         <v>3</v>
       </c>
       <c r="B25" s="8">
         <v>10</v>
       </c>
-      <c r="C25" t="s" s="2">
+      <c r="C25" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="D25" t="s" s="1">
+      <c r="D25" s="1" t="s">
         <v>60</v>
       </c>
       <c r="E25">
-        <v>89.0</v>
+        <v>89</v>
       </c>
       <c r="F25">
-        <v>68.0</v>
+        <v>68</v>
       </c>
       <c r="G25">
         <v>13.6</v>
@@ -1853,188 +1852,188 @@
         <v>6.5</v>
       </c>
       <c r="I25">
-        <v>1292.0</v>
+        <v>1292</v>
       </c>
       <c r="J25">
-        <v>880.0</v>
+        <v>880</v>
       </c>
       <c r="K25">
-        <v>2172.0</v>
+        <v>2172</v>
       </c>
       <c r="L25">
-        <v>1292.0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" dyDescent="0.2">
+        <v>1292</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A26">
         <v>4</v>
       </c>
       <c r="B26" s="8">
         <v>5</v>
       </c>
-      <c r="C26" t="s" s="1">
+      <c r="C26" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D26" t="s" s="1">
+      <c r="D26" s="1" t="s">
         <v>55</v>
       </c>
       <c r="E26">
-        <v>130.0</v>
+        <v>130</v>
       </c>
       <c r="F26">
-        <v>93.0</v>
+        <v>93</v>
       </c>
       <c r="G26">
-        <v>18.6</v>
+        <v>18.600000000000001</v>
       </c>
       <c r="H26">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="I26">
-        <v>1767.0</v>
+        <v>1767</v>
       </c>
       <c r="J26">
-        <v>1300.0</v>
+        <v>1300</v>
       </c>
       <c r="K26">
-        <v>3067.0</v>
+        <v>3067</v>
       </c>
       <c r="L26">
-        <v>1767.0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" dyDescent="0.2">
+        <v>1767</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A27">
         <v>4</v>
       </c>
       <c r="B27" s="8">
         <v>6</v>
       </c>
-      <c r="C27" t="s" s="1">
+      <c r="C27" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D27" t="s" s="1">
+      <c r="D27" s="1" t="s">
         <v>56</v>
       </c>
       <c r="E27">
-        <v>149.0</v>
+        <v>149</v>
       </c>
       <c r="F27">
-        <v>161.0</v>
+        <v>161</v>
       </c>
       <c r="G27">
-        <v>32.2</v>
+        <v>32.200000000000003</v>
       </c>
       <c r="H27">
-        <v>4.6</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="I27">
-        <v>3059.0</v>
+        <v>3059</v>
       </c>
       <c r="J27">
-        <v>1363.0</v>
+        <v>1363</v>
       </c>
       <c r="K27">
-        <v>4422.0</v>
+        <v>4422</v>
       </c>
       <c r="L27">
-        <v>3059.0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" dyDescent="0.2">
+        <v>3059</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A28">
         <v>4</v>
       </c>
       <c r="B28" s="8">
         <v>7</v>
       </c>
-      <c r="C28" t="s" s="1">
+      <c r="C28" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D28" t="s" s="11">
+      <c r="D28" s="11" t="s">
         <v>57</v>
       </c>
       <c r="E28">
-        <v>93.0</v>
+        <v>93</v>
       </c>
       <c r="F28">
-        <v>90.0</v>
+        <v>90</v>
       </c>
       <c r="G28">
-        <v>18.0</v>
+        <v>18</v>
       </c>
       <c r="H28">
         <v>5.2</v>
       </c>
       <c r="I28">
-        <v>1710.0</v>
+        <v>1710</v>
       </c>
       <c r="J28">
-        <v>875.0</v>
+        <v>875</v>
       </c>
       <c r="K28">
-        <v>2585.0</v>
+        <v>2585</v>
       </c>
       <c r="L28">
-        <v>1710.0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" dyDescent="0.2">
+        <v>1710</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A29">
         <v>4</v>
       </c>
       <c r="B29" s="8">
         <v>8</v>
       </c>
-      <c r="C29" t="s" s="1">
+      <c r="C29" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D29" t="s" s="1">
+      <c r="D29" s="1" t="s">
         <v>58</v>
       </c>
       <c r="E29">
-        <v>97.0</v>
+        <v>97</v>
       </c>
       <c r="F29">
-        <v>97.0</v>
+        <v>97</v>
       </c>
       <c r="G29">
-        <v>19.4</v>
+        <v>19.399999999999999</v>
       </c>
       <c r="H29">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="I29">
-        <v>1843.0</v>
+        <v>1843</v>
       </c>
       <c r="J29">
-        <v>905.0</v>
+        <v>905</v>
       </c>
       <c r="K29">
-        <v>2748.0</v>
+        <v>2748</v>
       </c>
       <c r="L29">
-        <v>1843.0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16" dyDescent="0.2">
+        <v>1843</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A30">
         <v>4</v>
       </c>
       <c r="B30" s="8">
         <v>9</v>
       </c>
-      <c r="C30" t="s" s="1">
+      <c r="C30" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D30" t="s" s="1">
+      <c r="D30" s="1" t="s">
         <v>59</v>
       </c>
       <c r="E30">
-        <v>76.0</v>
+        <v>76</v>
       </c>
       <c r="F30">
-        <v>91.0</v>
+        <v>91</v>
       </c>
       <c r="G30">
         <v>18.2</v>
@@ -2043,226 +2042,226 @@
         <v>4.2</v>
       </c>
       <c r="I30">
-        <v>1729.0</v>
+        <v>1729</v>
       </c>
       <c r="J30">
-        <v>674.0</v>
+        <v>674</v>
       </c>
       <c r="K30">
-        <v>2403.0</v>
+        <v>2403</v>
       </c>
       <c r="L30">
-        <v>1729.0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16" dyDescent="0.2">
+        <v>1729</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A31">
         <v>4</v>
       </c>
       <c r="B31" s="8">
         <v>10</v>
       </c>
-      <c r="C31" t="s" s="1">
+      <c r="C31" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D31" t="s" s="1">
+      <c r="D31" s="1" t="s">
         <v>60</v>
       </c>
       <c r="E31">
-        <v>246.0</v>
+        <v>246</v>
       </c>
       <c r="F31">
-        <v>110.0</v>
+        <v>110</v>
       </c>
       <c r="G31">
-        <v>22.0</v>
+        <v>22</v>
       </c>
       <c r="H31">
         <v>11.2</v>
       </c>
       <c r="I31">
-        <v>2090.0</v>
+        <v>2090</v>
       </c>
       <c r="J31">
-        <v>2613.0</v>
+        <v>2613</v>
       </c>
       <c r="K31">
-        <v>4703.0</v>
+        <v>4703</v>
       </c>
       <c r="L31">
-        <v>2613.0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16" dyDescent="0.2">
+        <v>2613</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A32">
         <v>5</v>
       </c>
       <c r="B32" s="8">
         <v>6</v>
       </c>
-      <c r="C32" t="s" s="1">
+      <c r="C32" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D32" t="s" s="1">
+      <c r="D32" s="1" t="s">
         <v>56</v>
       </c>
       <c r="E32">
-        <v>110.0</v>
+        <v>110</v>
       </c>
       <c r="F32">
-        <v>70.0</v>
+        <v>70</v>
       </c>
       <c r="G32">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="H32">
         <v>7.9</v>
       </c>
       <c r="I32">
-        <v>1330.0</v>
+        <v>1330</v>
       </c>
       <c r="J32">
-        <v>1120.0</v>
+        <v>1120</v>
       </c>
       <c r="K32">
-        <v>2450.0</v>
+        <v>2450</v>
       </c>
       <c r="L32">
-        <v>1330.0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" dyDescent="0.2">
+        <v>1330</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A33" s="10">
         <v>5</v>
       </c>
       <c r="B33" s="8">
         <v>7</v>
       </c>
-      <c r="C33" t="s" s="1">
+      <c r="C33" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D33" t="s" s="11">
+      <c r="D33" s="11" t="s">
         <v>57</v>
       </c>
       <c r="E33">
-        <v>168.0</v>
+        <v>168</v>
       </c>
       <c r="F33">
-        <v>173.0</v>
+        <v>173</v>
       </c>
       <c r="G33">
         <v>34.6</v>
       </c>
       <c r="H33">
-        <v>4.9</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="I33">
-        <v>3287.0</v>
+        <v>3287</v>
       </c>
       <c r="J33">
-        <v>1556.0</v>
+        <v>1556</v>
       </c>
       <c r="K33">
-        <v>4843.0</v>
+        <v>4843</v>
       </c>
       <c r="L33">
-        <v>3287.0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" dyDescent="0.2">
+        <v>3287</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A34">
         <v>5</v>
       </c>
       <c r="B34" s="8">
         <v>8</v>
       </c>
-      <c r="C34" t="s" s="1">
+      <c r="C34" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D34" t="s" s="1">
+      <c r="D34" s="1" t="s">
         <v>58</v>
       </c>
       <c r="E34">
-        <v>48.0</v>
+        <v>48</v>
       </c>
       <c r="F34">
-        <v>40.0</v>
+        <v>40</v>
       </c>
       <c r="G34">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="H34">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="I34">
-        <v>760.0</v>
+        <v>760</v>
       </c>
       <c r="J34">
-        <v>467.0</v>
+        <v>467</v>
       </c>
       <c r="K34">
-        <v>1227.0</v>
+        <v>1227</v>
       </c>
       <c r="L34">
-        <v>760.0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" dyDescent="0.2">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A35">
         <v>5</v>
       </c>
       <c r="B35" s="8">
         <v>9</v>
       </c>
-      <c r="C35" t="s" s="1">
+      <c r="C35" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D35" t="s" s="1">
+      <c r="D35" s="1" t="s">
         <v>59</v>
       </c>
       <c r="E35">
-        <v>60.0</v>
+        <v>60</v>
       </c>
       <c r="F35">
-        <v>55.0</v>
+        <v>55</v>
       </c>
       <c r="G35">
-        <v>11.0</v>
+        <v>11</v>
       </c>
       <c r="H35">
         <v>5.5</v>
       </c>
       <c r="I35">
-        <v>1045.0</v>
+        <v>1045</v>
       </c>
       <c r="J35">
-        <v>572.0</v>
+        <v>572</v>
       </c>
       <c r="K35">
-        <v>1617.0</v>
+        <v>1617</v>
       </c>
       <c r="L35">
-        <v>1045.0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16" dyDescent="0.2">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A36">
         <v>5</v>
       </c>
       <c r="B36" s="8">
         <v>10</v>
       </c>
-      <c r="C36" t="s" s="1">
+      <c r="C36" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D36" t="s" s="1">
+      <c r="D36" s="1" t="s">
         <v>60</v>
       </c>
       <c r="E36">
-        <v>145.0</v>
+        <v>145</v>
       </c>
       <c r="F36">
-        <v>131.0</v>
+        <v>131</v>
       </c>
       <c r="G36">
         <v>26.2</v>
@@ -2271,74 +2270,74 @@
         <v>5.5</v>
       </c>
       <c r="I36">
-        <v>2489.0</v>
+        <v>2489</v>
       </c>
       <c r="J36">
-        <v>1386.0</v>
+        <v>1386</v>
       </c>
       <c r="K36">
-        <v>3875.0</v>
+        <v>3875</v>
       </c>
       <c r="L36">
-        <v>2489.0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16" dyDescent="0.2">
+        <v>2489</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A37">
         <v>6</v>
       </c>
       <c r="B37" s="8">
         <v>7</v>
       </c>
-      <c r="C37" t="s" s="1">
+      <c r="C37" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="D37" t="s" s="11">
+      <c r="D37" s="11" t="s">
         <v>57</v>
       </c>
       <c r="E37">
-        <v>185.0</v>
+        <v>185</v>
       </c>
       <c r="F37">
-        <v>232.0</v>
+        <v>232</v>
       </c>
       <c r="G37">
         <v>46.4</v>
       </c>
       <c r="H37">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="I37">
-        <v>4408.0</v>
+        <v>4408</v>
       </c>
       <c r="J37">
-        <v>1617.0</v>
+        <v>1617</v>
       </c>
       <c r="K37">
-        <v>6025.0</v>
+        <v>6025</v>
       </c>
       <c r="L37">
-        <v>4408.0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:16" dyDescent="0.2">
+        <v>4408</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A38">
         <v>6</v>
       </c>
       <c r="B38" s="8">
         <v>8</v>
       </c>
-      <c r="C38" t="s" s="1">
+      <c r="C38" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="D38" t="s" s="1">
+      <c r="D38" s="1" t="s">
         <v>58</v>
       </c>
       <c r="E38">
-        <v>77.0</v>
+        <v>77</v>
       </c>
       <c r="F38">
-        <v>72.0</v>
+        <v>72</v>
       </c>
       <c r="G38">
         <v>14.4</v>
@@ -2347,74 +2346,74 @@
         <v>5.3</v>
       </c>
       <c r="I38">
-        <v>1368.0</v>
+        <v>1368</v>
       </c>
       <c r="J38">
-        <v>730.0</v>
+        <v>730</v>
       </c>
       <c r="K38">
-        <v>2098.0</v>
+        <v>2098</v>
       </c>
       <c r="L38">
-        <v>1368.0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16" dyDescent="0.2">
+        <v>1368</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A39">
         <v>6</v>
       </c>
       <c r="B39" s="8">
         <v>9</v>
       </c>
-      <c r="C39" t="s" s="1">
+      <c r="C39" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="D39" t="s" s="1">
+      <c r="D39" s="1" t="s">
         <v>59</v>
       </c>
       <c r="E39">
-        <v>78.0</v>
+        <v>78</v>
       </c>
       <c r="F39">
-        <v>89.0</v>
+        <v>89</v>
       </c>
       <c r="G39">
         <v>17.8</v>
       </c>
       <c r="H39">
-        <v>4.4</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="I39">
-        <v>1691.0</v>
+        <v>1691</v>
       </c>
       <c r="J39">
-        <v>702.0</v>
+        <v>702</v>
       </c>
       <c r="K39">
-        <v>2393.0</v>
+        <v>2393</v>
       </c>
       <c r="L39">
-        <v>1691.0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:16" dyDescent="0.2">
+        <v>1691</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A40">
         <v>6</v>
       </c>
       <c r="B40" s="8">
         <v>10</v>
       </c>
-      <c r="C40" t="s" s="1">
+      <c r="C40" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="D40" t="s" s="1">
+      <c r="D40" s="1" t="s">
         <v>60</v>
       </c>
       <c r="E40">
-        <v>224.0</v>
+        <v>224</v>
       </c>
       <c r="F40">
-        <v>192.0</v>
+        <v>192</v>
       </c>
       <c r="G40">
         <v>38.4</v>
@@ -2423,74 +2422,74 @@
         <v>5.8</v>
       </c>
       <c r="I40">
-        <v>3648.0</v>
+        <v>3648</v>
       </c>
       <c r="J40">
-        <v>2165.0</v>
+        <v>2165</v>
       </c>
       <c r="K40">
-        <v>5813.0</v>
+        <v>5813</v>
       </c>
       <c r="L40">
-        <v>3648.0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:16" dyDescent="0.2">
+        <v>3648</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A41">
         <v>7</v>
       </c>
       <c r="B41" s="8">
         <v>8</v>
       </c>
-      <c r="C41" t="s" s="1">
+      <c r="C41" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="D41" t="s" s="1">
+      <c r="D41" s="1" t="s">
         <v>58</v>
       </c>
       <c r="E41">
-        <v>131.0</v>
+        <v>131</v>
       </c>
       <c r="F41">
-        <v>160.0</v>
+        <v>160</v>
       </c>
       <c r="G41">
-        <v>32.0</v>
+        <v>32</v>
       </c>
       <c r="H41">
-        <v>4.1</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="I41">
-        <v>3040.0</v>
+        <v>3040</v>
       </c>
       <c r="J41">
-        <v>1155.0</v>
+        <v>1155</v>
       </c>
       <c r="K41">
-        <v>4195.0</v>
+        <v>4195</v>
       </c>
       <c r="L41">
-        <v>3040.0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:16" dyDescent="0.2">
+        <v>3040</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A42">
         <v>7</v>
       </c>
       <c r="B42" s="8">
         <v>9</v>
       </c>
-      <c r="C42" t="s" s="1">
+      <c r="C42" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="D42" t="s" s="1">
+      <c r="D42" s="1" t="s">
         <v>59</v>
       </c>
       <c r="E42">
-        <v>110.0</v>
+        <v>110</v>
       </c>
       <c r="F42">
-        <v>146.0</v>
+        <v>146</v>
       </c>
       <c r="G42">
         <v>29.2</v>
@@ -2499,36 +2498,36 @@
         <v>3.8</v>
       </c>
       <c r="I42">
-        <v>2774.0</v>
+        <v>2774</v>
       </c>
       <c r="J42">
-        <v>943.0</v>
+        <v>943</v>
       </c>
       <c r="K42">
-        <v>3717.0</v>
+        <v>3717</v>
       </c>
       <c r="L42">
-        <v>2774.0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:16" dyDescent="0.2">
+        <v>2774</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A43">
         <v>7</v>
       </c>
       <c r="B43" s="8">
         <v>10</v>
       </c>
-      <c r="C43" t="s" s="1">
+      <c r="C43" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="D43" t="s" s="1">
+      <c r="D43" s="1" t="s">
         <v>60</v>
       </c>
       <c r="E43">
-        <v>280.0</v>
+        <v>280</v>
       </c>
       <c r="F43">
-        <v>187.0</v>
+        <v>187</v>
       </c>
       <c r="G43">
         <v>37.4</v>
@@ -2537,36 +2536,36 @@
         <v>7.5</v>
       </c>
       <c r="I43">
-        <v>3553.0</v>
+        <v>3553</v>
       </c>
       <c r="J43">
-        <v>2830.0</v>
+        <v>2830</v>
       </c>
       <c r="K43">
-        <v>6383.0</v>
+        <v>6383</v>
       </c>
       <c r="L43">
-        <v>3553.0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:16" dyDescent="0.2">
+        <v>3553</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A44">
         <v>8</v>
       </c>
       <c r="B44" s="8">
         <v>9</v>
       </c>
-      <c r="C44" t="s" s="1">
+      <c r="C44" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D44" t="s" s="1">
+      <c r="D44" s="1" t="s">
         <v>59</v>
       </c>
       <c r="E44">
-        <v>26.0</v>
+        <v>26</v>
       </c>
       <c r="F44">
-        <v>19.0</v>
+        <v>19</v>
       </c>
       <c r="G44">
         <v>3.8</v>
@@ -2575,95 +2574,95 @@
         <v>6.8</v>
       </c>
       <c r="I44">
-        <v>361.0</v>
+        <v>361</v>
       </c>
       <c r="J44">
-        <v>259.0</v>
+        <v>259</v>
       </c>
       <c r="K44">
-        <v>620.0</v>
+        <v>620</v>
       </c>
       <c r="L44">
-        <v>361.0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:16" dyDescent="0.2">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A45">
         <v>8</v>
       </c>
       <c r="B45" s="8">
         <v>10</v>
       </c>
-      <c r="C45" t="s" s="1">
+      <c r="C45" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D45" t="s" s="1">
+      <c r="D45" s="1" t="s">
         <v>60</v>
       </c>
       <c r="E45">
-        <v>163.0</v>
+        <v>163</v>
       </c>
       <c r="F45">
-        <v>164.0</v>
+        <v>164</v>
       </c>
       <c r="G45">
-        <v>32.8</v>
+        <v>32.799999999999997</v>
       </c>
       <c r="H45">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="I45">
-        <v>3116.0</v>
+        <v>3116</v>
       </c>
       <c r="J45">
-        <v>1519.0</v>
+        <v>1519</v>
       </c>
       <c r="K45">
-        <v>4635.0</v>
+        <v>4635</v>
       </c>
       <c r="L45">
-        <v>3116.0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:16" dyDescent="0.2">
+        <v>3116</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A46">
         <v>9</v>
       </c>
       <c r="B46" s="8">
         <v>10</v>
       </c>
-      <c r="C46" t="s" s="1">
+      <c r="C46" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D46" t="s" s="1">
+      <c r="D46" s="1" t="s">
         <v>60</v>
       </c>
       <c r="E46">
-        <v>175.0</v>
+        <v>175</v>
       </c>
       <c r="F46">
-        <v>170.0</v>
+        <v>170</v>
       </c>
       <c r="G46">
-        <v>34.0</v>
+        <v>34</v>
       </c>
       <c r="H46">
-        <v>5.1</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="I46">
-        <v>3230.0</v>
+        <v>3230</v>
       </c>
       <c r="J46">
-        <v>1645.0</v>
+        <v>1645</v>
       </c>
       <c r="K46">
-        <v>4875.0</v>
+        <v>4875</v>
       </c>
       <c r="L46">
-        <v>3230.0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:16" dyDescent="0.2">
+        <v>3230</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A47">
         <v>1</v>
       </c>
@@ -2697,7 +2696,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:16" dyDescent="0.2">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A48">
         <v>2</v>
       </c>
@@ -2731,7 +2730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:16" dyDescent="0.2">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A49">
         <v>3</v>
       </c>
@@ -2765,7 +2764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:16" dyDescent="0.2">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A50">
         <v>4</v>
       </c>
@@ -2799,7 +2798,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:16" dyDescent="0.2">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A51">
         <v>5</v>
       </c>
@@ -2833,7 +2832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:16" dyDescent="0.2">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A52">
         <v>6</v>
       </c>
@@ -2865,7 +2864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:16" dyDescent="0.2">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A53">
         <v>7</v>
       </c>
@@ -2897,7 +2896,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:16" dyDescent="0.2">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A54">
         <v>8</v>
       </c>
@@ -2929,7 +2928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:16" dyDescent="0.2">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A55">
         <v>9</v>
       </c>
@@ -2961,7 +2960,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:16" dyDescent="0.2">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A56">
         <v>10</v>
       </c>
@@ -2993,13 +2992,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:16" dyDescent="0.2">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.4">
       <c r="G57" s="2"/>
     </row>
-    <row r="58" spans="1:16" dyDescent="0.2">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.4">
       <c r="G58" s="1"/>
     </row>
-    <row r="59" spans="1:16" dyDescent="0.2">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.4">
       <c r="G59" s="1"/>
     </row>
   </sheetData>

--- a/inputData/Parameters.xlsx
+++ b/inputData/Parameters.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kapta\Documents\DTU\Speciale\GitHubFiles\inputData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CBE765F-9084-4140-9ADF-71B92BC0CEA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4CDFB81-59AA-445D-89CD-4FF184343887}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
   </bookViews>
   <sheets>
     <sheet name="Parameters" sheetId="9" r:id="rId1"/>
@@ -832,7 +832,7 @@
         <v>6</v>
       </c>
       <c r="B17" s="4">
-        <v>780</v>
+        <v>400</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>14</v>

--- a/inputData/Parameters.xlsx
+++ b/inputData/Parameters.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sillewiberg/Desktop/Skole/Speciale/Master-Thesis-eVTOL-1/inputData/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC525445-B921-7444-8BE9-F0D2537C0186}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F278866-8B49-0647-A835-544B4947017F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16320" activeTab="1" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16320" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
   </bookViews>
   <sheets>
     <sheet name="Parameters" sheetId="9" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="61">
   <si>
     <t>cap_u</t>
   </si>
@@ -653,13 +653,13 @@
     <col min="2" max="2" width="10.83203125" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:4" dyDescent="0.2">
-      <c r="A2" t="s" s="1">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B2" s="4">
@@ -669,7 +669,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" dyDescent="0.2">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -680,7 +680,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:4" dyDescent="0.2">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>46</v>
       </c>
@@ -691,7 +691,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="5" spans="1:4" dyDescent="0.2">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -702,7 +702,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="6" spans="1:4" dyDescent="0.2">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -713,7 +713,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:4" dyDescent="0.2">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -724,7 +724,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:4" dyDescent="0.2">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -736,7 +736,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:4" dyDescent="0.2">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>0</v>
       </c>
@@ -747,7 +747,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:4" dyDescent="0.2">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>1</v>
       </c>
@@ -758,7 +758,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:4" dyDescent="0.2">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>45</v>
       </c>
@@ -769,7 +769,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="12" spans="1:4" dyDescent="0.2">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>2</v>
       </c>
@@ -780,18 +780,18 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="13" spans="1:4" dyDescent="0.2">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>42</v>
       </c>
       <c r="B13" s="4">
         <v>20</v>
       </c>
-      <c r="D13" t="s" s="3">
+      <c r="D13" s="3" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="14" spans="1:4" dyDescent="0.2">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -799,11 +799,11 @@
         <f>2.11*B20</f>
         <v>2.11</v>
       </c>
-      <c r="D14" t="s" s="3">
+      <c r="D14" s="3" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="15" spans="1:4" dyDescent="0.2">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>4</v>
       </c>
@@ -811,11 +811,11 @@
         <f>30/B20</f>
         <v>30</v>
       </c>
-      <c r="D15" t="s" s="3">
+      <c r="D15" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:4" dyDescent="0.2">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>5</v>
       </c>
@@ -823,30 +823,29 @@
         <f>20/B20</f>
         <v>20</v>
       </c>
-      <c r="D16" t="s" s="3">
+      <c r="D16" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:4" dyDescent="0.2">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>6</v>
       </c>
       <c r="B17" s="4">
-        <f>120/B20</f>
-        <v>120</v>
-      </c>
-      <c r="D17" t="s" s="3">
+        <v>780</v>
+      </c>
+      <c r="D17" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:4" dyDescent="0.2">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>41</v>
       </c>
       <c r="B20" s="4">
         <v>1</v>
       </c>
-      <c r="D20" t="s" s="3">
+      <c r="D20" s="3" t="s">
         <v>48</v>
       </c>
     </row>
@@ -869,44 +868,44 @@
     <col min="8" max="8" width="18.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" dyDescent="0.2">
-      <c r="A1" t="s" s="9">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A1" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="B1" t="s" s="5">
+      <c r="B1" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C1" t="s" s="5">
+      <c r="C1" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="D1" t="s" s="5">
+      <c r="D1" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="E1" t="s" s="5">
+      <c r="E1" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="F1" t="s" s="5">
+      <c r="F1" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="G1" t="s" s="5">
+      <c r="G1" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="H1" t="s" s="5">
+      <c r="H1" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="I1" t="s" s="5">
+      <c r="I1" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="J1" t="s" s="5">
+      <c r="J1" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="K1" t="s" s="5">
+      <c r="K1" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="L1" t="s" s="5">
+      <c r="L1" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="N1" t="s" s="6">
+      <c r="N1" s="6" t="s">
         <v>19</v>
       </c>
       <c r="O1" s="7">
@@ -914,24 +913,24 @@
       </c>
       <c r="P1" s="6"/>
     </row>
-    <row r="2" spans="1:16" dyDescent="0.2">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" s="8">
         <v>2</v>
       </c>
-      <c r="C2" t="s" s="1">
+      <c r="C2" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D2" t="s" s="2">
+      <c r="D2" s="2" t="s">
         <v>52</v>
       </c>
       <c r="E2">
-        <v>185.0</v>
+        <v>185</v>
       </c>
       <c r="F2">
-        <v>219.0</v>
+        <v>219</v>
       </c>
       <c r="G2">
         <v>43.8</v>
@@ -940,16 +939,16 @@
         <v>4.2</v>
       </c>
       <c r="I2">
-        <v>4161.0</v>
+        <v>4161</v>
       </c>
       <c r="J2">
-        <v>1647.0</v>
+        <v>1647</v>
       </c>
       <c r="K2">
-        <v>5808.0</v>
+        <v>5808</v>
       </c>
       <c r="L2">
-        <v>4161.0</v>
+        <v>4161</v>
       </c>
       <c r="N2" t="s">
         <v>29</v>
@@ -961,42 +960,42 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:16" dyDescent="0.2">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" s="8">
         <v>3</v>
       </c>
-      <c r="C3" t="s" s="1">
+      <c r="C3" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D3" t="s" s="2">
+      <c r="D3" s="2" t="s">
         <v>53</v>
       </c>
       <c r="E3">
-        <v>82.0</v>
+        <v>82</v>
       </c>
       <c r="F3">
-        <v>88.0</v>
+        <v>88</v>
       </c>
       <c r="G3">
-        <v>17.6</v>
+        <v>17.600000000000001</v>
       </c>
       <c r="H3">
         <v>4.7</v>
       </c>
       <c r="I3">
-        <v>1672.0</v>
+        <v>1672</v>
       </c>
       <c r="J3">
-        <v>751.0</v>
+        <v>751</v>
       </c>
       <c r="K3">
-        <v>2423.0</v>
+        <v>2423</v>
       </c>
       <c r="L3">
-        <v>1672.0</v>
+        <v>1672</v>
       </c>
       <c r="N3" t="s">
         <v>31</v>
@@ -1009,24 +1008,24 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:16" dyDescent="0.2">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>1</v>
       </c>
       <c r="B4" s="8">
         <v>4</v>
       </c>
-      <c r="C4" t="s" s="1">
+      <c r="C4" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D4" t="s" s="1">
+      <c r="D4" s="1" t="s">
         <v>54</v>
       </c>
       <c r="E4">
-        <v>228.0</v>
+        <v>228</v>
       </c>
       <c r="F4">
-        <v>147.0</v>
+        <v>147</v>
       </c>
       <c r="G4">
         <v>29.4</v>
@@ -1035,16 +1034,16 @@
         <v>7.8</v>
       </c>
       <c r="I4">
-        <v>2793.0</v>
+        <v>2793</v>
       </c>
       <c r="J4">
-        <v>2317.0</v>
+        <v>2317</v>
       </c>
       <c r="K4">
-        <v>5110.0</v>
+        <v>5110</v>
       </c>
       <c r="L4">
-        <v>2793.0</v>
+        <v>2793</v>
       </c>
       <c r="N4" t="s">
         <v>33</v>
@@ -1053,24 +1052,24 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="5" spans="1:16" dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>1</v>
       </c>
       <c r="B5" s="8">
         <v>5</v>
       </c>
-      <c r="C5" t="s" s="1">
+      <c r="C5" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D5" t="s" s="1">
+      <c r="D5" s="1" t="s">
         <v>55</v>
       </c>
       <c r="E5">
-        <v>126.0</v>
+        <v>126</v>
       </c>
       <c r="F5">
-        <v>147.0</v>
+        <v>147</v>
       </c>
       <c r="G5">
         <v>29.4</v>
@@ -1079,16 +1078,16 @@
         <v>4.3</v>
       </c>
       <c r="I5">
-        <v>2793.0</v>
+        <v>2793</v>
       </c>
       <c r="J5">
-        <v>1127.0</v>
+        <v>1127</v>
       </c>
       <c r="K5">
-        <v>3920.0</v>
+        <v>3920</v>
       </c>
       <c r="L5">
-        <v>2793.0</v>
+        <v>2793</v>
       </c>
       <c r="N5" t="s">
         <v>34</v>
@@ -1100,24 +1099,24 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:16" dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>1</v>
       </c>
       <c r="B6" s="8">
         <v>6</v>
       </c>
-      <c r="C6" t="s" s="1">
+      <c r="C6" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D6" t="s" s="1">
+      <c r="D6" s="1" t="s">
         <v>56</v>
       </c>
       <c r="E6">
-        <v>205.0</v>
+        <v>205</v>
       </c>
       <c r="F6">
-        <v>197.0</v>
+        <v>197</v>
       </c>
       <c r="G6">
         <v>39.4</v>
@@ -1126,37 +1125,37 @@
         <v>5.2</v>
       </c>
       <c r="I6">
-        <v>3743.0</v>
+        <v>3743</v>
       </c>
       <c r="J6">
-        <v>1932.0</v>
+        <v>1932</v>
       </c>
       <c r="K6">
-        <v>5675.0</v>
+        <v>5675</v>
       </c>
       <c r="L6">
-        <v>3743.0</v>
+        <v>3743</v>
       </c>
       <c r="O6" s="4"/>
     </row>
-    <row r="7" spans="1:16" dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>1</v>
       </c>
       <c r="B7" s="8">
         <v>7</v>
       </c>
-      <c r="C7" t="s" s="1">
+      <c r="C7" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D7" t="s" s="1">
+      <c r="D7" s="1" t="s">
         <v>57</v>
       </c>
       <c r="E7">
-        <v>263.0</v>
+        <v>263</v>
       </c>
       <c r="F7">
-        <v>227.0</v>
+        <v>227</v>
       </c>
       <c r="G7">
         <v>45.4</v>
@@ -1165,154 +1164,154 @@
         <v>5.8</v>
       </c>
       <c r="I7">
-        <v>4313.0</v>
+        <v>4313</v>
       </c>
       <c r="J7">
-        <v>2539.0</v>
+        <v>2539</v>
       </c>
       <c r="K7">
-        <v>6852.0</v>
+        <v>6852</v>
       </c>
       <c r="L7">
-        <v>4313.0</v>
+        <v>4313</v>
       </c>
       <c r="O7" s="4"/>
     </row>
-    <row r="8" spans="1:16" dyDescent="0.2">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>1</v>
       </c>
       <c r="B8" s="8">
         <v>8</v>
       </c>
-      <c r="C8" t="s" s="1">
+      <c r="C8" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D8" t="s" s="1">
+      <c r="D8" s="1" t="s">
         <v>58</v>
       </c>
       <c r="E8">
-        <v>143.0</v>
+        <v>143</v>
       </c>
       <c r="F8">
-        <v>184.0</v>
+        <v>184</v>
       </c>
       <c r="G8">
-        <v>36.8</v>
+        <v>36.799999999999997</v>
       </c>
       <c r="H8">
         <v>3.9</v>
       </c>
       <c r="I8">
-        <v>3496.0</v>
+        <v>3496</v>
       </c>
       <c r="J8">
-        <v>1239.0</v>
+        <v>1239</v>
       </c>
       <c r="K8">
-        <v>4735.0</v>
+        <v>4735</v>
       </c>
       <c r="L8">
-        <v>3496.0</v>
+        <v>3496</v>
       </c>
       <c r="O8" s="4"/>
     </row>
-    <row r="9" spans="1:16" dyDescent="0.2">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>1</v>
       </c>
       <c r="B9" s="8">
         <v>9</v>
       </c>
-      <c r="C9" t="s" s="1">
+      <c r="C9" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D9" t="s" s="1">
+      <c r="D9" s="1" t="s">
         <v>59</v>
       </c>
       <c r="E9">
-        <v>155.0</v>
+        <v>155</v>
       </c>
       <c r="F9">
-        <v>193.0</v>
+        <v>193</v>
       </c>
       <c r="G9">
         <v>38.6</v>
       </c>
       <c r="H9">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="I9">
-        <v>3667.0</v>
+        <v>3667</v>
       </c>
       <c r="J9">
-        <v>1358.0</v>
+        <v>1358</v>
       </c>
       <c r="K9">
-        <v>5025.0</v>
+        <v>5025</v>
       </c>
       <c r="L9">
-        <v>3667.0</v>
+        <v>3667</v>
       </c>
       <c r="O9" s="4"/>
     </row>
-    <row r="10" spans="1:16" dyDescent="0.2">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>1</v>
       </c>
       <c r="B10" s="8">
         <v>10</v>
       </c>
-      <c r="C10" t="s" s="1">
+      <c r="C10" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D10" t="s" s="1">
+      <c r="D10" s="1" t="s">
         <v>60</v>
       </c>
       <c r="E10">
-        <v>42.0</v>
+        <v>42</v>
       </c>
       <c r="F10">
-        <v>41.0</v>
+        <v>41</v>
       </c>
       <c r="G10">
-        <v>8.2</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="H10">
-        <v>5.1</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="I10">
-        <v>779.0</v>
+        <v>779</v>
       </c>
       <c r="J10">
-        <v>394.0</v>
+        <v>394</v>
       </c>
       <c r="K10">
-        <v>1173.0</v>
+        <v>1173</v>
       </c>
       <c r="L10">
-        <v>779.0</v>
+        <v>779</v>
       </c>
       <c r="O10" s="4"/>
     </row>
-    <row r="11" spans="1:16" dyDescent="0.2">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>2</v>
       </c>
       <c r="B11" s="8">
         <v>3</v>
       </c>
-      <c r="C11" t="s" s="2">
+      <c r="C11" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D11" t="s" s="2">
+      <c r="D11" s="2" t="s">
         <v>53</v>
       </c>
       <c r="E11">
-        <v>173.0</v>
+        <v>173</v>
       </c>
       <c r="F11">
-        <v>131.0</v>
+        <v>131</v>
       </c>
       <c r="G11">
         <v>26.2</v>
@@ -1321,226 +1320,226 @@
         <v>6.6</v>
       </c>
       <c r="I11">
-        <v>2489.0</v>
+        <v>2489</v>
       </c>
       <c r="J11">
-        <v>1713.0</v>
+        <v>1713</v>
       </c>
       <c r="K11">
-        <v>4202.0</v>
+        <v>4202</v>
       </c>
       <c r="L11">
-        <v>2489.0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" dyDescent="0.2">
+        <v>2489</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>2</v>
       </c>
       <c r="B12" s="8">
         <v>4</v>
       </c>
-      <c r="C12" t="s" s="2">
+      <c r="C12" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D12" t="s" s="1">
+      <c r="D12" s="1" t="s">
         <v>54</v>
       </c>
       <c r="E12">
-        <v>103.0</v>
+        <v>103</v>
       </c>
       <c r="F12">
-        <v>110.0</v>
+        <v>110</v>
       </c>
       <c r="G12">
-        <v>22.0</v>
+        <v>22</v>
       </c>
       <c r="H12">
         <v>4.7</v>
       </c>
       <c r="I12">
-        <v>2090.0</v>
+        <v>2090</v>
       </c>
       <c r="J12">
-        <v>945.0</v>
+        <v>945</v>
       </c>
       <c r="K12">
-        <v>3035.0</v>
+        <v>3035</v>
       </c>
       <c r="L12">
-        <v>2090.0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" dyDescent="0.2">
+        <v>2090</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>2</v>
       </c>
       <c r="B13" s="8">
         <v>5</v>
       </c>
-      <c r="C13" t="s" s="2">
+      <c r="C13" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D13" t="s" s="1">
+      <c r="D13" s="1" t="s">
         <v>55</v>
       </c>
       <c r="E13">
-        <v>89.0</v>
+        <v>89</v>
       </c>
       <c r="F13">
-        <v>80.0</v>
+        <v>80</v>
       </c>
       <c r="G13">
-        <v>16.0</v>
+        <v>16</v>
       </c>
       <c r="H13">
         <v>5.6</v>
       </c>
       <c r="I13">
-        <v>1520.0</v>
+        <v>1520</v>
       </c>
       <c r="J13">
-        <v>852.0</v>
+        <v>852</v>
       </c>
       <c r="K13">
-        <v>2372.0</v>
+        <v>2372</v>
       </c>
       <c r="L13">
-        <v>1520.0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" dyDescent="0.2">
+        <v>1520</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>2</v>
       </c>
       <c r="B14" s="8">
         <v>6</v>
       </c>
-      <c r="C14" t="s" s="2">
+      <c r="C14" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D14" t="s" s="1">
+      <c r="D14" s="1" t="s">
         <v>56</v>
       </c>
       <c r="E14">
-        <v>100.0</v>
+        <v>100</v>
       </c>
       <c r="F14">
-        <v>98.0</v>
+        <v>98</v>
       </c>
       <c r="G14">
-        <v>19.6</v>
+        <v>19.600000000000001</v>
       </c>
       <c r="H14">
-        <v>5.1</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="I14">
-        <v>1862.0</v>
+        <v>1862</v>
       </c>
       <c r="J14">
-        <v>938.0</v>
+        <v>938</v>
       </c>
       <c r="K14">
-        <v>2800.0</v>
+        <v>2800</v>
       </c>
       <c r="L14">
-        <v>1862.0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" dyDescent="0.2">
+        <v>1862</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>2</v>
       </c>
       <c r="B15" s="8">
         <v>7</v>
       </c>
-      <c r="C15" t="s" s="2">
+      <c r="C15" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D15" t="s" s="11">
+      <c r="D15" s="11" t="s">
         <v>57</v>
       </c>
       <c r="E15">
-        <v>138.0</v>
+        <v>138</v>
       </c>
       <c r="F15">
-        <v>151.0</v>
+        <v>151</v>
       </c>
       <c r="G15">
         <v>30.2</v>
       </c>
       <c r="H15">
-        <v>4.6</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="I15">
-        <v>2869.0</v>
+        <v>2869</v>
       </c>
       <c r="J15">
-        <v>1258.0</v>
+        <v>1258</v>
       </c>
       <c r="K15">
-        <v>4127.0</v>
+        <v>4127</v>
       </c>
       <c r="L15">
-        <v>2869.0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" dyDescent="0.2">
+        <v>2869</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>2</v>
       </c>
       <c r="B16" s="8">
         <v>8</v>
       </c>
-      <c r="C16" t="s" s="2">
+      <c r="C16" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D16" t="s" s="1">
+      <c r="D16" s="1" t="s">
         <v>58</v>
       </c>
       <c r="E16">
-        <v>55.0</v>
+        <v>55</v>
       </c>
       <c r="F16">
-        <v>40.0</v>
+        <v>40</v>
       </c>
       <c r="G16">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="H16">
         <v>6.9</v>
       </c>
       <c r="I16">
-        <v>760.0</v>
+        <v>760</v>
       </c>
       <c r="J16">
-        <v>548.0</v>
+        <v>548</v>
       </c>
       <c r="K16">
-        <v>1308.0</v>
+        <v>1308</v>
       </c>
       <c r="L16">
-        <v>760.0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" dyDescent="0.2">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>2</v>
       </c>
       <c r="B17" s="8">
         <v>9</v>
       </c>
-      <c r="C17" t="s" s="2">
+      <c r="C17" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D17" t="s" s="1">
+      <c r="D17" s="1" t="s">
         <v>59</v>
       </c>
       <c r="E17">
-        <v>38.0</v>
+        <v>38</v>
       </c>
       <c r="F17">
-        <v>26.0</v>
+        <v>26</v>
       </c>
       <c r="G17">
         <v>5.2</v>
@@ -1549,150 +1548,150 @@
         <v>7.3</v>
       </c>
       <c r="I17">
-        <v>494.0</v>
+        <v>494</v>
       </c>
       <c r="J17">
-        <v>383.0</v>
+        <v>383</v>
       </c>
       <c r="K17">
-        <v>877.0</v>
+        <v>877</v>
       </c>
       <c r="L17">
-        <v>494.0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" dyDescent="0.2">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>2</v>
       </c>
       <c r="B18" s="8">
         <v>10</v>
       </c>
-      <c r="C18" t="s" s="2">
+      <c r="C18" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D18" t="s" s="1">
+      <c r="D18" s="1" t="s">
         <v>60</v>
       </c>
       <c r="E18">
-        <v>205.0</v>
+        <v>205</v>
       </c>
       <c r="F18">
-        <v>196.0</v>
+        <v>196</v>
       </c>
       <c r="G18">
-        <v>39.2</v>
+        <v>39.200000000000003</v>
       </c>
       <c r="H18">
         <v>5.2</v>
       </c>
       <c r="I18">
-        <v>3724.0</v>
+        <v>3724</v>
       </c>
       <c r="J18">
-        <v>1934.0</v>
+        <v>1934</v>
       </c>
       <c r="K18">
-        <v>5658.0</v>
+        <v>5658</v>
       </c>
       <c r="L18">
-        <v>3724.0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" dyDescent="0.2">
+        <v>3724</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>3</v>
       </c>
       <c r="B19" s="8">
         <v>4</v>
       </c>
-      <c r="C19" t="s" s="2">
+      <c r="C19" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="D19" t="s" s="1">
+      <c r="D19" s="1" t="s">
         <v>54</v>
       </c>
       <c r="E19">
-        <v>215.0</v>
+        <v>215</v>
       </c>
       <c r="F19">
-        <v>77.0</v>
+        <v>77</v>
       </c>
       <c r="G19">
         <v>15.4</v>
       </c>
       <c r="H19">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="I19">
-        <v>1463.0</v>
+        <v>1463</v>
       </c>
       <c r="J19">
-        <v>2329.0</v>
+        <v>2329</v>
       </c>
       <c r="K19">
-        <v>3792.0</v>
+        <v>3792</v>
       </c>
       <c r="L19">
-        <v>2329.0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" dyDescent="0.2">
+        <v>2329</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>3</v>
       </c>
       <c r="B20" s="8">
         <v>5</v>
       </c>
-      <c r="C20" t="s" s="2">
+      <c r="C20" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="D20" t="s" s="1">
+      <c r="D20" s="1" t="s">
         <v>55</v>
       </c>
       <c r="E20">
-        <v>113.0</v>
+        <v>113</v>
       </c>
       <c r="F20">
-        <v>63.0</v>
+        <v>63</v>
       </c>
       <c r="G20">
         <v>12.6</v>
       </c>
       <c r="H20">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="I20">
-        <v>1197.0</v>
+        <v>1197</v>
       </c>
       <c r="J20">
-        <v>1171.0</v>
+        <v>1171</v>
       </c>
       <c r="K20">
-        <v>2368.0</v>
+        <v>2368</v>
       </c>
       <c r="L20">
-        <v>1197.0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" dyDescent="0.2">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>3</v>
       </c>
       <c r="B21" s="8">
         <v>6</v>
       </c>
-      <c r="C21" t="s" s="2">
+      <c r="C21" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="D21" t="s" s="1">
+      <c r="D21" s="1" t="s">
         <v>56</v>
       </c>
       <c r="E21">
-        <v>192.0</v>
+        <v>192</v>
       </c>
       <c r="F21">
-        <v>126.0</v>
+        <v>126</v>
       </c>
       <c r="G21">
         <v>25.2</v>
@@ -1701,36 +1700,36 @@
         <v>7.6</v>
       </c>
       <c r="I21">
-        <v>2394.0</v>
+        <v>2394</v>
       </c>
       <c r="J21">
-        <v>1946.0</v>
+        <v>1946</v>
       </c>
       <c r="K21">
-        <v>4340.0</v>
+        <v>4340</v>
       </c>
       <c r="L21">
-        <v>2394.0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" dyDescent="0.2">
+        <v>2394</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>3</v>
       </c>
       <c r="B22" s="8">
         <v>7</v>
       </c>
-      <c r="C22" t="s" s="2">
+      <c r="C22" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="D22" t="s" s="11">
+      <c r="D22" s="11" t="s">
         <v>57</v>
       </c>
       <c r="E22">
-        <v>250.0</v>
+        <v>250</v>
       </c>
       <c r="F22">
-        <v>167.0</v>
+        <v>167</v>
       </c>
       <c r="G22">
         <v>33.4</v>
@@ -1739,112 +1738,112 @@
         <v>7.5</v>
       </c>
       <c r="I22">
-        <v>3173.0</v>
+        <v>3173</v>
       </c>
       <c r="J22">
-        <v>2527.0</v>
+        <v>2527</v>
       </c>
       <c r="K22">
-        <v>5700.0</v>
+        <v>5700</v>
       </c>
       <c r="L22">
-        <v>3173.0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" dyDescent="0.2">
+        <v>3173</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>3</v>
       </c>
       <c r="B23" s="8">
         <v>8</v>
       </c>
-      <c r="C23" t="s" s="2">
+      <c r="C23" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="D23" t="s" s="1">
+      <c r="D23" s="1" t="s">
         <v>58</v>
       </c>
       <c r="E23">
-        <v>130.0</v>
+        <v>130</v>
       </c>
       <c r="F23">
-        <v>97.0</v>
+        <v>97</v>
       </c>
       <c r="G23">
-        <v>19.4</v>
+        <v>19.399999999999999</v>
       </c>
       <c r="H23">
         <v>6.7</v>
       </c>
       <c r="I23">
-        <v>1843.0</v>
+        <v>1843</v>
       </c>
       <c r="J23">
-        <v>1290.0</v>
+        <v>1290</v>
       </c>
       <c r="K23">
-        <v>3133.0</v>
+        <v>3133</v>
       </c>
       <c r="L23">
-        <v>1843.0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" dyDescent="0.2">
+        <v>1843</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>3</v>
       </c>
       <c r="B24" s="8">
         <v>9</v>
       </c>
-      <c r="C24" t="s" s="2">
+      <c r="C24" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="D24" t="s" s="1">
+      <c r="D24" s="1" t="s">
         <v>59</v>
       </c>
       <c r="E24">
-        <v>142.0</v>
+        <v>142</v>
       </c>
       <c r="F24">
-        <v>105.0</v>
+        <v>105</v>
       </c>
       <c r="G24">
-        <v>21.0</v>
+        <v>21</v>
       </c>
       <c r="H24">
         <v>6.8</v>
       </c>
       <c r="I24">
-        <v>1995.0</v>
+        <v>1995</v>
       </c>
       <c r="J24">
-        <v>1412.0</v>
+        <v>1412</v>
       </c>
       <c r="K24">
-        <v>3407.0</v>
+        <v>3407</v>
       </c>
       <c r="L24">
-        <v>1995.0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" dyDescent="0.2">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>3</v>
       </c>
       <c r="B25" s="8">
         <v>10</v>
       </c>
-      <c r="C25" t="s" s="2">
+      <c r="C25" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="D25" t="s" s="1">
+      <c r="D25" s="1" t="s">
         <v>60</v>
       </c>
       <c r="E25">
-        <v>89.0</v>
+        <v>89</v>
       </c>
       <c r="F25">
-        <v>68.0</v>
+        <v>68</v>
       </c>
       <c r="G25">
         <v>13.6</v>
@@ -1853,188 +1852,188 @@
         <v>6.5</v>
       </c>
       <c r="I25">
-        <v>1292.0</v>
+        <v>1292</v>
       </c>
       <c r="J25">
-        <v>880.0</v>
+        <v>880</v>
       </c>
       <c r="K25">
-        <v>2172.0</v>
+        <v>2172</v>
       </c>
       <c r="L25">
-        <v>1292.0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" dyDescent="0.2">
+        <v>1292</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>4</v>
       </c>
       <c r="B26" s="8">
         <v>5</v>
       </c>
-      <c r="C26" t="s" s="1">
+      <c r="C26" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D26" t="s" s="1">
+      <c r="D26" s="1" t="s">
         <v>55</v>
       </c>
       <c r="E26">
-        <v>130.0</v>
+        <v>130</v>
       </c>
       <c r="F26">
-        <v>93.0</v>
+        <v>93</v>
       </c>
       <c r="G26">
-        <v>18.6</v>
+        <v>18.600000000000001</v>
       </c>
       <c r="H26">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="I26">
-        <v>1767.0</v>
+        <v>1767</v>
       </c>
       <c r="J26">
-        <v>1300.0</v>
+        <v>1300</v>
       </c>
       <c r="K26">
-        <v>3067.0</v>
+        <v>3067</v>
       </c>
       <c r="L26">
-        <v>1767.0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" dyDescent="0.2">
+        <v>1767</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>4</v>
       </c>
       <c r="B27" s="8">
         <v>6</v>
       </c>
-      <c r="C27" t="s" s="1">
+      <c r="C27" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D27" t="s" s="1">
+      <c r="D27" s="1" t="s">
         <v>56</v>
       </c>
       <c r="E27">
-        <v>149.0</v>
+        <v>149</v>
       </c>
       <c r="F27">
-        <v>161.0</v>
+        <v>161</v>
       </c>
       <c r="G27">
-        <v>32.2</v>
+        <v>32.200000000000003</v>
       </c>
       <c r="H27">
-        <v>4.6</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="I27">
-        <v>3059.0</v>
+        <v>3059</v>
       </c>
       <c r="J27">
-        <v>1363.0</v>
+        <v>1363</v>
       </c>
       <c r="K27">
-        <v>4422.0</v>
+        <v>4422</v>
       </c>
       <c r="L27">
-        <v>3059.0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" dyDescent="0.2">
+        <v>3059</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>4</v>
       </c>
       <c r="B28" s="8">
         <v>7</v>
       </c>
-      <c r="C28" t="s" s="1">
+      <c r="C28" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D28" t="s" s="11">
+      <c r="D28" s="11" t="s">
         <v>57</v>
       </c>
       <c r="E28">
-        <v>93.0</v>
+        <v>93</v>
       </c>
       <c r="F28">
-        <v>90.0</v>
+        <v>90</v>
       </c>
       <c r="G28">
-        <v>18.0</v>
+        <v>18</v>
       </c>
       <c r="H28">
         <v>5.2</v>
       </c>
       <c r="I28">
-        <v>1710.0</v>
+        <v>1710</v>
       </c>
       <c r="J28">
-        <v>875.0</v>
+        <v>875</v>
       </c>
       <c r="K28">
-        <v>2585.0</v>
+        <v>2585</v>
       </c>
       <c r="L28">
-        <v>1710.0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" dyDescent="0.2">
+        <v>1710</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>4</v>
       </c>
       <c r="B29" s="8">
         <v>8</v>
       </c>
-      <c r="C29" t="s" s="1">
+      <c r="C29" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D29" t="s" s="1">
+      <c r="D29" s="1" t="s">
         <v>58</v>
       </c>
       <c r="E29">
-        <v>97.0</v>
+        <v>97</v>
       </c>
       <c r="F29">
-        <v>97.0</v>
+        <v>97</v>
       </c>
       <c r="G29">
-        <v>19.4</v>
+        <v>19.399999999999999</v>
       </c>
       <c r="H29">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="I29">
-        <v>1843.0</v>
+        <v>1843</v>
       </c>
       <c r="J29">
-        <v>905.0</v>
+        <v>905</v>
       </c>
       <c r="K29">
-        <v>2748.0</v>
+        <v>2748</v>
       </c>
       <c r="L29">
-        <v>1843.0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16" dyDescent="0.2">
+        <v>1843</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>4</v>
       </c>
       <c r="B30" s="8">
         <v>9</v>
       </c>
-      <c r="C30" t="s" s="1">
+      <c r="C30" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D30" t="s" s="1">
+      <c r="D30" s="1" t="s">
         <v>59</v>
       </c>
       <c r="E30">
-        <v>76.0</v>
+        <v>76</v>
       </c>
       <c r="F30">
-        <v>91.0</v>
+        <v>91</v>
       </c>
       <c r="G30">
         <v>18.2</v>
@@ -2043,226 +2042,226 @@
         <v>4.2</v>
       </c>
       <c r="I30">
-        <v>1729.0</v>
+        <v>1729</v>
       </c>
       <c r="J30">
-        <v>674.0</v>
+        <v>674</v>
       </c>
       <c r="K30">
-        <v>2403.0</v>
+        <v>2403</v>
       </c>
       <c r="L30">
-        <v>1729.0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16" dyDescent="0.2">
+        <v>1729</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>4</v>
       </c>
       <c r="B31" s="8">
         <v>10</v>
       </c>
-      <c r="C31" t="s" s="1">
+      <c r="C31" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D31" t="s" s="1">
+      <c r="D31" s="1" t="s">
         <v>60</v>
       </c>
       <c r="E31">
-        <v>246.0</v>
+        <v>246</v>
       </c>
       <c r="F31">
-        <v>110.0</v>
+        <v>110</v>
       </c>
       <c r="G31">
-        <v>22.0</v>
+        <v>22</v>
       </c>
       <c r="H31">
         <v>11.2</v>
       </c>
       <c r="I31">
-        <v>2090.0</v>
+        <v>2090</v>
       </c>
       <c r="J31">
-        <v>2613.0</v>
+        <v>2613</v>
       </c>
       <c r="K31">
-        <v>4703.0</v>
+        <v>4703</v>
       </c>
       <c r="L31">
-        <v>2613.0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16" dyDescent="0.2">
+        <v>2613</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>5</v>
       </c>
       <c r="B32" s="8">
         <v>6</v>
       </c>
-      <c r="C32" t="s" s="1">
+      <c r="C32" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D32" t="s" s="1">
+      <c r="D32" s="1" t="s">
         <v>56</v>
       </c>
       <c r="E32">
-        <v>110.0</v>
+        <v>110</v>
       </c>
       <c r="F32">
-        <v>70.0</v>
+        <v>70</v>
       </c>
       <c r="G32">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="H32">
         <v>7.9</v>
       </c>
       <c r="I32">
-        <v>1330.0</v>
+        <v>1330</v>
       </c>
       <c r="J32">
-        <v>1120.0</v>
+        <v>1120</v>
       </c>
       <c r="K32">
-        <v>2450.0</v>
+        <v>2450</v>
       </c>
       <c r="L32">
-        <v>1330.0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" dyDescent="0.2">
+        <v>1330</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A33" s="10">
         <v>5</v>
       </c>
       <c r="B33" s="8">
         <v>7</v>
       </c>
-      <c r="C33" t="s" s="1">
+      <c r="C33" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D33" t="s" s="11">
+      <c r="D33" s="11" t="s">
         <v>57</v>
       </c>
       <c r="E33">
-        <v>168.0</v>
+        <v>168</v>
       </c>
       <c r="F33">
-        <v>173.0</v>
+        <v>173</v>
       </c>
       <c r="G33">
         <v>34.6</v>
       </c>
       <c r="H33">
-        <v>4.9</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="I33">
-        <v>3287.0</v>
+        <v>3287</v>
       </c>
       <c r="J33">
-        <v>1556.0</v>
+        <v>1556</v>
       </c>
       <c r="K33">
-        <v>4843.0</v>
+        <v>4843</v>
       </c>
       <c r="L33">
-        <v>3287.0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" dyDescent="0.2">
+        <v>3287</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>5</v>
       </c>
       <c r="B34" s="8">
         <v>8</v>
       </c>
-      <c r="C34" t="s" s="1">
+      <c r="C34" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D34" t="s" s="1">
+      <c r="D34" s="1" t="s">
         <v>58</v>
       </c>
       <c r="E34">
-        <v>48.0</v>
+        <v>48</v>
       </c>
       <c r="F34">
-        <v>40.0</v>
+        <v>40</v>
       </c>
       <c r="G34">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="H34">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="I34">
-        <v>760.0</v>
+        <v>760</v>
       </c>
       <c r="J34">
-        <v>467.0</v>
+        <v>467</v>
       </c>
       <c r="K34">
-        <v>1227.0</v>
+        <v>1227</v>
       </c>
       <c r="L34">
-        <v>760.0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" dyDescent="0.2">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>5</v>
       </c>
       <c r="B35" s="8">
         <v>9</v>
       </c>
-      <c r="C35" t="s" s="1">
+      <c r="C35" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D35" t="s" s="1">
+      <c r="D35" s="1" t="s">
         <v>59</v>
       </c>
       <c r="E35">
-        <v>60.0</v>
+        <v>60</v>
       </c>
       <c r="F35">
-        <v>55.0</v>
+        <v>55</v>
       </c>
       <c r="G35">
-        <v>11.0</v>
+        <v>11</v>
       </c>
       <c r="H35">
         <v>5.5</v>
       </c>
       <c r="I35">
-        <v>1045.0</v>
+        <v>1045</v>
       </c>
       <c r="J35">
-        <v>572.0</v>
+        <v>572</v>
       </c>
       <c r="K35">
-        <v>1617.0</v>
+        <v>1617</v>
       </c>
       <c r="L35">
-        <v>1045.0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16" dyDescent="0.2">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>5</v>
       </c>
       <c r="B36" s="8">
         <v>10</v>
       </c>
-      <c r="C36" t="s" s="1">
+      <c r="C36" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D36" t="s" s="1">
+      <c r="D36" s="1" t="s">
         <v>60</v>
       </c>
       <c r="E36">
-        <v>145.0</v>
+        <v>145</v>
       </c>
       <c r="F36">
-        <v>131.0</v>
+        <v>131</v>
       </c>
       <c r="G36">
         <v>26.2</v>
@@ -2271,74 +2270,74 @@
         <v>5.5</v>
       </c>
       <c r="I36">
-        <v>2489.0</v>
+        <v>2489</v>
       </c>
       <c r="J36">
-        <v>1386.0</v>
+        <v>1386</v>
       </c>
       <c r="K36">
-        <v>3875.0</v>
+        <v>3875</v>
       </c>
       <c r="L36">
-        <v>2489.0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16" dyDescent="0.2">
+        <v>2489</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>6</v>
       </c>
       <c r="B37" s="8">
         <v>7</v>
       </c>
-      <c r="C37" t="s" s="1">
+      <c r="C37" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="D37" t="s" s="11">
+      <c r="D37" s="11" t="s">
         <v>57</v>
       </c>
       <c r="E37">
-        <v>185.0</v>
+        <v>185</v>
       </c>
       <c r="F37">
-        <v>232.0</v>
+        <v>232</v>
       </c>
       <c r="G37">
         <v>46.4</v>
       </c>
       <c r="H37">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="I37">
-        <v>4408.0</v>
+        <v>4408</v>
       </c>
       <c r="J37">
-        <v>1617.0</v>
+        <v>1617</v>
       </c>
       <c r="K37">
-        <v>6025.0</v>
+        <v>6025</v>
       </c>
       <c r="L37">
-        <v>4408.0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:16" dyDescent="0.2">
+        <v>4408</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>6</v>
       </c>
       <c r="B38" s="8">
         <v>8</v>
       </c>
-      <c r="C38" t="s" s="1">
+      <c r="C38" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="D38" t="s" s="1">
+      <c r="D38" s="1" t="s">
         <v>58</v>
       </c>
       <c r="E38">
-        <v>77.0</v>
+        <v>77</v>
       </c>
       <c r="F38">
-        <v>72.0</v>
+        <v>72</v>
       </c>
       <c r="G38">
         <v>14.4</v>
@@ -2347,74 +2346,74 @@
         <v>5.3</v>
       </c>
       <c r="I38">
-        <v>1368.0</v>
+        <v>1368</v>
       </c>
       <c r="J38">
-        <v>730.0</v>
+        <v>730</v>
       </c>
       <c r="K38">
-        <v>2098.0</v>
+        <v>2098</v>
       </c>
       <c r="L38">
-        <v>1368.0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16" dyDescent="0.2">
+        <v>1368</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>6</v>
       </c>
       <c r="B39" s="8">
         <v>9</v>
       </c>
-      <c r="C39" t="s" s="1">
+      <c r="C39" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="D39" t="s" s="1">
+      <c r="D39" s="1" t="s">
         <v>59</v>
       </c>
       <c r="E39">
-        <v>78.0</v>
+        <v>78</v>
       </c>
       <c r="F39">
-        <v>89.0</v>
+        <v>89</v>
       </c>
       <c r="G39">
         <v>17.8</v>
       </c>
       <c r="H39">
-        <v>4.4</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="I39">
-        <v>1691.0</v>
+        <v>1691</v>
       </c>
       <c r="J39">
-        <v>702.0</v>
+        <v>702</v>
       </c>
       <c r="K39">
-        <v>2393.0</v>
+        <v>2393</v>
       </c>
       <c r="L39">
-        <v>1691.0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:16" dyDescent="0.2">
+        <v>1691</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>6</v>
       </c>
       <c r="B40" s="8">
         <v>10</v>
       </c>
-      <c r="C40" t="s" s="1">
+      <c r="C40" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="D40" t="s" s="1">
+      <c r="D40" s="1" t="s">
         <v>60</v>
       </c>
       <c r="E40">
-        <v>224.0</v>
+        <v>224</v>
       </c>
       <c r="F40">
-        <v>192.0</v>
+        <v>192</v>
       </c>
       <c r="G40">
         <v>38.4</v>
@@ -2423,74 +2422,74 @@
         <v>5.8</v>
       </c>
       <c r="I40">
-        <v>3648.0</v>
+        <v>3648</v>
       </c>
       <c r="J40">
-        <v>2165.0</v>
+        <v>2165</v>
       </c>
       <c r="K40">
-        <v>5813.0</v>
+        <v>5813</v>
       </c>
       <c r="L40">
-        <v>3648.0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:16" dyDescent="0.2">
+        <v>3648</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>7</v>
       </c>
       <c r="B41" s="8">
         <v>8</v>
       </c>
-      <c r="C41" t="s" s="1">
+      <c r="C41" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="D41" t="s" s="1">
+      <c r="D41" s="1" t="s">
         <v>58</v>
       </c>
       <c r="E41">
-        <v>131.0</v>
+        <v>131</v>
       </c>
       <c r="F41">
-        <v>160.0</v>
+        <v>160</v>
       </c>
       <c r="G41">
-        <v>32.0</v>
+        <v>32</v>
       </c>
       <c r="H41">
-        <v>4.1</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="I41">
-        <v>3040.0</v>
+        <v>3040</v>
       </c>
       <c r="J41">
-        <v>1155.0</v>
+        <v>1155</v>
       </c>
       <c r="K41">
-        <v>4195.0</v>
+        <v>4195</v>
       </c>
       <c r="L41">
-        <v>3040.0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:16" dyDescent="0.2">
+        <v>3040</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>7</v>
       </c>
       <c r="B42" s="8">
         <v>9</v>
       </c>
-      <c r="C42" t="s" s="1">
+      <c r="C42" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="D42" t="s" s="1">
+      <c r="D42" s="1" t="s">
         <v>59</v>
       </c>
       <c r="E42">
-        <v>110.0</v>
+        <v>110</v>
       </c>
       <c r="F42">
-        <v>146.0</v>
+        <v>146</v>
       </c>
       <c r="G42">
         <v>29.2</v>
@@ -2499,36 +2498,36 @@
         <v>3.8</v>
       </c>
       <c r="I42">
-        <v>2774.0</v>
+        <v>2774</v>
       </c>
       <c r="J42">
-        <v>943.0</v>
+        <v>943</v>
       </c>
       <c r="K42">
-        <v>3717.0</v>
+        <v>3717</v>
       </c>
       <c r="L42">
-        <v>2774.0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:16" dyDescent="0.2">
+        <v>2774</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>7</v>
       </c>
       <c r="B43" s="8">
         <v>10</v>
       </c>
-      <c r="C43" t="s" s="1">
+      <c r="C43" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="D43" t="s" s="1">
+      <c r="D43" s="1" t="s">
         <v>60</v>
       </c>
       <c r="E43">
-        <v>280.0</v>
+        <v>280</v>
       </c>
       <c r="F43">
-        <v>187.0</v>
+        <v>187</v>
       </c>
       <c r="G43">
         <v>37.4</v>
@@ -2537,36 +2536,36 @@
         <v>7.5</v>
       </c>
       <c r="I43">
-        <v>3553.0</v>
+        <v>3553</v>
       </c>
       <c r="J43">
-        <v>2830.0</v>
+        <v>2830</v>
       </c>
       <c r="K43">
-        <v>6383.0</v>
+        <v>6383</v>
       </c>
       <c r="L43">
-        <v>3553.0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:16" dyDescent="0.2">
+        <v>3553</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>8</v>
       </c>
       <c r="B44" s="8">
         <v>9</v>
       </c>
-      <c r="C44" t="s" s="1">
+      <c r="C44" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D44" t="s" s="1">
+      <c r="D44" s="1" t="s">
         <v>59</v>
       </c>
       <c r="E44">
-        <v>26.0</v>
+        <v>26</v>
       </c>
       <c r="F44">
-        <v>19.0</v>
+        <v>19</v>
       </c>
       <c r="G44">
         <v>3.8</v>
@@ -2575,95 +2574,95 @@
         <v>6.8</v>
       </c>
       <c r="I44">
-        <v>361.0</v>
+        <v>361</v>
       </c>
       <c r="J44">
-        <v>259.0</v>
+        <v>259</v>
       </c>
       <c r="K44">
-        <v>620.0</v>
+        <v>620</v>
       </c>
       <c r="L44">
-        <v>361.0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:16" dyDescent="0.2">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>8</v>
       </c>
       <c r="B45" s="8">
         <v>10</v>
       </c>
-      <c r="C45" t="s" s="1">
+      <c r="C45" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D45" t="s" s="1">
+      <c r="D45" s="1" t="s">
         <v>60</v>
       </c>
       <c r="E45">
-        <v>163.0</v>
+        <v>163</v>
       </c>
       <c r="F45">
-        <v>164.0</v>
+        <v>164</v>
       </c>
       <c r="G45">
-        <v>32.8</v>
+        <v>32.799999999999997</v>
       </c>
       <c r="H45">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="I45">
-        <v>3116.0</v>
+        <v>3116</v>
       </c>
       <c r="J45">
-        <v>1519.0</v>
+        <v>1519</v>
       </c>
       <c r="K45">
-        <v>4635.0</v>
+        <v>4635</v>
       </c>
       <c r="L45">
-        <v>3116.0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:16" dyDescent="0.2">
+        <v>3116</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>9</v>
       </c>
       <c r="B46" s="8">
         <v>10</v>
       </c>
-      <c r="C46" t="s" s="1">
+      <c r="C46" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D46" t="s" s="1">
+      <c r="D46" s="1" t="s">
         <v>60</v>
       </c>
       <c r="E46">
-        <v>175.0</v>
+        <v>175</v>
       </c>
       <c r="F46">
-        <v>170.0</v>
+        <v>170</v>
       </c>
       <c r="G46">
-        <v>34.0</v>
+        <v>34</v>
       </c>
       <c r="H46">
-        <v>5.1</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="I46">
-        <v>3230.0</v>
+        <v>3230</v>
       </c>
       <c r="J46">
-        <v>1645.0</v>
+        <v>1645</v>
       </c>
       <c r="K46">
-        <v>4875.0</v>
+        <v>4875</v>
       </c>
       <c r="L46">
-        <v>3230.0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:16" dyDescent="0.2">
+        <v>3230</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>1</v>
       </c>
@@ -2697,7 +2696,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:16" dyDescent="0.2">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>2</v>
       </c>
@@ -2731,7 +2730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:16" dyDescent="0.2">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>3</v>
       </c>
@@ -2765,7 +2764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:16" dyDescent="0.2">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>4</v>
       </c>
@@ -2799,7 +2798,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:16" dyDescent="0.2">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>5</v>
       </c>
@@ -2833,7 +2832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:16" dyDescent="0.2">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>6</v>
       </c>
@@ -2865,7 +2864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:16" dyDescent="0.2">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>7</v>
       </c>
@@ -2897,7 +2896,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:16" dyDescent="0.2">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>8</v>
       </c>
@@ -2929,7 +2928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:16" dyDescent="0.2">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>9</v>
       </c>
@@ -2961,7 +2960,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:16" dyDescent="0.2">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>10</v>
       </c>
@@ -2993,13 +2992,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:16" dyDescent="0.2">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G57" s="2"/>
     </row>
-    <row r="58" spans="1:16" dyDescent="0.2">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G58" s="1"/>
     </row>
-    <row r="59" spans="1:16" dyDescent="0.2">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G59" s="1"/>
     </row>
   </sheetData>

--- a/inputData/Parameters.xlsx
+++ b/inputData/Parameters.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sillewiberg/Desktop/Skole/Speciale/Master-Thesis-eVTOL-1/inputData/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F278866-8B49-0647-A835-544B4947017F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D67F16C-CFBF-1048-9FB8-BA0CC02C49B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16320" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
   </bookViews>
@@ -66,9 +66,6 @@
     <t>fs_{i,j}=75% of fd_{i,j}</t>
   </si>
   <si>
-    <t>c_{i,j} = $1/km</t>
-  </si>
-  <si>
     <t>e_{i,j} = 1%/km</t>
   </si>
   <si>
@@ -220,6 +217,9 @@
   </si>
   <si>
     <t>(55.924974, 12.265524)</t>
+  </si>
+  <si>
+    <t>c_{i,j} = DKK 30/km</t>
   </si>
 </sst>
 </file>
@@ -655,12 +655,12 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B2" s="4">
         <v>5</v>
@@ -671,7 +671,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B3" s="4">
         <v>0.75</v>
@@ -682,58 +682,58 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B4" s="4">
         <v>400</v>
       </c>
       <c r="D4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B5" s="4">
         <v>300</v>
       </c>
       <c r="D5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B6" s="4">
-        <v>1.51</v>
+        <v>30</v>
       </c>
       <c r="D6" t="s">
-        <v>9</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B7" s="4">
         <v>0.3</v>
       </c>
       <c r="D7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B8" s="4">
         <f>0.2/B20</f>
         <v>0.2</v>
       </c>
       <c r="D8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
@@ -744,7 +744,7 @@
         <v>4</v>
       </c>
       <c r="D9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
@@ -760,7 +760,7 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B11" s="4">
         <v>80</v>
@@ -782,13 +782,13 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B13" s="4">
         <v>20</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
@@ -800,7 +800,7 @@
         <v>2.11</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
@@ -812,7 +812,7 @@
         <v>30</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
@@ -824,7 +824,7 @@
         <v>20</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
@@ -832,21 +832,22 @@
         <v>6</v>
       </c>
       <c r="B17" s="4">
+        <f>780/B20</f>
         <v>780</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B20" s="4">
         <v>1</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -870,43 +871,43 @@
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A1" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="C1" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C1" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="J1" s="5" t="s">
+      <c r="L1" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="K1" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="L1" s="5" t="s">
-        <v>28</v>
-      </c>
       <c r="N1" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O1" s="7">
         <v>0.2</v>
@@ -921,10 +922,10 @@
         <v>2</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>51</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>52</v>
       </c>
       <c r="E2">
         <v>185</v>
@@ -951,13 +952,13 @@
         <v>4161</v>
       </c>
       <c r="N2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O2" s="4">
         <v>19</v>
       </c>
       <c r="P2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.2">
@@ -968,10 +969,10 @@
         <v>3</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E3">
         <v>82</v>
@@ -998,14 +999,14 @@
         <v>1672</v>
       </c>
       <c r="N3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O3" s="4">
         <f>1000/60</f>
         <v>16.666666666666668</v>
       </c>
       <c r="P3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.2">
@@ -1016,10 +1017,10 @@
         <v>4</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E4">
         <v>228</v>
@@ -1046,7 +1047,7 @@
         <v>2793</v>
       </c>
       <c r="N4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O4" s="4">
         <v>0.7</v>
@@ -1060,10 +1061,10 @@
         <v>5</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E5">
         <v>126</v>
@@ -1090,13 +1091,13 @@
         <v>2793</v>
       </c>
       <c r="N5" t="s">
+        <v>33</v>
+      </c>
+      <c r="O5" s="4">
+        <v>0</v>
+      </c>
+      <c r="P5" t="s">
         <v>34</v>
-      </c>
-      <c r="O5" s="4">
-        <v>0</v>
-      </c>
-      <c r="P5" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.2">
@@ -1107,10 +1108,10 @@
         <v>6</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E6">
         <v>205</v>
@@ -1146,10 +1147,10 @@
         <v>7</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E7">
         <v>263</v>
@@ -1185,10 +1186,10 @@
         <v>8</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E8">
         <v>143</v>
@@ -1224,10 +1225,10 @@
         <v>9</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E9">
         <v>155</v>
@@ -1263,10 +1264,10 @@
         <v>10</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E10">
         <v>42</v>
@@ -1302,10 +1303,10 @@
         <v>3</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>52</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>53</v>
       </c>
       <c r="E11">
         <v>173</v>
@@ -1340,10 +1341,10 @@
         <v>4</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E12">
         <v>103</v>
@@ -1378,10 +1379,10 @@
         <v>5</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E13">
         <v>89</v>
@@ -1416,10 +1417,10 @@
         <v>6</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E14">
         <v>100</v>
@@ -1454,10 +1455,10 @@
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E15">
         <v>138</v>
@@ -1492,10 +1493,10 @@
         <v>8</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E16">
         <v>55</v>
@@ -1530,10 +1531,10 @@
         <v>9</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E17">
         <v>38</v>
@@ -1568,10 +1569,10 @@
         <v>10</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E18">
         <v>205</v>
@@ -1606,10 +1607,10 @@
         <v>4</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D19" s="1" t="s">
         <v>53</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>54</v>
       </c>
       <c r="E19">
         <v>215</v>
@@ -1644,10 +1645,10 @@
         <v>5</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E20">
         <v>113</v>
@@ -1682,10 +1683,10 @@
         <v>6</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E21">
         <v>192</v>
@@ -1720,10 +1721,10 @@
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E22">
         <v>250</v>
@@ -1758,10 +1759,10 @@
         <v>8</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E23">
         <v>130</v>
@@ -1796,10 +1797,10 @@
         <v>9</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E24">
         <v>142</v>
@@ -1834,10 +1835,10 @@
         <v>10</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E25">
         <v>89</v>
@@ -1872,10 +1873,10 @@
         <v>5</v>
       </c>
       <c r="C26" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D26" s="1" t="s">
         <v>54</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>55</v>
       </c>
       <c r="E26">
         <v>130</v>
@@ -1910,10 +1911,10 @@
         <v>6</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E27">
         <v>149</v>
@@ -1948,10 +1949,10 @@
         <v>7</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E28">
         <v>93</v>
@@ -1986,10 +1987,10 @@
         <v>8</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E29">
         <v>97</v>
@@ -2024,10 +2025,10 @@
         <v>9</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E30">
         <v>76</v>
@@ -2062,10 +2063,10 @@
         <v>10</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E31">
         <v>246</v>
@@ -2100,10 +2101,10 @@
         <v>6</v>
       </c>
       <c r="C32" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D32" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>56</v>
       </c>
       <c r="E32">
         <v>110</v>
@@ -2138,10 +2139,10 @@
         <v>7</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D33" s="11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E33">
         <v>168</v>
@@ -2176,10 +2177,10 @@
         <v>8</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E34">
         <v>48</v>
@@ -2214,10 +2215,10 @@
         <v>9</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E35">
         <v>60</v>
@@ -2252,10 +2253,10 @@
         <v>10</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E36">
         <v>145</v>
@@ -2290,10 +2291,10 @@
         <v>7</v>
       </c>
       <c r="C37" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D37" s="11" t="s">
         <v>56</v>
-      </c>
-      <c r="D37" s="11" t="s">
-        <v>57</v>
       </c>
       <c r="E37">
         <v>185</v>
@@ -2328,10 +2329,10 @@
         <v>8</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E38">
         <v>77</v>
@@ -2366,10 +2367,10 @@
         <v>9</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E39">
         <v>78</v>
@@ -2404,10 +2405,10 @@
         <v>10</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E40">
         <v>224</v>
@@ -2442,10 +2443,10 @@
         <v>8</v>
       </c>
       <c r="C41" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D41" s="1" t="s">
         <v>57</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>58</v>
       </c>
       <c r="E41">
         <v>131</v>
@@ -2480,10 +2481,10 @@
         <v>9</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E42">
         <v>110</v>
@@ -2518,10 +2519,10 @@
         <v>10</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E43">
         <v>280</v>
@@ -2556,10 +2557,10 @@
         <v>9</v>
       </c>
       <c r="C44" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D44" s="1" t="s">
         <v>58</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>59</v>
       </c>
       <c r="E44">
         <v>26</v>
@@ -2594,10 +2595,10 @@
         <v>10</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E45">
         <v>163</v>
@@ -2632,10 +2633,10 @@
         <v>10</v>
       </c>
       <c r="C46" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D46" s="1" t="s">
         <v>59</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>60</v>
       </c>
       <c r="E46">
         <v>175</v>

--- a/inputData/Parameters.xlsx
+++ b/inputData/Parameters.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sillewiberg/Desktop/Skole/Speciale/Master-Thesis-eVTOL-1/inputData/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kapta\Documents\DTU\Speciale\GitHubFiles\inputData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F278866-8B49-0647-A835-544B4947017F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6178247B-1275-40E8-B67D-0E5573380FE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16320" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
   </bookViews>
   <sheets>
     <sheet name="Parameters" sheetId="9" r:id="rId1"/>
@@ -647,18 +647,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B15C49E0-A7B4-734A-8962-DC2A879F4079}">
   <dimension ref="A1:D20"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="22.6640625" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>20</v>
       </c>
@@ -669,7 +669,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -680,7 +680,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>46</v>
       </c>
@@ -691,7 +691,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -702,7 +702,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -713,7 +713,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -724,7 +724,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -736,7 +736,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
         <v>0</v>
       </c>
@@ -747,7 +747,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
         <v>1</v>
       </c>
@@ -758,7 +758,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
         <v>45</v>
       </c>
@@ -769,7 +769,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
         <v>2</v>
       </c>
@@ -780,7 +780,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
         <v>42</v>
       </c>
@@ -791,7 +791,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -803,7 +803,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
         <v>4</v>
       </c>
@@ -815,7 +815,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
         <v>5</v>
       </c>
@@ -827,18 +827,18 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
         <v>6</v>
       </c>
       <c r="B17" s="4">
-        <v>780</v>
+        <v>120</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
         <v>41</v>
       </c>
@@ -858,7 +858,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAF0D5EA-53B5-1240-9D84-6FE223856A18}">
   <dimension ref="A1:P59"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="17.1640625" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="17.1640625" customWidth="1"/>
@@ -868,7 +868,7 @@
     <col min="8" max="8" width="18.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A1" s="9" t="s">
         <v>36</v>
       </c>
@@ -913,7 +913,7 @@
       </c>
       <c r="P1" s="6"/>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>1</v>
       </c>
@@ -960,7 +960,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1008,7 +1008,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>1</v>
       </c>
@@ -1052,7 +1052,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>1</v>
       </c>
@@ -1099,7 +1099,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>1</v>
       </c>
@@ -1138,7 +1138,7 @@
       </c>
       <c r="O6" s="4"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>1</v>
       </c>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="O7" s="4"/>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>1</v>
       </c>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="O8" s="4"/>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>1</v>
       </c>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="O9" s="4"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>1</v>
       </c>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="O10" s="4"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>2</v>
       </c>
@@ -1332,7 +1332,7 @@
         <v>2489</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>2</v>
       </c>
@@ -1370,7 +1370,7 @@
         <v>2090</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>2</v>
       </c>
@@ -1408,7 +1408,7 @@
         <v>1520</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>2</v>
       </c>
@@ -1446,7 +1446,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>2</v>
       </c>
@@ -1484,7 +1484,7 @@
         <v>2869</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A16">
         <v>2</v>
       </c>
@@ -1522,7 +1522,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A17">
         <v>2</v>
       </c>
@@ -1560,7 +1560,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A18">
         <v>2</v>
       </c>
@@ -1598,7 +1598,7 @@
         <v>3724</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A19">
         <v>3</v>
       </c>
@@ -1636,7 +1636,7 @@
         <v>2329</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A20">
         <v>3</v>
       </c>
@@ -1674,7 +1674,7 @@
         <v>1197</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A21">
         <v>3</v>
       </c>
@@ -1712,7 +1712,7 @@
         <v>2394</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A22">
         <v>3</v>
       </c>
@@ -1750,7 +1750,7 @@
         <v>3173</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A23">
         <v>3</v>
       </c>
@@ -1788,7 +1788,7 @@
         <v>1843</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A24">
         <v>3</v>
       </c>
@@ -1826,7 +1826,7 @@
         <v>1995</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A25">
         <v>3</v>
       </c>
@@ -1864,7 +1864,7 @@
         <v>1292</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A26">
         <v>4</v>
       </c>
@@ -1902,7 +1902,7 @@
         <v>1767</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A27">
         <v>4</v>
       </c>
@@ -1940,7 +1940,7 @@
         <v>3059</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A28">
         <v>4</v>
       </c>
@@ -1978,7 +1978,7 @@
         <v>1710</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A29">
         <v>4</v>
       </c>
@@ -2016,7 +2016,7 @@
         <v>1843</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A30">
         <v>4</v>
       </c>
@@ -2054,7 +2054,7 @@
         <v>1729</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A31">
         <v>4</v>
       </c>
@@ -2092,7 +2092,7 @@
         <v>2613</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A32">
         <v>5</v>
       </c>
@@ -2130,7 +2130,7 @@
         <v>1330</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A33" s="10">
         <v>5</v>
       </c>
@@ -2168,7 +2168,7 @@
         <v>3287</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A34">
         <v>5</v>
       </c>
@@ -2206,7 +2206,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A35">
         <v>5</v>
       </c>
@@ -2244,7 +2244,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A36">
         <v>5</v>
       </c>
@@ -2282,7 +2282,7 @@
         <v>2489</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A37">
         <v>6</v>
       </c>
@@ -2320,7 +2320,7 @@
         <v>4408</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A38">
         <v>6</v>
       </c>
@@ -2358,7 +2358,7 @@
         <v>1368</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A39">
         <v>6</v>
       </c>
@@ -2396,7 +2396,7 @@
         <v>1691</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A40">
         <v>6</v>
       </c>
@@ -2434,7 +2434,7 @@
         <v>3648</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A41">
         <v>7</v>
       </c>
@@ -2472,7 +2472,7 @@
         <v>3040</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A42">
         <v>7</v>
       </c>
@@ -2510,7 +2510,7 @@
         <v>2774</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A43">
         <v>7</v>
       </c>
@@ -2548,7 +2548,7 @@
         <v>3553</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A44">
         <v>8</v>
       </c>
@@ -2586,7 +2586,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A45">
         <v>8</v>
       </c>
@@ -2624,7 +2624,7 @@
         <v>3116</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A46">
         <v>9</v>
       </c>
@@ -2662,7 +2662,7 @@
         <v>3230</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A47">
         <v>1</v>
       </c>
@@ -2696,7 +2696,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A48">
         <v>2</v>
       </c>
@@ -2730,7 +2730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A49">
         <v>3</v>
       </c>
@@ -2764,7 +2764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A50">
         <v>4</v>
       </c>
@@ -2798,7 +2798,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A51">
         <v>5</v>
       </c>
@@ -2832,7 +2832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A52">
         <v>6</v>
       </c>
@@ -2864,7 +2864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A53">
         <v>7</v>
       </c>
@@ -2896,7 +2896,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A54">
         <v>8</v>
       </c>
@@ -2928,7 +2928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A55">
         <v>9</v>
       </c>
@@ -2960,7 +2960,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A56">
         <v>10</v>
       </c>
@@ -2992,13 +2992,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.4">
       <c r="G57" s="2"/>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.4">
       <c r="G58" s="1"/>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.4">
       <c r="G59" s="1"/>
     </row>
   </sheetData>

--- a/inputData/Parameters.xlsx
+++ b/inputData/Parameters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kapta\Documents\DTU\Speciale\GitHubFiles\inputData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6178247B-1275-40E8-B67D-0E5573380FE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{600B90F6-DDA5-479D-AA66-1FABE0EB37D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
   </bookViews>
@@ -707,7 +707,7 @@
         <v>17</v>
       </c>
       <c r="B6" s="4">
-        <v>1.51</v>
+        <v>30</v>
       </c>
       <c r="D6" t="s">
         <v>9</v>

--- a/inputData/Parameters.xlsx
+++ b/inputData/Parameters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kapta\Documents\DTU\Speciale\GitHubFiles\inputData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{600B90F6-DDA5-479D-AA66-1FABE0EB37D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1D16FEC-2EF1-4589-870D-FC6DDE26716C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
   </bookViews>

--- a/inputData/Parameters.xlsx
+++ b/inputData/Parameters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sillewiberg/Desktop/Skole/Speciale/Master-Thesis-eVTOL-1/inputData/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D67F16C-CFBF-1048-9FB8-BA0CC02C49B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E85465D4-856B-9E42-A246-955D2FB9123B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16320" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
   </bookViews>
@@ -832,7 +832,6 @@
         <v>6</v>
       </c>
       <c r="B17" s="4">
-        <f>780/B20</f>
         <v>780</v>
       </c>
       <c r="D17" s="3" t="s">

--- a/inputData/Parameters.xlsx
+++ b/inputData/Parameters.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kapta\Documents\DTU\Speciale\GitHubFiles\inputData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sillewiberg/Desktop/Skole/Speciale/Master-Thesis-eVTOL-1/inputData/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1D16FEC-2EF1-4589-870D-FC6DDE26716C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CFD3FE2-E715-F441-9BAF-D11E03A8D1DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
+    <workbookView xWindow="2000" yWindow="2000" windowWidth="19420" windowHeight="12840" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
   </bookViews>
   <sheets>
     <sheet name="Parameters" sheetId="9" r:id="rId1"/>
@@ -171,9 +171,6 @@
     <t>penalty for not serving passengergroup</t>
   </si>
   <si>
-    <t>penalty for exceeding bmax</t>
-  </si>
-  <si>
     <t>bmid</t>
   </si>
   <si>
@@ -220,6 +217,9 @@
   </si>
   <si>
     <t>(55.924974, 12.265524)</t>
+  </si>
+  <si>
+    <t>penalty for exceeding bmid</t>
   </si>
 </sst>
 </file>
@@ -647,18 +647,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B15C49E0-A7B4-734A-8962-DC2A879F4079}">
   <dimension ref="A1:D20"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="22.6640625" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>20</v>
       </c>
@@ -669,7 +669,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -680,18 +680,18 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B4" s="4">
         <v>400</v>
       </c>
       <c r="D4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -702,7 +702,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -713,7 +713,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -724,7 +724,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -736,7 +736,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>0</v>
       </c>
@@ -747,7 +747,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>1</v>
       </c>
@@ -758,18 +758,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B11" s="4">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="D11" s="3">
         <v>0.8</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>2</v>
       </c>
@@ -780,7 +780,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>42</v>
       </c>
@@ -788,10 +788,10 @@
         <v>20</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.4">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -803,7 +803,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>4</v>
       </c>
@@ -815,7 +815,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>5</v>
       </c>
@@ -827,7 +827,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>6</v>
       </c>
@@ -838,7 +838,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>41</v>
       </c>
@@ -846,7 +846,7 @@
         <v>1</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -858,7 +858,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAF0D5EA-53B5-1240-9D84-6FE223856A18}">
   <dimension ref="A1:P59"/>
-  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="17.1640625" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="17.1640625" customWidth="1"/>
@@ -868,7 +868,7 @@
     <col min="8" max="8" width="18.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A1" s="9" t="s">
         <v>36</v>
       </c>
@@ -876,10 +876,10 @@
         <v>37</v>
       </c>
       <c r="C1" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D1" s="5" t="s">
         <v>49</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>50</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>22</v>
@@ -913,7 +913,7 @@
       </c>
       <c r="P1" s="6"/>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -921,10 +921,10 @@
         <v>2</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>51</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>52</v>
       </c>
       <c r="E2">
         <v>185</v>
@@ -960,7 +960,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>1</v>
       </c>
@@ -968,10 +968,10 @@
         <v>3</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E3">
         <v>82</v>
@@ -1008,7 +1008,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>1</v>
       </c>
@@ -1016,10 +1016,10 @@
         <v>4</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E4">
         <v>228</v>
@@ -1052,7 +1052,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>1</v>
       </c>
@@ -1060,10 +1060,10 @@
         <v>5</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E5">
         <v>126</v>
@@ -1099,7 +1099,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>1</v>
       </c>
@@ -1107,10 +1107,10 @@
         <v>6</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E6">
         <v>205</v>
@@ -1138,7 +1138,7 @@
       </c>
       <c r="O6" s="4"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>1</v>
       </c>
@@ -1146,10 +1146,10 @@
         <v>7</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E7">
         <v>263</v>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="O7" s="4"/>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>1</v>
       </c>
@@ -1185,10 +1185,10 @@
         <v>8</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E8">
         <v>143</v>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="O8" s="4"/>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>1</v>
       </c>
@@ -1224,10 +1224,10 @@
         <v>9</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E9">
         <v>155</v>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="O9" s="4"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>1</v>
       </c>
@@ -1263,10 +1263,10 @@
         <v>10</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E10">
         <v>42</v>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="O10" s="4"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>2</v>
       </c>
@@ -1302,10 +1302,10 @@
         <v>3</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>52</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>53</v>
       </c>
       <c r="E11">
         <v>173</v>
@@ -1332,7 +1332,7 @@
         <v>2489</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>2</v>
       </c>
@@ -1340,10 +1340,10 @@
         <v>4</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E12">
         <v>103</v>
@@ -1370,7 +1370,7 @@
         <v>2090</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>2</v>
       </c>
@@ -1378,10 +1378,10 @@
         <v>5</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E13">
         <v>89</v>
@@ -1408,7 +1408,7 @@
         <v>1520</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>2</v>
       </c>
@@ -1416,10 +1416,10 @@
         <v>6</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E14">
         <v>100</v>
@@ -1446,7 +1446,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>2</v>
       </c>
@@ -1454,10 +1454,10 @@
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E15">
         <v>138</v>
@@ -1484,7 +1484,7 @@
         <v>2869</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>2</v>
       </c>
@@ -1492,10 +1492,10 @@
         <v>8</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E16">
         <v>55</v>
@@ -1522,7 +1522,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>2</v>
       </c>
@@ -1530,10 +1530,10 @@
         <v>9</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E17">
         <v>38</v>
@@ -1560,7 +1560,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>2</v>
       </c>
@@ -1568,10 +1568,10 @@
         <v>10</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E18">
         <v>205</v>
@@ -1598,7 +1598,7 @@
         <v>3724</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>3</v>
       </c>
@@ -1606,10 +1606,10 @@
         <v>4</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D19" s="1" t="s">
         <v>53</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>54</v>
       </c>
       <c r="E19">
         <v>215</v>
@@ -1636,7 +1636,7 @@
         <v>2329</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>3</v>
       </c>
@@ -1644,10 +1644,10 @@
         <v>5</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E20">
         <v>113</v>
@@ -1674,7 +1674,7 @@
         <v>1197</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>3</v>
       </c>
@@ -1682,10 +1682,10 @@
         <v>6</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E21">
         <v>192</v>
@@ -1712,7 +1712,7 @@
         <v>2394</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>3</v>
       </c>
@@ -1720,10 +1720,10 @@
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E22">
         <v>250</v>
@@ -1750,7 +1750,7 @@
         <v>3173</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>3</v>
       </c>
@@ -1758,10 +1758,10 @@
         <v>8</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E23">
         <v>130</v>
@@ -1788,7 +1788,7 @@
         <v>1843</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>3</v>
       </c>
@@ -1796,10 +1796,10 @@
         <v>9</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E24">
         <v>142</v>
@@ -1826,7 +1826,7 @@
         <v>1995</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>3</v>
       </c>
@@ -1834,10 +1834,10 @@
         <v>10</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E25">
         <v>89</v>
@@ -1864,7 +1864,7 @@
         <v>1292</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>4</v>
       </c>
@@ -1872,10 +1872,10 @@
         <v>5</v>
       </c>
       <c r="C26" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D26" s="1" t="s">
         <v>54</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>55</v>
       </c>
       <c r="E26">
         <v>130</v>
@@ -1902,7 +1902,7 @@
         <v>1767</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>4</v>
       </c>
@@ -1910,10 +1910,10 @@
         <v>6</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E27">
         <v>149</v>
@@ -1940,7 +1940,7 @@
         <v>3059</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>4</v>
       </c>
@@ -1948,10 +1948,10 @@
         <v>7</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E28">
         <v>93</v>
@@ -1978,7 +1978,7 @@
         <v>1710</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>4</v>
       </c>
@@ -1986,10 +1986,10 @@
         <v>8</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E29">
         <v>97</v>
@@ -2016,7 +2016,7 @@
         <v>1843</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>4</v>
       </c>
@@ -2024,10 +2024,10 @@
         <v>9</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E30">
         <v>76</v>
@@ -2054,7 +2054,7 @@
         <v>1729</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>4</v>
       </c>
@@ -2062,10 +2062,10 @@
         <v>10</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E31">
         <v>246</v>
@@ -2092,7 +2092,7 @@
         <v>2613</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>5</v>
       </c>
@@ -2100,10 +2100,10 @@
         <v>6</v>
       </c>
       <c r="C32" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D32" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>56</v>
       </c>
       <c r="E32">
         <v>110</v>
@@ -2130,7 +2130,7 @@
         <v>1330</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A33" s="10">
         <v>5</v>
       </c>
@@ -2138,10 +2138,10 @@
         <v>7</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D33" s="11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E33">
         <v>168</v>
@@ -2168,7 +2168,7 @@
         <v>3287</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>5</v>
       </c>
@@ -2176,10 +2176,10 @@
         <v>8</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E34">
         <v>48</v>
@@ -2206,7 +2206,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>5</v>
       </c>
@@ -2214,10 +2214,10 @@
         <v>9</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E35">
         <v>60</v>
@@ -2244,7 +2244,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>5</v>
       </c>
@@ -2252,10 +2252,10 @@
         <v>10</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E36">
         <v>145</v>
@@ -2282,7 +2282,7 @@
         <v>2489</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>6</v>
       </c>
@@ -2290,10 +2290,10 @@
         <v>7</v>
       </c>
       <c r="C37" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D37" s="11" t="s">
         <v>56</v>
-      </c>
-      <c r="D37" s="11" t="s">
-        <v>57</v>
       </c>
       <c r="E37">
         <v>185</v>
@@ -2320,7 +2320,7 @@
         <v>4408</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>6</v>
       </c>
@@ -2328,10 +2328,10 @@
         <v>8</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E38">
         <v>77</v>
@@ -2358,7 +2358,7 @@
         <v>1368</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>6</v>
       </c>
@@ -2366,10 +2366,10 @@
         <v>9</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E39">
         <v>78</v>
@@ -2396,7 +2396,7 @@
         <v>1691</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>6</v>
       </c>
@@ -2404,10 +2404,10 @@
         <v>10</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E40">
         <v>224</v>
@@ -2434,7 +2434,7 @@
         <v>3648</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>7</v>
       </c>
@@ -2442,10 +2442,10 @@
         <v>8</v>
       </c>
       <c r="C41" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D41" s="1" t="s">
         <v>57</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>58</v>
       </c>
       <c r="E41">
         <v>131</v>
@@ -2472,7 +2472,7 @@
         <v>3040</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>7</v>
       </c>
@@ -2480,10 +2480,10 @@
         <v>9</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E42">
         <v>110</v>
@@ -2510,7 +2510,7 @@
         <v>2774</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>7</v>
       </c>
@@ -2518,10 +2518,10 @@
         <v>10</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E43">
         <v>280</v>
@@ -2548,7 +2548,7 @@
         <v>3553</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>8</v>
       </c>
@@ -2556,10 +2556,10 @@
         <v>9</v>
       </c>
       <c r="C44" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D44" s="1" t="s">
         <v>58</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>59</v>
       </c>
       <c r="E44">
         <v>26</v>
@@ -2586,7 +2586,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>8</v>
       </c>
@@ -2594,10 +2594,10 @@
         <v>10</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E45">
         <v>163</v>
@@ -2624,7 +2624,7 @@
         <v>3116</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>9</v>
       </c>
@@ -2632,10 +2632,10 @@
         <v>10</v>
       </c>
       <c r="C46" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D46" s="1" t="s">
         <v>59</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>60</v>
       </c>
       <c r="E46">
         <v>175</v>
@@ -2662,7 +2662,7 @@
         <v>3230</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>1</v>
       </c>
@@ -2696,7 +2696,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>2</v>
       </c>
@@ -2730,7 +2730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>3</v>
       </c>
@@ -2764,7 +2764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>4</v>
       </c>
@@ -2798,7 +2798,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>5</v>
       </c>
@@ -2832,7 +2832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>6</v>
       </c>
@@ -2864,7 +2864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>7</v>
       </c>
@@ -2896,7 +2896,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>8</v>
       </c>
@@ -2928,7 +2928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>9</v>
       </c>
@@ -2960,7 +2960,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>10</v>
       </c>
@@ -2992,13 +2992,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G57" s="2"/>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G58" s="1"/>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G59" s="1"/>
     </row>
   </sheetData>

--- a/inputData/Parameters.xlsx
+++ b/inputData/Parameters.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sillewiberg/Desktop/Skole/Speciale/Master-Thesis-eVTOL-1/inputData/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CFD3FE2-E715-F441-9BAF-D11E03A8D1DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE494151-0397-8E43-9CE6-8F1B08E35F2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2000" yWindow="2000" windowWidth="19420" windowHeight="12840" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
+    <workbookView xWindow="2000" yWindow="500" windowWidth="19420" windowHeight="16320" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
   </bookViews>
   <sheets>
     <sheet name="Parameters" sheetId="9" r:id="rId1"/>
@@ -763,7 +763,7 @@
         <v>44</v>
       </c>
       <c r="B11" s="4">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="D11" s="3">
         <v>0.8</v>

--- a/inputData/Parameters.xlsx
+++ b/inputData/Parameters.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sillewiberg/Desktop/Skole/Speciale/Master-Thesis-eVTOL-1/inputData/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kapta\Documents\DTU\Speciale\GitHubFiles\inputData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE494151-0397-8E43-9CE6-8F1B08E35F2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14C88F75-73F9-431A-9C84-FF9086595067}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2000" yWindow="500" windowWidth="19420" windowHeight="16320" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
   </bookViews>
   <sheets>
     <sheet name="Parameters" sheetId="9" r:id="rId1"/>
@@ -647,18 +647,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B15C49E0-A7B4-734A-8962-DC2A879F4079}">
   <dimension ref="A1:D20"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.6640625" customWidth="1"/>
-    <col min="2" max="2" width="10.83203125" style="4"/>
+    <col min="1" max="1" width="22.625" customWidth="1"/>
+    <col min="2" max="2" width="10.875" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>20</v>
       </c>
@@ -669,7 +669,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -680,7 +680,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>45</v>
       </c>
@@ -691,7 +691,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -702,7 +702,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -713,7 +713,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -724,7 +724,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -736,7 +736,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>0</v>
       </c>
@@ -747,7 +747,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>1</v>
       </c>
@@ -758,7 +758,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>44</v>
       </c>
@@ -769,7 +769,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>2</v>
       </c>
@@ -780,7 +780,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>42</v>
       </c>
@@ -791,7 +791,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -803,7 +803,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>4</v>
       </c>
@@ -815,7 +815,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>5</v>
       </c>
@@ -827,18 +827,18 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>6</v>
       </c>
       <c r="B17" s="4">
-        <v>120</v>
+        <v>780</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>41</v>
       </c>
@@ -858,17 +858,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAF0D5EA-53B5-1240-9D84-6FE223856A18}">
   <dimension ref="A1:P59"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="17.1640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="17.1640625" customWidth="1"/>
-    <col min="5" max="5" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.1640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="17.125" customWidth="1"/>
+    <col min="5" max="5" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
         <v>36</v>
       </c>
@@ -913,7 +913,7 @@
       </c>
       <c r="P1" s="6"/>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -960,7 +960,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1008,7 +1008,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1</v>
       </c>
@@ -1052,7 +1052,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>1</v>
       </c>
@@ -1099,7 +1099,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>1</v>
       </c>
@@ -1138,7 +1138,7 @@
       </c>
       <c r="O6" s="4"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>1</v>
       </c>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="O7" s="4"/>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>1</v>
       </c>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="O8" s="4"/>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>1</v>
       </c>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="O9" s="4"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>1</v>
       </c>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="O10" s="4"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>2</v>
       </c>
@@ -1332,7 +1332,7 @@
         <v>2489</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>2</v>
       </c>
@@ -1370,7 +1370,7 @@
         <v>2090</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>2</v>
       </c>
@@ -1408,7 +1408,7 @@
         <v>1520</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>2</v>
       </c>
@@ -1446,7 +1446,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>2</v>
       </c>
@@ -1484,7 +1484,7 @@
         <v>2869</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>2</v>
       </c>
@@ -1522,7 +1522,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>2</v>
       </c>
@@ -1560,7 +1560,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>2</v>
       </c>
@@ -1598,7 +1598,7 @@
         <v>3724</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>3</v>
       </c>
@@ -1636,7 +1636,7 @@
         <v>2329</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>3</v>
       </c>
@@ -1674,7 +1674,7 @@
         <v>1197</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>3</v>
       </c>
@@ -1712,7 +1712,7 @@
         <v>2394</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>3</v>
       </c>
@@ -1750,7 +1750,7 @@
         <v>3173</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>3</v>
       </c>
@@ -1788,7 +1788,7 @@
         <v>1843</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>3</v>
       </c>
@@ -1826,7 +1826,7 @@
         <v>1995</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>3</v>
       </c>
@@ -1864,7 +1864,7 @@
         <v>1292</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>4</v>
       </c>
@@ -1902,7 +1902,7 @@
         <v>1767</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>4</v>
       </c>
@@ -1940,7 +1940,7 @@
         <v>3059</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>4</v>
       </c>
@@ -1978,7 +1978,7 @@
         <v>1710</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>4</v>
       </c>
@@ -2016,7 +2016,7 @@
         <v>1843</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>4</v>
       </c>
@@ -2054,7 +2054,7 @@
         <v>1729</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>4</v>
       </c>
@@ -2092,7 +2092,7 @@
         <v>2613</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>5</v>
       </c>
@@ -2130,7 +2130,7 @@
         <v>1330</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" s="10">
         <v>5</v>
       </c>
@@ -2168,7 +2168,7 @@
         <v>3287</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>5</v>
       </c>
@@ -2206,7 +2206,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>5</v>
       </c>
@@ -2244,7 +2244,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>5</v>
       </c>
@@ -2282,7 +2282,7 @@
         <v>2489</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>6</v>
       </c>
@@ -2320,7 +2320,7 @@
         <v>4408</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>6</v>
       </c>
@@ -2358,7 +2358,7 @@
         <v>1368</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>6</v>
       </c>
@@ -2396,7 +2396,7 @@
         <v>1691</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>6</v>
       </c>
@@ -2434,7 +2434,7 @@
         <v>3648</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>7</v>
       </c>
@@ -2472,7 +2472,7 @@
         <v>3040</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>7</v>
       </c>
@@ -2510,7 +2510,7 @@
         <v>2774</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>7</v>
       </c>
@@ -2548,7 +2548,7 @@
         <v>3553</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>8</v>
       </c>
@@ -2586,7 +2586,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>8</v>
       </c>
@@ -2624,7 +2624,7 @@
         <v>3116</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>9</v>
       </c>
@@ -2662,7 +2662,7 @@
         <v>3230</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>1</v>
       </c>
@@ -2696,7 +2696,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>2</v>
       </c>
@@ -2730,7 +2730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>3</v>
       </c>
@@ -2764,7 +2764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>4</v>
       </c>
@@ -2798,7 +2798,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>5</v>
       </c>
@@ -2832,7 +2832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>6</v>
       </c>
@@ -2864,7 +2864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>7</v>
       </c>
@@ -2896,7 +2896,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>8</v>
       </c>
@@ -2928,7 +2928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>9</v>
       </c>
@@ -2960,7 +2960,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>10</v>
       </c>
@@ -2992,13 +2992,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="G57" s="2"/>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="G58" s="1"/>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="G59" s="1"/>
     </row>
   </sheetData>

--- a/inputData/Parameters.xlsx
+++ b/inputData/Parameters.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kapta\Documents\DTU\Speciale\GitHubFiles\inputData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sillewiberg/Desktop/Skole/Speciale/Master-Thesis-eVTOL-1/inputData/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14C88F75-73F9-431A-9C84-FF9086595067}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{760003B1-6592-C542-B4ED-E39B117D197F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
+    <workbookView xWindow="14320" yWindow="500" windowWidth="14480" windowHeight="16340" activeTab="1" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
   </bookViews>
   <sheets>
     <sheet name="Parameters" sheetId="9" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="62">
   <si>
     <t>cap_u</t>
   </si>
@@ -210,16 +210,19 @@
     <t>(57.019081, 9.957817)</t>
   </si>
   <si>
-    <t>(55.581790, 9.722994)</t>
-  </si>
-  <si>
-    <t>(55.726059, 9.574035)</t>
-  </si>
-  <si>
     <t>(55.924974, 12.265524)</t>
   </si>
   <si>
     <t>penalty for exceeding bmid</t>
+  </si>
+  <si>
+    <t>(56.408780, 9.417814)</t>
+  </si>
+  <si>
+    <t>(55.088776, 14.721890)</t>
+  </si>
+  <si>
+    <t>(56.049305, 12.584406)</t>
   </si>
 </sst>
 </file>
@@ -647,19 +650,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B15C49E0-A7B4-734A-8962-DC2A879F4079}">
   <dimension ref="A1:D20"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="22.625" customWidth="1"/>
-    <col min="2" max="2" width="10.875" style="4"/>
+    <col min="1" max="1" width="22.6640625" customWidth="1"/>
+    <col min="2" max="2" width="10.83203125" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" dyDescent="0.2">
       <c r="A1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:4" dyDescent="0.2">
+      <c r="A2" t="s" s="1">
         <v>20</v>
       </c>
       <c r="B2" s="4">
@@ -669,7 +672,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" dyDescent="0.2">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -680,7 +683,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" dyDescent="0.2">
       <c r="A4" t="s">
         <v>45</v>
       </c>
@@ -691,7 +694,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" dyDescent="0.2">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -702,7 +705,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" dyDescent="0.2">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -713,7 +716,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" dyDescent="0.2">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -724,7 +727,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" dyDescent="0.2">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -736,7 +739,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" dyDescent="0.2">
       <c r="A9" t="s">
         <v>0</v>
       </c>
@@ -747,7 +750,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" dyDescent="0.2">
       <c r="A10" t="s">
         <v>1</v>
       </c>
@@ -758,7 +761,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" dyDescent="0.2">
       <c r="A11" t="s">
         <v>44</v>
       </c>
@@ -769,7 +772,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" dyDescent="0.2">
       <c r="A12" t="s">
         <v>2</v>
       </c>
@@ -780,18 +783,18 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" dyDescent="0.2">
       <c r="A13" t="s">
         <v>42</v>
       </c>
       <c r="B13" s="4">
         <v>20</v>
       </c>
-      <c r="D13" s="3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D13" t="s" s="3">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" dyDescent="0.2">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -799,11 +802,11 @@
         <f>2.11*B20</f>
         <v>2.11</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" t="s" s="3">
         <v>39</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" dyDescent="0.2">
       <c r="A15" t="s">
         <v>4</v>
       </c>
@@ -811,11 +814,11 @@
         <f>30/B20</f>
         <v>30</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="D15" t="s" s="3">
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" dyDescent="0.2">
       <c r="A16" t="s">
         <v>5</v>
       </c>
@@ -823,29 +826,29 @@
         <f>20/B20</f>
         <v>20</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="D16" t="s" s="3">
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" dyDescent="0.2">
       <c r="A17" t="s">
         <v>6</v>
       </c>
       <c r="B17" s="4">
-        <v>780</v>
-      </c>
-      <c r="D17" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D17" t="s" s="3">
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" dyDescent="0.2">
       <c r="A20" t="s">
         <v>41</v>
       </c>
       <c r="B20" s="4">
         <v>1</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="D20" t="s" s="3">
         <v>47</v>
       </c>
     </row>
@@ -858,54 +861,54 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAF0D5EA-53B5-1240-9D84-6FE223856A18}">
   <dimension ref="A1:P59"/>
-  <sheetFormatPr defaultColWidth="10.625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="17.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="17.125" customWidth="1"/>
-    <col min="5" max="5" width="12.125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="17.1640625" customWidth="1"/>
+    <col min="5" max="5" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:16" dyDescent="0.2">
+      <c r="A1" t="s" s="9">
         <v>36</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" t="s" s="5">
         <v>37</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" t="s" s="5">
         <v>48</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" t="s" s="5">
         <v>49</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" t="s" s="5">
         <v>22</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" t="s" s="5">
         <v>23</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" t="s" s="5">
         <v>24</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" t="s" s="5">
         <v>25</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" t="s" s="5">
         <v>26</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" t="s" s="5">
         <v>27</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="K1" t="s" s="5">
         <v>38</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="L1" t="s" s="5">
         <v>28</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="N1" t="s" s="6">
         <v>19</v>
       </c>
       <c r="O1" s="7">
@@ -913,24 +916,24 @@
       </c>
       <c r="P1" s="6"/>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" s="8">
         <v>2</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" t="s" s="1">
         <v>50</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" t="s" s="2">
         <v>51</v>
       </c>
       <c r="E2">
-        <v>185</v>
+        <v>185.0</v>
       </c>
       <c r="F2">
-        <v>219</v>
+        <v>219.0</v>
       </c>
       <c r="G2">
         <v>43.8</v>
@@ -939,16 +942,16 @@
         <v>4.2</v>
       </c>
       <c r="I2">
-        <v>4161</v>
+        <v>4161.0</v>
       </c>
       <c r="J2">
-        <v>1647</v>
+        <v>1647.0</v>
       </c>
       <c r="K2">
-        <v>5808</v>
+        <v>5808.0</v>
       </c>
       <c r="L2">
-        <v>4161</v>
+        <v>4161.0</v>
       </c>
       <c r="N2" t="s">
         <v>29</v>
@@ -960,42 +963,42 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" dyDescent="0.2">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" s="8">
         <v>3</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" t="s" s="1">
         <v>50</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" t="s" s="2">
         <v>52</v>
       </c>
       <c r="E3">
-        <v>82</v>
+        <v>82.0</v>
       </c>
       <c r="F3">
-        <v>88</v>
+        <v>88.0</v>
       </c>
       <c r="G3">
-        <v>17.600000000000001</v>
+        <v>17.6</v>
       </c>
       <c r="H3">
         <v>4.7</v>
       </c>
       <c r="I3">
-        <v>1672</v>
+        <v>1672.0</v>
       </c>
       <c r="J3">
-        <v>751</v>
+        <v>751.0</v>
       </c>
       <c r="K3">
-        <v>2423</v>
+        <v>2423.0</v>
       </c>
       <c r="L3">
-        <v>1672</v>
+        <v>1672.0</v>
       </c>
       <c r="N3" t="s">
         <v>31</v>
@@ -1008,24 +1011,24 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" dyDescent="0.2">
       <c r="A4">
         <v>1</v>
       </c>
       <c r="B4" s="8">
         <v>4</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" t="s" s="1">
         <v>50</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" t="s" s="1">
         <v>53</v>
       </c>
       <c r="E4">
-        <v>228</v>
+        <v>228.0</v>
       </c>
       <c r="F4">
-        <v>147</v>
+        <v>147.0</v>
       </c>
       <c r="G4">
         <v>29.4</v>
@@ -1034,16 +1037,16 @@
         <v>7.8</v>
       </c>
       <c r="I4">
-        <v>2793</v>
+        <v>2793.0</v>
       </c>
       <c r="J4">
-        <v>2317</v>
+        <v>2317.0</v>
       </c>
       <c r="K4">
-        <v>5110</v>
+        <v>5110.0</v>
       </c>
       <c r="L4">
-        <v>2793</v>
+        <v>2793.0</v>
       </c>
       <c r="N4" t="s">
         <v>33</v>
@@ -1052,24 +1055,24 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" dyDescent="0.2">
       <c r="A5">
         <v>1</v>
       </c>
       <c r="B5" s="8">
         <v>5</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" t="s" s="1">
         <v>50</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" t="s" s="1">
         <v>54</v>
       </c>
       <c r="E5">
-        <v>126</v>
+        <v>126.0</v>
       </c>
       <c r="F5">
-        <v>147</v>
+        <v>147.0</v>
       </c>
       <c r="G5">
         <v>29.4</v>
@@ -1078,16 +1081,16 @@
         <v>4.3</v>
       </c>
       <c r="I5">
-        <v>2793</v>
+        <v>2793.0</v>
       </c>
       <c r="J5">
-        <v>1127</v>
+        <v>1127.0</v>
       </c>
       <c r="K5">
-        <v>3920</v>
+        <v>3920.0</v>
       </c>
       <c r="L5">
-        <v>2793</v>
+        <v>2793.0</v>
       </c>
       <c r="N5" t="s">
         <v>34</v>
@@ -1099,24 +1102,24 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" dyDescent="0.2">
       <c r="A6">
         <v>1</v>
       </c>
       <c r="B6" s="8">
         <v>6</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" t="s" s="1">
         <v>50</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" t="s" s="1">
         <v>55</v>
       </c>
       <c r="E6">
-        <v>205</v>
+        <v>205.0</v>
       </c>
       <c r="F6">
-        <v>197</v>
+        <v>197.0</v>
       </c>
       <c r="G6">
         <v>39.4</v>
@@ -1125,37 +1128,37 @@
         <v>5.2</v>
       </c>
       <c r="I6">
-        <v>3743</v>
+        <v>3743.0</v>
       </c>
       <c r="J6">
-        <v>1932</v>
+        <v>1932.0</v>
       </c>
       <c r="K6">
-        <v>5675</v>
+        <v>5675.0</v>
       </c>
       <c r="L6">
-        <v>3743</v>
+        <v>3743.0</v>
       </c>
       <c r="O6" s="4"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" dyDescent="0.2">
       <c r="A7">
         <v>1</v>
       </c>
       <c r="B7" s="8">
         <v>7</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" t="s" s="1">
         <v>50</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" t="s" s="1">
         <v>56</v>
       </c>
       <c r="E7">
-        <v>263</v>
+        <v>263.0</v>
       </c>
       <c r="F7">
-        <v>227</v>
+        <v>227.0</v>
       </c>
       <c r="G7">
         <v>45.4</v>
@@ -1164,154 +1167,154 @@
         <v>5.8</v>
       </c>
       <c r="I7">
-        <v>4313</v>
+        <v>4313.0</v>
       </c>
       <c r="J7">
-        <v>2539</v>
+        <v>2539.0</v>
       </c>
       <c r="K7">
-        <v>6852</v>
+        <v>6852.0</v>
       </c>
       <c r="L7">
-        <v>4313</v>
+        <v>4313.0</v>
       </c>
       <c r="O7" s="4"/>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" dyDescent="0.2">
       <c r="A8">
         <v>1</v>
       </c>
       <c r="B8" s="8">
         <v>8</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" t="s" s="1">
         <v>50</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>57</v>
+      <c r="D8" t="s" s="1">
+        <v>60</v>
       </c>
       <c r="E8">
-        <v>143</v>
+        <v>156.0</v>
       </c>
       <c r="F8">
-        <v>184</v>
+        <v>144.0</v>
       </c>
       <c r="G8">
-        <v>36.799999999999997</v>
+        <v>28.8</v>
       </c>
       <c r="H8">
-        <v>3.9</v>
+        <v>5.4</v>
       </c>
       <c r="I8">
-        <v>3496</v>
+        <v>2736.0</v>
       </c>
       <c r="J8">
-        <v>1239</v>
+        <v>1484.0</v>
       </c>
       <c r="K8">
-        <v>4735</v>
+        <v>4220.0</v>
       </c>
       <c r="L8">
-        <v>3496</v>
+        <v>2736.0</v>
       </c>
       <c r="O8" s="4"/>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" dyDescent="0.2">
       <c r="A9">
         <v>1</v>
       </c>
       <c r="B9" s="8">
         <v>9</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" t="s" s="1">
         <v>50</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>58</v>
+      <c r="D9" t="s" s="1">
+        <v>59</v>
       </c>
       <c r="E9">
-        <v>155</v>
+        <v>230.0</v>
       </c>
       <c r="F9">
-        <v>193</v>
+        <v>219.0</v>
       </c>
       <c r="G9">
-        <v>38.6</v>
+        <v>43.8</v>
       </c>
       <c r="H9">
-        <v>4</v>
+        <v>5.3</v>
       </c>
       <c r="I9">
-        <v>3667</v>
+        <v>4161.0</v>
       </c>
       <c r="J9">
-        <v>1358</v>
+        <v>2172.0</v>
       </c>
       <c r="K9">
-        <v>5025</v>
+        <v>6333.0</v>
       </c>
       <c r="L9">
-        <v>3667</v>
+        <v>4161.0</v>
       </c>
       <c r="O9" s="4"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" dyDescent="0.2">
       <c r="A10">
         <v>1</v>
       </c>
       <c r="B10" s="8">
         <v>10</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" t="s" s="1">
         <v>50</v>
       </c>
-      <c r="D10" s="1" t="s">
-        <v>59</v>
+      <c r="D10" t="s" s="1">
+        <v>61</v>
       </c>
       <c r="E10">
-        <v>42</v>
+        <v>56.0</v>
       </c>
       <c r="F10">
-        <v>41</v>
+        <v>47.0</v>
       </c>
       <c r="G10">
-        <v>8.1999999999999993</v>
+        <v>9.4</v>
       </c>
       <c r="H10">
-        <v>5.0999999999999996</v>
+        <v>6.0</v>
       </c>
       <c r="I10">
-        <v>779</v>
+        <v>893.0</v>
       </c>
       <c r="J10">
-        <v>394</v>
+        <v>544.0</v>
       </c>
       <c r="K10">
-        <v>1173</v>
+        <v>1437.0</v>
       </c>
       <c r="L10">
-        <v>779</v>
+        <v>893.0</v>
       </c>
       <c r="O10" s="4"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" dyDescent="0.2">
       <c r="A11">
         <v>2</v>
       </c>
       <c r="B11" s="8">
         <v>3</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" t="s" s="2">
         <v>51</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" t="s" s="2">
         <v>52</v>
       </c>
       <c r="E11">
-        <v>173</v>
+        <v>173.0</v>
       </c>
       <c r="F11">
-        <v>131</v>
+        <v>131.0</v>
       </c>
       <c r="G11">
         <v>26.2</v>
@@ -1320,378 +1323,378 @@
         <v>6.6</v>
       </c>
       <c r="I11">
-        <v>2489</v>
+        <v>2489.0</v>
       </c>
       <c r="J11">
-        <v>1713</v>
+        <v>1713.0</v>
       </c>
       <c r="K11">
-        <v>4202</v>
+        <v>4202.0</v>
       </c>
       <c r="L11">
-        <v>2489</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+        <v>2489.0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" dyDescent="0.2">
       <c r="A12">
         <v>2</v>
       </c>
       <c r="B12" s="8">
         <v>4</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" t="s" s="2">
         <v>51</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D12" t="s" s="1">
         <v>53</v>
       </c>
       <c r="E12">
-        <v>103</v>
+        <v>103.0</v>
       </c>
       <c r="F12">
-        <v>110</v>
+        <v>110.0</v>
       </c>
       <c r="G12">
-        <v>22</v>
+        <v>22.0</v>
       </c>
       <c r="H12">
         <v>4.7</v>
       </c>
       <c r="I12">
-        <v>2090</v>
+        <v>2090.0</v>
       </c>
       <c r="J12">
-        <v>945</v>
+        <v>945.0</v>
       </c>
       <c r="K12">
-        <v>3035</v>
+        <v>3035.0</v>
       </c>
       <c r="L12">
-        <v>2090</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+        <v>2090.0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" dyDescent="0.2">
       <c r="A13">
         <v>2</v>
       </c>
       <c r="B13" s="8">
         <v>5</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" t="s" s="2">
         <v>51</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D13" t="s" s="1">
         <v>54</v>
       </c>
       <c r="E13">
-        <v>89</v>
+        <v>89.0</v>
       </c>
       <c r="F13">
-        <v>80</v>
+        <v>80.0</v>
       </c>
       <c r="G13">
-        <v>16</v>
+        <v>16.0</v>
       </c>
       <c r="H13">
         <v>5.6</v>
       </c>
       <c r="I13">
-        <v>1520</v>
+        <v>1520.0</v>
       </c>
       <c r="J13">
-        <v>852</v>
+        <v>852.0</v>
       </c>
       <c r="K13">
-        <v>2372</v>
+        <v>2372.0</v>
       </c>
       <c r="L13">
-        <v>1520</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+        <v>1520.0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" dyDescent="0.2">
       <c r="A14">
         <v>2</v>
       </c>
       <c r="B14" s="8">
         <v>6</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" t="s" s="2">
         <v>51</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="D14" t="s" s="1">
         <v>55</v>
       </c>
       <c r="E14">
-        <v>100</v>
+        <v>100.0</v>
       </c>
       <c r="F14">
-        <v>98</v>
+        <v>98.0</v>
       </c>
       <c r="G14">
-        <v>19.600000000000001</v>
+        <v>19.6</v>
       </c>
       <c r="H14">
-        <v>5.0999999999999996</v>
+        <v>5.1</v>
       </c>
       <c r="I14">
-        <v>1862</v>
+        <v>1862.0</v>
       </c>
       <c r="J14">
-        <v>938</v>
+        <v>938.0</v>
       </c>
       <c r="K14">
-        <v>2800</v>
+        <v>2800.0</v>
       </c>
       <c r="L14">
-        <v>1862</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+        <v>1862.0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" dyDescent="0.2">
       <c r="A15">
         <v>2</v>
       </c>
       <c r="B15" s="8">
         <v>7</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" t="s" s="2">
         <v>51</v>
       </c>
-      <c r="D15" s="11" t="s">
+      <c r="D15" t="s" s="11">
         <v>56</v>
       </c>
       <c r="E15">
-        <v>138</v>
+        <v>138.0</v>
       </c>
       <c r="F15">
-        <v>151</v>
+        <v>151.0</v>
       </c>
       <c r="G15">
         <v>30.2</v>
       </c>
       <c r="H15">
-        <v>4.5999999999999996</v>
+        <v>4.6</v>
       </c>
       <c r="I15">
-        <v>2869</v>
+        <v>2869.0</v>
       </c>
       <c r="J15">
-        <v>1258</v>
+        <v>1258.0</v>
       </c>
       <c r="K15">
-        <v>4127</v>
+        <v>4127.0</v>
       </c>
       <c r="L15">
-        <v>2869</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+        <v>2869.0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" dyDescent="0.2">
       <c r="A16">
         <v>2</v>
       </c>
       <c r="B16" s="8">
         <v>8</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" t="s" s="2">
         <v>51</v>
       </c>
-      <c r="D16" s="1" t="s">
-        <v>57</v>
+      <c r="D16" t="s" s="1">
+        <v>60</v>
       </c>
       <c r="E16">
-        <v>55</v>
+        <v>339.0</v>
       </c>
       <c r="F16">
-        <v>40</v>
+        <v>359.0</v>
       </c>
       <c r="G16">
-        <v>8</v>
+        <v>71.8</v>
       </c>
       <c r="H16">
-        <v>6.9</v>
+        <v>4.7</v>
       </c>
       <c r="I16">
-        <v>760</v>
+        <v>6821.0</v>
       </c>
       <c r="J16">
-        <v>548</v>
+        <v>3117.0</v>
       </c>
       <c r="K16">
-        <v>1308</v>
+        <v>9938.0</v>
       </c>
       <c r="L16">
-        <v>760</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+        <v>6821.0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" dyDescent="0.2">
       <c r="A17">
         <v>2</v>
       </c>
       <c r="B17" s="8">
         <v>9</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" t="s" s="2">
         <v>51</v>
       </c>
-      <c r="D17" s="1" t="s">
-        <v>58</v>
+      <c r="D17" t="s" s="1">
+        <v>59</v>
       </c>
       <c r="E17">
-        <v>38</v>
+        <v>87.0</v>
       </c>
       <c r="F17">
-        <v>26</v>
+        <v>76.0</v>
       </c>
       <c r="G17">
-        <v>5.2</v>
+        <v>15.2</v>
       </c>
       <c r="H17">
-        <v>7.3</v>
+        <v>5.7</v>
       </c>
       <c r="I17">
-        <v>494</v>
+        <v>1444.0</v>
       </c>
       <c r="J17">
-        <v>383</v>
+        <v>838.0</v>
       </c>
       <c r="K17">
-        <v>877</v>
+        <v>2282.0</v>
       </c>
       <c r="L17">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+        <v>1444.0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" dyDescent="0.2">
       <c r="A18">
         <v>2</v>
       </c>
       <c r="B18" s="8">
         <v>10</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" t="s" s="2">
         <v>51</v>
       </c>
-      <c r="D18" s="1" t="s">
-        <v>59</v>
+      <c r="D18" t="s" s="1">
+        <v>61</v>
       </c>
       <c r="E18">
-        <v>205</v>
+        <v>218.0</v>
       </c>
       <c r="F18">
-        <v>196</v>
+        <v>217.0</v>
       </c>
       <c r="G18">
-        <v>39.200000000000003</v>
+        <v>43.4</v>
       </c>
       <c r="H18">
-        <v>5.2</v>
+        <v>5.0</v>
       </c>
       <c r="I18">
-        <v>3724</v>
+        <v>4123.0</v>
       </c>
       <c r="J18">
-        <v>1934</v>
+        <v>2037.0</v>
       </c>
       <c r="K18">
-        <v>5658</v>
+        <v>6160.0</v>
       </c>
       <c r="L18">
-        <v>3724</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+        <v>4123.0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" dyDescent="0.2">
       <c r="A19">
         <v>3</v>
       </c>
       <c r="B19" s="8">
         <v>4</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" t="s" s="2">
         <v>52</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="D19" t="s" s="1">
         <v>53</v>
       </c>
       <c r="E19">
-        <v>215</v>
+        <v>215.0</v>
       </c>
       <c r="F19">
-        <v>77</v>
+        <v>77.0</v>
       </c>
       <c r="G19">
         <v>15.4</v>
       </c>
       <c r="H19">
-        <v>14</v>
+        <v>14.0</v>
       </c>
       <c r="I19">
-        <v>1463</v>
+        <v>1463.0</v>
       </c>
       <c r="J19">
-        <v>2329</v>
+        <v>2329.0</v>
       </c>
       <c r="K19">
-        <v>3792</v>
+        <v>3792.0</v>
       </c>
       <c r="L19">
-        <v>2329</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+        <v>2329.0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" dyDescent="0.2">
       <c r="A20">
         <v>3</v>
       </c>
       <c r="B20" s="8">
         <v>5</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C20" t="s" s="2">
         <v>52</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="D20" t="s" s="1">
         <v>54</v>
       </c>
       <c r="E20">
-        <v>113</v>
+        <v>113.0</v>
       </c>
       <c r="F20">
-        <v>63</v>
+        <v>63.0</v>
       </c>
       <c r="G20">
         <v>12.6</v>
       </c>
       <c r="H20">
-        <v>9</v>
+        <v>9.0</v>
       </c>
       <c r="I20">
-        <v>1197</v>
+        <v>1197.0</v>
       </c>
       <c r="J20">
-        <v>1171</v>
+        <v>1171.0</v>
       </c>
       <c r="K20">
-        <v>2368</v>
+        <v>2368.0</v>
       </c>
       <c r="L20">
-        <v>1197</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+        <v>1197.0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" dyDescent="0.2">
       <c r="A21">
         <v>3</v>
       </c>
       <c r="B21" s="8">
         <v>6</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C21" t="s" s="2">
         <v>52</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="D21" t="s" s="1">
         <v>55</v>
       </c>
       <c r="E21">
-        <v>192</v>
+        <v>192.0</v>
       </c>
       <c r="F21">
-        <v>126</v>
+        <v>126.0</v>
       </c>
       <c r="G21">
         <v>25.2</v>
@@ -1700,36 +1703,36 @@
         <v>7.6</v>
       </c>
       <c r="I21">
-        <v>2394</v>
+        <v>2394.0</v>
       </c>
       <c r="J21">
-        <v>1946</v>
+        <v>1946.0</v>
       </c>
       <c r="K21">
-        <v>4340</v>
+        <v>4340.0</v>
       </c>
       <c r="L21">
-        <v>2394</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+        <v>2394.0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" dyDescent="0.2">
       <c r="A22">
         <v>3</v>
       </c>
       <c r="B22" s="8">
         <v>7</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C22" t="s" s="2">
         <v>52</v>
       </c>
-      <c r="D22" s="11" t="s">
+      <c r="D22" t="s" s="11">
         <v>56</v>
       </c>
       <c r="E22">
-        <v>250</v>
+        <v>250.0</v>
       </c>
       <c r="F22">
-        <v>167</v>
+        <v>167.0</v>
       </c>
       <c r="G22">
         <v>33.4</v>
@@ -1738,796 +1741,796 @@
         <v>7.5</v>
       </c>
       <c r="I22">
-        <v>3173</v>
+        <v>3173.0</v>
       </c>
       <c r="J22">
-        <v>2527</v>
+        <v>2527.0</v>
       </c>
       <c r="K22">
-        <v>5700</v>
+        <v>5700.0</v>
       </c>
       <c r="L22">
-        <v>3173</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+        <v>3173.0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" dyDescent="0.2">
       <c r="A23">
         <v>3</v>
       </c>
       <c r="B23" s="8">
         <v>8</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C23" t="s" s="2">
         <v>52</v>
       </c>
-      <c r="D23" s="1" t="s">
-        <v>57</v>
+      <c r="D23" t="s" s="1">
+        <v>60</v>
       </c>
       <c r="E23">
-        <v>130</v>
+        <v>234.0</v>
       </c>
       <c r="F23">
-        <v>97</v>
+        <v>230.0</v>
       </c>
       <c r="G23">
-        <v>19.399999999999999</v>
+        <v>46.0</v>
       </c>
       <c r="H23">
-        <v>6.7</v>
+        <v>5.1</v>
       </c>
       <c r="I23">
-        <v>1843</v>
+        <v>4370.0</v>
       </c>
       <c r="J23">
-        <v>1290</v>
+        <v>2193.0</v>
       </c>
       <c r="K23">
-        <v>3133</v>
+        <v>6563.0</v>
       </c>
       <c r="L23">
-        <v>1843</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+        <v>4370.0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" dyDescent="0.2">
       <c r="A24">
         <v>3</v>
       </c>
       <c r="B24" s="8">
         <v>9</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C24" t="s" s="2">
         <v>52</v>
       </c>
-      <c r="D24" s="1" t="s">
-        <v>58</v>
+      <c r="D24" t="s" s="1">
+        <v>59</v>
       </c>
       <c r="E24">
-        <v>142</v>
+        <v>217.0</v>
       </c>
       <c r="F24">
-        <v>105</v>
+        <v>138.0</v>
       </c>
       <c r="G24">
-        <v>21</v>
+        <v>27.6</v>
       </c>
       <c r="H24">
-        <v>6.8</v>
+        <v>7.9</v>
       </c>
       <c r="I24">
-        <v>1995</v>
+        <v>2622.0</v>
       </c>
       <c r="J24">
-        <v>1412</v>
+        <v>2210.0</v>
       </c>
       <c r="K24">
-        <v>3407</v>
+        <v>4832.0</v>
       </c>
       <c r="L24">
-        <v>1995</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+        <v>2622.0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" dyDescent="0.2">
       <c r="A25">
         <v>3</v>
       </c>
       <c r="B25" s="8">
         <v>10</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C25" t="s" s="2">
         <v>52</v>
       </c>
-      <c r="D25" s="1" t="s">
-        <v>59</v>
+      <c r="D25" t="s" s="1">
+        <v>61</v>
       </c>
       <c r="E25">
-        <v>89</v>
+        <v>108.0</v>
       </c>
       <c r="F25">
-        <v>68</v>
+        <v>92.0</v>
       </c>
       <c r="G25">
-        <v>13.6</v>
+        <v>18.4</v>
       </c>
       <c r="H25">
-        <v>6.5</v>
+        <v>5.9</v>
       </c>
       <c r="I25">
-        <v>1292</v>
+        <v>1748.0</v>
       </c>
       <c r="J25">
-        <v>880</v>
+        <v>1045.0</v>
       </c>
       <c r="K25">
-        <v>2172</v>
+        <v>2793.0</v>
       </c>
       <c r="L25">
-        <v>1292</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+        <v>1748.0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" dyDescent="0.2">
       <c r="A26">
         <v>4</v>
       </c>
       <c r="B26" s="8">
         <v>5</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="C26" t="s" s="1">
         <v>53</v>
       </c>
-      <c r="D26" s="1" t="s">
+      <c r="D26" t="s" s="1">
         <v>54</v>
       </c>
       <c r="E26">
-        <v>130</v>
+        <v>130.0</v>
       </c>
       <c r="F26">
-        <v>93</v>
+        <v>93.0</v>
       </c>
       <c r="G26">
-        <v>18.600000000000001</v>
+        <v>18.6</v>
       </c>
       <c r="H26">
-        <v>7</v>
+        <v>7.0</v>
       </c>
       <c r="I26">
-        <v>1767</v>
+        <v>1767.0</v>
       </c>
       <c r="J26">
-        <v>1300</v>
+        <v>1300.0</v>
       </c>
       <c r="K26">
-        <v>3067</v>
+        <v>3067.0</v>
       </c>
       <c r="L26">
-        <v>1767</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+        <v>1767.0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" dyDescent="0.2">
       <c r="A27">
         <v>4</v>
       </c>
       <c r="B27" s="8">
         <v>6</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="C27" t="s" s="1">
         <v>53</v>
       </c>
-      <c r="D27" s="1" t="s">
+      <c r="D27" t="s" s="1">
         <v>55</v>
       </c>
       <c r="E27">
-        <v>149</v>
+        <v>149.0</v>
       </c>
       <c r="F27">
-        <v>161</v>
+        <v>161.0</v>
       </c>
       <c r="G27">
-        <v>32.200000000000003</v>
+        <v>32.2</v>
       </c>
       <c r="H27">
-        <v>4.5999999999999996</v>
+        <v>4.6</v>
       </c>
       <c r="I27">
-        <v>3059</v>
+        <v>3059.0</v>
       </c>
       <c r="J27">
-        <v>1363</v>
+        <v>1363.0</v>
       </c>
       <c r="K27">
-        <v>4422</v>
+        <v>4422.0</v>
       </c>
       <c r="L27">
-        <v>3059</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+        <v>3059.0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" dyDescent="0.2">
       <c r="A28">
         <v>4</v>
       </c>
       <c r="B28" s="8">
         <v>7</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="C28" t="s" s="1">
         <v>53</v>
       </c>
-      <c r="D28" s="11" t="s">
+      <c r="D28" t="s" s="11">
         <v>56</v>
       </c>
       <c r="E28">
-        <v>93</v>
+        <v>93.0</v>
       </c>
       <c r="F28">
-        <v>90</v>
+        <v>90.0</v>
       </c>
       <c r="G28">
-        <v>18</v>
+        <v>18.0</v>
       </c>
       <c r="H28">
         <v>5.2</v>
       </c>
       <c r="I28">
-        <v>1710</v>
+        <v>1710.0</v>
       </c>
       <c r="J28">
-        <v>875</v>
+        <v>875.0</v>
       </c>
       <c r="K28">
-        <v>2585</v>
+        <v>2585.0</v>
       </c>
       <c r="L28">
-        <v>1710</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+        <v>1710.0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" dyDescent="0.2">
       <c r="A29">
         <v>4</v>
       </c>
       <c r="B29" s="8">
         <v>8</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="C29" t="s" s="1">
         <v>53</v>
       </c>
-      <c r="D29" s="1" t="s">
-        <v>57</v>
+      <c r="D29" t="s" s="1">
+        <v>60</v>
       </c>
       <c r="E29">
-        <v>97</v>
+        <v>380.0</v>
       </c>
       <c r="F29">
-        <v>97</v>
+        <v>290.0</v>
       </c>
       <c r="G29">
-        <v>19.399999999999999</v>
+        <v>58.0</v>
       </c>
       <c r="H29">
-        <v>5</v>
+        <v>6.6</v>
       </c>
       <c r="I29">
-        <v>1843</v>
+        <v>5510.0</v>
       </c>
       <c r="J29">
-        <v>905</v>
+        <v>3757.0</v>
       </c>
       <c r="K29">
-        <v>2748</v>
+        <v>9267.0</v>
       </c>
       <c r="L29">
-        <v>1843</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+        <v>5510.0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" dyDescent="0.2">
       <c r="A30">
         <v>4</v>
       </c>
       <c r="B30" s="8">
         <v>9</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="C30" t="s" s="1">
         <v>53</v>
       </c>
-      <c r="D30" s="1" t="s">
-        <v>58</v>
+      <c r="D30" t="s" s="1">
+        <v>59</v>
       </c>
       <c r="E30">
-        <v>76</v>
+        <v>87.0</v>
       </c>
       <c r="F30">
-        <v>91</v>
+        <v>75.0</v>
       </c>
       <c r="G30">
-        <v>18.2</v>
+        <v>15.0</v>
       </c>
       <c r="H30">
-        <v>4.2</v>
+        <v>5.8</v>
       </c>
       <c r="I30">
-        <v>1729</v>
+        <v>1425.0</v>
       </c>
       <c r="J30">
-        <v>674</v>
+        <v>840.0</v>
       </c>
       <c r="K30">
-        <v>2403</v>
+        <v>2265.0</v>
       </c>
       <c r="L30">
-        <v>1729</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+        <v>1425.0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" dyDescent="0.2">
       <c r="A31">
         <v>4</v>
       </c>
       <c r="B31" s="8">
         <v>10</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C31" t="s" s="1">
         <v>53</v>
       </c>
-      <c r="D31" s="1" t="s">
-        <v>59</v>
+      <c r="D31" t="s" s="1">
+        <v>61</v>
       </c>
       <c r="E31">
-        <v>246</v>
+        <v>259.0</v>
       </c>
       <c r="F31">
-        <v>110</v>
+        <v>125.0</v>
       </c>
       <c r="G31">
-        <v>22</v>
+        <v>25.0</v>
       </c>
       <c r="H31">
-        <v>11.2</v>
+        <v>10.4</v>
       </c>
       <c r="I31">
-        <v>2090</v>
+        <v>2375.0</v>
       </c>
       <c r="J31">
-        <v>2613</v>
+        <v>2730.0</v>
       </c>
       <c r="K31">
-        <v>4703</v>
+        <v>5105.0</v>
       </c>
       <c r="L31">
-        <v>2613</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+        <v>2730.0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" dyDescent="0.2">
       <c r="A32">
         <v>5</v>
       </c>
       <c r="B32" s="8">
         <v>6</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="C32" t="s" s="1">
         <v>54</v>
       </c>
-      <c r="D32" s="1" t="s">
+      <c r="D32" t="s" s="1">
         <v>55</v>
       </c>
       <c r="E32">
-        <v>110</v>
+        <v>110.0</v>
       </c>
       <c r="F32">
-        <v>70</v>
+        <v>70.0</v>
       </c>
       <c r="G32">
-        <v>14</v>
+        <v>14.0</v>
       </c>
       <c r="H32">
         <v>7.9</v>
       </c>
       <c r="I32">
-        <v>1330</v>
+        <v>1330.0</v>
       </c>
       <c r="J32">
-        <v>1120</v>
+        <v>1120.0</v>
       </c>
       <c r="K32">
-        <v>2450</v>
+        <v>2450.0</v>
       </c>
       <c r="L32">
-        <v>1330</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+        <v>1330.0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" dyDescent="0.2">
       <c r="A33" s="10">
         <v>5</v>
       </c>
       <c r="B33" s="8">
         <v>7</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C33" t="s" s="1">
         <v>54</v>
       </c>
-      <c r="D33" s="11" t="s">
+      <c r="D33" t="s" s="11">
         <v>56</v>
       </c>
       <c r="E33">
-        <v>168</v>
+        <v>168.0</v>
       </c>
       <c r="F33">
-        <v>173</v>
+        <v>173.0</v>
       </c>
       <c r="G33">
         <v>34.6</v>
       </c>
       <c r="H33">
-        <v>4.9000000000000004</v>
+        <v>4.9</v>
       </c>
       <c r="I33">
-        <v>3287</v>
+        <v>3287.0</v>
       </c>
       <c r="J33">
-        <v>1556</v>
+        <v>1556.0</v>
       </c>
       <c r="K33">
-        <v>4843</v>
+        <v>4843.0</v>
       </c>
       <c r="L33">
-        <v>3287</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+        <v>3287.0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" dyDescent="0.2">
       <c r="A34">
         <v>5</v>
       </c>
       <c r="B34" s="8">
         <v>8</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="C34" t="s" s="1">
         <v>54</v>
       </c>
-      <c r="D34" s="1" t="s">
-        <v>57</v>
+      <c r="D34" t="s" s="1">
+        <v>60</v>
       </c>
       <c r="E34">
-        <v>48</v>
+        <v>279.0</v>
       </c>
       <c r="F34">
-        <v>40</v>
+        <v>281.0</v>
       </c>
       <c r="G34">
-        <v>8</v>
+        <v>56.2</v>
       </c>
       <c r="H34">
-        <v>6</v>
+        <v>5.0</v>
       </c>
       <c r="I34">
-        <v>760</v>
+        <v>5339.0</v>
       </c>
       <c r="J34">
-        <v>467</v>
+        <v>2599.0</v>
       </c>
       <c r="K34">
-        <v>1227</v>
+        <v>7938.0</v>
       </c>
       <c r="L34">
-        <v>760</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+        <v>5339.0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" dyDescent="0.2">
       <c r="A35">
         <v>5</v>
       </c>
       <c r="B35" s="8">
         <v>9</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="C35" t="s" s="1">
         <v>54</v>
       </c>
-      <c r="D35" s="1" t="s">
-        <v>58</v>
+      <c r="D35" t="s" s="1">
+        <v>59</v>
       </c>
       <c r="E35">
-        <v>60</v>
+        <v>136.0</v>
       </c>
       <c r="F35">
-        <v>55</v>
+        <v>118.0</v>
       </c>
       <c r="G35">
-        <v>11</v>
+        <v>23.6</v>
       </c>
       <c r="H35">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="I35">
-        <v>1045</v>
+        <v>2242.0</v>
       </c>
       <c r="J35">
-        <v>572</v>
+        <v>1311.0</v>
       </c>
       <c r="K35">
-        <v>1617</v>
+        <v>3553.0</v>
       </c>
       <c r="L35">
-        <v>1045</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+        <v>2242.0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" dyDescent="0.2">
       <c r="A36">
         <v>5</v>
       </c>
       <c r="B36" s="8">
         <v>10</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="C36" t="s" s="1">
         <v>54</v>
       </c>
-      <c r="D36" s="1" t="s">
-        <v>59</v>
+      <c r="D36" t="s" s="1">
+        <v>61</v>
       </c>
       <c r="E36">
-        <v>145</v>
+        <v>158.0</v>
       </c>
       <c r="F36">
-        <v>131</v>
+        <v>155.0</v>
       </c>
       <c r="G36">
-        <v>26.2</v>
+        <v>31.0</v>
       </c>
       <c r="H36">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="I36">
-        <v>2489</v>
+        <v>2945.0</v>
       </c>
       <c r="J36">
-        <v>1386</v>
+        <v>1482.0</v>
       </c>
       <c r="K36">
-        <v>3875</v>
+        <v>4427.0</v>
       </c>
       <c r="L36">
-        <v>2489</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+        <v>2945.0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" dyDescent="0.2">
       <c r="A37">
         <v>6</v>
       </c>
       <c r="B37" s="8">
         <v>7</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="C37" t="s" s="1">
         <v>55</v>
       </c>
-      <c r="D37" s="11" t="s">
+      <c r="D37" t="s" s="11">
         <v>56</v>
       </c>
       <c r="E37">
-        <v>185</v>
+        <v>185.0</v>
       </c>
       <c r="F37">
-        <v>232</v>
+        <v>232.0</v>
       </c>
       <c r="G37">
         <v>46.4</v>
       </c>
       <c r="H37">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="I37">
-        <v>4408</v>
+        <v>4408.0</v>
       </c>
       <c r="J37">
-        <v>1617</v>
+        <v>1617.0</v>
       </c>
       <c r="K37">
-        <v>6025</v>
+        <v>6025.0</v>
       </c>
       <c r="L37">
-        <v>4408</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+        <v>4408.0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" dyDescent="0.2">
       <c r="A38">
         <v>6</v>
       </c>
       <c r="B38" s="8">
         <v>8</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="C38" t="s" s="1">
         <v>55</v>
       </c>
-      <c r="D38" s="1" t="s">
-        <v>57</v>
+      <c r="D38" t="s" s="1">
+        <v>60</v>
       </c>
       <c r="E38">
-        <v>77</v>
+        <v>358.0</v>
       </c>
       <c r="F38">
-        <v>72</v>
+        <v>315.0</v>
       </c>
       <c r="G38">
-        <v>14.4</v>
+        <v>63.0</v>
       </c>
       <c r="H38">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="I38">
-        <v>1368</v>
+        <v>5985.0</v>
       </c>
       <c r="J38">
-        <v>730</v>
+        <v>3442.0</v>
       </c>
       <c r="K38">
-        <v>2098</v>
+        <v>9427.0</v>
       </c>
       <c r="L38">
-        <v>1368</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+        <v>5985.0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" dyDescent="0.2">
       <c r="A39">
         <v>6</v>
       </c>
       <c r="B39" s="8">
         <v>9</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="C39" t="s" s="1">
         <v>55</v>
       </c>
-      <c r="D39" s="1" t="s">
-        <v>58</v>
+      <c r="D39" t="s" s="1">
+        <v>59</v>
       </c>
       <c r="E39">
-        <v>78</v>
+        <v>153.0</v>
       </c>
       <c r="F39">
-        <v>89</v>
+        <v>166.0</v>
       </c>
       <c r="G39">
-        <v>17.8</v>
+        <v>33.2</v>
       </c>
       <c r="H39">
-        <v>4.4000000000000004</v>
+        <v>4.6</v>
       </c>
       <c r="I39">
-        <v>1691</v>
+        <v>3154.0</v>
       </c>
       <c r="J39">
-        <v>702</v>
+        <v>1398.0</v>
       </c>
       <c r="K39">
-        <v>2393</v>
+        <v>4552.0</v>
       </c>
       <c r="L39">
-        <v>1691</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+        <v>3154.0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" dyDescent="0.2">
       <c r="A40">
         <v>6</v>
       </c>
       <c r="B40" s="8">
         <v>10</v>
       </c>
-      <c r="C40" s="1" t="s">
+      <c r="C40" t="s" s="1">
         <v>55</v>
       </c>
-      <c r="D40" s="1" t="s">
-        <v>59</v>
+      <c r="D40" t="s" s="1">
+        <v>61</v>
       </c>
       <c r="E40">
-        <v>224</v>
+        <v>237.0</v>
       </c>
       <c r="F40">
-        <v>192</v>
+        <v>216.0</v>
       </c>
       <c r="G40">
-        <v>38.4</v>
+        <v>43.2</v>
       </c>
       <c r="H40">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="I40">
-        <v>3648</v>
+        <v>4104.0</v>
       </c>
       <c r="J40">
-        <v>2165</v>
+        <v>2261.0</v>
       </c>
       <c r="K40">
-        <v>5813</v>
+        <v>6365.0</v>
       </c>
       <c r="L40">
-        <v>3648</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+        <v>4104.0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" dyDescent="0.2">
       <c r="A41">
         <v>7</v>
       </c>
       <c r="B41" s="8">
         <v>8</v>
       </c>
-      <c r="C41" s="1" t="s">
+      <c r="C41" t="s" s="1">
         <v>56</v>
       </c>
-      <c r="D41" s="1" t="s">
-        <v>57</v>
+      <c r="D41" t="s" s="1">
+        <v>60</v>
       </c>
       <c r="E41">
-        <v>131</v>
+        <v>414.0</v>
       </c>
       <c r="F41">
-        <v>160</v>
+        <v>365.0</v>
       </c>
       <c r="G41">
-        <v>32</v>
+        <v>73.0</v>
       </c>
       <c r="H41">
-        <v>4.0999999999999996</v>
+        <v>5.7</v>
       </c>
       <c r="I41">
-        <v>3040</v>
+        <v>6935.0</v>
       </c>
       <c r="J41">
-        <v>1155</v>
+        <v>3978.0</v>
       </c>
       <c r="K41">
-        <v>4195</v>
+        <v>10913.0</v>
       </c>
       <c r="L41">
-        <v>3040</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+        <v>6935.0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" dyDescent="0.2">
       <c r="A42">
         <v>7</v>
       </c>
       <c r="B42" s="8">
         <v>9</v>
       </c>
-      <c r="C42" s="1" t="s">
+      <c r="C42" t="s" s="1">
         <v>56</v>
       </c>
-      <c r="D42" s="1" t="s">
-        <v>58</v>
+      <c r="D42" t="s" s="1">
+        <v>59</v>
       </c>
       <c r="E42">
-        <v>110</v>
+        <v>70.0</v>
       </c>
       <c r="F42">
-        <v>146</v>
+        <v>75.0</v>
       </c>
       <c r="G42">
-        <v>29.2</v>
+        <v>15.0</v>
       </c>
       <c r="H42">
-        <v>3.8</v>
+        <v>4.7</v>
       </c>
       <c r="I42">
-        <v>2774</v>
+        <v>1425.0</v>
       </c>
       <c r="J42">
-        <v>943</v>
+        <v>642.0</v>
       </c>
       <c r="K42">
-        <v>3717</v>
+        <v>2067.0</v>
       </c>
       <c r="L42">
-        <v>2774</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+        <v>1425.0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" dyDescent="0.2">
       <c r="A43">
         <v>7</v>
       </c>
       <c r="B43" s="8">
         <v>10</v>
       </c>
-      <c r="C43" s="1" t="s">
+      <c r="C43" t="s" s="1">
         <v>56</v>
       </c>
-      <c r="D43" s="1" t="s">
-        <v>59</v>
+      <c r="D43" t="s" s="1">
+        <v>57</v>
       </c>
       <c r="E43">
-        <v>280</v>
+        <v>280.0</v>
       </c>
       <c r="F43">
-        <v>187</v>
+        <v>187.0</v>
       </c>
       <c r="G43">
         <v>37.4</v>
@@ -2536,133 +2539,133 @@
         <v>7.5</v>
       </c>
       <c r="I43">
-        <v>3553</v>
+        <v>3553.0</v>
       </c>
       <c r="J43">
-        <v>2830</v>
+        <v>2830.0</v>
       </c>
       <c r="K43">
-        <v>6383</v>
+        <v>6383.0</v>
       </c>
       <c r="L43">
-        <v>3553</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+        <v>3553.0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" dyDescent="0.2">
       <c r="A44">
         <v>8</v>
       </c>
       <c r="B44" s="8">
         <v>9</v>
       </c>
-      <c r="C44" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>58</v>
+      <c r="C44" t="s" s="1">
+        <v>60</v>
+      </c>
+      <c r="D44" t="s" s="1">
+        <v>59</v>
       </c>
       <c r="E44">
-        <v>26</v>
+        <v>384.0</v>
       </c>
       <c r="F44">
-        <v>19</v>
+        <v>363.0</v>
       </c>
       <c r="G44">
-        <v>3.8</v>
+        <v>72.6</v>
       </c>
       <c r="H44">
-        <v>6.8</v>
+        <v>5.3</v>
       </c>
       <c r="I44">
-        <v>361</v>
+        <v>6897.0</v>
       </c>
       <c r="J44">
-        <v>259</v>
+        <v>3633.0</v>
       </c>
       <c r="K44">
-        <v>620</v>
+        <v>10530.0</v>
       </c>
       <c r="L44">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+        <v>6897.0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" dyDescent="0.2">
       <c r="A45">
         <v>8</v>
       </c>
       <c r="B45" s="8">
         <v>10</v>
       </c>
-      <c r="C45" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>59</v>
+      <c r="C45" t="s" s="1">
+        <v>60</v>
+      </c>
+      <c r="D45" t="s" s="1">
+        <v>61</v>
       </c>
       <c r="E45">
-        <v>163</v>
+        <v>209.0</v>
       </c>
       <c r="F45">
-        <v>164</v>
+        <v>172.0</v>
       </c>
       <c r="G45">
-        <v>32.799999999999997</v>
+        <v>34.4</v>
       </c>
       <c r="H45">
-        <v>5</v>
+        <v>6.1</v>
       </c>
       <c r="I45">
-        <v>3116</v>
+        <v>3268.0</v>
       </c>
       <c r="J45">
-        <v>1519</v>
+        <v>2037.0</v>
       </c>
       <c r="K45">
-        <v>4635</v>
+        <v>5305.0</v>
       </c>
       <c r="L45">
-        <v>3116</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+        <v>3268.0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" dyDescent="0.2">
       <c r="A46">
         <v>9</v>
       </c>
       <c r="B46" s="8">
         <v>10</v>
       </c>
-      <c r="C46" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="D46" s="1" t="s">
+      <c r="C46" t="s" s="1">
         <v>59</v>
       </c>
+      <c r="D46" t="s" s="1">
+        <v>61</v>
+      </c>
       <c r="E46">
-        <v>175</v>
+        <v>264.0</v>
       </c>
       <c r="F46">
-        <v>170</v>
+        <v>200.0</v>
       </c>
       <c r="G46">
-        <v>34</v>
+        <v>40.0</v>
       </c>
       <c r="H46">
-        <v>5.0999999999999996</v>
+        <v>6.6</v>
       </c>
       <c r="I46">
-        <v>3230</v>
+        <v>3800.0</v>
       </c>
       <c r="J46">
-        <v>1645</v>
+        <v>2613.0</v>
       </c>
       <c r="K46">
-        <v>4875</v>
+        <v>6413.0</v>
       </c>
       <c r="L46">
-        <v>3230</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+        <v>3800.0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" dyDescent="0.2">
       <c r="A47">
         <v>1</v>
       </c>
@@ -2696,7 +2699,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:16" dyDescent="0.2">
       <c r="A48">
         <v>2</v>
       </c>
@@ -2730,7 +2733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:16" dyDescent="0.2">
       <c r="A49">
         <v>3</v>
       </c>
@@ -2764,7 +2767,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:16" dyDescent="0.2">
       <c r="A50">
         <v>4</v>
       </c>
@@ -2798,7 +2801,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:16" dyDescent="0.2">
       <c r="A51">
         <v>5</v>
       </c>
@@ -2832,7 +2835,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:16" dyDescent="0.2">
       <c r="A52">
         <v>6</v>
       </c>
@@ -2864,7 +2867,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:16" dyDescent="0.2">
       <c r="A53">
         <v>7</v>
       </c>
@@ -2896,7 +2899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:16" dyDescent="0.2">
       <c r="A54">
         <v>8</v>
       </c>
@@ -2928,7 +2931,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:16" dyDescent="0.2">
       <c r="A55">
         <v>9</v>
       </c>
@@ -2960,7 +2963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:16" dyDescent="0.2">
       <c r="A56">
         <v>10</v>
       </c>
@@ -2992,13 +2995,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:16" dyDescent="0.2">
       <c r="G57" s="2"/>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:16" dyDescent="0.2">
       <c r="G58" s="1"/>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:16" dyDescent="0.2">
       <c r="G59" s="1"/>
     </row>
   </sheetData>

--- a/inputData/Parameters.xlsx
+++ b/inputData/Parameters.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kapta\Documents\DTU\Speciale\GitHubFiles\inputData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14C88F75-73F9-431A-9C84-FF9086595067}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{403A04AE-9353-4687-AFDD-C1005F9C0B01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
+    <workbookView xWindow="20" yWindow="740" windowWidth="19180" windowHeight="11260" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
   </bookViews>
   <sheets>
     <sheet name="Parameters" sheetId="9" r:id="rId1"/>
@@ -238,12 +238,14 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF0A0A0A"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -251,6 +253,7 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -272,6 +275,7 @@
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -647,18 +651,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B15C49E0-A7B4-734A-8962-DC2A879F4079}">
   <dimension ref="A1:D20"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="22.625" customWidth="1"/>
-    <col min="2" max="2" width="10.875" style="4"/>
+    <col min="1" max="1" width="22.58203125" customWidth="1"/>
+    <col min="2" max="2" width="10.83203125" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>20</v>
       </c>
@@ -669,7 +673,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -680,7 +684,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>45</v>
       </c>
@@ -691,7 +695,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -702,7 +706,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -713,7 +717,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -724,7 +728,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -736,7 +740,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
         <v>0</v>
       </c>
@@ -747,7 +751,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
         <v>1</v>
       </c>
@@ -758,7 +762,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
         <v>44</v>
       </c>
@@ -769,7 +773,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
         <v>2</v>
       </c>
@@ -780,7 +784,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
         <v>42</v>
       </c>
@@ -791,7 +795,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -803,31 +807,29 @@
         <v>39</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
         <v>4</v>
       </c>
       <c r="B15" s="4">
-        <f>30/B20</f>
         <v>30</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
         <v>5</v>
       </c>
       <c r="B16" s="4">
-        <f>20/B20</f>
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
         <v>6</v>
       </c>
@@ -838,7 +840,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
         <v>41</v>
       </c>
@@ -858,17 +860,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAF0D5EA-53B5-1240-9D84-6FE223856A18}">
   <dimension ref="A1:P59"/>
-  <sheetFormatPr defaultColWidth="10.625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="10.58203125" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" width="17.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="17.125" customWidth="1"/>
-    <col min="5" max="5" width="12.125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.08203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="17.08203125" customWidth="1"/>
+    <col min="5" max="5" width="12.08203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.08203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.08203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A1" s="9" t="s">
         <v>36</v>
       </c>
@@ -913,7 +915,7 @@
       </c>
       <c r="P1" s="6"/>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>1</v>
       </c>
@@ -960,7 +962,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1008,7 +1010,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>1</v>
       </c>
@@ -1052,7 +1054,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>1</v>
       </c>
@@ -1099,7 +1101,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>1</v>
       </c>
@@ -1138,7 +1140,7 @@
       </c>
       <c r="O6" s="4"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>1</v>
       </c>
@@ -1177,7 +1179,7 @@
       </c>
       <c r="O7" s="4"/>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>1</v>
       </c>
@@ -1216,7 +1218,7 @@
       </c>
       <c r="O8" s="4"/>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>1</v>
       </c>
@@ -1255,7 +1257,7 @@
       </c>
       <c r="O9" s="4"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>1</v>
       </c>
@@ -1294,7 +1296,7 @@
       </c>
       <c r="O10" s="4"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>2</v>
       </c>
@@ -1332,7 +1334,7 @@
         <v>2489</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>2</v>
       </c>
@@ -1370,7 +1372,7 @@
         <v>2090</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>2</v>
       </c>
@@ -1408,7 +1410,7 @@
         <v>1520</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>2</v>
       </c>
@@ -1446,7 +1448,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>2</v>
       </c>
@@ -1484,7 +1486,7 @@
         <v>2869</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A16">
         <v>2</v>
       </c>
@@ -1522,7 +1524,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A17">
         <v>2</v>
       </c>
@@ -1560,7 +1562,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A18">
         <v>2</v>
       </c>
@@ -1598,7 +1600,7 @@
         <v>3724</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A19">
         <v>3</v>
       </c>
@@ -1636,7 +1638,7 @@
         <v>2329</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A20">
         <v>3</v>
       </c>
@@ -1674,7 +1676,7 @@
         <v>1197</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A21">
         <v>3</v>
       </c>
@@ -1712,7 +1714,7 @@
         <v>2394</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A22">
         <v>3</v>
       </c>
@@ -1750,7 +1752,7 @@
         <v>3173</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A23">
         <v>3</v>
       </c>
@@ -1788,7 +1790,7 @@
         <v>1843</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A24">
         <v>3</v>
       </c>
@@ -1826,7 +1828,7 @@
         <v>1995</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A25">
         <v>3</v>
       </c>
@@ -1864,7 +1866,7 @@
         <v>1292</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A26">
         <v>4</v>
       </c>
@@ -1902,7 +1904,7 @@
         <v>1767</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A27">
         <v>4</v>
       </c>
@@ -1940,7 +1942,7 @@
         <v>3059</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A28">
         <v>4</v>
       </c>
@@ -1978,7 +1980,7 @@
         <v>1710</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A29">
         <v>4</v>
       </c>
@@ -2016,7 +2018,7 @@
         <v>1843</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A30">
         <v>4</v>
       </c>
@@ -2054,7 +2056,7 @@
         <v>1729</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A31">
         <v>4</v>
       </c>
@@ -2092,7 +2094,7 @@
         <v>2613</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A32">
         <v>5</v>
       </c>
@@ -2130,7 +2132,7 @@
         <v>1330</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A33" s="10">
         <v>5</v>
       </c>
@@ -2168,7 +2170,7 @@
         <v>3287</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A34">
         <v>5</v>
       </c>
@@ -2206,7 +2208,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A35">
         <v>5</v>
       </c>
@@ -2244,7 +2246,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A36">
         <v>5</v>
       </c>
@@ -2282,7 +2284,7 @@
         <v>2489</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A37">
         <v>6</v>
       </c>
@@ -2320,7 +2322,7 @@
         <v>4408</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A38">
         <v>6</v>
       </c>
@@ -2358,7 +2360,7 @@
         <v>1368</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A39">
         <v>6</v>
       </c>
@@ -2396,7 +2398,7 @@
         <v>1691</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A40">
         <v>6</v>
       </c>
@@ -2434,7 +2436,7 @@
         <v>3648</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A41">
         <v>7</v>
       </c>
@@ -2472,7 +2474,7 @@
         <v>3040</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A42">
         <v>7</v>
       </c>
@@ -2510,7 +2512,7 @@
         <v>2774</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A43">
         <v>7</v>
       </c>
@@ -2548,7 +2550,7 @@
         <v>3553</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A44">
         <v>8</v>
       </c>
@@ -2586,7 +2588,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A45">
         <v>8</v>
       </c>
@@ -2624,7 +2626,7 @@
         <v>3116</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A46">
         <v>9</v>
       </c>
@@ -2662,7 +2664,7 @@
         <v>3230</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A47">
         <v>1</v>
       </c>
@@ -2696,7 +2698,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A48">
         <v>2</v>
       </c>
@@ -2730,7 +2732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A49">
         <v>3</v>
       </c>
@@ -2764,7 +2766,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A50">
         <v>4</v>
       </c>
@@ -2798,7 +2800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A51">
         <v>5</v>
       </c>
@@ -2832,7 +2834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A52">
         <v>6</v>
       </c>
@@ -2864,7 +2866,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A53">
         <v>7</v>
       </c>
@@ -2896,7 +2898,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A54">
         <v>8</v>
       </c>
@@ -2928,7 +2930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A55">
         <v>9</v>
       </c>
@@ -2960,7 +2962,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A56">
         <v>10</v>
       </c>
@@ -2992,13 +2994,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.4">
       <c r="G57" s="2"/>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.4">
       <c r="G58" s="1"/>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.4">
       <c r="G59" s="1"/>
     </row>
   </sheetData>

--- a/inputData/Parameters.xlsx
+++ b/inputData/Parameters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sillewiberg/Desktop/Skole/Speciale/Master-Thesis-eVTOL-1/inputData/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{760003B1-6592-C542-B4ED-E39B117D197F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5E5E19C-E433-3D4B-B2DE-3F609C62E196}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14320" yWindow="500" windowWidth="14480" windowHeight="16340" activeTab="1" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="61">
   <si>
     <t>cap_u</t>
   </si>
@@ -208,9 +208,6 @@
   </si>
   <si>
     <t>(57.019081, 9.957817)</t>
-  </si>
-  <si>
-    <t>(55.924974, 12.265524)</t>
   </si>
   <si>
     <t>penalty for exceeding bmid</t>
@@ -791,7 +788,7 @@
         <v>20</v>
       </c>
       <c r="D13" t="s" s="3">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="14" spans="1:4" dyDescent="0.2">
@@ -1191,7 +1188,7 @@
         <v>50</v>
       </c>
       <c r="D8" t="s" s="1">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E8">
         <v>156.0</v>
@@ -1230,7 +1227,7 @@
         <v>50</v>
       </c>
       <c r="D9" t="s" s="1">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E9">
         <v>230.0</v>
@@ -1269,7 +1266,7 @@
         <v>50</v>
       </c>
       <c r="D10" t="s" s="1">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E10">
         <v>56.0</v>
@@ -1498,7 +1495,7 @@
         <v>51</v>
       </c>
       <c r="D16" t="s" s="1">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E16">
         <v>339.0</v>
@@ -1536,7 +1533,7 @@
         <v>51</v>
       </c>
       <c r="D17" t="s" s="1">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E17">
         <v>87.0</v>
@@ -1574,7 +1571,7 @@
         <v>51</v>
       </c>
       <c r="D18" t="s" s="1">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E18">
         <v>218.0</v>
@@ -1764,7 +1761,7 @@
         <v>52</v>
       </c>
       <c r="D23" t="s" s="1">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E23">
         <v>234.0</v>
@@ -1802,7 +1799,7 @@
         <v>52</v>
       </c>
       <c r="D24" t="s" s="1">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E24">
         <v>217.0</v>
@@ -1840,7 +1837,7 @@
         <v>52</v>
       </c>
       <c r="D25" t="s" s="1">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E25">
         <v>108.0</v>
@@ -1992,7 +1989,7 @@
         <v>53</v>
       </c>
       <c r="D29" t="s" s="1">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E29">
         <v>380.0</v>
@@ -2030,7 +2027,7 @@
         <v>53</v>
       </c>
       <c r="D30" t="s" s="1">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E30">
         <v>87.0</v>
@@ -2068,7 +2065,7 @@
         <v>53</v>
       </c>
       <c r="D31" t="s" s="1">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E31">
         <v>259.0</v>
@@ -2182,7 +2179,7 @@
         <v>54</v>
       </c>
       <c r="D34" t="s" s="1">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E34">
         <v>279.0</v>
@@ -2220,7 +2217,7 @@
         <v>54</v>
       </c>
       <c r="D35" t="s" s="1">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E35">
         <v>136.0</v>
@@ -2258,7 +2255,7 @@
         <v>54</v>
       </c>
       <c r="D36" t="s" s="1">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E36">
         <v>158.0</v>
@@ -2334,7 +2331,7 @@
         <v>55</v>
       </c>
       <c r="D38" t="s" s="1">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E38">
         <v>358.0</v>
@@ -2372,7 +2369,7 @@
         <v>55</v>
       </c>
       <c r="D39" t="s" s="1">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E39">
         <v>153.0</v>
@@ -2410,7 +2407,7 @@
         <v>55</v>
       </c>
       <c r="D40" t="s" s="1">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E40">
         <v>237.0</v>
@@ -2448,7 +2445,7 @@
         <v>56</v>
       </c>
       <c r="D41" t="s" s="1">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E41">
         <v>414.0</v>
@@ -2486,7 +2483,7 @@
         <v>56</v>
       </c>
       <c r="D42" t="s" s="1">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E42">
         <v>70.0</v>
@@ -2524,31 +2521,31 @@
         <v>56</v>
       </c>
       <c r="D43" t="s" s="1">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E43">
-        <v>280.0</v>
+        <v>293.0</v>
       </c>
       <c r="F43">
-        <v>187.0</v>
+        <v>194.0</v>
       </c>
       <c r="G43">
-        <v>37.4</v>
+        <v>38.8</v>
       </c>
       <c r="H43">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="I43">
-        <v>3553.0</v>
+        <v>3686.0</v>
       </c>
       <c r="J43">
-        <v>2830.0</v>
+        <v>2966.0</v>
       </c>
       <c r="K43">
-        <v>6383.0</v>
+        <v>6652.0</v>
       </c>
       <c r="L43">
-        <v>3553.0</v>
+        <v>3686.0</v>
       </c>
     </row>
     <row r="44" spans="1:16" dyDescent="0.2">
@@ -2559,10 +2556,10 @@
         <v>9</v>
       </c>
       <c r="C44" t="s" s="1">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D44" t="s" s="1">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E44">
         <v>384.0</v>
@@ -2597,10 +2594,10 @@
         <v>10</v>
       </c>
       <c r="C45" t="s" s="1">
+        <v>59</v>
+      </c>
+      <c r="D45" t="s" s="1">
         <v>60</v>
-      </c>
-      <c r="D45" t="s" s="1">
-        <v>61</v>
       </c>
       <c r="E45">
         <v>209.0</v>
@@ -2635,10 +2632,10 @@
         <v>10</v>
       </c>
       <c r="C46" t="s" s="1">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D46" t="s" s="1">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E46">
         <v>264.0</v>

--- a/inputData/Parameters.xlsx
+++ b/inputData/Parameters.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kapta\Documents\DTU\Speciale\GitHubFiles\inputData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sillewiberg/Desktop/Skole/Speciale/Master-Thesis-eVTOL-1/inputData/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{403A04AE-9353-4687-AFDD-C1005F9C0B01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5E5E19C-E433-3D4B-B2DE-3F609C62E196}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="740" windowWidth="19180" windowHeight="11260" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
+    <workbookView xWindow="14320" yWindow="500" windowWidth="14480" windowHeight="16340" activeTab="1" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
   </bookViews>
   <sheets>
     <sheet name="Parameters" sheetId="9" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="61">
   <si>
     <t>cap_u</t>
   </si>
@@ -210,16 +210,16 @@
     <t>(57.019081, 9.957817)</t>
   </si>
   <si>
-    <t>(55.581790, 9.722994)</t>
-  </si>
-  <si>
-    <t>(55.726059, 9.574035)</t>
-  </si>
-  <si>
-    <t>(55.924974, 12.265524)</t>
-  </si>
-  <si>
     <t>penalty for exceeding bmid</t>
+  </si>
+  <si>
+    <t>(56.408780, 9.417814)</t>
+  </si>
+  <si>
+    <t>(55.088776, 14.721890)</t>
+  </si>
+  <si>
+    <t>(56.049305, 12.584406)</t>
   </si>
 </sst>
 </file>
@@ -238,14 +238,12 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF0A0A0A"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -253,7 +251,6 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -275,7 +272,6 @@
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -651,19 +647,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B15C49E0-A7B4-734A-8962-DC2A879F4079}">
   <dimension ref="A1:D20"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="22.58203125" customWidth="1"/>
+    <col min="1" max="1" width="22.6640625" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:4" dyDescent="0.2">
       <c r="A1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:4" dyDescent="0.2">
+      <c r="A2" t="s" s="1">
         <v>20</v>
       </c>
       <c r="B2" s="4">
@@ -673,7 +669,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:4" dyDescent="0.2">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -684,7 +680,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:4" dyDescent="0.2">
       <c r="A4" t="s">
         <v>45</v>
       </c>
@@ -695,7 +691,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:4" dyDescent="0.2">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -706,7 +702,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:4" dyDescent="0.2">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -717,7 +713,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:4" dyDescent="0.2">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -728,7 +724,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:4" dyDescent="0.2">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -740,7 +736,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:4" dyDescent="0.2">
       <c r="A9" t="s">
         <v>0</v>
       </c>
@@ -751,7 +747,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:4" dyDescent="0.2">
       <c r="A10" t="s">
         <v>1</v>
       </c>
@@ -762,7 +758,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:4" dyDescent="0.2">
       <c r="A11" t="s">
         <v>44</v>
       </c>
@@ -773,7 +769,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:4" dyDescent="0.2">
       <c r="A12" t="s">
         <v>2</v>
       </c>
@@ -784,18 +780,18 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:4" dyDescent="0.2">
       <c r="A13" t="s">
         <v>42</v>
       </c>
       <c r="B13" s="4">
         <v>20</v>
       </c>
-      <c r="D13" s="3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="D13" t="s" s="3">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" dyDescent="0.2">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -803,51 +799,53 @@
         <f>2.11*B20</f>
         <v>2.11</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" t="s" s="3">
         <v>39</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:4" dyDescent="0.2">
       <c r="A15" t="s">
         <v>4</v>
       </c>
       <c r="B15" s="4">
+        <f>30/B20</f>
         <v>30</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="D15" t="s" s="3">
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:4" dyDescent="0.2">
       <c r="A16" t="s">
         <v>5</v>
       </c>
       <c r="B16" s="4">
-        <v>30</v>
-      </c>
-      <c r="D16" s="3" t="s">
+        <f>20/B20</f>
+        <v>20</v>
+      </c>
+      <c r="D16" t="s" s="3">
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:4" dyDescent="0.2">
       <c r="A17" t="s">
         <v>6</v>
       </c>
       <c r="B17" s="4">
-        <v>780</v>
-      </c>
-      <c r="D17" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D17" t="s" s="3">
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:4" dyDescent="0.2">
       <c r="A20" t="s">
         <v>41</v>
       </c>
       <c r="B20" s="4">
         <v>1</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="D20" t="s" s="3">
         <v>47</v>
       </c>
     </row>
@@ -860,54 +858,54 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAF0D5EA-53B5-1240-9D84-6FE223856A18}">
   <dimension ref="A1:P59"/>
-  <sheetFormatPr defaultColWidth="10.58203125" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="17.08203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="17.08203125" customWidth="1"/>
-    <col min="5" max="5" width="12.08203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="17.1640625" customWidth="1"/>
+    <col min="5" max="5" width="12.1640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.08203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.08203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:16" dyDescent="0.2">
+      <c r="A1" t="s" s="9">
         <v>36</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" t="s" s="5">
         <v>37</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" t="s" s="5">
         <v>48</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" t="s" s="5">
         <v>49</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" t="s" s="5">
         <v>22</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" t="s" s="5">
         <v>23</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" t="s" s="5">
         <v>24</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" t="s" s="5">
         <v>25</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" t="s" s="5">
         <v>26</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" t="s" s="5">
         <v>27</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="K1" t="s" s="5">
         <v>38</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="L1" t="s" s="5">
         <v>28</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="N1" t="s" s="6">
         <v>19</v>
       </c>
       <c r="O1" s="7">
@@ -915,24 +913,24 @@
       </c>
       <c r="P1" s="6"/>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:16" dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" s="8">
         <v>2</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" t="s" s="1">
         <v>50</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" t="s" s="2">
         <v>51</v>
       </c>
       <c r="E2">
-        <v>185</v>
+        <v>185.0</v>
       </c>
       <c r="F2">
-        <v>219</v>
+        <v>219.0</v>
       </c>
       <c r="G2">
         <v>43.8</v>
@@ -941,16 +939,16 @@
         <v>4.2</v>
       </c>
       <c r="I2">
-        <v>4161</v>
+        <v>4161.0</v>
       </c>
       <c r="J2">
-        <v>1647</v>
+        <v>1647.0</v>
       </c>
       <c r="K2">
-        <v>5808</v>
+        <v>5808.0</v>
       </c>
       <c r="L2">
-        <v>4161</v>
+        <v>4161.0</v>
       </c>
       <c r="N2" t="s">
         <v>29</v>
@@ -962,42 +960,42 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:16" dyDescent="0.2">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" s="8">
         <v>3</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" t="s" s="1">
         <v>50</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" t="s" s="2">
         <v>52</v>
       </c>
       <c r="E3">
-        <v>82</v>
+        <v>82.0</v>
       </c>
       <c r="F3">
-        <v>88</v>
+        <v>88.0</v>
       </c>
       <c r="G3">
-        <v>17.600000000000001</v>
+        <v>17.6</v>
       </c>
       <c r="H3">
         <v>4.7</v>
       </c>
       <c r="I3">
-        <v>1672</v>
+        <v>1672.0</v>
       </c>
       <c r="J3">
-        <v>751</v>
+        <v>751.0</v>
       </c>
       <c r="K3">
-        <v>2423</v>
+        <v>2423.0</v>
       </c>
       <c r="L3">
-        <v>1672</v>
+        <v>1672.0</v>
       </c>
       <c r="N3" t="s">
         <v>31</v>
@@ -1010,24 +1008,24 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:16" dyDescent="0.2">
       <c r="A4">
         <v>1</v>
       </c>
       <c r="B4" s="8">
         <v>4</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" t="s" s="1">
         <v>50</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" t="s" s="1">
         <v>53</v>
       </c>
       <c r="E4">
-        <v>228</v>
+        <v>228.0</v>
       </c>
       <c r="F4">
-        <v>147</v>
+        <v>147.0</v>
       </c>
       <c r="G4">
         <v>29.4</v>
@@ -1036,16 +1034,16 @@
         <v>7.8</v>
       </c>
       <c r="I4">
-        <v>2793</v>
+        <v>2793.0</v>
       </c>
       <c r="J4">
-        <v>2317</v>
+        <v>2317.0</v>
       </c>
       <c r="K4">
-        <v>5110</v>
+        <v>5110.0</v>
       </c>
       <c r="L4">
-        <v>2793</v>
+        <v>2793.0</v>
       </c>
       <c r="N4" t="s">
         <v>33</v>
@@ -1054,24 +1052,24 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:16" dyDescent="0.2">
       <c r="A5">
         <v>1</v>
       </c>
       <c r="B5" s="8">
         <v>5</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" t="s" s="1">
         <v>50</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" t="s" s="1">
         <v>54</v>
       </c>
       <c r="E5">
-        <v>126</v>
+        <v>126.0</v>
       </c>
       <c r="F5">
-        <v>147</v>
+        <v>147.0</v>
       </c>
       <c r="G5">
         <v>29.4</v>
@@ -1080,16 +1078,16 @@
         <v>4.3</v>
       </c>
       <c r="I5">
-        <v>2793</v>
+        <v>2793.0</v>
       </c>
       <c r="J5">
-        <v>1127</v>
+        <v>1127.0</v>
       </c>
       <c r="K5">
-        <v>3920</v>
+        <v>3920.0</v>
       </c>
       <c r="L5">
-        <v>2793</v>
+        <v>2793.0</v>
       </c>
       <c r="N5" t="s">
         <v>34</v>
@@ -1101,24 +1099,24 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:16" dyDescent="0.2">
       <c r="A6">
         <v>1</v>
       </c>
       <c r="B6" s="8">
         <v>6</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" t="s" s="1">
         <v>50</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" t="s" s="1">
         <v>55</v>
       </c>
       <c r="E6">
-        <v>205</v>
+        <v>205.0</v>
       </c>
       <c r="F6">
-        <v>197</v>
+        <v>197.0</v>
       </c>
       <c r="G6">
         <v>39.4</v>
@@ -1127,37 +1125,37 @@
         <v>5.2</v>
       </c>
       <c r="I6">
-        <v>3743</v>
+        <v>3743.0</v>
       </c>
       <c r="J6">
-        <v>1932</v>
+        <v>1932.0</v>
       </c>
       <c r="K6">
-        <v>5675</v>
+        <v>5675.0</v>
       </c>
       <c r="L6">
-        <v>3743</v>
+        <v>3743.0</v>
       </c>
       <c r="O6" s="4"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:16" dyDescent="0.2">
       <c r="A7">
         <v>1</v>
       </c>
       <c r="B7" s="8">
         <v>7</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" t="s" s="1">
         <v>50</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" t="s" s="1">
         <v>56</v>
       </c>
       <c r="E7">
-        <v>263</v>
+        <v>263.0</v>
       </c>
       <c r="F7">
-        <v>227</v>
+        <v>227.0</v>
       </c>
       <c r="G7">
         <v>45.4</v>
@@ -1166,154 +1164,154 @@
         <v>5.8</v>
       </c>
       <c r="I7">
-        <v>4313</v>
+        <v>4313.0</v>
       </c>
       <c r="J7">
-        <v>2539</v>
+        <v>2539.0</v>
       </c>
       <c r="K7">
-        <v>6852</v>
+        <v>6852.0</v>
       </c>
       <c r="L7">
-        <v>4313</v>
+        <v>4313.0</v>
       </c>
       <c r="O7" s="4"/>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:16" dyDescent="0.2">
       <c r="A8">
         <v>1</v>
       </c>
       <c r="B8" s="8">
         <v>8</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" t="s" s="1">
         <v>50</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>57</v>
+      <c r="D8" t="s" s="1">
+        <v>59</v>
       </c>
       <c r="E8">
-        <v>143</v>
+        <v>156.0</v>
       </c>
       <c r="F8">
-        <v>184</v>
+        <v>144.0</v>
       </c>
       <c r="G8">
-        <v>36.799999999999997</v>
+        <v>28.8</v>
       </c>
       <c r="H8">
-        <v>3.9</v>
+        <v>5.4</v>
       </c>
       <c r="I8">
-        <v>3496</v>
+        <v>2736.0</v>
       </c>
       <c r="J8">
-        <v>1239</v>
+        <v>1484.0</v>
       </c>
       <c r="K8">
-        <v>4735</v>
+        <v>4220.0</v>
       </c>
       <c r="L8">
-        <v>3496</v>
+        <v>2736.0</v>
       </c>
       <c r="O8" s="4"/>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:16" dyDescent="0.2">
       <c r="A9">
         <v>1</v>
       </c>
       <c r="B9" s="8">
         <v>9</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" t="s" s="1">
         <v>50</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" t="s" s="1">
         <v>58</v>
       </c>
       <c r="E9">
-        <v>155</v>
+        <v>230.0</v>
       </c>
       <c r="F9">
-        <v>193</v>
+        <v>219.0</v>
       </c>
       <c r="G9">
-        <v>38.6</v>
+        <v>43.8</v>
       </c>
       <c r="H9">
-        <v>4</v>
+        <v>5.3</v>
       </c>
       <c r="I9">
-        <v>3667</v>
+        <v>4161.0</v>
       </c>
       <c r="J9">
-        <v>1358</v>
+        <v>2172.0</v>
       </c>
       <c r="K9">
-        <v>5025</v>
+        <v>6333.0</v>
       </c>
       <c r="L9">
-        <v>3667</v>
+        <v>4161.0</v>
       </c>
       <c r="O9" s="4"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:16" dyDescent="0.2">
       <c r="A10">
         <v>1</v>
       </c>
       <c r="B10" s="8">
         <v>10</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" t="s" s="1">
         <v>50</v>
       </c>
-      <c r="D10" s="1" t="s">
-        <v>59</v>
+      <c r="D10" t="s" s="1">
+        <v>60</v>
       </c>
       <c r="E10">
-        <v>42</v>
+        <v>56.0</v>
       </c>
       <c r="F10">
-        <v>41</v>
+        <v>47.0</v>
       </c>
       <c r="G10">
-        <v>8.1999999999999993</v>
+        <v>9.4</v>
       </c>
       <c r="H10">
-        <v>5.0999999999999996</v>
+        <v>6.0</v>
       </c>
       <c r="I10">
-        <v>779</v>
+        <v>893.0</v>
       </c>
       <c r="J10">
-        <v>394</v>
+        <v>544.0</v>
       </c>
       <c r="K10">
-        <v>1173</v>
+        <v>1437.0</v>
       </c>
       <c r="L10">
-        <v>779</v>
+        <v>893.0</v>
       </c>
       <c r="O10" s="4"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:16" dyDescent="0.2">
       <c r="A11">
         <v>2</v>
       </c>
       <c r="B11" s="8">
         <v>3</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" t="s" s="2">
         <v>51</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" t="s" s="2">
         <v>52</v>
       </c>
       <c r="E11">
-        <v>173</v>
+        <v>173.0</v>
       </c>
       <c r="F11">
-        <v>131</v>
+        <v>131.0</v>
       </c>
       <c r="G11">
         <v>26.2</v>
@@ -1322,378 +1320,378 @@
         <v>6.6</v>
       </c>
       <c r="I11">
-        <v>2489</v>
+        <v>2489.0</v>
       </c>
       <c r="J11">
-        <v>1713</v>
+        <v>1713.0</v>
       </c>
       <c r="K11">
-        <v>4202</v>
+        <v>4202.0</v>
       </c>
       <c r="L11">
-        <v>2489</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.4">
+        <v>2489.0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" dyDescent="0.2">
       <c r="A12">
         <v>2</v>
       </c>
       <c r="B12" s="8">
         <v>4</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" t="s" s="2">
         <v>51</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D12" t="s" s="1">
         <v>53</v>
       </c>
       <c r="E12">
-        <v>103</v>
+        <v>103.0</v>
       </c>
       <c r="F12">
-        <v>110</v>
+        <v>110.0</v>
       </c>
       <c r="G12">
-        <v>22</v>
+        <v>22.0</v>
       </c>
       <c r="H12">
         <v>4.7</v>
       </c>
       <c r="I12">
-        <v>2090</v>
+        <v>2090.0</v>
       </c>
       <c r="J12">
-        <v>945</v>
+        <v>945.0</v>
       </c>
       <c r="K12">
-        <v>3035</v>
+        <v>3035.0</v>
       </c>
       <c r="L12">
-        <v>2090</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.4">
+        <v>2090.0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" dyDescent="0.2">
       <c r="A13">
         <v>2</v>
       </c>
       <c r="B13" s="8">
         <v>5</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" t="s" s="2">
         <v>51</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D13" t="s" s="1">
         <v>54</v>
       </c>
       <c r="E13">
-        <v>89</v>
+        <v>89.0</v>
       </c>
       <c r="F13">
-        <v>80</v>
+        <v>80.0</v>
       </c>
       <c r="G13">
-        <v>16</v>
+        <v>16.0</v>
       </c>
       <c r="H13">
         <v>5.6</v>
       </c>
       <c r="I13">
-        <v>1520</v>
+        <v>1520.0</v>
       </c>
       <c r="J13">
-        <v>852</v>
+        <v>852.0</v>
       </c>
       <c r="K13">
-        <v>2372</v>
+        <v>2372.0</v>
       </c>
       <c r="L13">
-        <v>1520</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.4">
+        <v>1520.0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" dyDescent="0.2">
       <c r="A14">
         <v>2</v>
       </c>
       <c r="B14" s="8">
         <v>6</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" t="s" s="2">
         <v>51</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="D14" t="s" s="1">
         <v>55</v>
       </c>
       <c r="E14">
-        <v>100</v>
+        <v>100.0</v>
       </c>
       <c r="F14">
-        <v>98</v>
+        <v>98.0</v>
       </c>
       <c r="G14">
-        <v>19.600000000000001</v>
+        <v>19.6</v>
       </c>
       <c r="H14">
-        <v>5.0999999999999996</v>
+        <v>5.1</v>
       </c>
       <c r="I14">
-        <v>1862</v>
+        <v>1862.0</v>
       </c>
       <c r="J14">
-        <v>938</v>
+        <v>938.0</v>
       </c>
       <c r="K14">
-        <v>2800</v>
+        <v>2800.0</v>
       </c>
       <c r="L14">
-        <v>1862</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.4">
+        <v>1862.0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" dyDescent="0.2">
       <c r="A15">
         <v>2</v>
       </c>
       <c r="B15" s="8">
         <v>7</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" t="s" s="2">
         <v>51</v>
       </c>
-      <c r="D15" s="11" t="s">
+      <c r="D15" t="s" s="11">
         <v>56</v>
       </c>
       <c r="E15">
-        <v>138</v>
+        <v>138.0</v>
       </c>
       <c r="F15">
-        <v>151</v>
+        <v>151.0</v>
       </c>
       <c r="G15">
         <v>30.2</v>
       </c>
       <c r="H15">
-        <v>4.5999999999999996</v>
+        <v>4.6</v>
       </c>
       <c r="I15">
-        <v>2869</v>
+        <v>2869.0</v>
       </c>
       <c r="J15">
-        <v>1258</v>
+        <v>1258.0</v>
       </c>
       <c r="K15">
-        <v>4127</v>
+        <v>4127.0</v>
       </c>
       <c r="L15">
-        <v>2869</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.4">
+        <v>2869.0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" dyDescent="0.2">
       <c r="A16">
         <v>2</v>
       </c>
       <c r="B16" s="8">
         <v>8</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" t="s" s="2">
         <v>51</v>
       </c>
-      <c r="D16" s="1" t="s">
-        <v>57</v>
+      <c r="D16" t="s" s="1">
+        <v>59</v>
       </c>
       <c r="E16">
-        <v>55</v>
+        <v>339.0</v>
       </c>
       <c r="F16">
-        <v>40</v>
+        <v>359.0</v>
       </c>
       <c r="G16">
-        <v>8</v>
+        <v>71.8</v>
       </c>
       <c r="H16">
-        <v>6.9</v>
+        <v>4.7</v>
       </c>
       <c r="I16">
-        <v>760</v>
+        <v>6821.0</v>
       </c>
       <c r="J16">
-        <v>548</v>
+        <v>3117.0</v>
       </c>
       <c r="K16">
-        <v>1308</v>
+        <v>9938.0</v>
       </c>
       <c r="L16">
-        <v>760</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.4">
+        <v>6821.0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" dyDescent="0.2">
       <c r="A17">
         <v>2</v>
       </c>
       <c r="B17" s="8">
         <v>9</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" t="s" s="2">
         <v>51</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="D17" t="s" s="1">
         <v>58</v>
       </c>
       <c r="E17">
-        <v>38</v>
+        <v>87.0</v>
       </c>
       <c r="F17">
-        <v>26</v>
+        <v>76.0</v>
       </c>
       <c r="G17">
-        <v>5.2</v>
+        <v>15.2</v>
       </c>
       <c r="H17">
-        <v>7.3</v>
+        <v>5.7</v>
       </c>
       <c r="I17">
-        <v>494</v>
+        <v>1444.0</v>
       </c>
       <c r="J17">
-        <v>383</v>
+        <v>838.0</v>
       </c>
       <c r="K17">
-        <v>877</v>
+        <v>2282.0</v>
       </c>
       <c r="L17">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.4">
+        <v>1444.0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" dyDescent="0.2">
       <c r="A18">
         <v>2</v>
       </c>
       <c r="B18" s="8">
         <v>10</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" t="s" s="2">
         <v>51</v>
       </c>
-      <c r="D18" s="1" t="s">
-        <v>59</v>
+      <c r="D18" t="s" s="1">
+        <v>60</v>
       </c>
       <c r="E18">
-        <v>205</v>
+        <v>218.0</v>
       </c>
       <c r="F18">
-        <v>196</v>
+        <v>217.0</v>
       </c>
       <c r="G18">
-        <v>39.200000000000003</v>
+        <v>43.4</v>
       </c>
       <c r="H18">
-        <v>5.2</v>
+        <v>5.0</v>
       </c>
       <c r="I18">
-        <v>3724</v>
+        <v>4123.0</v>
       </c>
       <c r="J18">
-        <v>1934</v>
+        <v>2037.0</v>
       </c>
       <c r="K18">
-        <v>5658</v>
+        <v>6160.0</v>
       </c>
       <c r="L18">
-        <v>3724</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.4">
+        <v>4123.0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" dyDescent="0.2">
       <c r="A19">
         <v>3</v>
       </c>
       <c r="B19" s="8">
         <v>4</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" t="s" s="2">
         <v>52</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="D19" t="s" s="1">
         <v>53</v>
       </c>
       <c r="E19">
-        <v>215</v>
+        <v>215.0</v>
       </c>
       <c r="F19">
-        <v>77</v>
+        <v>77.0</v>
       </c>
       <c r="G19">
         <v>15.4</v>
       </c>
       <c r="H19">
-        <v>14</v>
+        <v>14.0</v>
       </c>
       <c r="I19">
-        <v>1463</v>
+        <v>1463.0</v>
       </c>
       <c r="J19">
-        <v>2329</v>
+        <v>2329.0</v>
       </c>
       <c r="K19">
-        <v>3792</v>
+        <v>3792.0</v>
       </c>
       <c r="L19">
-        <v>2329</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.4">
+        <v>2329.0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" dyDescent="0.2">
       <c r="A20">
         <v>3</v>
       </c>
       <c r="B20" s="8">
         <v>5</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C20" t="s" s="2">
         <v>52</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="D20" t="s" s="1">
         <v>54</v>
       </c>
       <c r="E20">
-        <v>113</v>
+        <v>113.0</v>
       </c>
       <c r="F20">
-        <v>63</v>
+        <v>63.0</v>
       </c>
       <c r="G20">
         <v>12.6</v>
       </c>
       <c r="H20">
-        <v>9</v>
+        <v>9.0</v>
       </c>
       <c r="I20">
-        <v>1197</v>
+        <v>1197.0</v>
       </c>
       <c r="J20">
-        <v>1171</v>
+        <v>1171.0</v>
       </c>
       <c r="K20">
-        <v>2368</v>
+        <v>2368.0</v>
       </c>
       <c r="L20">
-        <v>1197</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.4">
+        <v>1197.0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" dyDescent="0.2">
       <c r="A21">
         <v>3</v>
       </c>
       <c r="B21" s="8">
         <v>6</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C21" t="s" s="2">
         <v>52</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="D21" t="s" s="1">
         <v>55</v>
       </c>
       <c r="E21">
-        <v>192</v>
+        <v>192.0</v>
       </c>
       <c r="F21">
-        <v>126</v>
+        <v>126.0</v>
       </c>
       <c r="G21">
         <v>25.2</v>
@@ -1702,36 +1700,36 @@
         <v>7.6</v>
       </c>
       <c r="I21">
-        <v>2394</v>
+        <v>2394.0</v>
       </c>
       <c r="J21">
-        <v>1946</v>
+        <v>1946.0</v>
       </c>
       <c r="K21">
-        <v>4340</v>
+        <v>4340.0</v>
       </c>
       <c r="L21">
-        <v>2394</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.4">
+        <v>2394.0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" dyDescent="0.2">
       <c r="A22">
         <v>3</v>
       </c>
       <c r="B22" s="8">
         <v>7</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C22" t="s" s="2">
         <v>52</v>
       </c>
-      <c r="D22" s="11" t="s">
+      <c r="D22" t="s" s="11">
         <v>56</v>
       </c>
       <c r="E22">
-        <v>250</v>
+        <v>250.0</v>
       </c>
       <c r="F22">
-        <v>167</v>
+        <v>167.0</v>
       </c>
       <c r="G22">
         <v>33.4</v>
@@ -1740,931 +1738,931 @@
         <v>7.5</v>
       </c>
       <c r="I22">
-        <v>3173</v>
+        <v>3173.0</v>
       </c>
       <c r="J22">
-        <v>2527</v>
+        <v>2527.0</v>
       </c>
       <c r="K22">
-        <v>5700</v>
+        <v>5700.0</v>
       </c>
       <c r="L22">
-        <v>3173</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.4">
+        <v>3173.0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" dyDescent="0.2">
       <c r="A23">
         <v>3</v>
       </c>
       <c r="B23" s="8">
         <v>8</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C23" t="s" s="2">
         <v>52</v>
       </c>
-      <c r="D23" s="1" t="s">
-        <v>57</v>
+      <c r="D23" t="s" s="1">
+        <v>59</v>
       </c>
       <c r="E23">
-        <v>130</v>
+        <v>234.0</v>
       </c>
       <c r="F23">
-        <v>97</v>
+        <v>230.0</v>
       </c>
       <c r="G23">
-        <v>19.399999999999999</v>
+        <v>46.0</v>
       </c>
       <c r="H23">
-        <v>6.7</v>
+        <v>5.1</v>
       </c>
       <c r="I23">
-        <v>1843</v>
+        <v>4370.0</v>
       </c>
       <c r="J23">
-        <v>1290</v>
+        <v>2193.0</v>
       </c>
       <c r="K23">
-        <v>3133</v>
+        <v>6563.0</v>
       </c>
       <c r="L23">
-        <v>1843</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.4">
+        <v>4370.0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" dyDescent="0.2">
       <c r="A24">
         <v>3</v>
       </c>
       <c r="B24" s="8">
         <v>9</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C24" t="s" s="2">
         <v>52</v>
       </c>
-      <c r="D24" s="1" t="s">
+      <c r="D24" t="s" s="1">
         <v>58</v>
       </c>
       <c r="E24">
-        <v>142</v>
+        <v>217.0</v>
       </c>
       <c r="F24">
-        <v>105</v>
+        <v>138.0</v>
       </c>
       <c r="G24">
-        <v>21</v>
+        <v>27.6</v>
       </c>
       <c r="H24">
-        <v>6.8</v>
+        <v>7.9</v>
       </c>
       <c r="I24">
-        <v>1995</v>
+        <v>2622.0</v>
       </c>
       <c r="J24">
-        <v>1412</v>
+        <v>2210.0</v>
       </c>
       <c r="K24">
-        <v>3407</v>
+        <v>4832.0</v>
       </c>
       <c r="L24">
-        <v>1995</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.4">
+        <v>2622.0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" dyDescent="0.2">
       <c r="A25">
         <v>3</v>
       </c>
       <c r="B25" s="8">
         <v>10</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C25" t="s" s="2">
         <v>52</v>
       </c>
-      <c r="D25" s="1" t="s">
-        <v>59</v>
+      <c r="D25" t="s" s="1">
+        <v>60</v>
       </c>
       <c r="E25">
-        <v>89</v>
+        <v>108.0</v>
       </c>
       <c r="F25">
-        <v>68</v>
+        <v>92.0</v>
       </c>
       <c r="G25">
-        <v>13.6</v>
+        <v>18.4</v>
       </c>
       <c r="H25">
-        <v>6.5</v>
+        <v>5.9</v>
       </c>
       <c r="I25">
-        <v>1292</v>
+        <v>1748.0</v>
       </c>
       <c r="J25">
-        <v>880</v>
+        <v>1045.0</v>
       </c>
       <c r="K25">
-        <v>2172</v>
+        <v>2793.0</v>
       </c>
       <c r="L25">
-        <v>1292</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.4">
+        <v>1748.0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" dyDescent="0.2">
       <c r="A26">
         <v>4</v>
       </c>
       <c r="B26" s="8">
         <v>5</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="C26" t="s" s="1">
         <v>53</v>
       </c>
-      <c r="D26" s="1" t="s">
+      <c r="D26" t="s" s="1">
         <v>54</v>
       </c>
       <c r="E26">
-        <v>130</v>
+        <v>130.0</v>
       </c>
       <c r="F26">
-        <v>93</v>
+        <v>93.0</v>
       </c>
       <c r="G26">
-        <v>18.600000000000001</v>
+        <v>18.6</v>
       </c>
       <c r="H26">
-        <v>7</v>
+        <v>7.0</v>
       </c>
       <c r="I26">
-        <v>1767</v>
+        <v>1767.0</v>
       </c>
       <c r="J26">
-        <v>1300</v>
+        <v>1300.0</v>
       </c>
       <c r="K26">
-        <v>3067</v>
+        <v>3067.0</v>
       </c>
       <c r="L26">
-        <v>1767</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.4">
+        <v>1767.0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" dyDescent="0.2">
       <c r="A27">
         <v>4</v>
       </c>
       <c r="B27" s="8">
         <v>6</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="C27" t="s" s="1">
         <v>53</v>
       </c>
-      <c r="D27" s="1" t="s">
+      <c r="D27" t="s" s="1">
         <v>55</v>
       </c>
       <c r="E27">
-        <v>149</v>
+        <v>149.0</v>
       </c>
       <c r="F27">
-        <v>161</v>
+        <v>161.0</v>
       </c>
       <c r="G27">
-        <v>32.200000000000003</v>
+        <v>32.2</v>
       </c>
       <c r="H27">
-        <v>4.5999999999999996</v>
+        <v>4.6</v>
       </c>
       <c r="I27">
-        <v>3059</v>
+        <v>3059.0</v>
       </c>
       <c r="J27">
-        <v>1363</v>
+        <v>1363.0</v>
       </c>
       <c r="K27">
-        <v>4422</v>
+        <v>4422.0</v>
       </c>
       <c r="L27">
-        <v>3059</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.4">
+        <v>3059.0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" dyDescent="0.2">
       <c r="A28">
         <v>4</v>
       </c>
       <c r="B28" s="8">
         <v>7</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="C28" t="s" s="1">
         <v>53</v>
       </c>
-      <c r="D28" s="11" t="s">
+      <c r="D28" t="s" s="11">
         <v>56</v>
       </c>
       <c r="E28">
-        <v>93</v>
+        <v>93.0</v>
       </c>
       <c r="F28">
-        <v>90</v>
+        <v>90.0</v>
       </c>
       <c r="G28">
-        <v>18</v>
+        <v>18.0</v>
       </c>
       <c r="H28">
         <v>5.2</v>
       </c>
       <c r="I28">
-        <v>1710</v>
+        <v>1710.0</v>
       </c>
       <c r="J28">
-        <v>875</v>
+        <v>875.0</v>
       </c>
       <c r="K28">
-        <v>2585</v>
+        <v>2585.0</v>
       </c>
       <c r="L28">
-        <v>1710</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.4">
+        <v>1710.0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" dyDescent="0.2">
       <c r="A29">
         <v>4</v>
       </c>
       <c r="B29" s="8">
         <v>8</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="C29" t="s" s="1">
         <v>53</v>
       </c>
-      <c r="D29" s="1" t="s">
-        <v>57</v>
+      <c r="D29" t="s" s="1">
+        <v>59</v>
       </c>
       <c r="E29">
-        <v>97</v>
+        <v>380.0</v>
       </c>
       <c r="F29">
-        <v>97</v>
+        <v>290.0</v>
       </c>
       <c r="G29">
-        <v>19.399999999999999</v>
+        <v>58.0</v>
       </c>
       <c r="H29">
-        <v>5</v>
+        <v>6.6</v>
       </c>
       <c r="I29">
-        <v>1843</v>
+        <v>5510.0</v>
       </c>
       <c r="J29">
-        <v>905</v>
+        <v>3757.0</v>
       </c>
       <c r="K29">
-        <v>2748</v>
+        <v>9267.0</v>
       </c>
       <c r="L29">
-        <v>1843</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.4">
+        <v>5510.0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" dyDescent="0.2">
       <c r="A30">
         <v>4</v>
       </c>
       <c r="B30" s="8">
         <v>9</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="C30" t="s" s="1">
         <v>53</v>
       </c>
-      <c r="D30" s="1" t="s">
+      <c r="D30" t="s" s="1">
         <v>58</v>
       </c>
       <c r="E30">
-        <v>76</v>
+        <v>87.0</v>
       </c>
       <c r="F30">
-        <v>91</v>
+        <v>75.0</v>
       </c>
       <c r="G30">
-        <v>18.2</v>
+        <v>15.0</v>
       </c>
       <c r="H30">
-        <v>4.2</v>
+        <v>5.8</v>
       </c>
       <c r="I30">
-        <v>1729</v>
+        <v>1425.0</v>
       </c>
       <c r="J30">
-        <v>674</v>
+        <v>840.0</v>
       </c>
       <c r="K30">
-        <v>2403</v>
+        <v>2265.0</v>
       </c>
       <c r="L30">
-        <v>1729</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.4">
+        <v>1425.0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" dyDescent="0.2">
       <c r="A31">
         <v>4</v>
       </c>
       <c r="B31" s="8">
         <v>10</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C31" t="s" s="1">
         <v>53</v>
       </c>
-      <c r="D31" s="1" t="s">
-        <v>59</v>
+      <c r="D31" t="s" s="1">
+        <v>60</v>
       </c>
       <c r="E31">
-        <v>246</v>
+        <v>259.0</v>
       </c>
       <c r="F31">
-        <v>110</v>
+        <v>125.0</v>
       </c>
       <c r="G31">
-        <v>22</v>
+        <v>25.0</v>
       </c>
       <c r="H31">
-        <v>11.2</v>
+        <v>10.4</v>
       </c>
       <c r="I31">
-        <v>2090</v>
+        <v>2375.0</v>
       </c>
       <c r="J31">
-        <v>2613</v>
+        <v>2730.0</v>
       </c>
       <c r="K31">
-        <v>4703</v>
+        <v>5105.0</v>
       </c>
       <c r="L31">
-        <v>2613</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.4">
+        <v>2730.0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" dyDescent="0.2">
       <c r="A32">
         <v>5</v>
       </c>
       <c r="B32" s="8">
         <v>6</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="C32" t="s" s="1">
         <v>54</v>
       </c>
-      <c r="D32" s="1" t="s">
+      <c r="D32" t="s" s="1">
         <v>55</v>
       </c>
       <c r="E32">
-        <v>110</v>
+        <v>110.0</v>
       </c>
       <c r="F32">
-        <v>70</v>
+        <v>70.0</v>
       </c>
       <c r="G32">
-        <v>14</v>
+        <v>14.0</v>
       </c>
       <c r="H32">
         <v>7.9</v>
       </c>
       <c r="I32">
-        <v>1330</v>
+        <v>1330.0</v>
       </c>
       <c r="J32">
-        <v>1120</v>
+        <v>1120.0</v>
       </c>
       <c r="K32">
-        <v>2450</v>
+        <v>2450.0</v>
       </c>
       <c r="L32">
-        <v>1330</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.4">
+        <v>1330.0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" dyDescent="0.2">
       <c r="A33" s="10">
         <v>5</v>
       </c>
       <c r="B33" s="8">
         <v>7</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C33" t="s" s="1">
         <v>54</v>
       </c>
-      <c r="D33" s="11" t="s">
+      <c r="D33" t="s" s="11">
         <v>56</v>
       </c>
       <c r="E33">
-        <v>168</v>
+        <v>168.0</v>
       </c>
       <c r="F33">
-        <v>173</v>
+        <v>173.0</v>
       </c>
       <c r="G33">
         <v>34.6</v>
       </c>
       <c r="H33">
-        <v>4.9000000000000004</v>
+        <v>4.9</v>
       </c>
       <c r="I33">
-        <v>3287</v>
+        <v>3287.0</v>
       </c>
       <c r="J33">
-        <v>1556</v>
+        <v>1556.0</v>
       </c>
       <c r="K33">
-        <v>4843</v>
+        <v>4843.0</v>
       </c>
       <c r="L33">
-        <v>3287</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.4">
+        <v>3287.0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" dyDescent="0.2">
       <c r="A34">
         <v>5</v>
       </c>
       <c r="B34" s="8">
         <v>8</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="C34" t="s" s="1">
         <v>54</v>
       </c>
-      <c r="D34" s="1" t="s">
-        <v>57</v>
+      <c r="D34" t="s" s="1">
+        <v>59</v>
       </c>
       <c r="E34">
-        <v>48</v>
+        <v>279.0</v>
       </c>
       <c r="F34">
-        <v>40</v>
+        <v>281.0</v>
       </c>
       <c r="G34">
-        <v>8</v>
+        <v>56.2</v>
       </c>
       <c r="H34">
-        <v>6</v>
+        <v>5.0</v>
       </c>
       <c r="I34">
-        <v>760</v>
+        <v>5339.0</v>
       </c>
       <c r="J34">
-        <v>467</v>
+        <v>2599.0</v>
       </c>
       <c r="K34">
-        <v>1227</v>
+        <v>7938.0</v>
       </c>
       <c r="L34">
-        <v>760</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.4">
+        <v>5339.0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" dyDescent="0.2">
       <c r="A35">
         <v>5</v>
       </c>
       <c r="B35" s="8">
         <v>9</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="C35" t="s" s="1">
         <v>54</v>
       </c>
-      <c r="D35" s="1" t="s">
+      <c r="D35" t="s" s="1">
         <v>58</v>
       </c>
       <c r="E35">
-        <v>60</v>
+        <v>136.0</v>
       </c>
       <c r="F35">
-        <v>55</v>
+        <v>118.0</v>
       </c>
       <c r="G35">
-        <v>11</v>
+        <v>23.6</v>
       </c>
       <c r="H35">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="I35">
-        <v>1045</v>
+        <v>2242.0</v>
       </c>
       <c r="J35">
-        <v>572</v>
+        <v>1311.0</v>
       </c>
       <c r="K35">
-        <v>1617</v>
+        <v>3553.0</v>
       </c>
       <c r="L35">
-        <v>1045</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.4">
+        <v>2242.0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" dyDescent="0.2">
       <c r="A36">
         <v>5</v>
       </c>
       <c r="B36" s="8">
         <v>10</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="C36" t="s" s="1">
         <v>54</v>
       </c>
-      <c r="D36" s="1" t="s">
-        <v>59</v>
+      <c r="D36" t="s" s="1">
+        <v>60</v>
       </c>
       <c r="E36">
-        <v>145</v>
+        <v>158.0</v>
       </c>
       <c r="F36">
-        <v>131</v>
+        <v>155.0</v>
       </c>
       <c r="G36">
-        <v>26.2</v>
+        <v>31.0</v>
       </c>
       <c r="H36">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="I36">
-        <v>2489</v>
+        <v>2945.0</v>
       </c>
       <c r="J36">
-        <v>1386</v>
+        <v>1482.0</v>
       </c>
       <c r="K36">
-        <v>3875</v>
+        <v>4427.0</v>
       </c>
       <c r="L36">
-        <v>2489</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.4">
+        <v>2945.0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" dyDescent="0.2">
       <c r="A37">
         <v>6</v>
       </c>
       <c r="B37" s="8">
         <v>7</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="C37" t="s" s="1">
         <v>55</v>
       </c>
-      <c r="D37" s="11" t="s">
+      <c r="D37" t="s" s="11">
         <v>56</v>
       </c>
       <c r="E37">
-        <v>185</v>
+        <v>185.0</v>
       </c>
       <c r="F37">
-        <v>232</v>
+        <v>232.0</v>
       </c>
       <c r="G37">
         <v>46.4</v>
       </c>
       <c r="H37">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="I37">
-        <v>4408</v>
+        <v>4408.0</v>
       </c>
       <c r="J37">
-        <v>1617</v>
+        <v>1617.0</v>
       </c>
       <c r="K37">
-        <v>6025</v>
+        <v>6025.0</v>
       </c>
       <c r="L37">
-        <v>4408</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.4">
+        <v>4408.0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" dyDescent="0.2">
       <c r="A38">
         <v>6</v>
       </c>
       <c r="B38" s="8">
         <v>8</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="C38" t="s" s="1">
         <v>55</v>
       </c>
-      <c r="D38" s="1" t="s">
-        <v>57</v>
+      <c r="D38" t="s" s="1">
+        <v>59</v>
       </c>
       <c r="E38">
-        <v>77</v>
+        <v>358.0</v>
       </c>
       <c r="F38">
-        <v>72</v>
+        <v>315.0</v>
       </c>
       <c r="G38">
-        <v>14.4</v>
+        <v>63.0</v>
       </c>
       <c r="H38">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="I38">
-        <v>1368</v>
+        <v>5985.0</v>
       </c>
       <c r="J38">
-        <v>730</v>
+        <v>3442.0</v>
       </c>
       <c r="K38">
-        <v>2098</v>
+        <v>9427.0</v>
       </c>
       <c r="L38">
-        <v>1368</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.4">
+        <v>5985.0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" dyDescent="0.2">
       <c r="A39">
         <v>6</v>
       </c>
       <c r="B39" s="8">
         <v>9</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="C39" t="s" s="1">
         <v>55</v>
       </c>
-      <c r="D39" s="1" t="s">
+      <c r="D39" t="s" s="1">
         <v>58</v>
       </c>
       <c r="E39">
-        <v>78</v>
+        <v>153.0</v>
       </c>
       <c r="F39">
-        <v>89</v>
+        <v>166.0</v>
       </c>
       <c r="G39">
-        <v>17.8</v>
+        <v>33.2</v>
       </c>
       <c r="H39">
-        <v>4.4000000000000004</v>
+        <v>4.6</v>
       </c>
       <c r="I39">
-        <v>1691</v>
+        <v>3154.0</v>
       </c>
       <c r="J39">
-        <v>702</v>
+        <v>1398.0</v>
       </c>
       <c r="K39">
-        <v>2393</v>
+        <v>4552.0</v>
       </c>
       <c r="L39">
-        <v>1691</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.4">
+        <v>3154.0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" dyDescent="0.2">
       <c r="A40">
         <v>6</v>
       </c>
       <c r="B40" s="8">
         <v>10</v>
       </c>
-      <c r="C40" s="1" t="s">
+      <c r="C40" t="s" s="1">
         <v>55</v>
       </c>
-      <c r="D40" s="1" t="s">
-        <v>59</v>
+      <c r="D40" t="s" s="1">
+        <v>60</v>
       </c>
       <c r="E40">
-        <v>224</v>
+        <v>237.0</v>
       </c>
       <c r="F40">
-        <v>192</v>
+        <v>216.0</v>
       </c>
       <c r="G40">
-        <v>38.4</v>
+        <v>43.2</v>
       </c>
       <c r="H40">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="I40">
-        <v>3648</v>
+        <v>4104.0</v>
       </c>
       <c r="J40">
-        <v>2165</v>
+        <v>2261.0</v>
       </c>
       <c r="K40">
-        <v>5813</v>
+        <v>6365.0</v>
       </c>
       <c r="L40">
-        <v>3648</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.4">
+        <v>4104.0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" dyDescent="0.2">
       <c r="A41">
         <v>7</v>
       </c>
       <c r="B41" s="8">
         <v>8</v>
       </c>
-      <c r="C41" s="1" t="s">
+      <c r="C41" t="s" s="1">
         <v>56</v>
       </c>
-      <c r="D41" s="1" t="s">
-        <v>57</v>
+      <c r="D41" t="s" s="1">
+        <v>59</v>
       </c>
       <c r="E41">
-        <v>131</v>
+        <v>414.0</v>
       </c>
       <c r="F41">
-        <v>160</v>
+        <v>365.0</v>
       </c>
       <c r="G41">
-        <v>32</v>
+        <v>73.0</v>
       </c>
       <c r="H41">
-        <v>4.0999999999999996</v>
+        <v>5.7</v>
       </c>
       <c r="I41">
-        <v>3040</v>
+        <v>6935.0</v>
       </c>
       <c r="J41">
-        <v>1155</v>
+        <v>3978.0</v>
       </c>
       <c r="K41">
-        <v>4195</v>
+        <v>10913.0</v>
       </c>
       <c r="L41">
-        <v>3040</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.4">
+        <v>6935.0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" dyDescent="0.2">
       <c r="A42">
         <v>7</v>
       </c>
       <c r="B42" s="8">
         <v>9</v>
       </c>
-      <c r="C42" s="1" t="s">
+      <c r="C42" t="s" s="1">
         <v>56</v>
       </c>
-      <c r="D42" s="1" t="s">
+      <c r="D42" t="s" s="1">
         <v>58</v>
       </c>
       <c r="E42">
-        <v>110</v>
+        <v>70.0</v>
       </c>
       <c r="F42">
-        <v>146</v>
+        <v>75.0</v>
       </c>
       <c r="G42">
-        <v>29.2</v>
+        <v>15.0</v>
       </c>
       <c r="H42">
-        <v>3.8</v>
+        <v>4.7</v>
       </c>
       <c r="I42">
-        <v>2774</v>
+        <v>1425.0</v>
       </c>
       <c r="J42">
-        <v>943</v>
+        <v>642.0</v>
       </c>
       <c r="K42">
-        <v>3717</v>
+        <v>2067.0</v>
       </c>
       <c r="L42">
-        <v>2774</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.4">
+        <v>1425.0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" dyDescent="0.2">
       <c r="A43">
         <v>7</v>
       </c>
       <c r="B43" s="8">
         <v>10</v>
       </c>
-      <c r="C43" s="1" t="s">
+      <c r="C43" t="s" s="1">
         <v>56</v>
       </c>
-      <c r="D43" s="1" t="s">
-        <v>59</v>
+      <c r="D43" t="s" s="1">
+        <v>60</v>
       </c>
       <c r="E43">
-        <v>280</v>
+        <v>293.0</v>
       </c>
       <c r="F43">
-        <v>187</v>
+        <v>194.0</v>
       </c>
       <c r="G43">
-        <v>37.4</v>
+        <v>38.8</v>
       </c>
       <c r="H43">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="I43">
-        <v>3553</v>
+        <v>3686.0</v>
       </c>
       <c r="J43">
-        <v>2830</v>
+        <v>2966.0</v>
       </c>
       <c r="K43">
-        <v>6383</v>
+        <v>6652.0</v>
       </c>
       <c r="L43">
-        <v>3553</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.4">
+        <v>3686.0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" dyDescent="0.2">
       <c r="A44">
         <v>8</v>
       </c>
       <c r="B44" s="8">
         <v>9</v>
       </c>
-      <c r="C44" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D44" s="1" t="s">
+      <c r="C44" t="s" s="1">
+        <v>59</v>
+      </c>
+      <c r="D44" t="s" s="1">
         <v>58</v>
       </c>
       <c r="E44">
-        <v>26</v>
+        <v>384.0</v>
       </c>
       <c r="F44">
-        <v>19</v>
+        <v>363.0</v>
       </c>
       <c r="G44">
-        <v>3.8</v>
+        <v>72.6</v>
       </c>
       <c r="H44">
-        <v>6.8</v>
+        <v>5.3</v>
       </c>
       <c r="I44">
-        <v>361</v>
+        <v>6897.0</v>
       </c>
       <c r="J44">
-        <v>259</v>
+        <v>3633.0</v>
       </c>
       <c r="K44">
-        <v>620</v>
+        <v>10530.0</v>
       </c>
       <c r="L44">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.4">
+        <v>6897.0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" dyDescent="0.2">
       <c r="A45">
         <v>8</v>
       </c>
       <c r="B45" s="8">
         <v>10</v>
       </c>
-      <c r="C45" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D45" s="1" t="s">
+      <c r="C45" t="s" s="1">
         <v>59</v>
       </c>
+      <c r="D45" t="s" s="1">
+        <v>60</v>
+      </c>
       <c r="E45">
-        <v>163</v>
+        <v>209.0</v>
       </c>
       <c r="F45">
-        <v>164</v>
+        <v>172.0</v>
       </c>
       <c r="G45">
-        <v>32.799999999999997</v>
+        <v>34.4</v>
       </c>
       <c r="H45">
-        <v>5</v>
+        <v>6.1</v>
       </c>
       <c r="I45">
-        <v>3116</v>
+        <v>3268.0</v>
       </c>
       <c r="J45">
-        <v>1519</v>
+        <v>2037.0</v>
       </c>
       <c r="K45">
-        <v>4635</v>
+        <v>5305.0</v>
       </c>
       <c r="L45">
-        <v>3116</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.4">
+        <v>3268.0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" dyDescent="0.2">
       <c r="A46">
         <v>9</v>
       </c>
       <c r="B46" s="8">
         <v>10</v>
       </c>
-      <c r="C46" s="1" t="s">
+      <c r="C46" t="s" s="1">
         <v>58</v>
       </c>
-      <c r="D46" s="1" t="s">
-        <v>59</v>
+      <c r="D46" t="s" s="1">
+        <v>60</v>
       </c>
       <c r="E46">
-        <v>175</v>
+        <v>264.0</v>
       </c>
       <c r="F46">
-        <v>170</v>
+        <v>200.0</v>
       </c>
       <c r="G46">
-        <v>34</v>
+        <v>40.0</v>
       </c>
       <c r="H46">
-        <v>5.0999999999999996</v>
+        <v>6.6</v>
       </c>
       <c r="I46">
-        <v>3230</v>
+        <v>3800.0</v>
       </c>
       <c r="J46">
-        <v>1645</v>
+        <v>2613.0</v>
       </c>
       <c r="K46">
-        <v>4875</v>
+        <v>6413.0</v>
       </c>
       <c r="L46">
-        <v>3230</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.4">
+        <v>3800.0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" dyDescent="0.2">
       <c r="A47">
         <v>1</v>
       </c>
@@ -2698,7 +2696,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:16" dyDescent="0.2">
       <c r="A48">
         <v>2</v>
       </c>
@@ -2732,7 +2730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:16" dyDescent="0.2">
       <c r="A49">
         <v>3</v>
       </c>
@@ -2766,7 +2764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:16" dyDescent="0.2">
       <c r="A50">
         <v>4</v>
       </c>
@@ -2800,7 +2798,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:16" dyDescent="0.2">
       <c r="A51">
         <v>5</v>
       </c>
@@ -2834,7 +2832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:16" dyDescent="0.2">
       <c r="A52">
         <v>6</v>
       </c>
@@ -2866,7 +2864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:16" dyDescent="0.2">
       <c r="A53">
         <v>7</v>
       </c>
@@ -2898,7 +2896,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:16" dyDescent="0.2">
       <c r="A54">
         <v>8</v>
       </c>
@@ -2930,7 +2928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:16" dyDescent="0.2">
       <c r="A55">
         <v>9</v>
       </c>
@@ -2962,7 +2960,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:16" dyDescent="0.2">
       <c r="A56">
         <v>10</v>
       </c>
@@ -2994,13 +2992,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:16" dyDescent="0.2">
       <c r="G57" s="2"/>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:16" dyDescent="0.2">
       <c r="G58" s="1"/>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:16" dyDescent="0.2">
       <c r="G59" s="1"/>
     </row>
   </sheetData>

--- a/inputData/Parameters.xlsx
+++ b/inputData/Parameters.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sillewiberg/Desktop/Skole/Speciale/Master-Thesis-eVTOL-1/inputData/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kapta\Documents\DTU\Speciale\GitHubFiles\inputData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5E5E19C-E433-3D4B-B2DE-3F609C62E196}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF37B58F-311A-4129-870D-B253556C8BAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14320" yWindow="500" windowWidth="14480" windowHeight="16340" activeTab="1" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
   </bookViews>
   <sheets>
     <sheet name="Parameters" sheetId="9" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="61">
   <si>
     <t>cap_u</t>
   </si>
@@ -647,19 +647,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B15C49E0-A7B4-734A-8962-DC2A879F4079}">
   <dimension ref="A1:D20"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="22.6640625" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:4" dyDescent="0.2">
-      <c r="A2" t="s" s="1">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A2" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B2" s="4">
@@ -669,7 +669,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" dyDescent="0.2">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -680,7 +680,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:4" dyDescent="0.2">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>45</v>
       </c>
@@ -691,7 +691,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="5" spans="1:4" dyDescent="0.2">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -702,7 +702,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="6" spans="1:4" dyDescent="0.2">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -713,7 +713,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:4" dyDescent="0.2">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -724,7 +724,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:4" dyDescent="0.2">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -736,7 +736,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:4" dyDescent="0.2">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
         <v>0</v>
       </c>
@@ -747,7 +747,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:4" dyDescent="0.2">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
         <v>1</v>
       </c>
@@ -758,7 +758,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:4" dyDescent="0.2">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
         <v>44</v>
       </c>
@@ -769,7 +769,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="12" spans="1:4" dyDescent="0.2">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
         <v>2</v>
       </c>
@@ -780,18 +780,18 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="13" spans="1:4" dyDescent="0.2">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
         <v>42</v>
       </c>
       <c r="B13" s="4">
         <v>20</v>
       </c>
-      <c r="D13" t="s" s="3">
+      <c r="D13" s="3" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="14" spans="1:4" dyDescent="0.2">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -799,11 +799,11 @@
         <f>2.11*B20</f>
         <v>2.11</v>
       </c>
-      <c r="D14" t="s" s="3">
+      <c r="D14" s="3" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="15" spans="1:4" dyDescent="0.2">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
         <v>4</v>
       </c>
@@ -811,11 +811,11 @@
         <f>30/B20</f>
         <v>30</v>
       </c>
-      <c r="D15" t="s" s="3">
+      <c r="D15" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:4" dyDescent="0.2">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
         <v>5</v>
       </c>
@@ -823,29 +823,29 @@
         <f>20/B20</f>
         <v>20</v>
       </c>
-      <c r="D16" t="s" s="3">
+      <c r="D16" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:4" dyDescent="0.2">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
         <v>6</v>
       </c>
       <c r="B17" s="4">
         <v>120</v>
       </c>
-      <c r="D17" t="s" s="3">
+      <c r="D17" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:4" dyDescent="0.2">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
         <v>41</v>
       </c>
       <c r="B20" s="4">
         <v>1</v>
       </c>
-      <c r="D20" t="s" s="3">
+      <c r="D20" s="3" t="s">
         <v>47</v>
       </c>
     </row>
@@ -858,7 +858,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAF0D5EA-53B5-1240-9D84-6FE223856A18}">
   <dimension ref="A1:P59"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="17.1640625" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="17.1640625" customWidth="1"/>
@@ -868,44 +868,44 @@
     <col min="8" max="8" width="18.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" dyDescent="0.2">
-      <c r="A1" t="s" s="9">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A1" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="B1" t="s" s="5">
+      <c r="B1" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C1" t="s" s="5">
+      <c r="C1" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="D1" t="s" s="5">
+      <c r="D1" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="E1" t="s" s="5">
+      <c r="E1" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="F1" t="s" s="5">
+      <c r="F1" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="G1" t="s" s="5">
+      <c r="G1" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="H1" t="s" s="5">
+      <c r="H1" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="I1" t="s" s="5">
+      <c r="I1" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="J1" t="s" s="5">
+      <c r="J1" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="K1" t="s" s="5">
+      <c r="K1" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="L1" t="s" s="5">
+      <c r="L1" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="N1" t="s" s="6">
+      <c r="N1" s="6" t="s">
         <v>19</v>
       </c>
       <c r="O1" s="7">
@@ -913,24 +913,24 @@
       </c>
       <c r="P1" s="6"/>
     </row>
-    <row r="2" spans="1:16" dyDescent="0.2">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" s="8">
         <v>2</v>
       </c>
-      <c r="C2" t="s" s="1">
+      <c r="C2" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D2" t="s" s="2">
+      <c r="D2" s="2" t="s">
         <v>51</v>
       </c>
       <c r="E2">
-        <v>185.0</v>
+        <v>185</v>
       </c>
       <c r="F2">
-        <v>219.0</v>
+        <v>219</v>
       </c>
       <c r="G2">
         <v>43.8</v>
@@ -939,16 +939,16 @@
         <v>4.2</v>
       </c>
       <c r="I2">
-        <v>4161.0</v>
+        <v>4161</v>
       </c>
       <c r="J2">
-        <v>1647.0</v>
+        <v>1647</v>
       </c>
       <c r="K2">
-        <v>5808.0</v>
+        <v>5808</v>
       </c>
       <c r="L2">
-        <v>4161.0</v>
+        <v>4161</v>
       </c>
       <c r="N2" t="s">
         <v>29</v>
@@ -960,42 +960,42 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:16" dyDescent="0.2">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" s="8">
         <v>3</v>
       </c>
-      <c r="C3" t="s" s="1">
+      <c r="C3" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D3" t="s" s="2">
+      <c r="D3" s="2" t="s">
         <v>52</v>
       </c>
       <c r="E3">
-        <v>82.0</v>
+        <v>82</v>
       </c>
       <c r="F3">
-        <v>88.0</v>
+        <v>88</v>
       </c>
       <c r="G3">
-        <v>17.6</v>
+        <v>17.600000000000001</v>
       </c>
       <c r="H3">
         <v>4.7</v>
       </c>
       <c r="I3">
-        <v>1672.0</v>
+        <v>1672</v>
       </c>
       <c r="J3">
-        <v>751.0</v>
+        <v>751</v>
       </c>
       <c r="K3">
-        <v>2423.0</v>
+        <v>2423</v>
       </c>
       <c r="L3">
-        <v>1672.0</v>
+        <v>1672</v>
       </c>
       <c r="N3" t="s">
         <v>31</v>
@@ -1008,24 +1008,24 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:16" dyDescent="0.2">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>1</v>
       </c>
       <c r="B4" s="8">
         <v>4</v>
       </c>
-      <c r="C4" t="s" s="1">
+      <c r="C4" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D4" t="s" s="1">
+      <c r="D4" s="1" t="s">
         <v>53</v>
       </c>
       <c r="E4">
-        <v>228.0</v>
+        <v>228</v>
       </c>
       <c r="F4">
-        <v>147.0</v>
+        <v>147</v>
       </c>
       <c r="G4">
         <v>29.4</v>
@@ -1034,16 +1034,16 @@
         <v>7.8</v>
       </c>
       <c r="I4">
-        <v>2793.0</v>
+        <v>2793</v>
       </c>
       <c r="J4">
-        <v>2317.0</v>
+        <v>2317</v>
       </c>
       <c r="K4">
-        <v>5110.0</v>
+        <v>5110</v>
       </c>
       <c r="L4">
-        <v>2793.0</v>
+        <v>2793</v>
       </c>
       <c r="N4" t="s">
         <v>33</v>
@@ -1052,24 +1052,24 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="5" spans="1:16" dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>1</v>
       </c>
       <c r="B5" s="8">
         <v>5</v>
       </c>
-      <c r="C5" t="s" s="1">
+      <c r="C5" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D5" t="s" s="1">
+      <c r="D5" s="1" t="s">
         <v>54</v>
       </c>
       <c r="E5">
-        <v>126.0</v>
+        <v>126</v>
       </c>
       <c r="F5">
-        <v>147.0</v>
+        <v>147</v>
       </c>
       <c r="G5">
         <v>29.4</v>
@@ -1078,16 +1078,16 @@
         <v>4.3</v>
       </c>
       <c r="I5">
-        <v>2793.0</v>
+        <v>2793</v>
       </c>
       <c r="J5">
-        <v>1127.0</v>
+        <v>1127</v>
       </c>
       <c r="K5">
-        <v>3920.0</v>
+        <v>3920</v>
       </c>
       <c r="L5">
-        <v>2793.0</v>
+        <v>2793</v>
       </c>
       <c r="N5" t="s">
         <v>34</v>
@@ -1099,24 +1099,24 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:16" dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>1</v>
       </c>
       <c r="B6" s="8">
         <v>6</v>
       </c>
-      <c r="C6" t="s" s="1">
+      <c r="C6" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D6" t="s" s="1">
+      <c r="D6" s="1" t="s">
         <v>55</v>
       </c>
       <c r="E6">
-        <v>205.0</v>
+        <v>205</v>
       </c>
       <c r="F6">
-        <v>197.0</v>
+        <v>197</v>
       </c>
       <c r="G6">
         <v>39.4</v>
@@ -1125,37 +1125,37 @@
         <v>5.2</v>
       </c>
       <c r="I6">
-        <v>3743.0</v>
+        <v>3743</v>
       </c>
       <c r="J6">
-        <v>1932.0</v>
+        <v>1932</v>
       </c>
       <c r="K6">
-        <v>5675.0</v>
+        <v>5675</v>
       </c>
       <c r="L6">
-        <v>3743.0</v>
+        <v>3743</v>
       </c>
       <c r="O6" s="4"/>
     </row>
-    <row r="7" spans="1:16" dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>1</v>
       </c>
       <c r="B7" s="8">
         <v>7</v>
       </c>
-      <c r="C7" t="s" s="1">
+      <c r="C7" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D7" t="s" s="1">
+      <c r="D7" s="1" t="s">
         <v>56</v>
       </c>
       <c r="E7">
-        <v>263.0</v>
+        <v>263</v>
       </c>
       <c r="F7">
-        <v>227.0</v>
+        <v>227</v>
       </c>
       <c r="G7">
         <v>45.4</v>
@@ -1164,37 +1164,37 @@
         <v>5.8</v>
       </c>
       <c r="I7">
-        <v>4313.0</v>
+        <v>4313</v>
       </c>
       <c r="J7">
-        <v>2539.0</v>
+        <v>2539</v>
       </c>
       <c r="K7">
-        <v>6852.0</v>
+        <v>6852</v>
       </c>
       <c r="L7">
-        <v>4313.0</v>
+        <v>4313</v>
       </c>
       <c r="O7" s="4"/>
     </row>
-    <row r="8" spans="1:16" dyDescent="0.2">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>1</v>
       </c>
       <c r="B8" s="8">
         <v>8</v>
       </c>
-      <c r="C8" t="s" s="1">
+      <c r="C8" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D8" t="s" s="1">
+      <c r="D8" s="1" t="s">
         <v>59</v>
       </c>
       <c r="E8">
-        <v>156.0</v>
+        <v>156</v>
       </c>
       <c r="F8">
-        <v>144.0</v>
+        <v>144</v>
       </c>
       <c r="G8">
         <v>28.8</v>
@@ -1203,37 +1203,37 @@
         <v>5.4</v>
       </c>
       <c r="I8">
-        <v>2736.0</v>
+        <v>2736</v>
       </c>
       <c r="J8">
-        <v>1484.0</v>
+        <v>1484</v>
       </c>
       <c r="K8">
-        <v>4220.0</v>
+        <v>4220</v>
       </c>
       <c r="L8">
-        <v>2736.0</v>
+        <v>2736</v>
       </c>
       <c r="O8" s="4"/>
     </row>
-    <row r="9" spans="1:16" dyDescent="0.2">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>1</v>
       </c>
       <c r="B9" s="8">
         <v>9</v>
       </c>
-      <c r="C9" t="s" s="1">
+      <c r="C9" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D9" t="s" s="1">
+      <c r="D9" s="1" t="s">
         <v>58</v>
       </c>
       <c r="E9">
-        <v>230.0</v>
+        <v>230</v>
       </c>
       <c r="F9">
-        <v>219.0</v>
+        <v>219</v>
       </c>
       <c r="G9">
         <v>43.8</v>
@@ -1242,76 +1242,76 @@
         <v>5.3</v>
       </c>
       <c r="I9">
-        <v>4161.0</v>
+        <v>4161</v>
       </c>
       <c r="J9">
-        <v>2172.0</v>
+        <v>2172</v>
       </c>
       <c r="K9">
-        <v>6333.0</v>
+        <v>6333</v>
       </c>
       <c r="L9">
-        <v>4161.0</v>
+        <v>4161</v>
       </c>
       <c r="O9" s="4"/>
     </row>
-    <row r="10" spans="1:16" dyDescent="0.2">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>1</v>
       </c>
       <c r="B10" s="8">
         <v>10</v>
       </c>
-      <c r="C10" t="s" s="1">
+      <c r="C10" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D10" t="s" s="1">
+      <c r="D10" s="1" t="s">
         <v>60</v>
       </c>
       <c r="E10">
-        <v>56.0</v>
+        <v>56</v>
       </c>
       <c r="F10">
-        <v>47.0</v>
+        <v>47</v>
       </c>
       <c r="G10">
         <v>9.4</v>
       </c>
       <c r="H10">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="I10">
-        <v>893.0</v>
+        <v>893</v>
       </c>
       <c r="J10">
-        <v>544.0</v>
+        <v>544</v>
       </c>
       <c r="K10">
-        <v>1437.0</v>
+        <v>1437</v>
       </c>
       <c r="L10">
-        <v>893.0</v>
+        <v>893</v>
       </c>
       <c r="O10" s="4"/>
     </row>
-    <row r="11" spans="1:16" dyDescent="0.2">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>2</v>
       </c>
       <c r="B11" s="8">
         <v>3</v>
       </c>
-      <c r="C11" t="s" s="2">
+      <c r="C11" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="D11" t="s" s="2">
+      <c r="D11" s="2" t="s">
         <v>52</v>
       </c>
       <c r="E11">
-        <v>173.0</v>
+        <v>173</v>
       </c>
       <c r="F11">
-        <v>131.0</v>
+        <v>131</v>
       </c>
       <c r="G11">
         <v>26.2</v>
@@ -1320,188 +1320,188 @@
         <v>6.6</v>
       </c>
       <c r="I11">
-        <v>2489.0</v>
+        <v>2489</v>
       </c>
       <c r="J11">
-        <v>1713.0</v>
+        <v>1713</v>
       </c>
       <c r="K11">
-        <v>4202.0</v>
+        <v>4202</v>
       </c>
       <c r="L11">
-        <v>2489.0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" dyDescent="0.2">
+        <v>2489</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>2</v>
       </c>
       <c r="B12" s="8">
         <v>4</v>
       </c>
-      <c r="C12" t="s" s="2">
+      <c r="C12" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="D12" t="s" s="1">
+      <c r="D12" s="1" t="s">
         <v>53</v>
       </c>
       <c r="E12">
-        <v>103.0</v>
+        <v>103</v>
       </c>
       <c r="F12">
-        <v>110.0</v>
+        <v>110</v>
       </c>
       <c r="G12">
-        <v>22.0</v>
+        <v>22</v>
       </c>
       <c r="H12">
         <v>4.7</v>
       </c>
       <c r="I12">
-        <v>2090.0</v>
+        <v>2090</v>
       </c>
       <c r="J12">
-        <v>945.0</v>
+        <v>945</v>
       </c>
       <c r="K12">
-        <v>3035.0</v>
+        <v>3035</v>
       </c>
       <c r="L12">
-        <v>2090.0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" dyDescent="0.2">
+        <v>2090</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>2</v>
       </c>
       <c r="B13" s="8">
         <v>5</v>
       </c>
-      <c r="C13" t="s" s="2">
+      <c r="C13" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="D13" t="s" s="1">
+      <c r="D13" s="1" t="s">
         <v>54</v>
       </c>
       <c r="E13">
-        <v>89.0</v>
+        <v>89</v>
       </c>
       <c r="F13">
-        <v>80.0</v>
+        <v>80</v>
       </c>
       <c r="G13">
-        <v>16.0</v>
+        <v>16</v>
       </c>
       <c r="H13">
         <v>5.6</v>
       </c>
       <c r="I13">
-        <v>1520.0</v>
+        <v>1520</v>
       </c>
       <c r="J13">
-        <v>852.0</v>
+        <v>852</v>
       </c>
       <c r="K13">
-        <v>2372.0</v>
+        <v>2372</v>
       </c>
       <c r="L13">
-        <v>1520.0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" dyDescent="0.2">
+        <v>1520</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>2</v>
       </c>
       <c r="B14" s="8">
         <v>6</v>
       </c>
-      <c r="C14" t="s" s="2">
+      <c r="C14" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="D14" t="s" s="1">
+      <c r="D14" s="1" t="s">
         <v>55</v>
       </c>
       <c r="E14">
-        <v>100.0</v>
+        <v>100</v>
       </c>
       <c r="F14">
-        <v>98.0</v>
+        <v>98</v>
       </c>
       <c r="G14">
-        <v>19.6</v>
+        <v>19.600000000000001</v>
       </c>
       <c r="H14">
-        <v>5.1</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="I14">
-        <v>1862.0</v>
+        <v>1862</v>
       </c>
       <c r="J14">
-        <v>938.0</v>
+        <v>938</v>
       </c>
       <c r="K14">
-        <v>2800.0</v>
+        <v>2800</v>
       </c>
       <c r="L14">
-        <v>1862.0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" dyDescent="0.2">
+        <v>1862</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>2</v>
       </c>
       <c r="B15" s="8">
         <v>7</v>
       </c>
-      <c r="C15" t="s" s="2">
+      <c r="C15" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="D15" t="s" s="11">
+      <c r="D15" s="11" t="s">
         <v>56</v>
       </c>
       <c r="E15">
-        <v>138.0</v>
+        <v>138</v>
       </c>
       <c r="F15">
-        <v>151.0</v>
+        <v>151</v>
       </c>
       <c r="G15">
         <v>30.2</v>
       </c>
       <c r="H15">
-        <v>4.6</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="I15">
-        <v>2869.0</v>
+        <v>2869</v>
       </c>
       <c r="J15">
-        <v>1258.0</v>
+        <v>1258</v>
       </c>
       <c r="K15">
-        <v>4127.0</v>
+        <v>4127</v>
       </c>
       <c r="L15">
-        <v>2869.0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" dyDescent="0.2">
+        <v>2869</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A16">
         <v>2</v>
       </c>
       <c r="B16" s="8">
         <v>8</v>
       </c>
-      <c r="C16" t="s" s="2">
+      <c r="C16" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="D16" t="s" s="1">
+      <c r="D16" s="1" t="s">
         <v>59</v>
       </c>
       <c r="E16">
-        <v>339.0</v>
+        <v>339</v>
       </c>
       <c r="F16">
-        <v>359.0</v>
+        <v>359</v>
       </c>
       <c r="G16">
         <v>71.8</v>
@@ -1510,36 +1510,36 @@
         <v>4.7</v>
       </c>
       <c r="I16">
-        <v>6821.0</v>
+        <v>6821</v>
       </c>
       <c r="J16">
-        <v>3117.0</v>
+        <v>3117</v>
       </c>
       <c r="K16">
-        <v>9938.0</v>
+        <v>9938</v>
       </c>
       <c r="L16">
-        <v>6821.0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" dyDescent="0.2">
+        <v>6821</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A17">
         <v>2</v>
       </c>
       <c r="B17" s="8">
         <v>9</v>
       </c>
-      <c r="C17" t="s" s="2">
+      <c r="C17" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="D17" t="s" s="1">
+      <c r="D17" s="1" t="s">
         <v>58</v>
       </c>
       <c r="E17">
-        <v>87.0</v>
+        <v>87</v>
       </c>
       <c r="F17">
-        <v>76.0</v>
+        <v>76</v>
       </c>
       <c r="G17">
         <v>15.2</v>
@@ -1548,150 +1548,150 @@
         <v>5.7</v>
       </c>
       <c r="I17">
-        <v>1444.0</v>
+        <v>1444</v>
       </c>
       <c r="J17">
-        <v>838.0</v>
+        <v>838</v>
       </c>
       <c r="K17">
-        <v>2282.0</v>
+        <v>2282</v>
       </c>
       <c r="L17">
-        <v>1444.0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" dyDescent="0.2">
+        <v>1444</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A18">
         <v>2</v>
       </c>
       <c r="B18" s="8">
         <v>10</v>
       </c>
-      <c r="C18" t="s" s="2">
+      <c r="C18" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="D18" t="s" s="1">
+      <c r="D18" s="1" t="s">
         <v>60</v>
       </c>
       <c r="E18">
-        <v>218.0</v>
+        <v>218</v>
       </c>
       <c r="F18">
-        <v>217.0</v>
+        <v>217</v>
       </c>
       <c r="G18">
         <v>43.4</v>
       </c>
       <c r="H18">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="I18">
-        <v>4123.0</v>
+        <v>4123</v>
       </c>
       <c r="J18">
-        <v>2037.0</v>
+        <v>2037</v>
       </c>
       <c r="K18">
-        <v>6160.0</v>
+        <v>6160</v>
       </c>
       <c r="L18">
-        <v>4123.0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" dyDescent="0.2">
+        <v>4123</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A19">
         <v>3</v>
       </c>
       <c r="B19" s="8">
         <v>4</v>
       </c>
-      <c r="C19" t="s" s="2">
+      <c r="C19" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D19" t="s" s="1">
+      <c r="D19" s="1" t="s">
         <v>53</v>
       </c>
       <c r="E19">
-        <v>215.0</v>
+        <v>215</v>
       </c>
       <c r="F19">
-        <v>77.0</v>
+        <v>77</v>
       </c>
       <c r="G19">
         <v>15.4</v>
       </c>
       <c r="H19">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="I19">
-        <v>1463.0</v>
+        <v>1463</v>
       </c>
       <c r="J19">
-        <v>2329.0</v>
+        <v>2329</v>
       </c>
       <c r="K19">
-        <v>3792.0</v>
+        <v>3792</v>
       </c>
       <c r="L19">
-        <v>2329.0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" dyDescent="0.2">
+        <v>2329</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A20">
         <v>3</v>
       </c>
       <c r="B20" s="8">
         <v>5</v>
       </c>
-      <c r="C20" t="s" s="2">
+      <c r="C20" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D20" t="s" s="1">
+      <c r="D20" s="1" t="s">
         <v>54</v>
       </c>
       <c r="E20">
-        <v>113.0</v>
+        <v>113</v>
       </c>
       <c r="F20">
-        <v>63.0</v>
+        <v>63</v>
       </c>
       <c r="G20">
         <v>12.6</v>
       </c>
       <c r="H20">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="I20">
-        <v>1197.0</v>
+        <v>1197</v>
       </c>
       <c r="J20">
-        <v>1171.0</v>
+        <v>1171</v>
       </c>
       <c r="K20">
-        <v>2368.0</v>
+        <v>2368</v>
       </c>
       <c r="L20">
-        <v>1197.0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" dyDescent="0.2">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A21">
         <v>3</v>
       </c>
       <c r="B21" s="8">
         <v>6</v>
       </c>
-      <c r="C21" t="s" s="2">
+      <c r="C21" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D21" t="s" s="1">
+      <c r="D21" s="1" t="s">
         <v>55</v>
       </c>
       <c r="E21">
-        <v>192.0</v>
+        <v>192</v>
       </c>
       <c r="F21">
-        <v>126.0</v>
+        <v>126</v>
       </c>
       <c r="G21">
         <v>25.2</v>
@@ -1700,36 +1700,36 @@
         <v>7.6</v>
       </c>
       <c r="I21">
-        <v>2394.0</v>
+        <v>2394</v>
       </c>
       <c r="J21">
-        <v>1946.0</v>
+        <v>1946</v>
       </c>
       <c r="K21">
-        <v>4340.0</v>
+        <v>4340</v>
       </c>
       <c r="L21">
-        <v>2394.0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" dyDescent="0.2">
+        <v>2394</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A22">
         <v>3</v>
       </c>
       <c r="B22" s="8">
         <v>7</v>
       </c>
-      <c r="C22" t="s" s="2">
+      <c r="C22" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D22" t="s" s="11">
+      <c r="D22" s="11" t="s">
         <v>56</v>
       </c>
       <c r="E22">
-        <v>250.0</v>
+        <v>250</v>
       </c>
       <c r="F22">
-        <v>167.0</v>
+        <v>167</v>
       </c>
       <c r="G22">
         <v>33.4</v>
@@ -1738,74 +1738,74 @@
         <v>7.5</v>
       </c>
       <c r="I22">
-        <v>3173.0</v>
+        <v>3173</v>
       </c>
       <c r="J22">
-        <v>2527.0</v>
+        <v>2527</v>
       </c>
       <c r="K22">
-        <v>5700.0</v>
+        <v>5700</v>
       </c>
       <c r="L22">
-        <v>3173.0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" dyDescent="0.2">
+        <v>3173</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A23">
         <v>3</v>
       </c>
       <c r="B23" s="8">
         <v>8</v>
       </c>
-      <c r="C23" t="s" s="2">
+      <c r="C23" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D23" t="s" s="1">
+      <c r="D23" s="1" t="s">
         <v>59</v>
       </c>
       <c r="E23">
-        <v>234.0</v>
+        <v>234</v>
       </c>
       <c r="F23">
-        <v>230.0</v>
+        <v>230</v>
       </c>
       <c r="G23">
-        <v>46.0</v>
+        <v>46</v>
       </c>
       <c r="H23">
-        <v>5.1</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="I23">
-        <v>4370.0</v>
+        <v>4370</v>
       </c>
       <c r="J23">
-        <v>2193.0</v>
+        <v>2193</v>
       </c>
       <c r="K23">
-        <v>6563.0</v>
+        <v>6563</v>
       </c>
       <c r="L23">
-        <v>4370.0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" dyDescent="0.2">
+        <v>4370</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A24">
         <v>3</v>
       </c>
       <c r="B24" s="8">
         <v>9</v>
       </c>
-      <c r="C24" t="s" s="2">
+      <c r="C24" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D24" t="s" s="1">
+      <c r="D24" s="1" t="s">
         <v>58</v>
       </c>
       <c r="E24">
-        <v>217.0</v>
+        <v>217</v>
       </c>
       <c r="F24">
-        <v>138.0</v>
+        <v>138</v>
       </c>
       <c r="G24">
         <v>27.6</v>
@@ -1814,416 +1814,416 @@
         <v>7.9</v>
       </c>
       <c r="I24">
-        <v>2622.0</v>
+        <v>2622</v>
       </c>
       <c r="J24">
-        <v>2210.0</v>
+        <v>2210</v>
       </c>
       <c r="K24">
-        <v>4832.0</v>
+        <v>4832</v>
       </c>
       <c r="L24">
-        <v>2622.0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" dyDescent="0.2">
+        <v>2622</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A25">
         <v>3</v>
       </c>
       <c r="B25" s="8">
         <v>10</v>
       </c>
-      <c r="C25" t="s" s="2">
+      <c r="C25" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D25" t="s" s="1">
+      <c r="D25" s="1" t="s">
         <v>60</v>
       </c>
       <c r="E25">
-        <v>108.0</v>
+        <v>108</v>
       </c>
       <c r="F25">
-        <v>92.0</v>
+        <v>92</v>
       </c>
       <c r="G25">
-        <v>18.4</v>
+        <v>18.399999999999999</v>
       </c>
       <c r="H25">
         <v>5.9</v>
       </c>
       <c r="I25">
-        <v>1748.0</v>
+        <v>1748</v>
       </c>
       <c r="J25">
-        <v>1045.0</v>
+        <v>1045</v>
       </c>
       <c r="K25">
-        <v>2793.0</v>
+        <v>2793</v>
       </c>
       <c r="L25">
-        <v>1748.0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" dyDescent="0.2">
+        <v>1748</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A26">
         <v>4</v>
       </c>
       <c r="B26" s="8">
         <v>5</v>
       </c>
-      <c r="C26" t="s" s="1">
+      <c r="C26" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D26" t="s" s="1">
+      <c r="D26" s="1" t="s">
         <v>54</v>
       </c>
       <c r="E26">
-        <v>130.0</v>
+        <v>130</v>
       </c>
       <c r="F26">
-        <v>93.0</v>
+        <v>93</v>
       </c>
       <c r="G26">
-        <v>18.6</v>
+        <v>18.600000000000001</v>
       </c>
       <c r="H26">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="I26">
-        <v>1767.0</v>
+        <v>1767</v>
       </c>
       <c r="J26">
-        <v>1300.0</v>
+        <v>1300</v>
       </c>
       <c r="K26">
-        <v>3067.0</v>
+        <v>3067</v>
       </c>
       <c r="L26">
-        <v>1767.0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" dyDescent="0.2">
+        <v>1767</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A27">
         <v>4</v>
       </c>
       <c r="B27" s="8">
         <v>6</v>
       </c>
-      <c r="C27" t="s" s="1">
+      <c r="C27" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D27" t="s" s="1">
+      <c r="D27" s="1" t="s">
         <v>55</v>
       </c>
       <c r="E27">
-        <v>149.0</v>
+        <v>149</v>
       </c>
       <c r="F27">
-        <v>161.0</v>
+        <v>161</v>
       </c>
       <c r="G27">
-        <v>32.2</v>
+        <v>32.200000000000003</v>
       </c>
       <c r="H27">
-        <v>4.6</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="I27">
-        <v>3059.0</v>
+        <v>3059</v>
       </c>
       <c r="J27">
-        <v>1363.0</v>
+        <v>1363</v>
       </c>
       <c r="K27">
-        <v>4422.0</v>
+        <v>4422</v>
       </c>
       <c r="L27">
-        <v>3059.0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" dyDescent="0.2">
+        <v>3059</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A28">
         <v>4</v>
       </c>
       <c r="B28" s="8">
         <v>7</v>
       </c>
-      <c r="C28" t="s" s="1">
+      <c r="C28" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D28" t="s" s="11">
+      <c r="D28" s="11" t="s">
         <v>56</v>
       </c>
       <c r="E28">
-        <v>93.0</v>
+        <v>93</v>
       </c>
       <c r="F28">
-        <v>90.0</v>
+        <v>90</v>
       </c>
       <c r="G28">
-        <v>18.0</v>
+        <v>18</v>
       </c>
       <c r="H28">
         <v>5.2</v>
       </c>
       <c r="I28">
-        <v>1710.0</v>
+        <v>1710</v>
       </c>
       <c r="J28">
-        <v>875.0</v>
+        <v>875</v>
       </c>
       <c r="K28">
-        <v>2585.0</v>
+        <v>2585</v>
       </c>
       <c r="L28">
-        <v>1710.0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" dyDescent="0.2">
+        <v>1710</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A29">
         <v>4</v>
       </c>
       <c r="B29" s="8">
         <v>8</v>
       </c>
-      <c r="C29" t="s" s="1">
+      <c r="C29" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D29" t="s" s="1">
+      <c r="D29" s="1" t="s">
         <v>59</v>
       </c>
       <c r="E29">
-        <v>380.0</v>
+        <v>380</v>
       </c>
       <c r="F29">
-        <v>290.0</v>
+        <v>290</v>
       </c>
       <c r="G29">
-        <v>58.0</v>
+        <v>58</v>
       </c>
       <c r="H29">
         <v>6.6</v>
       </c>
       <c r="I29">
-        <v>5510.0</v>
+        <v>5510</v>
       </c>
       <c r="J29">
-        <v>3757.0</v>
+        <v>3757</v>
       </c>
       <c r="K29">
-        <v>9267.0</v>
+        <v>9267</v>
       </c>
       <c r="L29">
-        <v>5510.0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16" dyDescent="0.2">
+        <v>5510</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A30">
         <v>4</v>
       </c>
       <c r="B30" s="8">
         <v>9</v>
       </c>
-      <c r="C30" t="s" s="1">
+      <c r="C30" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D30" t="s" s="1">
+      <c r="D30" s="1" t="s">
         <v>58</v>
       </c>
       <c r="E30">
-        <v>87.0</v>
+        <v>87</v>
       </c>
       <c r="F30">
-        <v>75.0</v>
+        <v>75</v>
       </c>
       <c r="G30">
-        <v>15.0</v>
+        <v>15</v>
       </c>
       <c r="H30">
         <v>5.8</v>
       </c>
       <c r="I30">
-        <v>1425.0</v>
+        <v>1425</v>
       </c>
       <c r="J30">
-        <v>840.0</v>
+        <v>840</v>
       </c>
       <c r="K30">
-        <v>2265.0</v>
+        <v>2265</v>
       </c>
       <c r="L30">
-        <v>1425.0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16" dyDescent="0.2">
+        <v>1425</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A31">
         <v>4</v>
       </c>
       <c r="B31" s="8">
         <v>10</v>
       </c>
-      <c r="C31" t="s" s="1">
+      <c r="C31" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D31" t="s" s="1">
+      <c r="D31" s="1" t="s">
         <v>60</v>
       </c>
       <c r="E31">
-        <v>259.0</v>
+        <v>259</v>
       </c>
       <c r="F31">
-        <v>125.0</v>
+        <v>125</v>
       </c>
       <c r="G31">
-        <v>25.0</v>
+        <v>25</v>
       </c>
       <c r="H31">
         <v>10.4</v>
       </c>
       <c r="I31">
-        <v>2375.0</v>
+        <v>2375</v>
       </c>
       <c r="J31">
-        <v>2730.0</v>
+        <v>2730</v>
       </c>
       <c r="K31">
-        <v>5105.0</v>
+        <v>5105</v>
       </c>
       <c r="L31">
-        <v>2730.0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16" dyDescent="0.2">
+        <v>2730</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A32">
         <v>5</v>
       </c>
       <c r="B32" s="8">
         <v>6</v>
       </c>
-      <c r="C32" t="s" s="1">
+      <c r="C32" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D32" t="s" s="1">
+      <c r="D32" s="1" t="s">
         <v>55</v>
       </c>
       <c r="E32">
-        <v>110.0</v>
+        <v>110</v>
       </c>
       <c r="F32">
-        <v>70.0</v>
+        <v>70</v>
       </c>
       <c r="G32">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="H32">
         <v>7.9</v>
       </c>
       <c r="I32">
-        <v>1330.0</v>
+        <v>1330</v>
       </c>
       <c r="J32">
-        <v>1120.0</v>
+        <v>1120</v>
       </c>
       <c r="K32">
-        <v>2450.0</v>
+        <v>2450</v>
       </c>
       <c r="L32">
-        <v>1330.0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" dyDescent="0.2">
+        <v>1330</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A33" s="10">
         <v>5</v>
       </c>
       <c r="B33" s="8">
         <v>7</v>
       </c>
-      <c r="C33" t="s" s="1">
+      <c r="C33" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D33" t="s" s="11">
+      <c r="D33" s="11" t="s">
         <v>56</v>
       </c>
       <c r="E33">
-        <v>168.0</v>
+        <v>168</v>
       </c>
       <c r="F33">
-        <v>173.0</v>
+        <v>173</v>
       </c>
       <c r="G33">
         <v>34.6</v>
       </c>
       <c r="H33">
-        <v>4.9</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="I33">
-        <v>3287.0</v>
+        <v>3287</v>
       </c>
       <c r="J33">
-        <v>1556.0</v>
+        <v>1556</v>
       </c>
       <c r="K33">
-        <v>4843.0</v>
+        <v>4843</v>
       </c>
       <c r="L33">
-        <v>3287.0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" dyDescent="0.2">
+        <v>3287</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A34">
         <v>5</v>
       </c>
       <c r="B34" s="8">
         <v>8</v>
       </c>
-      <c r="C34" t="s" s="1">
+      <c r="C34" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D34" t="s" s="1">
+      <c r="D34" s="1" t="s">
         <v>59</v>
       </c>
       <c r="E34">
-        <v>279.0</v>
+        <v>279</v>
       </c>
       <c r="F34">
-        <v>281.0</v>
+        <v>281</v>
       </c>
       <c r="G34">
         <v>56.2</v>
       </c>
       <c r="H34">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="I34">
-        <v>5339.0</v>
+        <v>5339</v>
       </c>
       <c r="J34">
-        <v>2599.0</v>
+        <v>2599</v>
       </c>
       <c r="K34">
-        <v>7938.0</v>
+        <v>7938</v>
       </c>
       <c r="L34">
-        <v>5339.0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" dyDescent="0.2">
+        <v>5339</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A35">
         <v>5</v>
       </c>
       <c r="B35" s="8">
         <v>9</v>
       </c>
-      <c r="C35" t="s" s="1">
+      <c r="C35" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D35" t="s" s="1">
+      <c r="D35" s="1" t="s">
         <v>58</v>
       </c>
       <c r="E35">
-        <v>136.0</v>
+        <v>136</v>
       </c>
       <c r="F35">
-        <v>118.0</v>
+        <v>118</v>
       </c>
       <c r="G35">
         <v>23.6</v>
@@ -2232,188 +2232,188 @@
         <v>5.8</v>
       </c>
       <c r="I35">
-        <v>2242.0</v>
+        <v>2242</v>
       </c>
       <c r="J35">
-        <v>1311.0</v>
+        <v>1311</v>
       </c>
       <c r="K35">
-        <v>3553.0</v>
+        <v>3553</v>
       </c>
       <c r="L35">
-        <v>2242.0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16" dyDescent="0.2">
+        <v>2242</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A36">
         <v>5</v>
       </c>
       <c r="B36" s="8">
         <v>10</v>
       </c>
-      <c r="C36" t="s" s="1">
+      <c r="C36" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D36" t="s" s="1">
+      <c r="D36" s="1" t="s">
         <v>60</v>
       </c>
       <c r="E36">
-        <v>158.0</v>
+        <v>158</v>
       </c>
       <c r="F36">
-        <v>155.0</v>
+        <v>155</v>
       </c>
       <c r="G36">
-        <v>31.0</v>
+        <v>31</v>
       </c>
       <c r="H36">
-        <v>5.1</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="I36">
-        <v>2945.0</v>
+        <v>2945</v>
       </c>
       <c r="J36">
-        <v>1482.0</v>
+        <v>1482</v>
       </c>
       <c r="K36">
-        <v>4427.0</v>
+        <v>4427</v>
       </c>
       <c r="L36">
-        <v>2945.0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16" dyDescent="0.2">
+        <v>2945</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A37">
         <v>6</v>
       </c>
       <c r="B37" s="8">
         <v>7</v>
       </c>
-      <c r="C37" t="s" s="1">
+      <c r="C37" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D37" t="s" s="11">
+      <c r="D37" s="11" t="s">
         <v>56</v>
       </c>
       <c r="E37">
-        <v>185.0</v>
+        <v>185</v>
       </c>
       <c r="F37">
-        <v>232.0</v>
+        <v>232</v>
       </c>
       <c r="G37">
         <v>46.4</v>
       </c>
       <c r="H37">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="I37">
-        <v>4408.0</v>
+        <v>4408</v>
       </c>
       <c r="J37">
-        <v>1617.0</v>
+        <v>1617</v>
       </c>
       <c r="K37">
-        <v>6025.0</v>
+        <v>6025</v>
       </c>
       <c r="L37">
-        <v>4408.0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:16" dyDescent="0.2">
+        <v>4408</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A38">
         <v>6</v>
       </c>
       <c r="B38" s="8">
         <v>8</v>
       </c>
-      <c r="C38" t="s" s="1">
+      <c r="C38" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D38" t="s" s="1">
+      <c r="D38" s="1" t="s">
         <v>59</v>
       </c>
       <c r="E38">
-        <v>358.0</v>
+        <v>358</v>
       </c>
       <c r="F38">
-        <v>315.0</v>
+        <v>315</v>
       </c>
       <c r="G38">
-        <v>63.0</v>
+        <v>63</v>
       </c>
       <c r="H38">
         <v>5.7</v>
       </c>
       <c r="I38">
-        <v>5985.0</v>
+        <v>5985</v>
       </c>
       <c r="J38">
-        <v>3442.0</v>
+        <v>3442</v>
       </c>
       <c r="K38">
-        <v>9427.0</v>
+        <v>9427</v>
       </c>
       <c r="L38">
-        <v>5985.0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16" dyDescent="0.2">
+        <v>5985</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A39">
         <v>6</v>
       </c>
       <c r="B39" s="8">
         <v>9</v>
       </c>
-      <c r="C39" t="s" s="1">
+      <c r="C39" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D39" t="s" s="1">
+      <c r="D39" s="1" t="s">
         <v>58</v>
       </c>
       <c r="E39">
-        <v>153.0</v>
+        <v>153</v>
       </c>
       <c r="F39">
-        <v>166.0</v>
+        <v>166</v>
       </c>
       <c r="G39">
-        <v>33.2</v>
+        <v>33.200000000000003</v>
       </c>
       <c r="H39">
-        <v>4.6</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="I39">
-        <v>3154.0</v>
+        <v>3154</v>
       </c>
       <c r="J39">
-        <v>1398.0</v>
+        <v>1398</v>
       </c>
       <c r="K39">
-        <v>4552.0</v>
+        <v>4552</v>
       </c>
       <c r="L39">
-        <v>3154.0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:16" dyDescent="0.2">
+        <v>3154</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A40">
         <v>6</v>
       </c>
       <c r="B40" s="8">
         <v>10</v>
       </c>
-      <c r="C40" t="s" s="1">
+      <c r="C40" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D40" t="s" s="1">
+      <c r="D40" s="1" t="s">
         <v>60</v>
       </c>
       <c r="E40">
-        <v>237.0</v>
+        <v>237</v>
       </c>
       <c r="F40">
-        <v>216.0</v>
+        <v>216</v>
       </c>
       <c r="G40">
         <v>43.2</v>
@@ -2422,188 +2422,188 @@
         <v>5.5</v>
       </c>
       <c r="I40">
-        <v>4104.0</v>
+        <v>4104</v>
       </c>
       <c r="J40">
-        <v>2261.0</v>
+        <v>2261</v>
       </c>
       <c r="K40">
-        <v>6365.0</v>
+        <v>6365</v>
       </c>
       <c r="L40">
-        <v>4104.0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:16" dyDescent="0.2">
+        <v>4104</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A41">
         <v>7</v>
       </c>
       <c r="B41" s="8">
         <v>8</v>
       </c>
-      <c r="C41" t="s" s="1">
+      <c r="C41" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="D41" t="s" s="1">
+      <c r="D41" s="1" t="s">
         <v>59</v>
       </c>
       <c r="E41">
-        <v>414.0</v>
+        <v>414</v>
       </c>
       <c r="F41">
-        <v>365.0</v>
+        <v>365</v>
       </c>
       <c r="G41">
-        <v>73.0</v>
+        <v>73</v>
       </c>
       <c r="H41">
         <v>5.7</v>
       </c>
       <c r="I41">
-        <v>6935.0</v>
+        <v>6935</v>
       </c>
       <c r="J41">
-        <v>3978.0</v>
+        <v>3978</v>
       </c>
       <c r="K41">
-        <v>10913.0</v>
+        <v>10913</v>
       </c>
       <c r="L41">
-        <v>6935.0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:16" dyDescent="0.2">
+        <v>6935</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A42">
         <v>7</v>
       </c>
       <c r="B42" s="8">
         <v>9</v>
       </c>
-      <c r="C42" t="s" s="1">
+      <c r="C42" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="D42" t="s" s="1">
+      <c r="D42" s="1" t="s">
         <v>58</v>
       </c>
       <c r="E42">
-        <v>70.0</v>
+        <v>70</v>
       </c>
       <c r="F42">
-        <v>75.0</v>
+        <v>75</v>
       </c>
       <c r="G42">
-        <v>15.0</v>
+        <v>15</v>
       </c>
       <c r="H42">
         <v>4.7</v>
       </c>
       <c r="I42">
-        <v>1425.0</v>
+        <v>1425</v>
       </c>
       <c r="J42">
-        <v>642.0</v>
+        <v>642</v>
       </c>
       <c r="K42">
-        <v>2067.0</v>
+        <v>2067</v>
       </c>
       <c r="L42">
-        <v>1425.0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:16" dyDescent="0.2">
+        <v>1425</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A43">
         <v>7</v>
       </c>
       <c r="B43" s="8">
         <v>10</v>
       </c>
-      <c r="C43" t="s" s="1">
+      <c r="C43" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="D43" t="s" s="1">
+      <c r="D43" s="1" t="s">
         <v>60</v>
       </c>
       <c r="E43">
-        <v>293.0</v>
+        <v>293</v>
       </c>
       <c r="F43">
-        <v>194.0</v>
+        <v>194</v>
       </c>
       <c r="G43">
-        <v>38.8</v>
+        <v>38.799999999999997</v>
       </c>
       <c r="H43">
         <v>7.6</v>
       </c>
       <c r="I43">
-        <v>3686.0</v>
+        <v>3686</v>
       </c>
       <c r="J43">
-        <v>2966.0</v>
+        <v>2966</v>
       </c>
       <c r="K43">
-        <v>6652.0</v>
+        <v>6652</v>
       </c>
       <c r="L43">
-        <v>3686.0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:16" dyDescent="0.2">
+        <v>3686</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A44">
         <v>8</v>
       </c>
       <c r="B44" s="8">
         <v>9</v>
       </c>
-      <c r="C44" t="s" s="1">
+      <c r="C44" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D44" t="s" s="1">
+      <c r="D44" s="1" t="s">
         <v>58</v>
       </c>
       <c r="E44">
-        <v>384.0</v>
+        <v>384</v>
       </c>
       <c r="F44">
-        <v>363.0</v>
+        <v>363</v>
       </c>
       <c r="G44">
-        <v>72.6</v>
+        <v>72.599999999999994</v>
       </c>
       <c r="H44">
         <v>5.3</v>
       </c>
       <c r="I44">
-        <v>6897.0</v>
+        <v>6897</v>
       </c>
       <c r="J44">
-        <v>3633.0</v>
+        <v>3633</v>
       </c>
       <c r="K44">
-        <v>10530.0</v>
+        <v>10530</v>
       </c>
       <c r="L44">
-        <v>6897.0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:16" dyDescent="0.2">
+        <v>6897</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A45">
         <v>8</v>
       </c>
       <c r="B45" s="8">
         <v>10</v>
       </c>
-      <c r="C45" t="s" s="1">
+      <c r="C45" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D45" t="s" s="1">
+      <c r="D45" s="1" t="s">
         <v>60</v>
       </c>
       <c r="E45">
-        <v>209.0</v>
+        <v>209</v>
       </c>
       <c r="F45">
-        <v>172.0</v>
+        <v>172</v>
       </c>
       <c r="G45">
         <v>34.4</v>
@@ -2612,57 +2612,57 @@
         <v>6.1</v>
       </c>
       <c r="I45">
-        <v>3268.0</v>
+        <v>3268</v>
       </c>
       <c r="J45">
-        <v>2037.0</v>
+        <v>2037</v>
       </c>
       <c r="K45">
-        <v>5305.0</v>
+        <v>5305</v>
       </c>
       <c r="L45">
-        <v>3268.0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:16" dyDescent="0.2">
+        <v>3268</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A46">
         <v>9</v>
       </c>
       <c r="B46" s="8">
         <v>10</v>
       </c>
-      <c r="C46" t="s" s="1">
+      <c r="C46" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D46" t="s" s="1">
+      <c r="D46" s="1" t="s">
         <v>60</v>
       </c>
       <c r="E46">
-        <v>264.0</v>
+        <v>264</v>
       </c>
       <c r="F46">
-        <v>200.0</v>
+        <v>200</v>
       </c>
       <c r="G46">
-        <v>40.0</v>
+        <v>40</v>
       </c>
       <c r="H46">
         <v>6.6</v>
       </c>
       <c r="I46">
-        <v>3800.0</v>
+        <v>3800</v>
       </c>
       <c r="J46">
-        <v>2613.0</v>
+        <v>2613</v>
       </c>
       <c r="K46">
-        <v>6413.0</v>
+        <v>6413</v>
       </c>
       <c r="L46">
-        <v>3800.0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:16" dyDescent="0.2">
+        <v>3800</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A47">
         <v>1</v>
       </c>
@@ -2696,7 +2696,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:16" dyDescent="0.2">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A48">
         <v>2</v>
       </c>
@@ -2730,7 +2730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:16" dyDescent="0.2">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A49">
         <v>3</v>
       </c>
@@ -2764,7 +2764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:16" dyDescent="0.2">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A50">
         <v>4</v>
       </c>
@@ -2798,7 +2798,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:16" dyDescent="0.2">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A51">
         <v>5</v>
       </c>
@@ -2832,7 +2832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:16" dyDescent="0.2">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A52">
         <v>6</v>
       </c>
@@ -2864,7 +2864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:16" dyDescent="0.2">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A53">
         <v>7</v>
       </c>
@@ -2896,7 +2896,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:16" dyDescent="0.2">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A54">
         <v>8</v>
       </c>
@@ -2928,7 +2928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:16" dyDescent="0.2">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A55">
         <v>9</v>
       </c>
@@ -2960,7 +2960,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:16" dyDescent="0.2">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A56">
         <v>10</v>
       </c>
@@ -2992,13 +2992,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:16" dyDescent="0.2">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.4">
       <c r="G57" s="2"/>
     </row>
-    <row r="58" spans="1:16" dyDescent="0.2">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.4">
       <c r="G58" s="1"/>
     </row>
-    <row r="59" spans="1:16" dyDescent="0.2">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.4">
       <c r="G59" s="1"/>
     </row>
   </sheetData>

--- a/inputData/Parameters.xlsx
+++ b/inputData/Parameters.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kapta\Documents\DTU\Speciale\GitHubFiles\inputData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF37B58F-311A-4129-870D-B253556C8BAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D8B4F36-188F-4430-BEA5-EDE57B764090}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="28800" windowHeight="15285" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
   </bookViews>
   <sheets>
     <sheet name="Parameters" sheetId="9" r:id="rId1"/>
@@ -647,18 +647,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B15C49E0-A7B4-734A-8962-DC2A879F4079}">
   <dimension ref="A1:D20"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.6640625" customWidth="1"/>
-    <col min="2" max="2" width="10.83203125" style="4"/>
+    <col min="1" max="1" width="22.625" customWidth="1"/>
+    <col min="2" max="2" width="10.875" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>20</v>
       </c>
@@ -669,7 +669,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -680,7 +680,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>45</v>
       </c>
@@ -691,7 +691,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -702,7 +702,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -713,7 +713,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -724,7 +724,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -736,7 +736,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>0</v>
       </c>
@@ -747,7 +747,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>1</v>
       </c>
@@ -758,7 +758,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>44</v>
       </c>
@@ -769,7 +769,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>2</v>
       </c>
@@ -780,7 +780,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>42</v>
       </c>
@@ -791,7 +791,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -803,7 +803,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>4</v>
       </c>
@@ -815,7 +815,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>5</v>
       </c>
@@ -827,7 +827,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>6</v>
       </c>
@@ -838,7 +838,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>41</v>
       </c>
@@ -858,17 +858,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAF0D5EA-53B5-1240-9D84-6FE223856A18}">
   <dimension ref="A1:P59"/>
-  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="10.625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="17.1640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="17.1640625" customWidth="1"/>
-    <col min="5" max="5" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.1640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="17.125" customWidth="1"/>
+    <col min="5" max="5" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
         <v>36</v>
       </c>
@@ -913,7 +913,7 @@
       </c>
       <c r="P1" s="6"/>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -960,7 +960,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1008,7 +1008,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1</v>
       </c>
@@ -1052,7 +1052,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>1</v>
       </c>
@@ -1099,7 +1099,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>1</v>
       </c>
@@ -1138,7 +1138,7 @@
       </c>
       <c r="O6" s="4"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>1</v>
       </c>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="O7" s="4"/>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>1</v>
       </c>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="O8" s="4"/>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>1</v>
       </c>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="O9" s="4"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>1</v>
       </c>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="O10" s="4"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>2</v>
       </c>
@@ -1332,7 +1332,7 @@
         <v>2489</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>2</v>
       </c>
@@ -1370,7 +1370,7 @@
         <v>2090</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>2</v>
       </c>
@@ -1408,7 +1408,7 @@
         <v>1520</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>2</v>
       </c>
@@ -1446,7 +1446,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>2</v>
       </c>
@@ -1484,7 +1484,7 @@
         <v>2869</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>2</v>
       </c>
@@ -1522,7 +1522,7 @@
         <v>6821</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>2</v>
       </c>
@@ -1560,7 +1560,7 @@
         <v>1444</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>2</v>
       </c>
@@ -1598,7 +1598,7 @@
         <v>4123</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>3</v>
       </c>
@@ -1636,7 +1636,7 @@
         <v>2329</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>3</v>
       </c>
@@ -1674,7 +1674,7 @@
         <v>1197</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>3</v>
       </c>
@@ -1712,7 +1712,7 @@
         <v>2394</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>3</v>
       </c>
@@ -1750,7 +1750,7 @@
         <v>3173</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>3</v>
       </c>
@@ -1788,7 +1788,7 @@
         <v>4370</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>3</v>
       </c>
@@ -1826,7 +1826,7 @@
         <v>2622</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>3</v>
       </c>
@@ -1864,7 +1864,7 @@
         <v>1748</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>4</v>
       </c>
@@ -1902,7 +1902,7 @@
         <v>1767</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>4</v>
       </c>
@@ -1940,7 +1940,7 @@
         <v>3059</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>4</v>
       </c>
@@ -1978,7 +1978,7 @@
         <v>1710</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>4</v>
       </c>
@@ -2016,7 +2016,7 @@
         <v>5510</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>4</v>
       </c>
@@ -2054,7 +2054,7 @@
         <v>1425</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>4</v>
       </c>
@@ -2092,7 +2092,7 @@
         <v>2730</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>5</v>
       </c>
@@ -2130,7 +2130,7 @@
         <v>1330</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" s="10">
         <v>5</v>
       </c>
@@ -2168,7 +2168,7 @@
         <v>3287</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>5</v>
       </c>
@@ -2206,7 +2206,7 @@
         <v>5339</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>5</v>
       </c>
@@ -2244,7 +2244,7 @@
         <v>2242</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>5</v>
       </c>
@@ -2282,7 +2282,7 @@
         <v>2945</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>6</v>
       </c>
@@ -2320,7 +2320,7 @@
         <v>4408</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>6</v>
       </c>
@@ -2358,7 +2358,7 @@
         <v>5985</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>6</v>
       </c>
@@ -2396,7 +2396,7 @@
         <v>3154</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>6</v>
       </c>
@@ -2434,7 +2434,7 @@
         <v>4104</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>7</v>
       </c>
@@ -2472,7 +2472,7 @@
         <v>6935</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>7</v>
       </c>
@@ -2510,7 +2510,7 @@
         <v>1425</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>7</v>
       </c>
@@ -2548,7 +2548,7 @@
         <v>3686</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>8</v>
       </c>
@@ -2586,7 +2586,7 @@
         <v>6897</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>8</v>
       </c>
@@ -2624,7 +2624,7 @@
         <v>3268</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>9</v>
       </c>
@@ -2662,7 +2662,7 @@
         <v>3800</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>1</v>
       </c>
@@ -2696,7 +2696,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>2</v>
       </c>
@@ -2730,7 +2730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>3</v>
       </c>
@@ -2764,7 +2764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>4</v>
       </c>
@@ -2798,7 +2798,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>5</v>
       </c>
@@ -2832,7 +2832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>6</v>
       </c>
@@ -2864,7 +2864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>7</v>
       </c>
@@ -2896,7 +2896,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>8</v>
       </c>
@@ -2928,7 +2928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>9</v>
       </c>
@@ -2960,7 +2960,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>10</v>
       </c>
@@ -2992,13 +2992,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="G57" s="2"/>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="G58" s="1"/>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="G59" s="1"/>
     </row>
   </sheetData>

--- a/inputData/Parameters.xlsx
+++ b/inputData/Parameters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kapta\Documents\DTU\Speciale\GitHubFiles\inputData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D8B4F36-188F-4430-BEA5-EDE57B764090}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92956B8D-EC89-438B-959C-6073760B8565}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1170" yWindow="1170" windowWidth="28800" windowHeight="15285" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
   </bookViews>

--- a/inputData/Parameters.xlsx
+++ b/inputData/Parameters.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sillewiberg/Desktop/Skole/Speciale/Master-Thesis-eVTOL-1/inputData/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5E5E19C-E433-3D4B-B2DE-3F609C62E196}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{285A916A-1F41-F247-83D3-EDA567740060}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14320" yWindow="500" windowWidth="14480" windowHeight="16340" activeTab="1" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
+    <workbookView xWindow="3780" yWindow="500" windowWidth="24100" windowHeight="16340" activeTab="1" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
   </bookViews>
   <sheets>
     <sheet name="Parameters" sheetId="9" r:id="rId1"/>
-    <sheet name="Prices" sheetId="12" r:id="rId2"/>
+    <sheet name="Prices" sheetId="13" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="64">
   <si>
     <t>cap_u</t>
   </si>
@@ -117,15 +117,6 @@
     <t>Hvor meget hurtigere</t>
   </si>
   <si>
-    <t>Fd km</t>
-  </si>
-  <si>
-    <t>Fd tid</t>
-  </si>
-  <si>
-    <t>fd max</t>
-  </si>
-  <si>
     <t>Passager km pris</t>
   </si>
   <si>
@@ -220,13 +211,35 @@
   </si>
   <si>
     <t>(56.049305, 12.584406)</t>
+  </si>
+  <si>
+    <t>Bil km</t>
+  </si>
+  <si>
+    <t>Pris (Bil udgift)</t>
+  </si>
+  <si>
+    <t>Færge (gns. Gælder kun Bornholm)</t>
+  </si>
+  <si>
+    <t>Base</t>
+  </si>
+  <si>
+    <t>Pris (udfra tidsbesparelse)</t>
+  </si>
+  <si>
+    <t>Km bil pris</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+  </numFmts>
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -254,13 +267,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <strike/>
       <sz val="12"/>
       <color theme="1"/>
@@ -274,16 +280,37 @@
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor theme="1"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -291,11 +318,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -304,19 +341,161 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Comma 2" xfId="1" xr:uid="{3F443CEB-12EE-CE40-919D-B2D7CC5BFB45}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="8">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -327,6 +506,35 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A5F7E4F6-7491-4341-B845-D9C56FE5CC4E}" name="Table13" displayName="Table13" ref="A1:N56" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6" headerRowCellStyle="Comma" dataCellStyle="Comma">
+  <autoFilter ref="A1:N56" xr:uid="{CEDCB4F7-0752-8449-BE87-89650C1E9E7C}"/>
+  <tableColumns count="14">
+    <tableColumn id="1" xr3:uid="{2A2695C6-A68E-C041-BC75-EFA31F851480}" name="From"/>
+    <tableColumn id="2" xr3:uid="{4C24D9BA-D998-1C4A-8BDD-9C74B2613626}" name="To" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{C153EFF4-EE60-214F-A0D9-CE4CBD6C1369}" name="cord_from"/>
+    <tableColumn id="4" xr3:uid="{0E692D3C-028D-854D-B6DC-0785857A89B2}" name="cord_to"/>
+    <tableColumn id="5" xr3:uid="{621A920E-8727-A84C-8354-C0314B894883}" name="Bil km"/>
+    <tableColumn id="6" xr3:uid="{05B8574E-549F-174E-A1BD-C32308BDD904}" name="Bil tid (min)"/>
+    <tableColumn id="7" xr3:uid="{34B264DD-E18C-BB44-A99F-AE468AD09318}" name="Km fugleflugt"/>
+    <tableColumn id="8" xr3:uid="{4ED8D766-18D9-2E4E-ABA8-5D82024DEF9E}" name="eVTOL flyvetid (min)"/>
+    <tableColumn id="9" xr3:uid="{6F2AA6F3-2957-8E4A-81D6-04A57CC27CB6}" name="Hvor meget hurtigere"/>
+    <tableColumn id="10" xr3:uid="{FC2DFE06-00B3-1248-BE67-9F4B24140294}" name="Pris (Bil udgift)" dataDxfId="4" dataCellStyle="Comma"/>
+    <tableColumn id="11" xr3:uid="{F02D0177-CA58-7D41-BEAD-61E4809519E9}" name="Færge (gns. Gælder kun Bornholm)" dataDxfId="3" dataCellStyle="Comma"/>
+    <tableColumn id="12" xr3:uid="{78168389-A3BA-2841-A18F-65C13542B373}" name="Base" dataDxfId="2" dataCellStyle="Comma">
+      <calculatedColumnFormula>$Q$5</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="13" xr3:uid="{2C989D0B-5016-2747-A74C-92EA5551800D}" name="Pris (udfra tidsbesparelse)" dataDxfId="1" dataCellStyle="Comma">
+      <calculatedColumnFormula>$Q$4*MAX(F2-G2*$Q$1)*$Q$3</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="14" xr3:uid="{9A2A4CEF-2EA6-0746-9778-A321DBFD7669}" name="fd_sum" dataDxfId="0" dataCellStyle="Comma">
+      <calculatedColumnFormula>SUM(J2:M2)</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -653,13 +861,13 @@
     <col min="2" max="2" width="10.83203125" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:4" dyDescent="0.2">
-      <c r="A2" t="s" s="1">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B2" s="4">
@@ -669,7 +877,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" dyDescent="0.2">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -680,18 +888,18 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:4" dyDescent="0.2">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B4" s="4">
         <v>400</v>
       </c>
       <c r="D4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" dyDescent="0.2">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -699,10 +907,10 @@
         <v>300</v>
       </c>
       <c r="D5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" dyDescent="0.2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -713,7 +921,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:4" dyDescent="0.2">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -724,7 +932,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:4" dyDescent="0.2">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -733,10 +941,10 @@
         <v>0.2</v>
       </c>
       <c r="D8" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" dyDescent="0.2">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>0</v>
       </c>
@@ -747,7 +955,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:4" dyDescent="0.2">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>1</v>
       </c>
@@ -758,9 +966,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:4" dyDescent="0.2">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B11" s="4">
         <v>80</v>
@@ -769,7 +977,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="12" spans="1:4" dyDescent="0.2">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>2</v>
       </c>
@@ -780,18 +988,18 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="13" spans="1:4" dyDescent="0.2">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B13" s="4">
         <v>20</v>
       </c>
-      <c r="D13" t="s" s="3">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" dyDescent="0.2">
+      <c r="D13" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -799,11 +1007,11 @@
         <f>2.11*B20</f>
         <v>2.11</v>
       </c>
-      <c r="D14" t="s" s="3">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" dyDescent="0.2">
+      <c r="D14" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>4</v>
       </c>
@@ -811,11 +1019,11 @@
         <f>30/B20</f>
         <v>30</v>
       </c>
-      <c r="D15" t="s" s="3">
+      <c r="D15" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:4" dyDescent="0.2">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>5</v>
       </c>
@@ -823,30 +1031,30 @@
         <f>20/B20</f>
         <v>20</v>
       </c>
-      <c r="D16" t="s" s="3">
+      <c r="D16" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:4" dyDescent="0.2">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>6</v>
       </c>
       <c r="B17" s="4">
         <v>120</v>
       </c>
-      <c r="D17" t="s" s="3">
+      <c r="D17" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:4" dyDescent="0.2">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B20" s="4">
         <v>1</v>
       </c>
-      <c r="D20" t="s" s="3">
-        <v>47</v>
+      <c r="D20" s="3" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -856,1821 +1064,2331 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAF0D5EA-53B5-1240-9D84-6FE223856A18}">
-  <dimension ref="A1:P59"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DADB4178-B179-4149-B262-7E1BF5344AD4}">
+  <dimension ref="A1:R56"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="17.1640625" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="17.1640625" customWidth="1"/>
     <col min="5" max="5" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5" customWidth="1"/>
     <col min="7" max="7" width="17.1640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.33203125" customWidth="1"/>
+    <col min="9" max="9" width="21" style="10" customWidth="1"/>
+    <col min="10" max="10" width="13.6640625" style="10" customWidth="1"/>
+    <col min="11" max="11" width="32.1640625" style="10" customWidth="1"/>
+    <col min="12" max="12" width="10.6640625" style="10"/>
+    <col min="13" max="13" width="27" style="10" customWidth="1"/>
+    <col min="14" max="14" width="10.83203125" style="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" dyDescent="0.2">
-      <c r="A1" t="s" s="9">
-        <v>36</v>
-      </c>
-      <c r="B1" t="s" s="5">
-        <v>37</v>
-      </c>
-      <c r="C1" t="s" s="5">
-        <v>48</v>
-      </c>
-      <c r="D1" t="s" s="5">
-        <v>49</v>
-      </c>
-      <c r="E1" t="s" s="5">
+    <row r="1" spans="1:18" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="E1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F1" t="s">
         <v>22</v>
       </c>
-      <c r="F1" t="s" s="5">
+      <c r="G1" t="s">
         <v>23</v>
       </c>
-      <c r="G1" t="s" s="5">
+      <c r="H1" t="s">
         <v>24</v>
       </c>
-      <c r="H1" t="s" s="5">
+      <c r="I1" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="I1" t="s" s="5">
-        <v>26</v>
-      </c>
-      <c r="J1" t="s" s="5">
-        <v>27</v>
-      </c>
-      <c r="K1" t="s" s="5">
-        <v>38</v>
-      </c>
-      <c r="L1" t="s" s="5">
-        <v>28</v>
-      </c>
-      <c r="N1" t="s" s="6">
+      <c r="J1" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="K1" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="L1" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="M1" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="N1" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="P1" t="s">
         <v>19</v>
       </c>
-      <c r="O1" s="7">
+      <c r="Q1">
         <v>0.2</v>
       </c>
-      <c r="P1" s="6"/>
-    </row>
-    <row r="2" spans="1:16" dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="8">
+      <c r="B2" s="6">
         <v>2</v>
       </c>
-      <c r="C2" t="s" s="1">
-        <v>50</v>
-      </c>
-      <c r="D2" t="s" s="2">
-        <v>51</v>
+      <c r="C2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="E2">
-        <v>185.0</v>
+        <v>267</v>
       </c>
       <c r="F2">
-        <v>219.0</v>
+        <v>185</v>
       </c>
       <c r="G2">
+        <v>219</v>
+      </c>
+      <c r="H2">
         <v>43.8</v>
       </c>
-      <c r="H2">
+      <c r="I2">
         <v>4.2</v>
       </c>
-      <c r="I2">
-        <v>4161.0</v>
-      </c>
-      <c r="J2">
-        <v>1647.0</v>
-      </c>
-      <c r="K2">
-        <v>5808.0</v>
-      </c>
-      <c r="L2">
-        <v>4161.0</v>
-      </c>
-      <c r="N2" t="s">
-        <v>29</v>
-      </c>
-      <c r="O2" s="4">
-        <v>19</v>
+      <c r="J2" s="10">
+        <f>$Q$6*E2</f>
+        <v>801</v>
+      </c>
+      <c r="K2" s="10">
+        <f>IF(A2=8,250,0)+IF(B2=8,250,0)</f>
+        <v>0</v>
+      </c>
+      <c r="L2" s="10">
+        <f>$Q$5</f>
+        <v>500</v>
+      </c>
+      <c r="M2" s="10">
+        <f>$Q$4*MAX(F2-G2*$Q$1)*$Q$3</f>
+        <v>941.33333333333326</v>
+      </c>
+      <c r="N2" s="10">
+        <f>SUM(J2:M2)</f>
+        <v>2242.333333333333</v>
       </c>
       <c r="P2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" dyDescent="0.2">
+        <v>26</v>
+      </c>
+      <c r="Q2">
+        <v>16</v>
+      </c>
+      <c r="R2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>1</v>
       </c>
-      <c r="B3" s="8">
+      <c r="B3" s="6">
         <v>3</v>
       </c>
-      <c r="C3" t="s" s="1">
-        <v>50</v>
-      </c>
-      <c r="D3" t="s" s="2">
-        <v>52</v>
+      <c r="C3" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>49</v>
       </c>
       <c r="E3">
-        <v>82.0</v>
+        <v>100</v>
       </c>
       <c r="F3">
-        <v>88.0</v>
+        <v>82</v>
       </c>
       <c r="G3">
-        <v>17.6</v>
+        <v>88</v>
       </c>
       <c r="H3">
+        <v>17.600000000000001</v>
+      </c>
+      <c r="I3">
         <v>4.7</v>
       </c>
-      <c r="I3">
-        <v>1672.0</v>
-      </c>
-      <c r="J3">
-        <v>751.0</v>
-      </c>
-      <c r="K3">
-        <v>2423.0</v>
-      </c>
-      <c r="L3">
-        <v>1672.0</v>
-      </c>
-      <c r="N3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O3" s="4">
-        <f>1000/60</f>
-        <v>16.666666666666668</v>
+      <c r="J3" s="10">
+        <f t="shared" ref="J3:J46" si="0">$Q$6*E3</f>
+        <v>300</v>
+      </c>
+      <c r="K3" s="10">
+        <f t="shared" ref="K3:K46" si="1">IF(A3=8,250,0)+IF(B3=8,250,0)</f>
+        <v>0</v>
+      </c>
+      <c r="L3" s="10">
+        <f t="shared" ref="L3:L46" si="2">$Q$5</f>
+        <v>500</v>
+      </c>
+      <c r="M3" s="10">
+        <f t="shared" ref="M3:M46" si="3">$Q$4*MAX(F3-G3*$Q$1)*$Q$3</f>
+        <v>429.33333333333337</v>
+      </c>
+      <c r="N3" s="10">
+        <f t="shared" ref="N3:N46" si="4">SUM(J3:M3)</f>
+        <v>1229.3333333333335</v>
       </c>
       <c r="P3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" dyDescent="0.2">
+        <v>28</v>
+      </c>
+      <c r="Q3">
+        <f>800/60</f>
+        <v>13.333333333333334</v>
+      </c>
+      <c r="R3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>1</v>
       </c>
-      <c r="B4" s="8">
+      <c r="B4" s="6">
         <v>4</v>
       </c>
-      <c r="C4" t="s" s="1">
+      <c r="C4" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D4" t="s" s="1">
-        <v>53</v>
-      </c>
       <c r="E4">
-        <v>228.0</v>
+        <v>347</v>
       </c>
       <c r="F4">
-        <v>147.0</v>
+        <v>228</v>
       </c>
       <c r="G4">
+        <v>147</v>
+      </c>
+      <c r="H4">
         <v>29.4</v>
       </c>
-      <c r="H4">
+      <c r="I4">
         <v>7.8</v>
       </c>
-      <c r="I4">
-        <v>2793.0</v>
-      </c>
-      <c r="J4">
-        <v>2317.0</v>
-      </c>
-      <c r="K4">
-        <v>5110.0</v>
-      </c>
-      <c r="L4">
-        <v>2793.0</v>
-      </c>
-      <c r="N4" t="s">
-        <v>33</v>
-      </c>
-      <c r="O4" s="4">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" dyDescent="0.2">
+      <c r="J4" s="10">
+        <f t="shared" si="0"/>
+        <v>1041</v>
+      </c>
+      <c r="K4" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L4" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M4" s="10">
+        <f>$Q$4*MAX(F4-G4*$Q$1)*$Q$3</f>
+        <v>1324</v>
+      </c>
+      <c r="N4" s="10">
+        <f>SUM(J4:M4)</f>
+        <v>2865</v>
+      </c>
+      <c r="P4" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q4">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>1</v>
       </c>
-      <c r="B5" s="8">
+      <c r="B5" s="6">
         <v>5</v>
       </c>
-      <c r="C5" t="s" s="1">
-        <v>50</v>
-      </c>
-      <c r="D5" t="s" s="1">
-        <v>54</v>
+      <c r="C5" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>51</v>
       </c>
       <c r="E5">
-        <v>126.0</v>
+        <v>177</v>
       </c>
       <c r="F5">
-        <v>147.0</v>
+        <v>126</v>
       </c>
       <c r="G5">
+        <v>147</v>
+      </c>
+      <c r="H5">
         <v>29.4</v>
       </c>
-      <c r="H5">
+      <c r="I5">
         <v>4.3</v>
       </c>
-      <c r="I5">
-        <v>2793.0</v>
-      </c>
-      <c r="J5">
-        <v>1127.0</v>
-      </c>
-      <c r="K5">
-        <v>3920.0</v>
-      </c>
-      <c r="L5">
-        <v>2793.0</v>
-      </c>
-      <c r="N5" t="s">
-        <v>34</v>
-      </c>
-      <c r="O5" s="4">
-        <v>0</v>
+      <c r="J5" s="10">
+        <f>$Q$6*E5</f>
+        <v>531</v>
+      </c>
+      <c r="K5" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L5" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M5" s="10">
+        <f>$Q$4*MAX(F5-G5*$Q$1)*$Q$3</f>
+        <v>644</v>
+      </c>
+      <c r="N5" s="10">
+        <f t="shared" si="4"/>
+        <v>1675</v>
       </c>
       <c r="P5" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" dyDescent="0.2">
+        <v>31</v>
+      </c>
+      <c r="Q5">
+        <v>500</v>
+      </c>
+      <c r="R5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>1</v>
       </c>
-      <c r="B6" s="8">
+      <c r="B6" s="6">
         <v>6</v>
       </c>
-      <c r="C6" t="s" s="1">
-        <v>50</v>
-      </c>
-      <c r="D6" t="s" s="1">
-        <v>55</v>
+      <c r="C6" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>52</v>
       </c>
       <c r="E6">
-        <v>205.0</v>
+        <v>325</v>
       </c>
       <c r="F6">
-        <v>197.0</v>
+        <v>205</v>
       </c>
       <c r="G6">
+        <v>197</v>
+      </c>
+      <c r="H6">
         <v>39.4</v>
       </c>
-      <c r="H6">
+      <c r="I6">
         <v>5.2</v>
       </c>
-      <c r="I6">
-        <v>3743.0</v>
-      </c>
-      <c r="J6">
-        <v>1932.0</v>
-      </c>
-      <c r="K6">
-        <v>5675.0</v>
-      </c>
-      <c r="L6">
-        <v>3743.0</v>
-      </c>
-      <c r="O6" s="4"/>
-    </row>
-    <row r="7" spans="1:16" dyDescent="0.2">
+      <c r="J6" s="10">
+        <f t="shared" si="0"/>
+        <v>975</v>
+      </c>
+      <c r="K6" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L6" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M6" s="10">
+        <f t="shared" si="3"/>
+        <v>1104</v>
+      </c>
+      <c r="N6" s="10">
+        <f t="shared" si="4"/>
+        <v>2579</v>
+      </c>
+      <c r="P6" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q6">
+        <v>3</v>
+      </c>
+      <c r="R6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>1</v>
       </c>
-      <c r="B7" s="8">
+      <c r="B7" s="6">
         <v>7</v>
       </c>
-      <c r="C7" t="s" s="1">
-        <v>50</v>
-      </c>
-      <c r="D7" t="s" s="1">
-        <v>56</v>
+      <c r="C7" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>53</v>
       </c>
       <c r="E7">
-        <v>263.0</v>
+        <v>415</v>
       </c>
       <c r="F7">
-        <v>227.0</v>
+        <v>263</v>
       </c>
       <c r="G7">
+        <v>227</v>
+      </c>
+      <c r="H7">
         <v>45.4</v>
       </c>
-      <c r="H7">
+      <c r="I7">
         <v>5.8</v>
       </c>
-      <c r="I7">
-        <v>4313.0</v>
-      </c>
-      <c r="J7">
-        <v>2539.0</v>
-      </c>
-      <c r="K7">
-        <v>6852.0</v>
-      </c>
-      <c r="L7">
-        <v>4313.0</v>
-      </c>
-      <c r="O7" s="4"/>
-    </row>
-    <row r="8" spans="1:16" dyDescent="0.2">
+      <c r="J7" s="10">
+        <f t="shared" si="0"/>
+        <v>1245</v>
+      </c>
+      <c r="K7" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L7" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M7" s="10">
+        <f t="shared" si="3"/>
+        <v>1450.6666666666667</v>
+      </c>
+      <c r="N7" s="10">
+        <f t="shared" si="4"/>
+        <v>3195.666666666667</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>1</v>
       </c>
-      <c r="B8" s="8">
+      <c r="B8" s="6">
         <v>8</v>
       </c>
-      <c r="C8" t="s" s="1">
-        <v>50</v>
-      </c>
-      <c r="D8" t="s" s="1">
-        <v>59</v>
+      <c r="C8" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>56</v>
       </c>
       <c r="E8">
-        <v>156.0</v>
+        <v>160</v>
       </c>
       <c r="F8">
-        <v>144.0</v>
+        <v>246</v>
       </c>
       <c r="G8">
+        <v>144</v>
+      </c>
+      <c r="H8">
         <v>28.8</v>
       </c>
-      <c r="H8">
-        <v>5.4</v>
-      </c>
       <c r="I8">
-        <v>2736.0</v>
-      </c>
-      <c r="J8">
-        <v>1484.0</v>
-      </c>
-      <c r="K8">
-        <v>4220.0</v>
-      </c>
-      <c r="L8">
-        <v>2736.0</v>
-      </c>
-      <c r="O8" s="4"/>
-    </row>
-    <row r="9" spans="1:16" dyDescent="0.2">
+        <v>8.5</v>
+      </c>
+      <c r="J8" s="10">
+        <f t="shared" si="0"/>
+        <v>480</v>
+      </c>
+      <c r="K8" s="10">
+        <f t="shared" si="1"/>
+        <v>250</v>
+      </c>
+      <c r="L8" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M8" s="10">
+        <f t="shared" si="3"/>
+        <v>1448</v>
+      </c>
+      <c r="N8" s="10">
+        <f t="shared" si="4"/>
+        <v>2678</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>1</v>
       </c>
-      <c r="B9" s="8">
+      <c r="B9" s="6">
         <v>9</v>
       </c>
-      <c r="C9" t="s" s="1">
-        <v>50</v>
-      </c>
-      <c r="D9" t="s" s="1">
-        <v>58</v>
+      <c r="C9" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>55</v>
       </c>
       <c r="E9">
-        <v>230.0</v>
+        <v>326</v>
       </c>
       <c r="F9">
-        <v>219.0</v>
+        <v>230</v>
       </c>
       <c r="G9">
+        <v>219</v>
+      </c>
+      <c r="H9">
         <v>43.8</v>
       </c>
-      <c r="H9">
+      <c r="I9">
         <v>5.3</v>
       </c>
-      <c r="I9">
-        <v>4161.0</v>
-      </c>
-      <c r="J9">
-        <v>2172.0</v>
-      </c>
-      <c r="K9">
-        <v>6333.0</v>
-      </c>
-      <c r="L9">
-        <v>4161.0</v>
-      </c>
-      <c r="O9" s="4"/>
-    </row>
-    <row r="10" spans="1:16" dyDescent="0.2">
+      <c r="J9" s="10">
+        <f t="shared" si="0"/>
+        <v>978</v>
+      </c>
+      <c r="K9" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L9" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M9" s="10">
+        <f>$Q$4*MAX(F9-G9*$Q$1)*$Q$3</f>
+        <v>1241.3333333333333</v>
+      </c>
+      <c r="N9" s="10">
+        <f t="shared" si="4"/>
+        <v>2719.333333333333</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>1</v>
       </c>
-      <c r="B10" s="8">
+      <c r="B10" s="6">
         <v>10</v>
       </c>
-      <c r="C10" t="s" s="1">
-        <v>50</v>
-      </c>
-      <c r="D10" t="s" s="1">
-        <v>60</v>
+      <c r="C10" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>57</v>
       </c>
       <c r="E10">
-        <v>56.0</v>
+        <v>70</v>
       </c>
       <c r="F10">
-        <v>47.0</v>
+        <v>56</v>
       </c>
       <c r="G10">
+        <v>47</v>
+      </c>
+      <c r="H10">
         <v>9.4</v>
       </c>
-      <c r="H10">
-        <v>6.0</v>
-      </c>
       <c r="I10">
-        <v>893.0</v>
-      </c>
-      <c r="J10">
-        <v>544.0</v>
-      </c>
-      <c r="K10">
-        <v>1437.0</v>
-      </c>
-      <c r="L10">
-        <v>893.0</v>
-      </c>
-      <c r="O10" s="4"/>
-    </row>
-    <row r="11" spans="1:16" dyDescent="0.2">
+        <v>6</v>
+      </c>
+      <c r="J10" s="10">
+        <f t="shared" si="0"/>
+        <v>210</v>
+      </c>
+      <c r="K10" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L10" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M10" s="10">
+        <f t="shared" si="3"/>
+        <v>310.66666666666669</v>
+      </c>
+      <c r="N10" s="10">
+        <f t="shared" si="4"/>
+        <v>1020.6666666666667</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>2</v>
       </c>
-      <c r="B11" s="8">
+      <c r="B11" s="6">
         <v>3</v>
       </c>
-      <c r="C11" t="s" s="2">
-        <v>51</v>
-      </c>
-      <c r="D11" t="s" s="2">
-        <v>52</v>
+      <c r="C11" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>49</v>
       </c>
       <c r="E11">
-        <v>173.0</v>
+        <v>211</v>
       </c>
       <c r="F11">
-        <v>131.0</v>
+        <v>173</v>
       </c>
       <c r="G11">
+        <v>131</v>
+      </c>
+      <c r="H11">
         <v>26.2</v>
       </c>
-      <c r="H11">
+      <c r="I11">
         <v>6.6</v>
       </c>
-      <c r="I11">
-        <v>2489.0</v>
-      </c>
-      <c r="J11">
-        <v>1713.0</v>
-      </c>
-      <c r="K11">
-        <v>4202.0</v>
-      </c>
-      <c r="L11">
-        <v>2489.0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" dyDescent="0.2">
+      <c r="J11" s="10">
+        <f t="shared" si="0"/>
+        <v>633</v>
+      </c>
+      <c r="K11" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L11" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M11" s="10">
+        <f t="shared" si="3"/>
+        <v>978.66666666666674</v>
+      </c>
+      <c r="N11" s="10">
+        <f t="shared" si="4"/>
+        <v>2111.666666666667</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>2</v>
       </c>
-      <c r="B12" s="8">
+      <c r="B12" s="6">
         <v>4</v>
       </c>
-      <c r="C12" t="s" s="2">
-        <v>51</v>
-      </c>
-      <c r="D12" t="s" s="1">
-        <v>53</v>
+      <c r="C12" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>50</v>
       </c>
       <c r="E12">
-        <v>103.0</v>
+        <v>137</v>
       </c>
       <c r="F12">
-        <v>110.0</v>
+        <v>103</v>
       </c>
       <c r="G12">
-        <v>22.0</v>
+        <v>110</v>
       </c>
       <c r="H12">
+        <v>22</v>
+      </c>
+      <c r="I12">
         <v>4.7</v>
       </c>
-      <c r="I12">
-        <v>2090.0</v>
-      </c>
-      <c r="J12">
-        <v>945.0</v>
-      </c>
-      <c r="K12">
-        <v>3035.0</v>
-      </c>
-      <c r="L12">
-        <v>2090.0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" dyDescent="0.2">
+      <c r="J12" s="10">
+        <f t="shared" si="0"/>
+        <v>411</v>
+      </c>
+      <c r="K12" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L12" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M12" s="10">
+        <f t="shared" si="3"/>
+        <v>540</v>
+      </c>
+      <c r="N12" s="10">
+        <f t="shared" si="4"/>
+        <v>1451</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>2</v>
       </c>
-      <c r="B13" s="8">
+      <c r="B13" s="6">
         <v>5</v>
       </c>
-      <c r="C13" t="s" s="2">
+      <c r="C13" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D13" t="s" s="1">
-        <v>54</v>
-      </c>
       <c r="E13">
-        <v>89.0</v>
+        <v>106</v>
       </c>
       <c r="F13">
-        <v>80.0</v>
+        <v>89</v>
       </c>
       <c r="G13">
-        <v>16.0</v>
+        <v>80</v>
       </c>
       <c r="H13">
+        <v>16</v>
+      </c>
+      <c r="I13">
         <v>5.6</v>
       </c>
-      <c r="I13">
-        <v>1520.0</v>
-      </c>
-      <c r="J13">
-        <v>852.0</v>
-      </c>
-      <c r="K13">
-        <v>2372.0</v>
-      </c>
-      <c r="L13">
-        <v>1520.0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" dyDescent="0.2">
+      <c r="J13" s="10">
+        <f t="shared" si="0"/>
+        <v>318</v>
+      </c>
+      <c r="K13" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L13" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M13" s="10">
+        <f t="shared" si="3"/>
+        <v>486.66666666666669</v>
+      </c>
+      <c r="N13" s="10">
+        <f t="shared" si="4"/>
+        <v>1304.6666666666667</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>2</v>
       </c>
-      <c r="B14" s="8">
+      <c r="B14" s="6">
         <v>6</v>
       </c>
-      <c r="C14" t="s" s="2">
-        <v>51</v>
-      </c>
-      <c r="D14" t="s" s="1">
-        <v>55</v>
+      <c r="C14" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>52</v>
       </c>
       <c r="E14">
-        <v>100.0</v>
+        <v>137</v>
       </c>
       <c r="F14">
-        <v>98.0</v>
+        <v>100</v>
       </c>
       <c r="G14">
-        <v>19.6</v>
+        <v>98</v>
       </c>
       <c r="H14">
-        <v>5.1</v>
+        <v>19.600000000000001</v>
       </c>
       <c r="I14">
-        <v>1862.0</v>
-      </c>
-      <c r="J14">
-        <v>938.0</v>
-      </c>
-      <c r="K14">
-        <v>2800.0</v>
-      </c>
-      <c r="L14">
-        <v>1862.0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" dyDescent="0.2">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="J14" s="10">
+        <f t="shared" si="0"/>
+        <v>411</v>
+      </c>
+      <c r="K14" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L14" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M14" s="10">
+        <f t="shared" si="3"/>
+        <v>536.00000000000011</v>
+      </c>
+      <c r="N14" s="10">
+        <f t="shared" si="4"/>
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>2</v>
       </c>
-      <c r="B15" s="8">
+      <c r="B15" s="6">
         <v>7</v>
       </c>
-      <c r="C15" t="s" s="2">
-        <v>51</v>
-      </c>
-      <c r="D15" t="s" s="11">
-        <v>56</v>
+      <c r="C15" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>53</v>
       </c>
       <c r="E15">
-        <v>138.0</v>
+        <v>205</v>
       </c>
       <c r="F15">
-        <v>151.0</v>
+        <v>138</v>
       </c>
       <c r="G15">
+        <v>151</v>
+      </c>
+      <c r="H15">
         <v>30.2</v>
       </c>
-      <c r="H15">
-        <v>4.6</v>
-      </c>
       <c r="I15">
-        <v>2869.0</v>
-      </c>
-      <c r="J15">
-        <v>1258.0</v>
-      </c>
-      <c r="K15">
-        <v>4127.0</v>
-      </c>
-      <c r="L15">
-        <v>2869.0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" dyDescent="0.2">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="J15" s="10">
+        <f t="shared" si="0"/>
+        <v>615</v>
+      </c>
+      <c r="K15" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L15" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M15" s="10">
+        <f t="shared" si="3"/>
+        <v>718.66666666666663</v>
+      </c>
+      <c r="N15" s="10">
+        <f t="shared" si="4"/>
+        <v>1833.6666666666665</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>2</v>
       </c>
-      <c r="B16" s="8">
+      <c r="B16" s="6">
         <v>8</v>
       </c>
-      <c r="C16" t="s" s="2">
-        <v>51</v>
-      </c>
-      <c r="D16" t="s" s="1">
-        <v>59</v>
+      <c r="C16" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>56</v>
       </c>
       <c r="E16">
-        <v>339.0</v>
+        <v>426</v>
       </c>
       <c r="F16">
-        <v>359.0</v>
+        <v>429</v>
       </c>
       <c r="G16">
+        <v>359</v>
+      </c>
+      <c r="H16">
         <v>71.8</v>
       </c>
-      <c r="H16">
-        <v>4.7</v>
-      </c>
       <c r="I16">
-        <v>6821.0</v>
-      </c>
-      <c r="J16">
-        <v>3117.0</v>
-      </c>
-      <c r="K16">
-        <v>9938.0</v>
-      </c>
-      <c r="L16">
-        <v>6821.0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" dyDescent="0.2">
+        <v>6</v>
+      </c>
+      <c r="J16" s="10">
+        <f t="shared" si="0"/>
+        <v>1278</v>
+      </c>
+      <c r="K16" s="10">
+        <f t="shared" si="1"/>
+        <v>250</v>
+      </c>
+      <c r="L16" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M16" s="10">
+        <f t="shared" si="3"/>
+        <v>2381.3333333333335</v>
+      </c>
+      <c r="N16" s="10">
+        <f t="shared" si="4"/>
+        <v>4409.3333333333339</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>2</v>
       </c>
-      <c r="B17" s="8">
+      <c r="B17" s="6">
         <v>9</v>
       </c>
-      <c r="C17" t="s" s="2">
-        <v>51</v>
-      </c>
-      <c r="D17" t="s" s="1">
-        <v>58</v>
+      <c r="C17" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>55</v>
       </c>
       <c r="E17">
-        <v>87.0</v>
+        <v>89</v>
       </c>
       <c r="F17">
-        <v>76.0</v>
+        <v>87</v>
       </c>
       <c r="G17">
+        <v>76</v>
+      </c>
+      <c r="H17">
         <v>15.2</v>
       </c>
-      <c r="H17">
+      <c r="I17">
         <v>5.7</v>
       </c>
-      <c r="I17">
-        <v>1444.0</v>
-      </c>
-      <c r="J17">
-        <v>838.0</v>
-      </c>
-      <c r="K17">
-        <v>2282.0</v>
-      </c>
-      <c r="L17">
-        <v>1444.0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" dyDescent="0.2">
+      <c r="J17" s="10">
+        <f t="shared" si="0"/>
+        <v>267</v>
+      </c>
+      <c r="K17" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L17" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M17" s="10">
+        <f t="shared" si="3"/>
+        <v>478.66666666666669</v>
+      </c>
+      <c r="N17" s="10">
+        <f t="shared" si="4"/>
+        <v>1245.6666666666667</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>2</v>
       </c>
-      <c r="B18" s="8">
+      <c r="B18" s="6">
         <v>10</v>
       </c>
-      <c r="C18" t="s" s="2">
-        <v>51</v>
-      </c>
-      <c r="D18" t="s" s="1">
-        <v>60</v>
+      <c r="C18" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>57</v>
       </c>
       <c r="E18">
-        <v>218.0</v>
+        <v>305</v>
       </c>
       <c r="F18">
-        <v>217.0</v>
+        <v>218</v>
       </c>
       <c r="G18">
+        <v>217</v>
+      </c>
+      <c r="H18">
         <v>43.4</v>
       </c>
-      <c r="H18">
-        <v>5.0</v>
-      </c>
       <c r="I18">
-        <v>4123.0</v>
-      </c>
-      <c r="J18">
-        <v>2037.0</v>
-      </c>
-      <c r="K18">
-        <v>6160.0</v>
-      </c>
-      <c r="L18">
-        <v>4123.0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" dyDescent="0.2">
+        <v>5</v>
+      </c>
+      <c r="J18" s="10">
+        <f t="shared" si="0"/>
+        <v>915</v>
+      </c>
+      <c r="K18" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L18" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M18" s="10">
+        <f t="shared" si="3"/>
+        <v>1164</v>
+      </c>
+      <c r="N18" s="10">
+        <f t="shared" si="4"/>
+        <v>2579</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>3</v>
       </c>
-      <c r="B19" s="8">
+      <c r="B19" s="6">
         <v>4</v>
       </c>
-      <c r="C19" t="s" s="2">
-        <v>52</v>
-      </c>
-      <c r="D19" t="s" s="1">
-        <v>53</v>
+      <c r="C19" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>50</v>
       </c>
       <c r="E19">
-        <v>215.0</v>
+        <v>291</v>
       </c>
       <c r="F19">
-        <v>77.0</v>
+        <v>215</v>
       </c>
       <c r="G19">
+        <v>77</v>
+      </c>
+      <c r="H19">
         <v>15.4</v>
       </c>
-      <c r="H19">
-        <v>14.0</v>
-      </c>
       <c r="I19">
-        <v>1463.0</v>
-      </c>
-      <c r="J19">
-        <v>2329.0</v>
-      </c>
-      <c r="K19">
-        <v>3792.0</v>
-      </c>
-      <c r="L19">
-        <v>2329.0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" dyDescent="0.2">
+        <v>14</v>
+      </c>
+      <c r="J19" s="10">
+        <f t="shared" si="0"/>
+        <v>873</v>
+      </c>
+      <c r="K19" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L19" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M19" s="10">
+        <f t="shared" si="3"/>
+        <v>1330.6666666666667</v>
+      </c>
+      <c r="N19" s="10">
+        <f t="shared" si="4"/>
+        <v>2703.666666666667</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>3</v>
       </c>
-      <c r="B20" s="8">
+      <c r="B20" s="6">
         <v>5</v>
       </c>
-      <c r="C20" t="s" s="2">
-        <v>52</v>
-      </c>
-      <c r="D20" t="s" s="1">
-        <v>54</v>
+      <c r="C20" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>51</v>
       </c>
       <c r="E20">
-        <v>113.0</v>
+        <v>121</v>
       </c>
       <c r="F20">
-        <v>63.0</v>
+        <v>113</v>
       </c>
       <c r="G20">
+        <v>63</v>
+      </c>
+      <c r="H20">
         <v>12.6</v>
       </c>
-      <c r="H20">
-        <v>9.0</v>
-      </c>
       <c r="I20">
-        <v>1197.0</v>
-      </c>
-      <c r="J20">
-        <v>1171.0</v>
-      </c>
-      <c r="K20">
-        <v>2368.0</v>
-      </c>
-      <c r="L20">
-        <v>1197.0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" dyDescent="0.2">
+        <v>9</v>
+      </c>
+      <c r="J20" s="10">
+        <f t="shared" si="0"/>
+        <v>363</v>
+      </c>
+      <c r="K20" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L20" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M20" s="10">
+        <f t="shared" si="3"/>
+        <v>669.33333333333337</v>
+      </c>
+      <c r="N20" s="10">
+        <f t="shared" si="4"/>
+        <v>1532.3333333333335</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>3</v>
       </c>
-      <c r="B21" s="8">
+      <c r="B21" s="6">
         <v>6</v>
       </c>
-      <c r="C21" t="s" s="2">
+      <c r="C21" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D21" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D21" t="s" s="1">
-        <v>55</v>
-      </c>
       <c r="E21">
-        <v>192.0</v>
+        <v>269</v>
       </c>
       <c r="F21">
-        <v>126.0</v>
+        <v>192</v>
       </c>
       <c r="G21">
+        <v>126</v>
+      </c>
+      <c r="H21">
         <v>25.2</v>
       </c>
-      <c r="H21">
+      <c r="I21">
         <v>7.6</v>
       </c>
-      <c r="I21">
-        <v>2394.0</v>
-      </c>
-      <c r="J21">
-        <v>1946.0</v>
-      </c>
-      <c r="K21">
-        <v>4340.0</v>
-      </c>
-      <c r="L21">
-        <v>2394.0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" dyDescent="0.2">
+      <c r="J21" s="10">
+        <f t="shared" si="0"/>
+        <v>807</v>
+      </c>
+      <c r="K21" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L21" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M21" s="10">
+        <f t="shared" si="3"/>
+        <v>1112.0000000000002</v>
+      </c>
+      <c r="N21" s="10">
+        <f t="shared" si="4"/>
+        <v>2419</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>3</v>
       </c>
-      <c r="B22" s="8">
+      <c r="B22" s="6">
         <v>7</v>
       </c>
-      <c r="C22" t="s" s="2">
-        <v>52</v>
-      </c>
-      <c r="D22" t="s" s="11">
-        <v>56</v>
+      <c r="C22" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>53</v>
       </c>
       <c r="E22">
-        <v>250.0</v>
+        <v>359</v>
       </c>
       <c r="F22">
-        <v>167.0</v>
+        <v>250</v>
       </c>
       <c r="G22">
+        <v>167</v>
+      </c>
+      <c r="H22">
         <v>33.4</v>
       </c>
-      <c r="H22">
+      <c r="I22">
         <v>7.5</v>
       </c>
-      <c r="I22">
-        <v>3173.0</v>
-      </c>
-      <c r="J22">
-        <v>2527.0</v>
-      </c>
-      <c r="K22">
-        <v>5700.0</v>
-      </c>
-      <c r="L22">
-        <v>3173.0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" dyDescent="0.2">
+      <c r="J22" s="10">
+        <f t="shared" si="0"/>
+        <v>1077</v>
+      </c>
+      <c r="K22" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L22" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M22" s="10">
+        <f t="shared" si="3"/>
+        <v>1444</v>
+      </c>
+      <c r="N22" s="10">
+        <f t="shared" si="4"/>
+        <v>3021</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>3</v>
       </c>
-      <c r="B23" s="8">
+      <c r="B23" s="6">
         <v>8</v>
       </c>
-      <c r="C23" t="s" s="2">
-        <v>52</v>
-      </c>
-      <c r="D23" t="s" s="1">
-        <v>59</v>
+      <c r="C23" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>56</v>
       </c>
       <c r="E23">
-        <v>234.0</v>
+        <v>259</v>
       </c>
       <c r="F23">
-        <v>230.0</v>
+        <v>324</v>
       </c>
       <c r="G23">
-        <v>46.0</v>
+        <v>230</v>
       </c>
       <c r="H23">
-        <v>5.1</v>
+        <v>46</v>
       </c>
       <c r="I23">
-        <v>4370.0</v>
-      </c>
-      <c r="J23">
-        <v>2193.0</v>
-      </c>
-      <c r="K23">
-        <v>6563.0</v>
-      </c>
-      <c r="L23">
-        <v>4370.0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" dyDescent="0.2">
+        <v>7</v>
+      </c>
+      <c r="J23" s="10">
+        <f t="shared" si="0"/>
+        <v>777</v>
+      </c>
+      <c r="K23" s="10">
+        <f t="shared" si="1"/>
+        <v>250</v>
+      </c>
+      <c r="L23" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M23" s="10">
+        <f t="shared" si="3"/>
+        <v>1853.3333333333335</v>
+      </c>
+      <c r="N23" s="10">
+        <f t="shared" si="4"/>
+        <v>3380.3333333333335</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>3</v>
       </c>
-      <c r="B24" s="8">
+      <c r="B24" s="6">
         <v>9</v>
       </c>
-      <c r="C24" t="s" s="2">
-        <v>52</v>
-      </c>
-      <c r="D24" t="s" s="1">
-        <v>58</v>
+      <c r="C24" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>55</v>
       </c>
       <c r="E24">
-        <v>217.0</v>
+        <v>270</v>
       </c>
       <c r="F24">
-        <v>138.0</v>
+        <v>217</v>
       </c>
       <c r="G24">
+        <v>138</v>
+      </c>
+      <c r="H24">
         <v>27.6</v>
       </c>
-      <c r="H24">
+      <c r="I24">
         <v>7.9</v>
       </c>
-      <c r="I24">
-        <v>2622.0</v>
-      </c>
-      <c r="J24">
-        <v>2210.0</v>
-      </c>
-      <c r="K24">
-        <v>4832.0</v>
-      </c>
-      <c r="L24">
-        <v>2622.0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" dyDescent="0.2">
+      <c r="J24" s="10">
+        <f t="shared" si="0"/>
+        <v>810</v>
+      </c>
+      <c r="K24" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L24" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M24" s="10">
+        <f t="shared" si="3"/>
+        <v>1262.6666666666667</v>
+      </c>
+      <c r="N24" s="10">
+        <f t="shared" si="4"/>
+        <v>2572.666666666667</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>3</v>
       </c>
-      <c r="B25" s="8">
+      <c r="B25" s="6">
         <v>10</v>
       </c>
-      <c r="C25" t="s" s="2">
-        <v>52</v>
-      </c>
-      <c r="D25" t="s" s="1">
-        <v>60</v>
+      <c r="C25" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>57</v>
       </c>
       <c r="E25">
-        <v>108.0</v>
+        <v>131</v>
       </c>
       <c r="F25">
-        <v>92.0</v>
+        <v>108</v>
       </c>
       <c r="G25">
-        <v>18.4</v>
+        <v>92</v>
       </c>
       <c r="H25">
+        <v>18.399999999999999</v>
+      </c>
+      <c r="I25">
         <v>5.9</v>
       </c>
-      <c r="I25">
-        <v>1748.0</v>
-      </c>
-      <c r="J25">
-        <v>1045.0</v>
-      </c>
-      <c r="K25">
-        <v>2793.0</v>
-      </c>
-      <c r="L25">
-        <v>1748.0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" dyDescent="0.2">
+      <c r="J25" s="10">
+        <f t="shared" si="0"/>
+        <v>393</v>
+      </c>
+      <c r="K25" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L25" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M25" s="10">
+        <f t="shared" si="3"/>
+        <v>597.33333333333337</v>
+      </c>
+      <c r="N25" s="10">
+        <f t="shared" si="4"/>
+        <v>1490.3333333333335</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>4</v>
       </c>
-      <c r="B26" s="8">
+      <c r="B26" s="6">
         <v>5</v>
       </c>
-      <c r="C26" t="s" s="1">
-        <v>53</v>
-      </c>
-      <c r="D26" t="s" s="1">
-        <v>54</v>
+      <c r="C26" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>51</v>
       </c>
       <c r="E26">
-        <v>130.0</v>
+        <v>187</v>
       </c>
       <c r="F26">
-        <v>93.0</v>
+        <v>130</v>
       </c>
       <c r="G26">
-        <v>18.6</v>
+        <v>93</v>
       </c>
       <c r="H26">
-        <v>7.0</v>
+        <v>18.600000000000001</v>
       </c>
       <c r="I26">
-        <v>1767.0</v>
-      </c>
-      <c r="J26">
-        <v>1300.0</v>
-      </c>
-      <c r="K26">
-        <v>3067.0</v>
-      </c>
-      <c r="L26">
-        <v>1767.0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" dyDescent="0.2">
+        <v>7</v>
+      </c>
+      <c r="J26" s="10">
+        <f t="shared" si="0"/>
+        <v>561</v>
+      </c>
+      <c r="K26" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L26" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M26" s="10">
+        <f t="shared" si="3"/>
+        <v>742.66666666666674</v>
+      </c>
+      <c r="N26" s="10">
+        <f t="shared" si="4"/>
+        <v>1803.6666666666667</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>4</v>
       </c>
-      <c r="B27" s="8">
+      <c r="B27" s="6">
         <v>6</v>
       </c>
-      <c r="C27" t="s" s="1">
-        <v>53</v>
-      </c>
-      <c r="D27" t="s" s="1">
-        <v>55</v>
+      <c r="C27" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>52</v>
       </c>
       <c r="E27">
-        <v>149.0</v>
+        <v>233</v>
       </c>
       <c r="F27">
-        <v>161.0</v>
+        <v>149</v>
       </c>
       <c r="G27">
-        <v>32.2</v>
+        <v>161</v>
       </c>
       <c r="H27">
-        <v>4.6</v>
+        <v>32.200000000000003</v>
       </c>
       <c r="I27">
-        <v>3059.0</v>
-      </c>
-      <c r="J27">
-        <v>1363.0</v>
-      </c>
-      <c r="K27">
-        <v>4422.0</v>
-      </c>
-      <c r="L27">
-        <v>3059.0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" dyDescent="0.2">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="J27" s="10">
+        <f t="shared" si="0"/>
+        <v>699</v>
+      </c>
+      <c r="K27" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L27" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M27" s="10">
+        <f t="shared" si="3"/>
+        <v>778.66666666666663</v>
+      </c>
+      <c r="N27" s="10">
+        <f t="shared" si="4"/>
+        <v>1977.6666666666665</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>4</v>
       </c>
-      <c r="B28" s="8">
+      <c r="B28" s="6">
         <v>7</v>
       </c>
-      <c r="C28" t="s" s="1">
+      <c r="C28" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D28" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="D28" t="s" s="11">
-        <v>56</v>
-      </c>
       <c r="E28">
-        <v>93.0</v>
+        <v>126</v>
       </c>
       <c r="F28">
-        <v>90.0</v>
+        <v>93</v>
       </c>
       <c r="G28">
-        <v>18.0</v>
+        <v>90</v>
       </c>
       <c r="H28">
+        <v>18</v>
+      </c>
+      <c r="I28">
         <v>5.2</v>
       </c>
-      <c r="I28">
-        <v>1710.0</v>
-      </c>
-      <c r="J28">
-        <v>875.0</v>
-      </c>
-      <c r="K28">
-        <v>2585.0</v>
-      </c>
-      <c r="L28">
-        <v>1710.0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" dyDescent="0.2">
+      <c r="J28" s="10">
+        <f t="shared" si="0"/>
+        <v>378</v>
+      </c>
+      <c r="K28" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L28" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M28" s="10">
+        <f t="shared" si="3"/>
+        <v>500</v>
+      </c>
+      <c r="N28" s="10">
+        <f t="shared" si="4"/>
+        <v>1378</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>4</v>
       </c>
-      <c r="B29" s="8">
+      <c r="B29" s="6">
         <v>8</v>
       </c>
-      <c r="C29" t="s" s="1">
-        <v>53</v>
-      </c>
-      <c r="D29" t="s" s="1">
-        <v>59</v>
+      <c r="C29" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>56</v>
       </c>
       <c r="E29">
-        <v>380.0</v>
+        <v>507</v>
       </c>
       <c r="F29">
-        <v>290.0</v>
+        <v>470</v>
       </c>
       <c r="G29">
-        <v>58.0</v>
+        <v>290</v>
       </c>
       <c r="H29">
-        <v>6.6</v>
+        <v>58</v>
       </c>
       <c r="I29">
-        <v>5510.0</v>
-      </c>
-      <c r="J29">
-        <v>3757.0</v>
-      </c>
-      <c r="K29">
-        <v>9267.0</v>
-      </c>
-      <c r="L29">
-        <v>5510.0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16" dyDescent="0.2">
+        <v>8.1</v>
+      </c>
+      <c r="J29" s="10">
+        <f t="shared" si="0"/>
+        <v>1521</v>
+      </c>
+      <c r="K29" s="10">
+        <f t="shared" si="1"/>
+        <v>250</v>
+      </c>
+      <c r="L29" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M29" s="10">
+        <f t="shared" si="3"/>
+        <v>2746.666666666667</v>
+      </c>
+      <c r="N29" s="10">
+        <f t="shared" si="4"/>
+        <v>5017.666666666667</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>4</v>
       </c>
-      <c r="B30" s="8">
+      <c r="B30" s="6">
         <v>9</v>
       </c>
-      <c r="C30" t="s" s="1">
-        <v>53</v>
-      </c>
-      <c r="D30" t="s" s="1">
-        <v>58</v>
+      <c r="C30" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>55</v>
       </c>
       <c r="E30">
-        <v>87.0</v>
+        <v>99</v>
       </c>
       <c r="F30">
-        <v>75.0</v>
+        <v>87</v>
       </c>
       <c r="G30">
-        <v>15.0</v>
+        <v>75</v>
       </c>
       <c r="H30">
+        <v>15</v>
+      </c>
+      <c r="I30">
         <v>5.8</v>
       </c>
-      <c r="I30">
-        <v>1425.0</v>
-      </c>
-      <c r="J30">
-        <v>840.0</v>
-      </c>
-      <c r="K30">
-        <v>2265.0</v>
-      </c>
-      <c r="L30">
-        <v>1425.0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16" dyDescent="0.2">
+      <c r="J30" s="10">
+        <f t="shared" si="0"/>
+        <v>297</v>
+      </c>
+      <c r="K30" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L30" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M30" s="10">
+        <f t="shared" si="3"/>
+        <v>480</v>
+      </c>
+      <c r="N30" s="10">
+        <f t="shared" si="4"/>
+        <v>1277</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>4</v>
       </c>
-      <c r="B31" s="8">
+      <c r="B31" s="6">
         <v>10</v>
       </c>
-      <c r="C31" t="s" s="1">
-        <v>53</v>
-      </c>
-      <c r="D31" t="s" s="1">
-        <v>60</v>
+      <c r="C31" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>57</v>
       </c>
       <c r="E31">
-        <v>259.0</v>
+        <v>387</v>
       </c>
       <c r="F31">
-        <v>125.0</v>
+        <v>259</v>
       </c>
       <c r="G31">
-        <v>25.0</v>
+        <v>125</v>
       </c>
       <c r="H31">
+        <v>25</v>
+      </c>
+      <c r="I31">
         <v>10.4</v>
       </c>
-      <c r="I31">
-        <v>2375.0</v>
-      </c>
-      <c r="J31">
-        <v>2730.0</v>
-      </c>
-      <c r="K31">
-        <v>5105.0</v>
-      </c>
-      <c r="L31">
-        <v>2730.0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16" dyDescent="0.2">
+      <c r="J31" s="10">
+        <f t="shared" si="0"/>
+        <v>1161</v>
+      </c>
+      <c r="K31" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L31" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M31" s="10">
+        <f t="shared" si="3"/>
+        <v>1560</v>
+      </c>
+      <c r="N31" s="10">
+        <f t="shared" si="4"/>
+        <v>3221</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>5</v>
       </c>
-      <c r="B32" s="8">
+      <c r="B32" s="6">
         <v>6</v>
       </c>
-      <c r="C32" t="s" s="1">
-        <v>54</v>
-      </c>
-      <c r="D32" t="s" s="1">
-        <v>55</v>
+      <c r="C32" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>52</v>
       </c>
       <c r="E32">
-        <v>110.0</v>
+        <v>164</v>
       </c>
       <c r="F32">
-        <v>70.0</v>
+        <v>110</v>
       </c>
       <c r="G32">
-        <v>14.0</v>
+        <v>70</v>
       </c>
       <c r="H32">
+        <v>14</v>
+      </c>
+      <c r="I32">
         <v>7.9</v>
       </c>
-      <c r="I32">
-        <v>1330.0</v>
-      </c>
-      <c r="J32">
-        <v>1120.0</v>
-      </c>
-      <c r="K32">
-        <v>2450.0</v>
-      </c>
-      <c r="L32">
-        <v>1330.0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" dyDescent="0.2">
-      <c r="A33" s="10">
+      <c r="J32" s="10">
+        <f t="shared" si="0"/>
+        <v>492</v>
+      </c>
+      <c r="K32" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L32" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M32" s="10">
+        <f t="shared" si="3"/>
+        <v>640</v>
+      </c>
+      <c r="N32" s="10">
+        <f t="shared" si="4"/>
+        <v>1632</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A33" s="8">
         <v>5</v>
       </c>
-      <c r="B33" s="8">
+      <c r="B33" s="6">
         <v>7</v>
       </c>
-      <c r="C33" t="s" s="1">
-        <v>54</v>
-      </c>
-      <c r="D33" t="s" s="11">
-        <v>56</v>
+      <c r="C33" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>53</v>
       </c>
       <c r="E33">
-        <v>168.0</v>
+        <v>254</v>
       </c>
       <c r="F33">
-        <v>173.0</v>
+        <v>168</v>
       </c>
       <c r="G33">
+        <v>173</v>
+      </c>
+      <c r="H33">
         <v>34.6</v>
       </c>
-      <c r="H33">
-        <v>4.9</v>
-      </c>
       <c r="I33">
-        <v>3287.0</v>
-      </c>
-      <c r="J33">
-        <v>1556.0</v>
-      </c>
-      <c r="K33">
-        <v>4843.0</v>
-      </c>
-      <c r="L33">
-        <v>3287.0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" dyDescent="0.2">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="J33" s="10">
+        <f t="shared" si="0"/>
+        <v>762</v>
+      </c>
+      <c r="K33" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L33" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M33" s="10">
+        <f t="shared" si="3"/>
+        <v>889.33333333333337</v>
+      </c>
+      <c r="N33" s="10">
+        <f t="shared" si="4"/>
+        <v>2151.3333333333335</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>5</v>
       </c>
-      <c r="B34" s="8">
+      <c r="B34" s="6">
         <v>8</v>
       </c>
-      <c r="C34" t="s" s="1">
-        <v>54</v>
-      </c>
-      <c r="D34" t="s" s="1">
-        <v>59</v>
+      <c r="C34" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>56</v>
       </c>
       <c r="E34">
-        <v>279.0</v>
+        <v>337</v>
       </c>
       <c r="F34">
-        <v>281.0</v>
+        <v>369</v>
       </c>
       <c r="G34">
+        <v>281</v>
+      </c>
+      <c r="H34">
         <v>56.2</v>
       </c>
-      <c r="H34">
-        <v>5.0</v>
-      </c>
       <c r="I34">
-        <v>5339.0</v>
-      </c>
-      <c r="J34">
-        <v>2599.0</v>
-      </c>
-      <c r="K34">
-        <v>7938.0</v>
-      </c>
-      <c r="L34">
-        <v>5339.0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" dyDescent="0.2">
+        <v>6.6</v>
+      </c>
+      <c r="J34" s="10">
+        <f t="shared" si="0"/>
+        <v>1011</v>
+      </c>
+      <c r="K34" s="10">
+        <f t="shared" si="1"/>
+        <v>250</v>
+      </c>
+      <c r="L34" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M34" s="10">
+        <f t="shared" si="3"/>
+        <v>2085.3333333333335</v>
+      </c>
+      <c r="N34" s="10">
+        <f t="shared" si="4"/>
+        <v>3846.3333333333335</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>5</v>
       </c>
-      <c r="B35" s="8">
+      <c r="B35" s="6">
         <v>9</v>
       </c>
-      <c r="C35" t="s" s="1">
-        <v>54</v>
-      </c>
-      <c r="D35" t="s" s="1">
-        <v>58</v>
+      <c r="C35" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>55</v>
       </c>
       <c r="E35">
-        <v>136.0</v>
+        <v>165</v>
       </c>
       <c r="F35">
-        <v>118.0</v>
+        <v>136</v>
       </c>
       <c r="G35">
+        <v>118</v>
+      </c>
+      <c r="H35">
         <v>23.6</v>
       </c>
-      <c r="H35">
+      <c r="I35">
         <v>5.8</v>
       </c>
-      <c r="I35">
-        <v>2242.0</v>
-      </c>
-      <c r="J35">
-        <v>1311.0</v>
-      </c>
-      <c r="K35">
-        <v>3553.0</v>
-      </c>
-      <c r="L35">
-        <v>2242.0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16" dyDescent="0.2">
+      <c r="J35" s="10">
+        <f t="shared" si="0"/>
+        <v>495</v>
+      </c>
+      <c r="K35" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L35" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M35" s="10">
+        <f t="shared" si="3"/>
+        <v>749.33333333333337</v>
+      </c>
+      <c r="N35" s="10">
+        <f t="shared" si="4"/>
+        <v>1744.3333333333335</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>5</v>
       </c>
-      <c r="B36" s="8">
+      <c r="B36" s="6">
         <v>10</v>
       </c>
-      <c r="C36" t="s" s="1">
-        <v>54</v>
-      </c>
-      <c r="D36" t="s" s="1">
-        <v>60</v>
+      <c r="C36" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>57</v>
       </c>
       <c r="E36">
-        <v>158.0</v>
+        <v>216</v>
       </c>
       <c r="F36">
-        <v>155.0</v>
+        <v>158</v>
       </c>
       <c r="G36">
-        <v>31.0</v>
+        <v>155</v>
       </c>
       <c r="H36">
-        <v>5.1</v>
+        <v>31</v>
       </c>
       <c r="I36">
-        <v>2945.0</v>
-      </c>
-      <c r="J36">
-        <v>1482.0</v>
-      </c>
-      <c r="K36">
-        <v>4427.0</v>
-      </c>
-      <c r="L36">
-        <v>2945.0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16" dyDescent="0.2">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="J36" s="10">
+        <f t="shared" si="0"/>
+        <v>648</v>
+      </c>
+      <c r="K36" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L36" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M36" s="10">
+        <f t="shared" si="3"/>
+        <v>846.66666666666674</v>
+      </c>
+      <c r="N36" s="10">
+        <f t="shared" si="4"/>
+        <v>1994.6666666666667</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>6</v>
       </c>
-      <c r="B37" s="8">
+      <c r="B37" s="6">
         <v>7</v>
       </c>
-      <c r="C37" t="s" s="1">
-        <v>55</v>
-      </c>
-      <c r="D37" t="s" s="11">
-        <v>56</v>
+      <c r="C37" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D37" s="9" t="s">
+        <v>53</v>
       </c>
       <c r="E37">
-        <v>185.0</v>
+        <v>299</v>
       </c>
       <c r="F37">
-        <v>232.0</v>
+        <v>185</v>
       </c>
       <c r="G37">
+        <v>232</v>
+      </c>
+      <c r="H37">
         <v>46.4</v>
       </c>
-      <c r="H37">
-        <v>4.0</v>
-      </c>
       <c r="I37">
-        <v>4408.0</v>
-      </c>
-      <c r="J37">
-        <v>1617.0</v>
-      </c>
-      <c r="K37">
-        <v>6025.0</v>
-      </c>
-      <c r="L37">
-        <v>4408.0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:16" dyDescent="0.2">
+        <v>4</v>
+      </c>
+      <c r="J37" s="10">
+        <f t="shared" si="0"/>
+        <v>897</v>
+      </c>
+      <c r="K37" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L37" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M37" s="10">
+        <f t="shared" si="3"/>
+        <v>924</v>
+      </c>
+      <c r="N37" s="10">
+        <f t="shared" si="4"/>
+        <v>2321</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>6</v>
       </c>
-      <c r="B38" s="8">
+      <c r="B38" s="6">
         <v>8</v>
       </c>
-      <c r="C38" t="s" s="1">
-        <v>55</v>
-      </c>
-      <c r="D38" t="s" s="1">
-        <v>59</v>
+      <c r="C38" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>56</v>
       </c>
       <c r="E38">
-        <v>358.0</v>
+        <v>484</v>
       </c>
       <c r="F38">
-        <v>315.0</v>
+        <v>448</v>
       </c>
       <c r="G38">
-        <v>63.0</v>
+        <v>315</v>
       </c>
       <c r="H38">
-        <v>5.7</v>
+        <v>63</v>
       </c>
       <c r="I38">
-        <v>5985.0</v>
-      </c>
-      <c r="J38">
-        <v>3442.0</v>
-      </c>
-      <c r="K38">
-        <v>9427.0</v>
-      </c>
-      <c r="L38">
-        <v>5985.0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16" dyDescent="0.2">
+        <v>7.1</v>
+      </c>
+      <c r="J38" s="10">
+        <f t="shared" si="0"/>
+        <v>1452</v>
+      </c>
+      <c r="K38" s="10">
+        <f t="shared" si="1"/>
+        <v>250</v>
+      </c>
+      <c r="L38" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M38" s="10">
+        <f t="shared" si="3"/>
+        <v>2566.666666666667</v>
+      </c>
+      <c r="N38" s="10">
+        <f t="shared" si="4"/>
+        <v>4768.666666666667</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>6</v>
       </c>
-      <c r="B39" s="8">
+      <c r="B39" s="6">
         <v>9</v>
       </c>
-      <c r="C39" t="s" s="1">
+      <c r="C39" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D39" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D39" t="s" s="1">
-        <v>58</v>
-      </c>
       <c r="E39">
-        <v>153.0</v>
+        <v>210</v>
       </c>
       <c r="F39">
-        <v>166.0</v>
+        <v>153</v>
       </c>
       <c r="G39">
-        <v>33.2</v>
+        <v>166</v>
       </c>
       <c r="H39">
-        <v>4.6</v>
+        <v>33.200000000000003</v>
       </c>
       <c r="I39">
-        <v>3154.0</v>
-      </c>
-      <c r="J39">
-        <v>1398.0</v>
-      </c>
-      <c r="K39">
-        <v>4552.0</v>
-      </c>
-      <c r="L39">
-        <v>3154.0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:16" dyDescent="0.2">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="J39" s="10">
+        <f t="shared" si="0"/>
+        <v>630</v>
+      </c>
+      <c r="K39" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L39" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M39" s="10">
+        <f t="shared" si="3"/>
+        <v>798.66666666666663</v>
+      </c>
+      <c r="N39" s="10">
+        <f t="shared" si="4"/>
+        <v>1928.6666666666665</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>6</v>
       </c>
-      <c r="B40" s="8">
+      <c r="B40" s="6">
         <v>10</v>
       </c>
-      <c r="C40" t="s" s="1">
-        <v>55</v>
-      </c>
-      <c r="D40" t="s" s="1">
-        <v>60</v>
+      <c r="C40" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>57</v>
       </c>
       <c r="E40">
-        <v>237.0</v>
+        <v>363</v>
       </c>
       <c r="F40">
-        <v>216.0</v>
+        <v>237</v>
       </c>
       <c r="G40">
+        <v>216</v>
+      </c>
+      <c r="H40">
         <v>43.2</v>
       </c>
-      <c r="H40">
+      <c r="I40">
         <v>5.5</v>
       </c>
-      <c r="I40">
-        <v>4104.0</v>
-      </c>
-      <c r="J40">
-        <v>2261.0</v>
-      </c>
-      <c r="K40">
-        <v>6365.0</v>
-      </c>
-      <c r="L40">
-        <v>4104.0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:16" dyDescent="0.2">
+      <c r="J40" s="10">
+        <f t="shared" si="0"/>
+        <v>1089</v>
+      </c>
+      <c r="K40" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L40" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M40" s="10">
+        <f t="shared" si="3"/>
+        <v>1292.0000000000002</v>
+      </c>
+      <c r="N40" s="10">
+        <f t="shared" si="4"/>
+        <v>2881</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>7</v>
       </c>
-      <c r="B41" s="8">
+      <c r="B41" s="6">
         <v>8</v>
       </c>
-      <c r="C41" t="s" s="1">
+      <c r="C41" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D41" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="D41" t="s" s="1">
-        <v>59</v>
-      </c>
       <c r="E41">
-        <v>414.0</v>
+        <v>575</v>
       </c>
       <c r="F41">
-        <v>365.0</v>
+        <v>504</v>
       </c>
       <c r="G41">
-        <v>73.0</v>
+        <v>365</v>
       </c>
       <c r="H41">
-        <v>5.7</v>
+        <v>73</v>
       </c>
       <c r="I41">
-        <v>6935.0</v>
-      </c>
-      <c r="J41">
-        <v>3978.0</v>
-      </c>
-      <c r="K41">
-        <v>10913.0</v>
-      </c>
-      <c r="L41">
-        <v>6935.0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:16" dyDescent="0.2">
+        <v>6.9</v>
+      </c>
+      <c r="J41" s="10">
+        <f t="shared" si="0"/>
+        <v>1725</v>
+      </c>
+      <c r="K41" s="10">
+        <f t="shared" si="1"/>
+        <v>250</v>
+      </c>
+      <c r="L41" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M41" s="10">
+        <f t="shared" si="3"/>
+        <v>2873.3333333333335</v>
+      </c>
+      <c r="N41" s="10">
+        <f>SUM(J41:M41)</f>
+        <v>5348.3333333333339</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>7</v>
       </c>
-      <c r="B42" s="8">
+      <c r="B42" s="6">
         <v>9</v>
       </c>
-      <c r="C42" t="s" s="1">
-        <v>56</v>
-      </c>
-      <c r="D42" t="s" s="1">
-        <v>58</v>
+      <c r="C42" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>55</v>
       </c>
       <c r="E42">
-        <v>70.0</v>
+        <v>84</v>
       </c>
       <c r="F42">
-        <v>75.0</v>
+        <v>70</v>
       </c>
       <c r="G42">
-        <v>15.0</v>
+        <v>75</v>
       </c>
       <c r="H42">
+        <v>15</v>
+      </c>
+      <c r="I42">
         <v>4.7</v>
       </c>
-      <c r="I42">
-        <v>1425.0</v>
-      </c>
-      <c r="J42">
-        <v>642.0</v>
-      </c>
-      <c r="K42">
-        <v>2067.0</v>
-      </c>
-      <c r="L42">
-        <v>1425.0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:16" dyDescent="0.2">
+      <c r="J42" s="10">
+        <f t="shared" si="0"/>
+        <v>252</v>
+      </c>
+      <c r="K42" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L42" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M42" s="10">
+        <f t="shared" si="3"/>
+        <v>366.66666666666669</v>
+      </c>
+      <c r="N42" s="10">
+        <f t="shared" si="4"/>
+        <v>1118.6666666666667</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>7</v>
       </c>
-      <c r="B43" s="8">
+      <c r="B43" s="6">
         <v>10</v>
       </c>
-      <c r="C43" t="s" s="1">
-        <v>56</v>
-      </c>
-      <c r="D43" t="s" s="1">
-        <v>60</v>
+      <c r="C43" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>57</v>
       </c>
       <c r="E43">
-        <v>293.0</v>
+        <v>454</v>
       </c>
       <c r="F43">
-        <v>194.0</v>
+        <v>293</v>
       </c>
       <c r="G43">
-        <v>38.8</v>
+        <v>194</v>
       </c>
       <c r="H43">
+        <v>38.799999999999997</v>
+      </c>
+      <c r="I43">
         <v>7.6</v>
       </c>
-      <c r="I43">
-        <v>3686.0</v>
-      </c>
-      <c r="J43">
-        <v>2966.0</v>
-      </c>
-      <c r="K43">
-        <v>6652.0</v>
-      </c>
-      <c r="L43">
-        <v>3686.0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:16" dyDescent="0.2">
+      <c r="J43" s="10">
+        <f t="shared" si="0"/>
+        <v>1362</v>
+      </c>
+      <c r="K43" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L43" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M43" s="10">
+        <f t="shared" si="3"/>
+        <v>1694.6666666666667</v>
+      </c>
+      <c r="N43" s="10">
+        <f t="shared" si="4"/>
+        <v>3556.666666666667</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>8</v>
       </c>
-      <c r="B44" s="8">
+      <c r="B44" s="6">
         <v>9</v>
       </c>
-      <c r="C44" t="s" s="1">
-        <v>59</v>
-      </c>
-      <c r="D44" t="s" s="1">
-        <v>58</v>
+      <c r="C44" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>55</v>
       </c>
       <c r="E44">
-        <v>384.0</v>
+        <v>486</v>
       </c>
       <c r="F44">
-        <v>363.0</v>
+        <v>474</v>
       </c>
       <c r="G44">
-        <v>72.6</v>
+        <v>363</v>
       </c>
       <c r="H44">
-        <v>5.3</v>
+        <v>72.599999999999994</v>
       </c>
       <c r="I44">
-        <v>6897.0</v>
-      </c>
-      <c r="J44">
-        <v>3633.0</v>
-      </c>
-      <c r="K44">
-        <v>10530.0</v>
-      </c>
-      <c r="L44">
-        <v>6897.0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:16" dyDescent="0.2">
+        <v>6.5</v>
+      </c>
+      <c r="J44" s="10">
+        <f t="shared" si="0"/>
+        <v>1458</v>
+      </c>
+      <c r="K44" s="10">
+        <f t="shared" si="1"/>
+        <v>250</v>
+      </c>
+      <c r="L44" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M44" s="10">
+        <f t="shared" si="3"/>
+        <v>2676</v>
+      </c>
+      <c r="N44" s="10">
+        <f t="shared" si="4"/>
+        <v>4884</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>8</v>
       </c>
-      <c r="B45" s="8">
+      <c r="B45" s="6">
         <v>10</v>
       </c>
-      <c r="C45" t="s" s="1">
-        <v>59</v>
-      </c>
-      <c r="D45" t="s" s="1">
-        <v>60</v>
+      <c r="C45" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>57</v>
       </c>
       <c r="E45">
-        <v>209.0</v>
+        <v>230</v>
       </c>
       <c r="F45">
-        <v>172.0</v>
+        <v>299</v>
       </c>
       <c r="G45">
+        <v>172</v>
+      </c>
+      <c r="H45">
         <v>34.4</v>
       </c>
-      <c r="H45">
-        <v>6.1</v>
-      </c>
       <c r="I45">
-        <v>3268.0</v>
-      </c>
-      <c r="J45">
-        <v>2037.0</v>
-      </c>
-      <c r="K45">
-        <v>5305.0</v>
-      </c>
-      <c r="L45">
-        <v>3268.0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:16" dyDescent="0.2">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="J45" s="10">
+        <f t="shared" si="0"/>
+        <v>690</v>
+      </c>
+      <c r="K45" s="10">
+        <f t="shared" si="1"/>
+        <v>250</v>
+      </c>
+      <c r="L45" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M45" s="10">
+        <f t="shared" si="3"/>
+        <v>1764.0000000000002</v>
+      </c>
+      <c r="N45" s="10">
+        <f t="shared" si="4"/>
+        <v>3204</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>9</v>
       </c>
-      <c r="B46" s="8">
+      <c r="B46" s="6">
         <v>10</v>
       </c>
-      <c r="C46" t="s" s="1">
-        <v>58</v>
-      </c>
-      <c r="D46" t="s" s="1">
-        <v>60</v>
+      <c r="C46" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>57</v>
       </c>
       <c r="E46">
-        <v>264.0</v>
+        <v>366</v>
       </c>
       <c r="F46">
-        <v>200.0</v>
+        <v>264</v>
       </c>
       <c r="G46">
-        <v>40.0</v>
+        <v>200</v>
       </c>
       <c r="H46">
+        <v>40</v>
+      </c>
+      <c r="I46">
         <v>6.6</v>
       </c>
-      <c r="I46">
-        <v>3800.0</v>
-      </c>
-      <c r="J46">
-        <v>2613.0</v>
-      </c>
-      <c r="K46">
-        <v>6413.0</v>
-      </c>
-      <c r="L46">
-        <v>3800.0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:16" dyDescent="0.2">
+      <c r="J46" s="10">
+        <f t="shared" si="0"/>
+        <v>1098</v>
+      </c>
+      <c r="K46" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L46" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M46" s="10">
+        <f t="shared" si="3"/>
+        <v>1493.3333333333335</v>
+      </c>
+      <c r="N46" s="10">
+        <f t="shared" si="4"/>
+        <v>3091.3333333333335</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>1</v>
       </c>
-      <c r="B47" s="8">
+      <c r="B47" s="6">
         <v>1</v>
       </c>
-      <c r="C47" s="8"/>
-      <c r="D47" s="8"/>
+      <c r="C47" s="6"/>
+      <c r="D47" s="6"/>
       <c r="E47">
         <v>0</v>
       </c>
@@ -2686,25 +3404,16 @@
       <c r="I47">
         <v>0</v>
       </c>
-      <c r="J47">
-        <v>0</v>
-      </c>
-      <c r="K47">
-        <v>0</v>
-      </c>
-      <c r="L47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:16" dyDescent="0.2">
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>2</v>
       </c>
-      <c r="B48" s="8">
+      <c r="B48" s="6">
         <v>2</v>
       </c>
-      <c r="C48" s="8"/>
-      <c r="D48" s="8"/>
+      <c r="C48" s="6"/>
+      <c r="D48" s="6"/>
       <c r="E48">
         <v>0</v>
       </c>
@@ -2720,25 +3429,16 @@
       <c r="I48">
         <v>0</v>
       </c>
-      <c r="J48">
-        <v>0</v>
-      </c>
-      <c r="K48">
-        <v>0</v>
-      </c>
-      <c r="L48">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:16" dyDescent="0.2">
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>3</v>
       </c>
-      <c r="B49" s="8">
+      <c r="B49" s="6">
         <v>3</v>
       </c>
-      <c r="C49" s="8"/>
-      <c r="D49" s="8"/>
+      <c r="C49" s="6"/>
+      <c r="D49" s="6"/>
       <c r="E49">
         <v>0</v>
       </c>
@@ -2754,25 +3454,16 @@
       <c r="I49">
         <v>0</v>
       </c>
-      <c r="J49">
-        <v>0</v>
-      </c>
-      <c r="K49">
-        <v>0</v>
-      </c>
-      <c r="L49">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:16" dyDescent="0.2">
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>4</v>
       </c>
-      <c r="B50" s="8">
+      <c r="B50" s="6">
         <v>4</v>
       </c>
-      <c r="C50" s="8"/>
-      <c r="D50" s="8"/>
+      <c r="C50" s="6"/>
+      <c r="D50" s="6"/>
       <c r="E50">
         <v>0</v>
       </c>
@@ -2788,25 +3479,16 @@
       <c r="I50">
         <v>0</v>
       </c>
-      <c r="J50">
-        <v>0</v>
-      </c>
-      <c r="K50">
-        <v>0</v>
-      </c>
-      <c r="L50">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:16" dyDescent="0.2">
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>5</v>
       </c>
-      <c r="B51" s="8">
+      <c r="B51" s="6">
         <v>5</v>
       </c>
-      <c r="C51" s="8"/>
-      <c r="D51" s="8"/>
+      <c r="C51" s="6"/>
+      <c r="D51" s="6"/>
       <c r="E51">
         <v>0</v>
       </c>
@@ -2822,21 +3504,12 @@
       <c r="I51">
         <v>0</v>
       </c>
-      <c r="J51">
-        <v>0</v>
-      </c>
-      <c r="K51">
-        <v>0</v>
-      </c>
-      <c r="L51">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:16" dyDescent="0.2">
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>6</v>
       </c>
-      <c r="B52" s="8">
+      <c r="B52" s="6">
         <v>6</v>
       </c>
       <c r="E52">
@@ -2854,21 +3527,12 @@
       <c r="I52">
         <v>0</v>
       </c>
-      <c r="J52">
-        <v>0</v>
-      </c>
-      <c r="K52">
-        <v>0</v>
-      </c>
-      <c r="L52">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:16" dyDescent="0.2">
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>7</v>
       </c>
-      <c r="B53" s="8">
+      <c r="B53" s="6">
         <v>7</v>
       </c>
       <c r="E53">
@@ -2886,21 +3550,12 @@
       <c r="I53">
         <v>0</v>
       </c>
-      <c r="J53">
-        <v>0</v>
-      </c>
-      <c r="K53">
-        <v>0</v>
-      </c>
-      <c r="L53">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:16" dyDescent="0.2">
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>8</v>
       </c>
-      <c r="B54" s="8">
+      <c r="B54" s="6">
         <v>8</v>
       </c>
       <c r="E54">
@@ -2918,21 +3573,12 @@
       <c r="I54">
         <v>0</v>
       </c>
-      <c r="J54">
-        <v>0</v>
-      </c>
-      <c r="K54">
-        <v>0</v>
-      </c>
-      <c r="L54">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:16" dyDescent="0.2">
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>9</v>
       </c>
-      <c r="B55" s="8">
+      <c r="B55" s="6">
         <v>9</v>
       </c>
       <c r="E55">
@@ -2950,21 +3596,12 @@
       <c r="I55">
         <v>0</v>
       </c>
-      <c r="J55">
-        <v>0</v>
-      </c>
-      <c r="K55">
-        <v>0</v>
-      </c>
-      <c r="L55">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:16" dyDescent="0.2">
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>10</v>
       </c>
-      <c r="B56" s="8">
+      <c r="B56" s="6">
         <v>10</v>
       </c>
       <c r="E56">
@@ -2982,39 +3619,9 @@
       <c r="I56">
         <v>0</v>
       </c>
-      <c r="J56">
-        <v>0</v>
-      </c>
-      <c r="K56">
-        <v>0</v>
-      </c>
-      <c r="L56">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:16" dyDescent="0.2">
-      <c r="G57" s="2"/>
-    </row>
-    <row r="58" spans="1:16" dyDescent="0.2">
-      <c r="G58" s="1"/>
-    </row>
-    <row r="59" spans="1:16" dyDescent="0.2">
-      <c r="G59" s="1"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="I2:I46">
-    <cfRule type="colorScale" priority="4">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J46">
+  <conditionalFormatting sqref="J2:J56">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -3026,7 +3633,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K46">
+  <conditionalFormatting sqref="M2:M56">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -3038,7 +3645,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L46">
+  <conditionalFormatting sqref="N2:N56">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -3051,5 +3658,8 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/inputData/Parameters.xlsx
+++ b/inputData/Parameters.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kapta\Documents\DTU\Speciale\GitHubFiles\inputData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sillewiberg/Desktop/Skole/Speciale/Master-Thesis-eVTOL-1/inputData/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D8B4F36-188F-4430-BEA5-EDE57B764090}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0218802E-FB40-954D-9A70-48D7F6E8A911}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="28800" windowHeight="15285" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
+    <workbookView xWindow="0" yWindow="1180" windowWidth="28800" windowHeight="15280" activeTab="1" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
   </bookViews>
   <sheets>
     <sheet name="Parameters" sheetId="9" r:id="rId1"/>
-    <sheet name="Prices" sheetId="12" r:id="rId2"/>
+    <sheet name="Prices" sheetId="13" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="64">
   <si>
     <t>cap_u</t>
   </si>
@@ -117,15 +117,6 @@
     <t>Hvor meget hurtigere</t>
   </si>
   <si>
-    <t>Fd km</t>
-  </si>
-  <si>
-    <t>Fd tid</t>
-  </si>
-  <si>
-    <t>fd max</t>
-  </si>
-  <si>
     <t>Passager km pris</t>
   </si>
   <si>
@@ -220,13 +211,35 @@
   </si>
   <si>
     <t>(56.049305, 12.584406)</t>
+  </si>
+  <si>
+    <t>Bil km</t>
+  </si>
+  <si>
+    <t>Pris (Bil udgift)</t>
+  </si>
+  <si>
+    <t>Færge (gns. Gælder kun Bornholm)</t>
+  </si>
+  <si>
+    <t>Base</t>
+  </si>
+  <si>
+    <t>Pris (udfra tidsbesparelse)</t>
+  </si>
+  <si>
+    <t>Km bil pris</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+  </numFmts>
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -254,13 +267,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <strike/>
       <sz val="12"/>
       <color theme="1"/>
@@ -274,16 +280,37 @@
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor theme="1"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -291,11 +318,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -304,19 +341,161 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Comma 2" xfId="1" xr:uid="{B5076C6D-4567-C74F-A5A8-80AE462FFA5E}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="8">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -327,6 +506,35 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3CFD079E-5109-8F49-8A19-E09E2BEBBC8C}" name="Table13" displayName="Table13" ref="A1:N56" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6" headerRowCellStyle="Comma" dataCellStyle="Comma">
+  <autoFilter ref="A1:N56" xr:uid="{CEDCB4F7-0752-8449-BE87-89650C1E9E7C}"/>
+  <tableColumns count="14">
+    <tableColumn id="1" xr3:uid="{0330B38A-598B-B64A-86F4-FA8E25EAC437}" name="From"/>
+    <tableColumn id="2" xr3:uid="{DA4E4644-7B10-0541-B73A-349A5A6836E2}" name="To" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{354A3716-07E2-0F49-9392-E1F6D4672CCE}" name="cord_from"/>
+    <tableColumn id="4" xr3:uid="{CA960CCE-0555-F44E-9C8F-AE9C1925F667}" name="cord_to"/>
+    <tableColumn id="5" xr3:uid="{D42F7B17-60EA-DB4D-8238-39B387D0ABC3}" name="Bil km"/>
+    <tableColumn id="6" xr3:uid="{4D9FAB2B-036C-054C-AB09-29F5B4ADED42}" name="Bil tid (min)"/>
+    <tableColumn id="7" xr3:uid="{59F6BECD-EB60-114E-826A-884ADDC4EE72}" name="Km fugleflugt"/>
+    <tableColumn id="8" xr3:uid="{605D45AE-CBF2-E342-BA16-1B205DDE6C4E}" name="eVTOL flyvetid (min)"/>
+    <tableColumn id="9" xr3:uid="{FCFA00C8-AEDC-F54B-AE4D-2360ACC6025E}" name="Hvor meget hurtigere"/>
+    <tableColumn id="10" xr3:uid="{DBB7D64B-F97D-5C46-B464-1DA11C10DF3A}" name="Pris (Bil udgift)" dataDxfId="4" dataCellStyle="Comma"/>
+    <tableColumn id="11" xr3:uid="{CC283087-BB53-D146-A233-2D178D7E3562}" name="Færge (gns. Gælder kun Bornholm)" dataDxfId="3" dataCellStyle="Comma"/>
+    <tableColumn id="12" xr3:uid="{B4DC4D17-2AE3-D34D-926C-7506AC52E6B8}" name="Base" dataDxfId="2" dataCellStyle="Comma">
+      <calculatedColumnFormula>$Q$5</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="13" xr3:uid="{E70B016F-0534-2048-951F-6FD04DC33B7C}" name="Pris (udfra tidsbesparelse)" dataDxfId="1" dataCellStyle="Comma">
+      <calculatedColumnFormula>$Q$4*MAX(F2-G2*$Q$1)*$Q$3</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="14" xr3:uid="{67EF8C2F-B7CB-8D4A-8447-692E942D0514}" name="fd_sum" dataDxfId="0" dataCellStyle="Comma">
+      <calculatedColumnFormula>SUM(J2:M2)</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -647,18 +855,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B15C49E0-A7B4-734A-8962-DC2A879F4079}">
   <dimension ref="A1:D20"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="22.625" customWidth="1"/>
-    <col min="2" max="2" width="10.875" style="4"/>
+    <col min="1" max="1" width="22.6640625" customWidth="1"/>
+    <col min="2" max="2" width="10.83203125" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>20</v>
       </c>
@@ -669,7 +877,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -680,18 +888,18 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B4" s="4">
         <v>400</v>
       </c>
       <c r="D4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -699,10 +907,10 @@
         <v>300</v>
       </c>
       <c r="D5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -713,7 +921,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -724,7 +932,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -733,10 +941,10 @@
         <v>0.2</v>
       </c>
       <c r="D8" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>0</v>
       </c>
@@ -747,7 +955,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>1</v>
       </c>
@@ -758,9 +966,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B11" s="4">
         <v>80</v>
@@ -769,7 +977,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>2</v>
       </c>
@@ -780,18 +988,18 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B13" s="4">
         <v>20</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -800,10 +1008,10 @@
         <v>2.11</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>4</v>
       </c>
@@ -815,7 +1023,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>5</v>
       </c>
@@ -827,7 +1035,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>6</v>
       </c>
@@ -838,15 +1046,15 @@
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B20" s="4">
         <v>1</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -856,1821 +1064,2331 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAF0D5EA-53B5-1240-9D84-6FE223856A18}">
-  <dimension ref="A1:P59"/>
-  <sheetFormatPr defaultColWidth="10.625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36FC1A80-FC3B-6349-8B7A-4A1A2A7C8FC7}">
+  <dimension ref="A1:R56"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="17.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="17.125" customWidth="1"/>
-    <col min="5" max="5" width="12.125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="17.1640625" customWidth="1"/>
+    <col min="5" max="5" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5" customWidth="1"/>
+    <col min="7" max="7" width="17.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.33203125" customWidth="1"/>
+    <col min="9" max="9" width="21" style="10" customWidth="1"/>
+    <col min="10" max="10" width="13.6640625" style="10" customWidth="1"/>
+    <col min="11" max="11" width="32.1640625" style="10" customWidth="1"/>
+    <col min="12" max="12" width="10.6640625" style="10"/>
+    <col min="13" max="13" width="27" style="10" customWidth="1"/>
+    <col min="14" max="14" width="10.83203125" style="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
-        <v>36</v>
+    <row r="1" spans="1:18" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1" s="7" t="s">
+        <v>33</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="E1" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="E1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F1" t="s">
         <v>22</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="G1" t="s">
         <v>23</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="H1" t="s">
         <v>24</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="I1" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="I1" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="L1" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="N1" s="6" t="s">
+      <c r="J1" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="K1" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="L1" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="M1" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="N1" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="P1" t="s">
         <v>19</v>
       </c>
-      <c r="O1" s="7">
+      <c r="Q1">
         <v>0.2</v>
       </c>
-      <c r="P1" s="6"/>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="8">
+      <c r="B2" s="6">
         <v>2</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E2">
+        <v>267</v>
+      </c>
+      <c r="F2">
         <v>185</v>
       </c>
-      <c r="F2">
+      <c r="G2">
         <v>219</v>
       </c>
-      <c r="G2">
+      <c r="H2">
         <v>43.8</v>
       </c>
-      <c r="H2">
+      <c r="I2">
         <v>4.2</v>
       </c>
-      <c r="I2">
-        <v>4161</v>
-      </c>
-      <c r="J2">
-        <v>1647</v>
-      </c>
-      <c r="K2">
-        <v>5808</v>
-      </c>
-      <c r="L2">
-        <v>4161</v>
-      </c>
-      <c r="N2" t="s">
-        <v>29</v>
-      </c>
-      <c r="O2" s="4">
-        <v>19</v>
+      <c r="J2" s="10">
+        <f>$Q$6*E2</f>
+        <v>801</v>
+      </c>
+      <c r="K2" s="10">
+        <f>IF(A2=8,250,0)+IF(B2=8,250,0)</f>
+        <v>0</v>
+      </c>
+      <c r="L2" s="10">
+        <f>$Q$5</f>
+        <v>500</v>
+      </c>
+      <c r="M2" s="10">
+        <f>$Q$4*MAX(F2-G2*$Q$1)*$Q$3</f>
+        <v>941.33333333333326</v>
+      </c>
+      <c r="N2" s="10">
+        <f>SUM(J2:M2)</f>
+        <v>2242.333333333333</v>
       </c>
       <c r="P2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="Q2">
+        <v>16</v>
+      </c>
+      <c r="R2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>1</v>
       </c>
-      <c r="B3" s="8">
+      <c r="B3" s="6">
         <v>3</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E3">
+        <v>100</v>
+      </c>
+      <c r="F3">
         <v>82</v>
       </c>
-      <c r="F3">
+      <c r="G3">
         <v>88</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>17.600000000000001</v>
       </c>
-      <c r="H3">
+      <c r="I3">
         <v>4.7</v>
       </c>
-      <c r="I3">
-        <v>1672</v>
-      </c>
-      <c r="J3">
-        <v>751</v>
-      </c>
-      <c r="K3">
-        <v>2423</v>
-      </c>
-      <c r="L3">
-        <v>1672</v>
-      </c>
-      <c r="N3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O3" s="4">
-        <f>1000/60</f>
-        <v>16.666666666666668</v>
+      <c r="J3" s="10">
+        <f t="shared" ref="J3:J46" si="0">$Q$6*E3</f>
+        <v>300</v>
+      </c>
+      <c r="K3" s="10">
+        <f t="shared" ref="K3:K46" si="1">IF(A3=8,250,0)+IF(B3=8,250,0)</f>
+        <v>0</v>
+      </c>
+      <c r="L3" s="10">
+        <f t="shared" ref="L3:L46" si="2">$Q$5</f>
+        <v>500</v>
+      </c>
+      <c r="M3" s="10">
+        <f t="shared" ref="M3:M46" si="3">$Q$4*MAX(F3-G3*$Q$1)*$Q$3</f>
+        <v>429.33333333333337</v>
+      </c>
+      <c r="N3" s="10">
+        <f t="shared" ref="N3:N46" si="4">SUM(J3:M3)</f>
+        <v>1229.3333333333335</v>
       </c>
       <c r="P3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+      <c r="Q3">
+        <f>800/60</f>
+        <v>13.333333333333334</v>
+      </c>
+      <c r="R3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>1</v>
       </c>
-      <c r="B4" s="8">
+      <c r="B4" s="6">
         <v>4</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>53</v>
-      </c>
       <c r="E4">
+        <v>347</v>
+      </c>
+      <c r="F4">
         <v>228</v>
       </c>
-      <c r="F4">
+      <c r="G4">
         <v>147</v>
       </c>
-      <c r="G4">
+      <c r="H4">
         <v>29.4</v>
       </c>
-      <c r="H4">
+      <c r="I4">
         <v>7.8</v>
       </c>
-      <c r="I4">
-        <v>2793</v>
-      </c>
-      <c r="J4">
-        <v>2317</v>
-      </c>
-      <c r="K4">
-        <v>5110</v>
-      </c>
-      <c r="L4">
-        <v>2793</v>
-      </c>
-      <c r="N4" t="s">
-        <v>33</v>
-      </c>
-      <c r="O4" s="4">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="J4" s="10">
+        <f t="shared" si="0"/>
+        <v>1041</v>
+      </c>
+      <c r="K4" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L4" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M4" s="10">
+        <f>$Q$4*MAX(F4-G4*$Q$1)*$Q$3</f>
+        <v>1324</v>
+      </c>
+      <c r="N4" s="10">
+        <f>SUM(J4:M4)</f>
+        <v>2865</v>
+      </c>
+      <c r="P4" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q4">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>1</v>
       </c>
-      <c r="B5" s="8">
+      <c r="B5" s="6">
         <v>5</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E5">
+        <v>177</v>
+      </c>
+      <c r="F5">
         <v>126</v>
       </c>
-      <c r="F5">
+      <c r="G5">
         <v>147</v>
       </c>
-      <c r="G5">
+      <c r="H5">
         <v>29.4</v>
       </c>
-      <c r="H5">
+      <c r="I5">
         <v>4.3</v>
       </c>
-      <c r="I5">
-        <v>2793</v>
-      </c>
-      <c r="J5">
-        <v>1127</v>
-      </c>
-      <c r="K5">
-        <v>3920</v>
-      </c>
-      <c r="L5">
-        <v>2793</v>
-      </c>
-      <c r="N5" t="s">
-        <v>34</v>
-      </c>
-      <c r="O5" s="4">
-        <v>0</v>
+      <c r="J5" s="10">
+        <f>$Q$6*E5</f>
+        <v>531</v>
+      </c>
+      <c r="K5" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L5" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M5" s="10">
+        <f>$Q$4*MAX(F5-G5*$Q$1)*$Q$3</f>
+        <v>644</v>
+      </c>
+      <c r="N5" s="10">
+        <f t="shared" si="4"/>
+        <v>1675</v>
       </c>
       <c r="P5" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+      <c r="Q5">
+        <v>500</v>
+      </c>
+      <c r="R5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>1</v>
       </c>
-      <c r="B6" s="8">
+      <c r="B6" s="6">
         <v>6</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E6">
+        <v>325</v>
+      </c>
+      <c r="F6">
         <v>205</v>
       </c>
-      <c r="F6">
+      <c r="G6">
         <v>197</v>
       </c>
-      <c r="G6">
+      <c r="H6">
         <v>39.4</v>
       </c>
-      <c r="H6">
+      <c r="I6">
         <v>5.2</v>
       </c>
-      <c r="I6">
-        <v>3743</v>
-      </c>
-      <c r="J6">
-        <v>1932</v>
-      </c>
-      <c r="K6">
-        <v>5675</v>
-      </c>
-      <c r="L6">
-        <v>3743</v>
-      </c>
-      <c r="O6" s="4"/>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="J6" s="10">
+        <f t="shared" si="0"/>
+        <v>975</v>
+      </c>
+      <c r="K6" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L6" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M6" s="10">
+        <f t="shared" si="3"/>
+        <v>1104</v>
+      </c>
+      <c r="N6" s="10">
+        <f t="shared" si="4"/>
+        <v>2579</v>
+      </c>
+      <c r="P6" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q6">
+        <v>3</v>
+      </c>
+      <c r="R6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>1</v>
       </c>
-      <c r="B7" s="8">
+      <c r="B7" s="6">
         <v>7</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E7">
+        <v>415</v>
+      </c>
+      <c r="F7">
         <v>263</v>
       </c>
-      <c r="F7">
+      <c r="G7">
         <v>227</v>
       </c>
-      <c r="G7">
+      <c r="H7">
         <v>45.4</v>
       </c>
-      <c r="H7">
+      <c r="I7">
         <v>5.8</v>
       </c>
-      <c r="I7">
-        <v>4313</v>
-      </c>
-      <c r="J7">
-        <v>2539</v>
-      </c>
-      <c r="K7">
-        <v>6852</v>
-      </c>
-      <c r="L7">
-        <v>4313</v>
-      </c>
-      <c r="O7" s="4"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="J7" s="10">
+        <f t="shared" si="0"/>
+        <v>1245</v>
+      </c>
+      <c r="K7" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L7" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M7" s="10">
+        <f t="shared" si="3"/>
+        <v>1450.6666666666667</v>
+      </c>
+      <c r="N7" s="10">
+        <f t="shared" si="4"/>
+        <v>3195.666666666667</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>1</v>
       </c>
-      <c r="B8" s="8">
+      <c r="B8" s="6">
         <v>8</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E8">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="F8">
+        <v>246</v>
+      </c>
+      <c r="G8">
         <v>144</v>
       </c>
-      <c r="G8">
+      <c r="H8">
         <v>28.8</v>
       </c>
-      <c r="H8">
-        <v>5.4</v>
-      </c>
       <c r="I8">
-        <v>2736</v>
-      </c>
-      <c r="J8">
-        <v>1484</v>
-      </c>
-      <c r="K8">
-        <v>4220</v>
-      </c>
-      <c r="L8">
-        <v>2736</v>
-      </c>
-      <c r="O8" s="4"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+        <v>8.5</v>
+      </c>
+      <c r="J8" s="10">
+        <f t="shared" si="0"/>
+        <v>480</v>
+      </c>
+      <c r="K8" s="10">
+        <f t="shared" si="1"/>
+        <v>250</v>
+      </c>
+      <c r="L8" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M8" s="10">
+        <f t="shared" si="3"/>
+        <v>1448</v>
+      </c>
+      <c r="N8" s="10">
+        <f t="shared" si="4"/>
+        <v>2678</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>1</v>
       </c>
-      <c r="B9" s="8">
+      <c r="B9" s="6">
         <v>9</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E9">
+        <v>326</v>
+      </c>
+      <c r="F9">
         <v>230</v>
       </c>
-      <c r="F9">
+      <c r="G9">
         <v>219</v>
       </c>
-      <c r="G9">
+      <c r="H9">
         <v>43.8</v>
       </c>
-      <c r="H9">
+      <c r="I9">
         <v>5.3</v>
       </c>
-      <c r="I9">
-        <v>4161</v>
-      </c>
-      <c r="J9">
-        <v>2172</v>
-      </c>
-      <c r="K9">
-        <v>6333</v>
-      </c>
-      <c r="L9">
-        <v>4161</v>
-      </c>
-      <c r="O9" s="4"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="J9" s="10">
+        <f t="shared" si="0"/>
+        <v>978</v>
+      </c>
+      <c r="K9" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L9" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M9" s="10">
+        <f>$Q$4*MAX(F9-G9*$Q$1)*$Q$3</f>
+        <v>1241.3333333333333</v>
+      </c>
+      <c r="N9" s="10">
+        <f t="shared" si="4"/>
+        <v>2719.333333333333</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>1</v>
       </c>
-      <c r="B10" s="8">
+      <c r="B10" s="6">
         <v>10</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E10">
+        <v>70</v>
+      </c>
+      <c r="F10">
         <v>56</v>
       </c>
-      <c r="F10">
+      <c r="G10">
         <v>47</v>
       </c>
-      <c r="G10">
+      <c r="H10">
         <v>9.4</v>
       </c>
-      <c r="H10">
+      <c r="I10">
         <v>6</v>
       </c>
-      <c r="I10">
-        <v>893</v>
-      </c>
-      <c r="J10">
-        <v>544</v>
-      </c>
-      <c r="K10">
-        <v>1437</v>
-      </c>
-      <c r="L10">
-        <v>893</v>
-      </c>
-      <c r="O10" s="4"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="J10" s="10">
+        <f t="shared" si="0"/>
+        <v>210</v>
+      </c>
+      <c r="K10" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L10" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M10" s="10">
+        <f t="shared" si="3"/>
+        <v>310.66666666666669</v>
+      </c>
+      <c r="N10" s="10">
+        <f t="shared" si="4"/>
+        <v>1020.6666666666667</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>2</v>
       </c>
-      <c r="B11" s="8">
+      <c r="B11" s="6">
         <v>3</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E11">
+        <v>211</v>
+      </c>
+      <c r="F11">
         <v>173</v>
       </c>
-      <c r="F11">
+      <c r="G11">
         <v>131</v>
       </c>
-      <c r="G11">
+      <c r="H11">
         <v>26.2</v>
       </c>
-      <c r="H11">
+      <c r="I11">
         <v>6.6</v>
       </c>
-      <c r="I11">
-        <v>2489</v>
-      </c>
-      <c r="J11">
-        <v>1713</v>
-      </c>
-      <c r="K11">
-        <v>4202</v>
-      </c>
-      <c r="L11">
-        <v>2489</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="J11" s="10">
+        <f t="shared" si="0"/>
+        <v>633</v>
+      </c>
+      <c r="K11" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L11" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M11" s="10">
+        <f t="shared" si="3"/>
+        <v>978.66666666666674</v>
+      </c>
+      <c r="N11" s="10">
+        <f t="shared" si="4"/>
+        <v>2111.666666666667</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>2</v>
       </c>
-      <c r="B12" s="8">
+      <c r="B12" s="6">
         <v>4</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E12">
+        <v>137</v>
+      </c>
+      <c r="F12">
         <v>103</v>
       </c>
-      <c r="F12">
+      <c r="G12">
         <v>110</v>
       </c>
-      <c r="G12">
+      <c r="H12">
         <v>22</v>
       </c>
-      <c r="H12">
+      <c r="I12">
         <v>4.7</v>
       </c>
-      <c r="I12">
-        <v>2090</v>
-      </c>
-      <c r="J12">
-        <v>945</v>
-      </c>
-      <c r="K12">
-        <v>3035</v>
-      </c>
-      <c r="L12">
-        <v>2090</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="J12" s="10">
+        <f t="shared" si="0"/>
+        <v>411</v>
+      </c>
+      <c r="K12" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L12" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M12" s="10">
+        <f t="shared" si="3"/>
+        <v>540</v>
+      </c>
+      <c r="N12" s="10">
+        <f t="shared" si="4"/>
+        <v>1451</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>2</v>
       </c>
-      <c r="B13" s="8">
+      <c r="B13" s="6">
         <v>5</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D13" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="E13">
+        <v>106</v>
+      </c>
+      <c r="F13">
         <v>89</v>
       </c>
-      <c r="F13">
+      <c r="G13">
         <v>80</v>
       </c>
-      <c r="G13">
+      <c r="H13">
         <v>16</v>
       </c>
-      <c r="H13">
+      <c r="I13">
         <v>5.6</v>
       </c>
-      <c r="I13">
-        <v>1520</v>
-      </c>
-      <c r="J13">
-        <v>852</v>
-      </c>
-      <c r="K13">
-        <v>2372</v>
-      </c>
-      <c r="L13">
-        <v>1520</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="J13" s="10">
+        <f t="shared" si="0"/>
+        <v>318</v>
+      </c>
+      <c r="K13" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L13" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M13" s="10">
+        <f t="shared" si="3"/>
+        <v>486.66666666666669</v>
+      </c>
+      <c r="N13" s="10">
+        <f t="shared" si="4"/>
+        <v>1304.6666666666667</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>2</v>
       </c>
-      <c r="B14" s="8">
+      <c r="B14" s="6">
         <v>6</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E14">
+        <v>137</v>
+      </c>
+      <c r="F14">
         <v>100</v>
       </c>
-      <c r="F14">
+      <c r="G14">
         <v>98</v>
       </c>
-      <c r="G14">
+      <c r="H14">
         <v>19.600000000000001</v>
       </c>
-      <c r="H14">
+      <c r="I14">
         <v>5.0999999999999996</v>
       </c>
-      <c r="I14">
-        <v>1862</v>
-      </c>
-      <c r="J14">
-        <v>938</v>
-      </c>
-      <c r="K14">
-        <v>2800</v>
-      </c>
-      <c r="L14">
-        <v>1862</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="J14" s="10">
+        <f t="shared" si="0"/>
+        <v>411</v>
+      </c>
+      <c r="K14" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L14" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M14" s="10">
+        <f t="shared" si="3"/>
+        <v>536.00000000000011</v>
+      </c>
+      <c r="N14" s="10">
+        <f t="shared" si="4"/>
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>2</v>
       </c>
-      <c r="B15" s="8">
+      <c r="B15" s="6">
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="D15" s="11" t="s">
-        <v>56</v>
+        <v>48</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>53</v>
       </c>
       <c r="E15">
+        <v>205</v>
+      </c>
+      <c r="F15">
         <v>138</v>
       </c>
-      <c r="F15">
+      <c r="G15">
         <v>151</v>
       </c>
-      <c r="G15">
+      <c r="H15">
         <v>30.2</v>
       </c>
-      <c r="H15">
+      <c r="I15">
         <v>4.5999999999999996</v>
       </c>
-      <c r="I15">
-        <v>2869</v>
-      </c>
-      <c r="J15">
-        <v>1258</v>
-      </c>
-      <c r="K15">
-        <v>4127</v>
-      </c>
-      <c r="L15">
-        <v>2869</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="J15" s="10">
+        <f t="shared" si="0"/>
+        <v>615</v>
+      </c>
+      <c r="K15" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L15" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M15" s="10">
+        <f t="shared" si="3"/>
+        <v>718.66666666666663</v>
+      </c>
+      <c r="N15" s="10">
+        <f t="shared" si="4"/>
+        <v>1833.6666666666665</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>2</v>
       </c>
-      <c r="B16" s="8">
+      <c r="B16" s="6">
         <v>8</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E16">
-        <v>339</v>
+        <v>426</v>
       </c>
       <c r="F16">
+        <v>429</v>
+      </c>
+      <c r="G16">
         <v>359</v>
       </c>
-      <c r="G16">
+      <c r="H16">
         <v>71.8</v>
       </c>
-      <c r="H16">
-        <v>4.7</v>
-      </c>
       <c r="I16">
-        <v>6821</v>
-      </c>
-      <c r="J16">
-        <v>3117</v>
-      </c>
-      <c r="K16">
-        <v>9938</v>
-      </c>
-      <c r="L16">
-        <v>6821</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="J16" s="10">
+        <f t="shared" si="0"/>
+        <v>1278</v>
+      </c>
+      <c r="K16" s="10">
+        <f t="shared" si="1"/>
+        <v>250</v>
+      </c>
+      <c r="L16" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M16" s="10">
+        <f t="shared" si="3"/>
+        <v>2381.3333333333335</v>
+      </c>
+      <c r="N16" s="10">
+        <f t="shared" si="4"/>
+        <v>4409.3333333333339</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>2</v>
       </c>
-      <c r="B17" s="8">
+      <c r="B17" s="6">
         <v>9</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E17">
+        <v>89</v>
+      </c>
+      <c r="F17">
         <v>87</v>
       </c>
-      <c r="F17">
+      <c r="G17">
         <v>76</v>
       </c>
-      <c r="G17">
+      <c r="H17">
         <v>15.2</v>
       </c>
-      <c r="H17">
+      <c r="I17">
         <v>5.7</v>
       </c>
-      <c r="I17">
-        <v>1444</v>
-      </c>
-      <c r="J17">
-        <v>838</v>
-      </c>
-      <c r="K17">
-        <v>2282</v>
-      </c>
-      <c r="L17">
-        <v>1444</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J17" s="10">
+        <f t="shared" si="0"/>
+        <v>267</v>
+      </c>
+      <c r="K17" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L17" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M17" s="10">
+        <f t="shared" si="3"/>
+        <v>478.66666666666669</v>
+      </c>
+      <c r="N17" s="10">
+        <f t="shared" si="4"/>
+        <v>1245.6666666666667</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>2</v>
       </c>
-      <c r="B18" s="8">
+      <c r="B18" s="6">
         <v>10</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E18">
+        <v>305</v>
+      </c>
+      <c r="F18">
         <v>218</v>
       </c>
-      <c r="F18">
+      <c r="G18">
         <v>217</v>
       </c>
-      <c r="G18">
+      <c r="H18">
         <v>43.4</v>
       </c>
-      <c r="H18">
+      <c r="I18">
         <v>5</v>
       </c>
-      <c r="I18">
-        <v>4123</v>
-      </c>
-      <c r="J18">
-        <v>2037</v>
-      </c>
-      <c r="K18">
-        <v>6160</v>
-      </c>
-      <c r="L18">
-        <v>4123</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J18" s="10">
+        <f t="shared" si="0"/>
+        <v>915</v>
+      </c>
+      <c r="K18" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L18" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M18" s="10">
+        <f t="shared" si="3"/>
+        <v>1164</v>
+      </c>
+      <c r="N18" s="10">
+        <f t="shared" si="4"/>
+        <v>2579</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>3</v>
       </c>
-      <c r="B19" s="8">
+      <c r="B19" s="6">
         <v>4</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E19">
+        <v>291</v>
+      </c>
+      <c r="F19">
         <v>215</v>
       </c>
-      <c r="F19">
+      <c r="G19">
         <v>77</v>
       </c>
-      <c r="G19">
+      <c r="H19">
         <v>15.4</v>
       </c>
-      <c r="H19">
+      <c r="I19">
         <v>14</v>
       </c>
-      <c r="I19">
-        <v>1463</v>
-      </c>
-      <c r="J19">
-        <v>2329</v>
-      </c>
-      <c r="K19">
-        <v>3792</v>
-      </c>
-      <c r="L19">
-        <v>2329</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J19" s="10">
+        <f t="shared" si="0"/>
+        <v>873</v>
+      </c>
+      <c r="K19" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L19" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M19" s="10">
+        <f t="shared" si="3"/>
+        <v>1330.6666666666667</v>
+      </c>
+      <c r="N19" s="10">
+        <f t="shared" si="4"/>
+        <v>2703.666666666667</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>3</v>
       </c>
-      <c r="B20" s="8">
+      <c r="B20" s="6">
         <v>5</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E20">
+        <v>121</v>
+      </c>
+      <c r="F20">
         <v>113</v>
       </c>
-      <c r="F20">
+      <c r="G20">
         <v>63</v>
       </c>
-      <c r="G20">
+      <c r="H20">
         <v>12.6</v>
       </c>
-      <c r="H20">
+      <c r="I20">
         <v>9</v>
       </c>
-      <c r="I20">
-        <v>1197</v>
-      </c>
-      <c r="J20">
-        <v>1171</v>
-      </c>
-      <c r="K20">
-        <v>2368</v>
-      </c>
-      <c r="L20">
-        <v>1197</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J20" s="10">
+        <f t="shared" si="0"/>
+        <v>363</v>
+      </c>
+      <c r="K20" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L20" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M20" s="10">
+        <f t="shared" si="3"/>
+        <v>669.33333333333337</v>
+      </c>
+      <c r="N20" s="10">
+        <f t="shared" si="4"/>
+        <v>1532.3333333333335</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>3</v>
       </c>
-      <c r="B21" s="8">
+      <c r="B21" s="6">
         <v>6</v>
       </c>
       <c r="C21" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D21" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D21" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="E21">
+        <v>269</v>
+      </c>
+      <c r="F21">
         <v>192</v>
       </c>
-      <c r="F21">
+      <c r="G21">
         <v>126</v>
       </c>
-      <c r="G21">
+      <c r="H21">
         <v>25.2</v>
       </c>
-      <c r="H21">
+      <c r="I21">
         <v>7.6</v>
       </c>
-      <c r="I21">
-        <v>2394</v>
-      </c>
-      <c r="J21">
-        <v>1946</v>
-      </c>
-      <c r="K21">
-        <v>4340</v>
-      </c>
-      <c r="L21">
-        <v>2394</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J21" s="10">
+        <f t="shared" si="0"/>
+        <v>807</v>
+      </c>
+      <c r="K21" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L21" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M21" s="10">
+        <f t="shared" si="3"/>
+        <v>1112.0000000000002</v>
+      </c>
+      <c r="N21" s="10">
+        <f t="shared" si="4"/>
+        <v>2419</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>3</v>
       </c>
-      <c r="B22" s="8">
+      <c r="B22" s="6">
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D22" s="11" t="s">
-        <v>56</v>
+        <v>49</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>53</v>
       </c>
       <c r="E22">
+        <v>359</v>
+      </c>
+      <c r="F22">
         <v>250</v>
       </c>
-      <c r="F22">
+      <c r="G22">
         <v>167</v>
       </c>
-      <c r="G22">
+      <c r="H22">
         <v>33.4</v>
       </c>
-      <c r="H22">
+      <c r="I22">
         <v>7.5</v>
       </c>
-      <c r="I22">
-        <v>3173</v>
-      </c>
-      <c r="J22">
-        <v>2527</v>
-      </c>
-      <c r="K22">
-        <v>5700</v>
-      </c>
-      <c r="L22">
-        <v>3173</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J22" s="10">
+        <f t="shared" si="0"/>
+        <v>1077</v>
+      </c>
+      <c r="K22" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L22" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M22" s="10">
+        <f t="shared" si="3"/>
+        <v>1444</v>
+      </c>
+      <c r="N22" s="10">
+        <f t="shared" si="4"/>
+        <v>3021</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>3</v>
       </c>
-      <c r="B23" s="8">
+      <c r="B23" s="6">
         <v>8</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E23">
-        <v>234</v>
+        <v>259</v>
       </c>
       <c r="F23">
+        <v>324</v>
+      </c>
+      <c r="G23">
         <v>230</v>
       </c>
-      <c r="G23">
+      <c r="H23">
         <v>46</v>
       </c>
-      <c r="H23">
-        <v>5.0999999999999996</v>
-      </c>
       <c r="I23">
-        <v>4370</v>
-      </c>
-      <c r="J23">
-        <v>2193</v>
-      </c>
-      <c r="K23">
-        <v>6563</v>
-      </c>
-      <c r="L23">
-        <v>4370</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="J23" s="10">
+        <f t="shared" si="0"/>
+        <v>777</v>
+      </c>
+      <c r="K23" s="10">
+        <f t="shared" si="1"/>
+        <v>250</v>
+      </c>
+      <c r="L23" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M23" s="10">
+        <f t="shared" si="3"/>
+        <v>1853.3333333333335</v>
+      </c>
+      <c r="N23" s="10">
+        <f t="shared" si="4"/>
+        <v>3380.3333333333335</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>3</v>
       </c>
-      <c r="B24" s="8">
+      <c r="B24" s="6">
         <v>9</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E24">
+        <v>270</v>
+      </c>
+      <c r="F24">
         <v>217</v>
       </c>
-      <c r="F24">
+      <c r="G24">
         <v>138</v>
       </c>
-      <c r="G24">
+      <c r="H24">
         <v>27.6</v>
       </c>
-      <c r="H24">
+      <c r="I24">
         <v>7.9</v>
       </c>
-      <c r="I24">
-        <v>2622</v>
-      </c>
-      <c r="J24">
-        <v>2210</v>
-      </c>
-      <c r="K24">
-        <v>4832</v>
-      </c>
-      <c r="L24">
-        <v>2622</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J24" s="10">
+        <f t="shared" si="0"/>
+        <v>810</v>
+      </c>
+      <c r="K24" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L24" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M24" s="10">
+        <f t="shared" si="3"/>
+        <v>1262.6666666666667</v>
+      </c>
+      <c r="N24" s="10">
+        <f t="shared" si="4"/>
+        <v>2572.666666666667</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>3</v>
       </c>
-      <c r="B25" s="8">
+      <c r="B25" s="6">
         <v>10</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E25">
+        <v>131</v>
+      </c>
+      <c r="F25">
         <v>108</v>
       </c>
-      <c r="F25">
+      <c r="G25">
         <v>92</v>
       </c>
-      <c r="G25">
+      <c r="H25">
         <v>18.399999999999999</v>
       </c>
-      <c r="H25">
+      <c r="I25">
         <v>5.9</v>
       </c>
-      <c r="I25">
-        <v>1748</v>
-      </c>
-      <c r="J25">
-        <v>1045</v>
-      </c>
-      <c r="K25">
-        <v>2793</v>
-      </c>
-      <c r="L25">
-        <v>1748</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J25" s="10">
+        <f t="shared" si="0"/>
+        <v>393</v>
+      </c>
+      <c r="K25" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L25" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M25" s="10">
+        <f t="shared" si="3"/>
+        <v>597.33333333333337</v>
+      </c>
+      <c r="N25" s="10">
+        <f t="shared" si="4"/>
+        <v>1490.3333333333335</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>4</v>
       </c>
-      <c r="B26" s="8">
+      <c r="B26" s="6">
         <v>5</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E26">
+        <v>187</v>
+      </c>
+      <c r="F26">
         <v>130</v>
       </c>
-      <c r="F26">
+      <c r="G26">
         <v>93</v>
       </c>
-      <c r="G26">
+      <c r="H26">
         <v>18.600000000000001</v>
       </c>
-      <c r="H26">
+      <c r="I26">
         <v>7</v>
       </c>
-      <c r="I26">
-        <v>1767</v>
-      </c>
-      <c r="J26">
-        <v>1300</v>
-      </c>
-      <c r="K26">
-        <v>3067</v>
-      </c>
-      <c r="L26">
-        <v>1767</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J26" s="10">
+        <f t="shared" si="0"/>
+        <v>561</v>
+      </c>
+      <c r="K26" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L26" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M26" s="10">
+        <f t="shared" si="3"/>
+        <v>742.66666666666674</v>
+      </c>
+      <c r="N26" s="10">
+        <f t="shared" si="4"/>
+        <v>1803.6666666666667</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>4</v>
       </c>
-      <c r="B27" s="8">
+      <c r="B27" s="6">
         <v>6</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E27">
+        <v>233</v>
+      </c>
+      <c r="F27">
         <v>149</v>
       </c>
-      <c r="F27">
+      <c r="G27">
         <v>161</v>
       </c>
-      <c r="G27">
+      <c r="H27">
         <v>32.200000000000003</v>
       </c>
-      <c r="H27">
+      <c r="I27">
         <v>4.5999999999999996</v>
       </c>
-      <c r="I27">
-        <v>3059</v>
-      </c>
-      <c r="J27">
-        <v>1363</v>
-      </c>
-      <c r="K27">
-        <v>4422</v>
-      </c>
-      <c r="L27">
-        <v>3059</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J27" s="10">
+        <f t="shared" si="0"/>
+        <v>699</v>
+      </c>
+      <c r="K27" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L27" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M27" s="10">
+        <f t="shared" si="3"/>
+        <v>778.66666666666663</v>
+      </c>
+      <c r="N27" s="10">
+        <f t="shared" si="4"/>
+        <v>1977.6666666666665</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>4</v>
       </c>
-      <c r="B28" s="8">
+      <c r="B28" s="6">
         <v>7</v>
       </c>
       <c r="C28" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D28" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="D28" s="11" t="s">
-        <v>56</v>
-      </c>
       <c r="E28">
+        <v>126</v>
+      </c>
+      <c r="F28">
         <v>93</v>
       </c>
-      <c r="F28">
+      <c r="G28">
         <v>90</v>
       </c>
-      <c r="G28">
+      <c r="H28">
         <v>18</v>
       </c>
-      <c r="H28">
+      <c r="I28">
         <v>5.2</v>
       </c>
-      <c r="I28">
-        <v>1710</v>
-      </c>
-      <c r="J28">
-        <v>875</v>
-      </c>
-      <c r="K28">
-        <v>2585</v>
-      </c>
-      <c r="L28">
-        <v>1710</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J28" s="10">
+        <f t="shared" si="0"/>
+        <v>378</v>
+      </c>
+      <c r="K28" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L28" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M28" s="10">
+        <f t="shared" si="3"/>
+        <v>500</v>
+      </c>
+      <c r="N28" s="10">
+        <f t="shared" si="4"/>
+        <v>1378</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>4</v>
       </c>
-      <c r="B29" s="8">
+      <c r="B29" s="6">
         <v>8</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E29">
-        <v>380</v>
+        <v>507</v>
       </c>
       <c r="F29">
+        <v>470</v>
+      </c>
+      <c r="G29">
         <v>290</v>
       </c>
-      <c r="G29">
+      <c r="H29">
         <v>58</v>
       </c>
-      <c r="H29">
-        <v>6.6</v>
-      </c>
       <c r="I29">
-        <v>5510</v>
-      </c>
-      <c r="J29">
-        <v>3757</v>
-      </c>
-      <c r="K29">
-        <v>9267</v>
-      </c>
-      <c r="L29">
-        <v>5510</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+        <v>8.1</v>
+      </c>
+      <c r="J29" s="10">
+        <f t="shared" si="0"/>
+        <v>1521</v>
+      </c>
+      <c r="K29" s="10">
+        <f t="shared" si="1"/>
+        <v>250</v>
+      </c>
+      <c r="L29" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M29" s="10">
+        <f t="shared" si="3"/>
+        <v>2746.666666666667</v>
+      </c>
+      <c r="N29" s="10">
+        <f t="shared" si="4"/>
+        <v>5017.666666666667</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>4</v>
       </c>
-      <c r="B30" s="8">
+      <c r="B30" s="6">
         <v>9</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E30">
+        <v>99</v>
+      </c>
+      <c r="F30">
         <v>87</v>
       </c>
-      <c r="F30">
+      <c r="G30">
         <v>75</v>
       </c>
-      <c r="G30">
+      <c r="H30">
         <v>15</v>
       </c>
-      <c r="H30">
+      <c r="I30">
         <v>5.8</v>
       </c>
-      <c r="I30">
-        <v>1425</v>
-      </c>
-      <c r="J30">
-        <v>840</v>
-      </c>
-      <c r="K30">
-        <v>2265</v>
-      </c>
-      <c r="L30">
-        <v>1425</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J30" s="10">
+        <f t="shared" si="0"/>
+        <v>297</v>
+      </c>
+      <c r="K30" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L30" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M30" s="10">
+        <f t="shared" si="3"/>
+        <v>480</v>
+      </c>
+      <c r="N30" s="10">
+        <f t="shared" si="4"/>
+        <v>1277</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>4</v>
       </c>
-      <c r="B31" s="8">
+      <c r="B31" s="6">
         <v>10</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E31">
+        <v>387</v>
+      </c>
+      <c r="F31">
         <v>259</v>
       </c>
-      <c r="F31">
+      <c r="G31">
         <v>125</v>
       </c>
-      <c r="G31">
+      <c r="H31">
         <v>25</v>
       </c>
-      <c r="H31">
+      <c r="I31">
         <v>10.4</v>
       </c>
-      <c r="I31">
-        <v>2375</v>
-      </c>
-      <c r="J31">
-        <v>2730</v>
-      </c>
-      <c r="K31">
-        <v>5105</v>
-      </c>
-      <c r="L31">
-        <v>2730</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J31" s="10">
+        <f t="shared" si="0"/>
+        <v>1161</v>
+      </c>
+      <c r="K31" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L31" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M31" s="10">
+        <f t="shared" si="3"/>
+        <v>1560</v>
+      </c>
+      <c r="N31" s="10">
+        <f t="shared" si="4"/>
+        <v>3221</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>5</v>
       </c>
-      <c r="B32" s="8">
+      <c r="B32" s="6">
         <v>6</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E32">
+        <v>164</v>
+      </c>
+      <c r="F32">
         <v>110</v>
       </c>
-      <c r="F32">
+      <c r="G32">
         <v>70</v>
       </c>
-      <c r="G32">
+      <c r="H32">
         <v>14</v>
       </c>
-      <c r="H32">
+      <c r="I32">
         <v>7.9</v>
       </c>
-      <c r="I32">
-        <v>1330</v>
-      </c>
-      <c r="J32">
-        <v>1120</v>
-      </c>
-      <c r="K32">
-        <v>2450</v>
-      </c>
-      <c r="L32">
-        <v>1330</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A33" s="10">
+      <c r="J32" s="10">
+        <f t="shared" si="0"/>
+        <v>492</v>
+      </c>
+      <c r="K32" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L32" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M32" s="10">
+        <f t="shared" si="3"/>
+        <v>640</v>
+      </c>
+      <c r="N32" s="10">
+        <f t="shared" si="4"/>
+        <v>1632</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A33" s="8">
         <v>5</v>
       </c>
-      <c r="B33" s="8">
+      <c r="B33" s="6">
         <v>7</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D33" s="11" t="s">
-        <v>56</v>
+        <v>51</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>53</v>
       </c>
       <c r="E33">
+        <v>254</v>
+      </c>
+      <c r="F33">
         <v>168</v>
       </c>
-      <c r="F33">
+      <c r="G33">
         <v>173</v>
       </c>
-      <c r="G33">
+      <c r="H33">
         <v>34.6</v>
       </c>
-      <c r="H33">
+      <c r="I33">
         <v>4.9000000000000004</v>
       </c>
-      <c r="I33">
-        <v>3287</v>
-      </c>
-      <c r="J33">
-        <v>1556</v>
-      </c>
-      <c r="K33">
-        <v>4843</v>
-      </c>
-      <c r="L33">
-        <v>3287</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J33" s="10">
+        <f t="shared" si="0"/>
+        <v>762</v>
+      </c>
+      <c r="K33" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L33" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M33" s="10">
+        <f t="shared" si="3"/>
+        <v>889.33333333333337</v>
+      </c>
+      <c r="N33" s="10">
+        <f t="shared" si="4"/>
+        <v>2151.3333333333335</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>5</v>
       </c>
-      <c r="B34" s="8">
+      <c r="B34" s="6">
         <v>8</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E34">
-        <v>279</v>
+        <v>337</v>
       </c>
       <c r="F34">
+        <v>369</v>
+      </c>
+      <c r="G34">
         <v>281</v>
       </c>
-      <c r="G34">
+      <c r="H34">
         <v>56.2</v>
       </c>
-      <c r="H34">
-        <v>5</v>
-      </c>
       <c r="I34">
-        <v>5339</v>
-      </c>
-      <c r="J34">
-        <v>2599</v>
-      </c>
-      <c r="K34">
-        <v>7938</v>
-      </c>
-      <c r="L34">
-        <v>5339</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+        <v>6.6</v>
+      </c>
+      <c r="J34" s="10">
+        <f t="shared" si="0"/>
+        <v>1011</v>
+      </c>
+      <c r="K34" s="10">
+        <f t="shared" si="1"/>
+        <v>250</v>
+      </c>
+      <c r="L34" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M34" s="10">
+        <f t="shared" si="3"/>
+        <v>2085.3333333333335</v>
+      </c>
+      <c r="N34" s="10">
+        <f t="shared" si="4"/>
+        <v>3846.3333333333335</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>5</v>
       </c>
-      <c r="B35" s="8">
+      <c r="B35" s="6">
         <v>9</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E35">
+        <v>165</v>
+      </c>
+      <c r="F35">
         <v>136</v>
       </c>
-      <c r="F35">
+      <c r="G35">
         <v>118</v>
       </c>
-      <c r="G35">
+      <c r="H35">
         <v>23.6</v>
       </c>
-      <c r="H35">
+      <c r="I35">
         <v>5.8</v>
       </c>
-      <c r="I35">
-        <v>2242</v>
-      </c>
-      <c r="J35">
-        <v>1311</v>
-      </c>
-      <c r="K35">
-        <v>3553</v>
-      </c>
-      <c r="L35">
-        <v>2242</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J35" s="10">
+        <f t="shared" si="0"/>
+        <v>495</v>
+      </c>
+      <c r="K35" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L35" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M35" s="10">
+        <f t="shared" si="3"/>
+        <v>749.33333333333337</v>
+      </c>
+      <c r="N35" s="10">
+        <f t="shared" si="4"/>
+        <v>1744.3333333333335</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>5</v>
       </c>
-      <c r="B36" s="8">
+      <c r="B36" s="6">
         <v>10</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E36">
+        <v>216</v>
+      </c>
+      <c r="F36">
         <v>158</v>
       </c>
-      <c r="F36">
+      <c r="G36">
         <v>155</v>
       </c>
-      <c r="G36">
+      <c r="H36">
         <v>31</v>
       </c>
-      <c r="H36">
+      <c r="I36">
         <v>5.0999999999999996</v>
       </c>
-      <c r="I36">
-        <v>2945</v>
-      </c>
-      <c r="J36">
-        <v>1482</v>
-      </c>
-      <c r="K36">
-        <v>4427</v>
-      </c>
-      <c r="L36">
-        <v>2945</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J36" s="10">
+        <f t="shared" si="0"/>
+        <v>648</v>
+      </c>
+      <c r="K36" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L36" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M36" s="10">
+        <f t="shared" si="3"/>
+        <v>846.66666666666674</v>
+      </c>
+      <c r="N36" s="10">
+        <f t="shared" si="4"/>
+        <v>1994.6666666666667</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>6</v>
       </c>
-      <c r="B37" s="8">
+      <c r="B37" s="6">
         <v>7</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="D37" s="11" t="s">
-        <v>56</v>
+        <v>52</v>
+      </c>
+      <c r="D37" s="9" t="s">
+        <v>53</v>
       </c>
       <c r="E37">
+        <v>299</v>
+      </c>
+      <c r="F37">
         <v>185</v>
       </c>
-      <c r="F37">
+      <c r="G37">
         <v>232</v>
       </c>
-      <c r="G37">
+      <c r="H37">
         <v>46.4</v>
       </c>
-      <c r="H37">
+      <c r="I37">
         <v>4</v>
       </c>
-      <c r="I37">
-        <v>4408</v>
-      </c>
-      <c r="J37">
-        <v>1617</v>
-      </c>
-      <c r="K37">
-        <v>6025</v>
-      </c>
-      <c r="L37">
-        <v>4408</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J37" s="10">
+        <f t="shared" si="0"/>
+        <v>897</v>
+      </c>
+      <c r="K37" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L37" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M37" s="10">
+        <f t="shared" si="3"/>
+        <v>924</v>
+      </c>
+      <c r="N37" s="10">
+        <f t="shared" si="4"/>
+        <v>2321</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>6</v>
       </c>
-      <c r="B38" s="8">
+      <c r="B38" s="6">
         <v>8</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E38">
-        <v>358</v>
+        <v>484</v>
       </c>
       <c r="F38">
+        <v>448</v>
+      </c>
+      <c r="G38">
         <v>315</v>
       </c>
-      <c r="G38">
+      <c r="H38">
         <v>63</v>
       </c>
-      <c r="H38">
-        <v>5.7</v>
-      </c>
       <c r="I38">
-        <v>5985</v>
-      </c>
-      <c r="J38">
-        <v>3442</v>
-      </c>
-      <c r="K38">
-        <v>9427</v>
-      </c>
-      <c r="L38">
-        <v>5985</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+        <v>7.1</v>
+      </c>
+      <c r="J38" s="10">
+        <f t="shared" si="0"/>
+        <v>1452</v>
+      </c>
+      <c r="K38" s="10">
+        <f t="shared" si="1"/>
+        <v>250</v>
+      </c>
+      <c r="L38" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M38" s="10">
+        <f t="shared" si="3"/>
+        <v>2566.666666666667</v>
+      </c>
+      <c r="N38" s="10">
+        <f t="shared" si="4"/>
+        <v>4768.666666666667</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>6</v>
       </c>
-      <c r="B39" s="8">
+      <c r="B39" s="6">
         <v>9</v>
       </c>
       <c r="C39" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D39" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D39" s="1" t="s">
-        <v>58</v>
-      </c>
       <c r="E39">
+        <v>210</v>
+      </c>
+      <c r="F39">
         <v>153</v>
       </c>
-      <c r="F39">
+      <c r="G39">
         <v>166</v>
       </c>
-      <c r="G39">
+      <c r="H39">
         <v>33.200000000000003</v>
       </c>
-      <c r="H39">
+      <c r="I39">
         <v>4.5999999999999996</v>
       </c>
-      <c r="I39">
-        <v>3154</v>
-      </c>
-      <c r="J39">
-        <v>1398</v>
-      </c>
-      <c r="K39">
-        <v>4552</v>
-      </c>
-      <c r="L39">
-        <v>3154</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J39" s="10">
+        <f t="shared" si="0"/>
+        <v>630</v>
+      </c>
+      <c r="K39" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L39" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M39" s="10">
+        <f t="shared" si="3"/>
+        <v>798.66666666666663</v>
+      </c>
+      <c r="N39" s="10">
+        <f t="shared" si="4"/>
+        <v>1928.6666666666665</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>6</v>
       </c>
-      <c r="B40" s="8">
+      <c r="B40" s="6">
         <v>10</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E40">
+        <v>363</v>
+      </c>
+      <c r="F40">
         <v>237</v>
       </c>
-      <c r="F40">
+      <c r="G40">
         <v>216</v>
       </c>
-      <c r="G40">
+      <c r="H40">
         <v>43.2</v>
       </c>
-      <c r="H40">
+      <c r="I40">
         <v>5.5</v>
       </c>
-      <c r="I40">
-        <v>4104</v>
-      </c>
-      <c r="J40">
-        <v>2261</v>
-      </c>
-      <c r="K40">
-        <v>6365</v>
-      </c>
-      <c r="L40">
-        <v>4104</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J40" s="10">
+        <f t="shared" si="0"/>
+        <v>1089</v>
+      </c>
+      <c r="K40" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L40" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M40" s="10">
+        <f t="shared" si="3"/>
+        <v>1292.0000000000002</v>
+      </c>
+      <c r="N40" s="10">
+        <f t="shared" si="4"/>
+        <v>2881</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>7</v>
       </c>
-      <c r="B41" s="8">
+      <c r="B41" s="6">
         <v>8</v>
       </c>
       <c r="C41" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D41" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="D41" s="1" t="s">
-        <v>59</v>
-      </c>
       <c r="E41">
-        <v>414</v>
+        <v>575</v>
       </c>
       <c r="F41">
+        <v>504</v>
+      </c>
+      <c r="G41">
         <v>365</v>
       </c>
-      <c r="G41">
+      <c r="H41">
         <v>73</v>
       </c>
-      <c r="H41">
-        <v>5.7</v>
-      </c>
       <c r="I41">
-        <v>6935</v>
-      </c>
-      <c r="J41">
-        <v>3978</v>
-      </c>
-      <c r="K41">
-        <v>10913</v>
-      </c>
-      <c r="L41">
-        <v>6935</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+        <v>6.9</v>
+      </c>
+      <c r="J41" s="10">
+        <f t="shared" si="0"/>
+        <v>1725</v>
+      </c>
+      <c r="K41" s="10">
+        <f t="shared" si="1"/>
+        <v>250</v>
+      </c>
+      <c r="L41" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M41" s="10">
+        <f t="shared" si="3"/>
+        <v>2873.3333333333335</v>
+      </c>
+      <c r="N41" s="10">
+        <f>SUM(J41:M41)</f>
+        <v>5348.3333333333339</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>7</v>
       </c>
-      <c r="B42" s="8">
+      <c r="B42" s="6">
         <v>9</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E42">
+        <v>84</v>
+      </c>
+      <c r="F42">
         <v>70</v>
       </c>
-      <c r="F42">
+      <c r="G42">
         <v>75</v>
       </c>
-      <c r="G42">
+      <c r="H42">
         <v>15</v>
       </c>
-      <c r="H42">
+      <c r="I42">
         <v>4.7</v>
       </c>
-      <c r="I42">
-        <v>1425</v>
-      </c>
-      <c r="J42">
-        <v>642</v>
-      </c>
-      <c r="K42">
-        <v>2067</v>
-      </c>
-      <c r="L42">
-        <v>1425</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J42" s="10">
+        <f t="shared" si="0"/>
+        <v>252</v>
+      </c>
+      <c r="K42" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L42" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M42" s="10">
+        <f t="shared" si="3"/>
+        <v>366.66666666666669</v>
+      </c>
+      <c r="N42" s="10">
+        <f t="shared" si="4"/>
+        <v>1118.6666666666667</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>7</v>
       </c>
-      <c r="B43" s="8">
+      <c r="B43" s="6">
         <v>10</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E43">
+        <v>454</v>
+      </c>
+      <c r="F43">
         <v>293</v>
       </c>
-      <c r="F43">
+      <c r="G43">
         <v>194</v>
       </c>
-      <c r="G43">
+      <c r="H43">
         <v>38.799999999999997</v>
       </c>
-      <c r="H43">
+      <c r="I43">
         <v>7.6</v>
       </c>
-      <c r="I43">
-        <v>3686</v>
-      </c>
-      <c r="J43">
-        <v>2966</v>
-      </c>
-      <c r="K43">
-        <v>6652</v>
-      </c>
-      <c r="L43">
-        <v>3686</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J43" s="10">
+        <f t="shared" si="0"/>
+        <v>1362</v>
+      </c>
+      <c r="K43" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L43" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M43" s="10">
+        <f t="shared" si="3"/>
+        <v>1694.6666666666667</v>
+      </c>
+      <c r="N43" s="10">
+        <f t="shared" si="4"/>
+        <v>3556.666666666667</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>8</v>
       </c>
-      <c r="B44" s="8">
+      <c r="B44" s="6">
         <v>9</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E44">
-        <v>384</v>
+        <v>486</v>
       </c>
       <c r="F44">
+        <v>474</v>
+      </c>
+      <c r="G44">
         <v>363</v>
       </c>
-      <c r="G44">
+      <c r="H44">
         <v>72.599999999999994</v>
       </c>
-      <c r="H44">
-        <v>5.3</v>
-      </c>
       <c r="I44">
-        <v>6897</v>
-      </c>
-      <c r="J44">
-        <v>3633</v>
-      </c>
-      <c r="K44">
-        <v>10530</v>
-      </c>
-      <c r="L44">
-        <v>6897</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+        <v>6.5</v>
+      </c>
+      <c r="J44" s="10">
+        <f t="shared" si="0"/>
+        <v>1458</v>
+      </c>
+      <c r="K44" s="10">
+        <f t="shared" si="1"/>
+        <v>250</v>
+      </c>
+      <c r="L44" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M44" s="10">
+        <f t="shared" si="3"/>
+        <v>2676</v>
+      </c>
+      <c r="N44" s="10">
+        <f t="shared" si="4"/>
+        <v>4884</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>8</v>
       </c>
-      <c r="B45" s="8">
+      <c r="B45" s="6">
         <v>10</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E45">
-        <v>209</v>
+        <v>230</v>
       </c>
       <c r="F45">
+        <v>299</v>
+      </c>
+      <c r="G45">
         <v>172</v>
       </c>
-      <c r="G45">
+      <c r="H45">
         <v>34.4</v>
       </c>
-      <c r="H45">
-        <v>6.1</v>
-      </c>
       <c r="I45">
-        <v>3268</v>
-      </c>
-      <c r="J45">
-        <v>2037</v>
-      </c>
-      <c r="K45">
-        <v>5305</v>
-      </c>
-      <c r="L45">
-        <v>3268</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="J45" s="10">
+        <f t="shared" si="0"/>
+        <v>690</v>
+      </c>
+      <c r="K45" s="10">
+        <f t="shared" si="1"/>
+        <v>250</v>
+      </c>
+      <c r="L45" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M45" s="10">
+        <f t="shared" si="3"/>
+        <v>1764.0000000000002</v>
+      </c>
+      <c r="N45" s="10">
+        <f t="shared" si="4"/>
+        <v>3204</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>9</v>
       </c>
-      <c r="B46" s="8">
+      <c r="B46" s="6">
         <v>10</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E46">
+        <v>366</v>
+      </c>
+      <c r="F46">
         <v>264</v>
       </c>
-      <c r="F46">
+      <c r="G46">
         <v>200</v>
       </c>
-      <c r="G46">
+      <c r="H46">
         <v>40</v>
       </c>
-      <c r="H46">
+      <c r="I46">
         <v>6.6</v>
       </c>
-      <c r="I46">
-        <v>3800</v>
-      </c>
-      <c r="J46">
-        <v>2613</v>
-      </c>
-      <c r="K46">
-        <v>6413</v>
-      </c>
-      <c r="L46">
-        <v>3800</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J46" s="10">
+        <f t="shared" si="0"/>
+        <v>1098</v>
+      </c>
+      <c r="K46" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L46" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M46" s="10">
+        <f t="shared" si="3"/>
+        <v>1493.3333333333335</v>
+      </c>
+      <c r="N46" s="10">
+        <f t="shared" si="4"/>
+        <v>3091.3333333333335</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>1</v>
       </c>
-      <c r="B47" s="8">
+      <c r="B47" s="6">
         <v>1</v>
       </c>
-      <c r="C47" s="8"/>
-      <c r="D47" s="8"/>
+      <c r="C47" s="6"/>
+      <c r="D47" s="6"/>
       <c r="E47">
         <v>0</v>
       </c>
@@ -2686,25 +3404,16 @@
       <c r="I47">
         <v>0</v>
       </c>
-      <c r="J47">
-        <v>0</v>
-      </c>
-      <c r="K47">
-        <v>0</v>
-      </c>
-      <c r="L47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>2</v>
       </c>
-      <c r="B48" s="8">
+      <c r="B48" s="6">
         <v>2</v>
       </c>
-      <c r="C48" s="8"/>
-      <c r="D48" s="8"/>
+      <c r="C48" s="6"/>
+      <c r="D48" s="6"/>
       <c r="E48">
         <v>0</v>
       </c>
@@ -2720,25 +3429,16 @@
       <c r="I48">
         <v>0</v>
       </c>
-      <c r="J48">
-        <v>0</v>
-      </c>
-      <c r="K48">
-        <v>0</v>
-      </c>
-      <c r="L48">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>3</v>
       </c>
-      <c r="B49" s="8">
+      <c r="B49" s="6">
         <v>3</v>
       </c>
-      <c r="C49" s="8"/>
-      <c r="D49" s="8"/>
+      <c r="C49" s="6"/>
+      <c r="D49" s="6"/>
       <c r="E49">
         <v>0</v>
       </c>
@@ -2754,25 +3454,16 @@
       <c r="I49">
         <v>0</v>
       </c>
-      <c r="J49">
-        <v>0</v>
-      </c>
-      <c r="K49">
-        <v>0</v>
-      </c>
-      <c r="L49">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>4</v>
       </c>
-      <c r="B50" s="8">
+      <c r="B50" s="6">
         <v>4</v>
       </c>
-      <c r="C50" s="8"/>
-      <c r="D50" s="8"/>
+      <c r="C50" s="6"/>
+      <c r="D50" s="6"/>
       <c r="E50">
         <v>0</v>
       </c>
@@ -2788,25 +3479,16 @@
       <c r="I50">
         <v>0</v>
       </c>
-      <c r="J50">
-        <v>0</v>
-      </c>
-      <c r="K50">
-        <v>0</v>
-      </c>
-      <c r="L50">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>5</v>
       </c>
-      <c r="B51" s="8">
+      <c r="B51" s="6">
         <v>5</v>
       </c>
-      <c r="C51" s="8"/>
-      <c r="D51" s="8"/>
+      <c r="C51" s="6"/>
+      <c r="D51" s="6"/>
       <c r="E51">
         <v>0</v>
       </c>
@@ -2822,21 +3504,12 @@
       <c r="I51">
         <v>0</v>
       </c>
-      <c r="J51">
-        <v>0</v>
-      </c>
-      <c r="K51">
-        <v>0</v>
-      </c>
-      <c r="L51">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>6</v>
       </c>
-      <c r="B52" s="8">
+      <c r="B52" s="6">
         <v>6</v>
       </c>
       <c r="E52">
@@ -2854,21 +3527,12 @@
       <c r="I52">
         <v>0</v>
       </c>
-      <c r="J52">
-        <v>0</v>
-      </c>
-      <c r="K52">
-        <v>0</v>
-      </c>
-      <c r="L52">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>7</v>
       </c>
-      <c r="B53" s="8">
+      <c r="B53" s="6">
         <v>7</v>
       </c>
       <c r="E53">
@@ -2886,21 +3550,12 @@
       <c r="I53">
         <v>0</v>
       </c>
-      <c r="J53">
-        <v>0</v>
-      </c>
-      <c r="K53">
-        <v>0</v>
-      </c>
-      <c r="L53">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>8</v>
       </c>
-      <c r="B54" s="8">
+      <c r="B54" s="6">
         <v>8</v>
       </c>
       <c r="E54">
@@ -2918,21 +3573,12 @@
       <c r="I54">
         <v>0</v>
       </c>
-      <c r="J54">
-        <v>0</v>
-      </c>
-      <c r="K54">
-        <v>0</v>
-      </c>
-      <c r="L54">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>9</v>
       </c>
-      <c r="B55" s="8">
+      <c r="B55" s="6">
         <v>9</v>
       </c>
       <c r="E55">
@@ -2950,21 +3596,12 @@
       <c r="I55">
         <v>0</v>
       </c>
-      <c r="J55">
-        <v>0</v>
-      </c>
-      <c r="K55">
-        <v>0</v>
-      </c>
-      <c r="L55">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>10</v>
       </c>
-      <c r="B56" s="8">
+      <c r="B56" s="6">
         <v>10</v>
       </c>
       <c r="E56">
@@ -2982,39 +3619,9 @@
       <c r="I56">
         <v>0</v>
       </c>
-      <c r="J56">
-        <v>0</v>
-      </c>
-      <c r="K56">
-        <v>0</v>
-      </c>
-      <c r="L56">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="G57" s="2"/>
-    </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="G58" s="1"/>
-    </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="G59" s="1"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="I2:I46">
-    <cfRule type="colorScale" priority="4">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J46">
+  <conditionalFormatting sqref="J2:J56">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -3026,7 +3633,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K46">
+  <conditionalFormatting sqref="M2:M56">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -3038,7 +3645,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L46">
+  <conditionalFormatting sqref="N2:N56">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -3051,5 +3658,8 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/inputData/Parameters.xlsx
+++ b/inputData/Parameters.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kapta\Documents\DTU\Speciale\GitHubFiles\inputData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sillewiberg/Desktop/Skole/Speciale/Master-Thesis-eVTOL-1/inputData/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92956B8D-EC89-438B-959C-6073760B8565}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0218802E-FB40-954D-9A70-48D7F6E8A911}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="28800" windowHeight="15285" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
+    <workbookView xWindow="0" yWindow="1180" windowWidth="28800" windowHeight="15280" activeTab="1" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
   </bookViews>
   <sheets>
     <sheet name="Parameters" sheetId="9" r:id="rId1"/>
-    <sheet name="Prices" sheetId="12" r:id="rId2"/>
+    <sheet name="Prices" sheetId="13" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="64">
   <si>
     <t>cap_u</t>
   </si>
@@ -117,15 +117,6 @@
     <t>Hvor meget hurtigere</t>
   </si>
   <si>
-    <t>Fd km</t>
-  </si>
-  <si>
-    <t>Fd tid</t>
-  </si>
-  <si>
-    <t>fd max</t>
-  </si>
-  <si>
     <t>Passager km pris</t>
   </si>
   <si>
@@ -220,13 +211,35 @@
   </si>
   <si>
     <t>(56.049305, 12.584406)</t>
+  </si>
+  <si>
+    <t>Bil km</t>
+  </si>
+  <si>
+    <t>Pris (Bil udgift)</t>
+  </si>
+  <si>
+    <t>Færge (gns. Gælder kun Bornholm)</t>
+  </si>
+  <si>
+    <t>Base</t>
+  </si>
+  <si>
+    <t>Pris (udfra tidsbesparelse)</t>
+  </si>
+  <si>
+    <t>Km bil pris</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+  </numFmts>
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -254,13 +267,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <strike/>
       <sz val="12"/>
       <color theme="1"/>
@@ -274,16 +280,37 @@
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor theme="1"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -291,11 +318,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -304,19 +341,161 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Comma 2" xfId="1" xr:uid="{B5076C6D-4567-C74F-A5A8-80AE462FFA5E}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="8">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -327,6 +506,35 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3CFD079E-5109-8F49-8A19-E09E2BEBBC8C}" name="Table13" displayName="Table13" ref="A1:N56" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6" headerRowCellStyle="Comma" dataCellStyle="Comma">
+  <autoFilter ref="A1:N56" xr:uid="{CEDCB4F7-0752-8449-BE87-89650C1E9E7C}"/>
+  <tableColumns count="14">
+    <tableColumn id="1" xr3:uid="{0330B38A-598B-B64A-86F4-FA8E25EAC437}" name="From"/>
+    <tableColumn id="2" xr3:uid="{DA4E4644-7B10-0541-B73A-349A5A6836E2}" name="To" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{354A3716-07E2-0F49-9392-E1F6D4672CCE}" name="cord_from"/>
+    <tableColumn id="4" xr3:uid="{CA960CCE-0555-F44E-9C8F-AE9C1925F667}" name="cord_to"/>
+    <tableColumn id="5" xr3:uid="{D42F7B17-60EA-DB4D-8238-39B387D0ABC3}" name="Bil km"/>
+    <tableColumn id="6" xr3:uid="{4D9FAB2B-036C-054C-AB09-29F5B4ADED42}" name="Bil tid (min)"/>
+    <tableColumn id="7" xr3:uid="{59F6BECD-EB60-114E-826A-884ADDC4EE72}" name="Km fugleflugt"/>
+    <tableColumn id="8" xr3:uid="{605D45AE-CBF2-E342-BA16-1B205DDE6C4E}" name="eVTOL flyvetid (min)"/>
+    <tableColumn id="9" xr3:uid="{FCFA00C8-AEDC-F54B-AE4D-2360ACC6025E}" name="Hvor meget hurtigere"/>
+    <tableColumn id="10" xr3:uid="{DBB7D64B-F97D-5C46-B464-1DA11C10DF3A}" name="Pris (Bil udgift)" dataDxfId="4" dataCellStyle="Comma"/>
+    <tableColumn id="11" xr3:uid="{CC283087-BB53-D146-A233-2D178D7E3562}" name="Færge (gns. Gælder kun Bornholm)" dataDxfId="3" dataCellStyle="Comma"/>
+    <tableColumn id="12" xr3:uid="{B4DC4D17-2AE3-D34D-926C-7506AC52E6B8}" name="Base" dataDxfId="2" dataCellStyle="Comma">
+      <calculatedColumnFormula>$Q$5</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="13" xr3:uid="{E70B016F-0534-2048-951F-6FD04DC33B7C}" name="Pris (udfra tidsbesparelse)" dataDxfId="1" dataCellStyle="Comma">
+      <calculatedColumnFormula>$Q$4*MAX(F2-G2*$Q$1)*$Q$3</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="14" xr3:uid="{67EF8C2F-B7CB-8D4A-8447-692E942D0514}" name="fd_sum" dataDxfId="0" dataCellStyle="Comma">
+      <calculatedColumnFormula>SUM(J2:M2)</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -647,18 +855,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B15C49E0-A7B4-734A-8962-DC2A879F4079}">
   <dimension ref="A1:D20"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="22.625" customWidth="1"/>
-    <col min="2" max="2" width="10.875" style="4"/>
+    <col min="1" max="1" width="22.6640625" customWidth="1"/>
+    <col min="2" max="2" width="10.83203125" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>20</v>
       </c>
@@ -669,7 +877,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -680,18 +888,18 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B4" s="4">
         <v>400</v>
       </c>
       <c r="D4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -699,10 +907,10 @@
         <v>300</v>
       </c>
       <c r="D5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -713,7 +921,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -724,7 +932,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -733,10 +941,10 @@
         <v>0.2</v>
       </c>
       <c r="D8" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>0</v>
       </c>
@@ -747,7 +955,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>1</v>
       </c>
@@ -758,9 +966,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B11" s="4">
         <v>80</v>
@@ -769,7 +977,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>2</v>
       </c>
@@ -780,18 +988,18 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B13" s="4">
         <v>20</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -800,10 +1008,10 @@
         <v>2.11</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>4</v>
       </c>
@@ -815,7 +1023,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>5</v>
       </c>
@@ -827,7 +1035,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>6</v>
       </c>
@@ -838,15 +1046,15 @@
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B20" s="4">
         <v>1</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -856,1821 +1064,2331 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAF0D5EA-53B5-1240-9D84-6FE223856A18}">
-  <dimension ref="A1:P59"/>
-  <sheetFormatPr defaultColWidth="10.625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36FC1A80-FC3B-6349-8B7A-4A1A2A7C8FC7}">
+  <dimension ref="A1:R56"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="17.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="17.125" customWidth="1"/>
-    <col min="5" max="5" width="12.125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="17.1640625" customWidth="1"/>
+    <col min="5" max="5" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5" customWidth="1"/>
+    <col min="7" max="7" width="17.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.33203125" customWidth="1"/>
+    <col min="9" max="9" width="21" style="10" customWidth="1"/>
+    <col min="10" max="10" width="13.6640625" style="10" customWidth="1"/>
+    <col min="11" max="11" width="32.1640625" style="10" customWidth="1"/>
+    <col min="12" max="12" width="10.6640625" style="10"/>
+    <col min="13" max="13" width="27" style="10" customWidth="1"/>
+    <col min="14" max="14" width="10.83203125" style="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
-        <v>36</v>
+    <row r="1" spans="1:18" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1" s="7" t="s">
+        <v>33</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="E1" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="E1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F1" t="s">
         <v>22</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="G1" t="s">
         <v>23</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="H1" t="s">
         <v>24</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="I1" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="I1" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="L1" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="N1" s="6" t="s">
+      <c r="J1" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="K1" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="L1" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="M1" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="N1" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="P1" t="s">
         <v>19</v>
       </c>
-      <c r="O1" s="7">
+      <c r="Q1">
         <v>0.2</v>
       </c>
-      <c r="P1" s="6"/>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="8">
+      <c r="B2" s="6">
         <v>2</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E2">
+        <v>267</v>
+      </c>
+      <c r="F2">
         <v>185</v>
       </c>
-      <c r="F2">
+      <c r="G2">
         <v>219</v>
       </c>
-      <c r="G2">
+      <c r="H2">
         <v>43.8</v>
       </c>
-      <c r="H2">
+      <c r="I2">
         <v>4.2</v>
       </c>
-      <c r="I2">
-        <v>4161</v>
-      </c>
-      <c r="J2">
-        <v>1647</v>
-      </c>
-      <c r="K2">
-        <v>5808</v>
-      </c>
-      <c r="L2">
-        <v>4161</v>
-      </c>
-      <c r="N2" t="s">
-        <v>29</v>
-      </c>
-      <c r="O2" s="4">
-        <v>19</v>
+      <c r="J2" s="10">
+        <f>$Q$6*E2</f>
+        <v>801</v>
+      </c>
+      <c r="K2" s="10">
+        <f>IF(A2=8,250,0)+IF(B2=8,250,0)</f>
+        <v>0</v>
+      </c>
+      <c r="L2" s="10">
+        <f>$Q$5</f>
+        <v>500</v>
+      </c>
+      <c r="M2" s="10">
+        <f>$Q$4*MAX(F2-G2*$Q$1)*$Q$3</f>
+        <v>941.33333333333326</v>
+      </c>
+      <c r="N2" s="10">
+        <f>SUM(J2:M2)</f>
+        <v>2242.333333333333</v>
       </c>
       <c r="P2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="Q2">
+        <v>16</v>
+      </c>
+      <c r="R2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>1</v>
       </c>
-      <c r="B3" s="8">
+      <c r="B3" s="6">
         <v>3</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E3">
+        <v>100</v>
+      </c>
+      <c r="F3">
         <v>82</v>
       </c>
-      <c r="F3">
+      <c r="G3">
         <v>88</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>17.600000000000001</v>
       </c>
-      <c r="H3">
+      <c r="I3">
         <v>4.7</v>
       </c>
-      <c r="I3">
-        <v>1672</v>
-      </c>
-      <c r="J3">
-        <v>751</v>
-      </c>
-      <c r="K3">
-        <v>2423</v>
-      </c>
-      <c r="L3">
-        <v>1672</v>
-      </c>
-      <c r="N3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O3" s="4">
-        <f>1000/60</f>
-        <v>16.666666666666668</v>
+      <c r="J3" s="10">
+        <f t="shared" ref="J3:J46" si="0">$Q$6*E3</f>
+        <v>300</v>
+      </c>
+      <c r="K3" s="10">
+        <f t="shared" ref="K3:K46" si="1">IF(A3=8,250,0)+IF(B3=8,250,0)</f>
+        <v>0</v>
+      </c>
+      <c r="L3" s="10">
+        <f t="shared" ref="L3:L46" si="2">$Q$5</f>
+        <v>500</v>
+      </c>
+      <c r="M3" s="10">
+        <f t="shared" ref="M3:M46" si="3">$Q$4*MAX(F3-G3*$Q$1)*$Q$3</f>
+        <v>429.33333333333337</v>
+      </c>
+      <c r="N3" s="10">
+        <f t="shared" ref="N3:N46" si="4">SUM(J3:M3)</f>
+        <v>1229.3333333333335</v>
       </c>
       <c r="P3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+      <c r="Q3">
+        <f>800/60</f>
+        <v>13.333333333333334</v>
+      </c>
+      <c r="R3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>1</v>
       </c>
-      <c r="B4" s="8">
+      <c r="B4" s="6">
         <v>4</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>53</v>
-      </c>
       <c r="E4">
+        <v>347</v>
+      </c>
+      <c r="F4">
         <v>228</v>
       </c>
-      <c r="F4">
+      <c r="G4">
         <v>147</v>
       </c>
-      <c r="G4">
+      <c r="H4">
         <v>29.4</v>
       </c>
-      <c r="H4">
+      <c r="I4">
         <v>7.8</v>
       </c>
-      <c r="I4">
-        <v>2793</v>
-      </c>
-      <c r="J4">
-        <v>2317</v>
-      </c>
-      <c r="K4">
-        <v>5110</v>
-      </c>
-      <c r="L4">
-        <v>2793</v>
-      </c>
-      <c r="N4" t="s">
-        <v>33</v>
-      </c>
-      <c r="O4" s="4">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="J4" s="10">
+        <f t="shared" si="0"/>
+        <v>1041</v>
+      </c>
+      <c r="K4" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L4" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M4" s="10">
+        <f>$Q$4*MAX(F4-G4*$Q$1)*$Q$3</f>
+        <v>1324</v>
+      </c>
+      <c r="N4" s="10">
+        <f>SUM(J4:M4)</f>
+        <v>2865</v>
+      </c>
+      <c r="P4" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q4">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>1</v>
       </c>
-      <c r="B5" s="8">
+      <c r="B5" s="6">
         <v>5</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E5">
+        <v>177</v>
+      </c>
+      <c r="F5">
         <v>126</v>
       </c>
-      <c r="F5">
+      <c r="G5">
         <v>147</v>
       </c>
-      <c r="G5">
+      <c r="H5">
         <v>29.4</v>
       </c>
-      <c r="H5">
+      <c r="I5">
         <v>4.3</v>
       </c>
-      <c r="I5">
-        <v>2793</v>
-      </c>
-      <c r="J5">
-        <v>1127</v>
-      </c>
-      <c r="K5">
-        <v>3920</v>
-      </c>
-      <c r="L5">
-        <v>2793</v>
-      </c>
-      <c r="N5" t="s">
-        <v>34</v>
-      </c>
-      <c r="O5" s="4">
-        <v>0</v>
+      <c r="J5" s="10">
+        <f>$Q$6*E5</f>
+        <v>531</v>
+      </c>
+      <c r="K5" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L5" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M5" s="10">
+        <f>$Q$4*MAX(F5-G5*$Q$1)*$Q$3</f>
+        <v>644</v>
+      </c>
+      <c r="N5" s="10">
+        <f t="shared" si="4"/>
+        <v>1675</v>
       </c>
       <c r="P5" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+      <c r="Q5">
+        <v>500</v>
+      </c>
+      <c r="R5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>1</v>
       </c>
-      <c r="B6" s="8">
+      <c r="B6" s="6">
         <v>6</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E6">
+        <v>325</v>
+      </c>
+      <c r="F6">
         <v>205</v>
       </c>
-      <c r="F6">
+      <c r="G6">
         <v>197</v>
       </c>
-      <c r="G6">
+      <c r="H6">
         <v>39.4</v>
       </c>
-      <c r="H6">
+      <c r="I6">
         <v>5.2</v>
       </c>
-      <c r="I6">
-        <v>3743</v>
-      </c>
-      <c r="J6">
-        <v>1932</v>
-      </c>
-      <c r="K6">
-        <v>5675</v>
-      </c>
-      <c r="L6">
-        <v>3743</v>
-      </c>
-      <c r="O6" s="4"/>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="J6" s="10">
+        <f t="shared" si="0"/>
+        <v>975</v>
+      </c>
+      <c r="K6" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L6" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M6" s="10">
+        <f t="shared" si="3"/>
+        <v>1104</v>
+      </c>
+      <c r="N6" s="10">
+        <f t="shared" si="4"/>
+        <v>2579</v>
+      </c>
+      <c r="P6" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q6">
+        <v>3</v>
+      </c>
+      <c r="R6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>1</v>
       </c>
-      <c r="B7" s="8">
+      <c r="B7" s="6">
         <v>7</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E7">
+        <v>415</v>
+      </c>
+      <c r="F7">
         <v>263</v>
       </c>
-      <c r="F7">
+      <c r="G7">
         <v>227</v>
       </c>
-      <c r="G7">
+      <c r="H7">
         <v>45.4</v>
       </c>
-      <c r="H7">
+      <c r="I7">
         <v>5.8</v>
       </c>
-      <c r="I7">
-        <v>4313</v>
-      </c>
-      <c r="J7">
-        <v>2539</v>
-      </c>
-      <c r="K7">
-        <v>6852</v>
-      </c>
-      <c r="L7">
-        <v>4313</v>
-      </c>
-      <c r="O7" s="4"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="J7" s="10">
+        <f t="shared" si="0"/>
+        <v>1245</v>
+      </c>
+      <c r="K7" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L7" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M7" s="10">
+        <f t="shared" si="3"/>
+        <v>1450.6666666666667</v>
+      </c>
+      <c r="N7" s="10">
+        <f t="shared" si="4"/>
+        <v>3195.666666666667</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>1</v>
       </c>
-      <c r="B8" s="8">
+      <c r="B8" s="6">
         <v>8</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E8">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="F8">
+        <v>246</v>
+      </c>
+      <c r="G8">
         <v>144</v>
       </c>
-      <c r="G8">
+      <c r="H8">
         <v>28.8</v>
       </c>
-      <c r="H8">
-        <v>5.4</v>
-      </c>
       <c r="I8">
-        <v>2736</v>
-      </c>
-      <c r="J8">
-        <v>1484</v>
-      </c>
-      <c r="K8">
-        <v>4220</v>
-      </c>
-      <c r="L8">
-        <v>2736</v>
-      </c>
-      <c r="O8" s="4"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+        <v>8.5</v>
+      </c>
+      <c r="J8" s="10">
+        <f t="shared" si="0"/>
+        <v>480</v>
+      </c>
+      <c r="K8" s="10">
+        <f t="shared" si="1"/>
+        <v>250</v>
+      </c>
+      <c r="L8" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M8" s="10">
+        <f t="shared" si="3"/>
+        <v>1448</v>
+      </c>
+      <c r="N8" s="10">
+        <f t="shared" si="4"/>
+        <v>2678</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>1</v>
       </c>
-      <c r="B9" s="8">
+      <c r="B9" s="6">
         <v>9</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E9">
+        <v>326</v>
+      </c>
+      <c r="F9">
         <v>230</v>
       </c>
-      <c r="F9">
+      <c r="G9">
         <v>219</v>
       </c>
-      <c r="G9">
+      <c r="H9">
         <v>43.8</v>
       </c>
-      <c r="H9">
+      <c r="I9">
         <v>5.3</v>
       </c>
-      <c r="I9">
-        <v>4161</v>
-      </c>
-      <c r="J9">
-        <v>2172</v>
-      </c>
-      <c r="K9">
-        <v>6333</v>
-      </c>
-      <c r="L9">
-        <v>4161</v>
-      </c>
-      <c r="O9" s="4"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="J9" s="10">
+        <f t="shared" si="0"/>
+        <v>978</v>
+      </c>
+      <c r="K9" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L9" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M9" s="10">
+        <f>$Q$4*MAX(F9-G9*$Q$1)*$Q$3</f>
+        <v>1241.3333333333333</v>
+      </c>
+      <c r="N9" s="10">
+        <f t="shared" si="4"/>
+        <v>2719.333333333333</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>1</v>
       </c>
-      <c r="B10" s="8">
+      <c r="B10" s="6">
         <v>10</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E10">
+        <v>70</v>
+      </c>
+      <c r="F10">
         <v>56</v>
       </c>
-      <c r="F10">
+      <c r="G10">
         <v>47</v>
       </c>
-      <c r="G10">
+      <c r="H10">
         <v>9.4</v>
       </c>
-      <c r="H10">
+      <c r="I10">
         <v>6</v>
       </c>
-      <c r="I10">
-        <v>893</v>
-      </c>
-      <c r="J10">
-        <v>544</v>
-      </c>
-      <c r="K10">
-        <v>1437</v>
-      </c>
-      <c r="L10">
-        <v>893</v>
-      </c>
-      <c r="O10" s="4"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="J10" s="10">
+        <f t="shared" si="0"/>
+        <v>210</v>
+      </c>
+      <c r="K10" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L10" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M10" s="10">
+        <f t="shared" si="3"/>
+        <v>310.66666666666669</v>
+      </c>
+      <c r="N10" s="10">
+        <f t="shared" si="4"/>
+        <v>1020.6666666666667</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>2</v>
       </c>
-      <c r="B11" s="8">
+      <c r="B11" s="6">
         <v>3</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E11">
+        <v>211</v>
+      </c>
+      <c r="F11">
         <v>173</v>
       </c>
-      <c r="F11">
+      <c r="G11">
         <v>131</v>
       </c>
-      <c r="G11">
+      <c r="H11">
         <v>26.2</v>
       </c>
-      <c r="H11">
+      <c r="I11">
         <v>6.6</v>
       </c>
-      <c r="I11">
-        <v>2489</v>
-      </c>
-      <c r="J11">
-        <v>1713</v>
-      </c>
-      <c r="K11">
-        <v>4202</v>
-      </c>
-      <c r="L11">
-        <v>2489</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="J11" s="10">
+        <f t="shared" si="0"/>
+        <v>633</v>
+      </c>
+      <c r="K11" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L11" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M11" s="10">
+        <f t="shared" si="3"/>
+        <v>978.66666666666674</v>
+      </c>
+      <c r="N11" s="10">
+        <f t="shared" si="4"/>
+        <v>2111.666666666667</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>2</v>
       </c>
-      <c r="B12" s="8">
+      <c r="B12" s="6">
         <v>4</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E12">
+        <v>137</v>
+      </c>
+      <c r="F12">
         <v>103</v>
       </c>
-      <c r="F12">
+      <c r="G12">
         <v>110</v>
       </c>
-      <c r="G12">
+      <c r="H12">
         <v>22</v>
       </c>
-      <c r="H12">
+      <c r="I12">
         <v>4.7</v>
       </c>
-      <c r="I12">
-        <v>2090</v>
-      </c>
-      <c r="J12">
-        <v>945</v>
-      </c>
-      <c r="K12">
-        <v>3035</v>
-      </c>
-      <c r="L12">
-        <v>2090</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="J12" s="10">
+        <f t="shared" si="0"/>
+        <v>411</v>
+      </c>
+      <c r="K12" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L12" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M12" s="10">
+        <f t="shared" si="3"/>
+        <v>540</v>
+      </c>
+      <c r="N12" s="10">
+        <f t="shared" si="4"/>
+        <v>1451</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>2</v>
       </c>
-      <c r="B13" s="8">
+      <c r="B13" s="6">
         <v>5</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D13" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="E13">
+        <v>106</v>
+      </c>
+      <c r="F13">
         <v>89</v>
       </c>
-      <c r="F13">
+      <c r="G13">
         <v>80</v>
       </c>
-      <c r="G13">
+      <c r="H13">
         <v>16</v>
       </c>
-      <c r="H13">
+      <c r="I13">
         <v>5.6</v>
       </c>
-      <c r="I13">
-        <v>1520</v>
-      </c>
-      <c r="J13">
-        <v>852</v>
-      </c>
-      <c r="K13">
-        <v>2372</v>
-      </c>
-      <c r="L13">
-        <v>1520</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="J13" s="10">
+        <f t="shared" si="0"/>
+        <v>318</v>
+      </c>
+      <c r="K13" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L13" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M13" s="10">
+        <f t="shared" si="3"/>
+        <v>486.66666666666669</v>
+      </c>
+      <c r="N13" s="10">
+        <f t="shared" si="4"/>
+        <v>1304.6666666666667</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>2</v>
       </c>
-      <c r="B14" s="8">
+      <c r="B14" s="6">
         <v>6</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E14">
+        <v>137</v>
+      </c>
+      <c r="F14">
         <v>100</v>
       </c>
-      <c r="F14">
+      <c r="G14">
         <v>98</v>
       </c>
-      <c r="G14">
+      <c r="H14">
         <v>19.600000000000001</v>
       </c>
-      <c r="H14">
+      <c r="I14">
         <v>5.0999999999999996</v>
       </c>
-      <c r="I14">
-        <v>1862</v>
-      </c>
-      <c r="J14">
-        <v>938</v>
-      </c>
-      <c r="K14">
-        <v>2800</v>
-      </c>
-      <c r="L14">
-        <v>1862</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="J14" s="10">
+        <f t="shared" si="0"/>
+        <v>411</v>
+      </c>
+      <c r="K14" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L14" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M14" s="10">
+        <f t="shared" si="3"/>
+        <v>536.00000000000011</v>
+      </c>
+      <c r="N14" s="10">
+        <f t="shared" si="4"/>
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>2</v>
       </c>
-      <c r="B15" s="8">
+      <c r="B15" s="6">
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="D15" s="11" t="s">
-        <v>56</v>
+        <v>48</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>53</v>
       </c>
       <c r="E15">
+        <v>205</v>
+      </c>
+      <c r="F15">
         <v>138</v>
       </c>
-      <c r="F15">
+      <c r="G15">
         <v>151</v>
       </c>
-      <c r="G15">
+      <c r="H15">
         <v>30.2</v>
       </c>
-      <c r="H15">
+      <c r="I15">
         <v>4.5999999999999996</v>
       </c>
-      <c r="I15">
-        <v>2869</v>
-      </c>
-      <c r="J15">
-        <v>1258</v>
-      </c>
-      <c r="K15">
-        <v>4127</v>
-      </c>
-      <c r="L15">
-        <v>2869</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="J15" s="10">
+        <f t="shared" si="0"/>
+        <v>615</v>
+      </c>
+      <c r="K15" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L15" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M15" s="10">
+        <f t="shared" si="3"/>
+        <v>718.66666666666663</v>
+      </c>
+      <c r="N15" s="10">
+        <f t="shared" si="4"/>
+        <v>1833.6666666666665</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>2</v>
       </c>
-      <c r="B16" s="8">
+      <c r="B16" s="6">
         <v>8</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E16">
-        <v>339</v>
+        <v>426</v>
       </c>
       <c r="F16">
+        <v>429</v>
+      </c>
+      <c r="G16">
         <v>359</v>
       </c>
-      <c r="G16">
+      <c r="H16">
         <v>71.8</v>
       </c>
-      <c r="H16">
-        <v>4.7</v>
-      </c>
       <c r="I16">
-        <v>6821</v>
-      </c>
-      <c r="J16">
-        <v>3117</v>
-      </c>
-      <c r="K16">
-        <v>9938</v>
-      </c>
-      <c r="L16">
-        <v>6821</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="J16" s="10">
+        <f t="shared" si="0"/>
+        <v>1278</v>
+      </c>
+      <c r="K16" s="10">
+        <f t="shared" si="1"/>
+        <v>250</v>
+      </c>
+      <c r="L16" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M16" s="10">
+        <f t="shared" si="3"/>
+        <v>2381.3333333333335</v>
+      </c>
+      <c r="N16" s="10">
+        <f t="shared" si="4"/>
+        <v>4409.3333333333339</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>2</v>
       </c>
-      <c r="B17" s="8">
+      <c r="B17" s="6">
         <v>9</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E17">
+        <v>89</v>
+      </c>
+      <c r="F17">
         <v>87</v>
       </c>
-      <c r="F17">
+      <c r="G17">
         <v>76</v>
       </c>
-      <c r="G17">
+      <c r="H17">
         <v>15.2</v>
       </c>
-      <c r="H17">
+      <c r="I17">
         <v>5.7</v>
       </c>
-      <c r="I17">
-        <v>1444</v>
-      </c>
-      <c r="J17">
-        <v>838</v>
-      </c>
-      <c r="K17">
-        <v>2282</v>
-      </c>
-      <c r="L17">
-        <v>1444</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J17" s="10">
+        <f t="shared" si="0"/>
+        <v>267</v>
+      </c>
+      <c r="K17" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L17" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M17" s="10">
+        <f t="shared" si="3"/>
+        <v>478.66666666666669</v>
+      </c>
+      <c r="N17" s="10">
+        <f t="shared" si="4"/>
+        <v>1245.6666666666667</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>2</v>
       </c>
-      <c r="B18" s="8">
+      <c r="B18" s="6">
         <v>10</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E18">
+        <v>305</v>
+      </c>
+      <c r="F18">
         <v>218</v>
       </c>
-      <c r="F18">
+      <c r="G18">
         <v>217</v>
       </c>
-      <c r="G18">
+      <c r="H18">
         <v>43.4</v>
       </c>
-      <c r="H18">
+      <c r="I18">
         <v>5</v>
       </c>
-      <c r="I18">
-        <v>4123</v>
-      </c>
-      <c r="J18">
-        <v>2037</v>
-      </c>
-      <c r="K18">
-        <v>6160</v>
-      </c>
-      <c r="L18">
-        <v>4123</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J18" s="10">
+        <f t="shared" si="0"/>
+        <v>915</v>
+      </c>
+      <c r="K18" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L18" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M18" s="10">
+        <f t="shared" si="3"/>
+        <v>1164</v>
+      </c>
+      <c r="N18" s="10">
+        <f t="shared" si="4"/>
+        <v>2579</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>3</v>
       </c>
-      <c r="B19" s="8">
+      <c r="B19" s="6">
         <v>4</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E19">
+        <v>291</v>
+      </c>
+      <c r="F19">
         <v>215</v>
       </c>
-      <c r="F19">
+      <c r="G19">
         <v>77</v>
       </c>
-      <c r="G19">
+      <c r="H19">
         <v>15.4</v>
       </c>
-      <c r="H19">
+      <c r="I19">
         <v>14</v>
       </c>
-      <c r="I19">
-        <v>1463</v>
-      </c>
-      <c r="J19">
-        <v>2329</v>
-      </c>
-      <c r="K19">
-        <v>3792</v>
-      </c>
-      <c r="L19">
-        <v>2329</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J19" s="10">
+        <f t="shared" si="0"/>
+        <v>873</v>
+      </c>
+      <c r="K19" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L19" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M19" s="10">
+        <f t="shared" si="3"/>
+        <v>1330.6666666666667</v>
+      </c>
+      <c r="N19" s="10">
+        <f t="shared" si="4"/>
+        <v>2703.666666666667</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>3</v>
       </c>
-      <c r="B20" s="8">
+      <c r="B20" s="6">
         <v>5</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E20">
+        <v>121</v>
+      </c>
+      <c r="F20">
         <v>113</v>
       </c>
-      <c r="F20">
+      <c r="G20">
         <v>63</v>
       </c>
-      <c r="G20">
+      <c r="H20">
         <v>12.6</v>
       </c>
-      <c r="H20">
+      <c r="I20">
         <v>9</v>
       </c>
-      <c r="I20">
-        <v>1197</v>
-      </c>
-      <c r="J20">
-        <v>1171</v>
-      </c>
-      <c r="K20">
-        <v>2368</v>
-      </c>
-      <c r="L20">
-        <v>1197</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J20" s="10">
+        <f t="shared" si="0"/>
+        <v>363</v>
+      </c>
+      <c r="K20" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L20" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M20" s="10">
+        <f t="shared" si="3"/>
+        <v>669.33333333333337</v>
+      </c>
+      <c r="N20" s="10">
+        <f t="shared" si="4"/>
+        <v>1532.3333333333335</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>3</v>
       </c>
-      <c r="B21" s="8">
+      <c r="B21" s="6">
         <v>6</v>
       </c>
       <c r="C21" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D21" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D21" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="E21">
+        <v>269</v>
+      </c>
+      <c r="F21">
         <v>192</v>
       </c>
-      <c r="F21">
+      <c r="G21">
         <v>126</v>
       </c>
-      <c r="G21">
+      <c r="H21">
         <v>25.2</v>
       </c>
-      <c r="H21">
+      <c r="I21">
         <v>7.6</v>
       </c>
-      <c r="I21">
-        <v>2394</v>
-      </c>
-      <c r="J21">
-        <v>1946</v>
-      </c>
-      <c r="K21">
-        <v>4340</v>
-      </c>
-      <c r="L21">
-        <v>2394</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J21" s="10">
+        <f t="shared" si="0"/>
+        <v>807</v>
+      </c>
+      <c r="K21" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L21" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M21" s="10">
+        <f t="shared" si="3"/>
+        <v>1112.0000000000002</v>
+      </c>
+      <c r="N21" s="10">
+        <f t="shared" si="4"/>
+        <v>2419</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>3</v>
       </c>
-      <c r="B22" s="8">
+      <c r="B22" s="6">
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D22" s="11" t="s">
-        <v>56</v>
+        <v>49</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>53</v>
       </c>
       <c r="E22">
+        <v>359</v>
+      </c>
+      <c r="F22">
         <v>250</v>
       </c>
-      <c r="F22">
+      <c r="G22">
         <v>167</v>
       </c>
-      <c r="G22">
+      <c r="H22">
         <v>33.4</v>
       </c>
-      <c r="H22">
+      <c r="I22">
         <v>7.5</v>
       </c>
-      <c r="I22">
-        <v>3173</v>
-      </c>
-      <c r="J22">
-        <v>2527</v>
-      </c>
-      <c r="K22">
-        <v>5700</v>
-      </c>
-      <c r="L22">
-        <v>3173</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J22" s="10">
+        <f t="shared" si="0"/>
+        <v>1077</v>
+      </c>
+      <c r="K22" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L22" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M22" s="10">
+        <f t="shared" si="3"/>
+        <v>1444</v>
+      </c>
+      <c r="N22" s="10">
+        <f t="shared" si="4"/>
+        <v>3021</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>3</v>
       </c>
-      <c r="B23" s="8">
+      <c r="B23" s="6">
         <v>8</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E23">
-        <v>234</v>
+        <v>259</v>
       </c>
       <c r="F23">
+        <v>324</v>
+      </c>
+      <c r="G23">
         <v>230</v>
       </c>
-      <c r="G23">
+      <c r="H23">
         <v>46</v>
       </c>
-      <c r="H23">
-        <v>5.0999999999999996</v>
-      </c>
       <c r="I23">
-        <v>4370</v>
-      </c>
-      <c r="J23">
-        <v>2193</v>
-      </c>
-      <c r="K23">
-        <v>6563</v>
-      </c>
-      <c r="L23">
-        <v>4370</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="J23" s="10">
+        <f t="shared" si="0"/>
+        <v>777</v>
+      </c>
+      <c r="K23" s="10">
+        <f t="shared" si="1"/>
+        <v>250</v>
+      </c>
+      <c r="L23" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M23" s="10">
+        <f t="shared" si="3"/>
+        <v>1853.3333333333335</v>
+      </c>
+      <c r="N23" s="10">
+        <f t="shared" si="4"/>
+        <v>3380.3333333333335</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>3</v>
       </c>
-      <c r="B24" s="8">
+      <c r="B24" s="6">
         <v>9</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E24">
+        <v>270</v>
+      </c>
+      <c r="F24">
         <v>217</v>
       </c>
-      <c r="F24">
+      <c r="G24">
         <v>138</v>
       </c>
-      <c r="G24">
+      <c r="H24">
         <v>27.6</v>
       </c>
-      <c r="H24">
+      <c r="I24">
         <v>7.9</v>
       </c>
-      <c r="I24">
-        <v>2622</v>
-      </c>
-      <c r="J24">
-        <v>2210</v>
-      </c>
-      <c r="K24">
-        <v>4832</v>
-      </c>
-      <c r="L24">
-        <v>2622</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J24" s="10">
+        <f t="shared" si="0"/>
+        <v>810</v>
+      </c>
+      <c r="K24" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L24" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M24" s="10">
+        <f t="shared" si="3"/>
+        <v>1262.6666666666667</v>
+      </c>
+      <c r="N24" s="10">
+        <f t="shared" si="4"/>
+        <v>2572.666666666667</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>3</v>
       </c>
-      <c r="B25" s="8">
+      <c r="B25" s="6">
         <v>10</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E25">
+        <v>131</v>
+      </c>
+      <c r="F25">
         <v>108</v>
       </c>
-      <c r="F25">
+      <c r="G25">
         <v>92</v>
       </c>
-      <c r="G25">
+      <c r="H25">
         <v>18.399999999999999</v>
       </c>
-      <c r="H25">
+      <c r="I25">
         <v>5.9</v>
       </c>
-      <c r="I25">
-        <v>1748</v>
-      </c>
-      <c r="J25">
-        <v>1045</v>
-      </c>
-      <c r="K25">
-        <v>2793</v>
-      </c>
-      <c r="L25">
-        <v>1748</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J25" s="10">
+        <f t="shared" si="0"/>
+        <v>393</v>
+      </c>
+      <c r="K25" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L25" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M25" s="10">
+        <f t="shared" si="3"/>
+        <v>597.33333333333337</v>
+      </c>
+      <c r="N25" s="10">
+        <f t="shared" si="4"/>
+        <v>1490.3333333333335</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>4</v>
       </c>
-      <c r="B26" s="8">
+      <c r="B26" s="6">
         <v>5</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E26">
+        <v>187</v>
+      </c>
+      <c r="F26">
         <v>130</v>
       </c>
-      <c r="F26">
+      <c r="G26">
         <v>93</v>
       </c>
-      <c r="G26">
+      <c r="H26">
         <v>18.600000000000001</v>
       </c>
-      <c r="H26">
+      <c r="I26">
         <v>7</v>
       </c>
-      <c r="I26">
-        <v>1767</v>
-      </c>
-      <c r="J26">
-        <v>1300</v>
-      </c>
-      <c r="K26">
-        <v>3067</v>
-      </c>
-      <c r="L26">
-        <v>1767</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J26" s="10">
+        <f t="shared" si="0"/>
+        <v>561</v>
+      </c>
+      <c r="K26" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L26" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M26" s="10">
+        <f t="shared" si="3"/>
+        <v>742.66666666666674</v>
+      </c>
+      <c r="N26" s="10">
+        <f t="shared" si="4"/>
+        <v>1803.6666666666667</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>4</v>
       </c>
-      <c r="B27" s="8">
+      <c r="B27" s="6">
         <v>6</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E27">
+        <v>233</v>
+      </c>
+      <c r="F27">
         <v>149</v>
       </c>
-      <c r="F27">
+      <c r="G27">
         <v>161</v>
       </c>
-      <c r="G27">
+      <c r="H27">
         <v>32.200000000000003</v>
       </c>
-      <c r="H27">
+      <c r="I27">
         <v>4.5999999999999996</v>
       </c>
-      <c r="I27">
-        <v>3059</v>
-      </c>
-      <c r="J27">
-        <v>1363</v>
-      </c>
-      <c r="K27">
-        <v>4422</v>
-      </c>
-      <c r="L27">
-        <v>3059</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J27" s="10">
+        <f t="shared" si="0"/>
+        <v>699</v>
+      </c>
+      <c r="K27" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L27" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M27" s="10">
+        <f t="shared" si="3"/>
+        <v>778.66666666666663</v>
+      </c>
+      <c r="N27" s="10">
+        <f t="shared" si="4"/>
+        <v>1977.6666666666665</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>4</v>
       </c>
-      <c r="B28" s="8">
+      <c r="B28" s="6">
         <v>7</v>
       </c>
       <c r="C28" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D28" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="D28" s="11" t="s">
-        <v>56</v>
-      </c>
       <c r="E28">
+        <v>126</v>
+      </c>
+      <c r="F28">
         <v>93</v>
       </c>
-      <c r="F28">
+      <c r="G28">
         <v>90</v>
       </c>
-      <c r="G28">
+      <c r="H28">
         <v>18</v>
       </c>
-      <c r="H28">
+      <c r="I28">
         <v>5.2</v>
       </c>
-      <c r="I28">
-        <v>1710</v>
-      </c>
-      <c r="J28">
-        <v>875</v>
-      </c>
-      <c r="K28">
-        <v>2585</v>
-      </c>
-      <c r="L28">
-        <v>1710</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J28" s="10">
+        <f t="shared" si="0"/>
+        <v>378</v>
+      </c>
+      <c r="K28" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L28" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M28" s="10">
+        <f t="shared" si="3"/>
+        <v>500</v>
+      </c>
+      <c r="N28" s="10">
+        <f t="shared" si="4"/>
+        <v>1378</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>4</v>
       </c>
-      <c r="B29" s="8">
+      <c r="B29" s="6">
         <v>8</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E29">
-        <v>380</v>
+        <v>507</v>
       </c>
       <c r="F29">
+        <v>470</v>
+      </c>
+      <c r="G29">
         <v>290</v>
       </c>
-      <c r="G29">
+      <c r="H29">
         <v>58</v>
       </c>
-      <c r="H29">
-        <v>6.6</v>
-      </c>
       <c r="I29">
-        <v>5510</v>
-      </c>
-      <c r="J29">
-        <v>3757</v>
-      </c>
-      <c r="K29">
-        <v>9267</v>
-      </c>
-      <c r="L29">
-        <v>5510</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+        <v>8.1</v>
+      </c>
+      <c r="J29" s="10">
+        <f t="shared" si="0"/>
+        <v>1521</v>
+      </c>
+      <c r="K29" s="10">
+        <f t="shared" si="1"/>
+        <v>250</v>
+      </c>
+      <c r="L29" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M29" s="10">
+        <f t="shared" si="3"/>
+        <v>2746.666666666667</v>
+      </c>
+      <c r="N29" s="10">
+        <f t="shared" si="4"/>
+        <v>5017.666666666667</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>4</v>
       </c>
-      <c r="B30" s="8">
+      <c r="B30" s="6">
         <v>9</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E30">
+        <v>99</v>
+      </c>
+      <c r="F30">
         <v>87</v>
       </c>
-      <c r="F30">
+      <c r="G30">
         <v>75</v>
       </c>
-      <c r="G30">
+      <c r="H30">
         <v>15</v>
       </c>
-      <c r="H30">
+      <c r="I30">
         <v>5.8</v>
       </c>
-      <c r="I30">
-        <v>1425</v>
-      </c>
-      <c r="J30">
-        <v>840</v>
-      </c>
-      <c r="K30">
-        <v>2265</v>
-      </c>
-      <c r="L30">
-        <v>1425</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J30" s="10">
+        <f t="shared" si="0"/>
+        <v>297</v>
+      </c>
+      <c r="K30" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L30" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M30" s="10">
+        <f t="shared" si="3"/>
+        <v>480</v>
+      </c>
+      <c r="N30" s="10">
+        <f t="shared" si="4"/>
+        <v>1277</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>4</v>
       </c>
-      <c r="B31" s="8">
+      <c r="B31" s="6">
         <v>10</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E31">
+        <v>387</v>
+      </c>
+      <c r="F31">
         <v>259</v>
       </c>
-      <c r="F31">
+      <c r="G31">
         <v>125</v>
       </c>
-      <c r="G31">
+      <c r="H31">
         <v>25</v>
       </c>
-      <c r="H31">
+      <c r="I31">
         <v>10.4</v>
       </c>
-      <c r="I31">
-        <v>2375</v>
-      </c>
-      <c r="J31">
-        <v>2730</v>
-      </c>
-      <c r="K31">
-        <v>5105</v>
-      </c>
-      <c r="L31">
-        <v>2730</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J31" s="10">
+        <f t="shared" si="0"/>
+        <v>1161</v>
+      </c>
+      <c r="K31" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L31" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M31" s="10">
+        <f t="shared" si="3"/>
+        <v>1560</v>
+      </c>
+      <c r="N31" s="10">
+        <f t="shared" si="4"/>
+        <v>3221</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>5</v>
       </c>
-      <c r="B32" s="8">
+      <c r="B32" s="6">
         <v>6</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E32">
+        <v>164</v>
+      </c>
+      <c r="F32">
         <v>110</v>
       </c>
-      <c r="F32">
+      <c r="G32">
         <v>70</v>
       </c>
-      <c r="G32">
+      <c r="H32">
         <v>14</v>
       </c>
-      <c r="H32">
+      <c r="I32">
         <v>7.9</v>
       </c>
-      <c r="I32">
-        <v>1330</v>
-      </c>
-      <c r="J32">
-        <v>1120</v>
-      </c>
-      <c r="K32">
-        <v>2450</v>
-      </c>
-      <c r="L32">
-        <v>1330</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A33" s="10">
+      <c r="J32" s="10">
+        <f t="shared" si="0"/>
+        <v>492</v>
+      </c>
+      <c r="K32" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L32" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M32" s="10">
+        <f t="shared" si="3"/>
+        <v>640</v>
+      </c>
+      <c r="N32" s="10">
+        <f t="shared" si="4"/>
+        <v>1632</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A33" s="8">
         <v>5</v>
       </c>
-      <c r="B33" s="8">
+      <c r="B33" s="6">
         <v>7</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D33" s="11" t="s">
-        <v>56</v>
+        <v>51</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>53</v>
       </c>
       <c r="E33">
+        <v>254</v>
+      </c>
+      <c r="F33">
         <v>168</v>
       </c>
-      <c r="F33">
+      <c r="G33">
         <v>173</v>
       </c>
-      <c r="G33">
+      <c r="H33">
         <v>34.6</v>
       </c>
-      <c r="H33">
+      <c r="I33">
         <v>4.9000000000000004</v>
       </c>
-      <c r="I33">
-        <v>3287</v>
-      </c>
-      <c r="J33">
-        <v>1556</v>
-      </c>
-      <c r="K33">
-        <v>4843</v>
-      </c>
-      <c r="L33">
-        <v>3287</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J33" s="10">
+        <f t="shared" si="0"/>
+        <v>762</v>
+      </c>
+      <c r="K33" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L33" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M33" s="10">
+        <f t="shared" si="3"/>
+        <v>889.33333333333337</v>
+      </c>
+      <c r="N33" s="10">
+        <f t="shared" si="4"/>
+        <v>2151.3333333333335</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>5</v>
       </c>
-      <c r="B34" s="8">
+      <c r="B34" s="6">
         <v>8</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E34">
-        <v>279</v>
+        <v>337</v>
       </c>
       <c r="F34">
+        <v>369</v>
+      </c>
+      <c r="G34">
         <v>281</v>
       </c>
-      <c r="G34">
+      <c r="H34">
         <v>56.2</v>
       </c>
-      <c r="H34">
-        <v>5</v>
-      </c>
       <c r="I34">
-        <v>5339</v>
-      </c>
-      <c r="J34">
-        <v>2599</v>
-      </c>
-      <c r="K34">
-        <v>7938</v>
-      </c>
-      <c r="L34">
-        <v>5339</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+        <v>6.6</v>
+      </c>
+      <c r="J34" s="10">
+        <f t="shared" si="0"/>
+        <v>1011</v>
+      </c>
+      <c r="K34" s="10">
+        <f t="shared" si="1"/>
+        <v>250</v>
+      </c>
+      <c r="L34" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M34" s="10">
+        <f t="shared" si="3"/>
+        <v>2085.3333333333335</v>
+      </c>
+      <c r="N34" s="10">
+        <f t="shared" si="4"/>
+        <v>3846.3333333333335</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>5</v>
       </c>
-      <c r="B35" s="8">
+      <c r="B35" s="6">
         <v>9</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E35">
+        <v>165</v>
+      </c>
+      <c r="F35">
         <v>136</v>
       </c>
-      <c r="F35">
+      <c r="G35">
         <v>118</v>
       </c>
-      <c r="G35">
+      <c r="H35">
         <v>23.6</v>
       </c>
-      <c r="H35">
+      <c r="I35">
         <v>5.8</v>
       </c>
-      <c r="I35">
-        <v>2242</v>
-      </c>
-      <c r="J35">
-        <v>1311</v>
-      </c>
-      <c r="K35">
-        <v>3553</v>
-      </c>
-      <c r="L35">
-        <v>2242</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J35" s="10">
+        <f t="shared" si="0"/>
+        <v>495</v>
+      </c>
+      <c r="K35" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L35" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M35" s="10">
+        <f t="shared" si="3"/>
+        <v>749.33333333333337</v>
+      </c>
+      <c r="N35" s="10">
+        <f t="shared" si="4"/>
+        <v>1744.3333333333335</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>5</v>
       </c>
-      <c r="B36" s="8">
+      <c r="B36" s="6">
         <v>10</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E36">
+        <v>216</v>
+      </c>
+      <c r="F36">
         <v>158</v>
       </c>
-      <c r="F36">
+      <c r="G36">
         <v>155</v>
       </c>
-      <c r="G36">
+      <c r="H36">
         <v>31</v>
       </c>
-      <c r="H36">
+      <c r="I36">
         <v>5.0999999999999996</v>
       </c>
-      <c r="I36">
-        <v>2945</v>
-      </c>
-      <c r="J36">
-        <v>1482</v>
-      </c>
-      <c r="K36">
-        <v>4427</v>
-      </c>
-      <c r="L36">
-        <v>2945</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J36" s="10">
+        <f t="shared" si="0"/>
+        <v>648</v>
+      </c>
+      <c r="K36" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L36" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M36" s="10">
+        <f t="shared" si="3"/>
+        <v>846.66666666666674</v>
+      </c>
+      <c r="N36" s="10">
+        <f t="shared" si="4"/>
+        <v>1994.6666666666667</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>6</v>
       </c>
-      <c r="B37" s="8">
+      <c r="B37" s="6">
         <v>7</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="D37" s="11" t="s">
-        <v>56</v>
+        <v>52</v>
+      </c>
+      <c r="D37" s="9" t="s">
+        <v>53</v>
       </c>
       <c r="E37">
+        <v>299</v>
+      </c>
+      <c r="F37">
         <v>185</v>
       </c>
-      <c r="F37">
+      <c r="G37">
         <v>232</v>
       </c>
-      <c r="G37">
+      <c r="H37">
         <v>46.4</v>
       </c>
-      <c r="H37">
+      <c r="I37">
         <v>4</v>
       </c>
-      <c r="I37">
-        <v>4408</v>
-      </c>
-      <c r="J37">
-        <v>1617</v>
-      </c>
-      <c r="K37">
-        <v>6025</v>
-      </c>
-      <c r="L37">
-        <v>4408</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J37" s="10">
+        <f t="shared" si="0"/>
+        <v>897</v>
+      </c>
+      <c r="K37" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L37" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M37" s="10">
+        <f t="shared" si="3"/>
+        <v>924</v>
+      </c>
+      <c r="N37" s="10">
+        <f t="shared" si="4"/>
+        <v>2321</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>6</v>
       </c>
-      <c r="B38" s="8">
+      <c r="B38" s="6">
         <v>8</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E38">
-        <v>358</v>
+        <v>484</v>
       </c>
       <c r="F38">
+        <v>448</v>
+      </c>
+      <c r="G38">
         <v>315</v>
       </c>
-      <c r="G38">
+      <c r="H38">
         <v>63</v>
       </c>
-      <c r="H38">
-        <v>5.7</v>
-      </c>
       <c r="I38">
-        <v>5985</v>
-      </c>
-      <c r="J38">
-        <v>3442</v>
-      </c>
-      <c r="K38">
-        <v>9427</v>
-      </c>
-      <c r="L38">
-        <v>5985</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+        <v>7.1</v>
+      </c>
+      <c r="J38" s="10">
+        <f t="shared" si="0"/>
+        <v>1452</v>
+      </c>
+      <c r="K38" s="10">
+        <f t="shared" si="1"/>
+        <v>250</v>
+      </c>
+      <c r="L38" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M38" s="10">
+        <f t="shared" si="3"/>
+        <v>2566.666666666667</v>
+      </c>
+      <c r="N38" s="10">
+        <f t="shared" si="4"/>
+        <v>4768.666666666667</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>6</v>
       </c>
-      <c r="B39" s="8">
+      <c r="B39" s="6">
         <v>9</v>
       </c>
       <c r="C39" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D39" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D39" s="1" t="s">
-        <v>58</v>
-      </c>
       <c r="E39">
+        <v>210</v>
+      </c>
+      <c r="F39">
         <v>153</v>
       </c>
-      <c r="F39">
+      <c r="G39">
         <v>166</v>
       </c>
-      <c r="G39">
+      <c r="H39">
         <v>33.200000000000003</v>
       </c>
-      <c r="H39">
+      <c r="I39">
         <v>4.5999999999999996</v>
       </c>
-      <c r="I39">
-        <v>3154</v>
-      </c>
-      <c r="J39">
-        <v>1398</v>
-      </c>
-      <c r="K39">
-        <v>4552</v>
-      </c>
-      <c r="L39">
-        <v>3154</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J39" s="10">
+        <f t="shared" si="0"/>
+        <v>630</v>
+      </c>
+      <c r="K39" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L39" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M39" s="10">
+        <f t="shared" si="3"/>
+        <v>798.66666666666663</v>
+      </c>
+      <c r="N39" s="10">
+        <f t="shared" si="4"/>
+        <v>1928.6666666666665</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>6</v>
       </c>
-      <c r="B40" s="8">
+      <c r="B40" s="6">
         <v>10</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E40">
+        <v>363</v>
+      </c>
+      <c r="F40">
         <v>237</v>
       </c>
-      <c r="F40">
+      <c r="G40">
         <v>216</v>
       </c>
-      <c r="G40">
+      <c r="H40">
         <v>43.2</v>
       </c>
-      <c r="H40">
+      <c r="I40">
         <v>5.5</v>
       </c>
-      <c r="I40">
-        <v>4104</v>
-      </c>
-      <c r="J40">
-        <v>2261</v>
-      </c>
-      <c r="K40">
-        <v>6365</v>
-      </c>
-      <c r="L40">
-        <v>4104</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J40" s="10">
+        <f t="shared" si="0"/>
+        <v>1089</v>
+      </c>
+      <c r="K40" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L40" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M40" s="10">
+        <f t="shared" si="3"/>
+        <v>1292.0000000000002</v>
+      </c>
+      <c r="N40" s="10">
+        <f t="shared" si="4"/>
+        <v>2881</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>7</v>
       </c>
-      <c r="B41" s="8">
+      <c r="B41" s="6">
         <v>8</v>
       </c>
       <c r="C41" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D41" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="D41" s="1" t="s">
-        <v>59</v>
-      </c>
       <c r="E41">
-        <v>414</v>
+        <v>575</v>
       </c>
       <c r="F41">
+        <v>504</v>
+      </c>
+      <c r="G41">
         <v>365</v>
       </c>
-      <c r="G41">
+      <c r="H41">
         <v>73</v>
       </c>
-      <c r="H41">
-        <v>5.7</v>
-      </c>
       <c r="I41">
-        <v>6935</v>
-      </c>
-      <c r="J41">
-        <v>3978</v>
-      </c>
-      <c r="K41">
-        <v>10913</v>
-      </c>
-      <c r="L41">
-        <v>6935</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+        <v>6.9</v>
+      </c>
+      <c r="J41" s="10">
+        <f t="shared" si="0"/>
+        <v>1725</v>
+      </c>
+      <c r="K41" s="10">
+        <f t="shared" si="1"/>
+        <v>250</v>
+      </c>
+      <c r="L41" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M41" s="10">
+        <f t="shared" si="3"/>
+        <v>2873.3333333333335</v>
+      </c>
+      <c r="N41" s="10">
+        <f>SUM(J41:M41)</f>
+        <v>5348.3333333333339</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>7</v>
       </c>
-      <c r="B42" s="8">
+      <c r="B42" s="6">
         <v>9</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E42">
+        <v>84</v>
+      </c>
+      <c r="F42">
         <v>70</v>
       </c>
-      <c r="F42">
+      <c r="G42">
         <v>75</v>
       </c>
-      <c r="G42">
+      <c r="H42">
         <v>15</v>
       </c>
-      <c r="H42">
+      <c r="I42">
         <v>4.7</v>
       </c>
-      <c r="I42">
-        <v>1425</v>
-      </c>
-      <c r="J42">
-        <v>642</v>
-      </c>
-      <c r="K42">
-        <v>2067</v>
-      </c>
-      <c r="L42">
-        <v>1425</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J42" s="10">
+        <f t="shared" si="0"/>
+        <v>252</v>
+      </c>
+      <c r="K42" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L42" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M42" s="10">
+        <f t="shared" si="3"/>
+        <v>366.66666666666669</v>
+      </c>
+      <c r="N42" s="10">
+        <f t="shared" si="4"/>
+        <v>1118.6666666666667</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>7</v>
       </c>
-      <c r="B43" s="8">
+      <c r="B43" s="6">
         <v>10</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E43">
+        <v>454</v>
+      </c>
+      <c r="F43">
         <v>293</v>
       </c>
-      <c r="F43">
+      <c r="G43">
         <v>194</v>
       </c>
-      <c r="G43">
+      <c r="H43">
         <v>38.799999999999997</v>
       </c>
-      <c r="H43">
+      <c r="I43">
         <v>7.6</v>
       </c>
-      <c r="I43">
-        <v>3686</v>
-      </c>
-      <c r="J43">
-        <v>2966</v>
-      </c>
-      <c r="K43">
-        <v>6652</v>
-      </c>
-      <c r="L43">
-        <v>3686</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J43" s="10">
+        <f t="shared" si="0"/>
+        <v>1362</v>
+      </c>
+      <c r="K43" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L43" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M43" s="10">
+        <f t="shared" si="3"/>
+        <v>1694.6666666666667</v>
+      </c>
+      <c r="N43" s="10">
+        <f t="shared" si="4"/>
+        <v>3556.666666666667</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>8</v>
       </c>
-      <c r="B44" s="8">
+      <c r="B44" s="6">
         <v>9</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E44">
-        <v>384</v>
+        <v>486</v>
       </c>
       <c r="F44">
+        <v>474</v>
+      </c>
+      <c r="G44">
         <v>363</v>
       </c>
-      <c r="G44">
+      <c r="H44">
         <v>72.599999999999994</v>
       </c>
-      <c r="H44">
-        <v>5.3</v>
-      </c>
       <c r="I44">
-        <v>6897</v>
-      </c>
-      <c r="J44">
-        <v>3633</v>
-      </c>
-      <c r="K44">
-        <v>10530</v>
-      </c>
-      <c r="L44">
-        <v>6897</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+        <v>6.5</v>
+      </c>
+      <c r="J44" s="10">
+        <f t="shared" si="0"/>
+        <v>1458</v>
+      </c>
+      <c r="K44" s="10">
+        <f t="shared" si="1"/>
+        <v>250</v>
+      </c>
+      <c r="L44" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M44" s="10">
+        <f t="shared" si="3"/>
+        <v>2676</v>
+      </c>
+      <c r="N44" s="10">
+        <f t="shared" si="4"/>
+        <v>4884</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>8</v>
       </c>
-      <c r="B45" s="8">
+      <c r="B45" s="6">
         <v>10</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E45">
-        <v>209</v>
+        <v>230</v>
       </c>
       <c r="F45">
+        <v>299</v>
+      </c>
+      <c r="G45">
         <v>172</v>
       </c>
-      <c r="G45">
+      <c r="H45">
         <v>34.4</v>
       </c>
-      <c r="H45">
-        <v>6.1</v>
-      </c>
       <c r="I45">
-        <v>3268</v>
-      </c>
-      <c r="J45">
-        <v>2037</v>
-      </c>
-      <c r="K45">
-        <v>5305</v>
-      </c>
-      <c r="L45">
-        <v>3268</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="J45" s="10">
+        <f t="shared" si="0"/>
+        <v>690</v>
+      </c>
+      <c r="K45" s="10">
+        <f t="shared" si="1"/>
+        <v>250</v>
+      </c>
+      <c r="L45" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M45" s="10">
+        <f t="shared" si="3"/>
+        <v>1764.0000000000002</v>
+      </c>
+      <c r="N45" s="10">
+        <f t="shared" si="4"/>
+        <v>3204</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>9</v>
       </c>
-      <c r="B46" s="8">
+      <c r="B46" s="6">
         <v>10</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E46">
+        <v>366</v>
+      </c>
+      <c r="F46">
         <v>264</v>
       </c>
-      <c r="F46">
+      <c r="G46">
         <v>200</v>
       </c>
-      <c r="G46">
+      <c r="H46">
         <v>40</v>
       </c>
-      <c r="H46">
+      <c r="I46">
         <v>6.6</v>
       </c>
-      <c r="I46">
-        <v>3800</v>
-      </c>
-      <c r="J46">
-        <v>2613</v>
-      </c>
-      <c r="K46">
-        <v>6413</v>
-      </c>
-      <c r="L46">
-        <v>3800</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J46" s="10">
+        <f t="shared" si="0"/>
+        <v>1098</v>
+      </c>
+      <c r="K46" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L46" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="M46" s="10">
+        <f t="shared" si="3"/>
+        <v>1493.3333333333335</v>
+      </c>
+      <c r="N46" s="10">
+        <f t="shared" si="4"/>
+        <v>3091.3333333333335</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>1</v>
       </c>
-      <c r="B47" s="8">
+      <c r="B47" s="6">
         <v>1</v>
       </c>
-      <c r="C47" s="8"/>
-      <c r="D47" s="8"/>
+      <c r="C47" s="6"/>
+      <c r="D47" s="6"/>
       <c r="E47">
         <v>0</v>
       </c>
@@ -2686,25 +3404,16 @@
       <c r="I47">
         <v>0</v>
       </c>
-      <c r="J47">
-        <v>0</v>
-      </c>
-      <c r="K47">
-        <v>0</v>
-      </c>
-      <c r="L47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>2</v>
       </c>
-      <c r="B48" s="8">
+      <c r="B48" s="6">
         <v>2</v>
       </c>
-      <c r="C48" s="8"/>
-      <c r="D48" s="8"/>
+      <c r="C48" s="6"/>
+      <c r="D48" s="6"/>
       <c r="E48">
         <v>0</v>
       </c>
@@ -2720,25 +3429,16 @@
       <c r="I48">
         <v>0</v>
       </c>
-      <c r="J48">
-        <v>0</v>
-      </c>
-      <c r="K48">
-        <v>0</v>
-      </c>
-      <c r="L48">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>3</v>
       </c>
-      <c r="B49" s="8">
+      <c r="B49" s="6">
         <v>3</v>
       </c>
-      <c r="C49" s="8"/>
-      <c r="D49" s="8"/>
+      <c r="C49" s="6"/>
+      <c r="D49" s="6"/>
       <c r="E49">
         <v>0</v>
       </c>
@@ -2754,25 +3454,16 @@
       <c r="I49">
         <v>0</v>
       </c>
-      <c r="J49">
-        <v>0</v>
-      </c>
-      <c r="K49">
-        <v>0</v>
-      </c>
-      <c r="L49">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>4</v>
       </c>
-      <c r="B50" s="8">
+      <c r="B50" s="6">
         <v>4</v>
       </c>
-      <c r="C50" s="8"/>
-      <c r="D50" s="8"/>
+      <c r="C50" s="6"/>
+      <c r="D50" s="6"/>
       <c r="E50">
         <v>0</v>
       </c>
@@ -2788,25 +3479,16 @@
       <c r="I50">
         <v>0</v>
       </c>
-      <c r="J50">
-        <v>0</v>
-      </c>
-      <c r="K50">
-        <v>0</v>
-      </c>
-      <c r="L50">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>5</v>
       </c>
-      <c r="B51" s="8">
+      <c r="B51" s="6">
         <v>5</v>
       </c>
-      <c r="C51" s="8"/>
-      <c r="D51" s="8"/>
+      <c r="C51" s="6"/>
+      <c r="D51" s="6"/>
       <c r="E51">
         <v>0</v>
       </c>
@@ -2822,21 +3504,12 @@
       <c r="I51">
         <v>0</v>
       </c>
-      <c r="J51">
-        <v>0</v>
-      </c>
-      <c r="K51">
-        <v>0</v>
-      </c>
-      <c r="L51">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>6</v>
       </c>
-      <c r="B52" s="8">
+      <c r="B52" s="6">
         <v>6</v>
       </c>
       <c r="E52">
@@ -2854,21 +3527,12 @@
       <c r="I52">
         <v>0</v>
       </c>
-      <c r="J52">
-        <v>0</v>
-      </c>
-      <c r="K52">
-        <v>0</v>
-      </c>
-      <c r="L52">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>7</v>
       </c>
-      <c r="B53" s="8">
+      <c r="B53" s="6">
         <v>7</v>
       </c>
       <c r="E53">
@@ -2886,21 +3550,12 @@
       <c r="I53">
         <v>0</v>
       </c>
-      <c r="J53">
-        <v>0</v>
-      </c>
-      <c r="K53">
-        <v>0</v>
-      </c>
-      <c r="L53">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>8</v>
       </c>
-      <c r="B54" s="8">
+      <c r="B54" s="6">
         <v>8</v>
       </c>
       <c r="E54">
@@ -2918,21 +3573,12 @@
       <c r="I54">
         <v>0</v>
       </c>
-      <c r="J54">
-        <v>0</v>
-      </c>
-      <c r="K54">
-        <v>0</v>
-      </c>
-      <c r="L54">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>9</v>
       </c>
-      <c r="B55" s="8">
+      <c r="B55" s="6">
         <v>9</v>
       </c>
       <c r="E55">
@@ -2950,21 +3596,12 @@
       <c r="I55">
         <v>0</v>
       </c>
-      <c r="J55">
-        <v>0</v>
-      </c>
-      <c r="K55">
-        <v>0</v>
-      </c>
-      <c r="L55">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>10</v>
       </c>
-      <c r="B56" s="8">
+      <c r="B56" s="6">
         <v>10</v>
       </c>
       <c r="E56">
@@ -2982,39 +3619,9 @@
       <c r="I56">
         <v>0</v>
       </c>
-      <c r="J56">
-        <v>0</v>
-      </c>
-      <c r="K56">
-        <v>0</v>
-      </c>
-      <c r="L56">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="G57" s="2"/>
-    </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="G58" s="1"/>
-    </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="G59" s="1"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="I2:I46">
-    <cfRule type="colorScale" priority="4">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J46">
+  <conditionalFormatting sqref="J2:J56">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -3026,7 +3633,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K46">
+  <conditionalFormatting sqref="M2:M56">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -3038,7 +3645,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L46">
+  <conditionalFormatting sqref="N2:N56">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -3051,5 +3658,8 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/inputData/Parameters.xlsx
+++ b/inputData/Parameters.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sillewiberg/Desktop/Skole/Speciale/Master-Thesis-eVTOL-1/inputData/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kapta\Documents\DTU\Speciale\GitHubFiles\inputData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0218802E-FB40-954D-9A70-48D7F6E8A911}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5B1B232-F1DE-494C-9564-42A59FF0DB02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1180" windowWidth="28800" windowHeight="15280" activeTab="1" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
   </bookViews>
   <sheets>
     <sheet name="Parameters" sheetId="9" r:id="rId1"/>
@@ -509,7 +509,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3CFD079E-5109-8F49-8A19-E09E2BEBBC8C}" name="Table13" displayName="Table13" ref="A1:N56" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6" headerRowCellStyle="Comma" dataCellStyle="Comma">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3CFD079E-5109-8F49-8A19-E09E2BEBBC8C}" name="Table13" displayName="Table13" ref="A1:N56" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6">
   <autoFilter ref="A1:N56" xr:uid="{CEDCB4F7-0752-8449-BE87-89650C1E9E7C}"/>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{0330B38A-598B-B64A-86F4-FA8E25EAC437}" name="From"/>
@@ -521,15 +521,15 @@
     <tableColumn id="7" xr3:uid="{59F6BECD-EB60-114E-826A-884ADDC4EE72}" name="Km fugleflugt"/>
     <tableColumn id="8" xr3:uid="{605D45AE-CBF2-E342-BA16-1B205DDE6C4E}" name="eVTOL flyvetid (min)"/>
     <tableColumn id="9" xr3:uid="{FCFA00C8-AEDC-F54B-AE4D-2360ACC6025E}" name="Hvor meget hurtigere"/>
-    <tableColumn id="10" xr3:uid="{DBB7D64B-F97D-5C46-B464-1DA11C10DF3A}" name="Pris (Bil udgift)" dataDxfId="4" dataCellStyle="Comma"/>
-    <tableColumn id="11" xr3:uid="{CC283087-BB53-D146-A233-2D178D7E3562}" name="Færge (gns. Gælder kun Bornholm)" dataDxfId="3" dataCellStyle="Comma"/>
-    <tableColumn id="12" xr3:uid="{B4DC4D17-2AE3-D34D-926C-7506AC52E6B8}" name="Base" dataDxfId="2" dataCellStyle="Comma">
+    <tableColumn id="10" xr3:uid="{DBB7D64B-F97D-5C46-B464-1DA11C10DF3A}" name="Pris (Bil udgift)" dataDxfId="4"/>
+    <tableColumn id="11" xr3:uid="{CC283087-BB53-D146-A233-2D178D7E3562}" name="Færge (gns. Gælder kun Bornholm)" dataDxfId="3"/>
+    <tableColumn id="12" xr3:uid="{B4DC4D17-2AE3-D34D-926C-7506AC52E6B8}" name="Base" dataDxfId="2">
       <calculatedColumnFormula>$Q$5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{E70B016F-0534-2048-951F-6FD04DC33B7C}" name="Pris (udfra tidsbesparelse)" dataDxfId="1" dataCellStyle="Comma">
+    <tableColumn id="13" xr3:uid="{E70B016F-0534-2048-951F-6FD04DC33B7C}" name="Pris (udfra tidsbesparelse)" dataDxfId="1">
       <calculatedColumnFormula>$Q$4*MAX(F2-G2*$Q$1)*$Q$3</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{67EF8C2F-B7CB-8D4A-8447-692E942D0514}" name="fd_sum" dataDxfId="0" dataCellStyle="Comma">
+    <tableColumn id="14" xr3:uid="{67EF8C2F-B7CB-8D4A-8447-692E942D0514}" name="fd_sum" dataDxfId="0">
       <calculatedColumnFormula>SUM(J2:M2)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -855,18 +855,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B15C49E0-A7B4-734A-8962-DC2A879F4079}">
   <dimension ref="A1:D20"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.6640625" customWidth="1"/>
-    <col min="2" max="2" width="10.83203125" style="4"/>
+    <col min="1" max="1" width="22.625" customWidth="1"/>
+    <col min="2" max="2" width="10.875" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>20</v>
       </c>
@@ -877,7 +877,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -888,7 +888,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>42</v>
       </c>
@@ -899,7 +899,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -910,7 +910,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -921,7 +921,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -932,7 +932,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -944,7 +944,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>0</v>
       </c>
@@ -955,7 +955,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>1</v>
       </c>
@@ -966,7 +966,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>41</v>
       </c>
@@ -977,7 +977,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>2</v>
       </c>
@@ -988,7 +988,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>39</v>
       </c>
@@ -999,7 +999,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -1011,7 +1011,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>4</v>
       </c>
@@ -1023,7 +1023,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>5</v>
       </c>
@@ -1035,7 +1035,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>6</v>
       </c>
@@ -1046,7 +1046,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>38</v>
       </c>
@@ -1066,23 +1066,23 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36FC1A80-FC3B-6349-8B7A-4A1A2A7C8FC7}">
   <dimension ref="A1:R56"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="17.1640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="17.1640625" customWidth="1"/>
-    <col min="5" max="5" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="17.125" customWidth="1"/>
+    <col min="5" max="5" width="12.125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.5" customWidth="1"/>
-    <col min="7" max="7" width="17.1640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.33203125" customWidth="1"/>
+    <col min="7" max="7" width="17.125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.375" customWidth="1"/>
     <col min="9" max="9" width="21" style="10" customWidth="1"/>
-    <col min="10" max="10" width="13.6640625" style="10" customWidth="1"/>
-    <col min="11" max="11" width="32.1640625" style="10" customWidth="1"/>
-    <col min="12" max="12" width="10.6640625" style="10"/>
+    <col min="10" max="10" width="13.625" style="10" customWidth="1"/>
+    <col min="11" max="11" width="32.125" style="10" customWidth="1"/>
+    <col min="12" max="12" width="10.625" style="10"/>
     <col min="13" max="13" width="27" style="10" customWidth="1"/>
-    <col min="14" max="14" width="10.83203125" style="10" customWidth="1"/>
+    <col min="14" max="14" width="10.875" style="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>33</v>
       </c>
@@ -1132,7 +1132,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1190,7 +1190,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1249,7 +1249,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1</v>
       </c>
@@ -1304,7 +1304,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>1</v>
       </c>
@@ -1362,7 +1362,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>1</v>
       </c>
@@ -1420,7 +1420,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>1</v>
       </c>
@@ -1469,7 +1469,7 @@
         <v>3195.666666666667</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>1</v>
       </c>
@@ -1518,7 +1518,7 @@
         <v>2678</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>1</v>
       </c>
@@ -1567,7 +1567,7 @@
         <v>2719.333333333333</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>1</v>
       </c>
@@ -1616,7 +1616,7 @@
         <v>1020.6666666666667</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>2</v>
       </c>
@@ -1665,7 +1665,7 @@
         <v>2111.666666666667</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>2</v>
       </c>
@@ -1714,7 +1714,7 @@
         <v>1451</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>2</v>
       </c>
@@ -1763,7 +1763,7 @@
         <v>1304.6666666666667</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>2</v>
       </c>
@@ -1812,7 +1812,7 @@
         <v>1447</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>2</v>
       </c>
@@ -1861,7 +1861,7 @@
         <v>1833.6666666666665</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>2</v>
       </c>
@@ -1910,7 +1910,7 @@
         <v>4409.3333333333339</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>2</v>
       </c>
@@ -1959,7 +1959,7 @@
         <v>1245.6666666666667</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>2</v>
       </c>
@@ -2008,7 +2008,7 @@
         <v>2579</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>3</v>
       </c>
@@ -2057,7 +2057,7 @@
         <v>2703.666666666667</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>3</v>
       </c>
@@ -2106,7 +2106,7 @@
         <v>1532.3333333333335</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>3</v>
       </c>
@@ -2155,7 +2155,7 @@
         <v>2419</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>3</v>
       </c>
@@ -2204,7 +2204,7 @@
         <v>3021</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>3</v>
       </c>
@@ -2253,7 +2253,7 @@
         <v>3380.3333333333335</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>3</v>
       </c>
@@ -2302,7 +2302,7 @@
         <v>2572.666666666667</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>3</v>
       </c>
@@ -2351,7 +2351,7 @@
         <v>1490.3333333333335</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>4</v>
       </c>
@@ -2400,7 +2400,7 @@
         <v>1803.6666666666667</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>4</v>
       </c>
@@ -2449,7 +2449,7 @@
         <v>1977.6666666666665</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>4</v>
       </c>
@@ -2498,7 +2498,7 @@
         <v>1378</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>4</v>
       </c>
@@ -2547,7 +2547,7 @@
         <v>5017.666666666667</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>4</v>
       </c>
@@ -2596,7 +2596,7 @@
         <v>1277</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>4</v>
       </c>
@@ -2645,7 +2645,7 @@
         <v>3221</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>5</v>
       </c>
@@ -2694,7 +2694,7 @@
         <v>1632</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="8">
         <v>5</v>
       </c>
@@ -2743,7 +2743,7 @@
         <v>2151.3333333333335</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>5</v>
       </c>
@@ -2792,7 +2792,7 @@
         <v>3846.3333333333335</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>5</v>
       </c>
@@ -2841,7 +2841,7 @@
         <v>1744.3333333333335</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>5</v>
       </c>
@@ -2890,7 +2890,7 @@
         <v>1994.6666666666667</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>6</v>
       </c>
@@ -2939,7 +2939,7 @@
         <v>2321</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>6</v>
       </c>
@@ -2988,7 +2988,7 @@
         <v>4768.666666666667</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>6</v>
       </c>
@@ -3037,7 +3037,7 @@
         <v>1928.6666666666665</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>6</v>
       </c>
@@ -3086,7 +3086,7 @@
         <v>2881</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>7</v>
       </c>
@@ -3135,7 +3135,7 @@
         <v>5348.3333333333339</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>7</v>
       </c>
@@ -3184,7 +3184,7 @@
         <v>1118.6666666666667</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>7</v>
       </c>
@@ -3233,7 +3233,7 @@
         <v>3556.666666666667</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>8</v>
       </c>
@@ -3282,7 +3282,7 @@
         <v>4884</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>8</v>
       </c>
@@ -3331,7 +3331,7 @@
         <v>3204</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>9</v>
       </c>
@@ -3380,7 +3380,7 @@
         <v>3091.3333333333335</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>1</v>
       </c>
@@ -3404,8 +3404,11 @@
       <c r="I47">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N47" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>2</v>
       </c>
@@ -3429,8 +3432,11 @@
       <c r="I48">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="N48" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>3</v>
       </c>
@@ -3454,8 +3460,11 @@
       <c r="I49">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="N49" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>4</v>
       </c>
@@ -3479,8 +3488,11 @@
       <c r="I50">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="N50" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>5</v>
       </c>
@@ -3504,8 +3516,11 @@
       <c r="I51">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="N51" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>6</v>
       </c>
@@ -3527,8 +3542,11 @@
       <c r="I52">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="N52" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>7</v>
       </c>
@@ -3550,8 +3568,11 @@
       <c r="I53">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="N53" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>8</v>
       </c>
@@ -3573,8 +3594,11 @@
       <c r="I54">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="N54" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>9</v>
       </c>
@@ -3596,8 +3620,11 @@
       <c r="I55">
         <v>0</v>
       </c>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="N55" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>10</v>
       </c>
@@ -3617,6 +3644,9 @@
         <v>0</v>
       </c>
       <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="N56" s="10">
         <v>0</v>
       </c>
     </row>

--- a/inputData/Parameters.xlsx
+++ b/inputData/Parameters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sillewiberg/Desktop/Skole/Speciale/Master-Thesis-eVTOL-1/inputData/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0218802E-FB40-954D-9A70-48D7F6E8A911}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21CFE9F0-9491-344D-9EBC-B9F3AE46A71C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="1180" windowWidth="28800" windowHeight="15280" activeTab="1" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
   </bookViews>
@@ -509,7 +509,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3CFD079E-5109-8F49-8A19-E09E2BEBBC8C}" name="Table13" displayName="Table13" ref="A1:N56" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6" headerRowCellStyle="Comma" dataCellStyle="Comma">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3CFD079E-5109-8F49-8A19-E09E2BEBBC8C}" name="Table13" displayName="Table13" ref="A1:N56" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6">
   <autoFilter ref="A1:N56" xr:uid="{CEDCB4F7-0752-8449-BE87-89650C1E9E7C}"/>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{0330B38A-598B-B64A-86F4-FA8E25EAC437}" name="From"/>
@@ -521,15 +521,15 @@
     <tableColumn id="7" xr3:uid="{59F6BECD-EB60-114E-826A-884ADDC4EE72}" name="Km fugleflugt"/>
     <tableColumn id="8" xr3:uid="{605D45AE-CBF2-E342-BA16-1B205DDE6C4E}" name="eVTOL flyvetid (min)"/>
     <tableColumn id="9" xr3:uid="{FCFA00C8-AEDC-F54B-AE4D-2360ACC6025E}" name="Hvor meget hurtigere"/>
-    <tableColumn id="10" xr3:uid="{DBB7D64B-F97D-5C46-B464-1DA11C10DF3A}" name="Pris (Bil udgift)" dataDxfId="4" dataCellStyle="Comma"/>
-    <tableColumn id="11" xr3:uid="{CC283087-BB53-D146-A233-2D178D7E3562}" name="Færge (gns. Gælder kun Bornholm)" dataDxfId="3" dataCellStyle="Comma"/>
-    <tableColumn id="12" xr3:uid="{B4DC4D17-2AE3-D34D-926C-7506AC52E6B8}" name="Base" dataDxfId="2" dataCellStyle="Comma">
+    <tableColumn id="10" xr3:uid="{DBB7D64B-F97D-5C46-B464-1DA11C10DF3A}" name="Pris (Bil udgift)" dataDxfId="4"/>
+    <tableColumn id="11" xr3:uid="{CC283087-BB53-D146-A233-2D178D7E3562}" name="Færge (gns. Gælder kun Bornholm)" dataDxfId="3"/>
+    <tableColumn id="12" xr3:uid="{B4DC4D17-2AE3-D34D-926C-7506AC52E6B8}" name="Base" dataDxfId="2">
       <calculatedColumnFormula>$Q$5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{E70B016F-0534-2048-951F-6FD04DC33B7C}" name="Pris (udfra tidsbesparelse)" dataDxfId="1" dataCellStyle="Comma">
+    <tableColumn id="13" xr3:uid="{E70B016F-0534-2048-951F-6FD04DC33B7C}" name="Pris (udfra tidsbesparelse)" dataDxfId="1">
       <calculatedColumnFormula>$Q$4*MAX(F2-G2*$Q$1)*$Q$3</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{67EF8C2F-B7CB-8D4A-8447-692E942D0514}" name="fd_sum" dataDxfId="0" dataCellStyle="Comma">
+    <tableColumn id="14" xr3:uid="{67EF8C2F-B7CB-8D4A-8447-692E942D0514}" name="fd_sum" dataDxfId="0">
       <calculatedColumnFormula>SUM(J2:M2)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3404,6 +3404,9 @@
       <c r="I47">
         <v>0</v>
       </c>
+      <c r="N47" s="10">
+        <v>0</v>
+      </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A48">
@@ -3429,8 +3432,11 @@
       <c r="I48">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="N48" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>3</v>
       </c>
@@ -3454,8 +3460,11 @@
       <c r="I49">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="N49" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>4</v>
       </c>
@@ -3479,8 +3488,11 @@
       <c r="I50">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="N50" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>5</v>
       </c>
@@ -3504,8 +3516,11 @@
       <c r="I51">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="N51" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>6</v>
       </c>
@@ -3527,8 +3542,11 @@
       <c r="I52">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="N52" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>7</v>
       </c>
@@ -3550,8 +3568,11 @@
       <c r="I53">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="N53" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>8</v>
       </c>
@@ -3573,8 +3594,11 @@
       <c r="I54">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="N54" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>9</v>
       </c>
@@ -3596,8 +3620,11 @@
       <c r="I55">
         <v>0</v>
       </c>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="N55" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>10</v>
       </c>
@@ -3617,6 +3644,9 @@
         <v>0</v>
       </c>
       <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="N56" s="10">
         <v>0</v>
       </c>
     </row>

--- a/inputData/Parameters.xlsx
+++ b/inputData/Parameters.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kapta\Documents\DTU\Speciale\GitHubFiles\inputData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5B1B232-F1DE-494C-9564-42A59FF0DB02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E176EE89-673E-4976-B303-40CB55BA9645}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
   </bookViews>
   <sheets>
     <sheet name="Parameters" sheetId="9" r:id="rId1"/>
@@ -251,12 +251,14 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF0A0A0A"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -264,6 +266,7 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -278,6 +281,7 @@
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -855,18 +859,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B15C49E0-A7B4-734A-8962-DC2A879F4079}">
   <dimension ref="A1:D20"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="22.625" customWidth="1"/>
-    <col min="2" max="2" width="10.875" style="4"/>
+    <col min="1" max="1" width="22.58203125" customWidth="1"/>
+    <col min="2" max="2" width="10.83203125" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>20</v>
       </c>
@@ -877,7 +881,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -888,7 +892,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>42</v>
       </c>
@@ -899,7 +903,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -910,7 +914,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -921,7 +925,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -932,7 +936,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -944,7 +948,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
         <v>0</v>
       </c>
@@ -955,7 +959,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
         <v>1</v>
       </c>
@@ -966,7 +970,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
         <v>41</v>
       </c>
@@ -977,7 +981,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
         <v>2</v>
       </c>
@@ -988,7 +992,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
         <v>39</v>
       </c>
@@ -999,7 +1003,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -1011,7 +1015,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
         <v>4</v>
       </c>
@@ -1023,7 +1027,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
         <v>5</v>
       </c>
@@ -1035,7 +1039,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
         <v>6</v>
       </c>
@@ -1046,7 +1050,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
         <v>38</v>
       </c>
@@ -1066,23 +1070,23 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36FC1A80-FC3B-6349-8B7A-4A1A2A7C8FC7}">
   <dimension ref="A1:R56"/>
-  <sheetFormatPr defaultColWidth="10.625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="10.58203125" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" width="17.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="17.125" customWidth="1"/>
-    <col min="5" max="5" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.08203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="17.08203125" customWidth="1"/>
+    <col min="5" max="5" width="12.08203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.5" customWidth="1"/>
-    <col min="7" max="7" width="17.125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.375" customWidth="1"/>
+    <col min="7" max="7" width="17.08203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.33203125" customWidth="1"/>
     <col min="9" max="9" width="21" style="10" customWidth="1"/>
-    <col min="10" max="10" width="13.625" style="10" customWidth="1"/>
-    <col min="11" max="11" width="32.125" style="10" customWidth="1"/>
-    <col min="12" max="12" width="10.625" style="10"/>
+    <col min="10" max="10" width="13.58203125" style="10" customWidth="1"/>
+    <col min="11" max="11" width="32.08203125" style="10" customWidth="1"/>
+    <col min="12" max="12" width="10.58203125" style="10"/>
     <col min="13" max="13" width="27" style="10" customWidth="1"/>
-    <col min="14" max="14" width="10.875" style="10" customWidth="1"/>
+    <col min="14" max="14" width="10.83203125" style="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A1" s="7" t="s">
         <v>33</v>
       </c>
@@ -1132,7 +1136,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1190,7 +1194,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1249,7 +1253,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>1</v>
       </c>
@@ -1304,7 +1308,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>1</v>
       </c>
@@ -1362,7 +1366,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>1</v>
       </c>
@@ -1420,7 +1424,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>1</v>
       </c>
@@ -1469,7 +1473,7 @@
         <v>3195.666666666667</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>1</v>
       </c>
@@ -1518,7 +1522,7 @@
         <v>2678</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>1</v>
       </c>
@@ -1567,7 +1571,7 @@
         <v>2719.333333333333</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>1</v>
       </c>
@@ -1616,7 +1620,7 @@
         <v>1020.6666666666667</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>2</v>
       </c>
@@ -1665,7 +1669,7 @@
         <v>2111.666666666667</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>2</v>
       </c>
@@ -1714,7 +1718,7 @@
         <v>1451</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>2</v>
       </c>
@@ -1763,7 +1767,7 @@
         <v>1304.6666666666667</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>2</v>
       </c>
@@ -1812,7 +1816,7 @@
         <v>1447</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>2</v>
       </c>
@@ -1861,7 +1865,7 @@
         <v>1833.6666666666665</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A16">
         <v>2</v>
       </c>
@@ -1910,7 +1914,7 @@
         <v>4409.3333333333339</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A17">
         <v>2</v>
       </c>
@@ -1959,7 +1963,7 @@
         <v>1245.6666666666667</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A18">
         <v>2</v>
       </c>
@@ -2008,7 +2012,7 @@
         <v>2579</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A19">
         <v>3</v>
       </c>
@@ -2057,7 +2061,7 @@
         <v>2703.666666666667</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A20">
         <v>3</v>
       </c>
@@ -2106,7 +2110,7 @@
         <v>1532.3333333333335</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A21">
         <v>3</v>
       </c>
@@ -2155,7 +2159,7 @@
         <v>2419</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A22">
         <v>3</v>
       </c>
@@ -2204,7 +2208,7 @@
         <v>3021</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A23">
         <v>3</v>
       </c>
@@ -2253,7 +2257,7 @@
         <v>3380.3333333333335</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A24">
         <v>3</v>
       </c>
@@ -2302,7 +2306,7 @@
         <v>2572.666666666667</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A25">
         <v>3</v>
       </c>
@@ -2351,7 +2355,7 @@
         <v>1490.3333333333335</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A26">
         <v>4</v>
       </c>
@@ -2400,7 +2404,7 @@
         <v>1803.6666666666667</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A27">
         <v>4</v>
       </c>
@@ -2449,7 +2453,7 @@
         <v>1977.6666666666665</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A28">
         <v>4</v>
       </c>
@@ -2498,7 +2502,7 @@
         <v>1378</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A29">
         <v>4</v>
       </c>
@@ -2547,7 +2551,7 @@
         <v>5017.666666666667</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A30">
         <v>4</v>
       </c>
@@ -2596,7 +2600,7 @@
         <v>1277</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A31">
         <v>4</v>
       </c>
@@ -2645,7 +2649,7 @@
         <v>3221</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A32">
         <v>5</v>
       </c>
@@ -2694,7 +2698,7 @@
         <v>1632</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A33" s="8">
         <v>5</v>
       </c>
@@ -2743,7 +2747,7 @@
         <v>2151.3333333333335</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A34">
         <v>5</v>
       </c>
@@ -2792,7 +2796,7 @@
         <v>3846.3333333333335</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A35">
         <v>5</v>
       </c>
@@ -2841,7 +2845,7 @@
         <v>1744.3333333333335</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A36">
         <v>5</v>
       </c>
@@ -2890,7 +2894,7 @@
         <v>1994.6666666666667</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A37">
         <v>6</v>
       </c>
@@ -2939,7 +2943,7 @@
         <v>2321</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A38">
         <v>6</v>
       </c>
@@ -2988,7 +2992,7 @@
         <v>4768.666666666667</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A39">
         <v>6</v>
       </c>
@@ -3037,7 +3041,7 @@
         <v>1928.6666666666665</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A40">
         <v>6</v>
       </c>
@@ -3086,7 +3090,7 @@
         <v>2881</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A41">
         <v>7</v>
       </c>
@@ -3135,7 +3139,7 @@
         <v>5348.3333333333339</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A42">
         <v>7</v>
       </c>
@@ -3184,7 +3188,7 @@
         <v>1118.6666666666667</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A43">
         <v>7</v>
       </c>
@@ -3233,7 +3237,7 @@
         <v>3556.666666666667</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A44">
         <v>8</v>
       </c>
@@ -3282,7 +3286,7 @@
         <v>4884</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A45">
         <v>8</v>
       </c>
@@ -3331,7 +3335,7 @@
         <v>3204</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A46">
         <v>9</v>
       </c>
@@ -3380,7 +3384,7 @@
         <v>3091.3333333333335</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A47">
         <v>1</v>
       </c>
@@ -3408,7 +3412,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A48">
         <v>2</v>
       </c>
@@ -3436,7 +3440,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A49">
         <v>3</v>
       </c>
@@ -3464,7 +3468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A50">
         <v>4</v>
       </c>
@@ -3492,7 +3496,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A51">
         <v>5</v>
       </c>
@@ -3520,7 +3524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A52">
         <v>6</v>
       </c>
@@ -3546,7 +3550,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A53">
         <v>7</v>
       </c>
@@ -3572,7 +3576,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A54">
         <v>8</v>
       </c>
@@ -3598,7 +3602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A55">
         <v>9</v>
       </c>
@@ -3624,7 +3628,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A56">
         <v>10</v>
       </c>

--- a/inputData/Parameters.xlsx
+++ b/inputData/Parameters.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kapta\Documents\DTU\Speciale\GitHubFiles\inputData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E176EE89-673E-4976-B303-40CB55BA9645}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FEEFDC1-2528-412E-A048-A5496A0C33BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="28695" windowHeight="15225" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
   </bookViews>
   <sheets>
     <sheet name="Parameters" sheetId="9" r:id="rId1"/>
@@ -239,7 +239,7 @@
     <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -299,6 +299,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -336,7 +342,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -358,6 +364,7 @@
     <xf numFmtId="165" fontId="7" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma 2" xfId="1" xr:uid="{B5076C6D-4567-C74F-A5A8-80AE462FFA5E}"/>
@@ -859,18 +866,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B15C49E0-A7B4-734A-8962-DC2A879F4079}">
   <dimension ref="A1:D20"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.58203125" customWidth="1"/>
-    <col min="2" max="2" width="10.83203125" style="4"/>
+    <col min="1" max="1" width="22.625" customWidth="1"/>
+    <col min="2" max="2" width="10.875" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>20</v>
       </c>
@@ -881,7 +888,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -892,7 +899,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>42</v>
       </c>
@@ -903,7 +910,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -914,18 +921,18 @@
         <v>40</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="4">
+      <c r="B6" s="13">
         <v>30</v>
       </c>
       <c r="D6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -936,7 +943,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -948,7 +955,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>0</v>
       </c>
@@ -959,7 +966,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>1</v>
       </c>
@@ -970,7 +977,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>41</v>
       </c>
@@ -981,7 +988,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>2</v>
       </c>
@@ -992,7 +999,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>39</v>
       </c>
@@ -1003,7 +1010,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -1015,42 +1022,40 @@
         <v>36</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>4</v>
       </c>
-      <c r="B15" s="4">
-        <f>30/B20</f>
+      <c r="B15" s="13">
         <v>30</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>5</v>
       </c>
       <c r="B16" s="4">
-        <f>20/B20</f>
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>6</v>
       </c>
       <c r="B17" s="4">
-        <v>120</v>
+        <v>780</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>38</v>
       </c>
@@ -1063,30 +1068,30 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36FC1A80-FC3B-6349-8B7A-4A1A2A7C8FC7}">
   <dimension ref="A1:R56"/>
-  <sheetFormatPr defaultColWidth="10.58203125" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="10.625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="17.08203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="17.08203125" customWidth="1"/>
-    <col min="5" max="5" width="12.08203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="17.125" customWidth="1"/>
+    <col min="5" max="5" width="12.125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.5" customWidth="1"/>
-    <col min="7" max="7" width="17.08203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.33203125" customWidth="1"/>
+    <col min="7" max="7" width="17.125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.375" customWidth="1"/>
     <col min="9" max="9" width="21" style="10" customWidth="1"/>
-    <col min="10" max="10" width="13.58203125" style="10" customWidth="1"/>
-    <col min="11" max="11" width="32.08203125" style="10" customWidth="1"/>
-    <col min="12" max="12" width="10.58203125" style="10"/>
+    <col min="10" max="10" width="13.625" style="10" customWidth="1"/>
+    <col min="11" max="11" width="32.125" style="10" customWidth="1"/>
+    <col min="12" max="12" width="10.625" style="10"/>
     <col min="13" max="13" width="27" style="10" customWidth="1"/>
-    <col min="14" max="14" width="10.83203125" style="10" customWidth="1"/>
+    <col min="14" max="14" width="10.875" style="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>33</v>
       </c>
@@ -1136,7 +1141,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1194,7 +1199,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1253,7 +1258,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1</v>
       </c>
@@ -1308,7 +1313,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>1</v>
       </c>
@@ -1366,7 +1371,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>1</v>
       </c>
@@ -1424,7 +1429,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>1</v>
       </c>
@@ -1473,7 +1478,7 @@
         <v>3195.666666666667</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>1</v>
       </c>
@@ -1522,7 +1527,7 @@
         <v>2678</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>1</v>
       </c>
@@ -1571,7 +1576,7 @@
         <v>2719.333333333333</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>1</v>
       </c>
@@ -1620,7 +1625,7 @@
         <v>1020.6666666666667</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>2</v>
       </c>
@@ -1669,7 +1674,7 @@
         <v>2111.666666666667</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>2</v>
       </c>
@@ -1718,7 +1723,7 @@
         <v>1451</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>2</v>
       </c>
@@ -1767,7 +1772,7 @@
         <v>1304.6666666666667</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>2</v>
       </c>
@@ -1816,7 +1821,7 @@
         <v>1447</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>2</v>
       </c>
@@ -1865,7 +1870,7 @@
         <v>1833.6666666666665</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>2</v>
       </c>
@@ -1914,7 +1919,7 @@
         <v>4409.3333333333339</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>2</v>
       </c>
@@ -1963,7 +1968,7 @@
         <v>1245.6666666666667</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>2</v>
       </c>
@@ -2012,7 +2017,7 @@
         <v>2579</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>3</v>
       </c>
@@ -2061,7 +2066,7 @@
         <v>2703.666666666667</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>3</v>
       </c>
@@ -2110,7 +2115,7 @@
         <v>1532.3333333333335</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>3</v>
       </c>
@@ -2159,7 +2164,7 @@
         <v>2419</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>3</v>
       </c>
@@ -2208,7 +2213,7 @@
         <v>3021</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>3</v>
       </c>
@@ -2257,7 +2262,7 @@
         <v>3380.3333333333335</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>3</v>
       </c>
@@ -2306,7 +2311,7 @@
         <v>2572.666666666667</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>3</v>
       </c>
@@ -2355,7 +2360,7 @@
         <v>1490.3333333333335</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>4</v>
       </c>
@@ -2404,7 +2409,7 @@
         <v>1803.6666666666667</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>4</v>
       </c>
@@ -2453,7 +2458,7 @@
         <v>1977.6666666666665</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>4</v>
       </c>
@@ -2502,7 +2507,7 @@
         <v>1378</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>4</v>
       </c>
@@ -2551,7 +2556,7 @@
         <v>5017.666666666667</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>4</v>
       </c>
@@ -2600,7 +2605,7 @@
         <v>1277</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>4</v>
       </c>
@@ -2649,7 +2654,7 @@
         <v>3221</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>5</v>
       </c>
@@ -2698,7 +2703,7 @@
         <v>1632</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="8">
         <v>5</v>
       </c>
@@ -2747,7 +2752,7 @@
         <v>2151.3333333333335</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>5</v>
       </c>
@@ -2796,7 +2801,7 @@
         <v>3846.3333333333335</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>5</v>
       </c>
@@ -2845,7 +2850,7 @@
         <v>1744.3333333333335</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>5</v>
       </c>
@@ -2894,7 +2899,7 @@
         <v>1994.6666666666667</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>6</v>
       </c>
@@ -2943,7 +2948,7 @@
         <v>2321</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>6</v>
       </c>
@@ -2992,7 +2997,7 @@
         <v>4768.666666666667</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>6</v>
       </c>
@@ -3041,7 +3046,7 @@
         <v>1928.6666666666665</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>6</v>
       </c>
@@ -3090,7 +3095,7 @@
         <v>2881</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>7</v>
       </c>
@@ -3139,7 +3144,7 @@
         <v>5348.3333333333339</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>7</v>
       </c>
@@ -3188,7 +3193,7 @@
         <v>1118.6666666666667</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>7</v>
       </c>
@@ -3237,7 +3242,7 @@
         <v>3556.666666666667</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>8</v>
       </c>
@@ -3286,7 +3291,7 @@
         <v>4884</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>8</v>
       </c>
@@ -3335,7 +3340,7 @@
         <v>3204</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>9</v>
       </c>
@@ -3384,7 +3389,7 @@
         <v>3091.3333333333335</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>1</v>
       </c>
@@ -3412,7 +3417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>2</v>
       </c>
@@ -3440,7 +3445,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>3</v>
       </c>
@@ -3468,7 +3473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>4</v>
       </c>
@@ -3496,7 +3501,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>5</v>
       </c>
@@ -3524,7 +3529,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>6</v>
       </c>
@@ -3550,7 +3555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>7</v>
       </c>
@@ -3576,7 +3581,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>8</v>
       </c>
@@ -3602,7 +3607,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>9</v>
       </c>
@@ -3628,7 +3633,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>10</v>
       </c>

--- a/inputData/Parameters.xlsx
+++ b/inputData/Parameters.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kapta\Documents\DTU\Speciale\GitHubFiles\inputData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FEEFDC1-2528-412E-A048-A5496A0C33BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B63FF40-87B6-411A-8870-D5C9EA36E7E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="28695" windowHeight="15225" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
+    <workbookView xWindow="10" yWindow="10" windowWidth="19180" windowHeight="11260" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
   </bookViews>
   <sheets>
     <sheet name="Parameters" sheetId="9" r:id="rId1"/>
@@ -168,9 +168,6 @@
     <t>opening_cost</t>
   </si>
   <si>
-    <t>cost of opening a vertiport</t>
-  </si>
-  <si>
     <t>minuts/unit</t>
   </si>
   <si>
@@ -229,6 +226,9 @@
   </si>
   <si>
     <t>Km bil pris</t>
+  </si>
+  <si>
+    <t>cost of opening a plane</t>
   </si>
 </sst>
 </file>
@@ -866,18 +866,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B15C49E0-A7B4-734A-8962-DC2A879F4079}">
   <dimension ref="A1:D20"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="22.625" customWidth="1"/>
-    <col min="2" max="2" width="10.875" style="4"/>
+    <col min="1" max="1" width="22.58203125" customWidth="1"/>
+    <col min="2" max="2" width="10.83203125" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>20</v>
       </c>
@@ -888,7 +888,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -899,7 +899,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>42</v>
       </c>
@@ -907,10 +907,10 @@
         <v>400</v>
       </c>
       <c r="D4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -921,7 +921,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -932,7 +932,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -943,7 +943,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -955,7 +955,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
         <v>0</v>
       </c>
@@ -966,7 +966,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
         <v>1</v>
       </c>
@@ -977,7 +977,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
         <v>41</v>
       </c>
@@ -988,7 +988,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
         <v>2</v>
       </c>
@@ -999,7 +999,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
         <v>39</v>
       </c>
@@ -1007,10 +1007,10 @@
         <v>20</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -1022,7 +1022,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
         <v>4</v>
       </c>
@@ -1033,29 +1033,29 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
         <v>5</v>
       </c>
       <c r="B16" s="4">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
         <v>6</v>
       </c>
       <c r="B17" s="4">
-        <v>780</v>
+        <v>120</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
         <v>38</v>
       </c>
@@ -1063,7 +1063,7 @@
         <v>1</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -1075,23 +1075,23 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36FC1A80-FC3B-6349-8B7A-4A1A2A7C8FC7}">
   <dimension ref="A1:R56"/>
-  <sheetFormatPr defaultColWidth="10.625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="10.58203125" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" width="17.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="17.125" customWidth="1"/>
-    <col min="5" max="5" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.08203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="17.08203125" customWidth="1"/>
+    <col min="5" max="5" width="12.08203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.5" customWidth="1"/>
-    <col min="7" max="7" width="17.125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.375" customWidth="1"/>
+    <col min="7" max="7" width="17.08203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.33203125" customWidth="1"/>
     <col min="9" max="9" width="21" style="10" customWidth="1"/>
-    <col min="10" max="10" width="13.625" style="10" customWidth="1"/>
-    <col min="11" max="11" width="32.125" style="10" customWidth="1"/>
-    <col min="12" max="12" width="10.625" style="10"/>
+    <col min="10" max="10" width="13.58203125" style="10" customWidth="1"/>
+    <col min="11" max="11" width="32.08203125" style="10" customWidth="1"/>
+    <col min="12" max="12" width="10.58203125" style="10"/>
     <col min="13" max="13" width="27" style="10" customWidth="1"/>
-    <col min="14" max="14" width="10.875" style="10" customWidth="1"/>
+    <col min="14" max="14" width="10.83203125" style="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A1" s="7" t="s">
         <v>33</v>
       </c>
@@ -1099,13 +1099,13 @@
         <v>34</v>
       </c>
       <c r="C1" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D1" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="D1" s="5" t="s">
-        <v>46</v>
-      </c>
       <c r="E1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F1" t="s">
         <v>22</v>
@@ -1120,16 +1120,16 @@
         <v>25</v>
       </c>
       <c r="J1" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="K1" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="K1" s="11" t="s">
+      <c r="L1" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="L1" s="10" t="s">
+      <c r="M1" s="12" t="s">
         <v>61</v>
-      </c>
-      <c r="M1" s="12" t="s">
-        <v>62</v>
       </c>
       <c r="N1" s="10" t="s">
         <v>35</v>
@@ -1141,7 +1141,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1149,10 +1149,10 @@
         <v>2</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>47</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>48</v>
       </c>
       <c r="E2">
         <v>267</v>
@@ -1199,7 +1199,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1207,10 +1207,10 @@
         <v>3</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E3">
         <v>100</v>
@@ -1258,7 +1258,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>1</v>
       </c>
@@ -1266,10 +1266,10 @@
         <v>4</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E4">
         <v>347</v>
@@ -1313,7 +1313,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>1</v>
       </c>
@@ -1321,10 +1321,10 @@
         <v>5</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E5">
         <v>177</v>
@@ -1371,7 +1371,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>1</v>
       </c>
@@ -1379,10 +1379,10 @@
         <v>6</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E6">
         <v>325</v>
@@ -1420,7 +1420,7 @@
         <v>2579</v>
       </c>
       <c r="P6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q6">
         <v>3</v>
@@ -1429,7 +1429,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>1</v>
       </c>
@@ -1437,10 +1437,10 @@
         <v>7</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E7">
         <v>415</v>
@@ -1478,7 +1478,7 @@
         <v>3195.666666666667</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>1</v>
       </c>
@@ -1486,10 +1486,10 @@
         <v>8</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E8">
         <v>160</v>
@@ -1527,7 +1527,7 @@
         <v>2678</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>1</v>
       </c>
@@ -1535,10 +1535,10 @@
         <v>9</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E9">
         <v>326</v>
@@ -1576,7 +1576,7 @@
         <v>2719.333333333333</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>1</v>
       </c>
@@ -1584,10 +1584,10 @@
         <v>10</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E10">
         <v>70</v>
@@ -1625,7 +1625,7 @@
         <v>1020.6666666666667</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>2</v>
       </c>
@@ -1633,10 +1633,10 @@
         <v>3</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>48</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>49</v>
       </c>
       <c r="E11">
         <v>211</v>
@@ -1674,7 +1674,7 @@
         <v>2111.666666666667</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>2</v>
       </c>
@@ -1682,10 +1682,10 @@
         <v>4</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E12">
         <v>137</v>
@@ -1723,7 +1723,7 @@
         <v>1451</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>2</v>
       </c>
@@ -1731,10 +1731,10 @@
         <v>5</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E13">
         <v>106</v>
@@ -1772,7 +1772,7 @@
         <v>1304.6666666666667</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>2</v>
       </c>
@@ -1780,10 +1780,10 @@
         <v>6</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E14">
         <v>137</v>
@@ -1821,7 +1821,7 @@
         <v>1447</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>2</v>
       </c>
@@ -1829,10 +1829,10 @@
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E15">
         <v>205</v>
@@ -1870,7 +1870,7 @@
         <v>1833.6666666666665</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A16">
         <v>2</v>
       </c>
@@ -1878,10 +1878,10 @@
         <v>8</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E16">
         <v>426</v>
@@ -1919,7 +1919,7 @@
         <v>4409.3333333333339</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A17">
         <v>2</v>
       </c>
@@ -1927,10 +1927,10 @@
         <v>9</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E17">
         <v>89</v>
@@ -1968,7 +1968,7 @@
         <v>1245.6666666666667</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A18">
         <v>2</v>
       </c>
@@ -1976,10 +1976,10 @@
         <v>10</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E18">
         <v>305</v>
@@ -2017,7 +2017,7 @@
         <v>2579</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A19">
         <v>3</v>
       </c>
@@ -2025,10 +2025,10 @@
         <v>4</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D19" s="1" t="s">
         <v>49</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>50</v>
       </c>
       <c r="E19">
         <v>291</v>
@@ -2066,7 +2066,7 @@
         <v>2703.666666666667</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A20">
         <v>3</v>
       </c>
@@ -2074,10 +2074,10 @@
         <v>5</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E20">
         <v>121</v>
@@ -2115,7 +2115,7 @@
         <v>1532.3333333333335</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A21">
         <v>3</v>
       </c>
@@ -2123,10 +2123,10 @@
         <v>6</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E21">
         <v>269</v>
@@ -2164,7 +2164,7 @@
         <v>2419</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A22">
         <v>3</v>
       </c>
@@ -2172,10 +2172,10 @@
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E22">
         <v>359</v>
@@ -2213,7 +2213,7 @@
         <v>3021</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A23">
         <v>3</v>
       </c>
@@ -2221,10 +2221,10 @@
         <v>8</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E23">
         <v>259</v>
@@ -2262,7 +2262,7 @@
         <v>3380.3333333333335</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A24">
         <v>3</v>
       </c>
@@ -2270,10 +2270,10 @@
         <v>9</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E24">
         <v>270</v>
@@ -2311,7 +2311,7 @@
         <v>2572.666666666667</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A25">
         <v>3</v>
       </c>
@@ -2319,10 +2319,10 @@
         <v>10</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E25">
         <v>131</v>
@@ -2360,7 +2360,7 @@
         <v>1490.3333333333335</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A26">
         <v>4</v>
       </c>
@@ -2368,10 +2368,10 @@
         <v>5</v>
       </c>
       <c r="C26" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D26" s="1" t="s">
         <v>50</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>51</v>
       </c>
       <c r="E26">
         <v>187</v>
@@ -2409,7 +2409,7 @@
         <v>1803.6666666666667</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A27">
         <v>4</v>
       </c>
@@ -2417,10 +2417,10 @@
         <v>6</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E27">
         <v>233</v>
@@ -2458,7 +2458,7 @@
         <v>1977.6666666666665</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A28">
         <v>4</v>
       </c>
@@ -2466,10 +2466,10 @@
         <v>7</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E28">
         <v>126</v>
@@ -2507,7 +2507,7 @@
         <v>1378</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A29">
         <v>4</v>
       </c>
@@ -2515,10 +2515,10 @@
         <v>8</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E29">
         <v>507</v>
@@ -2556,7 +2556,7 @@
         <v>5017.666666666667</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A30">
         <v>4</v>
       </c>
@@ -2564,10 +2564,10 @@
         <v>9</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E30">
         <v>99</v>
@@ -2605,7 +2605,7 @@
         <v>1277</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A31">
         <v>4</v>
       </c>
@@ -2613,10 +2613,10 @@
         <v>10</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E31">
         <v>387</v>
@@ -2654,7 +2654,7 @@
         <v>3221</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A32">
         <v>5</v>
       </c>
@@ -2662,10 +2662,10 @@
         <v>6</v>
       </c>
       <c r="C32" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D32" s="1" t="s">
         <v>51</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>52</v>
       </c>
       <c r="E32">
         <v>164</v>
@@ -2703,7 +2703,7 @@
         <v>1632</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A33" s="8">
         <v>5</v>
       </c>
@@ -2711,10 +2711,10 @@
         <v>7</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E33">
         <v>254</v>
@@ -2752,7 +2752,7 @@
         <v>2151.3333333333335</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A34">
         <v>5</v>
       </c>
@@ -2760,10 +2760,10 @@
         <v>8</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E34">
         <v>337</v>
@@ -2801,7 +2801,7 @@
         <v>3846.3333333333335</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A35">
         <v>5</v>
       </c>
@@ -2809,10 +2809,10 @@
         <v>9</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E35">
         <v>165</v>
@@ -2850,7 +2850,7 @@
         <v>1744.3333333333335</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A36">
         <v>5</v>
       </c>
@@ -2858,10 +2858,10 @@
         <v>10</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E36">
         <v>216</v>
@@ -2899,7 +2899,7 @@
         <v>1994.6666666666667</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A37">
         <v>6</v>
       </c>
@@ -2907,10 +2907,10 @@
         <v>7</v>
       </c>
       <c r="C37" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D37" s="9" t="s">
         <v>52</v>
-      </c>
-      <c r="D37" s="9" t="s">
-        <v>53</v>
       </c>
       <c r="E37">
         <v>299</v>
@@ -2948,7 +2948,7 @@
         <v>2321</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A38">
         <v>6</v>
       </c>
@@ -2956,10 +2956,10 @@
         <v>8</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E38">
         <v>484</v>
@@ -2997,7 +2997,7 @@
         <v>4768.666666666667</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A39">
         <v>6</v>
       </c>
@@ -3005,10 +3005,10 @@
         <v>9</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E39">
         <v>210</v>
@@ -3046,7 +3046,7 @@
         <v>1928.6666666666665</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A40">
         <v>6</v>
       </c>
@@ -3054,10 +3054,10 @@
         <v>10</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E40">
         <v>363</v>
@@ -3095,7 +3095,7 @@
         <v>2881</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A41">
         <v>7</v>
       </c>
@@ -3103,10 +3103,10 @@
         <v>8</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E41">
         <v>575</v>
@@ -3144,7 +3144,7 @@
         <v>5348.3333333333339</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A42">
         <v>7</v>
       </c>
@@ -3152,10 +3152,10 @@
         <v>9</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E42">
         <v>84</v>
@@ -3193,7 +3193,7 @@
         <v>1118.6666666666667</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A43">
         <v>7</v>
       </c>
@@ -3201,10 +3201,10 @@
         <v>10</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E43">
         <v>454</v>
@@ -3242,7 +3242,7 @@
         <v>3556.666666666667</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A44">
         <v>8</v>
       </c>
@@ -3250,10 +3250,10 @@
         <v>9</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E44">
         <v>486</v>
@@ -3291,7 +3291,7 @@
         <v>4884</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A45">
         <v>8</v>
       </c>
@@ -3299,10 +3299,10 @@
         <v>10</v>
       </c>
       <c r="C45" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D45" s="1" t="s">
         <v>56</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>57</v>
       </c>
       <c r="E45">
         <v>230</v>
@@ -3340,7 +3340,7 @@
         <v>3204</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A46">
         <v>9</v>
       </c>
@@ -3348,10 +3348,10 @@
         <v>10</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E46">
         <v>366</v>
@@ -3389,7 +3389,7 @@
         <v>3091.3333333333335</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A47">
         <v>1</v>
       </c>
@@ -3417,7 +3417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A48">
         <v>2</v>
       </c>
@@ -3445,7 +3445,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A49">
         <v>3</v>
       </c>
@@ -3473,7 +3473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A50">
         <v>4</v>
       </c>
@@ -3501,7 +3501,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A51">
         <v>5</v>
       </c>
@@ -3529,7 +3529,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A52">
         <v>6</v>
       </c>
@@ -3555,7 +3555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A53">
         <v>7</v>
       </c>
@@ -3581,7 +3581,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A54">
         <v>8</v>
       </c>
@@ -3607,7 +3607,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A55">
         <v>9</v>
       </c>
@@ -3633,7 +3633,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A56">
         <v>10</v>
       </c>

--- a/inputData/Parameters.xlsx
+++ b/inputData/Parameters.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kapta\Documents\DTU\Speciale\GitHubFiles\inputData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B63FF40-87B6-411A-8870-D5C9EA36E7E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E26374B0-B803-46AA-9BAD-2EB0F92993D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10" yWindow="10" windowWidth="19180" windowHeight="11260" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
   </bookViews>
   <sheets>
     <sheet name="Parameters" sheetId="9" r:id="rId1"/>
@@ -904,7 +904,7 @@
         <v>42</v>
       </c>
       <c r="B4" s="4">
-        <v>400</v>
+        <v>800</v>
       </c>
       <c r="D4" t="s">
         <v>63</v>
@@ -926,7 +926,7 @@
         <v>17</v>
       </c>
       <c r="B6" s="13">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="D6" t="s">
         <v>9</v>
@@ -1027,7 +1027,7 @@
         <v>4</v>
       </c>
       <c r="B15" s="13">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>12</v>
@@ -1049,7 +1049,7 @@
         <v>6</v>
       </c>
       <c r="B17" s="4">
-        <v>120</v>
+        <v>780</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>14</v>

--- a/inputData/Parameters.xlsx
+++ b/inputData/Parameters.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10621"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kapta\Documents\DTU\Speciale\GitHubFiles\inputData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sillewiberg/Desktop/Skole/Speciale/Master-Thesis-eVTOL-1/inputData/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E176EE89-673E-4976-B303-40CB55BA9645}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0B7FF55-156A-354B-BC75-FD9D1E8C7CD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="19420" windowHeight="11500" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
   </bookViews>
   <sheets>
     <sheet name="Parameters" sheetId="9" r:id="rId1"/>
@@ -859,18 +859,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B15C49E0-A7B4-734A-8962-DC2A879F4079}">
   <dimension ref="A1:D20"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="22.58203125" customWidth="1"/>
+    <col min="1" max="1" width="22.5" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>20</v>
       </c>
@@ -881,7 +881,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -892,7 +892,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>42</v>
       </c>
@@ -903,7 +903,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -914,7 +914,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -925,7 +925,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -936,7 +936,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -948,7 +948,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>0</v>
       </c>
@@ -959,7 +959,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>1</v>
       </c>
@@ -970,7 +970,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>41</v>
       </c>
@@ -981,7 +981,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>2</v>
       </c>
@@ -992,7 +992,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>39</v>
       </c>
@@ -1003,7 +1003,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -1015,7 +1015,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>4</v>
       </c>
@@ -1027,7 +1027,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>5</v>
       </c>
@@ -1039,18 +1039,18 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>6</v>
       </c>
       <c r="B17" s="4">
-        <v>120</v>
+        <v>780</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>38</v>
       </c>
@@ -1070,23 +1070,23 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36FC1A80-FC3B-6349-8B7A-4A1A2A7C8FC7}">
   <dimension ref="A1:R56"/>
-  <sheetFormatPr defaultColWidth="10.58203125" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.5" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="17.08203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="17.08203125" customWidth="1"/>
-    <col min="5" max="5" width="12.08203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="17" customWidth="1"/>
+    <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.5" customWidth="1"/>
-    <col min="7" max="7" width="17.08203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="19.33203125" customWidth="1"/>
     <col min="9" max="9" width="21" style="10" customWidth="1"/>
-    <col min="10" max="10" width="13.58203125" style="10" customWidth="1"/>
-    <col min="11" max="11" width="32.08203125" style="10" customWidth="1"/>
-    <col min="12" max="12" width="10.58203125" style="10"/>
+    <col min="10" max="10" width="13.5" style="10" customWidth="1"/>
+    <col min="11" max="11" width="32" style="10" customWidth="1"/>
+    <col min="12" max="12" width="10.5" style="10"/>
     <col min="13" max="13" width="27" style="10" customWidth="1"/>
     <col min="14" max="14" width="10.83203125" style="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:18" ht="17" x14ac:dyDescent="0.2">
       <c r="A1" s="7" t="s">
         <v>33</v>
       </c>
@@ -1136,7 +1136,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1194,7 +1194,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1253,7 +1253,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>1</v>
       </c>
@@ -1308,7 +1308,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>1</v>
       </c>
@@ -1366,7 +1366,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>1</v>
       </c>
@@ -1424,7 +1424,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>1</v>
       </c>
@@ -1473,7 +1473,7 @@
         <v>3195.666666666667</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>1</v>
       </c>
@@ -1522,7 +1522,7 @@
         <v>2678</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>1</v>
       </c>
@@ -1571,7 +1571,7 @@
         <v>2719.333333333333</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>1</v>
       </c>
@@ -1620,7 +1620,7 @@
         <v>1020.6666666666667</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>2</v>
       </c>
@@ -1669,7 +1669,7 @@
         <v>2111.666666666667</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>2</v>
       </c>
@@ -1718,7 +1718,7 @@
         <v>1451</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>2</v>
       </c>
@@ -1767,7 +1767,7 @@
         <v>1304.6666666666667</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>2</v>
       </c>
@@ -1816,7 +1816,7 @@
         <v>1447</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>2</v>
       </c>
@@ -1865,7 +1865,7 @@
         <v>1833.6666666666665</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>2</v>
       </c>
@@ -1914,7 +1914,7 @@
         <v>4409.3333333333339</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>2</v>
       </c>
@@ -1963,7 +1963,7 @@
         <v>1245.6666666666667</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>2</v>
       </c>
@@ -2012,7 +2012,7 @@
         <v>2579</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>3</v>
       </c>
@@ -2061,7 +2061,7 @@
         <v>2703.666666666667</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>3</v>
       </c>
@@ -2110,7 +2110,7 @@
         <v>1532.3333333333335</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>3</v>
       </c>
@@ -2159,7 +2159,7 @@
         <v>2419</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>3</v>
       </c>
@@ -2208,7 +2208,7 @@
         <v>3021</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>3</v>
       </c>
@@ -2257,7 +2257,7 @@
         <v>3380.3333333333335</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>3</v>
       </c>
@@ -2306,7 +2306,7 @@
         <v>2572.666666666667</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>3</v>
       </c>
@@ -2355,7 +2355,7 @@
         <v>1490.3333333333335</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>4</v>
       </c>
@@ -2404,7 +2404,7 @@
         <v>1803.6666666666667</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>4</v>
       </c>
@@ -2453,7 +2453,7 @@
         <v>1977.6666666666665</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>4</v>
       </c>
@@ -2502,7 +2502,7 @@
         <v>1378</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>4</v>
       </c>
@@ -2551,7 +2551,7 @@
         <v>5017.666666666667</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>4</v>
       </c>
@@ -2600,7 +2600,7 @@
         <v>1277</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>4</v>
       </c>
@@ -2649,7 +2649,7 @@
         <v>3221</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>5</v>
       </c>
@@ -2698,7 +2698,7 @@
         <v>1632</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A33" s="8">
         <v>5</v>
       </c>
@@ -2747,7 +2747,7 @@
         <v>2151.3333333333335</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>5</v>
       </c>
@@ -2796,7 +2796,7 @@
         <v>3846.3333333333335</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>5</v>
       </c>
@@ -2845,7 +2845,7 @@
         <v>1744.3333333333335</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>5</v>
       </c>
@@ -2894,7 +2894,7 @@
         <v>1994.6666666666667</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>6</v>
       </c>
@@ -2943,7 +2943,7 @@
         <v>2321</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>6</v>
       </c>
@@ -2992,7 +2992,7 @@
         <v>4768.666666666667</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>6</v>
       </c>
@@ -3041,7 +3041,7 @@
         <v>1928.6666666666665</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>6</v>
       </c>
@@ -3090,7 +3090,7 @@
         <v>2881</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>7</v>
       </c>
@@ -3139,7 +3139,7 @@
         <v>5348.3333333333339</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>7</v>
       </c>
@@ -3188,7 +3188,7 @@
         <v>1118.6666666666667</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>7</v>
       </c>
@@ -3237,7 +3237,7 @@
         <v>3556.666666666667</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>8</v>
       </c>
@@ -3286,7 +3286,7 @@
         <v>4884</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>8</v>
       </c>
@@ -3335,7 +3335,7 @@
         <v>3204</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>9</v>
       </c>
@@ -3384,7 +3384,7 @@
         <v>3091.3333333333335</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>1</v>
       </c>
@@ -3412,7 +3412,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>2</v>
       </c>
@@ -3440,7 +3440,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>3</v>
       </c>
@@ -3468,7 +3468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>4</v>
       </c>
@@ -3496,7 +3496,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>5</v>
       </c>
@@ -3524,7 +3524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>6</v>
       </c>
@@ -3550,7 +3550,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>7</v>
       </c>
@@ -3576,7 +3576,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>8</v>
       </c>
@@ -3602,7 +3602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>9</v>
       </c>
@@ -3628,7 +3628,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>10</v>
       </c>

--- a/inputData/Parameters.xlsx
+++ b/inputData/Parameters.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sillewiberg/Desktop/Skole/Speciale/Master-Thesis-eVTOL-1/inputData/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0B7FF55-156A-354B-BC75-FD9D1E8C7CD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{790B5307-2403-C641-8776-35D3AA6BEDBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="19420" windowHeight="11500" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="19420" windowHeight="15100" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
   </bookViews>
   <sheets>
     <sheet name="Parameters" sheetId="9" r:id="rId1"/>
@@ -1044,7 +1044,7 @@
         <v>6</v>
       </c>
       <c r="B17" s="4">
-        <v>780</v>
+        <v>120</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>14</v>

--- a/inputData/Parameters.xlsx
+++ b/inputData/Parameters.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10621"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kapta\Documents\DTU\Speciale\GitHubFiles\inputData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/asbb/Desktop/Speciale/Master-Thesis-eVTOL/inputData/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E26374B0-B803-46AA-9BAD-2EB0F92993D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7674647F-1577-C742-B86E-64C2C43BD08B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
   </bookViews>
   <sheets>
     <sheet name="Parameters" sheetId="9" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="110">
   <si>
     <t>cap_u</t>
   </si>
@@ -168,6 +168,9 @@
     <t>opening_cost</t>
   </si>
   <si>
+    <t>cost of opening a vertiport</t>
+  </si>
+  <si>
     <t>minuts/unit</t>
   </si>
   <si>
@@ -228,7 +231,142 @@
     <t>Km bil pris</t>
   </si>
   <si>
-    <t>cost of opening a plane</t>
+    <t>Copenhagen / Billund</t>
+  </si>
+  <si>
+    <t>Copenhagen / Kalundborg</t>
+  </si>
+  <si>
+    <t>Copenhagen / Aarhus</t>
+  </si>
+  <si>
+    <t>Copenhagen / Odense</t>
+  </si>
+  <si>
+    <t>Copenhagen / Sønderborg</t>
+  </si>
+  <si>
+    <t>Copenhagen / Aalborg</t>
+  </si>
+  <si>
+    <t>Copenhagen / Bornholm</t>
+  </si>
+  <si>
+    <t>Copenhagen / Viborg</t>
+  </si>
+  <si>
+    <t>Copenhagen / Helsingør</t>
+  </si>
+  <si>
+    <t>Billund / Kalundborg</t>
+  </si>
+  <si>
+    <t>Billund / Aarhus</t>
+  </si>
+  <si>
+    <t>Billund / Odense</t>
+  </si>
+  <si>
+    <t>Billund / Sønderborg</t>
+  </si>
+  <si>
+    <t>Billund / Aalborg</t>
+  </si>
+  <si>
+    <t>Billund / Bornholm</t>
+  </si>
+  <si>
+    <t>Billund / Viborg</t>
+  </si>
+  <si>
+    <t>Billund / Helsingør</t>
+  </si>
+  <si>
+    <t>Kalundborg / Aarhus</t>
+  </si>
+  <si>
+    <t>Kalundborg / Odense</t>
+  </si>
+  <si>
+    <t>Kalundborg / Sønderborg</t>
+  </si>
+  <si>
+    <t>Kalundborg / Aalborg</t>
+  </si>
+  <si>
+    <t>Kalundborg / Bornholm</t>
+  </si>
+  <si>
+    <t>Kalundborg / Viborg</t>
+  </si>
+  <si>
+    <t>Kalundborg / Helsingør</t>
+  </si>
+  <si>
+    <t>Aarhus / Odense</t>
+  </si>
+  <si>
+    <t>Aarhus / Sønderborg</t>
+  </si>
+  <si>
+    <t>Aarhus / Aalborg</t>
+  </si>
+  <si>
+    <t>Aarhus / Bornholm</t>
+  </si>
+  <si>
+    <t>Aarhus / Viborg</t>
+  </si>
+  <si>
+    <t>Aarhus / Helsingør</t>
+  </si>
+  <si>
+    <t>Odense / Sønderborg</t>
+  </si>
+  <si>
+    <t>Odense / Aalborg</t>
+  </si>
+  <si>
+    <t>Odense / Bornholm</t>
+  </si>
+  <si>
+    <t>Odense / Viborg</t>
+  </si>
+  <si>
+    <t>Odense / Helsingør</t>
+  </si>
+  <si>
+    <t>Sønderborg / Aalborg</t>
+  </si>
+  <si>
+    <t>Sønderborg / Bornholm</t>
+  </si>
+  <si>
+    <t>Sønderborg / Viborg</t>
+  </si>
+  <si>
+    <t>Sønderborg / Helsingør</t>
+  </si>
+  <si>
+    <t>Aalborg / Bornholm</t>
+  </si>
+  <si>
+    <t>Aalborg / Viborg</t>
+  </si>
+  <si>
+    <t>Aalborg / Helsingør</t>
+  </si>
+  <si>
+    <t>Bornholm / Viborg</t>
+  </si>
+  <si>
+    <t>Bornholm / Helsingør</t>
+  </si>
+  <si>
+    <t>Viborg / Helsingør</t>
+  </si>
+  <si>
+    <t>tot</t>
   </si>
 </sst>
 </file>
@@ -236,10 +374,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -299,12 +437,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="12"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -340,9 +472,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -357,14 +489,15 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma 2" xfId="1" xr:uid="{B5076C6D-4567-C74F-A5A8-80AE462FFA5E}"/>
@@ -388,7 +521,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+      <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
     </dxf>
     <dxf>
       <font>
@@ -407,7 +540,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+      <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
     </dxf>
     <dxf>
       <font>
@@ -426,7 +559,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+      <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
     </dxf>
     <dxf>
       <font>
@@ -445,7 +578,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+      <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
     </dxf>
     <dxf>
       <font>
@@ -464,7 +597,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+      <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -504,10 +637,22 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+      <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFBBCCE4"/>
+      <color rgb="FFFAECEC"/>
+      <color rgb="FF6B2424"/>
+      <color rgb="FFEDA7E1"/>
+      <color rgb="FFCE6E6E"/>
+      <color rgb="FFFF2500"/>
+      <color rgb="FFD27677"/>
+      <color rgb="FFBE5857"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -519,9 +664,3419 @@
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="3200" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="2800" b="1">
+                <a:latin typeface="Georgia" panose="02040502050405020303" pitchFamily="18" charset="0"/>
+                <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+              </a:rPr>
+              <a:t>Value-Based</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" sz="2800" b="1" baseline="0">
+                <a:latin typeface="Georgia" panose="02040502050405020303" pitchFamily="18" charset="0"/>
+                <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+              </a:rPr>
+              <a:t> Fare Structure</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US" sz="2800" b="1">
+              <a:latin typeface="Georgia" panose="02040502050405020303" pitchFamily="18" charset="0"/>
+              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            </a:endParaRPr>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.22996186657990692"/>
+          <c:y val="3.6589227962857615E-2"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="3200" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.21404582874218667"/>
+          <c:y val="0.19850819667408129"/>
+          <c:w val="0.7704272495741169"/>
+          <c:h val="0.64362778981782287"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Base fee</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Prices!$A$2:$A$10</c:f>
+              <c:strCache>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>Copenhagen / Billund</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Copenhagen / Kalundborg</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Copenhagen / Aarhus</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Copenhagen / Odense</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Copenhagen / Sønderborg</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Copenhagen / Aalborg</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Copenhagen / Bornholm</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Copenhagen / Viborg</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Copenhagen / Helsingør</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Prices!$M$2:$M$10</c:f>
+              <c:numCache>
+                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"??_);_(@_)</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>500</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-A3F7-C943-93D6-EBF754D8830F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Car Travel Cost</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Prices!$A$2:$A$10</c:f>
+              <c:strCache>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>Copenhagen / Billund</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Copenhagen / Kalundborg</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Copenhagen / Aarhus</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Copenhagen / Odense</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Copenhagen / Sønderborg</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Copenhagen / Aalborg</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Copenhagen / Bornholm</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Copenhagen / Viborg</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Copenhagen / Helsingør</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Prices!$K$2:$K$10</c:f>
+              <c:numCache>
+                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"??_);_(@_)</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>801</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>300</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1041</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>531</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>975</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1245</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>480</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>978</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>210</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-A3F7-C943-93D6-EBF754D8830F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>Time Saving Value</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="CE6E6E"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="6B2424"/>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Prices!$A$2:$A$10</c:f>
+              <c:strCache>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>Copenhagen / Billund</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Copenhagen / Kalundborg</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Copenhagen / Aarhus</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Copenhagen / Odense</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Copenhagen / Sønderborg</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Copenhagen / Aalborg</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Copenhagen / Bornholm</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Copenhagen / Viborg</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Copenhagen / Helsingør</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Prices!$N$2:$N$10</c:f>
+              <c:numCache>
+                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"??_);_(@_)</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>941.33333333333326</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>429.33333333333337</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1324</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>644</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1104</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1450.6666666666667</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1448</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1241.3333333333333</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>310.66666666666669</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-A3F7-C943-93D6-EBF754D8830F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:v>Ferry Surcharge</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Prices!$A$2:$A$10</c:f>
+              <c:strCache>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>Copenhagen / Billund</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Copenhagen / Kalundborg</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Copenhagen / Aarhus</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Copenhagen / Odense</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Copenhagen / Sønderborg</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Copenhagen / Aalborg</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Copenhagen / Bornholm</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Copenhagen / Viborg</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Copenhagen / Helsingør</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Prices!$L$2:$L$10</c:f>
+              <c:numCache>
+                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"??_);_(@_)</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>250</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-A3F7-C943-93D6-EBF754D8830F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="75"/>
+        <c:overlap val="100"/>
+        <c:axId val="1393023039"/>
+        <c:axId val="1393024751"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1393023039"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Georgia" panose="02040502050405020303" pitchFamily="18" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1393024751"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1393024751"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="[$DKK]\ #,##0" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Georgia" panose="02040502050405020303" pitchFamily="18" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1393023039"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="4.8522721099798403E-2"/>
+          <c:y val="0.13701258594091603"/>
+          <c:w val="0.89999998828986194"/>
+          <c:h val="3.8565073758588253E-2"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Georgia" panose="02040502050405020303" pitchFamily="18" charset="0"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr rot="-5400000" vert="horz"/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="1">
+                <a:latin typeface="Georgia" panose="02040502050405020303" pitchFamily="18" charset="0"/>
+                <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+              </a:rPr>
+              <a:t>Value-Based</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="1" baseline="0">
+                <a:latin typeface="Georgia" panose="02040502050405020303" pitchFamily="18" charset="0"/>
+                <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+              </a:rPr>
+              <a:t> Fare Structure</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US" sz="1400" b="1">
+              <a:latin typeface="Georgia" panose="02040502050405020303" pitchFamily="18" charset="0"/>
+              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            </a:endParaRPr>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.26457343315334486"/>
+          <c:y val="1.6800301342885675E-2"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.21404582874218667"/>
+          <c:y val="6.2649942591367414E-2"/>
+          <c:w val="0.7704272495741169"/>
+          <c:h val="0.90084215602163209"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Base fee</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Prices!$A$2:$A$46</c:f>
+              <c:strCache>
+                <c:ptCount val="45"/>
+                <c:pt idx="0">
+                  <c:v>Copenhagen / Billund</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Copenhagen / Kalundborg</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Copenhagen / Aarhus</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Copenhagen / Odense</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Copenhagen / Sønderborg</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Copenhagen / Aalborg</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Copenhagen / Bornholm</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Copenhagen / Viborg</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Copenhagen / Helsingør</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Billund / Kalundborg</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Billund / Aarhus</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Billund / Odense</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>Billund / Sønderborg</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>Billund / Aalborg</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>Billund / Bornholm</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>Billund / Viborg</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>Billund / Helsingør</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>Kalundborg / Aarhus</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>Kalundborg / Odense</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>Kalundborg / Sønderborg</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>Kalundborg / Aalborg</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>Kalundborg / Bornholm</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>Kalundborg / Viborg</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>Kalundborg / Helsingør</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>Aarhus / Odense</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>Aarhus / Sønderborg</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>Aarhus / Aalborg</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>Aarhus / Bornholm</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>Aarhus / Viborg</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>Aarhus / Helsingør</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>Odense / Sønderborg</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>Odense / Aalborg</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>Odense / Bornholm</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>Odense / Viborg</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>Odense / Helsingør</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>Sønderborg / Aalborg</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>Sønderborg / Bornholm</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>Sønderborg / Viborg</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>Sønderborg / Helsingør</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>Aalborg / Bornholm</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>Aalborg / Viborg</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>Aalborg / Helsingør</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>Bornholm / Viborg</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>Bornholm / Helsingør</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>Viborg / Helsingør</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Prices!$M$2:$M$46</c:f>
+              <c:numCache>
+                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"??_);_(@_)</c:formatCode>
+                <c:ptCount val="45"/>
+                <c:pt idx="0">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>500</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-5667-FA4E-8307-A6F7928299DD}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Car Travel Cost</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Prices!$A$2:$A$46</c:f>
+              <c:strCache>
+                <c:ptCount val="45"/>
+                <c:pt idx="0">
+                  <c:v>Copenhagen / Billund</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Copenhagen / Kalundborg</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Copenhagen / Aarhus</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Copenhagen / Odense</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Copenhagen / Sønderborg</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Copenhagen / Aalborg</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Copenhagen / Bornholm</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Copenhagen / Viborg</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Copenhagen / Helsingør</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Billund / Kalundborg</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Billund / Aarhus</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Billund / Odense</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>Billund / Sønderborg</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>Billund / Aalborg</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>Billund / Bornholm</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>Billund / Viborg</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>Billund / Helsingør</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>Kalundborg / Aarhus</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>Kalundborg / Odense</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>Kalundborg / Sønderborg</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>Kalundborg / Aalborg</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>Kalundborg / Bornholm</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>Kalundborg / Viborg</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>Kalundborg / Helsingør</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>Aarhus / Odense</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>Aarhus / Sønderborg</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>Aarhus / Aalborg</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>Aarhus / Bornholm</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>Aarhus / Viborg</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>Aarhus / Helsingør</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>Odense / Sønderborg</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>Odense / Aalborg</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>Odense / Bornholm</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>Odense / Viborg</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>Odense / Helsingør</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>Sønderborg / Aalborg</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>Sønderborg / Bornholm</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>Sønderborg / Viborg</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>Sønderborg / Helsingør</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>Aalborg / Bornholm</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>Aalborg / Viborg</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>Aalborg / Helsingør</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>Bornholm / Viborg</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>Bornholm / Helsingør</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>Viborg / Helsingør</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Prices!$K$2:$K$46</c:f>
+              <c:numCache>
+                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"??_);_(@_)</c:formatCode>
+                <c:ptCount val="45"/>
+                <c:pt idx="0">
+                  <c:v>801</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>300</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1041</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>531</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>975</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1245</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>480</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>978</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>210</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>633</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>411</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>318</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>411</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>615</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1278</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>267</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>915</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>873</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>363</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>807</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1077</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>777</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>810</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>393</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>561</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>699</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>378</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>1521</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>297</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>1161</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>492</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>762</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>1011</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>495</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>648</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>897</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>1452</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>630</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>1089</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>1725</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>252</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>1362</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>1458</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>690</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>1098</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-5667-FA4E-8307-A6F7928299DD}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>Time Saving Value</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="CE6E6E"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="6B2424"/>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Prices!$A$2:$A$46</c:f>
+              <c:strCache>
+                <c:ptCount val="45"/>
+                <c:pt idx="0">
+                  <c:v>Copenhagen / Billund</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Copenhagen / Kalundborg</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Copenhagen / Aarhus</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Copenhagen / Odense</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Copenhagen / Sønderborg</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Copenhagen / Aalborg</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Copenhagen / Bornholm</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Copenhagen / Viborg</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Copenhagen / Helsingør</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Billund / Kalundborg</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Billund / Aarhus</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Billund / Odense</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>Billund / Sønderborg</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>Billund / Aalborg</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>Billund / Bornholm</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>Billund / Viborg</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>Billund / Helsingør</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>Kalundborg / Aarhus</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>Kalundborg / Odense</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>Kalundborg / Sønderborg</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>Kalundborg / Aalborg</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>Kalundborg / Bornholm</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>Kalundborg / Viborg</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>Kalundborg / Helsingør</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>Aarhus / Odense</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>Aarhus / Sønderborg</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>Aarhus / Aalborg</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>Aarhus / Bornholm</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>Aarhus / Viborg</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>Aarhus / Helsingør</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>Odense / Sønderborg</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>Odense / Aalborg</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>Odense / Bornholm</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>Odense / Viborg</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>Odense / Helsingør</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>Sønderborg / Aalborg</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>Sønderborg / Bornholm</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>Sønderborg / Viborg</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>Sønderborg / Helsingør</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>Aalborg / Bornholm</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>Aalborg / Viborg</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>Aalborg / Helsingør</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>Bornholm / Viborg</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>Bornholm / Helsingør</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>Viborg / Helsingør</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Prices!$N$2:$N$46</c:f>
+              <c:numCache>
+                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"??_);_(@_)</c:formatCode>
+                <c:ptCount val="45"/>
+                <c:pt idx="0">
+                  <c:v>941.33333333333326</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>429.33333333333337</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1324</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>644</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1104</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1450.6666666666667</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1448</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1241.3333333333333</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>310.66666666666669</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>978.66666666666674</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>540</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>486.66666666666669</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>536.00000000000011</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>718.66666666666663</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2381.3333333333335</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>478.66666666666669</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1164</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1330.6666666666667</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>669.33333333333337</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1112.0000000000002</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1444</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1853.3333333333335</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>1262.6666666666667</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>597.33333333333337</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>742.66666666666674</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>778.66666666666663</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>2746.666666666667</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>480</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>1560</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>640</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>889.33333333333337</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>2085.3333333333335</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>749.33333333333337</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>846.66666666666674</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>924</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>2566.666666666667</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>798.66666666666663</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>1292.0000000000002</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>2873.3333333333335</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>366.66666666666669</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>1694.6666666666667</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>2676</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>1764.0000000000002</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>1493.3333333333335</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-5667-FA4E-8307-A6F7928299DD}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:v>Ferry Surcharge</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Prices!$A$2:$A$46</c:f>
+              <c:strCache>
+                <c:ptCount val="45"/>
+                <c:pt idx="0">
+                  <c:v>Copenhagen / Billund</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Copenhagen / Kalundborg</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Copenhagen / Aarhus</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Copenhagen / Odense</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Copenhagen / Sønderborg</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Copenhagen / Aalborg</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Copenhagen / Bornholm</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Copenhagen / Viborg</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Copenhagen / Helsingør</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Billund / Kalundborg</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Billund / Aarhus</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Billund / Odense</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>Billund / Sønderborg</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>Billund / Aalborg</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>Billund / Bornholm</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>Billund / Viborg</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>Billund / Helsingør</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>Kalundborg / Aarhus</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>Kalundborg / Odense</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>Kalundborg / Sønderborg</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>Kalundborg / Aalborg</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>Kalundborg / Bornholm</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>Kalundborg / Viborg</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>Kalundborg / Helsingør</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>Aarhus / Odense</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>Aarhus / Sønderborg</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>Aarhus / Aalborg</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>Aarhus / Bornholm</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>Aarhus / Viborg</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>Aarhus / Helsingør</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>Odense / Sønderborg</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>Odense / Aalborg</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>Odense / Bornholm</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>Odense / Viborg</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>Odense / Helsingør</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>Sønderborg / Aalborg</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>Sønderborg / Bornholm</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>Sønderborg / Viborg</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>Sønderborg / Helsingør</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>Aalborg / Bornholm</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>Aalborg / Viborg</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>Aalborg / Helsingør</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>Bornholm / Viborg</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>Bornholm / Helsingør</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>Viborg / Helsingør</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Prices!$L$2:$L$46</c:f>
+              <c:numCache>
+                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"??_);_(@_)</c:formatCode>
+                <c:ptCount val="45"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>250</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>250</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>250</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>250</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>250</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>250</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>250</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>250</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>250</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-5667-FA4E-8307-A6F7928299DD}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="75"/>
+        <c:overlap val="100"/>
+        <c:axId val="1393023039"/>
+        <c:axId val="1393024751"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1393023039"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Georgia" panose="02040502050405020303" pitchFamily="18" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1393024751"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1393024751"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="5500"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="[$DKK]\ #,##0" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Georgia" panose="02040502050405020303" pitchFamily="18" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1393023039"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="4.6214585357570982E-2"/>
+          <c:y val="2.9213114784751127E-2"/>
+          <c:w val="0.8999999426991564"/>
+          <c:h val="3.8530299046324643E-2"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Georgia" panose="02040502050405020303" pitchFamily="18" charset="0"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr rot="0" vert="horz"/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="297">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="297">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>792487</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>52280</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>577563</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>69563</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A3E0D721-651A-715E-24B4-38BEC063F814}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>46566</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>29634</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>165100</xdr:colOff>
+      <xdr:row>95</xdr:row>
+      <xdr:rowOff>105835</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="7" name="Chart 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9D6C708B-4A54-AF44-8EF1-7ECEE5F62108}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3CFD079E-5109-8F49-8A19-E09E2BEBBC8C}" name="Table13" displayName="Table13" ref="A1:N56" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6">
-  <autoFilter ref="A1:N56" xr:uid="{CEDCB4F7-0752-8449-BE87-89650C1E9E7C}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3CFD079E-5109-8F49-8A19-E09E2BEBBC8C}" name="Table13" displayName="Table13" ref="B1:O56" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6">
+  <autoFilter ref="B1:O56" xr:uid="{CEDCB4F7-0752-8449-BE87-89650C1E9E7C}"/>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{0330B38A-598B-B64A-86F4-FA8E25EAC437}" name="From"/>
     <tableColumn id="2" xr3:uid="{DA4E4644-7B10-0541-B73A-349A5A6836E2}" name="To" dataDxfId="5"/>
@@ -535,13 +4090,13 @@
     <tableColumn id="10" xr3:uid="{DBB7D64B-F97D-5C46-B464-1DA11C10DF3A}" name="Pris (Bil udgift)" dataDxfId="4"/>
     <tableColumn id="11" xr3:uid="{CC283087-BB53-D146-A233-2D178D7E3562}" name="Færge (gns. Gælder kun Bornholm)" dataDxfId="3"/>
     <tableColumn id="12" xr3:uid="{B4DC4D17-2AE3-D34D-926C-7506AC52E6B8}" name="Base" dataDxfId="2">
-      <calculatedColumnFormula>$Q$5</calculatedColumnFormula>
+      <calculatedColumnFormula>$R$5</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="13" xr3:uid="{E70B016F-0534-2048-951F-6FD04DC33B7C}" name="Pris (udfra tidsbesparelse)" dataDxfId="1">
-      <calculatedColumnFormula>$Q$4*MAX(F2-G2*$Q$1)*$Q$3</calculatedColumnFormula>
+      <calculatedColumnFormula>$R$4*MAX(G2-H2*$R$1)*$R$3</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="14" xr3:uid="{67EF8C2F-B7CB-8D4A-8447-692E942D0514}" name="fd_sum" dataDxfId="0">
-      <calculatedColumnFormula>SUM(J2:M2)</calculatedColumnFormula>
+      <calculatedColumnFormula>SUM(K2:N2)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -866,18 +4421,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B15C49E0-A7B4-734A-8962-DC2A879F4079}">
   <dimension ref="A1:D20"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="22.58203125" customWidth="1"/>
+    <col min="1" max="1" width="22.5" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>20</v>
       </c>
@@ -888,7 +4443,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -899,18 +4454,18 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>42</v>
       </c>
       <c r="B4" s="4">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="D4" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -921,18 +4476,18 @@
         <v>40</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="13">
-        <v>15</v>
+      <c r="B6" s="4">
+        <v>30</v>
       </c>
       <c r="D6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -943,7 +4498,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -955,7 +4510,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>0</v>
       </c>
@@ -966,7 +4521,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>1</v>
       </c>
@@ -977,7 +4532,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>41</v>
       </c>
@@ -988,7 +4543,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>2</v>
       </c>
@@ -999,7 +4554,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>39</v>
       </c>
@@ -1007,10 +4562,10 @@
         <v>20</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -1022,29 +4577,31 @@
         <v>36</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>4</v>
       </c>
-      <c r="B15" s="13">
-        <v>15</v>
+      <c r="B15" s="4">
+        <f>30/B20</f>
+        <v>30</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>5</v>
       </c>
       <c r="B16" s="4">
+        <f>20/B20</f>
         <v>20</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>6</v>
       </c>
@@ -1055,7 +4612,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>38</v>
       </c>
@@ -1063,2344 +4620,2555 @@
         <v>1</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36FC1A80-FC3B-6349-8B7A-4A1A2A7C8FC7}">
-  <dimension ref="A1:R56"/>
-  <sheetFormatPr defaultColWidth="10.58203125" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:T56"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.5" defaultRowHeight="16" outlineLevelCol="2" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="17.08203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="17.08203125" customWidth="1"/>
-    <col min="5" max="5" width="12.08203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5" customWidth="1"/>
-    <col min="7" max="7" width="17.08203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.33203125" customWidth="1"/>
-    <col min="9" max="9" width="21" style="10" customWidth="1"/>
-    <col min="10" max="10" width="13.58203125" style="10" customWidth="1"/>
-    <col min="11" max="11" width="32.08203125" style="10" customWidth="1"/>
-    <col min="12" max="12" width="10.58203125" style="10"/>
-    <col min="13" max="13" width="27" style="10" customWidth="1"/>
-    <col min="14" max="14" width="10.83203125" style="10" customWidth="1"/>
+    <col min="1" max="1" width="19.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="17" customWidth="1" outlineLevel="2"/>
+    <col min="6" max="6" width="12" customWidth="1" outlineLevel="2"/>
+    <col min="7" max="7" width="12.5" customWidth="1" outlineLevel="2"/>
+    <col min="8" max="8" width="17" customWidth="1" outlineLevel="1"/>
+    <col min="9" max="9" width="19.33203125" customWidth="1" outlineLevel="2"/>
+    <col min="10" max="10" width="21" style="10" customWidth="1" outlineLevel="2"/>
+    <col min="11" max="11" width="13.5" style="10" customWidth="1" outlineLevel="2"/>
+    <col min="12" max="12" width="32" style="10" customWidth="1" outlineLevel="2"/>
+    <col min="13" max="13" width="10.5" style="10" customWidth="1" outlineLevel="2"/>
+    <col min="14" max="14" width="27" style="10" customWidth="1" outlineLevel="1"/>
+    <col min="15" max="15" width="10.83203125" style="10" customWidth="1"/>
+    <col min="17" max="17" width="13.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:19" ht="17" x14ac:dyDescent="0.2">
+      <c r="B1" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="C1" s="5" t="s">
         <v>34</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>44</v>
       </c>
       <c r="D1" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="E1" t="s">
-        <v>57</v>
+      <c r="E1" s="5" t="s">
+        <v>46</v>
       </c>
       <c r="F1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G1" t="s">
         <v>22</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>23</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>24</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="J1" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="J1" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="K1" s="11" t="s">
+      <c r="K1" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="L1" s="10" t="s">
+      <c r="L1" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M1" s="12" t="s">
+      <c r="M1" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="N1" s="10" t="s">
+      <c r="N1" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="O1" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>19</v>
       </c>
-      <c r="Q1">
+      <c r="R1">
         <v>0.2</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A2">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B2">
         <v>1</v>
       </c>
-      <c r="B2" s="6">
+      <c r="C2" s="6">
         <v>2</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F2">
         <v>267</v>
       </c>
-      <c r="F2">
+      <c r="G2">
         <v>185</v>
       </c>
-      <c r="G2">
+      <c r="H2">
         <v>219</v>
       </c>
-      <c r="H2">
+      <c r="I2">
         <v>43.8</v>
       </c>
-      <c r="I2">
+      <c r="J2">
         <v>4.2</v>
       </c>
-      <c r="J2" s="10">
-        <f>$Q$6*E2</f>
+      <c r="K2" s="10">
+        <f>$R$6*F2</f>
         <v>801</v>
       </c>
-      <c r="K2" s="10">
-        <f>IF(A2=8,250,0)+IF(B2=8,250,0)</f>
-        <v>0</v>
-      </c>
       <c r="L2" s="10">
-        <f>$Q$5</f>
+        <f>IF(B2=8,250,0)+IF(C2=8,250,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M2" s="10">
+        <f>$R$5</f>
         <v>500</v>
       </c>
-      <c r="M2" s="10">
-        <f>$Q$4*MAX(F2-G2*$Q$1)*$Q$3</f>
+      <c r="N2" s="10">
+        <f>$R$4*MAX(G2-H2*$R$1)*$R$3</f>
         <v>941.33333333333326</v>
       </c>
-      <c r="N2" s="10">
-        <f>SUM(J2:M2)</f>
+      <c r="O2" s="10">
+        <f>SUM(K2:N2)</f>
         <v>2242.333333333333</v>
       </c>
-      <c r="P2" t="s">
+      <c r="Q2" t="s">
         <v>26</v>
       </c>
-      <c r="Q2">
+      <c r="R2">
         <v>16</v>
       </c>
-      <c r="R2" t="s">
+      <c r="S2" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A3">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B3">
         <v>1</v>
       </c>
-      <c r="B3" s="6">
+      <c r="C3" s="6">
         <v>3</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E3">
+      <c r="D3" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F3">
         <v>100</v>
       </c>
-      <c r="F3">
+      <c r="G3">
         <v>82</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>88</v>
       </c>
-      <c r="H3">
+      <c r="I3">
         <v>17.600000000000001</v>
       </c>
-      <c r="I3">
+      <c r="J3">
         <v>4.7</v>
       </c>
-      <c r="J3" s="10">
-        <f t="shared" ref="J3:J46" si="0">$Q$6*E3</f>
+      <c r="K3" s="10">
+        <f t="shared" ref="K3:K46" si="0">$R$6*F3</f>
         <v>300</v>
       </c>
-      <c r="K3" s="10">
-        <f t="shared" ref="K3:K46" si="1">IF(A3=8,250,0)+IF(B3=8,250,0)</f>
-        <v>0</v>
-      </c>
       <c r="L3" s="10">
-        <f t="shared" ref="L3:L46" si="2">$Q$5</f>
+        <f t="shared" ref="L3:L46" si="1">IF(B3=8,250,0)+IF(C3=8,250,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M3" s="10">
+        <f t="shared" ref="M3:M46" si="2">$R$5</f>
         <v>500</v>
       </c>
-      <c r="M3" s="10">
-        <f t="shared" ref="M3:M46" si="3">$Q$4*MAX(F3-G3*$Q$1)*$Q$3</f>
+      <c r="N3" s="10">
+        <f t="shared" ref="N3:N46" si="3">$R$4*MAX(G3-H3*$R$1)*$R$3</f>
         <v>429.33333333333337</v>
       </c>
-      <c r="N3" s="10">
-        <f t="shared" ref="N3:N46" si="4">SUM(J3:M3)</f>
+      <c r="O3" s="10">
+        <f t="shared" ref="O3:O56" si="4">SUM(K3:N3)</f>
         <v>1229.3333333333335</v>
       </c>
-      <c r="P3" t="s">
+      <c r="Q3" t="s">
         <v>28</v>
       </c>
-      <c r="Q3">
+      <c r="R3">
         <f>800/60</f>
         <v>13.333333333333334</v>
       </c>
-      <c r="R3" t="s">
+      <c r="S3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A4">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B4">
         <v>1</v>
       </c>
-      <c r="B4" s="6">
+      <c r="C4" s="6">
         <v>4</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>46</v>
-      </c>
       <c r="D4" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="E4">
+        <v>47</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F4">
         <v>347</v>
       </c>
-      <c r="F4">
+      <c r="G4">
         <v>228</v>
       </c>
-      <c r="G4">
+      <c r="H4">
         <v>147</v>
       </c>
-      <c r="H4">
+      <c r="I4">
         <v>29.4</v>
       </c>
-      <c r="I4">
+      <c r="J4">
         <v>7.8</v>
       </c>
-      <c r="J4" s="10">
+      <c r="K4" s="10">
         <f t="shared" si="0"/>
         <v>1041</v>
       </c>
-      <c r="K4" s="10">
+      <c r="L4" s="10">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L4" s="10">
+      <c r="M4" s="10">
         <f t="shared" si="2"/>
         <v>500</v>
       </c>
-      <c r="M4" s="10">
-        <f>$Q$4*MAX(F4-G4*$Q$1)*$Q$3</f>
+      <c r="N4" s="10">
+        <f>$R$4*MAX(G4-H4*$R$1)*$R$3</f>
         <v>1324</v>
       </c>
-      <c r="N4" s="10">
-        <f>SUM(J4:M4)</f>
+      <c r="O4" s="10">
+        <f t="shared" si="4"/>
         <v>2865</v>
       </c>
-      <c r="P4" t="s">
+      <c r="Q4" t="s">
         <v>30</v>
       </c>
-      <c r="Q4">
+      <c r="R4">
         <v>0.5</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A5">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B5">
         <v>1</v>
       </c>
-      <c r="B5" s="6">
+      <c r="C5" s="6">
         <v>5</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>46</v>
-      </c>
       <c r="D5" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E5">
+        <v>47</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F5">
         <v>177</v>
       </c>
-      <c r="F5">
+      <c r="G5">
         <v>126</v>
       </c>
-      <c r="G5">
+      <c r="H5">
         <v>147</v>
       </c>
-      <c r="H5">
+      <c r="I5">
         <v>29.4</v>
       </c>
-      <c r="I5">
+      <c r="J5">
         <v>4.3</v>
       </c>
-      <c r="J5" s="10">
-        <f>$Q$6*E5</f>
+      <c r="K5" s="10">
+        <f>$R$6*F5</f>
         <v>531</v>
       </c>
-      <c r="K5" s="10">
+      <c r="L5" s="10">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L5" s="10">
+      <c r="M5" s="10">
         <f t="shared" si="2"/>
         <v>500</v>
       </c>
-      <c r="M5" s="10">
-        <f>$Q$4*MAX(F5-G5*$Q$1)*$Q$3</f>
+      <c r="N5" s="10">
+        <f>$R$4*MAX(G5-H5*$R$1)*$R$3</f>
         <v>644</v>
       </c>
-      <c r="N5" s="10">
+      <c r="O5" s="10">
         <f t="shared" si="4"/>
         <v>1675</v>
       </c>
-      <c r="P5" t="s">
+      <c r="Q5" t="s">
         <v>31</v>
       </c>
-      <c r="Q5">
+      <c r="R5">
         <v>500</v>
       </c>
-      <c r="R5" t="s">
+      <c r="S5" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A6">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>68</v>
+      </c>
+      <c r="B6">
         <v>1</v>
       </c>
-      <c r="B6" s="6">
+      <c r="C6" s="6">
         <v>6</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>46</v>
-      </c>
       <c r="D6" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="E6">
+        <v>47</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F6">
         <v>325</v>
       </c>
-      <c r="F6">
+      <c r="G6">
         <v>205</v>
       </c>
-      <c r="G6">
+      <c r="H6">
         <v>197</v>
       </c>
-      <c r="H6">
+      <c r="I6">
         <v>39.4</v>
       </c>
-      <c r="I6">
+      <c r="J6">
         <v>5.2</v>
       </c>
-      <c r="J6" s="10">
+      <c r="K6" s="10">
         <f t="shared" si="0"/>
         <v>975</v>
       </c>
-      <c r="K6" s="10">
+      <c r="L6" s="10">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L6" s="10">
+      <c r="M6" s="10">
         <f t="shared" si="2"/>
         <v>500</v>
       </c>
-      <c r="M6" s="10">
+      <c r="N6" s="10">
         <f t="shared" si="3"/>
         <v>1104</v>
       </c>
-      <c r="N6" s="10">
+      <c r="O6" s="10">
         <f t="shared" si="4"/>
         <v>2579</v>
       </c>
-      <c r="P6" t="s">
-        <v>62</v>
-      </c>
-      <c r="Q6">
+      <c r="Q6" t="s">
+        <v>63</v>
+      </c>
+      <c r="R6">
         <v>3</v>
       </c>
-      <c r="R6" t="s">
+      <c r="S6" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A7">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>69</v>
+      </c>
+      <c r="B7">
         <v>1</v>
       </c>
-      <c r="B7" s="6">
+      <c r="C7" s="6">
         <v>7</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>46</v>
-      </c>
       <c r="D7" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="E7">
+        <v>47</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F7">
         <v>415</v>
       </c>
-      <c r="F7">
+      <c r="G7">
         <v>263</v>
       </c>
-      <c r="G7">
+      <c r="H7">
         <v>227</v>
       </c>
-      <c r="H7">
+      <c r="I7">
         <v>45.4</v>
       </c>
-      <c r="I7">
+      <c r="J7">
         <v>5.8</v>
       </c>
-      <c r="J7" s="10">
+      <c r="K7" s="10">
         <f t="shared" si="0"/>
         <v>1245</v>
       </c>
-      <c r="K7" s="10">
+      <c r="L7" s="10">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L7" s="10">
+      <c r="M7" s="10">
         <f t="shared" si="2"/>
         <v>500</v>
       </c>
-      <c r="M7" s="10">
+      <c r="N7" s="10">
         <f t="shared" si="3"/>
         <v>1450.6666666666667</v>
       </c>
-      <c r="N7" s="10">
+      <c r="O7" s="10">
         <f t="shared" si="4"/>
         <v>3195.666666666667</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A8">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>70</v>
+      </c>
+      <c r="B8">
         <v>1</v>
       </c>
-      <c r="B8" s="6">
+      <c r="C8" s="6">
         <v>8</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>46</v>
-      </c>
       <c r="D8" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="E8">
+        <v>47</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F8">
         <v>160</v>
       </c>
-      <c r="F8">
+      <c r="G8">
         <v>246</v>
       </c>
-      <c r="G8">
+      <c r="H8">
         <v>144</v>
       </c>
-      <c r="H8">
+      <c r="I8">
         <v>28.8</v>
       </c>
-      <c r="I8">
+      <c r="J8">
         <v>8.5</v>
       </c>
-      <c r="J8" s="10">
+      <c r="K8" s="10">
         <f t="shared" si="0"/>
         <v>480</v>
       </c>
-      <c r="K8" s="10">
+      <c r="L8" s="10">
         <f t="shared" si="1"/>
         <v>250</v>
       </c>
-      <c r="L8" s="10">
+      <c r="M8" s="10">
         <f t="shared" si="2"/>
         <v>500</v>
       </c>
-      <c r="M8" s="10">
+      <c r="N8" s="10">
         <f t="shared" si="3"/>
         <v>1448</v>
       </c>
-      <c r="N8" s="10">
+      <c r="O8" s="10">
         <f t="shared" si="4"/>
         <v>2678</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A9">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>71</v>
+      </c>
+      <c r="B9">
         <v>1</v>
       </c>
-      <c r="B9" s="6">
+      <c r="C9" s="6">
         <v>9</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>46</v>
-      </c>
       <c r="D9" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E9">
+        <v>47</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F9">
         <v>326</v>
       </c>
-      <c r="F9">
+      <c r="G9">
         <v>230</v>
       </c>
-      <c r="G9">
+      <c r="H9">
         <v>219</v>
       </c>
-      <c r="H9">
+      <c r="I9">
         <v>43.8</v>
       </c>
-      <c r="I9">
+      <c r="J9">
         <v>5.3</v>
       </c>
-      <c r="J9" s="10">
+      <c r="K9" s="10">
         <f t="shared" si="0"/>
         <v>978</v>
       </c>
-      <c r="K9" s="10">
+      <c r="L9" s="10">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L9" s="10">
+      <c r="M9" s="10">
         <f t="shared" si="2"/>
         <v>500</v>
       </c>
-      <c r="M9" s="10">
-        <f>$Q$4*MAX(F9-G9*$Q$1)*$Q$3</f>
+      <c r="N9" s="10">
+        <f>$R$4*MAX(G9-H9*$R$1)*$R$3</f>
         <v>1241.3333333333333</v>
       </c>
-      <c r="N9" s="10">
+      <c r="O9" s="10">
         <f t="shared" si="4"/>
         <v>2719.333333333333</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A10">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>72</v>
+      </c>
+      <c r="B10">
         <v>1</v>
       </c>
-      <c r="B10" s="6">
+      <c r="C10" s="6">
         <v>10</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>46</v>
-      </c>
       <c r="D10" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F10">
+        <v>70</v>
+      </c>
+      <c r="G10">
         <v>56</v>
       </c>
-      <c r="E10">
-        <v>70</v>
-      </c>
-      <c r="F10">
-        <v>56</v>
-      </c>
-      <c r="G10">
+      <c r="H10">
         <v>47</v>
       </c>
-      <c r="H10">
+      <c r="I10">
         <v>9.4</v>
       </c>
-      <c r="I10">
+      <c r="J10">
         <v>6</v>
       </c>
-      <c r="J10" s="10">
+      <c r="K10" s="10">
         <f t="shared" si="0"/>
         <v>210</v>
       </c>
-      <c r="K10" s="10">
+      <c r="L10" s="10">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L10" s="10">
+      <c r="M10" s="10">
         <f t="shared" si="2"/>
         <v>500</v>
       </c>
-      <c r="M10" s="10">
+      <c r="N10" s="10">
         <f t="shared" si="3"/>
         <v>310.66666666666669</v>
       </c>
-      <c r="N10" s="10">
+      <c r="O10" s="10">
         <f t="shared" si="4"/>
         <v>1020.6666666666667</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A11">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>73</v>
+      </c>
+      <c r="B11">
         <v>2</v>
       </c>
-      <c r="B11" s="6">
+      <c r="C11" s="6">
         <v>3</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>47</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="E11">
+      <c r="E11" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F11">
         <v>211</v>
       </c>
-      <c r="F11">
+      <c r="G11">
         <v>173</v>
       </c>
-      <c r="G11">
+      <c r="H11">
         <v>131</v>
       </c>
-      <c r="H11">
+      <c r="I11">
         <v>26.2</v>
       </c>
-      <c r="I11">
+      <c r="J11">
         <v>6.6</v>
       </c>
-      <c r="J11" s="10">
+      <c r="K11" s="10">
         <f t="shared" si="0"/>
         <v>633</v>
       </c>
-      <c r="K11" s="10">
+      <c r="L11" s="10">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L11" s="10">
+      <c r="M11" s="10">
         <f t="shared" si="2"/>
         <v>500</v>
       </c>
-      <c r="M11" s="10">
+      <c r="N11" s="10">
         <f t="shared" si="3"/>
         <v>978.66666666666674</v>
       </c>
-      <c r="N11" s="10">
+      <c r="O11" s="10">
         <f t="shared" si="4"/>
         <v>2111.666666666667</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A12">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>74</v>
+      </c>
+      <c r="B12">
         <v>2</v>
       </c>
-      <c r="B12" s="6">
+      <c r="C12" s="6">
         <v>4</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="E12">
+      <c r="D12" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F12">
         <v>137</v>
       </c>
-      <c r="F12">
+      <c r="G12">
         <v>103</v>
       </c>
-      <c r="G12">
+      <c r="H12">
         <v>110</v>
       </c>
-      <c r="H12">
+      <c r="I12">
         <v>22</v>
       </c>
-      <c r="I12">
+      <c r="J12">
         <v>4.7</v>
       </c>
-      <c r="J12" s="10">
+      <c r="K12" s="10">
         <f t="shared" si="0"/>
         <v>411</v>
       </c>
-      <c r="K12" s="10">
+      <c r="L12" s="10">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L12" s="10">
+      <c r="M12" s="10">
         <f t="shared" si="2"/>
         <v>500</v>
       </c>
-      <c r="M12" s="10">
+      <c r="N12" s="10">
         <f t="shared" si="3"/>
         <v>540</v>
       </c>
-      <c r="N12" s="10">
+      <c r="O12" s="10">
         <f t="shared" si="4"/>
         <v>1451</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A13">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>75</v>
+      </c>
+      <c r="B13">
         <v>2</v>
       </c>
-      <c r="B13" s="6">
+      <c r="C13" s="6">
         <v>5</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E13">
+      <c r="D13" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F13">
         <v>106</v>
       </c>
-      <c r="F13">
+      <c r="G13">
         <v>89</v>
       </c>
-      <c r="G13">
+      <c r="H13">
         <v>80</v>
       </c>
-      <c r="H13">
+      <c r="I13">
         <v>16</v>
       </c>
-      <c r="I13">
+      <c r="J13">
         <v>5.6</v>
       </c>
-      <c r="J13" s="10">
+      <c r="K13" s="10">
         <f t="shared" si="0"/>
         <v>318</v>
       </c>
-      <c r="K13" s="10">
+      <c r="L13" s="10">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L13" s="10">
+      <c r="M13" s="10">
         <f t="shared" si="2"/>
         <v>500</v>
       </c>
-      <c r="M13" s="10">
+      <c r="N13" s="10">
         <f t="shared" si="3"/>
         <v>486.66666666666669</v>
       </c>
-      <c r="N13" s="10">
+      <c r="O13" s="10">
         <f t="shared" si="4"/>
         <v>1304.6666666666667</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A14">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>76</v>
+      </c>
+      <c r="B14">
         <v>2</v>
       </c>
-      <c r="B14" s="6">
+      <c r="C14" s="6">
         <v>6</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="E14">
+      <c r="D14" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F14">
         <v>137</v>
       </c>
-      <c r="F14">
+      <c r="G14">
         <v>100</v>
       </c>
-      <c r="G14">
+      <c r="H14">
         <v>98</v>
       </c>
-      <c r="H14">
+      <c r="I14">
         <v>19.600000000000001</v>
       </c>
-      <c r="I14">
+      <c r="J14">
         <v>5.0999999999999996</v>
       </c>
-      <c r="J14" s="10">
+      <c r="K14" s="10">
         <f t="shared" si="0"/>
         <v>411</v>
       </c>
-      <c r="K14" s="10">
+      <c r="L14" s="10">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L14" s="10">
+      <c r="M14" s="10">
         <f t="shared" si="2"/>
         <v>500</v>
       </c>
-      <c r="M14" s="10">
+      <c r="N14" s="10">
         <f t="shared" si="3"/>
         <v>536.00000000000011</v>
       </c>
-      <c r="N14" s="10">
+      <c r="O14" s="10">
         <f t="shared" si="4"/>
         <v>1447</v>
       </c>
+      <c r="R14">
+        <v>15</v>
+      </c>
+      <c r="S14" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A15">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>77</v>
+      </c>
+      <c r="B15">
         <v>2</v>
       </c>
-      <c r="B15" s="6">
+      <c r="C15" s="6">
         <v>7</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="E15">
+      <c r="D15" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="F15">
         <v>205</v>
       </c>
-      <c r="F15">
+      <c r="G15">
         <v>138</v>
       </c>
-      <c r="G15">
+      <c r="H15">
         <v>151</v>
       </c>
-      <c r="H15">
+      <c r="I15">
         <v>30.2</v>
       </c>
-      <c r="I15">
+      <c r="J15">
         <v>4.5999999999999996</v>
       </c>
-      <c r="J15" s="10">
+      <c r="K15" s="10">
         <f t="shared" si="0"/>
         <v>615</v>
       </c>
-      <c r="K15" s="10">
+      <c r="L15" s="10">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L15" s="10">
+      <c r="M15" s="10">
         <f t="shared" si="2"/>
         <v>500</v>
       </c>
-      <c r="M15" s="10">
+      <c r="N15" s="10">
         <f t="shared" si="3"/>
         <v>718.66666666666663</v>
       </c>
-      <c r="N15" s="10">
+      <c r="O15" s="10">
         <f t="shared" si="4"/>
         <v>1833.6666666666665</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A16">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>78</v>
+      </c>
+      <c r="B16">
         <v>2</v>
       </c>
-      <c r="B16" s="6">
+      <c r="C16" s="6">
         <v>8</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="E16">
+      <c r="D16" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F16">
         <v>426</v>
       </c>
-      <c r="F16">
+      <c r="G16">
         <v>429</v>
       </c>
-      <c r="G16">
+      <c r="H16">
         <v>359</v>
       </c>
-      <c r="H16">
+      <c r="I16">
         <v>71.8</v>
       </c>
-      <c r="I16">
+      <c r="J16">
         <v>6</v>
       </c>
-      <c r="J16" s="10">
+      <c r="K16" s="10">
         <f t="shared" si="0"/>
         <v>1278</v>
       </c>
-      <c r="K16" s="10">
+      <c r="L16" s="10">
         <f t="shared" si="1"/>
         <v>250</v>
       </c>
-      <c r="L16" s="10">
+      <c r="M16" s="10">
         <f t="shared" si="2"/>
         <v>500</v>
       </c>
-      <c r="M16" s="10">
+      <c r="N16" s="10">
         <f t="shared" si="3"/>
         <v>2381.3333333333335</v>
       </c>
-      <c r="N16" s="10">
+      <c r="O16" s="10">
         <f t="shared" si="4"/>
         <v>4409.3333333333339</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A17">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>79</v>
+      </c>
+      <c r="B17">
         <v>2</v>
       </c>
-      <c r="B17" s="6">
+      <c r="C17" s="6">
         <v>9</v>
       </c>
-      <c r="C17" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E17">
+      <c r="D17" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F17">
         <v>89</v>
       </c>
-      <c r="F17">
+      <c r="G17">
         <v>87</v>
       </c>
-      <c r="G17">
+      <c r="H17">
         <v>76</v>
       </c>
-      <c r="H17">
+      <c r="I17">
         <v>15.2</v>
       </c>
-      <c r="I17">
+      <c r="J17">
         <v>5.7</v>
       </c>
-      <c r="J17" s="10">
+      <c r="K17" s="10">
         <f t="shared" si="0"/>
         <v>267</v>
       </c>
-      <c r="K17" s="10">
+      <c r="L17" s="10">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L17" s="10">
+      <c r="M17" s="10">
         <f t="shared" si="2"/>
         <v>500</v>
       </c>
-      <c r="M17" s="10">
+      <c r="N17" s="10">
         <f t="shared" si="3"/>
         <v>478.66666666666669</v>
       </c>
-      <c r="N17" s="10">
+      <c r="O17" s="10">
         <f t="shared" si="4"/>
         <v>1245.6666666666667</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A18">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>80</v>
+      </c>
+      <c r="B18">
         <v>2</v>
       </c>
-      <c r="B18" s="6">
+      <c r="C18" s="6">
         <v>10</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E18">
+      <c r="D18" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F18">
         <v>305</v>
       </c>
-      <c r="F18">
+      <c r="G18">
         <v>218</v>
       </c>
-      <c r="G18">
+      <c r="H18">
         <v>217</v>
       </c>
-      <c r="H18">
+      <c r="I18">
         <v>43.4</v>
       </c>
-      <c r="I18">
+      <c r="J18">
         <v>5</v>
       </c>
-      <c r="J18" s="10">
+      <c r="K18" s="10">
         <f t="shared" si="0"/>
         <v>915</v>
       </c>
-      <c r="K18" s="10">
+      <c r="L18" s="10">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L18" s="10">
+      <c r="M18" s="10">
         <f t="shared" si="2"/>
         <v>500</v>
       </c>
-      <c r="M18" s="10">
+      <c r="N18" s="10">
         <f t="shared" si="3"/>
         <v>1164</v>
       </c>
-      <c r="N18" s="10">
+      <c r="O18" s="10">
         <f t="shared" si="4"/>
         <v>2579</v>
       </c>
+      <c r="Q18" s="13">
+        <f>3*O4*1</f>
+        <v>8595</v>
+      </c>
+      <c r="R18">
+        <f>R14*H4+R14*H31</f>
+        <v>4080</v>
+      </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A19">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>81</v>
+      </c>
+      <c r="B19">
         <v>3</v>
       </c>
-      <c r="B19" s="6">
+      <c r="C19" s="6">
         <v>4</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D19" s="1" t="s">
+      <c r="D19" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="E19">
+      <c r="E19" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F19">
         <v>291</v>
       </c>
-      <c r="F19">
+      <c r="G19">
         <v>215</v>
       </c>
-      <c r="G19">
+      <c r="H19">
         <v>77</v>
       </c>
-      <c r="H19">
+      <c r="I19">
         <v>15.4</v>
       </c>
-      <c r="I19">
+      <c r="J19">
         <v>14</v>
       </c>
-      <c r="J19" s="10">
+      <c r="K19" s="10">
         <f t="shared" si="0"/>
         <v>873</v>
       </c>
-      <c r="K19" s="10">
+      <c r="L19" s="10">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L19" s="10">
+      <c r="M19" s="10">
         <f t="shared" si="2"/>
         <v>500</v>
       </c>
-      <c r="M19" s="10">
+      <c r="N19" s="10">
         <f t="shared" si="3"/>
         <v>1330.6666666666667</v>
       </c>
-      <c r="N19" s="10">
+      <c r="O19" s="10">
         <f t="shared" si="4"/>
         <v>2703.666666666667</v>
       </c>
+      <c r="Q19" s="14">
+        <f>4*O33*1+2*O32*1</f>
+        <v>11869.333333333334</v>
+      </c>
+      <c r="R19">
+        <f>H33*R14+R14*H32+H27*R14</f>
+        <v>6060</v>
+      </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A20">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>82</v>
+      </c>
+      <c r="B20">
         <v>3</v>
       </c>
-      <c r="B20" s="6">
+      <c r="C20" s="6">
         <v>5</v>
       </c>
-      <c r="C20" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E20">
+      <c r="D20" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F20">
         <v>121</v>
       </c>
-      <c r="F20">
+      <c r="G20">
         <v>113</v>
       </c>
-      <c r="G20">
+      <c r="H20">
         <v>63</v>
       </c>
-      <c r="H20">
+      <c r="I20">
         <v>12.6</v>
       </c>
-      <c r="I20">
+      <c r="J20">
         <v>9</v>
       </c>
-      <c r="J20" s="10">
+      <c r="K20" s="10">
         <f t="shared" si="0"/>
         <v>363</v>
       </c>
-      <c r="K20" s="10">
+      <c r="L20" s="10">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L20" s="10">
+      <c r="M20" s="10">
         <f t="shared" si="2"/>
         <v>500</v>
       </c>
-      <c r="M20" s="10">
+      <c r="N20" s="10">
         <f t="shared" si="3"/>
         <v>669.33333333333337</v>
       </c>
-      <c r="N20" s="10">
+      <c r="O20" s="10">
         <f t="shared" si="4"/>
         <v>1532.3333333333335</v>
       </c>
+      <c r="Q20" s="13">
+        <f>4*O4*0.75+4*O4*0.75</f>
+        <v>17190</v>
+      </c>
+      <c r="R20" s="13">
+        <f>H4*R14+R14*H4+R14*H27</f>
+        <v>6825</v>
+      </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A21">
+    <row r="21" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>83</v>
+      </c>
+      <c r="B21">
         <v>3</v>
       </c>
-      <c r="B21" s="6">
+      <c r="C21" s="6">
         <v>6</v>
       </c>
-      <c r="C21" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="E21">
+      <c r="D21" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F21">
         <v>269</v>
       </c>
-      <c r="F21">
+      <c r="G21">
         <v>192</v>
       </c>
-      <c r="G21">
+      <c r="H21">
         <v>126</v>
       </c>
-      <c r="H21">
+      <c r="I21">
         <v>25.2</v>
       </c>
-      <c r="I21">
+      <c r="J21">
         <v>7.6</v>
       </c>
-      <c r="J21" s="10">
+      <c r="K21" s="10">
         <f t="shared" si="0"/>
         <v>807</v>
       </c>
-      <c r="K21" s="10">
+      <c r="L21" s="10">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L21" s="10">
+      <c r="M21" s="10">
         <f t="shared" si="2"/>
         <v>500</v>
       </c>
-      <c r="M21" s="10">
+      <c r="N21" s="10">
         <f t="shared" si="3"/>
         <v>1112.0000000000002</v>
       </c>
-      <c r="N21" s="10">
+      <c r="O21" s="10">
         <f t="shared" si="4"/>
         <v>2419</v>
       </c>
+      <c r="Q21" s="14">
+        <f>4*O4*0.75+4*O4*0.75+4*O4*0.75</f>
+        <v>25785</v>
+      </c>
+      <c r="R21">
+        <f>H19*R14+R14*H4+H4*R14+R14*H3+H26*R14</f>
+        <v>8280</v>
+      </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A22">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>84</v>
+      </c>
+      <c r="B22">
         <v>3</v>
       </c>
-      <c r="B22" s="6">
+      <c r="C22" s="6">
         <v>7</v>
       </c>
-      <c r="C22" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D22" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="E22">
+      <c r="D22" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E22" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="F22">
         <v>359</v>
       </c>
-      <c r="F22">
+      <c r="G22">
         <v>250</v>
       </c>
-      <c r="G22">
+      <c r="H22">
         <v>167</v>
       </c>
-      <c r="H22">
+      <c r="I22">
         <v>33.4</v>
       </c>
-      <c r="I22">
+      <c r="J22">
         <v>7.5</v>
       </c>
-      <c r="J22" s="10">
+      <c r="K22" s="10">
         <f t="shared" si="0"/>
         <v>1077</v>
       </c>
-      <c r="K22" s="10">
+      <c r="L22" s="10">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L22" s="10">
+      <c r="M22" s="10">
         <f t="shared" si="2"/>
         <v>500</v>
       </c>
-      <c r="M22" s="10">
+      <c r="N22" s="10">
         <f t="shared" si="3"/>
         <v>1444</v>
       </c>
-      <c r="N22" s="10">
+      <c r="O22" s="10">
         <f t="shared" si="4"/>
         <v>3021</v>
       </c>
+      <c r="Q22" s="14">
+        <f>2*O32*0.75</f>
+        <v>2448</v>
+      </c>
+      <c r="R22">
+        <f>R14*H32+R14*H3+R14*H4</f>
+        <v>4575</v>
+      </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A23">
+    <row r="23" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>85</v>
+      </c>
+      <c r="B23">
         <v>3</v>
       </c>
-      <c r="B23" s="6">
+      <c r="C23" s="6">
         <v>8</v>
       </c>
-      <c r="C23" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="E23">
+      <c r="D23" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F23">
         <v>259</v>
       </c>
-      <c r="F23">
+      <c r="G23">
         <v>324</v>
       </c>
-      <c r="G23">
+      <c r="H23">
         <v>230</v>
       </c>
-      <c r="H23">
+      <c r="I23">
         <v>46</v>
       </c>
-      <c r="I23">
+      <c r="J23">
         <v>7</v>
       </c>
-      <c r="J23" s="10">
+      <c r="K23" s="10">
         <f t="shared" si="0"/>
         <v>777</v>
       </c>
-      <c r="K23" s="10">
+      <c r="L23" s="10">
         <f t="shared" si="1"/>
         <v>250</v>
       </c>
-      <c r="L23" s="10">
+      <c r="M23" s="10">
         <f t="shared" si="2"/>
         <v>500</v>
       </c>
-      <c r="M23" s="10">
+      <c r="N23" s="10">
         <f t="shared" si="3"/>
         <v>1853.3333333333335</v>
       </c>
-      <c r="N23" s="10">
+      <c r="O23" s="10">
         <f t="shared" si="4"/>
         <v>3380.3333333333335</v>
       </c>
+      <c r="Q23" s="14">
+        <f>3*O4*0.75+3*O4*1</f>
+        <v>15041.25</v>
+      </c>
+      <c r="R23">
+        <f>R14*H4+R14*H4+R14*H13</f>
+        <v>5610</v>
+      </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A24">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>86</v>
+      </c>
+      <c r="B24">
         <v>3</v>
       </c>
-      <c r="B24" s="6">
+      <c r="C24" s="6">
         <v>9</v>
       </c>
-      <c r="C24" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E24">
+      <c r="D24" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F24">
         <v>270</v>
       </c>
-      <c r="F24">
+      <c r="G24">
         <v>217</v>
       </c>
-      <c r="G24">
+      <c r="H24">
         <v>138</v>
       </c>
-      <c r="H24">
+      <c r="I24">
         <v>27.6</v>
       </c>
-      <c r="I24">
+      <c r="J24">
         <v>7.9</v>
       </c>
-      <c r="J24" s="10">
+      <c r="K24" s="10">
         <f t="shared" si="0"/>
         <v>810</v>
       </c>
-      <c r="K24" s="10">
+      <c r="L24" s="10">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L24" s="10">
+      <c r="M24" s="10">
         <f t="shared" si="2"/>
         <v>500</v>
       </c>
-      <c r="M24" s="10">
+      <c r="N24" s="10">
         <f t="shared" si="3"/>
         <v>1262.6666666666667</v>
       </c>
-      <c r="N24" s="10">
+      <c r="O24" s="10">
         <f t="shared" si="4"/>
         <v>2572.666666666667</v>
       </c>
+      <c r="Q24" s="13"/>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A25">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>87</v>
+      </c>
+      <c r="B25">
         <v>3</v>
       </c>
-      <c r="B25" s="6">
+      <c r="C25" s="6">
         <v>10</v>
       </c>
-      <c r="C25" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E25">
+      <c r="D25" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F25">
         <v>131</v>
       </c>
-      <c r="F25">
+      <c r="G25">
         <v>108</v>
       </c>
-      <c r="G25">
+      <c r="H25">
         <v>92</v>
       </c>
-      <c r="H25">
+      <c r="I25">
         <v>18.399999999999999</v>
       </c>
-      <c r="I25">
+      <c r="J25">
         <v>5.9</v>
       </c>
-      <c r="J25" s="10">
+      <c r="K25" s="10">
         <f t="shared" si="0"/>
         <v>393</v>
       </c>
-      <c r="K25" s="10">
+      <c r="L25" s="10">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L25" s="10">
+      <c r="M25" s="10">
         <f t="shared" si="2"/>
         <v>500</v>
       </c>
-      <c r="M25" s="10">
+      <c r="N25" s="10">
         <f t="shared" si="3"/>
         <v>597.33333333333337</v>
       </c>
-      <c r="N25" s="10">
+      <c r="O25" s="10">
         <f t="shared" si="4"/>
         <v>1490.3333333333335</v>
       </c>
+      <c r="Q25" s="13"/>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A26">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>88</v>
+      </c>
+      <c r="B26">
         <v>4</v>
       </c>
-      <c r="B26" s="6">
+      <c r="C26" s="6">
         <v>5</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>49</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E26">
+      <c r="E26" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F26">
         <v>187</v>
       </c>
-      <c r="F26">
+      <c r="G26">
         <v>130</v>
       </c>
-      <c r="G26">
+      <c r="H26">
         <v>93</v>
       </c>
-      <c r="H26">
+      <c r="I26">
         <v>18.600000000000001</v>
       </c>
-      <c r="I26">
+      <c r="J26">
         <v>7</v>
       </c>
-      <c r="J26" s="10">
+      <c r="K26" s="10">
         <f t="shared" si="0"/>
         <v>561</v>
       </c>
-      <c r="K26" s="10">
+      <c r="L26" s="10">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L26" s="10">
+      <c r="M26" s="10">
         <f t="shared" si="2"/>
         <v>500</v>
       </c>
-      <c r="M26" s="10">
+      <c r="N26" s="10">
         <f t="shared" si="3"/>
         <v>742.66666666666674</v>
       </c>
-      <c r="N26" s="10">
+      <c r="O26" s="10">
         <f t="shared" si="4"/>
         <v>1803.6666666666667</v>
       </c>
+      <c r="Q26" s="13"/>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A27">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>89</v>
+      </c>
+      <c r="B27">
         <v>4</v>
       </c>
-      <c r="B27" s="6">
+      <c r="C27" s="6">
         <v>6</v>
       </c>
-      <c r="C27" s="1" t="s">
-        <v>49</v>
-      </c>
       <c r="D27" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="E27">
+        <v>50</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F27">
         <v>233</v>
       </c>
-      <c r="F27">
+      <c r="G27">
         <v>149</v>
       </c>
-      <c r="G27">
+      <c r="H27">
         <v>161</v>
       </c>
-      <c r="H27">
+      <c r="I27">
         <v>32.200000000000003</v>
       </c>
-      <c r="I27">
+      <c r="J27">
         <v>4.5999999999999996</v>
       </c>
-      <c r="J27" s="10">
+      <c r="K27" s="10">
         <f t="shared" si="0"/>
         <v>699</v>
       </c>
-      <c r="K27" s="10">
+      <c r="L27" s="10">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L27" s="10">
+      <c r="M27" s="10">
         <f t="shared" si="2"/>
         <v>500</v>
       </c>
-      <c r="M27" s="10">
+      <c r="N27" s="10">
         <f t="shared" si="3"/>
         <v>778.66666666666663</v>
       </c>
-      <c r="N27" s="10">
+      <c r="O27" s="10">
         <f t="shared" si="4"/>
         <v>1977.6666666666665</v>
       </c>
+      <c r="P27" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q27" s="13">
+        <f>SUM(Q18:Q26)</f>
+        <v>80928.583333333343</v>
+      </c>
+      <c r="R27" s="13">
+        <f>-SUM(R18:R26)</f>
+        <v>-35430</v>
+      </c>
+      <c r="S27" s="13">
+        <f>Q27+R27</f>
+        <v>45498.583333333343</v>
+      </c>
+      <c r="T27">
+        <f>-SUM(T18:T26)</f>
+        <v>0</v>
+      </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A28">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>90</v>
+      </c>
+      <c r="B28">
         <v>4</v>
       </c>
-      <c r="B28" s="6">
+      <c r="C28" s="6">
         <v>7</v>
       </c>
-      <c r="C28" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D28" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="E28">
+      <c r="D28" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E28" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="F28">
         <v>126</v>
       </c>
-      <c r="F28">
+      <c r="G28">
         <v>93</v>
       </c>
-      <c r="G28">
+      <c r="H28">
         <v>90</v>
       </c>
-      <c r="H28">
+      <c r="I28">
         <v>18</v>
       </c>
-      <c r="I28">
+      <c r="J28">
         <v>5.2</v>
       </c>
-      <c r="J28" s="10">
+      <c r="K28" s="10">
         <f t="shared" si="0"/>
         <v>378</v>
       </c>
-      <c r="K28" s="10">
+      <c r="L28" s="10">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L28" s="10">
+      <c r="M28" s="10">
         <f t="shared" si="2"/>
         <v>500</v>
       </c>
-      <c r="M28" s="10">
+      <c r="N28" s="10">
         <f t="shared" si="3"/>
         <v>500</v>
       </c>
-      <c r="N28" s="10">
+      <c r="O28" s="10">
         <f t="shared" si="4"/>
         <v>1378</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A29">
+    <row r="29" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>91</v>
+      </c>
+      <c r="B29">
         <v>4</v>
       </c>
-      <c r="B29" s="6">
+      <c r="C29" s="6">
         <v>8</v>
       </c>
-      <c r="C29" s="1" t="s">
-        <v>49</v>
-      </c>
       <c r="D29" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="E29">
+        <v>50</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F29">
         <v>507</v>
       </c>
-      <c r="F29">
+      <c r="G29">
         <v>470</v>
       </c>
-      <c r="G29">
+      <c r="H29">
         <v>290</v>
       </c>
-      <c r="H29">
+      <c r="I29">
         <v>58</v>
       </c>
-      <c r="I29">
+      <c r="J29">
         <v>8.1</v>
       </c>
-      <c r="J29" s="10">
+      <c r="K29" s="10">
         <f t="shared" si="0"/>
         <v>1521</v>
       </c>
-      <c r="K29" s="10">
+      <c r="L29" s="10">
         <f t="shared" si="1"/>
         <v>250</v>
       </c>
-      <c r="L29" s="10">
+      <c r="M29" s="10">
         <f t="shared" si="2"/>
         <v>500</v>
       </c>
-      <c r="M29" s="10">
+      <c r="N29" s="10">
         <f t="shared" si="3"/>
         <v>2746.666666666667</v>
       </c>
-      <c r="N29" s="10">
+      <c r="O29" s="10">
         <f t="shared" si="4"/>
         <v>5017.666666666667</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A30">
+    <row r="30" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>92</v>
+      </c>
+      <c r="B30">
         <v>4</v>
       </c>
-      <c r="B30" s="6">
+      <c r="C30" s="6">
         <v>9</v>
       </c>
-      <c r="C30" s="1" t="s">
-        <v>49</v>
-      </c>
       <c r="D30" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E30">
+        <v>50</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F30">
         <v>99</v>
       </c>
-      <c r="F30">
+      <c r="G30">
         <v>87</v>
       </c>
-      <c r="G30">
+      <c r="H30">
         <v>75</v>
       </c>
-      <c r="H30">
+      <c r="I30">
         <v>15</v>
       </c>
-      <c r="I30">
+      <c r="J30">
         <v>5.8</v>
       </c>
-      <c r="J30" s="10">
+      <c r="K30" s="10">
         <f t="shared" si="0"/>
         <v>297</v>
       </c>
-      <c r="K30" s="10">
+      <c r="L30" s="10">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L30" s="10">
+      <c r="M30" s="10">
         <f t="shared" si="2"/>
         <v>500</v>
       </c>
-      <c r="M30" s="10">
+      <c r="N30" s="10">
         <f t="shared" si="3"/>
         <v>480</v>
       </c>
-      <c r="N30" s="10">
+      <c r="O30" s="10">
         <f t="shared" si="4"/>
         <v>1277</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A31">
+    <row r="31" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>93</v>
+      </c>
+      <c r="B31">
         <v>4</v>
       </c>
-      <c r="B31" s="6">
+      <c r="C31" s="6">
         <v>10</v>
       </c>
-      <c r="C31" s="1" t="s">
-        <v>49</v>
-      </c>
       <c r="D31" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E31">
+        <v>50</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F31">
         <v>387</v>
       </c>
-      <c r="F31">
+      <c r="G31">
         <v>259</v>
       </c>
-      <c r="G31">
+      <c r="H31">
         <v>125</v>
       </c>
-      <c r="H31">
+      <c r="I31">
         <v>25</v>
       </c>
-      <c r="I31">
+      <c r="J31">
         <v>10.4</v>
       </c>
-      <c r="J31" s="10">
+      <c r="K31" s="10">
         <f t="shared" si="0"/>
         <v>1161</v>
       </c>
-      <c r="K31" s="10">
+      <c r="L31" s="10">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L31" s="10">
+      <c r="M31" s="10">
         <f t="shared" si="2"/>
         <v>500</v>
       </c>
-      <c r="M31" s="10">
+      <c r="N31" s="10">
         <f t="shared" si="3"/>
         <v>1560</v>
       </c>
-      <c r="N31" s="10">
+      <c r="O31" s="10">
         <f t="shared" si="4"/>
         <v>3221</v>
       </c>
+      <c r="S31" s="14"/>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A32">
+    <row r="32" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>94</v>
+      </c>
+      <c r="B32">
         <v>5</v>
       </c>
-      <c r="B32" s="6">
+      <c r="C32" s="6">
         <v>6</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>50</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="E32">
+      <c r="E32" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F32">
         <v>164</v>
       </c>
-      <c r="F32">
+      <c r="G32">
         <v>110</v>
       </c>
-      <c r="G32">
+      <c r="H32">
         <v>70</v>
       </c>
-      <c r="H32">
+      <c r="I32">
         <v>14</v>
       </c>
-      <c r="I32">
+      <c r="J32">
         <v>7.9</v>
       </c>
-      <c r="J32" s="10">
+      <c r="K32" s="10">
         <f t="shared" si="0"/>
         <v>492</v>
       </c>
-      <c r="K32" s="10">
+      <c r="L32" s="10">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L32" s="10">
+      <c r="M32" s="10">
         <f t="shared" si="2"/>
         <v>500</v>
       </c>
-      <c r="M32" s="10">
+      <c r="N32" s="10">
         <f t="shared" si="3"/>
         <v>640</v>
       </c>
-      <c r="N32" s="10">
+      <c r="O32" s="10">
         <f t="shared" si="4"/>
         <v>1632</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A33" s="8">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>95</v>
+      </c>
+      <c r="B33" s="8">
         <v>5</v>
       </c>
-      <c r="B33" s="6">
+      <c r="C33" s="6">
         <v>7</v>
       </c>
-      <c r="C33" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D33" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="E33">
+      <c r="D33" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E33" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="F33">
         <v>254</v>
       </c>
-      <c r="F33">
+      <c r="G33">
         <v>168</v>
       </c>
-      <c r="G33">
+      <c r="H33">
         <v>173</v>
       </c>
-      <c r="H33">
+      <c r="I33">
         <v>34.6</v>
       </c>
-      <c r="I33">
+      <c r="J33">
         <v>4.9000000000000004</v>
       </c>
-      <c r="J33" s="10">
+      <c r="K33" s="10">
         <f t="shared" si="0"/>
         <v>762</v>
       </c>
-      <c r="K33" s="10">
+      <c r="L33" s="10">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L33" s="10">
+      <c r="M33" s="10">
         <f t="shared" si="2"/>
         <v>500</v>
       </c>
-      <c r="M33" s="10">
+      <c r="N33" s="10">
         <f t="shared" si="3"/>
         <v>889.33333333333337</v>
       </c>
-      <c r="N33" s="10">
+      <c r="O33" s="10">
         <f t="shared" si="4"/>
         <v>2151.3333333333335</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A34">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>96</v>
+      </c>
+      <c r="B34">
         <v>5</v>
       </c>
-      <c r="B34" s="6">
+      <c r="C34" s="6">
         <v>8</v>
       </c>
-      <c r="C34" s="1" t="s">
-        <v>50</v>
-      </c>
       <c r="D34" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="E34">
+        <v>51</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F34">
         <v>337</v>
       </c>
-      <c r="F34">
+      <c r="G34">
         <v>369</v>
       </c>
-      <c r="G34">
+      <c r="H34">
         <v>281</v>
       </c>
-      <c r="H34">
+      <c r="I34">
         <v>56.2</v>
       </c>
-      <c r="I34">
+      <c r="J34">
         <v>6.6</v>
       </c>
-      <c r="J34" s="10">
+      <c r="K34" s="10">
         <f t="shared" si="0"/>
         <v>1011</v>
       </c>
-      <c r="K34" s="10">
+      <c r="L34" s="10">
         <f t="shared" si="1"/>
         <v>250</v>
       </c>
-      <c r="L34" s="10">
+      <c r="M34" s="10">
         <f t="shared" si="2"/>
         <v>500</v>
       </c>
-      <c r="M34" s="10">
+      <c r="N34" s="10">
         <f t="shared" si="3"/>
         <v>2085.3333333333335</v>
       </c>
-      <c r="N34" s="10">
+      <c r="O34" s="10">
         <f t="shared" si="4"/>
         <v>3846.3333333333335</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A35">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>97</v>
+      </c>
+      <c r="B35">
         <v>5</v>
       </c>
-      <c r="B35" s="6">
+      <c r="C35" s="6">
         <v>9</v>
       </c>
-      <c r="C35" s="1" t="s">
-        <v>50</v>
-      </c>
       <c r="D35" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E35">
+        <v>51</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F35">
         <v>165</v>
       </c>
-      <c r="F35">
+      <c r="G35">
         <v>136</v>
       </c>
-      <c r="G35">
+      <c r="H35">
         <v>118</v>
       </c>
-      <c r="H35">
+      <c r="I35">
         <v>23.6</v>
       </c>
-      <c r="I35">
+      <c r="J35">
         <v>5.8</v>
       </c>
-      <c r="J35" s="10">
+      <c r="K35" s="10">
         <f t="shared" si="0"/>
         <v>495</v>
       </c>
-      <c r="K35" s="10">
+      <c r="L35" s="10">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L35" s="10">
+      <c r="M35" s="10">
         <f t="shared" si="2"/>
         <v>500</v>
       </c>
-      <c r="M35" s="10">
+      <c r="N35" s="10">
         <f t="shared" si="3"/>
         <v>749.33333333333337</v>
       </c>
-      <c r="N35" s="10">
+      <c r="O35" s="10">
         <f t="shared" si="4"/>
         <v>1744.3333333333335</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A36">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>98</v>
+      </c>
+      <c r="B36">
         <v>5</v>
       </c>
-      <c r="B36" s="6">
+      <c r="C36" s="6">
         <v>10</v>
       </c>
-      <c r="C36" s="1" t="s">
-        <v>50</v>
-      </c>
       <c r="D36" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E36">
+        <v>51</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F36">
         <v>216</v>
       </c>
-      <c r="F36">
+      <c r="G36">
         <v>158</v>
       </c>
-      <c r="G36">
+      <c r="H36">
         <v>155</v>
       </c>
-      <c r="H36">
+      <c r="I36">
         <v>31</v>
       </c>
-      <c r="I36">
+      <c r="J36">
         <v>5.0999999999999996</v>
       </c>
-      <c r="J36" s="10">
+      <c r="K36" s="10">
         <f t="shared" si="0"/>
         <v>648</v>
       </c>
-      <c r="K36" s="10">
+      <c r="L36" s="10">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L36" s="10">
+      <c r="M36" s="10">
         <f t="shared" si="2"/>
         <v>500</v>
       </c>
-      <c r="M36" s="10">
+      <c r="N36" s="10">
         <f t="shared" si="3"/>
         <v>846.66666666666674</v>
       </c>
-      <c r="N36" s="10">
+      <c r="O36" s="10">
         <f t="shared" si="4"/>
         <v>1994.6666666666667</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A37">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>99</v>
+      </c>
+      <c r="B37">
         <v>6</v>
       </c>
-      <c r="B37" s="6">
+      <c r="C37" s="6">
         <v>7</v>
       </c>
-      <c r="C37" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="D37" s="9" t="s">
+      <c r="D37" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="E37">
+      <c r="E37" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="F37">
         <v>299</v>
       </c>
-      <c r="F37">
+      <c r="G37">
         <v>185</v>
       </c>
-      <c r="G37">
+      <c r="H37">
         <v>232</v>
       </c>
-      <c r="H37">
+      <c r="I37">
         <v>46.4</v>
       </c>
-      <c r="I37">
+      <c r="J37">
         <v>4</v>
       </c>
-      <c r="J37" s="10">
+      <c r="K37" s="10">
         <f t="shared" si="0"/>
         <v>897</v>
       </c>
-      <c r="K37" s="10">
+      <c r="L37" s="10">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L37" s="10">
+      <c r="M37" s="10">
         <f t="shared" si="2"/>
         <v>500</v>
       </c>
-      <c r="M37" s="10">
+      <c r="N37" s="10">
         <f t="shared" si="3"/>
         <v>924</v>
       </c>
-      <c r="N37" s="10">
+      <c r="O37" s="10">
         <f t="shared" si="4"/>
         <v>2321</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A38">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>100</v>
+      </c>
+      <c r="B38">
         <v>6</v>
       </c>
-      <c r="B38" s="6">
+      <c r="C38" s="6">
         <v>8</v>
       </c>
-      <c r="C38" s="1" t="s">
-        <v>51</v>
-      </c>
       <c r="D38" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="E38">
+        <v>52</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F38">
         <v>484</v>
       </c>
-      <c r="F38">
+      <c r="G38">
         <v>448</v>
       </c>
-      <c r="G38">
+      <c r="H38">
         <v>315</v>
       </c>
-      <c r="H38">
+      <c r="I38">
         <v>63</v>
       </c>
-      <c r="I38">
+      <c r="J38">
         <v>7.1</v>
       </c>
-      <c r="J38" s="10">
+      <c r="K38" s="10">
         <f t="shared" si="0"/>
         <v>1452</v>
       </c>
-      <c r="K38" s="10">
+      <c r="L38" s="10">
         <f t="shared" si="1"/>
         <v>250</v>
       </c>
-      <c r="L38" s="10">
+      <c r="M38" s="10">
         <f t="shared" si="2"/>
         <v>500</v>
       </c>
-      <c r="M38" s="10">
+      <c r="N38" s="10">
         <f t="shared" si="3"/>
         <v>2566.666666666667</v>
       </c>
-      <c r="N38" s="10">
+      <c r="O38" s="10">
         <f t="shared" si="4"/>
         <v>4768.666666666667</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A39">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>101</v>
+      </c>
+      <c r="B39">
         <v>6</v>
       </c>
-      <c r="B39" s="6">
+      <c r="C39" s="6">
         <v>9</v>
       </c>
-      <c r="C39" s="1" t="s">
-        <v>51</v>
-      </c>
       <c r="D39" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E39">
+        <v>52</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F39">
         <v>210</v>
       </c>
-      <c r="F39">
+      <c r="G39">
         <v>153</v>
       </c>
-      <c r="G39">
+      <c r="H39">
         <v>166</v>
       </c>
-      <c r="H39">
+      <c r="I39">
         <v>33.200000000000003</v>
       </c>
-      <c r="I39">
+      <c r="J39">
         <v>4.5999999999999996</v>
       </c>
-      <c r="J39" s="10">
+      <c r="K39" s="10">
         <f t="shared" si="0"/>
         <v>630</v>
       </c>
-      <c r="K39" s="10">
+      <c r="L39" s="10">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L39" s="10">
+      <c r="M39" s="10">
         <f t="shared" si="2"/>
         <v>500</v>
       </c>
-      <c r="M39" s="10">
+      <c r="N39" s="10">
         <f t="shared" si="3"/>
         <v>798.66666666666663</v>
       </c>
-      <c r="N39" s="10">
+      <c r="O39" s="10">
         <f t="shared" si="4"/>
         <v>1928.6666666666665</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A40">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>102</v>
+      </c>
+      <c r="B40">
         <v>6</v>
       </c>
-      <c r="B40" s="6">
+      <c r="C40" s="6">
         <v>10</v>
       </c>
-      <c r="C40" s="1" t="s">
-        <v>51</v>
-      </c>
       <c r="D40" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E40">
+        <v>52</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F40">
         <v>363</v>
       </c>
-      <c r="F40">
+      <c r="G40">
         <v>237</v>
       </c>
-      <c r="G40">
+      <c r="H40">
         <v>216</v>
       </c>
-      <c r="H40">
+      <c r="I40">
         <v>43.2</v>
       </c>
-      <c r="I40">
+      <c r="J40">
         <v>5.5</v>
       </c>
-      <c r="J40" s="10">
+      <c r="K40" s="10">
         <f t="shared" si="0"/>
         <v>1089</v>
       </c>
-      <c r="K40" s="10">
+      <c r="L40" s="10">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L40" s="10">
+      <c r="M40" s="10">
         <f t="shared" si="2"/>
         <v>500</v>
       </c>
-      <c r="M40" s="10">
+      <c r="N40" s="10">
         <f t="shared" si="3"/>
         <v>1292.0000000000002</v>
       </c>
-      <c r="N40" s="10">
+      <c r="O40" s="10">
         <f t="shared" si="4"/>
         <v>2881</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A41">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>103</v>
+      </c>
+      <c r="B41">
         <v>7</v>
       </c>
-      <c r="B41" s="6">
+      <c r="C41" s="6">
         <v>8</v>
       </c>
-      <c r="C41" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="D41" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="E41">
+        <v>53</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F41">
         <v>575</v>
       </c>
-      <c r="F41">
+      <c r="G41">
         <v>504</v>
       </c>
-      <c r="G41">
+      <c r="H41">
         <v>365</v>
       </c>
-      <c r="H41">
+      <c r="I41">
         <v>73</v>
       </c>
-      <c r="I41">
+      <c r="J41">
         <v>6.9</v>
       </c>
-      <c r="J41" s="10">
+      <c r="K41" s="10">
         <f t="shared" si="0"/>
         <v>1725</v>
       </c>
-      <c r="K41" s="10">
+      <c r="L41" s="10">
         <f t="shared" si="1"/>
         <v>250</v>
       </c>
-      <c r="L41" s="10">
+      <c r="M41" s="10">
         <f t="shared" si="2"/>
         <v>500</v>
       </c>
-      <c r="M41" s="10">
+      <c r="N41" s="10">
         <f t="shared" si="3"/>
         <v>2873.3333333333335</v>
       </c>
-      <c r="N41" s="10">
-        <f>SUM(J41:M41)</f>
+      <c r="O41" s="10">
+        <f t="shared" si="4"/>
         <v>5348.3333333333339</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A42">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>104</v>
+      </c>
+      <c r="B42">
         <v>7</v>
       </c>
-      <c r="B42" s="6">
+      <c r="C42" s="6">
         <v>9</v>
       </c>
-      <c r="C42" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="D42" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E42">
+        <v>53</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F42">
         <v>84</v>
       </c>
-      <c r="F42">
+      <c r="G42">
         <v>70</v>
       </c>
-      <c r="G42">
+      <c r="H42">
         <v>75</v>
       </c>
-      <c r="H42">
+      <c r="I42">
         <v>15</v>
       </c>
-      <c r="I42">
+      <c r="J42">
         <v>4.7</v>
       </c>
-      <c r="J42" s="10">
+      <c r="K42" s="10">
         <f t="shared" si="0"/>
         <v>252</v>
       </c>
-      <c r="K42" s="10">
+      <c r="L42" s="10">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L42" s="10">
+      <c r="M42" s="10">
         <f t="shared" si="2"/>
         <v>500</v>
       </c>
-      <c r="M42" s="10">
+      <c r="N42" s="10">
         <f t="shared" si="3"/>
         <v>366.66666666666669</v>
       </c>
-      <c r="N42" s="10">
+      <c r="O42" s="10">
         <f t="shared" si="4"/>
         <v>1118.6666666666667</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A43">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>105</v>
+      </c>
+      <c r="B43">
         <v>7</v>
       </c>
-      <c r="B43" s="6">
+      <c r="C43" s="6">
         <v>10</v>
       </c>
-      <c r="C43" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="D43" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E43">
+        <v>53</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F43">
         <v>454</v>
       </c>
-      <c r="F43">
+      <c r="G43">
         <v>293</v>
       </c>
-      <c r="G43">
+      <c r="H43">
         <v>194</v>
       </c>
-      <c r="H43">
+      <c r="I43">
         <v>38.799999999999997</v>
       </c>
-      <c r="I43">
+      <c r="J43">
         <v>7.6</v>
       </c>
-      <c r="J43" s="10">
+      <c r="K43" s="10">
         <f t="shared" si="0"/>
         <v>1362</v>
       </c>
-      <c r="K43" s="10">
+      <c r="L43" s="10">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L43" s="10">
+      <c r="M43" s="10">
         <f t="shared" si="2"/>
         <v>500</v>
       </c>
-      <c r="M43" s="10">
+      <c r="N43" s="10">
         <f t="shared" si="3"/>
         <v>1694.6666666666667</v>
       </c>
-      <c r="N43" s="10">
+      <c r="O43" s="10">
         <f t="shared" si="4"/>
         <v>3556.666666666667</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A44">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>106</v>
+      </c>
+      <c r="B44">
         <v>8</v>
       </c>
-      <c r="B44" s="6">
+      <c r="C44" s="6">
         <v>9</v>
       </c>
-      <c r="C44" s="1" t="s">
+      <c r="D44" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E44" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D44" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E44">
+      <c r="F44">
         <v>486</v>
       </c>
-      <c r="F44">
+      <c r="G44">
         <v>474</v>
       </c>
-      <c r="G44">
+      <c r="H44">
         <v>363</v>
       </c>
-      <c r="H44">
+      <c r="I44">
         <v>72.599999999999994</v>
       </c>
-      <c r="I44">
+      <c r="J44">
         <v>6.5</v>
       </c>
-      <c r="J44" s="10">
+      <c r="K44" s="10">
         <f t="shared" si="0"/>
         <v>1458</v>
       </c>
-      <c r="K44" s="10">
+      <c r="L44" s="10">
         <f t="shared" si="1"/>
         <v>250</v>
       </c>
-      <c r="L44" s="10">
+      <c r="M44" s="10">
         <f t="shared" si="2"/>
         <v>500</v>
       </c>
-      <c r="M44" s="10">
+      <c r="N44" s="10">
         <f t="shared" si="3"/>
         <v>2676</v>
       </c>
-      <c r="N44" s="10">
+      <c r="O44" s="10">
         <f t="shared" si="4"/>
         <v>4884</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A45">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>107</v>
+      </c>
+      <c r="B45">
         <v>8</v>
       </c>
-      <c r="B45" s="6">
+      <c r="C45" s="6">
         <v>10</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>55</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="E45">
+      <c r="E45" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F45">
         <v>230</v>
       </c>
-      <c r="F45">
+      <c r="G45">
         <v>299</v>
       </c>
-      <c r="G45">
+      <c r="H45">
         <v>172</v>
       </c>
-      <c r="H45">
+      <c r="I45">
         <v>34.4</v>
       </c>
-      <c r="I45">
+      <c r="J45">
         <v>8.6999999999999993</v>
       </c>
-      <c r="J45" s="10">
+      <c r="K45" s="10">
         <f t="shared" si="0"/>
         <v>690</v>
       </c>
-      <c r="K45" s="10">
+      <c r="L45" s="10">
         <f t="shared" si="1"/>
         <v>250</v>
       </c>
-      <c r="L45" s="10">
+      <c r="M45" s="10">
         <f t="shared" si="2"/>
         <v>500</v>
       </c>
-      <c r="M45" s="10">
+      <c r="N45" s="10">
         <f t="shared" si="3"/>
         <v>1764.0000000000002</v>
       </c>
-      <c r="N45" s="10">
+      <c r="O45" s="10">
         <f t="shared" si="4"/>
         <v>3204</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A46">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>108</v>
+      </c>
+      <c r="B46">
         <v>9</v>
       </c>
-      <c r="B46" s="6">
+      <c r="C46" s="6">
         <v>10</v>
       </c>
-      <c r="C46" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="D46" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E46">
+        <v>55</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F46">
         <v>366</v>
       </c>
-      <c r="F46">
+      <c r="G46">
         <v>264</v>
       </c>
-      <c r="G46">
+      <c r="H46">
         <v>200</v>
       </c>
-      <c r="H46">
+      <c r="I46">
         <v>40</v>
       </c>
-      <c r="I46">
+      <c r="J46">
         <v>6.6</v>
       </c>
-      <c r="J46" s="10">
+      <c r="K46" s="10">
         <f t="shared" si="0"/>
         <v>1098</v>
       </c>
-      <c r="K46" s="10">
+      <c r="L46" s="10">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L46" s="10">
+      <c r="M46" s="10">
         <f t="shared" si="2"/>
         <v>500</v>
       </c>
-      <c r="M46" s="10">
+      <c r="N46" s="10">
         <f t="shared" si="3"/>
         <v>1493.3333333333335</v>
       </c>
-      <c r="N46" s="10">
+      <c r="O46" s="10">
         <f t="shared" si="4"/>
         <v>3091.3333333333335</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A47">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B47">
         <v>1</v>
       </c>
-      <c r="B47" s="6">
+      <c r="C47" s="6">
         <v>1</v>
       </c>
-      <c r="C47" s="6"/>
       <c r="D47" s="6"/>
-      <c r="E47">
-        <v>0</v>
-      </c>
+      <c r="E47" s="6"/>
       <c r="F47">
         <v>0</v>
       </c>
@@ -3413,22 +7181,23 @@
       <c r="I47">
         <v>0</v>
       </c>
-      <c r="N47" s="10">
+      <c r="J47">
+        <v>0</v>
+      </c>
+      <c r="O47" s="10">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A48">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B48">
         <v>2</v>
       </c>
-      <c r="B48" s="6">
+      <c r="C48" s="6">
         <v>2</v>
       </c>
-      <c r="C48" s="6"/>
       <c r="D48" s="6"/>
-      <c r="E48">
-        <v>0</v>
-      </c>
+      <c r="E48" s="6"/>
       <c r="F48">
         <v>0</v>
       </c>
@@ -3441,22 +7210,23 @@
       <c r="I48">
         <v>0</v>
       </c>
-      <c r="N48" s="10">
+      <c r="J48">
+        <v>0</v>
+      </c>
+      <c r="O48" s="10">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A49">
+    <row r="49" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B49">
         <v>3</v>
       </c>
-      <c r="B49" s="6">
+      <c r="C49" s="6">
         <v>3</v>
       </c>
-      <c r="C49" s="6"/>
       <c r="D49" s="6"/>
-      <c r="E49">
-        <v>0</v>
-      </c>
+      <c r="E49" s="6"/>
       <c r="F49">
         <v>0</v>
       </c>
@@ -3469,22 +7239,23 @@
       <c r="I49">
         <v>0</v>
       </c>
-      <c r="N49" s="10">
+      <c r="J49">
+        <v>0</v>
+      </c>
+      <c r="O49" s="10">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A50">
+    <row r="50" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B50">
         <v>4</v>
       </c>
-      <c r="B50" s="6">
+      <c r="C50" s="6">
         <v>4</v>
       </c>
-      <c r="C50" s="6"/>
       <c r="D50" s="6"/>
-      <c r="E50">
-        <v>0</v>
-      </c>
+      <c r="E50" s="6"/>
       <c r="F50">
         <v>0</v>
       </c>
@@ -3497,22 +7268,23 @@
       <c r="I50">
         <v>0</v>
       </c>
-      <c r="N50" s="10">
+      <c r="J50">
+        <v>0</v>
+      </c>
+      <c r="O50" s="10">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A51">
+    <row r="51" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B51">
         <v>5</v>
       </c>
-      <c r="B51" s="6">
+      <c r="C51" s="6">
         <v>5</v>
       </c>
-      <c r="C51" s="6"/>
       <c r="D51" s="6"/>
-      <c r="E51">
-        <v>0</v>
-      </c>
+      <c r="E51" s="6"/>
       <c r="F51">
         <v>0</v>
       </c>
@@ -3525,20 +7297,21 @@
       <c r="I51">
         <v>0</v>
       </c>
-      <c r="N51" s="10">
+      <c r="J51">
+        <v>0</v>
+      </c>
+      <c r="O51" s="10">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A52">
+    <row r="52" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B52">
         <v>6</v>
       </c>
-      <c r="B52" s="6">
+      <c r="C52" s="6">
         <v>6</v>
       </c>
-      <c r="E52">
-        <v>0</v>
-      </c>
       <c r="F52">
         <v>0</v>
       </c>
@@ -3551,20 +7324,21 @@
       <c r="I52">
         <v>0</v>
       </c>
-      <c r="N52" s="10">
+      <c r="J52">
+        <v>0</v>
+      </c>
+      <c r="O52" s="10">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A53">
+    <row r="53" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B53">
         <v>7</v>
       </c>
-      <c r="B53" s="6">
+      <c r="C53" s="6">
         <v>7</v>
       </c>
-      <c r="E53">
-        <v>0</v>
-      </c>
       <c r="F53">
         <v>0</v>
       </c>
@@ -3577,20 +7351,21 @@
       <c r="I53">
         <v>0</v>
       </c>
-      <c r="N53" s="10">
+      <c r="J53">
+        <v>0</v>
+      </c>
+      <c r="O53" s="10">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A54">
+    <row r="54" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B54">
         <v>8</v>
       </c>
-      <c r="B54" s="6">
+      <c r="C54" s="6">
         <v>8</v>
       </c>
-      <c r="E54">
-        <v>0</v>
-      </c>
       <c r="F54">
         <v>0</v>
       </c>
@@ -3603,20 +7378,21 @@
       <c r="I54">
         <v>0</v>
       </c>
-      <c r="N54" s="10">
+      <c r="J54">
+        <v>0</v>
+      </c>
+      <c r="O54" s="10">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A55">
+    <row r="55" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B55">
         <v>9</v>
       </c>
-      <c r="B55" s="6">
+      <c r="C55" s="6">
         <v>9</v>
       </c>
-      <c r="E55">
-        <v>0</v>
-      </c>
       <c r="F55">
         <v>0</v>
       </c>
@@ -3629,20 +7405,21 @@
       <c r="I55">
         <v>0</v>
       </c>
-      <c r="N55" s="10">
+      <c r="J55">
+        <v>0</v>
+      </c>
+      <c r="O55" s="10">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A56">
+    <row r="56" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B56">
         <v>10</v>
       </c>
-      <c r="B56" s="6">
+      <c r="C56" s="6">
         <v>10</v>
       </c>
-      <c r="E56">
-        <v>0</v>
-      </c>
       <c r="F56">
         <v>0</v>
       </c>
@@ -3655,12 +7432,16 @@
       <c r="I56">
         <v>0</v>
       </c>
-      <c r="N56" s="10">
+      <c r="J56">
+        <v>0</v>
+      </c>
+      <c r="O56" s="10">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="J2:J56">
+  <conditionalFormatting sqref="K2:K56">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -3672,7 +7453,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M56">
+  <conditionalFormatting sqref="N2:N56">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -3684,7 +7465,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N56">
+  <conditionalFormatting sqref="O2:O56">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -3697,8 +7478,10 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+  <drawing r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
--- a/inputData/Parameters.xlsx
+++ b/inputData/Parameters.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kapta\Documents\DTU\Speciale\GitHubFiles\inputData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D110A94-AF59-4DEE-B0A7-9701E8494890}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E4D3BF5-A5E6-40D6-9AAC-2AE2AB1E92BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="20" windowWidth="19180" windowHeight="11260" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
+    <workbookView xWindow="20" yWindow="110" windowWidth="19180" windowHeight="11260" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
   </bookViews>
   <sheets>
     <sheet name="Parameters" sheetId="9" r:id="rId1"/>
@@ -865,19 +865,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B15C49E0-A7B4-734A-8962-DC2A879F4079}">
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="22.58203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>20</v>
       </c>
@@ -888,7 +888,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -899,7 +899,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>42</v>
       </c>
@@ -910,7 +910,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -921,7 +921,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -932,7 +932,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -943,7 +943,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -955,7 +955,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
         <v>0</v>
       </c>
@@ -966,7 +966,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
         <v>1</v>
       </c>
@@ -977,7 +977,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
         <v>41</v>
       </c>
@@ -987,8 +987,12 @@
       <c r="D11" s="3">
         <v>0.8</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="H11">
+        <f>0.3*200</f>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
         <v>2</v>
       </c>
@@ -999,7 +1003,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
         <v>39</v>
       </c>
@@ -1010,7 +1014,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -1022,7 +1026,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
         <v>4</v>
       </c>
@@ -1033,7 +1037,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
         <v>5</v>
       </c>
@@ -1049,7 +1053,7 @@
         <v>6</v>
       </c>
       <c r="B17" s="4">
-        <v>780</v>
+        <v>120</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>14</v>

--- a/inputData/Parameters.xlsx
+++ b/inputData/Parameters.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kapta\Documents\DTU\Speciale\GitHubFiles\inputData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E4D3BF5-A5E6-40D6-9AAC-2AE2AB1E92BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{875C8D67-1E56-4772-89F1-C0D410A0D44C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="110" windowWidth="19180" windowHeight="11260" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
+    <workbookView xWindow="20" yWindow="740" windowWidth="19180" windowHeight="11260" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
   </bookViews>
   <sheets>
     <sheet name="Parameters" sheetId="9" r:id="rId1"/>
@@ -865,19 +865,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B15C49E0-A7B4-734A-8962-DC2A879F4079}">
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="22.58203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>20</v>
       </c>
@@ -888,7 +888,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -899,7 +899,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>42</v>
       </c>
@@ -910,7 +910,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -921,7 +921,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -932,7 +932,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -943,7 +943,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -955,7 +955,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
         <v>0</v>
       </c>
@@ -966,7 +966,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
         <v>1</v>
       </c>
@@ -977,7 +977,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
         <v>41</v>
       </c>
@@ -987,12 +987,8 @@
       <c r="D11" s="3">
         <v>0.8</v>
       </c>
-      <c r="H11">
-        <f>0.3*200</f>
-        <v>60</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
         <v>2</v>
       </c>
@@ -1003,7 +999,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
         <v>39</v>
       </c>
@@ -1014,7 +1010,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -1026,7 +1022,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
         <v>4</v>
       </c>
@@ -1037,7 +1033,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
         <v>5</v>
       </c>
